--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1315" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD2C1E3-D1A8-4596-A93E-26E11B274DD5}"/>
+  <xr:revisionPtr revIDLastSave="1412" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E95C25A-8713-4A22-B042-A81569C24A85}"/>
   <bookViews>
-    <workbookView xWindow="28845" yWindow="-1185" windowWidth="38505" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="77">
   <si>
     <t>Batch Data</t>
   </si>
@@ -117,12 +117,6 @@
   </si>
   <si>
     <t>Model Glucose Input Julia</t>
-  </si>
-  <si>
-    <t>Feed Rate (mL/hour) Python</t>
-  </si>
-  <si>
-    <t>Feed Rate (mL/hour) Julia</t>
   </si>
   <si>
     <t>Julia</t>
@@ -227,16 +221,10 @@
     <t>Amount of Glucose (mL) Julia</t>
   </si>
   <si>
-    <t>Feed Flow Rate based on CSFR (mL/hr)</t>
-  </si>
-  <si>
     <t>Feed Fed based on CSFR (mL)</t>
   </si>
   <si>
     <t>Online pH</t>
-  </si>
-  <si>
-    <t>Feed Flow Rate (mL/hr)</t>
   </si>
   <si>
     <t>Calculations</t>
@@ -246,9 +234,6 @@
   </si>
   <si>
     <t>MPC Data</t>
-  </si>
-  <si>
-    <t>Feed Rate based on CSFR (mL/hr)</t>
   </si>
   <si>
     <t>Flow Rates to Copy to System</t>
@@ -268,14 +253,33 @@
   <si>
     <t>Process Setpoints</t>
   </si>
+  <si>
+    <t>Feed Flow Rate based on CSFR (mL/min)</t>
+  </si>
+  <si>
+    <t>Feed Rate (mL/min) Python</t>
+  </si>
+  <si>
+    <t>Feed Rate (mL/min) Julia</t>
+  </si>
+  <si>
+    <t>Feed Rate based on CSFR (mL/min)</t>
+  </si>
+  <si>
+    <t>Pump RPM</t>
+  </si>
+  <si>
+    <t>Feed Flow Rate (mL/min)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -944,7 +948,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -1006,33 +1010,6 @@
     <xf numFmtId="165" fontId="0" fillId="39" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="39" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1069,7 +1046,47 @@
     <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1464,93 +1481,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI80"/>
+  <dimension ref="A1:BJ80"/>
   <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="10.6640625" customWidth="1"/>
     <col min="6" max="59" width="12.77734375" customWidth="1"/>
     <col min="60" max="60" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="16.21875" customWidth="1"/>
+    <col min="61" max="62" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61" t="s">
+    <row r="1" spans="1:62" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="63"/>
-      <c r="AB1" s="73" t="s">
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
+      <c r="W1" s="69"/>
+      <c r="X1" s="69"/>
+      <c r="Y1" s="69"/>
+      <c r="Z1" s="69"/>
+      <c r="AA1" s="70"/>
+      <c r="AB1" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="74"/>
-      <c r="AF1" s="74"/>
-      <c r="AG1" s="74"/>
-      <c r="AH1" s="74"/>
-      <c r="AI1" s="74"/>
-      <c r="AJ1" s="74"/>
-      <c r="AK1" s="74"/>
-      <c r="AL1" s="74"/>
-      <c r="AM1" s="74"/>
-      <c r="AN1" s="75"/>
-      <c r="AO1" s="68" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP1" s="68"/>
-      <c r="AQ1" s="68"/>
-      <c r="AR1" s="68"/>
-      <c r="AS1" s="69"/>
-      <c r="AT1" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="AU1" s="71"/>
-      <c r="AV1" s="72"/>
-      <c r="AW1" s="66" t="s">
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="65"/>
+      <c r="AG1" s="65"/>
+      <c r="AH1" s="65"/>
+      <c r="AI1" s="65"/>
+      <c r="AJ1" s="65"/>
+      <c r="AK1" s="65"/>
+      <c r="AL1" s="65"/>
+      <c r="AM1" s="65"/>
+      <c r="AN1" s="66"/>
+      <c r="AO1" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP1" s="59"/>
+      <c r="AQ1" s="59"/>
+      <c r="AR1" s="59"/>
+      <c r="AS1" s="60"/>
+      <c r="AT1" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU1" s="62"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="57" t="s">
+        <v>62</v>
+      </c>
+      <c r="AX1" s="58"/>
+      <c r="AY1" s="58"/>
+      <c r="AZ1" s="58"/>
+      <c r="BA1" s="58"/>
+      <c r="BB1" s="58"/>
+      <c r="BC1" s="58"/>
+      <c r="BD1" s="58"/>
+      <c r="BE1" s="58"/>
+      <c r="BF1" s="58"/>
+      <c r="BG1" s="58"/>
+      <c r="BH1" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="AX1" s="67"/>
-      <c r="AY1" s="67"/>
-      <c r="AZ1" s="67"/>
-      <c r="BA1" s="67"/>
-      <c r="BB1" s="67"/>
-      <c r="BC1" s="67"/>
-      <c r="BD1" s="67"/>
-      <c r="BE1" s="67"/>
-      <c r="BF1" s="67"/>
-      <c r="BG1" s="67"/>
-      <c r="BH1" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="BI1" s="65"/>
+      <c r="BI1" s="81"/>
+      <c r="BJ1" s="56"/>
     </row>
-    <row r="2" spans="1:61" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:62" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="36" t="s">
         <v>3</v>
       </c>
@@ -1566,107 +1584,107 @@
       <c r="E2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="56" t="s">
+      <c r="G2" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="75" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="59" t="s">
+      <c r="M2" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="57" t="s">
+      <c r="N2" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="57" t="s">
+      <c r="O2" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="57" t="s">
+      <c r="Q2" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="57" t="s">
+      <c r="R2" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="T2" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="57" t="s">
+      <c r="U2" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="R2" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" s="57" t="s">
-        <v>6</v>
-      </c>
-      <c r="T2" s="57" t="s">
+      <c r="V2" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="57" t="s">
+      <c r="W2" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="57" t="s">
+      <c r="X2" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="57" t="s">
+      <c r="Y2" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="X2" s="57" t="s">
+      <c r="Z2" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="57" t="s">
+      <c r="AA2" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="Z2" s="57" t="s">
+      <c r="AB2" s="41" t="s">
         <v>44</v>
-      </c>
-      <c r="AA2" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB2" s="41" t="s">
-        <v>46</v>
       </c>
       <c r="AC2" s="36" t="s">
         <v>20</v>
       </c>
       <c r="AD2" s="36" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AE2" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF2" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG2" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="AF2" s="36" t="s">
+      <c r="AH2" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="AG2" s="36" t="s">
+      <c r="AI2" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ2" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK2" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL2" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="AH2" s="36" t="s">
+      <c r="AM2" s="36" t="s">
         <v>50</v>
-      </c>
-      <c r="AI2" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ2" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK2" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL2" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM2" s="36" t="s">
-        <v>52</v>
       </c>
       <c r="AN2" s="24" t="s">
         <v>16</v>
@@ -1696,51 +1714,54 @@
         <v>25</v>
       </c>
       <c r="AW2" s="36" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="AX2" s="36" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AY2" s="36" t="s">
         <v>15</v>
       </c>
       <c r="AZ2" s="36" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="BA2" s="36" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="BB2" s="36" t="s">
         <v>17</v>
       </c>
       <c r="BC2" s="36" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="BD2" s="36" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="BE2" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="BF2" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="BG2" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH2" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI2" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="BJ2" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="BF2" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="BG2" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="BH2" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="BI2" s="24" t="s">
-        <v>74</v>
-      </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4">
         <v>12</v>
@@ -1752,7 +1773,9 @@
         <v>45449.560416666704</v>
       </c>
       <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
+      <c r="G3" s="10">
+        <v>127.2368</v>
+      </c>
       <c r="H3" s="10">
         <v>13.6</v>
       </c>
@@ -1871,11 +1894,12 @@
       <c r="AU3" s="16"/>
       <c r="AV3" s="42"/>
       <c r="AW3" s="15">
-        <f>AS3*I3*AY3*0.06</f>
-        <v>0.40945499999999996</v>
+        <f>AS3*I3*AY3/1000</f>
+        <v>6.8242499999999996E-3</v>
       </c>
       <c r="AX3" s="16">
-        <v>0</v>
+        <f>AW3*24</f>
+        <v>0.16378199999999998</v>
       </c>
       <c r="AY3" s="16">
         <f>AO3-AN3</f>
@@ -1894,14 +1918,14 @@
         <v>0</v>
       </c>
       <c r="BC3" s="17" t="str">
-        <f>IF(B3="Python",AT3*AO3/24,"")</f>
+        <f>IF(B3="Python",AT3*AO3/24/60,"")</f>
         <v/>
       </c>
       <c r="BD3" s="17" t="str">
-        <f t="shared" ref="BD3:BD34" si="0">IF(B3="Julia",AU3*AY3/24,"")</f>
-        <v/>
-      </c>
-      <c r="BE3" s="17">
+        <f>IF(B3="Julia",AU3*AY3/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE3" s="76">
         <f>IF(B3="No MPC", AS3*I3*AY3/1000,"")</f>
         <v>6.8242499999999996E-3</v>
       </c>
@@ -1909,24 +1933,28 @@
         <v>0</v>
       </c>
       <c r="BG3" s="17" t="str">
-        <f t="shared" ref="BG3:BG34" si="1">IF(B3="Julia",AV3*AY3,"")</f>
+        <f t="shared" ref="BG3:BG34" si="0">IF(B3="Julia",AV3*AY3,"")</f>
         <v/>
       </c>
       <c r="BH3" s="48">
+        <f>IF(BC3&lt;&gt;"",BC3/0.000385,IF(BD3&lt;&gt;"",BD3/0.000385,BE3/0.000385))</f>
+        <v>17.725324675324675</v>
+      </c>
+      <c r="BI3" s="85">
         <f>IF(BC3&lt;&gt;"",BC3,IF(BD3&lt;&gt;"",BD3,BE3))</f>
         <v>6.8242499999999996E-3</v>
       </c>
-      <c r="BI3" s="53">
+      <c r="BJ3" s="53">
         <f>IF(BF3&lt;&gt;"",BF3,BG3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="30">
         <v>12</v>
@@ -1938,7 +1966,9 @@
         <v>45449.564282407402</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="32"/>
+      <c r="G4" s="32">
+        <v>128.01390000000001</v>
+      </c>
       <c r="H4" s="32">
         <v>12.5</v>
       </c>
@@ -2020,13 +2050,13 @@
       <c r="AH4" s="33">
         <v>0.1</v>
       </c>
-      <c r="AI4" s="76">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="76">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="76">
+      <c r="AI4" s="33">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="33">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="33">
         <v>0</v>
       </c>
       <c r="AL4" s="33">
@@ -2053,66 +2083,73 @@
       <c r="AS4" s="33">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AT4" s="18"/>
+      <c r="AT4" s="18">
+        <v>4.4999999999999997E-3</v>
+      </c>
       <c r="AU4" s="33"/>
       <c r="AV4" s="43"/>
       <c r="AW4" s="18">
-        <f t="shared" ref="AW4:AW67" si="2">AS4*I4*AY4*0.06</f>
-        <v>0.37609199999999993</v>
+        <f t="shared" ref="AW4:AW67" si="1">AS4*I4*AY4/1000</f>
+        <v>6.2681999999999989E-3</v>
       </c>
       <c r="AX4" s="33">
-        <v>0</v>
+        <f t="shared" ref="AX4:AX8" si="2">AW4*24</f>
+        <v>0.15043679999999998</v>
       </c>
       <c r="AY4" s="33">
-        <f t="shared" ref="AY4:AY8" si="3">AO4-AN4</f>
+        <f>AO4-AN4</f>
         <v>1685</v>
       </c>
       <c r="AZ4" s="34">
-        <f t="shared" ref="AZ4:AZ67" si="4">IFERROR(AJ4/AY4,0)</f>
+        <f t="shared" ref="AZ4:AZ67" si="3">IFERROR(AJ4/AY4,0)</f>
         <v>0</v>
       </c>
       <c r="BA4" s="34">
-        <f t="shared" ref="BA4:BA34" si="5">AJ4/AO4</f>
+        <f t="shared" ref="BA3:BA34" si="4">AJ4/AO4</f>
         <v>0</v>
       </c>
       <c r="BB4" s="34">
-        <f t="shared" ref="BB4:BB34" si="6">AI4*24</f>
+        <f t="shared" ref="BB3:BB34" si="5">AI4*24</f>
         <v>0</v>
       </c>
       <c r="BC4" s="34">
-        <f>IF(B4="Python",AT4*AY4/24,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD4" s="34" t="str">
+        <f>IF(B4="Python",AT4*AO4/24/60,"")</f>
+        <v>5.3124999999999995E-3</v>
+      </c>
+      <c r="BD4" s="80" t="str">
+        <f>IF(B4="Julia",AU4*AY4/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE4" s="77" t="str">
+        <f t="shared" ref="BE4:BE67" si="6">IF(B4="No MPC", AS4*I4*AY4/1000,"")</f>
+        <v/>
+      </c>
+      <c r="BF4" s="34">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="BE4" s="34" t="str">
-        <f t="shared" ref="BE3:BE34" si="7">IF(B4="No MPC", AS4*I4*AY4*0.06,"")</f>
-        <v/>
-      </c>
-      <c r="BF4" s="34">
-        <v>0</v>
-      </c>
-      <c r="BG4" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
       <c r="BH4" s="49">
-        <f t="shared" ref="BH4:BH67" si="8">IF(BC4&lt;&gt;"",BC4,IF(BD4&lt;&gt;"",BD4,BE4))</f>
-        <v>0</v>
-      </c>
-      <c r="BI4" s="51">
-        <f t="shared" ref="BI4:BI67" si="9">IF(BF4&lt;&gt;"",BF4,BG4)</f>
+        <f t="shared" ref="BH4:BH67" si="7">IF(BC4&lt;&gt;"",BC4/0.000385,IF(BD4&lt;&gt;"",BD4/0.000385,BE4/0.000385))</f>
+        <v>13.798701298701298</v>
+      </c>
+      <c r="BI4" s="86">
+        <f t="shared" ref="BI4:BI67" si="8">IF(BC4&lt;&gt;"",BC4,IF(BD4&lt;&gt;"",BD4,BE4))</f>
+        <v>5.3124999999999995E-3</v>
+      </c>
+      <c r="BJ4" s="51">
+        <f t="shared" ref="BJ4:BJ67" si="9">IF(BF4&lt;&gt;"",BF4,BG4)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="30">
         <v>12</v>
@@ -2124,7 +2161,9 @@
         <v>45449.567604166703</v>
       </c>
       <c r="F5" s="11"/>
-      <c r="G5" s="32"/>
+      <c r="G5" s="32">
+        <v>131.52670000000001</v>
+      </c>
       <c r="H5" s="32">
         <v>13.5</v>
       </c>
@@ -2206,13 +2245,13 @@
       <c r="AH5" s="33">
         <v>0.1</v>
       </c>
-      <c r="AI5" s="76">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="76">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="76">
+      <c r="AI5" s="33">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="33">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="33">
         <v>0</v>
       </c>
       <c r="AL5" s="33">
@@ -2239,66 +2278,73 @@
       <c r="AS5" s="33">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AT5" s="18"/>
+      <c r="AT5" s="18">
+        <v>4.4999999999999997E-3</v>
+      </c>
       <c r="AU5" s="33"/>
       <c r="AV5" s="43"/>
       <c r="AW5" s="18">
+        <f t="shared" si="1"/>
+        <v>6.7231499999999998E-3</v>
+      </c>
+      <c r="AX5" s="33">
         <f t="shared" si="2"/>
-        <v>0.40338899999999994</v>
-      </c>
-      <c r="AX5" s="33">
-        <v>0</v>
+        <v>0.16135559999999999</v>
       </c>
       <c r="AY5" s="33">
+        <f t="shared" ref="AY4:AY8" si="10">AO5-AN5</f>
+        <v>1685</v>
+      </c>
+      <c r="AZ5" s="34">
         <f t="shared" si="3"/>
-        <v>1685</v>
-      </c>
-      <c r="AZ5" s="34">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA5" s="34">
+      <c r="BB5" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB5" s="34">
+      <c r="BC5" s="34">
+        <f>IF(B5="Python",AT5*AO5/24/60,"")</f>
+        <v>5.3124999999999995E-3</v>
+      </c>
+      <c r="BD5" s="80" t="str">
+        <f>IF(B5="Julia",AU5*AY5/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE5" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC5" s="34">
-        <f t="shared" ref="BC5:BC35" si="10">IF(B5="Python",AT5*AY5/24,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD5" s="34" t="str">
+        <v/>
+      </c>
+      <c r="BF5" s="34">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="BE5" s="34" t="str">
+      <c r="BH5" s="49">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="BF5" s="34">
-        <v>0</v>
-      </c>
-      <c r="BG5" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="BH5" s="49">
+        <v>13.798701298701298</v>
+      </c>
+      <c r="BI5" s="86">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BI5" s="51">
+        <v>5.3124999999999995E-3</v>
+      </c>
+      <c r="BJ5" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" s="30">
         <v>15</v>
@@ -2310,7 +2356,9 @@
         <v>45449.570925925902</v>
       </c>
       <c r="F6" s="11"/>
-      <c r="G6" s="32"/>
+      <c r="G6" s="32">
+        <v>162.4066</v>
+      </c>
       <c r="H6" s="32">
         <v>16.3</v>
       </c>
@@ -2392,13 +2440,13 @@
       <c r="AH6" s="33">
         <v>0.1</v>
       </c>
-      <c r="AI6" s="76">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="76">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="76">
+      <c r="AI6" s="33">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="33">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="33">
         <v>0</v>
       </c>
       <c r="AL6" s="33">
@@ -2429,62 +2477,67 @@
       <c r="AU6" s="33"/>
       <c r="AV6" s="43"/>
       <c r="AW6" s="18">
+        <f t="shared" si="1"/>
+        <v>8.1385499999999996E-3</v>
+      </c>
+      <c r="AX6" s="33">
         <f t="shared" si="2"/>
-        <v>0.488313</v>
-      </c>
-      <c r="AX6" s="33">
-        <v>0</v>
+        <v>0.19532519999999998</v>
       </c>
       <c r="AY6" s="33">
+        <f t="shared" si="10"/>
+        <v>1685</v>
+      </c>
+      <c r="AZ6" s="34">
         <f t="shared" si="3"/>
-        <v>1685</v>
-      </c>
-      <c r="AZ6" s="34">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA6" s="34">
+      <c r="BB6" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB6" s="34">
+      <c r="BC6" s="34" t="str">
+        <f>IF(B6="Python",AT6*AO6/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD6" s="80" t="str">
+        <f>IF(B6="Julia",AU6*AY6/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE6" s="77">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC6" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD6" s="34" t="str">
+        <v>8.1385499999999996E-3</v>
+      </c>
+      <c r="BF6" s="34">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="BE6" s="34">
+      <c r="BH6" s="49">
         <f t="shared" si="7"/>
-        <v>0.488313</v>
-      </c>
-      <c r="BF6" s="34">
-        <v>0</v>
-      </c>
-      <c r="BG6" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="BH6" s="49">
+        <v>21.13909090909091</v>
+      </c>
+      <c r="BI6" s="86">
         <f t="shared" si="8"/>
-        <v>0.488313</v>
-      </c>
-      <c r="BI6" s="51">
+        <v>8.1385499999999996E-3</v>
+      </c>
+      <c r="BJ6" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C7" s="30">
         <v>12</v>
@@ -2496,7 +2549,9 @@
         <v>45449.573888888903</v>
       </c>
       <c r="F7" s="11"/>
-      <c r="G7" s="32"/>
+      <c r="G7" s="32">
+        <v>115.47369999999999</v>
+      </c>
       <c r="H7" s="32">
         <v>12.2</v>
       </c>
@@ -2578,13 +2633,13 @@
       <c r="AH7" s="33">
         <v>0.1</v>
       </c>
-      <c r="AI7" s="76">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="76">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="76">
+      <c r="AI7" s="33">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="33">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="33">
         <v>0</v>
       </c>
       <c r="AL7" s="33">
@@ -2613,48 +2668,49 @@
       </c>
       <c r="AT7" s="18"/>
       <c r="AU7">
-        <v>8.8700831999999896E-3</v>
+        <v>5.22719999999999E-3</v>
       </c>
       <c r="AV7" s="43">
         <v>0</v>
       </c>
       <c r="AW7" s="18">
+        <f t="shared" si="1"/>
+        <v>6.1165499999999992E-3</v>
+      </c>
+      <c r="AX7" s="33">
         <f t="shared" si="2"/>
-        <v>0.36699299999999996</v>
-      </c>
-      <c r="AX7" s="33">
-        <v>0</v>
+        <v>0.14679719999999999</v>
       </c>
       <c r="AY7" s="33">
+        <f t="shared" si="10"/>
+        <v>1685</v>
+      </c>
+      <c r="AZ7" s="34">
         <f t="shared" si="3"/>
-        <v>1685</v>
-      </c>
-      <c r="AZ7" s="34">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA7" s="34">
+      <c r="BB7" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB7" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="BC7" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD7" s="34">
-        <f>IF(B7="Julia",AU7*AY7/24,"")</f>
-        <v>0.62275375799999921</v>
-      </c>
-      <c r="BE7" s="34" t="str">
-        <f t="shared" si="7"/>
+        <f>IF(B7="Python",AT7*AO7/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD7" s="79">
+        <f>IF(B7="Julia",AU7*AY7/24/60,"")</f>
+        <v>6.116549999999988E-3</v>
+      </c>
+      <c r="BE7" s="79" t="str">
+        <f>IF(B7="No MPC", AS7*I7*AY7/1000,"")</f>
         <v/>
       </c>
       <c r="BF7" s="34" t="str">
-        <f t="shared" ref="BF7:BF8" si="11">IF(IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, "")&lt;0,0,IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, ""))</f>
+        <f t="shared" ref="BF4:BF8" si="11">IF(IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, "")&lt;0,0,IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, ""))</f>
         <v/>
       </c>
       <c r="BG7" s="34">
@@ -2662,20 +2718,24 @@
         <v>0</v>
       </c>
       <c r="BH7" s="49">
+        <f t="shared" si="7"/>
+        <v>15.887142857142827</v>
+      </c>
+      <c r="BI7" s="86">
         <f t="shared" si="8"/>
-        <v>0.62275375799999921</v>
-      </c>
-      <c r="BI7" s="51">
+        <v>6.116549999999988E-3</v>
+      </c>
+      <c r="BJ7" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C8" s="7">
         <v>12</v>
@@ -2687,7 +2747,9 @@
         <v>45449.576921296299</v>
       </c>
       <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
+      <c r="G8" s="14">
+        <v>122.6279</v>
+      </c>
       <c r="H8" s="14">
         <v>13</v>
       </c>
@@ -2804,44 +2866,45 @@
       </c>
       <c r="AT8" s="19"/>
       <c r="AU8">
-        <v>9.4517279999999908E-3</v>
+        <v>5.5727999999999897E-3</v>
       </c>
       <c r="AV8" s="44">
         <v>0</v>
       </c>
       <c r="AW8" s="19">
+        <f t="shared" si="1"/>
+        <v>6.5209499999999993E-3</v>
+      </c>
+      <c r="AX8" s="20">
         <f t="shared" si="2"/>
-        <v>0.39125699999999991</v>
-      </c>
-      <c r="AX8" s="20">
-        <v>0</v>
+        <v>0.1565028</v>
       </c>
       <c r="AY8" s="20">
+        <f t="shared" si="10"/>
+        <v>1685</v>
+      </c>
+      <c r="AZ8" s="21">
         <f t="shared" si="3"/>
-        <v>1685</v>
-      </c>
-      <c r="AZ8" s="21">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA8" s="21">
+      <c r="BB8" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB8" s="21">
+      <c r="BC8" s="21" t="str">
+        <f>IF(B8="Python",AT8*AO8/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD8" s="79">
+        <f>IF(B8="Julia",AU8*AY8/24/60,"")</f>
+        <v>6.520949999999988E-3</v>
+      </c>
+      <c r="BE8" s="78" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC8" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD8" s="21">
-        <f t="shared" si="0"/>
-        <v>0.66359006999999937</v>
-      </c>
-      <c r="BE8" s="21" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF8" s="21" t="str">
@@ -2849,24 +2912,28 @@
         <v/>
       </c>
       <c r="BG8" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BH8" s="50">
+        <f t="shared" si="7"/>
+        <v>16.937532467532439</v>
+      </c>
+      <c r="BI8" s="87">
         <f t="shared" si="8"/>
-        <v>0.66359006999999937</v>
-      </c>
-      <c r="BI8" s="52">
+        <v>6.520949999999988E-3</v>
+      </c>
+      <c r="BJ8" s="52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
@@ -2931,39 +2998,39 @@
       <c r="AU9" s="16"/>
       <c r="AV9" s="42"/>
       <c r="AW9" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX9" s="16">
         <f t="shared" ref="AX9:AX40" si="12">AW3*24</f>
-        <v>9.8269199999999994</v>
+        <v>0.16378199999999998</v>
       </c>
       <c r="AY9" s="16">
         <f>AY3+SUM(AF9:AH9,AL9:AM9)-AN9</f>
         <v>1670</v>
       </c>
       <c r="AZ9" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA9" s="17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA9" s="17">
+      <c r="BB9" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB9" s="17">
+      <c r="BC9" s="17" t="str">
+        <f>IF(B9="Python",AT9*AO9/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD9" s="17" t="str">
+        <f>IF(B9="Julia",AU9*AY9/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE9" s="76">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC9" s="17" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD9" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE9" s="17">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BF9" s="17">
@@ -2971,24 +3038,28 @@
         <v>20.875</v>
       </c>
       <c r="BG9" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH9" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI9" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI9" s="51">
+      <c r="BJ9" s="51">
         <f t="shared" si="9"/>
         <v>20.875</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="30">
         <v>12</v>
@@ -3036,39 +3107,39 @@
       <c r="AU10" s="33"/>
       <c r="AV10" s="43"/>
       <c r="AW10" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX10" s="33">
         <f t="shared" si="12"/>
-        <v>9.0262079999999987</v>
+        <v>0.15043679999999998</v>
       </c>
       <c r="AY10" s="33">
-        <f t="shared" ref="AY10:AY40" si="13">AY4+SUM(AF10:AH10,AL10:AM10)-AN10</f>
+        <f t="shared" ref="AY9:AY40" si="13">AY4+SUM(AF10:AH10,AL10:AM10)-AN10</f>
         <v>1670</v>
       </c>
       <c r="AZ10" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA10" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA10" s="34">
+      <c r="BB10" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB10" s="34">
+      <c r="BC10" s="34">
+        <f>IF(B10="Python",AT10*AO10/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD10" s="80" t="str">
+        <f>IF(B10="Julia",AU10*AY10/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE10" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC10" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD10" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE10" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF10" s="34">
@@ -3076,24 +3147,28 @@
         <v>20.875</v>
       </c>
       <c r="BG10" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH10" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI10" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI10" s="51">
+      <c r="BJ10" s="51">
         <f t="shared" si="9"/>
         <v>20.875</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="30">
         <v>12</v>
@@ -3142,39 +3217,39 @@
       <c r="AU11" s="33"/>
       <c r="AV11" s="43"/>
       <c r="AW11" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX11" s="33">
         <f t="shared" si="12"/>
-        <v>9.6813359999999982</v>
+        <v>0.16135559999999999</v>
       </c>
       <c r="AY11" s="33">
         <f t="shared" si="13"/>
         <v>1670</v>
       </c>
       <c r="AZ11" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA11" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA11" s="34">
+      <c r="BB11" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB11" s="34">
+      <c r="BC11" s="34">
+        <f>IF(B11="Python",AT11*AO11/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD11" s="80" t="str">
+        <f>IF(B11="Julia",AU11*AY11/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE11" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC11" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD11" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE11" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF11" s="34">
@@ -3182,24 +3257,28 @@
         <v>20.875</v>
       </c>
       <c r="BG11" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH11" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI11" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI11" s="51">
+      <c r="BJ11" s="51">
         <f t="shared" si="9"/>
         <v>20.875</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" s="30">
         <v>15</v>
@@ -3248,39 +3327,39 @@
       <c r="AU12" s="33"/>
       <c r="AV12" s="43"/>
       <c r="AW12" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX12" s="33">
         <f t="shared" si="12"/>
-        <v>11.719512</v>
+        <v>0.19532519999999998</v>
       </c>
       <c r="AY12" s="33">
         <f t="shared" si="13"/>
         <v>1670</v>
       </c>
       <c r="AZ12" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA12" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA12" s="34">
+      <c r="BB12" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB12" s="34">
+      <c r="BC12" s="34" t="str">
+        <f>IF(B12="Python",AT12*AO12/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD12" s="80" t="str">
+        <f>IF(B12="Julia",AU12*AY12/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE12" s="77">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC12" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD12" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE12" s="34">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BF12" s="34">
@@ -3288,24 +3367,28 @@
         <v>20.875</v>
       </c>
       <c r="BG12" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH12" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI12" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI12" s="51">
+      <c r="BJ12" s="51">
         <f t="shared" si="9"/>
         <v>20.875</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" s="30">
         <v>12</v>
@@ -3370,64 +3453,68 @@
       <c r="AU13" s="33"/>
       <c r="AV13" s="43"/>
       <c r="AW13" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX13" s="33">
         <f t="shared" si="12"/>
-        <v>8.8078319999999994</v>
+        <v>0.14679719999999999</v>
       </c>
       <c r="AY13" s="33">
         <f t="shared" si="13"/>
         <v>1670</v>
       </c>
       <c r="AZ13" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA13" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA13" s="34">
+      <c r="BB13" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB13" s="34">
+      <c r="BC13" s="34" t="str">
+        <f>IF(B13="Python",AT13*AO13/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD13" s="80">
+        <f>IF(B13="Julia",AU13*AY13/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE13" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC13" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD13" s="34">
+        <v/>
+      </c>
+      <c r="BF13" s="34" t="str">
+        <f t="shared" ref="BF10:BF73" si="15">IF(O13&lt;1.5, IF(B13&lt;&gt;"Julia",((3-O13)*AY13)/400, ""),0)</f>
+        <v/>
+      </c>
+      <c r="BG13" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE13" s="34" t="str">
+      <c r="BH13" s="49">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="BF13" s="34" t="str">
-        <f t="shared" ref="BF13:BF73" si="15">IF(O13&lt;1.5, IF(B13&lt;&gt;"Julia",((3-O13)*AY13)/400, ""),0)</f>
-        <v/>
-      </c>
-      <c r="BG13" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BH13" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI13" s="51">
+      <c r="BJ13" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="7">
         <v>12</v>
@@ -3492,39 +3579,39 @@
       <c r="AU14" s="20"/>
       <c r="AV14" s="44"/>
       <c r="AW14" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX14" s="20">
         <f t="shared" si="12"/>
-        <v>9.3901679999999974</v>
+        <v>0.1565028</v>
       </c>
       <c r="AY14" s="20">
         <f t="shared" si="13"/>
         <v>1670</v>
       </c>
       <c r="AZ14" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA14" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA14" s="21">
+      <c r="BB14" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB14" s="21">
+      <c r="BC14" s="21" t="str">
+        <f>IF(B14="Python",AT14*AO14/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD14" s="21">
+        <f>IF(B14="Julia",AU14*AY14/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE14" s="78" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC14" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD14" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BE14" s="21" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF14" s="21" t="str">
@@ -3532,24 +3619,28 @@
         <v/>
       </c>
       <c r="BG14" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BH14" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI14" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI14" s="51">
+      <c r="BJ14" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" s="4">
         <v>12</v>
@@ -3614,7 +3705,7 @@
       <c r="AU15" s="16"/>
       <c r="AV15" s="42"/>
       <c r="AW15" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX15" s="16">
@@ -3626,27 +3717,27 @@
         <v>1655</v>
       </c>
       <c r="AZ15" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA15" s="17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA15" s="17">
+      <c r="BB15" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB15" s="17">
+      <c r="BC15" s="17" t="str">
+        <f>IF(B15="Python",AT15*AO15/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD15" s="17" t="str">
+        <f>IF(B15="Julia",AU15*AY15/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE15" s="76">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC15" s="17" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD15" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE15" s="17">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BF15" s="17">
@@ -3654,24 +3745,28 @@
         <v>12.4125</v>
       </c>
       <c r="BG15" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH15" s="48">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI15" s="85">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI15" s="53">
+      <c r="BJ15" s="53">
         <f t="shared" si="9"/>
         <v>12.4125</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="30">
         <v>12</v>
@@ -3736,7 +3831,7 @@
       <c r="AU16" s="33"/>
       <c r="AV16" s="43"/>
       <c r="AW16" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX16" s="33">
@@ -3748,27 +3843,27 @@
         <v>1655</v>
       </c>
       <c r="AZ16" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA16" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA16" s="34">
+      <c r="BB16" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB16" s="34">
+      <c r="BC16" s="34">
+        <f>IF(B16="Python",AT16*AO16/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD16" s="80" t="str">
+        <f>IF(B16="Julia",AU16*AY16/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE16" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC16" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD16" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE16" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF16" s="34">
@@ -3776,24 +3871,28 @@
         <v>12.4125</v>
       </c>
       <c r="BG16" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH16" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI16" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI16" s="51">
+      <c r="BJ16" s="51">
         <f t="shared" si="9"/>
         <v>12.4125</v>
       </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C17" s="30">
         <v>12</v>
@@ -3858,7 +3957,7 @@
       <c r="AU17" s="33"/>
       <c r="AV17" s="43"/>
       <c r="AW17" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX17" s="33">
@@ -3870,27 +3969,27 @@
         <v>1655</v>
       </c>
       <c r="AZ17" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA17" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA17" s="34">
+      <c r="BB17" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB17" s="34">
+      <c r="BC17" s="34">
+        <f>IF(B17="Python",AT17*AO17/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD17" s="80" t="str">
+        <f>IF(B17="Julia",AU17*AY17/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE17" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC17" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD17" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE17" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF17" s="34">
@@ -3898,24 +3997,28 @@
         <v>12.4125</v>
       </c>
       <c r="BG17" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH17" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI17" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI17" s="51">
+      <c r="BJ17" s="51">
         <f t="shared" si="9"/>
         <v>12.4125</v>
       </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C18" s="30">
         <v>15</v>
@@ -3980,7 +4083,7 @@
       <c r="AU18" s="33"/>
       <c r="AV18" s="43"/>
       <c r="AW18" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX18" s="33">
@@ -3992,27 +4095,27 @@
         <v>1655</v>
       </c>
       <c r="AZ18" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA18" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA18" s="34">
+      <c r="BB18" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB18" s="34">
+      <c r="BC18" s="34" t="str">
+        <f>IF(B18="Python",AT18*AO18/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD18" s="80" t="str">
+        <f>IF(B18="Julia",AU18*AY18/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE18" s="77">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC18" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD18" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE18" s="34">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BF18" s="34">
@@ -4020,24 +4123,28 @@
         <v>12.4125</v>
       </c>
       <c r="BG18" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH18" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI18" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI18" s="51">
+      <c r="BJ18" s="51">
         <f t="shared" si="9"/>
         <v>12.4125</v>
       </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" s="30">
         <v>12</v>
@@ -4102,7 +4209,7 @@
       <c r="AU19" s="33"/>
       <c r="AV19" s="43"/>
       <c r="AW19" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX19" s="33">
@@ -4114,27 +4221,27 @@
         <v>1655</v>
       </c>
       <c r="AZ19" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA19" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA19" s="34">
+      <c r="BB19" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB19" s="34">
+      <c r="BC19" s="34" t="str">
+        <f>IF(B19="Python",AT19*AO19/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD19" s="80">
+        <f>IF(B19="Julia",AU19*AY19/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE19" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC19" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD19" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BE19" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF19" s="34" t="str">
@@ -4142,24 +4249,28 @@
         <v/>
       </c>
       <c r="BG19" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BH19" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI19" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI19" s="51">
+      <c r="BJ19" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" s="7">
         <v>12</v>
@@ -4224,7 +4335,7 @@
       <c r="AU20" s="20"/>
       <c r="AV20" s="44"/>
       <c r="AW20" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX20" s="20">
@@ -4236,27 +4347,27 @@
         <v>1655</v>
       </c>
       <c r="AZ20" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA20" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA20" s="21">
+      <c r="BB20" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB20" s="21">
+      <c r="BC20" s="21" t="str">
+        <f>IF(B20="Python",AT20*AO20/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD20" s="21">
+        <f>IF(B20="Julia",AU20*AY20/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE20" s="78" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC20" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD20" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BE20" s="21" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF20" s="21" t="str">
@@ -4264,24 +4375,28 @@
         <v/>
       </c>
       <c r="BG20" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BH20" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI20" s="87">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI20" s="52">
+      <c r="BJ20" s="52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" s="4">
         <v>12</v>
@@ -4346,7 +4461,7 @@
       <c r="AU21" s="16"/>
       <c r="AV21" s="42"/>
       <c r="AW21" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX21" s="16">
@@ -4358,27 +4473,27 @@
         <v>1640</v>
       </c>
       <c r="AZ21" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA21" s="17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA21" s="17">
+      <c r="BB21" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB21" s="17">
+      <c r="BC21" s="17" t="str">
+        <f>IF(B21="Python",AT21*AO21/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD21" s="17" t="str">
+        <f>IF(B21="Julia",AU21*AY21/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE21" s="76">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC21" s="17" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD21" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE21" s="17">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BF21" s="17">
@@ -4386,24 +4501,28 @@
         <v>12.3</v>
       </c>
       <c r="BG21" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH21" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI21" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI21" s="51">
+      <c r="BJ21" s="51">
         <f t="shared" si="9"/>
         <v>12.3</v>
       </c>
     </row>
-    <row r="22" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="30">
         <v>12</v>
@@ -4468,7 +4587,7 @@
       <c r="AU22" s="33"/>
       <c r="AV22" s="43"/>
       <c r="AW22" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX22" s="33">
@@ -4480,27 +4599,27 @@
         <v>1640</v>
       </c>
       <c r="AZ22" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA22" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA22" s="34">
+      <c r="BB22" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB22" s="34">
+      <c r="BC22" s="34">
+        <f>IF(B22="Python",AT22*AO22/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD22" s="80" t="str">
+        <f>IF(B22="Julia",AU22*AY22/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE22" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC22" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD22" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE22" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF22" s="34">
@@ -4508,24 +4627,28 @@
         <v>12.3</v>
       </c>
       <c r="BG22" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH22" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI22" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI22" s="51">
+      <c r="BJ22" s="51">
         <f t="shared" si="9"/>
         <v>12.3</v>
       </c>
     </row>
-    <row r="23" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C23" s="30">
         <v>12</v>
@@ -4590,7 +4713,7 @@
       <c r="AU23" s="33"/>
       <c r="AV23" s="43"/>
       <c r="AW23" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX23" s="33">
@@ -4602,27 +4725,27 @@
         <v>1640</v>
       </c>
       <c r="AZ23" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA23" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA23" s="34">
+      <c r="BB23" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB23" s="34">
+      <c r="BC23" s="34">
+        <f>IF(B23="Python",AT23*AO23/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD23" s="80" t="str">
+        <f>IF(B23="Julia",AU23*AY23/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE23" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC23" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD23" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE23" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF23" s="34">
@@ -4630,24 +4753,28 @@
         <v>12.3</v>
       </c>
       <c r="BG23" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH23" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI23" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI23" s="51">
+      <c r="BJ23" s="51">
         <f t="shared" si="9"/>
         <v>12.3</v>
       </c>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C24" s="30">
         <v>15</v>
@@ -4712,7 +4839,7 @@
       <c r="AU24" s="33"/>
       <c r="AV24" s="43"/>
       <c r="AW24" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX24" s="33">
@@ -4724,27 +4851,27 @@
         <v>1640</v>
       </c>
       <c r="AZ24" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA24" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA24" s="34">
+      <c r="BB24" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB24" s="34">
+      <c r="BC24" s="34" t="str">
+        <f>IF(B24="Python",AT24*AO24/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD24" s="80" t="str">
+        <f>IF(B24="Julia",AU24*AY24/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE24" s="77">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC24" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD24" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE24" s="34">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BF24" s="34">
@@ -4752,24 +4879,28 @@
         <v>12.3</v>
       </c>
       <c r="BG24" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH24" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI24" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI24" s="51">
+      <c r="BJ24" s="51">
         <f t="shared" si="9"/>
         <v>12.3</v>
       </c>
     </row>
-    <row r="25" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="30">
         <v>12</v>
@@ -4834,7 +4965,7 @@
       <c r="AU25" s="33"/>
       <c r="AV25" s="43"/>
       <c r="AW25" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX25" s="33">
@@ -4846,27 +4977,27 @@
         <v>1640</v>
       </c>
       <c r="AZ25" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA25" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA25" s="34">
+      <c r="BB25" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB25" s="34">
+      <c r="BC25" s="34" t="str">
+        <f>IF(B25="Python",AT25*AO25/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD25" s="80">
+        <f>IF(B25="Julia",AU25*AY25/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE25" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC25" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD25" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BE25" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF25" s="34" t="str">
@@ -4874,24 +5005,28 @@
         <v/>
       </c>
       <c r="BG25" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BH25" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI25" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI25" s="51">
+      <c r="BJ25" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C26" s="7">
         <v>12</v>
@@ -4956,7 +5091,7 @@
       <c r="AU26" s="20"/>
       <c r="AV26" s="44"/>
       <c r="AW26" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX26" s="20">
@@ -4968,27 +5103,27 @@
         <v>1640</v>
       </c>
       <c r="AZ26" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA26" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA26" s="21">
+      <c r="BB26" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB26" s="21">
+      <c r="BC26" s="21" t="str">
+        <f>IF(B26="Python",AT26*AO26/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD26" s="21">
+        <f>IF(B26="Julia",AU26*AY26/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE26" s="78" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC26" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD26" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BE26" s="21" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF26" s="21" t="str">
@@ -4996,24 +5131,28 @@
         <v/>
       </c>
       <c r="BG26" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BH26" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI26" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI26" s="51">
+      <c r="BJ26" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4">
         <v>12</v>
@@ -5078,7 +5217,7 @@
       <c r="AU27" s="16"/>
       <c r="AV27" s="42"/>
       <c r="AW27" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX27" s="16">
@@ -5090,27 +5229,27 @@
         <v>1625</v>
       </c>
       <c r="AZ27" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA27" s="17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA27" s="17">
+      <c r="BB27" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB27" s="17">
+      <c r="BC27" s="17" t="str">
+        <f>IF(B27="Python",AT27*AO27/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD27" s="17" t="str">
+        <f>IF(B27="Julia",AU27*AY27/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE27" s="76">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC27" s="17" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD27" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE27" s="17">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BF27" s="17">
@@ -5118,24 +5257,28 @@
         <v>12.1875</v>
       </c>
       <c r="BG27" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH27" s="48">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI27" s="85">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI27" s="53">
+      <c r="BJ27" s="53">
         <f t="shared" si="9"/>
         <v>12.1875</v>
       </c>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C28" s="30">
         <v>12</v>
@@ -5200,7 +5343,7 @@
       <c r="AU28" s="33"/>
       <c r="AV28" s="43"/>
       <c r="AW28" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX28" s="33">
@@ -5212,27 +5355,27 @@
         <v>1625</v>
       </c>
       <c r="AZ28" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA28" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA28" s="34">
+      <c r="BB28" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB28" s="34">
+      <c r="BC28" s="34">
+        <f>IF(B28="Python",AT28*AO28/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD28" s="80" t="str">
+        <f>IF(B28="Julia",AU28*AY28/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE28" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC28" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD28" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE28" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF28" s="34">
@@ -5240,24 +5383,28 @@
         <v>12.1875</v>
       </c>
       <c r="BG28" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH28" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI28" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI28" s="51">
+      <c r="BJ28" s="51">
         <f t="shared" si="9"/>
         <v>12.1875</v>
       </c>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C29" s="30">
         <v>12</v>
@@ -5322,7 +5469,7 @@
       <c r="AU29" s="33"/>
       <c r="AV29" s="43"/>
       <c r="AW29" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX29" s="33">
@@ -5334,27 +5481,27 @@
         <v>1625</v>
       </c>
       <c r="AZ29" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA29" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA29" s="34">
+      <c r="BB29" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB29" s="34">
+      <c r="BC29" s="34">
+        <f>IF(B29="Python",AT29*AO29/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD29" s="80" t="str">
+        <f>IF(B29="Julia",AU29*AY29/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE29" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC29" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD29" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE29" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF29" s="34">
@@ -5362,24 +5509,28 @@
         <v>12.1875</v>
       </c>
       <c r="BG29" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH29" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI29" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI29" s="51">
+      <c r="BJ29" s="51">
         <f t="shared" si="9"/>
         <v>12.1875</v>
       </c>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C30" s="30">
         <v>15</v>
@@ -5444,7 +5595,7 @@
       <c r="AU30" s="33"/>
       <c r="AV30" s="43"/>
       <c r="AW30" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX30" s="33">
@@ -5456,27 +5607,27 @@
         <v>1625</v>
       </c>
       <c r="AZ30" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA30" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA30" s="34">
+      <c r="BB30" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB30" s="34">
+      <c r="BC30" s="34" t="str">
+        <f>IF(B30="Python",AT30*AO30/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD30" s="80" t="str">
+        <f>IF(B30="Julia",AU30*AY30/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE30" s="77">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC30" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD30" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE30" s="34">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BF30" s="34">
@@ -5484,24 +5635,28 @@
         <v>12.1875</v>
       </c>
       <c r="BG30" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH30" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI30" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI30" s="51">
+      <c r="BJ30" s="51">
         <f t="shared" si="9"/>
         <v>12.1875</v>
       </c>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C31" s="30">
         <v>12</v>
@@ -5566,7 +5721,7 @@
       <c r="AU31" s="33"/>
       <c r="AV31" s="43"/>
       <c r="AW31" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX31" s="33">
@@ -5578,27 +5733,27 @@
         <v>1625</v>
       </c>
       <c r="AZ31" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA31" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA31" s="34">
+      <c r="BB31" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB31" s="34">
+      <c r="BC31" s="34" t="str">
+        <f>IF(B31="Python",AT31*AO31/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD31" s="80">
+        <f>IF(B31="Julia",AU31*AY31/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE31" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC31" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD31" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BE31" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF31" s="34" t="str">
@@ -5606,24 +5761,28 @@
         <v/>
       </c>
       <c r="BG31" s="34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BH31" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI31" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI31" s="51">
+      <c r="BJ31" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C32" s="7">
         <v>12</v>
@@ -5688,7 +5847,7 @@
       <c r="AU32" s="20"/>
       <c r="AV32" s="44"/>
       <c r="AW32" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX32" s="20">
@@ -5700,27 +5859,27 @@
         <v>1625</v>
       </c>
       <c r="AZ32" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA32" s="21">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA32" s="21">
+      <c r="BB32" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB32" s="21">
+      <c r="BC32" s="21" t="str">
+        <f>IF(B32="Python",AT32*AO32/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD32" s="21">
+        <f>IF(B32="Julia",AU32*AY32/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE32" s="78" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC32" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD32" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BE32" s="21" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF32" s="21" t="str">
@@ -5728,24 +5887,28 @@
         <v/>
       </c>
       <c r="BG32" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BH32" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI32" s="87">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI32" s="52">
+      <c r="BJ32" s="52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C33" s="4">
         <v>12</v>
@@ -5810,7 +5973,7 @@
       <c r="AU33" s="16"/>
       <c r="AV33" s="42"/>
       <c r="AW33" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX33" s="16">
@@ -5822,27 +5985,27 @@
         <v>1610</v>
       </c>
       <c r="AZ33" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA33" s="17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA33" s="17">
+      <c r="BB33" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB33" s="17">
+      <c r="BC33" s="17" t="str">
+        <f>IF(B33="Python",AT33*AO33/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD33" s="17" t="str">
+        <f>IF(B33="Julia",AU33*AY33/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE33" s="76">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC33" s="17" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="BD33" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE33" s="17">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BF33" s="17">
@@ -5850,24 +6013,28 @@
         <v>12.074999999999999</v>
       </c>
       <c r="BG33" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH33" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI33" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI33" s="51">
+      <c r="BJ33" s="51">
         <f t="shared" si="9"/>
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C34" s="30">
         <v>12</v>
@@ -5932,7 +6099,7 @@
       <c r="AU34" s="33"/>
       <c r="AV34" s="43"/>
       <c r="AW34" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX34" s="33">
@@ -5944,27 +6111,27 @@
         <v>1610</v>
       </c>
       <c r="AZ34" s="34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA34" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA34" s="34">
+      <c r="BB34" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB34" s="34">
+      <c r="BC34" s="34">
+        <f>IF(B34="Python",AT34*AO34/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD34" s="80" t="str">
+        <f>IF(B34="Julia",AU34*AY34/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE34" s="77" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC34" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD34" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BE34" s="34" t="str">
-        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="BF34" s="34">
@@ -5972,24 +6139,28 @@
         <v>12.074999999999999</v>
       </c>
       <c r="BG34" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BH34" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI34" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI34" s="51">
+      <c r="BJ34" s="51">
         <f t="shared" si="9"/>
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C35" s="30">
         <v>12</v>
@@ -6054,7 +6225,7 @@
       <c r="AU35" s="33"/>
       <c r="AV35" s="43"/>
       <c r="AW35" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX35" s="33">
@@ -6066,7 +6237,7 @@
         <v>1610</v>
       </c>
       <c r="AZ35" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA35" s="34">
@@ -6078,15 +6249,15 @@
         <v>0</v>
       </c>
       <c r="BC35" s="34">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BD35" s="34" t="str">
-        <f t="shared" ref="BD35:BD66" si="18">IF(B35="Julia",AU35*AY35/24,"")</f>
-        <v/>
-      </c>
-      <c r="BE35" s="34" t="str">
-        <f t="shared" ref="BE35:BE66" si="19">IF(B35="No MPC", AS35*I35*AY35*0.06,"")</f>
+        <f>IF(B35="Python",AT35*AO35/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD35" s="80" t="str">
+        <f>IF(B35="Julia",AU35*AY35/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE35" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF35" s="34">
@@ -6094,24 +6265,28 @@
         <v>12.074999999999999</v>
       </c>
       <c r="BG35" s="34" t="str">
-        <f t="shared" ref="BG35:BG66" si="20">IF(B35="Julia",AV35*AY35,"")</f>
+        <f t="shared" ref="BG35:BG66" si="18">IF(B35="Julia",AV35*AY35,"")</f>
         <v/>
       </c>
       <c r="BH35" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI35" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI35" s="51">
+      <c r="BJ35" s="51">
         <f t="shared" si="9"/>
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C36" s="30">
         <v>15</v>
@@ -6176,7 +6351,7 @@
       <c r="AU36" s="33"/>
       <c r="AV36" s="43"/>
       <c r="AW36" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX36" s="33">
@@ -6188,7 +6363,7 @@
         <v>1610</v>
       </c>
       <c r="AZ36" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA36" s="34">
@@ -6200,15 +6375,15 @@
         <v>0</v>
       </c>
       <c r="BC36" s="34" t="str">
-        <f t="shared" ref="BC36:BC67" si="21">IF(B36="Python",AT36*AY36/24,"")</f>
-        <v/>
-      </c>
-      <c r="BD36" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE36" s="34">
-        <f t="shared" si="19"/>
+        <f>IF(B36="Python",AT36*AO36/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD36" s="80" t="str">
+        <f>IF(B36="Julia",AU36*AY36/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE36" s="77">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF36" s="34">
@@ -6216,24 +6391,28 @@
         <v>12.074999999999999</v>
       </c>
       <c r="BG36" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH36" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI36" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI36" s="51">
+      <c r="BJ36" s="51">
         <f t="shared" si="9"/>
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C37" s="30">
         <v>12</v>
@@ -6298,7 +6477,7 @@
       <c r="AU37" s="33"/>
       <c r="AV37" s="43"/>
       <c r="AW37" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX37" s="33">
@@ -6310,7 +6489,7 @@
         <v>1610</v>
       </c>
       <c r="AZ37" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA37" s="34">
@@ -6322,15 +6501,15 @@
         <v>0</v>
       </c>
       <c r="BC37" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD37" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE37" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B37="Python",AT37*AO37/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD37" s="80">
+        <f>IF(B37="Julia",AU37*AY37/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE37" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF37" s="34" t="str">
@@ -6338,24 +6517,28 @@
         <v/>
       </c>
       <c r="BG37" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH37" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI37" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI37" s="51">
+      <c r="BJ37" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C38" s="7">
         <v>12</v>
@@ -6420,7 +6603,7 @@
       <c r="AU38" s="20"/>
       <c r="AV38" s="44"/>
       <c r="AW38" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX38" s="20">
@@ -6432,7 +6615,7 @@
         <v>1610</v>
       </c>
       <c r="AZ38" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA38" s="21">
@@ -6444,15 +6627,15 @@
         <v>0</v>
       </c>
       <c r="BC38" s="21" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B38="Python",AT38*AO38/24/60,"")</f>
         <v/>
       </c>
       <c r="BD38" s="21">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE38" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B38="Julia",AU38*AY38/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE38" s="78" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF38" s="21" t="str">
@@ -6460,24 +6643,28 @@
         <v/>
       </c>
       <c r="BG38" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH38" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI38" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI38" s="51">
+      <c r="BJ38" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C39" s="4">
         <v>12</v>
@@ -6542,7 +6729,7 @@
       <c r="AU39" s="16"/>
       <c r="AV39" s="42"/>
       <c r="AW39" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX39" s="16">
@@ -6554,7 +6741,7 @@
         <v>1595</v>
       </c>
       <c r="AZ39" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA39" s="17">
@@ -6566,15 +6753,15 @@
         <v>0</v>
       </c>
       <c r="BC39" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B39="Python",AT39*AO39/24/60,"")</f>
         <v/>
       </c>
       <c r="BD39" s="17" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE39" s="17">
-        <f t="shared" si="19"/>
+        <f>IF(B39="Julia",AU39*AY39/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE39" s="76">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF39" s="17">
@@ -6582,24 +6769,28 @@
         <v>11.9625</v>
       </c>
       <c r="BG39" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH39" s="48">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI39" s="85">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI39" s="53">
+      <c r="BJ39" s="53">
         <f t="shared" si="9"/>
         <v>11.9625</v>
       </c>
     </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C40" s="30">
         <v>12</v>
@@ -6664,7 +6855,7 @@
       <c r="AU40" s="33"/>
       <c r="AV40" s="43"/>
       <c r="AW40" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX40" s="33">
@@ -6676,7 +6867,7 @@
         <v>1595</v>
       </c>
       <c r="AZ40" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA40" s="34">
@@ -6688,15 +6879,15 @@
         <v>0</v>
       </c>
       <c r="BC40" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD40" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE40" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B40="Python",AT40*AO40/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD40" s="80" t="str">
+        <f>IF(B40="Julia",AU40*AY40/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE40" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF40" s="34">
@@ -6704,24 +6895,28 @@
         <v>11.9625</v>
       </c>
       <c r="BG40" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH40" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI40" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI40" s="51">
+      <c r="BJ40" s="51">
         <f t="shared" si="9"/>
         <v>11.9625</v>
       </c>
     </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C41" s="30">
         <v>12</v>
@@ -6786,19 +6981,19 @@
       <c r="AU41" s="33"/>
       <c r="AV41" s="43"/>
       <c r="AW41" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX41" s="33">
-        <f t="shared" ref="AX41:AX72" si="22">AW35*24</f>
+        <f t="shared" ref="AX41:AX72" si="19">AW35*24</f>
         <v>0</v>
       </c>
       <c r="AY41" s="33">
-        <f t="shared" ref="AY41:AY72" si="23">AY35+SUM(AF41:AH41,AL41:AM41)-AN41</f>
+        <f t="shared" ref="AY41:AY72" si="20">AY35+SUM(AF41:AH41,AL41:AM41)-AN41</f>
         <v>1595</v>
       </c>
       <c r="AZ41" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA41" s="34">
@@ -6810,15 +7005,15 @@
         <v>0</v>
       </c>
       <c r="BC41" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD41" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE41" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B41="Python",AT41*AO41/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD41" s="80" t="str">
+        <f>IF(B41="Julia",AU41*AY41/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE41" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF41" s="34">
@@ -6826,24 +7021,28 @@
         <v>11.9625</v>
       </c>
       <c r="BG41" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH41" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI41" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI41" s="51">
+      <c r="BJ41" s="51">
         <f t="shared" si="9"/>
         <v>11.9625</v>
       </c>
     </row>
-    <row r="42" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C42" s="30">
         <v>15</v>
@@ -6908,19 +7107,19 @@
       <c r="AU42" s="33"/>
       <c r="AV42" s="43"/>
       <c r="AW42" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX42" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY42" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1595</v>
       </c>
       <c r="AZ42" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA42" s="34">
@@ -6932,15 +7131,15 @@
         <v>0</v>
       </c>
       <c r="BC42" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD42" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE42" s="34">
-        <f t="shared" si="19"/>
+        <f>IF(B42="Python",AT42*AO42/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD42" s="80" t="str">
+        <f>IF(B42="Julia",AU42*AY42/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE42" s="77">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF42" s="34">
@@ -6948,24 +7147,28 @@
         <v>11.9625</v>
       </c>
       <c r="BG42" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH42" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI42" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI42" s="51">
+      <c r="BJ42" s="51">
         <f t="shared" si="9"/>
         <v>11.9625</v>
       </c>
     </row>
-    <row r="43" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B43" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C43" s="30">
         <v>12</v>
@@ -7030,19 +7233,19 @@
       <c r="AU43" s="33"/>
       <c r="AV43" s="43"/>
       <c r="AW43" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX43" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY43" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1595</v>
       </c>
       <c r="AZ43" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA43" s="34">
@@ -7054,15 +7257,15 @@
         <v>0</v>
       </c>
       <c r="BC43" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD43" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE43" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B43="Python",AT43*AO43/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD43" s="80">
+        <f>IF(B43="Julia",AU43*AY43/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE43" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF43" s="34" t="str">
@@ -7070,24 +7273,28 @@
         <v/>
       </c>
       <c r="BG43" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH43" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI43" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI43" s="51">
+      <c r="BJ43" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C44" s="7">
         <v>12</v>
@@ -7152,19 +7359,19 @@
       <c r="AU44" s="20"/>
       <c r="AV44" s="44"/>
       <c r="AW44" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX44" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY44" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1595</v>
       </c>
       <c r="AZ44" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA44" s="21">
@@ -7176,15 +7383,15 @@
         <v>0</v>
       </c>
       <c r="BC44" s="21" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B44="Python",AT44*AO44/24/60,"")</f>
         <v/>
       </c>
       <c r="BD44" s="21">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE44" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B44="Julia",AU44*AY44/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE44" s="78" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF44" s="21" t="str">
@@ -7192,24 +7399,28 @@
         <v/>
       </c>
       <c r="BG44" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH44" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI44" s="87">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI44" s="52">
+      <c r="BJ44" s="52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C45" s="4">
         <v>12</v>
@@ -7274,19 +7485,19 @@
       <c r="AU45" s="16"/>
       <c r="AV45" s="42"/>
       <c r="AW45" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX45" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY45" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1580</v>
       </c>
       <c r="AZ45" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA45" s="17">
@@ -7298,15 +7509,15 @@
         <v>0</v>
       </c>
       <c r="BC45" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B45="Python",AT45*AO45/24/60,"")</f>
         <v/>
       </c>
       <c r="BD45" s="17" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE45" s="17">
-        <f t="shared" si="19"/>
+        <f>IF(B45="Julia",AU45*AY45/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE45" s="76">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF45" s="17">
@@ -7314,24 +7525,28 @@
         <v>11.85</v>
       </c>
       <c r="BG45" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH45" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI45" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI45" s="51">
+      <c r="BJ45" s="51">
         <f t="shared" si="9"/>
         <v>11.85</v>
       </c>
     </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C46" s="30">
         <v>12</v>
@@ -7396,19 +7611,19 @@
       <c r="AU46" s="33"/>
       <c r="AV46" s="43"/>
       <c r="AW46" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX46" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY46" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1580</v>
       </c>
       <c r="AZ46" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA46" s="34">
@@ -7420,15 +7635,15 @@
         <v>0</v>
       </c>
       <c r="BC46" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD46" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE46" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B46="Python",AT46*AO46/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD46" s="80" t="str">
+        <f>IF(B46="Julia",AU46*AY46/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE46" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF46" s="34">
@@ -7436,24 +7651,28 @@
         <v>11.85</v>
       </c>
       <c r="BG46" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH46" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI46" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI46" s="51">
+      <c r="BJ46" s="51">
         <f t="shared" si="9"/>
         <v>11.85</v>
       </c>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C47" s="30">
         <v>12</v>
@@ -7518,19 +7737,19 @@
       <c r="AU47" s="33"/>
       <c r="AV47" s="43"/>
       <c r="AW47" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX47" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY47" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1580</v>
       </c>
       <c r="AZ47" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA47" s="34">
@@ -7542,15 +7761,15 @@
         <v>0</v>
       </c>
       <c r="BC47" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD47" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE47" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B47="Python",AT47*AO47/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD47" s="80" t="str">
+        <f>IF(B47="Julia",AU47*AY47/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE47" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF47" s="34">
@@ -7558,24 +7777,28 @@
         <v>11.85</v>
       </c>
       <c r="BG47" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH47" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI47" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI47" s="51">
+      <c r="BJ47" s="51">
         <f t="shared" si="9"/>
         <v>11.85</v>
       </c>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C48" s="30">
         <v>15</v>
@@ -7640,19 +7863,19 @@
       <c r="AU48" s="33"/>
       <c r="AV48" s="43"/>
       <c r="AW48" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX48" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY48" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1580</v>
       </c>
       <c r="AZ48" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA48" s="34">
@@ -7664,15 +7887,15 @@
         <v>0</v>
       </c>
       <c r="BC48" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD48" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE48" s="34">
-        <f t="shared" si="19"/>
+        <f>IF(B48="Python",AT48*AO48/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD48" s="80" t="str">
+        <f>IF(B48="Julia",AU48*AY48/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE48" s="77">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF48" s="34">
@@ -7680,24 +7903,28 @@
         <v>11.85</v>
       </c>
       <c r="BG48" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH48" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI48" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI48" s="51">
+      <c r="BJ48" s="51">
         <f t="shared" si="9"/>
         <v>11.85</v>
       </c>
     </row>
-    <row r="49" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C49" s="30">
         <v>12</v>
@@ -7762,19 +7989,19 @@
       <c r="AU49" s="33"/>
       <c r="AV49" s="43"/>
       <c r="AW49" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX49" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY49" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1580</v>
       </c>
       <c r="AZ49" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA49" s="34">
@@ -7786,15 +8013,15 @@
         <v>0</v>
       </c>
       <c r="BC49" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD49" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE49" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B49="Python",AT49*AO49/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD49" s="80">
+        <f>IF(B49="Julia",AU49*AY49/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE49" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF49" s="34" t="str">
@@ -7802,24 +8029,28 @@
         <v/>
       </c>
       <c r="BG49" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH49" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI49" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI49" s="51">
+      <c r="BJ49" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C50" s="7">
         <v>12</v>
@@ -7884,19 +8115,19 @@
       <c r="AU50" s="20"/>
       <c r="AV50" s="44"/>
       <c r="AW50" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX50" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY50" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1580</v>
       </c>
       <c r="AZ50" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA50" s="21">
@@ -7908,15 +8139,15 @@
         <v>0</v>
       </c>
       <c r="BC50" s="21" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B50="Python",AT50*AO50/24/60,"")</f>
         <v/>
       </c>
       <c r="BD50" s="21">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE50" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B50="Julia",AU50*AY50/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE50" s="78" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF50" s="21" t="str">
@@ -7924,24 +8155,28 @@
         <v/>
       </c>
       <c r="BG50" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH50" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI50" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI50" s="51">
+      <c r="BJ50" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C51" s="4">
         <v>12</v>
@@ -8006,19 +8241,19 @@
       <c r="AU51" s="16"/>
       <c r="AV51" s="42"/>
       <c r="AW51" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX51" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY51" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1565</v>
       </c>
       <c r="AZ51" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA51" s="17">
@@ -8030,15 +8265,15 @@
         <v>0</v>
       </c>
       <c r="BC51" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B51="Python",AT51*AO51/24/60,"")</f>
         <v/>
       </c>
       <c r="BD51" s="17" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE51" s="17">
-        <f t="shared" si="19"/>
+        <f>IF(B51="Julia",AU51*AY51/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE51" s="76">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF51" s="17">
@@ -8046,24 +8281,28 @@
         <v>11.737500000000001</v>
       </c>
       <c r="BG51" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH51" s="48">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI51" s="85">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI51" s="53">
+      <c r="BJ51" s="53">
         <f t="shared" si="9"/>
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C52" s="30">
         <v>12</v>
@@ -8128,19 +8367,19 @@
       <c r="AU52" s="33"/>
       <c r="AV52" s="43"/>
       <c r="AW52" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX52" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY52" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1565</v>
       </c>
       <c r="AZ52" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA52" s="34">
@@ -8152,15 +8391,15 @@
         <v>0</v>
       </c>
       <c r="BC52" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD52" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE52" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B52="Python",AT52*AO52/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD52" s="80" t="str">
+        <f>IF(B52="Julia",AU52*AY52/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE52" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF52" s="34">
@@ -8168,24 +8407,28 @@
         <v>11.737500000000001</v>
       </c>
       <c r="BG52" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH52" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI52" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI52" s="51">
+      <c r="BJ52" s="51">
         <f t="shared" si="9"/>
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C53" s="30">
         <v>12</v>
@@ -8250,19 +8493,19 @@
       <c r="AU53" s="33"/>
       <c r="AV53" s="43"/>
       <c r="AW53" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX53" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY53" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1565</v>
       </c>
       <c r="AZ53" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA53" s="34">
@@ -8274,15 +8517,15 @@
         <v>0</v>
       </c>
       <c r="BC53" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD53" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE53" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B53="Python",AT53*AO53/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD53" s="80" t="str">
+        <f>IF(B53="Julia",AU53*AY53/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE53" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF53" s="34">
@@ -8290,24 +8533,28 @@
         <v>11.737500000000001</v>
       </c>
       <c r="BG53" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH53" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI53" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI53" s="51">
+      <c r="BJ53" s="51">
         <f t="shared" si="9"/>
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C54" s="30">
         <v>15</v>
@@ -8372,19 +8619,19 @@
       <c r="AU54" s="33"/>
       <c r="AV54" s="43"/>
       <c r="AW54" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX54" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY54" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1565</v>
       </c>
       <c r="AZ54" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA54" s="34">
@@ -8396,15 +8643,15 @@
         <v>0</v>
       </c>
       <c r="BC54" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD54" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE54" s="34">
-        <f t="shared" si="19"/>
+        <f>IF(B54="Python",AT54*AO54/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD54" s="80" t="str">
+        <f>IF(B54="Julia",AU54*AY54/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE54" s="77">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF54" s="34">
@@ -8412,24 +8659,28 @@
         <v>11.737500000000001</v>
       </c>
       <c r="BG54" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH54" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI54" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI54" s="51">
+      <c r="BJ54" s="51">
         <f t="shared" si="9"/>
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C55" s="30">
         <v>12</v>
@@ -8494,19 +8745,19 @@
       <c r="AU55" s="33"/>
       <c r="AV55" s="43"/>
       <c r="AW55" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX55" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY55" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1565</v>
       </c>
       <c r="AZ55" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA55" s="34">
@@ -8518,15 +8769,15 @@
         <v>0</v>
       </c>
       <c r="BC55" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD55" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE55" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B55="Python",AT55*AO55/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD55" s="80">
+        <f>IF(B55="Julia",AU55*AY55/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE55" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF55" s="34" t="str">
@@ -8534,24 +8785,28 @@
         <v/>
       </c>
       <c r="BG55" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH55" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI55" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI55" s="51">
+      <c r="BJ55" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C56" s="7">
         <v>12</v>
@@ -8616,19 +8871,19 @@
       <c r="AU56" s="20"/>
       <c r="AV56" s="44"/>
       <c r="AW56" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX56" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY56" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1565</v>
       </c>
       <c r="AZ56" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA56" s="21">
@@ -8640,15 +8895,15 @@
         <v>0</v>
       </c>
       <c r="BC56" s="21" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B56="Python",AT56*AO56/24/60,"")</f>
         <v/>
       </c>
       <c r="BD56" s="21">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE56" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B56="Julia",AU56*AY56/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE56" s="78" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF56" s="21" t="str">
@@ -8656,24 +8911,28 @@
         <v/>
       </c>
       <c r="BG56" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH56" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI56" s="87">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI56" s="52">
+      <c r="BJ56" s="52">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C57" s="4">
         <v>12</v>
@@ -8738,19 +8997,19 @@
       <c r="AU57" s="16"/>
       <c r="AV57" s="42"/>
       <c r="AW57" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX57" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY57" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1550</v>
       </c>
       <c r="AZ57" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA57" s="17">
@@ -8762,15 +9021,15 @@
         <v>0</v>
       </c>
       <c r="BC57" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B57="Python",AT57*AO57/24/60,"")</f>
         <v/>
       </c>
       <c r="BD57" s="17" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE57" s="17">
-        <f t="shared" si="19"/>
+        <f>IF(B57="Julia",AU57*AY57/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE57" s="76">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF57" s="17">
@@ -8778,24 +9037,28 @@
         <v>11.625</v>
       </c>
       <c r="BG57" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH57" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI57" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI57" s="51">
+      <c r="BJ57" s="51">
         <f t="shared" si="9"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="58" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C58" s="30">
         <v>12</v>
@@ -8860,19 +9123,19 @@
       <c r="AU58" s="33"/>
       <c r="AV58" s="43"/>
       <c r="AW58" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX58" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY58" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1550</v>
       </c>
       <c r="AZ58" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA58" s="34">
@@ -8884,15 +9147,15 @@
         <v>0</v>
       </c>
       <c r="BC58" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD58" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE58" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B58="Python",AT58*AO58/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD58" s="80" t="str">
+        <f>IF(B58="Julia",AU58*AY58/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE58" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF58" s="34">
@@ -8900,24 +9163,28 @@
         <v>11.625</v>
       </c>
       <c r="BG58" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH58" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI58" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI58" s="51">
+      <c r="BJ58" s="51">
         <f t="shared" si="9"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="59" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C59" s="30">
         <v>12</v>
@@ -8982,19 +9249,19 @@
       <c r="AU59" s="33"/>
       <c r="AV59" s="43"/>
       <c r="AW59" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX59" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY59" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1550</v>
       </c>
       <c r="AZ59" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA59" s="34">
@@ -9006,15 +9273,15 @@
         <v>0</v>
       </c>
       <c r="BC59" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD59" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE59" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B59="Python",AT59*AO59/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD59" s="80" t="str">
+        <f>IF(B59="Julia",AU59*AY59/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE59" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF59" s="34">
@@ -9022,24 +9289,28 @@
         <v>11.625</v>
       </c>
       <c r="BG59" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH59" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI59" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI59" s="51">
+      <c r="BJ59" s="51">
         <f t="shared" si="9"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="60" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C60" s="30">
         <v>15</v>
@@ -9104,19 +9375,19 @@
       <c r="AU60" s="33"/>
       <c r="AV60" s="43"/>
       <c r="AW60" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX60" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY60" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1550</v>
       </c>
       <c r="AZ60" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA60" s="34">
@@ -9128,15 +9399,15 @@
         <v>0</v>
       </c>
       <c r="BC60" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD60" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE60" s="34">
-        <f t="shared" si="19"/>
+        <f>IF(B60="Python",AT60*AO60/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD60" s="80" t="str">
+        <f>IF(B60="Julia",AU60*AY60/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE60" s="77">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF60" s="34">
@@ -9144,24 +9415,28 @@
         <v>11.625</v>
       </c>
       <c r="BG60" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH60" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI60" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI60" s="51">
+      <c r="BJ60" s="51">
         <f t="shared" si="9"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="61" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C61" s="30">
         <v>12</v>
@@ -9226,19 +9501,19 @@
       <c r="AU61" s="33"/>
       <c r="AV61" s="43"/>
       <c r="AW61" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX61" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY61" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1550</v>
       </c>
       <c r="AZ61" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA61" s="34">
@@ -9250,15 +9525,15 @@
         <v>0</v>
       </c>
       <c r="BC61" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD61" s="34">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE61" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B61="Python",AT61*AO61/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD61" s="80">
+        <f>IF(B61="Julia",AU61*AY61/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE61" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF61" s="34" t="str">
@@ -9266,24 +9541,28 @@
         <v/>
       </c>
       <c r="BG61" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH61" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI61" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI61" s="51">
+      <c r="BJ61" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C62" s="7">
         <v>12</v>
@@ -9348,19 +9627,19 @@
       <c r="AU62" s="20"/>
       <c r="AV62" s="44"/>
       <c r="AW62" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX62" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY62" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1550</v>
       </c>
       <c r="AZ62" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA62" s="21">
@@ -9372,15 +9651,15 @@
         <v>0</v>
       </c>
       <c r="BC62" s="21" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B62="Python",AT62*AO62/24/60,"")</f>
         <v/>
       </c>
       <c r="BD62" s="21">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="BE62" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B62="Julia",AU62*AY62/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE62" s="78" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF62" s="21" t="str">
@@ -9388,24 +9667,28 @@
         <v/>
       </c>
       <c r="BG62" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BH62" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI62" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI62" s="51">
+      <c r="BJ62" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C63" s="4">
         <v>12</v>
@@ -9470,19 +9753,19 @@
       <c r="AU63" s="16"/>
       <c r="AV63" s="42"/>
       <c r="AW63" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX63" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY63" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1535</v>
       </c>
       <c r="AZ63" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA63" s="17">
@@ -9494,15 +9777,15 @@
         <v>0</v>
       </c>
       <c r="BC63" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f>IF(B63="Python",AT63*AO63/24/60,"")</f>
         <v/>
       </c>
       <c r="BD63" s="17" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE63" s="17">
-        <f t="shared" si="19"/>
+        <f>IF(B63="Julia",AU63*AY63/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE63" s="76">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF63" s="17">
@@ -9510,24 +9793,28 @@
         <v>11.512499999999999</v>
       </c>
       <c r="BG63" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH63" s="48">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI63" s="85">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI63" s="53">
+      <c r="BJ63" s="53">
         <f t="shared" si="9"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C64" s="30">
         <v>12</v>
@@ -9592,19 +9879,19 @@
       <c r="AU64" s="33"/>
       <c r="AV64" s="43"/>
       <c r="AW64" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX64" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY64" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1535</v>
       </c>
       <c r="AZ64" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA64" s="34">
@@ -9616,15 +9903,15 @@
         <v>0</v>
       </c>
       <c r="BC64" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD64" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE64" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B64="Python",AT64*AO64/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD64" s="80" t="str">
+        <f>IF(B64="Julia",AU64*AY64/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE64" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF64" s="34">
@@ -9632,24 +9919,28 @@
         <v>11.512499999999999</v>
       </c>
       <c r="BG64" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH64" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI64" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI64" s="51">
+      <c r="BJ64" s="51">
         <f t="shared" si="9"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C65" s="30">
         <v>12</v>
@@ -9714,19 +10005,19 @@
       <c r="AU65" s="33"/>
       <c r="AV65" s="43"/>
       <c r="AW65" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX65" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY65" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1535</v>
       </c>
       <c r="AZ65" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA65" s="34">
@@ -9738,15 +10029,15 @@
         <v>0</v>
       </c>
       <c r="BC65" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="BD65" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE65" s="34" t="str">
-        <f t="shared" si="19"/>
+        <f>IF(B65="Python",AT65*AO65/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD65" s="80" t="str">
+        <f>IF(B65="Julia",AU65*AY65/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE65" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF65" s="34">
@@ -9754,24 +10045,28 @@
         <v>11.512499999999999</v>
       </c>
       <c r="BG65" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH65" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI65" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI65" s="51">
+      <c r="BJ65" s="51">
         <f t="shared" si="9"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C66" s="30">
         <v>15</v>
@@ -9836,19 +10131,19 @@
       <c r="AU66" s="33"/>
       <c r="AV66" s="43"/>
       <c r="AW66" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX66" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY66" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1535</v>
       </c>
       <c r="AZ66" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA66" s="34">
@@ -9860,15 +10155,15 @@
         <v>0</v>
       </c>
       <c r="BC66" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD66" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BE66" s="34">
-        <f t="shared" si="19"/>
+        <f>IF(B66="Python",AT66*AO66/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD66" s="80" t="str">
+        <f>IF(B66="Julia",AU66*AY66/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE66" s="77">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BF66" s="34">
@@ -9876,24 +10171,28 @@
         <v>11.512499999999999</v>
       </c>
       <c r="BG66" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BH66" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI66" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI66" s="51">
+      <c r="BJ66" s="51">
         <f t="shared" si="9"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C67" s="30">
         <v>12</v>
@@ -9958,39 +10257,39 @@
       <c r="AU67" s="33"/>
       <c r="AV67" s="43"/>
       <c r="AW67" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AX67" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AY67" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1535</v>
       </c>
       <c r="AZ67" s="34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BA67" s="34">
-        <f t="shared" ref="BA67:BA80" si="24">AJ67/AO67</f>
+        <f t="shared" ref="BA67:BA80" si="21">AJ67/AO67</f>
         <v>0</v>
       </c>
       <c r="BB67" s="34">
-        <f t="shared" ref="BB67:BB80" si="25">AI67*24</f>
+        <f t="shared" ref="BB67:BB80" si="22">AI67*24</f>
         <v>0</v>
       </c>
       <c r="BC67" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="BD67" s="34">
-        <f t="shared" ref="BD67:BD80" si="26">IF(B67="Julia",AU67*AY67/24,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE67" s="34" t="str">
-        <f t="shared" ref="BE67:BE80" si="27">IF(B67="No MPC", AS67*I67*AY67*0.06,"")</f>
+        <f>IF(B67="Python",AT67*AO67/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD67" s="80">
+        <f>IF(B67="Julia",AU67*AY67/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE67" s="77" t="str">
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="BF67" s="34" t="str">
@@ -9998,24 +10297,28 @@
         <v/>
       </c>
       <c r="BG67" s="34">
-        <f t="shared" ref="BG67:BG80" si="28">IF(B67="Julia",AV67*AY67,"")</f>
+        <f t="shared" ref="BG67:BG80" si="23">IF(B67="Julia",AV67*AY67,"")</f>
         <v>0</v>
       </c>
       <c r="BH67" s="49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BI67" s="86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI67" s="51">
+      <c r="BJ67" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C68" s="7">
         <v>12</v>
@@ -10080,39 +10383,39 @@
       <c r="AU68" s="20"/>
       <c r="AV68" s="44"/>
       <c r="AW68" s="19">
-        <f t="shared" ref="AW68:AW80" si="29">AS68*I68*AY68*0.06</f>
+        <f t="shared" ref="AW68:AW80" si="24">AS68*I68*AY68/1000</f>
         <v>0</v>
       </c>
       <c r="AX68" s="20">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AY68" s="20">
+        <f t="shared" si="20"/>
+        <v>1535</v>
+      </c>
+      <c r="AZ68" s="21">
+        <f t="shared" ref="AZ68:AZ80" si="25">IFERROR(AJ68/AY68,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA68" s="21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB68" s="21">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY68" s="20">
-        <f t="shared" si="23"/>
-        <v>1535</v>
-      </c>
-      <c r="AZ68" s="21">
-        <f t="shared" ref="AZ68:AZ80" si="30">IFERROR(AJ68/AY68,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BA68" s="21">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB68" s="21">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
       <c r="BC68" s="21" t="str">
-        <f t="shared" ref="BC68:BC80" si="31">IF(B68="Python",AT68*AY68/24,"")</f>
+        <f>IF(B68="Python",AT68*AO68/24/60,"")</f>
         <v/>
       </c>
       <c r="BD68" s="21">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BE68" s="21" t="str">
-        <f t="shared" si="27"/>
+        <f>IF(B68="Julia",AU68*AY68/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE68" s="78" t="str">
+        <f t="shared" ref="BE68:BE80" si="26">IF(B68="No MPC", AS68*I68*AY68/1000,"")</f>
         <v/>
       </c>
       <c r="BF68" s="21" t="str">
@@ -10120,24 +10423,28 @@
         <v/>
       </c>
       <c r="BG68" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BH68" s="50">
-        <f t="shared" ref="BH68:BH80" si="32">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
-        <v>0</v>
-      </c>
-      <c r="BI68" s="52">
-        <f t="shared" ref="BI68:BI80" si="33">IF(BF68&lt;&gt;"",BF68,BG68)</f>
+        <f t="shared" ref="BH68:BH80" si="27">IF(BC68&lt;&gt;"",BC68/0.000385,IF(BD68&lt;&gt;"",BD68/0.000385,BE68/0.000385))</f>
+        <v>0</v>
+      </c>
+      <c r="BI68" s="87">
+        <f t="shared" ref="BI68:BI74" si="28">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
+        <v>0</v>
+      </c>
+      <c r="BJ68" s="52">
+        <f t="shared" ref="BJ68:BJ80" si="29">IF(BF68&lt;&gt;"",BF68,BG68)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C69" s="4">
         <v>12</v>
@@ -10202,39 +10509,39 @@
       <c r="AU69" s="16"/>
       <c r="AV69" s="42"/>
       <c r="AW69" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AX69" s="16">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AY69" s="16">
+        <f t="shared" si="20"/>
+        <v>1520</v>
+      </c>
+      <c r="AZ69" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA69" s="17">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB69" s="17">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY69" s="16">
-        <f t="shared" si="23"/>
-        <v>1520</v>
-      </c>
-      <c r="AZ69" s="17">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA69" s="17">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB69" s="17">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
       <c r="BC69" s="17" t="str">
-        <f t="shared" si="31"/>
+        <f>IF(B69="Python",AT69*AO69/24/60,"")</f>
         <v/>
       </c>
       <c r="BD69" s="17" t="str">
+        <f>IF(B69="Julia",AU69*AY69/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE69" s="76">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="BE69" s="17">
-        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF69" s="17">
@@ -10242,24 +10549,28 @@
         <v>11.4</v>
       </c>
       <c r="BG69" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="BH69" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI69" s="86">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH69" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI69" s="51">
-        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BJ69" s="51">
+        <f t="shared" si="29"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="70" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C70" s="30">
         <v>12</v>
@@ -10324,39 +10635,39 @@
       <c r="AU70" s="33"/>
       <c r="AV70" s="43"/>
       <c r="AW70" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AX70" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AY70" s="33">
+        <f t="shared" si="20"/>
+        <v>1520</v>
+      </c>
+      <c r="AZ70" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA70" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB70" s="34">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY70" s="33">
-        <f t="shared" si="23"/>
-        <v>1520</v>
-      </c>
-      <c r="AZ70" s="34">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA70" s="34">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB70" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
       <c r="BC70" s="34">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BD70" s="34" t="str">
+        <f>IF(B70="Python",AT70*AO70/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD70" s="80" t="str">
+        <f>IF(B70="Julia",AU70*AY70/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE70" s="77" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="BE70" s="34" t="str">
-        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF70" s="34">
@@ -10364,24 +10675,28 @@
         <v>11.4</v>
       </c>
       <c r="BG70" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="BH70" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI70" s="86">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH70" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI70" s="51">
-        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BJ70" s="51">
+        <f t="shared" si="29"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="71" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C71" s="30">
         <v>12</v>
@@ -10446,39 +10761,39 @@
       <c r="AU71" s="33"/>
       <c r="AV71" s="43"/>
       <c r="AW71" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AX71" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AY71" s="33">
+        <f t="shared" si="20"/>
+        <v>1520</v>
+      </c>
+      <c r="AZ71" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA71" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB71" s="34">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY71" s="33">
-        <f t="shared" si="23"/>
-        <v>1520</v>
-      </c>
-      <c r="AZ71" s="34">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA71" s="34">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB71" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
       <c r="BC71" s="34">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BD71" s="34" t="str">
+        <f>IF(B71="Python",AT71*AO71/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD71" s="80" t="str">
+        <f>IF(B71="Julia",AU71*AY71/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE71" s="77" t="str">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="BE71" s="34" t="str">
-        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF71" s="34">
@@ -10486,24 +10801,28 @@
         <v>11.4</v>
       </c>
       <c r="BG71" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="BH71" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI71" s="86">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH71" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI71" s="51">
-        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BJ71" s="51">
+        <f t="shared" si="29"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="72" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C72" s="30">
         <v>15</v>
@@ -10568,39 +10887,39 @@
       <c r="AU72" s="33"/>
       <c r="AV72" s="43"/>
       <c r="AW72" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AX72" s="33">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AY72" s="33">
+        <f t="shared" si="20"/>
+        <v>1520</v>
+      </c>
+      <c r="AZ72" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA72" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB72" s="34">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY72" s="33">
-        <f t="shared" si="23"/>
-        <v>1520</v>
-      </c>
-      <c r="AZ72" s="34">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA72" s="34">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB72" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
       <c r="BC72" s="34" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BD72" s="34" t="str">
+        <f>IF(B72="Python",AT72*AO72/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD72" s="80" t="str">
+        <f>IF(B72="Julia",AU72*AY72/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE72" s="77">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="BE72" s="34">
-        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF72" s="34">
@@ -10608,24 +10927,28 @@
         <v>11.4</v>
       </c>
       <c r="BG72" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="BH72" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI72" s="86">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH72" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI72" s="51">
-        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BJ72" s="51">
+        <f t="shared" si="29"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="73" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C73" s="30">
         <v>12</v>
@@ -10690,39 +11013,39 @@
       <c r="AU73" s="33"/>
       <c r="AV73" s="43"/>
       <c r="AW73" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AX73" s="33">
-        <f t="shared" ref="AX73:AX80" si="34">AW67*24</f>
+        <f t="shared" ref="AX73:AX104" si="30">AW67*24</f>
         <v>0</v>
       </c>
       <c r="AY73" s="33">
-        <f t="shared" ref="AY73:AY80" si="35">AY67+SUM(AF73:AH73,AL73:AM73)-AN73</f>
+        <f t="shared" ref="AY73:AY104" si="31">AY67+SUM(AF73:AH73,AL73:AM73)-AN73</f>
         <v>1520</v>
       </c>
       <c r="AZ73" s="34">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BA73" s="34">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB73" s="34">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC73" s="34" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BD73" s="34">
+        <f>IF(B73="Python",AT73*AO73/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD73" s="80">
+        <f>IF(B73="Julia",AU73*AY73/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE73" s="77" t="str">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BE73" s="34" t="str">
-        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF73" s="34" t="str">
@@ -10730,24 +11053,28 @@
         <v/>
       </c>
       <c r="BG73" s="34">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BH73" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI73" s="86">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="BH73" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI73" s="51">
-        <f t="shared" si="33"/>
+      <c r="BJ73" s="51">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C74" s="7">
         <v>12</v>
@@ -10812,64 +11139,68 @@
       <c r="AU74" s="20"/>
       <c r="AV74" s="44"/>
       <c r="AW74" s="19">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AX74" s="20">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AY74" s="20">
+        <f t="shared" si="31"/>
+        <v>1520</v>
+      </c>
+      <c r="AZ74" s="21">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA74" s="21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB74" s="21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC74" s="21" t="str">
+        <f>IF(B74="Python",AT74*AO74/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD74" s="21">
+        <f>IF(B74="Julia",AU74*AY74/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE74" s="78" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="BF74" s="21" t="str">
+        <f t="shared" ref="BF74:BF80" si="32">IF(O74&lt;1.5, IF(B74&lt;&gt;"Julia",((3-O74)*AY74)/400, ""),0)</f>
+        <v/>
+      </c>
+      <c r="BG74" s="21">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BH74" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI74" s="86">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BJ74" s="51">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AX74" s="20">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="AY74" s="20">
-        <f t="shared" si="35"/>
-        <v>1520</v>
-      </c>
-      <c r="AZ74" s="21">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA74" s="21">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB74" s="21">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC74" s="21" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BD74" s="21">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BE74" s="21" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BF74" s="21" t="str">
-        <f t="shared" ref="BF74:BF80" si="36">IF(O74&lt;1.5, IF(B74&lt;&gt;"Julia",((3-O74)*AY74)/400, ""),0)</f>
-        <v/>
-      </c>
-      <c r="BG74" s="21">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BH74" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI74" s="51">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="75" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C75" s="4">
         <v>12</v>
@@ -10934,64 +11265,65 @@
       <c r="AU75" s="4"/>
       <c r="AV75" s="25"/>
       <c r="AW75" s="15">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AX75" s="16">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AY75" s="16">
+        <f t="shared" si="31"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ75" s="17">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA75" s="17">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB75" s="17">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC75" s="17" t="str">
+        <f>IF(B75="Python",AT75*AO75/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD75" s="17" t="str">
+        <f>IF(B75="Julia",AU75*AY75/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE75" s="76">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BF75" s="17">
+        <f t="shared" si="32"/>
+        <v>11.2875</v>
+      </c>
+      <c r="BG75" s="17" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="BH75" s="48">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI75" s="82"/>
+      <c r="BJ75" s="53">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX75" s="16">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="AY75" s="16">
-        <f t="shared" si="35"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ75" s="17">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA75" s="17">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB75" s="17">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC75" s="17" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BD75" s="17" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="BE75" s="17">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BF75" s="17">
-        <f t="shared" si="36"/>
         <v>11.2875</v>
       </c>
-      <c r="BG75" s="17" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH75" s="48">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI75" s="53">
-        <f t="shared" si="33"/>
-        <v>11.2875</v>
-      </c>
     </row>
-    <row r="76" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C76" s="30">
         <v>12</v>
@@ -11056,64 +11388,65 @@
       <c r="AU76" s="30"/>
       <c r="AV76" s="2"/>
       <c r="AW76" s="18">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AX76" s="33">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AY76" s="33">
+        <f t="shared" si="31"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ76" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA76" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB76" s="34">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC76" s="34">
+        <f>IF(B76="Python",AT76*AO76/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD76" s="80" t="str">
+        <f>IF(B76="Julia",AU76*AY76/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE76" s="77" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="BF76" s="34">
+        <f t="shared" si="32"/>
+        <v>11.2875</v>
+      </c>
+      <c r="BG76" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="BH76" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI76" s="83"/>
+      <c r="BJ76" s="51">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX76" s="33">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="AY76" s="33">
-        <f t="shared" si="35"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ76" s="34">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA76" s="34">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB76" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC76" s="34">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BD76" s="34" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="BE76" s="34" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BF76" s="34">
-        <f t="shared" si="36"/>
         <v>11.2875</v>
       </c>
-      <c r="BG76" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH76" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI76" s="51">
-        <f t="shared" si="33"/>
-        <v>11.2875</v>
-      </c>
     </row>
-    <row r="77" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C77" s="30">
         <v>12</v>
@@ -11178,64 +11511,65 @@
       <c r="AU77" s="33"/>
       <c r="AV77" s="43"/>
       <c r="AW77" s="18">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AX77" s="33">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AY77" s="33">
+        <f t="shared" si="31"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ77" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA77" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB77" s="34">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC77" s="34">
+        <f>IF(B77="Python",AT77*AO77/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD77" s="80" t="str">
+        <f>IF(B77="Julia",AU77*AY77/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE77" s="77" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="BF77" s="34">
+        <f t="shared" si="32"/>
+        <v>11.2875</v>
+      </c>
+      <c r="BG77" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="BH77" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI77" s="83"/>
+      <c r="BJ77" s="51">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX77" s="33">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="AY77" s="33">
-        <f t="shared" si="35"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ77" s="34">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA77" s="34">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB77" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC77" s="34">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BD77" s="34" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="BE77" s="34" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BF77" s="34">
-        <f t="shared" si="36"/>
         <v>11.2875</v>
       </c>
-      <c r="BG77" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH77" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI77" s="51">
-        <f t="shared" si="33"/>
-        <v>11.2875</v>
-      </c>
     </row>
-    <row r="78" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C78" s="30">
         <v>15</v>
@@ -11300,64 +11634,65 @@
       <c r="AU78" s="33"/>
       <c r="AV78" s="43"/>
       <c r="AW78" s="18">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AX78" s="33">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AY78" s="33">
+        <f t="shared" si="31"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ78" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA78" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB78" s="34">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC78" s="34" t="str">
+        <f>IF(B78="Python",AT78*AO78/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD78" s="80" t="str">
+        <f>IF(B78="Julia",AU78*AY78/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE78" s="77">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BF78" s="34">
+        <f t="shared" si="32"/>
+        <v>11.2875</v>
+      </c>
+      <c r="BG78" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="BH78" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI78" s="83"/>
+      <c r="BJ78" s="51">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX78" s="33">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="AY78" s="33">
-        <f t="shared" si="35"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ78" s="34">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA78" s="34">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB78" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC78" s="34" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BD78" s="34" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="BE78" s="34">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BF78" s="34">
-        <f t="shared" si="36"/>
         <v>11.2875</v>
       </c>
-      <c r="BG78" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH78" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI78" s="51">
-        <f t="shared" si="33"/>
-        <v>11.2875</v>
-      </c>
     </row>
-    <row r="79" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C79" s="30">
         <v>12</v>
@@ -11422,64 +11757,65 @@
       <c r="AU79" s="33"/>
       <c r="AV79" s="43"/>
       <c r="AW79" s="18">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AX79" s="33">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AY79" s="33">
+        <f t="shared" si="31"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ79" s="34">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA79" s="34">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB79" s="34">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC79" s="34" t="str">
+        <f>IF(B79="Python",AT79*AO79/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD79" s="80">
+        <f>IF(B79="Julia",AU79*AY79/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE79" s="77" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="BF79" s="34" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="BG79" s="34">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BH79" s="49">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI79" s="83"/>
+      <c r="BJ79" s="51">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AX79" s="33">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="AY79" s="33">
-        <f t="shared" si="35"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ79" s="34">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA79" s="34">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB79" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC79" s="34" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BD79" s="34">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BE79" s="34" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BF79" s="34" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="BG79" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BH79" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI79" s="51">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="80" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C80" s="7">
         <v>12</v>
@@ -11544,55 +11880,56 @@
       <c r="AU80" s="20"/>
       <c r="AV80" s="44"/>
       <c r="AW80" s="19">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AX80" s="20">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AY80" s="20">
+        <f t="shared" si="31"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ80" s="21">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA80" s="21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB80" s="21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="BC80" s="21" t="str">
+        <f>IF(B80="Python",AT80*AO80/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD80" s="21">
+        <f>IF(B80="Julia",AU80*AY80/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE80" s="78" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="BF80" s="21" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="BG80" s="21">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BH80" s="50">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BI80" s="84"/>
+      <c r="BJ80" s="52">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX80" s="20">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="AY80" s="20">
-        <f t="shared" si="35"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ80" s="21">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BA80" s="21">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BB80" s="21">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BC80" s="21" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BD80" s="21">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BE80" s="21" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BF80" s="21" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="BG80" s="21">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BH80" s="50">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI80" s="52">
-        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -11601,7 +11938,7 @@
   <mergeCells count="7">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:AA1"/>
-    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="BH1:BJ1"/>
     <mergeCell ref="AW1:BG1"/>
     <mergeCell ref="AO1:AS1"/>
     <mergeCell ref="AT1:AV1"/>
@@ -11634,12 +11971,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11866,27 +12212,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11911,18 +12251,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yl604392\Git\state-space-model\data\MR24-030 Experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1412" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E95C25A-8713-4A22-B042-A81569C24A85}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1728AB44-0F33-44D5-B6B8-28AA24DDCA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -1010,7 +1010,48 @@
     <xf numFmtId="165" fontId="0" fillId="39" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="39" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1046,47 +1087,6 @@
     <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1137,14 +1137,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1178,10 +1178,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1482,93 +1478,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BJ80"/>
-  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="10.6640625" customWidth="1"/>
-    <col min="6" max="59" width="12.77734375" customWidth="1"/>
-    <col min="60" max="60" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="61" max="62" width="16.21875" customWidth="1"/>
+    <col min="2" max="4" width="10.7109375" customWidth="1"/>
+    <col min="6" max="59" width="12.7109375" customWidth="1"/>
+    <col min="60" max="60" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="68" t="s">
+    <row r="1" spans="1:62" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="69"/>
-      <c r="W1" s="69"/>
-      <c r="X1" s="69"/>
-      <c r="Y1" s="69"/>
-      <c r="Z1" s="69"/>
-      <c r="AA1" s="70"/>
-      <c r="AB1" s="64" t="s">
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="65"/>
-      <c r="AG1" s="65"/>
-      <c r="AH1" s="65"/>
-      <c r="AI1" s="65"/>
-      <c r="AJ1" s="65"/>
-      <c r="AK1" s="65"/>
-      <c r="AL1" s="65"/>
-      <c r="AM1" s="65"/>
-      <c r="AN1" s="66"/>
-      <c r="AO1" s="59" t="s">
+      <c r="AC1" s="86"/>
+      <c r="AD1" s="86"/>
+      <c r="AE1" s="86"/>
+      <c r="AF1" s="86"/>
+      <c r="AG1" s="86"/>
+      <c r="AH1" s="86"/>
+      <c r="AI1" s="86"/>
+      <c r="AJ1" s="86"/>
+      <c r="AK1" s="86"/>
+      <c r="AL1" s="86"/>
+      <c r="AM1" s="86"/>
+      <c r="AN1" s="87"/>
+      <c r="AO1" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="AP1" s="59"/>
-      <c r="AQ1" s="59"/>
-      <c r="AR1" s="59"/>
-      <c r="AS1" s="60"/>
-      <c r="AT1" s="61" t="s">
+      <c r="AP1" s="80"/>
+      <c r="AQ1" s="80"/>
+      <c r="AR1" s="80"/>
+      <c r="AS1" s="81"/>
+      <c r="AT1" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="63"/>
-      <c r="AW1" s="57" t="s">
+      <c r="AU1" s="83"/>
+      <c r="AV1" s="84"/>
+      <c r="AW1" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="AX1" s="58"/>
-      <c r="AY1" s="58"/>
-      <c r="AZ1" s="58"/>
-      <c r="BA1" s="58"/>
-      <c r="BB1" s="58"/>
-      <c r="BC1" s="58"/>
-      <c r="BD1" s="58"/>
-      <c r="BE1" s="58"/>
-      <c r="BF1" s="58"/>
-      <c r="BG1" s="58"/>
-      <c r="BH1" s="55" t="s">
+      <c r="AX1" s="79"/>
+      <c r="AY1" s="79"/>
+      <c r="AZ1" s="79"/>
+      <c r="BA1" s="79"/>
+      <c r="BB1" s="79"/>
+      <c r="BC1" s="79"/>
+      <c r="BD1" s="79"/>
+      <c r="BE1" s="79"/>
+      <c r="BF1" s="79"/>
+      <c r="BG1" s="79"/>
+      <c r="BH1" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="BI1" s="81"/>
-      <c r="BJ1" s="56"/>
+      <c r="BI1" s="76"/>
+      <c r="BJ1" s="77"/>
     </row>
-    <row r="2" spans="1:62" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:62" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
         <v>3</v>
       </c>
@@ -1584,70 +1580,70 @@
       <c r="E2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="75" t="s">
+      <c r="H2" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="75" t="s">
+      <c r="J2" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="75" t="s">
+      <c r="K2" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="73" t="s">
+      <c r="L2" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="73" t="s">
+      <c r="M2" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="73" t="s">
+      <c r="N2" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="73" t="s">
+      <c r="O2" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="73" t="s">
+      <c r="P2" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="73" t="s">
+      <c r="Q2" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="73" t="s">
+      <c r="R2" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="S2" s="73" t="s">
+      <c r="S2" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="73" t="s">
+      <c r="T2" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="73" t="s">
+      <c r="U2" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="V2" s="73" t="s">
+      <c r="V2" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="W2" s="73" t="s">
+      <c r="W2" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="X2" s="73" t="s">
+      <c r="X2" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="Y2" s="73" t="s">
+      <c r="Y2" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="Z2" s="73" t="s">
+      <c r="Z2" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AA2" s="74" t="s">
+      <c r="AA2" s="58" t="s">
         <v>43</v>
       </c>
       <c r="AB2" s="41" t="s">
@@ -1756,7 +1752,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -1906,7 +1902,7 @@
         <v>1685</v>
       </c>
       <c r="AZ3" s="17">
-        <f>IFERROR(AJ3/AY3,0)</f>
+        <f>IF(ISBLANK(AJ3),NA(),IFERROR(AJ3/AY3,0))</f>
         <v>0</v>
       </c>
       <c r="BA3" s="17">
@@ -1918,14 +1914,14 @@
         <v>0</v>
       </c>
       <c r="BC3" s="17" t="str">
-        <f>IF(B3="Python",AT3*AO3/24/60,"")</f>
+        <f t="shared" ref="BC3:BC34" si="0">IF(B3="Python",AT3*AO3/24/60,"")</f>
         <v/>
       </c>
       <c r="BD3" s="17" t="str">
-        <f>IF(B3="Julia",AU3*AY3/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE3" s="76">
+        <f t="shared" ref="BD3:BD34" si="1">IF(B3="Julia",AU3*AY3/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE3" s="60">
         <f>IF(B3="No MPC", AS3*I3*AY3/1000,"")</f>
         <v>6.8242499999999996E-3</v>
       </c>
@@ -1933,14 +1929,14 @@
         <v>0</v>
       </c>
       <c r="BG3" s="17" t="str">
-        <f t="shared" ref="BG3:BG34" si="0">IF(B3="Julia",AV3*AY3,"")</f>
+        <f t="shared" ref="BG3:BG34" si="2">IF(B3="Julia",AV3*AY3,"")</f>
         <v/>
       </c>
       <c r="BH3" s="48">
         <f>IF(BC3&lt;&gt;"",BC3/0.000385,IF(BD3&lt;&gt;"",BD3/0.000385,BE3/0.000385))</f>
         <v>17.725324675324675</v>
       </c>
-      <c r="BI3" s="85">
+      <c r="BI3" s="68">
         <f>IF(BC3&lt;&gt;"",BC3,IF(BD3&lt;&gt;"",BD3,BE3))</f>
         <v>6.8242499999999996E-3</v>
       </c>
@@ -1949,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>54</v>
       </c>
@@ -2089,11 +2085,11 @@
       <c r="AU4" s="33"/>
       <c r="AV4" s="43"/>
       <c r="AW4" s="18">
-        <f t="shared" ref="AW4:AW67" si="1">AS4*I4*AY4/1000</f>
+        <f t="shared" ref="AW4:AW67" si="3">AS4*I4*AY4/1000</f>
         <v>6.2681999999999989E-3</v>
       </c>
       <c r="AX4" s="33">
-        <f t="shared" ref="AX4:AX8" si="2">AW4*24</f>
+        <f t="shared" ref="AX4:AX8" si="4">AW4*24</f>
         <v>0.15043679999999998</v>
       </c>
       <c r="AY4" s="33">
@@ -2101,50 +2097,50 @@
         <v>1685</v>
       </c>
       <c r="AZ4" s="34">
-        <f t="shared" ref="AZ4:AZ67" si="3">IFERROR(AJ4/AY4,0)</f>
+        <f t="shared" ref="AZ4:AZ67" si="5">IF(ISBLANK(AJ4),NA(),IFERROR(AJ4/AY4,0))</f>
         <v>0</v>
       </c>
       <c r="BA4" s="34">
-        <f t="shared" ref="BA3:BA34" si="4">AJ4/AO4</f>
+        <f t="shared" ref="BA4:BA34" si="6">AJ4/AO4</f>
         <v>0</v>
       </c>
       <c r="BB4" s="34">
-        <f t="shared" ref="BB3:BB34" si="5">AI4*24</f>
+        <f t="shared" ref="BB4:BB34" si="7">AI4*24</f>
         <v>0</v>
       </c>
       <c r="BC4" s="34">
-        <f>IF(B4="Python",AT4*AO4/24/60,"")</f>
+        <f t="shared" si="0"/>
         <v>5.3124999999999995E-3</v>
       </c>
-      <c r="BD4" s="80" t="str">
-        <f>IF(B4="Julia",AU4*AY4/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE4" s="77" t="str">
-        <f t="shared" ref="BE4:BE67" si="6">IF(B4="No MPC", AS4*I4*AY4/1000,"")</f>
+      <c r="BD4" s="64" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="BE4" s="61" t="str">
+        <f t="shared" ref="BE4:BE67" si="8">IF(B4="No MPC", AS4*I4*AY4/1000,"")</f>
         <v/>
       </c>
       <c r="BF4" s="34">
         <v>0</v>
       </c>
       <c r="BG4" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH4" s="49">
-        <f t="shared" ref="BH4:BH67" si="7">IF(BC4&lt;&gt;"",BC4/0.000385,IF(BD4&lt;&gt;"",BD4/0.000385,BE4/0.000385))</f>
+        <f t="shared" ref="BH4:BH67" si="9">IF(BC4&lt;&gt;"",BC4/0.000385,IF(BD4&lt;&gt;"",BD4/0.000385,BE4/0.000385))</f>
         <v>13.798701298701298</v>
       </c>
-      <c r="BI4" s="86">
-        <f t="shared" ref="BI4:BI67" si="8">IF(BC4&lt;&gt;"",BC4,IF(BD4&lt;&gt;"",BD4,BE4))</f>
+      <c r="BI4" s="69">
+        <f t="shared" ref="BI4:BI67" si="10">IF(BC4&lt;&gt;"",BC4,IF(BD4&lt;&gt;"",BD4,BE4))</f>
         <v>5.3124999999999995E-3</v>
       </c>
       <c r="BJ4" s="51">
-        <f t="shared" ref="BJ4:BJ67" si="9">IF(BF4&lt;&gt;"",BF4,BG4)</f>
+        <f t="shared" ref="BJ4:BJ67" si="11">IF(BF4&lt;&gt;"",BF4,BG4)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>55</v>
       </c>
@@ -2284,62 +2280,62 @@
       <c r="AU5" s="33"/>
       <c r="AV5" s="43"/>
       <c r="AW5" s="18">
+        <f t="shared" si="3"/>
+        <v>6.7231499999999998E-3</v>
+      </c>
+      <c r="AX5" s="33">
+        <f t="shared" si="4"/>
+        <v>0.16135559999999999</v>
+      </c>
+      <c r="AY5" s="33">
+        <f t="shared" ref="AY5:AY8" si="12">AO5-AN5</f>
+        <v>1685</v>
+      </c>
+      <c r="AZ5" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BA5" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB5" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC5" s="34">
+        <f t="shared" si="0"/>
+        <v>5.3124999999999995E-3</v>
+      </c>
+      <c r="BD5" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>6.7231499999999998E-3</v>
-      </c>
-      <c r="AX5" s="33">
+        <v/>
+      </c>
+      <c r="BE5" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF5" s="34">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="34" t="str">
         <f t="shared" si="2"/>
-        <v>0.16135559999999999</v>
-      </c>
-      <c r="AY5" s="33">
-        <f t="shared" ref="AY4:AY8" si="10">AO5-AN5</f>
-        <v>1685</v>
-      </c>
-      <c r="AZ5" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA5" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB5" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC5" s="34">
-        <f>IF(B5="Python",AT5*AO5/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BH5" s="49">
+        <f t="shared" si="9"/>
+        <v>13.798701298701298</v>
+      </c>
+      <c r="BI5" s="69">
+        <f t="shared" si="10"/>
         <v>5.3124999999999995E-3</v>
       </c>
-      <c r="BD5" s="80" t="str">
-        <f>IF(B5="Julia",AU5*AY5/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE5" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF5" s="34">
-        <v>0</v>
-      </c>
-      <c r="BG5" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BH5" s="49">
-        <f t="shared" si="7"/>
-        <v>13.798701298701298</v>
-      </c>
-      <c r="BI5" s="86">
-        <f t="shared" si="8"/>
-        <v>5.3124999999999995E-3</v>
-      </c>
       <c r="BJ5" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
@@ -2477,62 +2473,62 @@
       <c r="AU6" s="33"/>
       <c r="AV6" s="43"/>
       <c r="AW6" s="18">
+        <f t="shared" si="3"/>
+        <v>8.1385499999999996E-3</v>
+      </c>
+      <c r="AX6" s="33">
+        <f t="shared" si="4"/>
+        <v>0.19532519999999998</v>
+      </c>
+      <c r="AY6" s="33">
+        <f t="shared" si="12"/>
+        <v>1685</v>
+      </c>
+      <c r="AZ6" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BA6" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB6" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD6" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>8.1385499999999996E-3</v>
-      </c>
-      <c r="AX6" s="33">
-        <f t="shared" si="2"/>
-        <v>0.19532519999999998</v>
-      </c>
-      <c r="AY6" s="33">
-        <f t="shared" si="10"/>
-        <v>1685</v>
-      </c>
-      <c r="AZ6" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA6" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB6" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC6" s="34" t="str">
-        <f>IF(B6="Python",AT6*AO6/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD6" s="80" t="str">
-        <f>IF(B6="Julia",AU6*AY6/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE6" s="77">
-        <f t="shared" si="6"/>
-        <v>8.1385499999999996E-3</v>
-      </c>
-      <c r="BF6" s="34">
-        <v>0</v>
-      </c>
-      <c r="BG6" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="BH6" s="49">
-        <f t="shared" si="7"/>
-        <v>21.13909090909091</v>
-      </c>
-      <c r="BI6" s="86">
+        <v/>
+      </c>
+      <c r="BE6" s="61">
         <f t="shared" si="8"/>
         <v>8.1385499999999996E-3</v>
       </c>
+      <c r="BF6" s="34">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="34" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="BH6" s="49">
+        <f t="shared" si="9"/>
+        <v>21.13909090909091</v>
+      </c>
+      <c r="BI6" s="69">
+        <f t="shared" si="10"/>
+        <v>8.1385499999999996E-3</v>
+      </c>
       <c r="BJ6" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>57</v>
       </c>
@@ -2674,43 +2670,43 @@
         <v>0</v>
       </c>
       <c r="AW7" s="18">
+        <f t="shared" si="3"/>
+        <v>6.1165499999999992E-3</v>
+      </c>
+      <c r="AX7" s="33">
+        <f t="shared" si="4"/>
+        <v>0.14679719999999999</v>
+      </c>
+      <c r="AY7" s="33">
+        <f t="shared" si="12"/>
+        <v>1685</v>
+      </c>
+      <c r="AZ7" s="34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BA7" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB7" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC7" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD7" s="63">
         <f t="shared" si="1"/>
-        <v>6.1165499999999992E-3</v>
-      </c>
-      <c r="AX7" s="33">
-        <f t="shared" si="2"/>
-        <v>0.14679719999999999</v>
-      </c>
-      <c r="AY7" s="33">
-        <f t="shared" si="10"/>
-        <v>1685</v>
-      </c>
-      <c r="AZ7" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA7" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB7" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC7" s="34" t="str">
-        <f>IF(B7="Python",AT7*AO7/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD7" s="79">
-        <f>IF(B7="Julia",AU7*AY7/24/60,"")</f>
         <v>6.116549999999988E-3</v>
       </c>
-      <c r="BE7" s="79" t="str">
+      <c r="BE7" s="63" t="str">
         <f>IF(B7="No MPC", AS7*I7*AY7/1000,"")</f>
         <v/>
       </c>
       <c r="BF7" s="34" t="str">
-        <f t="shared" ref="BF4:BF8" si="11">IF(IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, "")&lt;0,0,IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, ""))</f>
+        <f t="shared" ref="BF7:BF8" si="13">IF(IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, "")&lt;0,0,IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, ""))</f>
         <v/>
       </c>
       <c r="BG7" s="34">
@@ -2718,19 +2714,19 @@
         <v>0</v>
       </c>
       <c r="BH7" s="49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>15.887142857142827</v>
       </c>
-      <c r="BI7" s="86">
-        <f t="shared" si="8"/>
+      <c r="BI7" s="69">
+        <f t="shared" si="10"/>
         <v>6.116549999999988E-3</v>
       </c>
       <c r="BJ7" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>58</v>
       </c>
@@ -2872,63 +2868,63 @@
         <v>0</v>
       </c>
       <c r="AW8" s="19">
+        <f t="shared" si="3"/>
+        <v>6.5209499999999993E-3</v>
+      </c>
+      <c r="AX8" s="20">
+        <f t="shared" si="4"/>
+        <v>0.1565028</v>
+      </c>
+      <c r="AY8" s="20">
+        <f t="shared" si="12"/>
+        <v>1685</v>
+      </c>
+      <c r="AZ8" s="21">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BA8" s="21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB8" s="21">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC8" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD8" s="63">
         <f t="shared" si="1"/>
-        <v>6.5209499999999993E-3</v>
-      </c>
-      <c r="AX8" s="20">
+        <v>6.520949999999988E-3</v>
+      </c>
+      <c r="BE8" s="62" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF8" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="BG8" s="21">
         <f t="shared" si="2"/>
-        <v>0.1565028</v>
-      </c>
-      <c r="AY8" s="20">
+        <v>0</v>
+      </c>
+      <c r="BH8" s="50">
+        <f t="shared" si="9"/>
+        <v>16.937532467532439</v>
+      </c>
+      <c r="BI8" s="70">
         <f t="shared" si="10"/>
-        <v>1685</v>
-      </c>
-      <c r="AZ8" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA8" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB8" s="21">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC8" s="21" t="str">
-        <f>IF(B8="Python",AT8*AO8/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD8" s="79">
-        <f>IF(B8="Julia",AU8*AY8/24/60,"")</f>
         <v>6.520949999999988E-3</v>
       </c>
-      <c r="BE8" s="78" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF8" s="21" t="str">
+      <c r="BJ8" s="52">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="BG8" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BH8" s="50">
-        <f t="shared" si="7"/>
-        <v>16.937532467532439</v>
-      </c>
-      <c r="BI8" s="87">
-        <f t="shared" si="8"/>
-        <v>6.520949999999988E-3</v>
-      </c>
-      <c r="BJ8" s="52">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>53</v>
       </c>
@@ -2998,39 +2994,39 @@
       <c r="AU9" s="16"/>
       <c r="AV9" s="42"/>
       <c r="AW9" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX9" s="16">
-        <f t="shared" ref="AX9:AX40" si="12">AW3*24</f>
+        <f t="shared" ref="AX9:AX40" si="14">AW3*24</f>
         <v>0.16378199999999998</v>
       </c>
       <c r="AY9" s="16">
         <f>AY3+SUM(AF9:AH9,AL9:AM9)-AN9</f>
         <v>1670</v>
       </c>
-      <c r="AZ9" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="AZ9" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
       <c r="BA9" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB9" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BC9" s="17" t="str">
-        <f>IF(B9="Python",AT9*AO9/24/60,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="BD9" s="17" t="str">
-        <f>IF(B9="Julia",AU9*AY9/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE9" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="BE9" s="60">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BF9" s="17">
@@ -3038,23 +3034,23 @@
         <v>20.875</v>
       </c>
       <c r="BG9" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH9" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI9" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI9" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ9" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20.875</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -3107,63 +3103,63 @@
       <c r="AU10" s="33"/>
       <c r="AV10" s="43"/>
       <c r="AW10" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX10" s="33">
+        <f t="shared" si="14"/>
+        <v>0.15043679999999998</v>
+      </c>
+      <c r="AY10" s="33">
+        <f t="shared" ref="AY10:AY40" si="15">AY4+SUM(AF10:AH10,AL10:AM10)-AN10</f>
+        <v>1670</v>
+      </c>
+      <c r="AZ10" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA10" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB10" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC10" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD10" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX10" s="33">
-        <f t="shared" si="12"/>
-        <v>0.15043679999999998</v>
-      </c>
-      <c r="AY10" s="33">
-        <f t="shared" ref="AY9:AY40" si="13">AY4+SUM(AF10:AH10,AL10:AM10)-AN10</f>
-        <v>1670</v>
-      </c>
-      <c r="AZ10" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA10" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB10" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC10" s="34">
-        <f>IF(B10="Python",AT10*AO10/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD10" s="80" t="str">
-        <f>IF(B10="Julia",AU10*AY10/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE10" s="77" t="str">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE10" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF10" s="34">
-        <f t="shared" ref="BF10:BF12" si="14">IF(O10&lt;10, IF(B10&lt;&gt;"Julia",((5-O10)*AY10)/400, ""),0)</f>
+        <f t="shared" ref="BF10:BF12" si="16">IF(O10&lt;10, IF(B10&lt;&gt;"Julia",((5-O10)*AY10)/400, ""),0)</f>
         <v>20.875</v>
       </c>
       <c r="BG10" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH10" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI10" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI10" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ10" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20.875</v>
       </c>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
@@ -3217,63 +3213,63 @@
       <c r="AU11" s="33"/>
       <c r="AV11" s="43"/>
       <c r="AW11" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX11" s="33">
+        <f t="shared" si="14"/>
+        <v>0.16135559999999999</v>
+      </c>
+      <c r="AY11" s="33">
+        <f t="shared" si="15"/>
+        <v>1670</v>
+      </c>
+      <c r="AZ11" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA11" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB11" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC11" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD11" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX11" s="33">
-        <f t="shared" si="12"/>
-        <v>0.16135559999999999</v>
-      </c>
-      <c r="AY11" s="33">
-        <f t="shared" si="13"/>
-        <v>1670</v>
-      </c>
-      <c r="AZ11" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA11" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB11" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC11" s="34">
-        <f>IF(B11="Python",AT11*AO11/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD11" s="80" t="str">
-        <f>IF(B11="Julia",AU11*AY11/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE11" s="77" t="str">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE11" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF11" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>20.875</v>
       </c>
       <c r="BG11" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH11" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI11" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI11" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ11" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20.875</v>
       </c>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
@@ -3327,63 +3323,63 @@
       <c r="AU12" s="33"/>
       <c r="AV12" s="43"/>
       <c r="AW12" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX12" s="33">
+        <f t="shared" si="14"/>
+        <v>0.19532519999999998</v>
+      </c>
+      <c r="AY12" s="33">
+        <f t="shared" si="15"/>
+        <v>1670</v>
+      </c>
+      <c r="AZ12" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA12" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB12" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC12" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD12" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX12" s="33">
-        <f t="shared" si="12"/>
-        <v>0.19532519999999998</v>
-      </c>
-      <c r="AY12" s="33">
-        <f t="shared" si="13"/>
-        <v>1670</v>
-      </c>
-      <c r="AZ12" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA12" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB12" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC12" s="34" t="str">
-        <f>IF(B12="Python",AT12*AO12/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD12" s="80" t="str">
-        <f>IF(B12="Julia",AU12*AY12/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE12" s="77">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE12" s="61">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BF12" s="34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>20.875</v>
       </c>
       <c r="BG12" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH12" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI12" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI12" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ12" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20.875</v>
       </c>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
@@ -3453,63 +3449,63 @@
       <c r="AU13" s="33"/>
       <c r="AV13" s="43"/>
       <c r="AW13" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX13" s="33">
+        <f t="shared" si="14"/>
+        <v>0.14679719999999999</v>
+      </c>
+      <c r="AY13" s="33">
+        <f t="shared" si="15"/>
+        <v>1670</v>
+      </c>
+      <c r="AZ13" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA13" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB13" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC13" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD13" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX13" s="33">
-        <f t="shared" si="12"/>
-        <v>0.14679719999999999</v>
-      </c>
-      <c r="AY13" s="33">
-        <f t="shared" si="13"/>
-        <v>1670</v>
-      </c>
-      <c r="AZ13" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA13" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB13" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC13" s="34" t="str">
-        <f>IF(B13="Python",AT13*AO13/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD13" s="80">
-        <f>IF(B13="Julia",AU13*AY13/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE13" s="77" t="str">
-        <f t="shared" si="6"/>
+      <c r="BE13" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF13" s="34" t="str">
-        <f t="shared" ref="BF10:BF73" si="15">IF(O13&lt;1.5, IF(B13&lt;&gt;"Julia",((3-O13)*AY13)/400, ""),0)</f>
+        <f t="shared" ref="BF13:BF73" si="17">IF(O13&lt;1.5, IF(B13&lt;&gt;"Julia",((3-O13)*AY13)/400, ""),0)</f>
         <v/>
       </c>
       <c r="BG13" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BH13" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI13" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI13" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ13" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>58</v>
       </c>
@@ -3579,63 +3575,63 @@
       <c r="AU14" s="20"/>
       <c r="AV14" s="44"/>
       <c r="AW14" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX14" s="20">
+        <f t="shared" si="14"/>
+        <v>0.1565028</v>
+      </c>
+      <c r="AY14" s="20">
+        <f t="shared" si="15"/>
+        <v>1670</v>
+      </c>
+      <c r="AZ14" s="21" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA14" s="21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB14" s="21">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC14" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD14" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX14" s="20">
-        <f t="shared" si="12"/>
-        <v>0.1565028</v>
-      </c>
-      <c r="AY14" s="20">
-        <f t="shared" si="13"/>
-        <v>1670</v>
-      </c>
-      <c r="AZ14" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA14" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB14" s="21">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC14" s="21" t="str">
-        <f>IF(B14="Python",AT14*AO14/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD14" s="21">
-        <f>IF(B14="Julia",AU14*AY14/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE14" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="BE14" s="62" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF14" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG14" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BH14" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI14" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI14" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ14" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>53</v>
       </c>
@@ -3705,39 +3701,39 @@
       <c r="AU15" s="16"/>
       <c r="AV15" s="42"/>
       <c r="AW15" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX15" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY15" s="16">
+        <f t="shared" si="15"/>
+        <v>1655</v>
+      </c>
+      <c r="AZ15" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA15" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB15" s="17">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC15" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD15" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX15" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY15" s="16">
-        <f t="shared" si="13"/>
-        <v>1655</v>
-      </c>
-      <c r="AZ15" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA15" s="17">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB15" s="17">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC15" s="17" t="str">
-        <f>IF(B15="Python",AT15*AO15/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD15" s="17" t="str">
-        <f>IF(B15="Julia",AU15*AY15/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE15" s="76">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE15" s="60">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BF15" s="17">
@@ -3745,23 +3741,23 @@
         <v>12.4125</v>
       </c>
       <c r="BG15" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH15" s="48">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI15" s="85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI15" s="68">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ15" s="53">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.4125</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
@@ -3831,63 +3827,63 @@
       <c r="AU16" s="33"/>
       <c r="AV16" s="43"/>
       <c r="AW16" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX16" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY16" s="33">
+        <f t="shared" si="15"/>
+        <v>1655</v>
+      </c>
+      <c r="AZ16" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA16" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB16" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC16" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD16" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX16" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY16" s="33">
-        <f t="shared" si="13"/>
-        <v>1655</v>
-      </c>
-      <c r="AZ16" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA16" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB16" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC16" s="34">
-        <f>IF(B16="Python",AT16*AO16/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD16" s="80" t="str">
-        <f>IF(B16="Julia",AU16*AY16/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE16" s="77" t="str">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE16" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF16" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.4125</v>
       </c>
       <c r="BG16" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH16" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI16" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI16" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ16" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.4125</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>55</v>
       </c>
@@ -3957,63 +3953,63 @@
       <c r="AU17" s="33"/>
       <c r="AV17" s="43"/>
       <c r="AW17" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX17" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY17" s="33">
+        <f t="shared" si="15"/>
+        <v>1655</v>
+      </c>
+      <c r="AZ17" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA17" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB17" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC17" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD17" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX17" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY17" s="33">
-        <f t="shared" si="13"/>
-        <v>1655</v>
-      </c>
-      <c r="AZ17" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA17" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB17" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC17" s="34">
-        <f>IF(B17="Python",AT17*AO17/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD17" s="80" t="str">
-        <f>IF(B17="Julia",AU17*AY17/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE17" s="77" t="str">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE17" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF17" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.4125</v>
       </c>
       <c r="BG17" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH17" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI17" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI17" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ17" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.4125</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -4083,63 +4079,63 @@
       <c r="AU18" s="33"/>
       <c r="AV18" s="43"/>
       <c r="AW18" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX18" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY18" s="33">
+        <f t="shared" si="15"/>
+        <v>1655</v>
+      </c>
+      <c r="AZ18" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA18" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB18" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC18" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD18" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX18" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY18" s="33">
-        <f t="shared" si="13"/>
-        <v>1655</v>
-      </c>
-      <c r="AZ18" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA18" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB18" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC18" s="34" t="str">
-        <f>IF(B18="Python",AT18*AO18/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD18" s="80" t="str">
-        <f>IF(B18="Julia",AU18*AY18/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE18" s="77">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE18" s="61">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BF18" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.4125</v>
       </c>
       <c r="BG18" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH18" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI18" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI18" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ18" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.4125</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
@@ -4209,63 +4205,63 @@
       <c r="AU19" s="33"/>
       <c r="AV19" s="43"/>
       <c r="AW19" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX19" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY19" s="33">
+        <f t="shared" si="15"/>
+        <v>1655</v>
+      </c>
+      <c r="AZ19" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA19" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB19" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC19" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD19" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX19" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY19" s="33">
-        <f t="shared" si="13"/>
-        <v>1655</v>
-      </c>
-      <c r="AZ19" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA19" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB19" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC19" s="34" t="str">
-        <f>IF(B19="Python",AT19*AO19/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD19" s="80">
-        <f>IF(B19="Julia",AU19*AY19/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE19" s="77" t="str">
-        <f t="shared" si="6"/>
+      <c r="BE19" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF19" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG19" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BH19" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI19" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI19" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ19" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>58</v>
       </c>
@@ -4335,63 +4331,63 @@
       <c r="AU20" s="20"/>
       <c r="AV20" s="44"/>
       <c r="AW20" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX20" s="20">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY20" s="20">
+        <f t="shared" si="15"/>
+        <v>1655</v>
+      </c>
+      <c r="AZ20" s="21" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA20" s="21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB20" s="21">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC20" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD20" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX20" s="20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY20" s="20">
-        <f t="shared" si="13"/>
-        <v>1655</v>
-      </c>
-      <c r="AZ20" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA20" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB20" s="21">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC20" s="21" t="str">
-        <f>IF(B20="Python",AT20*AO20/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD20" s="21">
-        <f>IF(B20="Julia",AU20*AY20/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE20" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="BE20" s="62" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF20" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG20" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BH20" s="50">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI20" s="87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI20" s="70">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ20" s="52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
@@ -4461,63 +4457,63 @@
       <c r="AU21" s="16"/>
       <c r="AV21" s="42"/>
       <c r="AW21" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX21" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY21" s="16">
+        <f t="shared" si="15"/>
+        <v>1640</v>
+      </c>
+      <c r="AZ21" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA21" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB21" s="17">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC21" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD21" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX21" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY21" s="16">
-        <f t="shared" si="13"/>
-        <v>1640</v>
-      </c>
-      <c r="AZ21" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA21" s="17">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB21" s="17">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC21" s="17" t="str">
-        <f>IF(B21="Python",AT21*AO21/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD21" s="17" t="str">
-        <f>IF(B21="Julia",AU21*AY21/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE21" s="76">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE21" s="60">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BF21" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.3</v>
       </c>
       <c r="BG21" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH21" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI21" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI21" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ21" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.3</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -4587,63 +4583,63 @@
       <c r="AU22" s="33"/>
       <c r="AV22" s="43"/>
       <c r="AW22" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX22" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY22" s="33">
+        <f t="shared" si="15"/>
+        <v>1640</v>
+      </c>
+      <c r="AZ22" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA22" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB22" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC22" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD22" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX22" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY22" s="33">
-        <f t="shared" si="13"/>
-        <v>1640</v>
-      </c>
-      <c r="AZ22" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA22" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB22" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC22" s="34">
-        <f>IF(B22="Python",AT22*AO22/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD22" s="80" t="str">
-        <f>IF(B22="Julia",AU22*AY22/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE22" s="77" t="str">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE22" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF22" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.3</v>
       </c>
       <c r="BG22" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH22" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI22" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI22" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ22" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.3</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -4713,63 +4709,63 @@
       <c r="AU23" s="33"/>
       <c r="AV23" s="43"/>
       <c r="AW23" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX23" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY23" s="33">
+        <f t="shared" si="15"/>
+        <v>1640</v>
+      </c>
+      <c r="AZ23" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA23" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB23" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC23" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD23" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX23" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY23" s="33">
-        <f t="shared" si="13"/>
-        <v>1640</v>
-      </c>
-      <c r="AZ23" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA23" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB23" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC23" s="34">
-        <f>IF(B23="Python",AT23*AO23/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD23" s="80" t="str">
-        <f>IF(B23="Julia",AU23*AY23/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE23" s="77" t="str">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE23" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF23" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.3</v>
       </c>
       <c r="BG23" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH23" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI23" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI23" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ23" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.3</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>56</v>
       </c>
@@ -4839,63 +4835,63 @@
       <c r="AU24" s="33"/>
       <c r="AV24" s="43"/>
       <c r="AW24" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX24" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY24" s="33">
+        <f t="shared" si="15"/>
+        <v>1640</v>
+      </c>
+      <c r="AZ24" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA24" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB24" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC24" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD24" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX24" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY24" s="33">
-        <f t="shared" si="13"/>
-        <v>1640</v>
-      </c>
-      <c r="AZ24" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA24" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB24" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC24" s="34" t="str">
-        <f>IF(B24="Python",AT24*AO24/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD24" s="80" t="str">
-        <f>IF(B24="Julia",AU24*AY24/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE24" s="77">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE24" s="61">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BF24" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.3</v>
       </c>
       <c r="BG24" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH24" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI24" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI24" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ24" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.3</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
@@ -4965,63 +4961,63 @@
       <c r="AU25" s="33"/>
       <c r="AV25" s="43"/>
       <c r="AW25" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX25" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="33">
+        <f t="shared" si="15"/>
+        <v>1640</v>
+      </c>
+      <c r="AZ25" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA25" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB25" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC25" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD25" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX25" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY25" s="33">
-        <f t="shared" si="13"/>
-        <v>1640</v>
-      </c>
-      <c r="AZ25" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA25" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB25" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC25" s="34" t="str">
-        <f>IF(B25="Python",AT25*AO25/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD25" s="80">
-        <f>IF(B25="Julia",AU25*AY25/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE25" s="77" t="str">
-        <f t="shared" si="6"/>
+      <c r="BE25" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF25" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG25" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BH25" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI25" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI25" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ25" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>58</v>
       </c>
@@ -5091,63 +5087,63 @@
       <c r="AU26" s="20"/>
       <c r="AV26" s="44"/>
       <c r="AW26" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX26" s="20">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY26" s="20">
+        <f t="shared" si="15"/>
+        <v>1640</v>
+      </c>
+      <c r="AZ26" s="21" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA26" s="21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB26" s="21">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC26" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD26" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX26" s="20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY26" s="20">
-        <f t="shared" si="13"/>
-        <v>1640</v>
-      </c>
-      <c r="AZ26" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA26" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB26" s="21">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC26" s="21" t="str">
-        <f>IF(B26="Python",AT26*AO26/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD26" s="21">
-        <f>IF(B26="Julia",AU26*AY26/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE26" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="BE26" s="62" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF26" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG26" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BH26" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI26" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI26" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ26" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>53</v>
       </c>
@@ -5217,63 +5213,63 @@
       <c r="AU27" s="16"/>
       <c r="AV27" s="42"/>
       <c r="AW27" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX27" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY27" s="16">
+        <f t="shared" si="15"/>
+        <v>1625</v>
+      </c>
+      <c r="AZ27" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA27" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB27" s="17">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC27" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD27" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX27" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY27" s="16">
-        <f t="shared" si="13"/>
-        <v>1625</v>
-      </c>
-      <c r="AZ27" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA27" s="17">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB27" s="17">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC27" s="17" t="str">
-        <f>IF(B27="Python",AT27*AO27/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD27" s="17" t="str">
-        <f>IF(B27="Julia",AU27*AY27/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE27" s="76">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE27" s="60">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BF27" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.1875</v>
       </c>
       <c r="BG27" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH27" s="48">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI27" s="85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI27" s="68">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ27" s="53">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.1875</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -5343,63 +5339,63 @@
       <c r="AU28" s="33"/>
       <c r="AV28" s="43"/>
       <c r="AW28" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX28" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY28" s="33">
+        <f t="shared" si="15"/>
+        <v>1625</v>
+      </c>
+      <c r="AZ28" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA28" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB28" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC28" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD28" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX28" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY28" s="33">
-        <f t="shared" si="13"/>
-        <v>1625</v>
-      </c>
-      <c r="AZ28" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA28" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB28" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC28" s="34">
-        <f>IF(B28="Python",AT28*AO28/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD28" s="80" t="str">
-        <f>IF(B28="Julia",AU28*AY28/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE28" s="77" t="str">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE28" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF28" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.1875</v>
       </c>
       <c r="BG28" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH28" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI28" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI28" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ28" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.1875</v>
       </c>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>55</v>
       </c>
@@ -5469,63 +5465,63 @@
       <c r="AU29" s="33"/>
       <c r="AV29" s="43"/>
       <c r="AW29" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX29" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY29" s="33">
+        <f t="shared" si="15"/>
+        <v>1625</v>
+      </c>
+      <c r="AZ29" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA29" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB29" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC29" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD29" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX29" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY29" s="33">
-        <f t="shared" si="13"/>
-        <v>1625</v>
-      </c>
-      <c r="AZ29" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA29" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB29" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC29" s="34">
-        <f>IF(B29="Python",AT29*AO29/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD29" s="80" t="str">
-        <f>IF(B29="Julia",AU29*AY29/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE29" s="77" t="str">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE29" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF29" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.1875</v>
       </c>
       <c r="BG29" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH29" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI29" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI29" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ29" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.1875</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
@@ -5595,63 +5591,63 @@
       <c r="AU30" s="33"/>
       <c r="AV30" s="43"/>
       <c r="AW30" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX30" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY30" s="33">
+        <f t="shared" si="15"/>
+        <v>1625</v>
+      </c>
+      <c r="AZ30" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA30" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB30" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC30" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD30" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX30" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY30" s="33">
-        <f t="shared" si="13"/>
-        <v>1625</v>
-      </c>
-      <c r="AZ30" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA30" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB30" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC30" s="34" t="str">
-        <f>IF(B30="Python",AT30*AO30/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD30" s="80" t="str">
-        <f>IF(B30="Julia",AU30*AY30/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE30" s="77">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE30" s="61">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BF30" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.1875</v>
       </c>
       <c r="BG30" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH30" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI30" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI30" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ30" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.1875</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>57</v>
       </c>
@@ -5721,63 +5717,63 @@
       <c r="AU31" s="33"/>
       <c r="AV31" s="43"/>
       <c r="AW31" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX31" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY31" s="33">
+        <f t="shared" si="15"/>
+        <v>1625</v>
+      </c>
+      <c r="AZ31" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA31" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB31" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC31" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD31" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX31" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY31" s="33">
-        <f t="shared" si="13"/>
-        <v>1625</v>
-      </c>
-      <c r="AZ31" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA31" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB31" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC31" s="34" t="str">
-        <f>IF(B31="Python",AT31*AO31/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD31" s="80">
-        <f>IF(B31="Julia",AU31*AY31/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE31" s="77" t="str">
-        <f t="shared" si="6"/>
+      <c r="BE31" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF31" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG31" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BH31" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI31" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI31" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ31" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>58</v>
       </c>
@@ -5847,63 +5843,63 @@
       <c r="AU32" s="20"/>
       <c r="AV32" s="44"/>
       <c r="AW32" s="19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX32" s="20">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY32" s="20">
+        <f t="shared" si="15"/>
+        <v>1625</v>
+      </c>
+      <c r="AZ32" s="21" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA32" s="21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB32" s="21">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC32" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD32" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX32" s="20">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY32" s="20">
-        <f t="shared" si="13"/>
-        <v>1625</v>
-      </c>
-      <c r="AZ32" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA32" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB32" s="21">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC32" s="21" t="str">
-        <f>IF(B32="Python",AT32*AO32/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD32" s="21">
-        <f>IF(B32="Julia",AU32*AY32/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE32" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="BE32" s="62" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF32" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG32" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BH32" s="50">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI32" s="87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI32" s="70">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ32" s="52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>53</v>
       </c>
@@ -5973,63 +5969,63 @@
       <c r="AU33" s="16"/>
       <c r="AV33" s="42"/>
       <c r="AW33" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX33" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY33" s="16">
+        <f t="shared" si="15"/>
+        <v>1610</v>
+      </c>
+      <c r="AZ33" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA33" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB33" s="17">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC33" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="BD33" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX33" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY33" s="16">
-        <f t="shared" si="13"/>
-        <v>1610</v>
-      </c>
-      <c r="AZ33" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA33" s="17">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB33" s="17">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC33" s="17" t="str">
-        <f>IF(B33="Python",AT33*AO33/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD33" s="17" t="str">
-        <f>IF(B33="Julia",AU33*AY33/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE33" s="76">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE33" s="60">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="BF33" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.074999999999999</v>
       </c>
       <c r="BG33" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH33" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI33" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI33" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ33" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>54</v>
       </c>
@@ -6099,63 +6095,63 @@
       <c r="AU34" s="33"/>
       <c r="AV34" s="43"/>
       <c r="AW34" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX34" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY34" s="33">
+        <f t="shared" si="15"/>
+        <v>1610</v>
+      </c>
+      <c r="AZ34" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA34" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB34" s="34">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC34" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD34" s="64" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AX34" s="33">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AY34" s="33">
-        <f t="shared" si="13"/>
-        <v>1610</v>
-      </c>
-      <c r="AZ34" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA34" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BB34" s="34">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC34" s="34">
-        <f>IF(B34="Python",AT34*AO34/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD34" s="80" t="str">
-        <f>IF(B34="Julia",AU34*AY34/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE34" s="77" t="str">
-        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BE34" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF34" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.074999999999999</v>
       </c>
       <c r="BG34" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BH34" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI34" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI34" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ34" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
@@ -6225,63 +6221,63 @@
       <c r="AU35" s="33"/>
       <c r="AV35" s="43"/>
       <c r="AW35" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX35" s="33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AY35" s="33">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1610</v>
       </c>
-      <c r="AZ35" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="AZ35" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
       <c r="BA35" s="34">
-        <f t="shared" ref="BA35:BA66" si="16">AJ35/AO35</f>
+        <f t="shared" ref="BA35:BA66" si="18">AJ35/AO35</f>
         <v>0</v>
       </c>
       <c r="BB35" s="34">
-        <f t="shared" ref="BB35:BB66" si="17">AI35*24</f>
+        <f t="shared" ref="BB35:BB66" si="19">AI35*24</f>
         <v>0</v>
       </c>
       <c r="BC35" s="34">
-        <f>IF(B35="Python",AT35*AO35/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD35" s="80" t="str">
-        <f>IF(B35="Julia",AU35*AY35/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE35" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="BC35:BC66" si="20">IF(B35="Python",AT35*AO35/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BD35" s="64" t="str">
+        <f t="shared" ref="BD35:BD66" si="21">IF(B35="Julia",AU35*AY35/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BE35" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF35" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.074999999999999</v>
       </c>
       <c r="BG35" s="34" t="str">
-        <f t="shared" ref="BG35:BG66" si="18">IF(B35="Julia",AV35*AY35,"")</f>
+        <f t="shared" ref="BG35:BG66" si="22">IF(B35="Julia",AV35*AY35,"")</f>
         <v/>
       </c>
       <c r="BH35" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI35" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI35" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ35" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>56</v>
       </c>
@@ -6351,63 +6347,63 @@
       <c r="AU36" s="33"/>
       <c r="AV36" s="43"/>
       <c r="AW36" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX36" s="33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AY36" s="33">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1610</v>
       </c>
-      <c r="AZ36" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="AZ36" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
       <c r="BA36" s="34">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BB36" s="34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BC36" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="BD36" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE36" s="61">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF36" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC36" s="34" t="str">
-        <f>IF(B36="Python",AT36*AO36/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD36" s="80" t="str">
-        <f>IF(B36="Julia",AU36*AY36/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE36" s="77">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF36" s="34">
-        <f t="shared" si="15"/>
         <v>12.074999999999999</v>
       </c>
       <c r="BG36" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH36" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI36" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI36" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ36" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>57</v>
       </c>
@@ -6477,63 +6473,63 @@
       <c r="AU37" s="33"/>
       <c r="AV37" s="43"/>
       <c r="AW37" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX37" s="33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AY37" s="33">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1610</v>
       </c>
-      <c r="AZ37" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="AZ37" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
       <c r="BA37" s="34">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BB37" s="34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BC37" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="BD37" s="64">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE37" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF37" s="34" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC37" s="34" t="str">
-        <f>IF(B37="Python",AT37*AO37/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD37" s="80">
-        <f>IF(B37="Julia",AU37*AY37/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE37" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF37" s="34" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG37" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH37" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI37" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI37" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ37" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>58</v>
       </c>
@@ -6603,63 +6599,63 @@
       <c r="AU38" s="20"/>
       <c r="AV38" s="44"/>
       <c r="AW38" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX38" s="20">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AY38" s="20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1610</v>
       </c>
-      <c r="AZ38" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="AZ38" s="21" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
       <c r="BA38" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BB38" s="21">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BC38" s="21" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="BD38" s="21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE38" s="62" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF38" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC38" s="21" t="str">
-        <f>IF(B38="Python",AT38*AO38/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD38" s="21">
-        <f>IF(B38="Julia",AU38*AY38/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE38" s="78" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF38" s="21" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG38" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH38" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI38" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI38" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ38" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>53</v>
       </c>
@@ -6729,63 +6725,63 @@
       <c r="AU39" s="16"/>
       <c r="AV39" s="42"/>
       <c r="AW39" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX39" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AY39" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1595</v>
       </c>
-      <c r="AZ39" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="AZ39" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
       <c r="BA39" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BB39" s="17">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BC39" s="17" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="BD39" s="17" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE39" s="60">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF39" s="17">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC39" s="17" t="str">
-        <f>IF(B39="Python",AT39*AO39/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD39" s="17" t="str">
-        <f>IF(B39="Julia",AU39*AY39/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE39" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF39" s="17">
-        <f t="shared" si="15"/>
         <v>11.9625</v>
       </c>
       <c r="BG39" s="17" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH39" s="48">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI39" s="85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI39" s="68">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ39" s="53">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.9625</v>
       </c>
     </row>
-    <row r="40" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>54</v>
       </c>
@@ -6855,63 +6851,63 @@
       <c r="AU40" s="33"/>
       <c r="AV40" s="43"/>
       <c r="AW40" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX40" s="33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AY40" s="33">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1595</v>
       </c>
-      <c r="AZ40" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="AZ40" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
       <c r="BA40" s="34">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BB40" s="34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BC40" s="34">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BD40" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE40" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF40" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC40" s="34">
-        <f>IF(B40="Python",AT40*AO40/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD40" s="80" t="str">
-        <f>IF(B40="Julia",AU40*AY40/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE40" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF40" s="34">
-        <f t="shared" si="15"/>
         <v>11.9625</v>
       </c>
       <c r="BG40" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH40" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI40" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI40" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ40" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.9625</v>
       </c>
     </row>
-    <row r="41" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>55</v>
       </c>
@@ -6981,63 +6977,63 @@
       <c r="AU41" s="33"/>
       <c r="AV41" s="43"/>
       <c r="AW41" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX41" s="33">
-        <f t="shared" ref="AX41:AX72" si="19">AW35*24</f>
+        <f t="shared" ref="AX41:AX72" si="23">AW35*24</f>
         <v>0</v>
       </c>
       <c r="AY41" s="33">
-        <f t="shared" ref="AY41:AY72" si="20">AY35+SUM(AF41:AH41,AL41:AM41)-AN41</f>
+        <f t="shared" ref="AY41:AY72" si="24">AY35+SUM(AF41:AH41,AL41:AM41)-AN41</f>
         <v>1595</v>
       </c>
-      <c r="AZ41" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="AZ41" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
       <c r="BA41" s="34">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="BB41" s="34">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BC41" s="34">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BD41" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE41" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF41" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC41" s="34">
-        <f>IF(B41="Python",AT41*AO41/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD41" s="80" t="str">
-        <f>IF(B41="Julia",AU41*AY41/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE41" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF41" s="34">
-        <f t="shared" si="15"/>
         <v>11.9625</v>
       </c>
       <c r="BG41" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH41" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI41" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI41" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ41" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.9625</v>
       </c>
     </row>
-    <row r="42" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>56</v>
       </c>
@@ -7107,63 +7103,63 @@
       <c r="AU42" s="33"/>
       <c r="AV42" s="43"/>
       <c r="AW42" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX42" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY42" s="33">
+        <f t="shared" si="24"/>
+        <v>1595</v>
+      </c>
+      <c r="AZ42" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA42" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB42" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY42" s="33">
+      <c r="BC42" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>1595</v>
-      </c>
-      <c r="AZ42" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA42" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB42" s="34">
+        <v/>
+      </c>
+      <c r="BD42" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE42" s="61">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF42" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC42" s="34" t="str">
-        <f>IF(B42="Python",AT42*AO42/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD42" s="80" t="str">
-        <f>IF(B42="Julia",AU42*AY42/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE42" s="77">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF42" s="34">
-        <f t="shared" si="15"/>
         <v>11.9625</v>
       </c>
       <c r="BG42" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH42" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI42" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI42" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ42" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.9625</v>
       </c>
     </row>
-    <row r="43" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>57</v>
       </c>
@@ -7233,63 +7229,63 @@
       <c r="AU43" s="33"/>
       <c r="AV43" s="43"/>
       <c r="AW43" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX43" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY43" s="33">
+        <f t="shared" si="24"/>
+        <v>1595</v>
+      </c>
+      <c r="AZ43" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA43" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB43" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY43" s="33">
+      <c r="BC43" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>1595</v>
-      </c>
-      <c r="AZ43" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA43" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB43" s="34">
+        <v/>
+      </c>
+      <c r="BD43" s="64">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE43" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF43" s="34" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC43" s="34" t="str">
-        <f>IF(B43="Python",AT43*AO43/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD43" s="80">
-        <f>IF(B43="Julia",AU43*AY43/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE43" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF43" s="34" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG43" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH43" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI43" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI43" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ43" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>58</v>
       </c>
@@ -7359,63 +7355,63 @@
       <c r="AU44" s="20"/>
       <c r="AV44" s="44"/>
       <c r="AW44" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX44" s="20">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY44" s="20">
+        <f t="shared" si="24"/>
+        <v>1595</v>
+      </c>
+      <c r="AZ44" s="21" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA44" s="21">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB44" s="21">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY44" s="20">
+      <c r="BC44" s="21" t="str">
         <f t="shared" si="20"/>
-        <v>1595</v>
-      </c>
-      <c r="AZ44" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA44" s="21">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB44" s="21">
+        <v/>
+      </c>
+      <c r="BD44" s="21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE44" s="62" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF44" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC44" s="21" t="str">
-        <f>IF(B44="Python",AT44*AO44/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD44" s="21">
-        <f>IF(B44="Julia",AU44*AY44/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE44" s="78" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF44" s="21" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG44" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH44" s="50">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI44" s="87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI44" s="70">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ44" s="52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>53</v>
       </c>
@@ -7485,63 +7481,63 @@
       <c r="AU45" s="16"/>
       <c r="AV45" s="42"/>
       <c r="AW45" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX45" s="16">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY45" s="16">
+        <f t="shared" si="24"/>
+        <v>1580</v>
+      </c>
+      <c r="AZ45" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA45" s="17">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB45" s="17">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY45" s="16">
+      <c r="BC45" s="17" t="str">
         <f t="shared" si="20"/>
-        <v>1580</v>
-      </c>
-      <c r="AZ45" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA45" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB45" s="17">
+        <v/>
+      </c>
+      <c r="BD45" s="17" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE45" s="60">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF45" s="17">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC45" s="17" t="str">
-        <f>IF(B45="Python",AT45*AO45/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD45" s="17" t="str">
-        <f>IF(B45="Julia",AU45*AY45/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE45" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF45" s="17">
-        <f t="shared" si="15"/>
         <v>11.85</v>
       </c>
       <c r="BG45" s="17" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH45" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI45" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI45" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ45" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.85</v>
       </c>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>54</v>
       </c>
@@ -7611,63 +7607,63 @@
       <c r="AU46" s="33"/>
       <c r="AV46" s="43"/>
       <c r="AW46" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX46" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY46" s="33">
+        <f t="shared" si="24"/>
+        <v>1580</v>
+      </c>
+      <c r="AZ46" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA46" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB46" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY46" s="33">
+      <c r="BC46" s="34">
         <f t="shared" si="20"/>
-        <v>1580</v>
-      </c>
-      <c r="AZ46" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA46" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB46" s="34">
+        <v>0</v>
+      </c>
+      <c r="BD46" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE46" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF46" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC46" s="34">
-        <f>IF(B46="Python",AT46*AO46/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD46" s="80" t="str">
-        <f>IF(B46="Julia",AU46*AY46/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE46" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF46" s="34">
-        <f t="shared" si="15"/>
         <v>11.85</v>
       </c>
       <c r="BG46" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH46" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI46" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI46" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ46" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.85</v>
       </c>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>55</v>
       </c>
@@ -7737,63 +7733,63 @@
       <c r="AU47" s="33"/>
       <c r="AV47" s="43"/>
       <c r="AW47" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX47" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY47" s="33">
+        <f t="shared" si="24"/>
+        <v>1580</v>
+      </c>
+      <c r="AZ47" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA47" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB47" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY47" s="33">
+      <c r="BC47" s="34">
         <f t="shared" si="20"/>
-        <v>1580</v>
-      </c>
-      <c r="AZ47" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA47" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB47" s="34">
+        <v>0</v>
+      </c>
+      <c r="BD47" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE47" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF47" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC47" s="34">
-        <f>IF(B47="Python",AT47*AO47/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD47" s="80" t="str">
-        <f>IF(B47="Julia",AU47*AY47/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE47" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF47" s="34">
-        <f t="shared" si="15"/>
         <v>11.85</v>
       </c>
       <c r="BG47" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH47" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI47" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI47" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ47" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.85</v>
       </c>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
@@ -7863,63 +7859,63 @@
       <c r="AU48" s="33"/>
       <c r="AV48" s="43"/>
       <c r="AW48" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX48" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY48" s="33">
+        <f t="shared" si="24"/>
+        <v>1580</v>
+      </c>
+      <c r="AZ48" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA48" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB48" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY48" s="33">
+      <c r="BC48" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>1580</v>
-      </c>
-      <c r="AZ48" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA48" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB48" s="34">
+        <v/>
+      </c>
+      <c r="BD48" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE48" s="61">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF48" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC48" s="34" t="str">
-        <f>IF(B48="Python",AT48*AO48/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD48" s="80" t="str">
-        <f>IF(B48="Julia",AU48*AY48/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE48" s="77">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF48" s="34">
-        <f t="shared" si="15"/>
         <v>11.85</v>
       </c>
       <c r="BG48" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH48" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI48" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI48" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ48" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.85</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -7989,63 +7985,63 @@
       <c r="AU49" s="33"/>
       <c r="AV49" s="43"/>
       <c r="AW49" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX49" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY49" s="33">
+        <f t="shared" si="24"/>
+        <v>1580</v>
+      </c>
+      <c r="AZ49" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA49" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB49" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY49" s="33">
+      <c r="BC49" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>1580</v>
-      </c>
-      <c r="AZ49" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA49" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB49" s="34">
+        <v/>
+      </c>
+      <c r="BD49" s="64">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE49" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF49" s="34" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC49" s="34" t="str">
-        <f>IF(B49="Python",AT49*AO49/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD49" s="80">
-        <f>IF(B49="Julia",AU49*AY49/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE49" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF49" s="34" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG49" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH49" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI49" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI49" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ49" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>58</v>
       </c>
@@ -8115,63 +8111,63 @@
       <c r="AU50" s="20"/>
       <c r="AV50" s="44"/>
       <c r="AW50" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX50" s="20">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY50" s="20">
+        <f t="shared" si="24"/>
+        <v>1580</v>
+      </c>
+      <c r="AZ50" s="21" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA50" s="21">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB50" s="21">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY50" s="20">
+      <c r="BC50" s="21" t="str">
         <f t="shared" si="20"/>
-        <v>1580</v>
-      </c>
-      <c r="AZ50" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA50" s="21">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB50" s="21">
+        <v/>
+      </c>
+      <c r="BD50" s="21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE50" s="62" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF50" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC50" s="21" t="str">
-        <f>IF(B50="Python",AT50*AO50/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD50" s="21">
-        <f>IF(B50="Julia",AU50*AY50/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE50" s="78" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF50" s="21" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG50" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH50" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI50" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI50" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ50" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
@@ -8241,63 +8237,63 @@
       <c r="AU51" s="16"/>
       <c r="AV51" s="42"/>
       <c r="AW51" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX51" s="16">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY51" s="16">
+        <f t="shared" si="24"/>
+        <v>1565</v>
+      </c>
+      <c r="AZ51" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA51" s="17">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB51" s="17">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY51" s="16">
+      <c r="BC51" s="17" t="str">
         <f t="shared" si="20"/>
-        <v>1565</v>
-      </c>
-      <c r="AZ51" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA51" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB51" s="17">
+        <v/>
+      </c>
+      <c r="BD51" s="17" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE51" s="60">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF51" s="17">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC51" s="17" t="str">
-        <f>IF(B51="Python",AT51*AO51/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD51" s="17" t="str">
-        <f>IF(B51="Julia",AU51*AY51/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE51" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF51" s="17">
-        <f t="shared" si="15"/>
         <v>11.737500000000001</v>
       </c>
       <c r="BG51" s="17" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH51" s="48">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI51" s="85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI51" s="68">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ51" s="53">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>54</v>
       </c>
@@ -8367,63 +8363,63 @@
       <c r="AU52" s="33"/>
       <c r="AV52" s="43"/>
       <c r="AW52" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX52" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY52" s="33">
+        <f t="shared" si="24"/>
+        <v>1565</v>
+      </c>
+      <c r="AZ52" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA52" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB52" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY52" s="33">
+      <c r="BC52" s="34">
         <f t="shared" si="20"/>
-        <v>1565</v>
-      </c>
-      <c r="AZ52" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA52" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB52" s="34">
+        <v>0</v>
+      </c>
+      <c r="BD52" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE52" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF52" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC52" s="34">
-        <f>IF(B52="Python",AT52*AO52/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD52" s="80" t="str">
-        <f>IF(B52="Julia",AU52*AY52/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE52" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF52" s="34">
-        <f t="shared" si="15"/>
         <v>11.737500000000001</v>
       </c>
       <c r="BG52" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH52" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI52" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI52" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ52" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>55</v>
       </c>
@@ -8493,63 +8489,63 @@
       <c r="AU53" s="33"/>
       <c r="AV53" s="43"/>
       <c r="AW53" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX53" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY53" s="33">
+        <f t="shared" si="24"/>
+        <v>1565</v>
+      </c>
+      <c r="AZ53" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA53" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB53" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY53" s="33">
+      <c r="BC53" s="34">
         <f t="shared" si="20"/>
-        <v>1565</v>
-      </c>
-      <c r="AZ53" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA53" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB53" s="34">
+        <v>0</v>
+      </c>
+      <c r="BD53" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE53" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF53" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC53" s="34">
-        <f>IF(B53="Python",AT53*AO53/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD53" s="80" t="str">
-        <f>IF(B53="Julia",AU53*AY53/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE53" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF53" s="34">
-        <f t="shared" si="15"/>
         <v>11.737500000000001</v>
       </c>
       <c r="BG53" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH53" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI53" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI53" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ53" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>56</v>
       </c>
@@ -8619,63 +8615,63 @@
       <c r="AU54" s="33"/>
       <c r="AV54" s="43"/>
       <c r="AW54" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX54" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY54" s="33">
+        <f t="shared" si="24"/>
+        <v>1565</v>
+      </c>
+      <c r="AZ54" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA54" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB54" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY54" s="33">
+      <c r="BC54" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>1565</v>
-      </c>
-      <c r="AZ54" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA54" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB54" s="34">
+        <v/>
+      </c>
+      <c r="BD54" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE54" s="61">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF54" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC54" s="34" t="str">
-        <f>IF(B54="Python",AT54*AO54/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD54" s="80" t="str">
-        <f>IF(B54="Julia",AU54*AY54/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE54" s="77">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF54" s="34">
-        <f t="shared" si="15"/>
         <v>11.737500000000001</v>
       </c>
       <c r="BG54" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH54" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI54" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI54" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ54" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>57</v>
       </c>
@@ -8745,63 +8741,63 @@
       <c r="AU55" s="33"/>
       <c r="AV55" s="43"/>
       <c r="AW55" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX55" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY55" s="33">
+        <f t="shared" si="24"/>
+        <v>1565</v>
+      </c>
+      <c r="AZ55" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA55" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB55" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY55" s="33">
+      <c r="BC55" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>1565</v>
-      </c>
-      <c r="AZ55" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA55" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB55" s="34">
+        <v/>
+      </c>
+      <c r="BD55" s="64">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE55" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF55" s="34" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC55" s="34" t="str">
-        <f>IF(B55="Python",AT55*AO55/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD55" s="80">
-        <f>IF(B55="Julia",AU55*AY55/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE55" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF55" s="34" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG55" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH55" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI55" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI55" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ55" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
@@ -8871,63 +8867,63 @@
       <c r="AU56" s="20"/>
       <c r="AV56" s="44"/>
       <c r="AW56" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX56" s="20">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY56" s="20">
+        <f t="shared" si="24"/>
+        <v>1565</v>
+      </c>
+      <c r="AZ56" s="21" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA56" s="21">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB56" s="21">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY56" s="20">
+      <c r="BC56" s="21" t="str">
         <f t="shared" si="20"/>
-        <v>1565</v>
-      </c>
-      <c r="AZ56" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA56" s="21">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB56" s="21">
+        <v/>
+      </c>
+      <c r="BD56" s="21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE56" s="62" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF56" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC56" s="21" t="str">
-        <f>IF(B56="Python",AT56*AO56/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD56" s="21">
-        <f>IF(B56="Julia",AU56*AY56/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE56" s="78" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF56" s="21" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG56" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH56" s="50">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI56" s="87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI56" s="70">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ56" s="52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>53</v>
       </c>
@@ -8997,63 +8993,63 @@
       <c r="AU57" s="16"/>
       <c r="AV57" s="42"/>
       <c r="AW57" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX57" s="16">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY57" s="16">
+        <f t="shared" si="24"/>
+        <v>1550</v>
+      </c>
+      <c r="AZ57" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA57" s="17">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB57" s="17">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY57" s="16">
+      <c r="BC57" s="17" t="str">
         <f t="shared" si="20"/>
-        <v>1550</v>
-      </c>
-      <c r="AZ57" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA57" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB57" s="17">
+        <v/>
+      </c>
+      <c r="BD57" s="17" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE57" s="60">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF57" s="17">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC57" s="17" t="str">
-        <f>IF(B57="Python",AT57*AO57/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD57" s="17" t="str">
-        <f>IF(B57="Julia",AU57*AY57/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE57" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF57" s="17">
-        <f t="shared" si="15"/>
         <v>11.625</v>
       </c>
       <c r="BG57" s="17" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH57" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI57" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI57" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ57" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>54</v>
       </c>
@@ -9123,63 +9119,63 @@
       <c r="AU58" s="33"/>
       <c r="AV58" s="43"/>
       <c r="AW58" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX58" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY58" s="33">
+        <f t="shared" si="24"/>
+        <v>1550</v>
+      </c>
+      <c r="AZ58" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA58" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB58" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY58" s="33">
+      <c r="BC58" s="34">
         <f t="shared" si="20"/>
-        <v>1550</v>
-      </c>
-      <c r="AZ58" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA58" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB58" s="34">
+        <v>0</v>
+      </c>
+      <c r="BD58" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE58" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF58" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC58" s="34">
-        <f>IF(B58="Python",AT58*AO58/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD58" s="80" t="str">
-        <f>IF(B58="Julia",AU58*AY58/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE58" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF58" s="34">
-        <f t="shared" si="15"/>
         <v>11.625</v>
       </c>
       <c r="BG58" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH58" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI58" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI58" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ58" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>55</v>
       </c>
@@ -9249,63 +9245,63 @@
       <c r="AU59" s="33"/>
       <c r="AV59" s="43"/>
       <c r="AW59" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX59" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY59" s="33">
+        <f t="shared" si="24"/>
+        <v>1550</v>
+      </c>
+      <c r="AZ59" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA59" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB59" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY59" s="33">
+      <c r="BC59" s="34">
         <f t="shared" si="20"/>
-        <v>1550</v>
-      </c>
-      <c r="AZ59" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA59" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB59" s="34">
+        <v>0</v>
+      </c>
+      <c r="BD59" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE59" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF59" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC59" s="34">
-        <f>IF(B59="Python",AT59*AO59/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD59" s="80" t="str">
-        <f>IF(B59="Julia",AU59*AY59/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE59" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF59" s="34">
-        <f t="shared" si="15"/>
         <v>11.625</v>
       </c>
       <c r="BG59" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH59" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI59" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI59" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ59" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="60" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>56</v>
       </c>
@@ -9375,63 +9371,63 @@
       <c r="AU60" s="33"/>
       <c r="AV60" s="43"/>
       <c r="AW60" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX60" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY60" s="33">
+        <f t="shared" si="24"/>
+        <v>1550</v>
+      </c>
+      <c r="AZ60" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA60" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB60" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY60" s="33">
+      <c r="BC60" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>1550</v>
-      </c>
-      <c r="AZ60" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA60" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB60" s="34">
+        <v/>
+      </c>
+      <c r="BD60" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE60" s="61">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF60" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC60" s="34" t="str">
-        <f>IF(B60="Python",AT60*AO60/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD60" s="80" t="str">
-        <f>IF(B60="Julia",AU60*AY60/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE60" s="77">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF60" s="34">
-        <f t="shared" si="15"/>
         <v>11.625</v>
       </c>
       <c r="BG60" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH60" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI60" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI60" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ60" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>57</v>
       </c>
@@ -9501,63 +9497,63 @@
       <c r="AU61" s="33"/>
       <c r="AV61" s="43"/>
       <c r="AW61" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX61" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY61" s="33">
+        <f t="shared" si="24"/>
+        <v>1550</v>
+      </c>
+      <c r="AZ61" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA61" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB61" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY61" s="33">
+      <c r="BC61" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>1550</v>
-      </c>
-      <c r="AZ61" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA61" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB61" s="34">
+        <v/>
+      </c>
+      <c r="BD61" s="64">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE61" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF61" s="34" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC61" s="34" t="str">
-        <f>IF(B61="Python",AT61*AO61/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD61" s="80">
-        <f>IF(B61="Julia",AU61*AY61/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE61" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF61" s="34" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG61" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH61" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI61" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI61" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ61" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>58</v>
       </c>
@@ -9627,63 +9623,63 @@
       <c r="AU62" s="20"/>
       <c r="AV62" s="44"/>
       <c r="AW62" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX62" s="20">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY62" s="20">
+        <f t="shared" si="24"/>
+        <v>1550</v>
+      </c>
+      <c r="AZ62" s="21" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA62" s="21">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB62" s="21">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY62" s="20">
+      <c r="BC62" s="21" t="str">
         <f t="shared" si="20"/>
-        <v>1550</v>
-      </c>
-      <c r="AZ62" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA62" s="21">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB62" s="21">
+        <v/>
+      </c>
+      <c r="BD62" s="21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BE62" s="62" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF62" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC62" s="21" t="str">
-        <f>IF(B62="Python",AT62*AO62/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD62" s="21">
-        <f>IF(B62="Julia",AU62*AY62/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE62" s="78" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF62" s="21" t="str">
-        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="BG62" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH62" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI62" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI62" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ62" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>53</v>
       </c>
@@ -9753,63 +9749,63 @@
       <c r="AU63" s="16"/>
       <c r="AV63" s="42"/>
       <c r="AW63" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX63" s="16">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY63" s="16">
+        <f t="shared" si="24"/>
+        <v>1535</v>
+      </c>
+      <c r="AZ63" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA63" s="17">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB63" s="17">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY63" s="16">
+      <c r="BC63" s="17" t="str">
         <f t="shared" si="20"/>
-        <v>1535</v>
-      </c>
-      <c r="AZ63" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA63" s="17">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB63" s="17">
+        <v/>
+      </c>
+      <c r="BD63" s="17" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE63" s="60">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF63" s="17">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC63" s="17" t="str">
-        <f>IF(B63="Python",AT63*AO63/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD63" s="17" t="str">
-        <f>IF(B63="Julia",AU63*AY63/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE63" s="76">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF63" s="17">
-        <f t="shared" si="15"/>
         <v>11.512499999999999</v>
       </c>
       <c r="BG63" s="17" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH63" s="48">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI63" s="85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI63" s="68">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ63" s="53">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>54</v>
       </c>
@@ -9879,63 +9875,63 @@
       <c r="AU64" s="33"/>
       <c r="AV64" s="43"/>
       <c r="AW64" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX64" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY64" s="33">
+        <f t="shared" si="24"/>
+        <v>1535</v>
+      </c>
+      <c r="AZ64" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA64" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB64" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY64" s="33">
+      <c r="BC64" s="34">
         <f t="shared" si="20"/>
-        <v>1535</v>
-      </c>
-      <c r="AZ64" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA64" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB64" s="34">
+        <v>0</v>
+      </c>
+      <c r="BD64" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE64" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF64" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC64" s="34">
-        <f>IF(B64="Python",AT64*AO64/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD64" s="80" t="str">
-        <f>IF(B64="Julia",AU64*AY64/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE64" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF64" s="34">
-        <f t="shared" si="15"/>
         <v>11.512499999999999</v>
       </c>
       <c r="BG64" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH64" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI64" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI64" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ64" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>55</v>
       </c>
@@ -10005,63 +10001,63 @@
       <c r="AU65" s="33"/>
       <c r="AV65" s="43"/>
       <c r="AW65" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX65" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY65" s="33">
+        <f t="shared" si="24"/>
+        <v>1535</v>
+      </c>
+      <c r="AZ65" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA65" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB65" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY65" s="33">
+      <c r="BC65" s="34">
         <f t="shared" si="20"/>
-        <v>1535</v>
-      </c>
-      <c r="AZ65" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA65" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB65" s="34">
+        <v>0</v>
+      </c>
+      <c r="BD65" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE65" s="61" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="BF65" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC65" s="34">
-        <f>IF(B65="Python",AT65*AO65/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD65" s="80" t="str">
-        <f>IF(B65="Julia",AU65*AY65/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE65" s="77" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BF65" s="34">
-        <f t="shared" si="15"/>
         <v>11.512499999999999</v>
       </c>
       <c r="BG65" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH65" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI65" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI65" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ65" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>56</v>
       </c>
@@ -10131,63 +10127,63 @@
       <c r="AU66" s="33"/>
       <c r="AV66" s="43"/>
       <c r="AW66" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX66" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY66" s="33">
+        <f t="shared" si="24"/>
+        <v>1535</v>
+      </c>
+      <c r="AZ66" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA66" s="34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BB66" s="34">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AY66" s="33">
+      <c r="BC66" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>1535</v>
-      </c>
-      <c r="AZ66" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA66" s="34">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BB66" s="34">
+        <v/>
+      </c>
+      <c r="BD66" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="BE66" s="61">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BF66" s="34">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BC66" s="34" t="str">
-        <f>IF(B66="Python",AT66*AO66/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD66" s="80" t="str">
-        <f>IF(B66="Julia",AU66*AY66/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE66" s="77">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF66" s="34">
-        <f t="shared" si="15"/>
         <v>11.512499999999999</v>
       </c>
       <c r="BG66" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="BH66" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI66" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI66" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ66" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>57</v>
       </c>
@@ -10257,63 +10253,63 @@
       <c r="AU67" s="33"/>
       <c r="AV67" s="43"/>
       <c r="AW67" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AX67" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AY67" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>1535</v>
       </c>
-      <c r="AZ67" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="AZ67" s="34" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
       </c>
       <c r="BA67" s="34">
-        <f t="shared" ref="BA67:BA80" si="21">AJ67/AO67</f>
+        <f t="shared" ref="BA67:BA80" si="25">AJ67/AO67</f>
         <v>0</v>
       </c>
       <c r="BB67" s="34">
-        <f t="shared" ref="BB67:BB80" si="22">AI67*24</f>
+        <f t="shared" ref="BB67:BB80" si="26">AI67*24</f>
         <v>0</v>
       </c>
       <c r="BC67" s="34" t="str">
-        <f>IF(B67="Python",AT67*AO67/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD67" s="80">
-        <f>IF(B67="Julia",AU67*AY67/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE67" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="BC67:BC80" si="27">IF(B67="Python",AT67*AO67/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD67" s="64">
+        <f t="shared" ref="BD67:BD80" si="28">IF(B67="Julia",AU67*AY67/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BE67" s="61" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF67" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG67" s="34">
-        <f t="shared" ref="BG67:BG80" si="23">IF(B67="Julia",AV67*AY67,"")</f>
+        <f t="shared" ref="BG67:BG80" si="29">IF(B67="Julia",AV67*AY67,"")</f>
         <v>0</v>
       </c>
       <c r="BH67" s="49">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI67" s="86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BI67" s="69">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ67" s="51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>58</v>
       </c>
@@ -10383,63 +10379,63 @@
       <c r="AU68" s="20"/>
       <c r="AV68" s="44"/>
       <c r="AW68" s="19">
-        <f t="shared" ref="AW68:AW80" si="24">AS68*I68*AY68/1000</f>
+        <f t="shared" ref="AW68:AW80" si="30">AS68*I68*AY68/1000</f>
         <v>0</v>
       </c>
       <c r="AX68" s="20">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AY68" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>1535</v>
       </c>
-      <c r="AZ68" s="21">
-        <f t="shared" ref="AZ68:AZ80" si="25">IFERROR(AJ68/AY68,0)</f>
-        <v>0</v>
+      <c r="AZ68" s="21" t="e">
+        <f t="shared" ref="AZ68:AZ80" si="31">IF(ISBLANK(AJ68),NA(),IFERROR(AJ68/AY68,0))</f>
+        <v>#N/A</v>
       </c>
       <c r="BA68" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BB68" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC68" s="21" t="str">
-        <f>IF(B68="Python",AT68*AO68/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BD68" s="21">
-        <f>IF(B68="Julia",AU68*AY68/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE68" s="78" t="str">
-        <f t="shared" ref="BE68:BE80" si="26">IF(B68="No MPC", AS68*I68*AY68/1000,"")</f>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BE68" s="62" t="str">
+        <f t="shared" ref="BE68:BE80" si="32">IF(B68="No MPC", AS68*I68*AY68/1000,"")</f>
         <v/>
       </c>
       <c r="BF68" s="21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG68" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BH68" s="50">
-        <f t="shared" ref="BH68:BH80" si="27">IF(BC68&lt;&gt;"",BC68/0.000385,IF(BD68&lt;&gt;"",BD68/0.000385,BE68/0.000385))</f>
-        <v>0</v>
-      </c>
-      <c r="BI68" s="87">
-        <f t="shared" ref="BI68:BI74" si="28">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
+        <f t="shared" ref="BH68:BH80" si="33">IF(BC68&lt;&gt;"",BC68/0.000385,IF(BD68&lt;&gt;"",BD68/0.000385,BE68/0.000385))</f>
+        <v>0</v>
+      </c>
+      <c r="BI68" s="70">
+        <f t="shared" ref="BI68:BI74" si="34">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
         <v>0</v>
       </c>
       <c r="BJ68" s="52">
-        <f t="shared" ref="BJ68:BJ80" si="29">IF(BF68&lt;&gt;"",BF68,BG68)</f>
+        <f t="shared" ref="BJ68:BJ80" si="35">IF(BF68&lt;&gt;"",BF68,BG68)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>53</v>
       </c>
@@ -10509,63 +10505,63 @@
       <c r="AU69" s="16"/>
       <c r="AV69" s="42"/>
       <c r="AW69" s="15">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AX69" s="16">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY69" s="16">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AX69" s="16">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AY69" s="16">
-        <f t="shared" si="20"/>
         <v>1520</v>
       </c>
-      <c r="AZ69" s="17">
+      <c r="AZ69" s="17" t="e">
+        <f t="shared" si="31"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA69" s="17">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA69" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB69" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC69" s="17" t="str">
-        <f>IF(B69="Python",AT69*AO69/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BD69" s="17" t="str">
-        <f>IF(B69="Julia",AU69*AY69/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE69" s="76">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="BE69" s="60">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BF69" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.4</v>
       </c>
       <c r="BG69" s="17" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BH69" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI69" s="86">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI69" s="69">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BJ69" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="70" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>54</v>
       </c>
@@ -10635,63 +10631,63 @@
       <c r="AU70" s="33"/>
       <c r="AV70" s="43"/>
       <c r="AW70" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AX70" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY70" s="33">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AX70" s="33">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AY70" s="33">
-        <f t="shared" si="20"/>
         <v>1520</v>
       </c>
-      <c r="AZ70" s="34">
+      <c r="AZ70" s="34" t="e">
+        <f t="shared" si="31"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA70" s="34">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA70" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB70" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC70" s="34">
-        <f>IF(B70="Python",AT70*AO70/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD70" s="80" t="str">
-        <f>IF(B70="Julia",AU70*AY70/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE70" s="77" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BD70" s="64" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="BE70" s="61" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BF70" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.4</v>
       </c>
       <c r="BG70" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BH70" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI70" s="86">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI70" s="69">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BJ70" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="71" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>55</v>
       </c>
@@ -10761,63 +10757,63 @@
       <c r="AU71" s="33"/>
       <c r="AV71" s="43"/>
       <c r="AW71" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AX71" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY71" s="33">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AX71" s="33">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AY71" s="33">
-        <f t="shared" si="20"/>
         <v>1520</v>
       </c>
-      <c r="AZ71" s="34">
+      <c r="AZ71" s="34" t="e">
+        <f t="shared" si="31"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA71" s="34">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA71" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB71" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC71" s="34">
-        <f>IF(B71="Python",AT71*AO71/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD71" s="80" t="str">
-        <f>IF(B71="Julia",AU71*AY71/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE71" s="77" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BD71" s="64" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="BE71" s="61" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BF71" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.4</v>
       </c>
       <c r="BG71" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BH71" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI71" s="86">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI71" s="69">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BJ71" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="72" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>56</v>
       </c>
@@ -10887,63 +10883,63 @@
       <c r="AU72" s="33"/>
       <c r="AV72" s="43"/>
       <c r="AW72" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AX72" s="33">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AY72" s="33">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AX72" s="33">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="AY72" s="33">
-        <f t="shared" si="20"/>
         <v>1520</v>
       </c>
-      <c r="AZ72" s="34">
+      <c r="AZ72" s="34" t="e">
+        <f t="shared" si="31"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA72" s="34">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA72" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB72" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC72" s="34" t="str">
-        <f>IF(B72="Python",AT72*AO72/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD72" s="80" t="str">
-        <f>IF(B72="Julia",AU72*AY72/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE72" s="77">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="BD72" s="64" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="BE72" s="61">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BF72" s="34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.4</v>
       </c>
       <c r="BG72" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BH72" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI72" s="86">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI72" s="69">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BJ72" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="73" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>57</v>
       </c>
@@ -11013,63 +11009,63 @@
       <c r="AU73" s="33"/>
       <c r="AV73" s="43"/>
       <c r="AW73" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AX73" s="33">
-        <f t="shared" ref="AX73:AX104" si="30">AW67*24</f>
+        <f t="shared" ref="AX73:AX80" si="36">AW67*24</f>
         <v>0</v>
       </c>
       <c r="AY73" s="33">
-        <f t="shared" ref="AY73:AY104" si="31">AY67+SUM(AF73:AH73,AL73:AM73)-AN73</f>
+        <f t="shared" ref="AY73:AY80" si="37">AY67+SUM(AF73:AH73,AL73:AM73)-AN73</f>
         <v>1520</v>
       </c>
-      <c r="AZ73" s="34">
+      <c r="AZ73" s="34" t="e">
+        <f t="shared" si="31"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA73" s="34">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA73" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB73" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC73" s="34" t="str">
-        <f>IF(B73="Python",AT73*AO73/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD73" s="80">
-        <f>IF(B73="Julia",AU73*AY73/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE73" s="77" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="BD73" s="64">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BE73" s="61" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BF73" s="34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG73" s="34">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BH73" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI73" s="86">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI73" s="69">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BJ73" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>58</v>
       </c>
@@ -11139,63 +11135,63 @@
       <c r="AU74" s="20"/>
       <c r="AV74" s="44"/>
       <c r="AW74" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AX74" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AY74" s="20">
+        <f t="shared" si="37"/>
+        <v>1520</v>
+      </c>
+      <c r="AZ74" s="21" t="e">
         <f t="shared" si="31"/>
-        <v>1520</v>
-      </c>
-      <c r="AZ74" s="21">
+        <v>#N/A</v>
+      </c>
+      <c r="BA74" s="21">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA74" s="21">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB74" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC74" s="21" t="str">
-        <f>IF(B74="Python",AT74*AO74/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BD74" s="21">
-        <f>IF(B74="Julia",AU74*AY74/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE74" s="78" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BE74" s="62" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BF74" s="21" t="str">
-        <f t="shared" ref="BF74:BF80" si="32">IF(O74&lt;1.5, IF(B74&lt;&gt;"Julia",((3-O74)*AY74)/400, ""),0)</f>
+        <f t="shared" ref="BF74:BF80" si="38">IF(O74&lt;1.5, IF(B74&lt;&gt;"Julia",((3-O74)*AY74)/400, ""),0)</f>
         <v/>
       </c>
       <c r="BG74" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BH74" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI74" s="86">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI74" s="69">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BJ74" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>53</v>
       </c>
@@ -11265,60 +11261,60 @@
       <c r="AU75" s="4"/>
       <c r="AV75" s="25"/>
       <c r="AW75" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AX75" s="16">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AY75" s="16">
+        <f t="shared" si="37"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ75" s="17" t="e">
         <f t="shared" si="31"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ75" s="17">
+        <v>#N/A</v>
+      </c>
+      <c r="BA75" s="17">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA75" s="17">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB75" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC75" s="17" t="str">
-        <f>IF(B75="Python",AT75*AO75/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BD75" s="17" t="str">
-        <f>IF(B75="Julia",AU75*AY75/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE75" s="76">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="BE75" s="60">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BF75" s="17">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>11.2875</v>
       </c>
       <c r="BG75" s="17" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BH75" s="48">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI75" s="82"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI75" s="65"/>
       <c r="BJ75" s="53">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>11.2875</v>
       </c>
     </row>
-    <row r="76" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>54</v>
       </c>
@@ -11388,60 +11384,60 @@
       <c r="AU76" s="30"/>
       <c r="AV76" s="2"/>
       <c r="AW76" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AX76" s="33">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AY76" s="33">
+        <f t="shared" si="37"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ76" s="34" t="e">
         <f t="shared" si="31"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ76" s="34">
+        <v>#N/A</v>
+      </c>
+      <c r="BA76" s="34">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA76" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB76" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC76" s="34">
-        <f>IF(B76="Python",AT76*AO76/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD76" s="80" t="str">
-        <f>IF(B76="Julia",AU76*AY76/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE76" s="77" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BD76" s="64" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="BE76" s="61" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BF76" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>11.2875</v>
       </c>
       <c r="BG76" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BH76" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI76" s="83"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI76" s="66"/>
       <c r="BJ76" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>11.2875</v>
       </c>
     </row>
-    <row r="77" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>55</v>
       </c>
@@ -11511,60 +11507,60 @@
       <c r="AU77" s="33"/>
       <c r="AV77" s="43"/>
       <c r="AW77" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AX77" s="33">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AY77" s="33">
+        <f t="shared" si="37"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ77" s="34" t="e">
         <f t="shared" si="31"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ77" s="34">
+        <v>#N/A</v>
+      </c>
+      <c r="BA77" s="34">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA77" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB77" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC77" s="34">
-        <f>IF(B77="Python",AT77*AO77/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BD77" s="80" t="str">
-        <f>IF(B77="Julia",AU77*AY77/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE77" s="77" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BD77" s="64" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="BE77" s="61" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BF77" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>11.2875</v>
       </c>
       <c r="BG77" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BH77" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI77" s="83"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI77" s="66"/>
       <c r="BJ77" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>11.2875</v>
       </c>
     </row>
-    <row r="78" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>56</v>
       </c>
@@ -11634,60 +11630,60 @@
       <c r="AU78" s="33"/>
       <c r="AV78" s="43"/>
       <c r="AW78" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AX78" s="33">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AY78" s="33">
+        <f t="shared" si="37"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ78" s="34" t="e">
         <f t="shared" si="31"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ78" s="34">
+        <v>#N/A</v>
+      </c>
+      <c r="BA78" s="34">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA78" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB78" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC78" s="34" t="str">
-        <f>IF(B78="Python",AT78*AO78/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD78" s="80" t="str">
-        <f>IF(B78="Julia",AU78*AY78/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE78" s="77">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="BD78" s="64" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="BE78" s="61">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BF78" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>11.2875</v>
       </c>
       <c r="BG78" s="34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BH78" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI78" s="83"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI78" s="66"/>
       <c r="BJ78" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>11.2875</v>
       </c>
     </row>
-    <row r="79" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>57</v>
       </c>
@@ -11757,60 +11753,60 @@
       <c r="AU79" s="33"/>
       <c r="AV79" s="43"/>
       <c r="AW79" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AX79" s="33">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AY79" s="33">
+        <f t="shared" si="37"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ79" s="34" t="e">
         <f t="shared" si="31"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ79" s="34">
+        <v>#N/A</v>
+      </c>
+      <c r="BA79" s="34">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA79" s="34">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB79" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC79" s="34" t="str">
-        <f>IF(B79="Python",AT79*AO79/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD79" s="80">
-        <f>IF(B79="Julia",AU79*AY79/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE79" s="77" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="BD79" s="64">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BE79" s="61" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BF79" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="BG79" s="34">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BH79" s="49">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI79" s="83"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI79" s="66"/>
       <c r="BJ79" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>58</v>
       </c>
@@ -11880,56 +11876,56 @@
       <c r="AU80" s="20"/>
       <c r="AV80" s="44"/>
       <c r="AW80" s="19">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AX80" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AY80" s="20">
+        <f t="shared" si="37"/>
+        <v>1505</v>
+      </c>
+      <c r="AZ80" s="21" t="e">
         <f t="shared" si="31"/>
-        <v>1505</v>
-      </c>
-      <c r="AZ80" s="21">
+        <v>#N/A</v>
+      </c>
+      <c r="BA80" s="21">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BA80" s="21">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="BB80" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BC80" s="21" t="str">
-        <f>IF(B80="Python",AT80*AO80/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BD80" s="21">
-        <f>IF(B80="Julia",AU80*AY80/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE80" s="78" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BE80" s="62" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BF80" s="21" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="BG80" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BH80" s="50">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI80" s="84"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BI80" s="67"/>
       <c r="BJ80" s="52">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -11951,17 +11947,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY3:BB80">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="11">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="11">
       <formula>LEN(TRIM(AY3))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW3:AX80">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="2">
       <formula>LEN(TRIM(AW3))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU3:AV80">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>IF($B3 = "Julia", TRUE, FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11971,21 +11967,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12212,21 +12199,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12251,9 +12244,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yl604392\Git\state-space-model\data\MR24-030 Experiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1728AB44-0F33-44D5-B6B8-28AA24DDCA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1456" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C30635D3-09A0-4173-9F39-19F0C3F69858}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1033,9 +1033,9 @@
     <xf numFmtId="165" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1137,14 +1137,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1854,7 +1854,7 @@
         <v>0.1</v>
       </c>
       <c r="AI3" s="16">
-        <v>0</v>
+        <v>6.8242499999999996E-3</v>
       </c>
       <c r="AJ3" s="16">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="AL3" s="16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AM3" s="16">
         <v>0</v>
@@ -1911,10 +1911,10 @@
       </c>
       <c r="BB3" s="17">
         <f>AI3*24</f>
-        <v>0</v>
+        <v>0.16378199999999998</v>
       </c>
       <c r="BC3" s="17" t="str">
-        <f t="shared" ref="BC3:BC34" si="0">IF(B3="Python",AT3*AO3/24/60,"")</f>
+        <f t="shared" ref="BC3" si="0">IF(B3="Python",AT3*AO3/24/60,"")</f>
         <v/>
       </c>
       <c r="BD3" s="17" t="str">
@@ -2047,7 +2047,7 @@
         <v>0.1</v>
       </c>
       <c r="AI4" s="33">
-        <v>0</v>
+        <v>5.2656249999999995E-3</v>
       </c>
       <c r="AJ4" s="33">
         <v>0</v>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="AL4" s="33">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM4" s="33">
         <v>0</v>
@@ -2106,11 +2106,11 @@
       </c>
       <c r="BB4" s="34">
         <f t="shared" ref="BB4:BB34" si="7">AI4*24</f>
-        <v>0</v>
+        <v>0.12637499999999999</v>
       </c>
       <c r="BC4" s="34">
-        <f t="shared" si="0"/>
-        <v>5.3124999999999995E-3</v>
+        <f>IF(B4="Python",AT4*AY4/24/60,"")</f>
+        <v>5.2656249999999995E-3</v>
       </c>
       <c r="BD4" s="64" t="str">
         <f t="shared" si="1"/>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="BH4" s="49">
         <f t="shared" ref="BH4:BH67" si="9">IF(BC4&lt;&gt;"",BC4/0.000385,IF(BD4&lt;&gt;"",BD4/0.000385,BE4/0.000385))</f>
-        <v>13.798701298701298</v>
+        <v>13.676948051948051</v>
       </c>
       <c r="BI4" s="69">
         <f t="shared" ref="BI4:BI67" si="10">IF(BC4&lt;&gt;"",BC4,IF(BD4&lt;&gt;"",BD4,BE4))</f>
-        <v>5.3124999999999995E-3</v>
+        <v>5.2656249999999995E-3</v>
       </c>
       <c r="BJ4" s="51">
         <f t="shared" ref="BJ4:BJ67" si="11">IF(BF4&lt;&gt;"",BF4,BG4)</f>
@@ -2242,7 +2242,7 @@
         <v>0.1</v>
       </c>
       <c r="AI5" s="33">
-        <v>0</v>
+        <v>5.2656249999999995E-3</v>
       </c>
       <c r="AJ5" s="33">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="AL5" s="33">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM5" s="33">
         <v>0</v>
@@ -2301,11 +2301,11 @@
       </c>
       <c r="BB5" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.12637499999999999</v>
       </c>
       <c r="BC5" s="34">
-        <f t="shared" si="0"/>
-        <v>5.3124999999999995E-3</v>
+        <f t="shared" ref="BC5:BC68" si="13">IF(B5="Python",AT5*AY5/24/60,"")</f>
+        <v>5.2656249999999995E-3</v>
       </c>
       <c r="BD5" s="64" t="str">
         <f t="shared" si="1"/>
@@ -2324,11 +2324,11 @@
       </c>
       <c r="BH5" s="49">
         <f t="shared" si="9"/>
-        <v>13.798701298701298</v>
+        <v>13.676948051948051</v>
       </c>
       <c r="BI5" s="69">
         <f t="shared" si="10"/>
-        <v>5.3124999999999995E-3</v>
+        <v>5.2656249999999995E-3</v>
       </c>
       <c r="BJ5" s="51">
         <f t="shared" si="11"/>
@@ -2437,7 +2437,7 @@
         <v>0.1</v>
       </c>
       <c r="AI6" s="33">
-        <v>0</v>
+        <v>8.1385499999999996E-3</v>
       </c>
       <c r="AJ6" s="33">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="AL6" s="33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM6" s="33">
         <v>0</v>
@@ -2494,10 +2494,10 @@
       </c>
       <c r="BB6" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.19532519999999998</v>
       </c>
       <c r="BC6" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD6" s="64" t="str">
@@ -2630,7 +2630,7 @@
         <v>0.1</v>
       </c>
       <c r="AI7" s="33">
-        <v>0</v>
+        <v>6.116549999999988E-3</v>
       </c>
       <c r="AJ7" s="33">
         <v>0</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="AL7" s="33">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AM7" s="33">
         <v>0</v>
@@ -2691,10 +2691,10 @@
       </c>
       <c r="BB7" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.14679719999999971</v>
       </c>
       <c r="BC7" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD7" s="63">
@@ -2706,7 +2706,7 @@
         <v/>
       </c>
       <c r="BF7" s="34" t="str">
-        <f t="shared" ref="BF7:BF8" si="13">IF(IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, "")&lt;0,0,IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, ""))</f>
+        <f t="shared" ref="BF7:BF8" si="14">IF(IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, "")&lt;0,0,IF(B7&lt;&gt;"Julia",((5-O7)*AY7)/400, ""))</f>
         <v/>
       </c>
       <c r="BG7" s="34">
@@ -2828,7 +2828,7 @@
         <v>0.1</v>
       </c>
       <c r="AI8" s="20">
-        <v>0</v>
+        <v>6.520949999999988E-3</v>
       </c>
       <c r="AJ8" s="20">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="AL8" s="20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AM8" s="20">
         <v>0</v>
@@ -2889,10 +2889,10 @@
       </c>
       <c r="BB8" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.15650279999999972</v>
       </c>
       <c r="BC8" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD8" s="63">
@@ -2904,7 +2904,7 @@
         <v/>
       </c>
       <c r="BF8" s="21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="BG8" s="21">
@@ -2937,39 +2937,99 @@
       <c r="D9" s="39">
         <v>1</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5">
+        <v>45450.408518518503</v>
+      </c>
       <c r="F9" s="9"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="15"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="16"/>
+      <c r="H9" s="10">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="I9" s="10">
+        <v>19.2</v>
+      </c>
+      <c r="J9" s="10">
+        <v>99</v>
+      </c>
+      <c r="K9" s="10">
+        <v>16.8</v>
+      </c>
+      <c r="L9" s="10">
+        <v>323</v>
+      </c>
+      <c r="M9" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0.91</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="R9" s="10">
+        <v>2.88</v>
+      </c>
+      <c r="S9" s="10">
+        <v>7.0629999999999997</v>
+      </c>
+      <c r="T9" s="10">
+        <v>103.9</v>
+      </c>
+      <c r="U9" s="10">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="V9" s="10">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="W9" s="10">
+        <v>129.4</v>
+      </c>
+      <c r="X9" s="10">
+        <v>28.6</v>
+      </c>
+      <c r="Y9" s="10">
+        <v>91.1</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>53</v>
+      </c>
+      <c r="AA9" s="27">
+        <v>7.1</v>
+      </c>
+      <c r="AB9" s="15">
+        <v>299</v>
+      </c>
+      <c r="AC9" s="16">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="AD9" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="AE9" s="16">
+        <v>34</v>
+      </c>
+      <c r="AF9" s="16">
+        <v>16.54</v>
+      </c>
+      <c r="AG9" s="16">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="16">
+        <v>0.2</v>
+      </c>
       <c r="AI9" s="16"/>
-      <c r="AJ9" s="16"/>
-      <c r="AK9" s="16"/>
+      <c r="AJ9" s="16">
+        <v>8</v>
+      </c>
+      <c r="AK9" s="16">
+        <v>0</v>
+      </c>
       <c r="AL9" s="16"/>
       <c r="AM9" s="16"/>
       <c r="AN9" s="45">
@@ -2995,30 +3055,30 @@
       <c r="AV9" s="42"/>
       <c r="AW9" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.7156223999999985E-3</v>
       </c>
       <c r="AX9" s="16">
-        <f t="shared" ref="AX9:AX40" si="14">AW3*24</f>
+        <f t="shared" ref="AX9:AX40" si="15">AW3*24</f>
         <v>0.16378199999999998</v>
       </c>
       <c r="AY9" s="16">
         <f>AY3+SUM(AF9:AH9,AL9:AM9)-AN9</f>
-        <v>1670</v>
-      </c>
-      <c r="AZ9" s="17" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>1686.74</v>
+      </c>
+      <c r="AZ9" s="17">
+        <f>IF(ISBLANK(AJ9),NA(),IFERROR(AJ9/AY9,0))</f>
+        <v>4.7428767919181379E-3</v>
       </c>
       <c r="BA9" s="17">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4.7058823529411761E-3</v>
       </c>
       <c r="BB9" s="17">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BC9" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD9" s="17" t="str">
@@ -3027,11 +3087,11 @@
       </c>
       <c r="BE9" s="60">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9.7156223999999985E-3</v>
       </c>
       <c r="BF9" s="17">
         <f>IF(O9&lt;10, IF(B9&lt;&gt;"Julia",((5-O9)*AY9)/400, ""),0)</f>
-        <v>20.875</v>
+        <v>17.246916500000001</v>
       </c>
       <c r="BG9" s="17" t="str">
         <f t="shared" si="2"/>
@@ -3039,15 +3099,15 @@
       </c>
       <c r="BH9" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>25.235382857142856</v>
       </c>
       <c r="BI9" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>9.7156223999999985E-3</v>
       </c>
       <c r="BJ9" s="51">
         <f t="shared" si="11"/>
-        <v>20.875</v>
+        <v>17.246916500000001</v>
       </c>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.25">
@@ -3063,22 +3123,99 @@
       <c r="D10" s="38">
         <v>1</v>
       </c>
-      <c r="E10" s="31"/>
+      <c r="E10" s="31">
+        <v>45450.411412037</v>
+      </c>
       <c r="F10" s="11"/>
       <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="AA10" s="28"/>
-      <c r="AB10" s="18"/>
-      <c r="AC10" s="33"/>
-      <c r="AD10" s="33"/>
-      <c r="AE10" s="33"/>
-      <c r="AF10" s="33"/>
-      <c r="AG10" s="33"/>
-      <c r="AH10" s="33"/>
+      <c r="H10" s="32">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="I10" s="32">
+        <v>15.9</v>
+      </c>
+      <c r="J10">
+        <v>98.8</v>
+      </c>
+      <c r="K10">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="L10">
+        <v>337</v>
+      </c>
+      <c r="M10">
+        <v>1.8</v>
+      </c>
+      <c r="N10">
+        <v>0.49</v>
+      </c>
+      <c r="O10">
+        <v>0.85</v>
+      </c>
+      <c r="P10">
+        <v>0.36</v>
+      </c>
+      <c r="Q10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="R10">
+        <v>2.93</v>
+      </c>
+      <c r="S10">
+        <v>7.0960000000000001</v>
+      </c>
+      <c r="T10">
+        <v>116.1</v>
+      </c>
+      <c r="U10">
+        <v>53</v>
+      </c>
+      <c r="V10">
+        <v>4.71</v>
+      </c>
+      <c r="W10">
+        <v>134</v>
+      </c>
+      <c r="X10">
+        <v>34.6</v>
+      </c>
+      <c r="Y10">
+        <v>101.8</v>
+      </c>
+      <c r="Z10">
+        <v>43</v>
+      </c>
+      <c r="AA10" s="28">
+        <v>7.1349999999999998</v>
+      </c>
+      <c r="AB10" s="18">
+        <v>300</v>
+      </c>
+      <c r="AC10" s="33">
+        <v>0.499</v>
+      </c>
+      <c r="AD10" s="33">
+        <v>7.1</v>
+      </c>
+      <c r="AE10" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF10" s="33">
+        <v>19.440000000000001</v>
+      </c>
+      <c r="AG10" s="33">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="33">
+        <v>0.2</v>
+      </c>
       <c r="AI10" s="33"/>
-      <c r="AJ10" s="33"/>
-      <c r="AK10" s="33"/>
+      <c r="AJ10" s="33">
+        <v>6</v>
+      </c>
+      <c r="AK10" s="33">
+        <v>0</v>
+      </c>
       <c r="AL10" s="33"/>
       <c r="AM10" s="33"/>
       <c r="AN10" s="46">
@@ -3104,30 +3241,30 @@
       <c r="AV10" s="43"/>
       <c r="AW10" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.0595828000000012E-3</v>
       </c>
       <c r="AX10" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.15043679999999998</v>
       </c>
       <c r="AY10" s="33">
-        <f t="shared" ref="AY10:AY40" si="15">AY4+SUM(AF10:AH10,AL10:AM10)-AN10</f>
-        <v>1670</v>
-      </c>
-      <c r="AZ10" s="34" t="e">
+        <f t="shared" ref="AY10:AY40" si="16">AY4+SUM(AF10:AH10,AL10:AM10)-AN10</f>
+        <v>1689.64</v>
+      </c>
+      <c r="AZ10" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>3.5510522951634664E-3</v>
       </c>
       <c r="BA10" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3.5294117647058825E-3</v>
       </c>
       <c r="BB10" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BC10" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD10" s="64" t="str">
@@ -3139,8 +3276,8 @@
         <v/>
       </c>
       <c r="BF10" s="34">
-        <f t="shared" ref="BF10:BF12" si="16">IF(O10&lt;10, IF(B10&lt;&gt;"Julia",((5-O10)*AY10)/400, ""),0)</f>
-        <v>20.875</v>
+        <f t="shared" ref="BF10:BF12" si="17">IF(O10&lt;10, IF(B10&lt;&gt;"Julia",((5-O10)*AY10)/400, ""),0)</f>
+        <v>17.530015000000002</v>
       </c>
       <c r="BG10" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3156,7 +3293,7 @@
       </c>
       <c r="BJ10" s="51">
         <f t="shared" si="11"/>
-        <v>20.875</v>
+        <v>17.530015000000002</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.25">
@@ -3172,23 +3309,99 @@
       <c r="D11" s="38">
         <v>1</v>
       </c>
-      <c r="E11" s="31"/>
+      <c r="E11" s="31">
+        <v>45450.415150462999</v>
+      </c>
       <c r="F11" s="11"/>
       <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="O11" s="54"/>
-      <c r="AA11" s="28"/>
-      <c r="AB11" s="18"/>
-      <c r="AC11" s="33"/>
-      <c r="AD11" s="33"/>
-      <c r="AE11" s="33"/>
-      <c r="AF11" s="33"/>
-      <c r="AG11" s="33"/>
-      <c r="AH11" s="33"/>
+      <c r="H11" s="32">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="I11" s="32">
+        <v>15.9</v>
+      </c>
+      <c r="J11">
+        <v>98.4</v>
+      </c>
+      <c r="K11">
+        <v>16.8</v>
+      </c>
+      <c r="L11">
+        <v>325</v>
+      </c>
+      <c r="M11">
+        <v>1.55</v>
+      </c>
+      <c r="N11">
+        <v>0.51</v>
+      </c>
+      <c r="O11" s="54">
+        <v>0.92</v>
+      </c>
+      <c r="P11">
+        <v>0.34</v>
+      </c>
+      <c r="Q11">
+        <v>2.38</v>
+      </c>
+      <c r="R11">
+        <v>2.83</v>
+      </c>
+      <c r="S11">
+        <v>7.0750000000000002</v>
+      </c>
+      <c r="T11">
+        <v>86.9</v>
+      </c>
+      <c r="U11">
+        <v>52.5</v>
+      </c>
+      <c r="V11">
+        <v>4.74</v>
+      </c>
+      <c r="W11">
+        <v>125.8</v>
+      </c>
+      <c r="X11">
+        <v>24.6</v>
+      </c>
+      <c r="Y11">
+        <v>76.2</v>
+      </c>
+      <c r="Z11">
+        <v>42.5</v>
+      </c>
+      <c r="AA11" s="28">
+        <v>7.1130000000000004</v>
+      </c>
+      <c r="AB11" s="18">
+        <v>299</v>
+      </c>
+      <c r="AC11" s="33">
+        <v>0.495</v>
+      </c>
+      <c r="AD11" s="33">
+        <v>7.1</v>
+      </c>
+      <c r="AE11" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF11" s="33">
+        <v>14.23</v>
+      </c>
+      <c r="AG11" s="33">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="33">
+        <v>0.2</v>
+      </c>
       <c r="AI11" s="33"/>
-      <c r="AJ11" s="33"/>
-      <c r="AK11" s="33"/>
+      <c r="AJ11" s="33">
+        <v>6</v>
+      </c>
+      <c r="AK11" s="33">
+        <v>0</v>
+      </c>
       <c r="AL11" s="33"/>
       <c r="AM11" s="33"/>
       <c r="AN11" s="46">
@@ -3214,30 +3427,30 @@
       <c r="AV11" s="43"/>
       <c r="AW11" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.0347310999999994E-3</v>
       </c>
       <c r="AX11" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.16135559999999999</v>
       </c>
       <c r="AY11" s="33">
-        <f t="shared" si="15"/>
-        <v>1670</v>
-      </c>
-      <c r="AZ11" s="34" t="e">
+        <f t="shared" si="16"/>
+        <v>1684.43</v>
+      </c>
+      <c r="AZ11" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>3.5620358222069187E-3</v>
       </c>
       <c r="BA11" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3.5294117647058825E-3</v>
       </c>
       <c r="BB11" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BC11" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD11" s="64" t="str">
@@ -3249,8 +3462,8 @@
         <v/>
       </c>
       <c r="BF11" s="34">
-        <f t="shared" si="16"/>
-        <v>20.875</v>
+        <f t="shared" si="17"/>
+        <v>17.181186</v>
       </c>
       <c r="BG11" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3266,7 +3479,7 @@
       </c>
       <c r="BJ11" s="51">
         <f t="shared" si="11"/>
-        <v>20.875</v>
+        <v>17.181186</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.25">
@@ -3282,23 +3495,99 @@
       <c r="D12" s="38">
         <v>1</v>
       </c>
-      <c r="E12" s="31"/>
+      <c r="E12" s="31">
+        <v>45450.439641203702</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="O12" s="54"/>
-      <c r="AA12" s="28"/>
-      <c r="AB12" s="18"/>
-      <c r="AC12" s="33"/>
-      <c r="AD12" s="33"/>
-      <c r="AE12" s="33"/>
-      <c r="AF12" s="33"/>
-      <c r="AG12" s="33"/>
-      <c r="AH12" s="33"/>
+      <c r="H12" s="32">
+        <v>25.1</v>
+      </c>
+      <c r="I12" s="32">
+        <v>24.6</v>
+      </c>
+      <c r="J12">
+        <v>98.3</v>
+      </c>
+      <c r="K12">
+        <v>15.1</v>
+      </c>
+      <c r="L12">
+        <v>316</v>
+      </c>
+      <c r="M12">
+        <v>0.42</v>
+      </c>
+      <c r="N12">
+        <v>0.48</v>
+      </c>
+      <c r="O12" s="54">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0.02</v>
+      </c>
+      <c r="Q12">
+        <v>1.87</v>
+      </c>
+      <c r="R12">
+        <v>2.46</v>
+      </c>
+      <c r="S12">
+        <v>7.1150000000000002</v>
+      </c>
+      <c r="T12">
+        <v>117.2</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>4.46</v>
+      </c>
+      <c r="W12">
+        <v>130.6</v>
+      </c>
+      <c r="X12">
+        <v>36.4</v>
+      </c>
+      <c r="Y12">
+        <v>102.8</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="28">
+        <v>7.1529999999999996</v>
+      </c>
+      <c r="AB12" s="18">
+        <v>300</v>
+      </c>
+      <c r="AC12" s="33">
+        <v>6.3E-2</v>
+      </c>
+      <c r="AD12" s="33">
+        <v>7.12</v>
+      </c>
+      <c r="AE12" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF12" s="33">
+        <v>14.91</v>
+      </c>
+      <c r="AG12" s="33">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="33">
+        <v>0.2</v>
+      </c>
       <c r="AI12" s="33"/>
-      <c r="AJ12" s="33"/>
-      <c r="AK12" s="33"/>
+      <c r="AJ12" s="33">
+        <v>10</v>
+      </c>
+      <c r="AK12" s="33">
+        <v>0</v>
+      </c>
       <c r="AL12" s="33"/>
       <c r="AM12" s="33"/>
       <c r="AN12" s="46">
@@ -3324,30 +3613,30 @@
       <c r="AV12" s="43"/>
       <c r="AW12" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.2436111799999998E-2</v>
       </c>
       <c r="AX12" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.19532519999999998</v>
       </c>
       <c r="AY12" s="33">
-        <f t="shared" si="15"/>
-        <v>1670</v>
-      </c>
-      <c r="AZ12" s="34" t="e">
+        <f t="shared" si="16"/>
+        <v>1685.11</v>
+      </c>
+      <c r="AZ12" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>5.9343306965123944E-3</v>
       </c>
       <c r="BA12" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5.8823529411764705E-3</v>
       </c>
       <c r="BB12" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BC12" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD12" s="64" t="str">
@@ -3356,11 +3645,11 @@
       </c>
       <c r="BE12" s="61">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.2436111799999998E-2</v>
       </c>
       <c r="BF12" s="34">
-        <f t="shared" si="16"/>
-        <v>20.875</v>
+        <f t="shared" si="17"/>
+        <v>21.063874999999999</v>
       </c>
       <c r="BG12" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3368,15 +3657,15 @@
       </c>
       <c r="BH12" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>32.30158909090909</v>
       </c>
       <c r="BI12" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1.2436111799999998E-2</v>
       </c>
       <c r="BJ12" s="51">
         <f t="shared" si="11"/>
-        <v>20.875</v>
+        <v>21.063874999999999</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.25">
@@ -3392,39 +3681,99 @@
       <c r="D13" s="38">
         <v>1</v>
       </c>
-      <c r="E13" s="31"/>
+      <c r="E13" s="31">
+        <v>45450.444930555597</v>
+      </c>
       <c r="F13" s="11"/>
       <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="32"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="32"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="18"/>
-      <c r="AC13" s="33"/>
-      <c r="AD13" s="33"/>
-      <c r="AE13" s="33"/>
-      <c r="AF13" s="33"/>
-      <c r="AG13" s="33"/>
-      <c r="AH13" s="33"/>
+      <c r="H13" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="I13" s="32">
+        <v>15.2</v>
+      </c>
+      <c r="J13" s="32">
+        <v>98.7</v>
+      </c>
+      <c r="K13" s="32">
+        <v>17.2</v>
+      </c>
+      <c r="L13" s="32">
+        <v>341</v>
+      </c>
+      <c r="M13" s="32">
+        <v>1.92</v>
+      </c>
+      <c r="N13" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="O13" s="32">
+        <v>1.72</v>
+      </c>
+      <c r="P13" s="32">
+        <v>0.4</v>
+      </c>
+      <c r="Q13" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="R13" s="32">
+        <v>3</v>
+      </c>
+      <c r="S13" s="32">
+        <v>7.0839999999999996</v>
+      </c>
+      <c r="T13" s="32">
+        <v>105.5</v>
+      </c>
+      <c r="U13" s="32">
+        <v>44.2</v>
+      </c>
+      <c r="V13" s="32">
+        <v>4.88</v>
+      </c>
+      <c r="W13" s="32">
+        <v>131.6</v>
+      </c>
+      <c r="X13" s="32">
+        <v>30.5</v>
+      </c>
+      <c r="Y13" s="32">
+        <v>92.5</v>
+      </c>
+      <c r="Z13" s="32">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="AA13" s="28">
+        <v>7.1210000000000004</v>
+      </c>
+      <c r="AB13" s="18">
+        <v>301</v>
+      </c>
+      <c r="AC13" s="33">
+        <v>0.53799999999999992</v>
+      </c>
+      <c r="AD13" s="33">
+        <v>7.1</v>
+      </c>
+      <c r="AE13" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF13" s="33">
+        <v>18.03</v>
+      </c>
+      <c r="AG13" s="33">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="33">
+        <v>0.2</v>
+      </c>
       <c r="AI13" s="33"/>
-      <c r="AJ13" s="33"/>
-      <c r="AK13" s="33"/>
+      <c r="AJ13" s="33">
+        <v>7</v>
+      </c>
+      <c r="AK13" s="33">
+        <v>0</v>
+      </c>
       <c r="AL13" s="33"/>
       <c r="AM13" s="33"/>
       <c r="AN13" s="46">
@@ -3450,43 +3799,43 @@
       <c r="AV13" s="43"/>
       <c r="AW13" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.6983287999999993E-3</v>
       </c>
       <c r="AX13" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.14679719999999999</v>
       </c>
       <c r="AY13" s="33">
-        <f t="shared" si="15"/>
-        <v>1670</v>
-      </c>
-      <c r="AZ13" s="34" t="e">
+        <f t="shared" si="16"/>
+        <v>1688.23</v>
+      </c>
+      <c r="AZ13" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>4.1463544659199282E-3</v>
       </c>
       <c r="BA13" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4.1176470588235297E-3</v>
       </c>
       <c r="BB13" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BC13" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD13" s="64">
-        <f t="shared" si="1"/>
+        <f>IF(B13="Julia",AU13*AY13/24/60,"")</f>
         <v>0</v>
       </c>
       <c r="BE13" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="BF13" s="34" t="str">
-        <f t="shared" ref="BF13:BF73" si="17">IF(O13&lt;1.5, IF(B13&lt;&gt;"Julia",((3-O13)*AY13)/400, ""),0)</f>
-        <v/>
+      <c r="BF13" s="34">
+        <f t="shared" ref="BF13:BF73" si="18">IF(O13&lt;1.5, IF(B13&lt;&gt;"Julia",((3-O13)*AY13)/400, ""),0)</f>
+        <v>0</v>
       </c>
       <c r="BG13" s="34">
         <f t="shared" si="2"/>
@@ -3518,39 +3867,99 @@
       <c r="D14" s="40">
         <v>1</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="8">
+        <v>45450.4586921296</v>
+      </c>
       <c r="F14" s="13"/>
       <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="19"/>
-      <c r="AC14" s="20"/>
-      <c r="AD14" s="20"/>
-      <c r="AE14" s="20"/>
-      <c r="AF14" s="20"/>
-      <c r="AG14" s="20"/>
-      <c r="AH14" s="20"/>
+      <c r="H14" s="14">
+        <v>16.5</v>
+      </c>
+      <c r="I14" s="14">
+        <v>16.2</v>
+      </c>
+      <c r="J14" s="14">
+        <v>98.4</v>
+      </c>
+      <c r="K14" s="14">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="L14" s="14">
+        <v>333</v>
+      </c>
+      <c r="M14" s="14">
+        <v>1.73</v>
+      </c>
+      <c r="N14" s="14">
+        <v>0.49</v>
+      </c>
+      <c r="O14" s="14">
+        <v>0.86</v>
+      </c>
+      <c r="P14" s="14">
+        <v>0.34</v>
+      </c>
+      <c r="Q14" s="14">
+        <v>2.46</v>
+      </c>
+      <c r="R14" s="14">
+        <v>3</v>
+      </c>
+      <c r="S14" s="14">
+        <v>7.077</v>
+      </c>
+      <c r="T14" s="14">
+        <v>108.3</v>
+      </c>
+      <c r="U14" s="14">
+        <v>48.9</v>
+      </c>
+      <c r="V14" s="14">
+        <v>4.7</v>
+      </c>
+      <c r="W14" s="14">
+        <v>133.6</v>
+      </c>
+      <c r="X14" s="14">
+        <v>30.8</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>95</v>
+      </c>
+      <c r="Z14" s="14">
+        <v>39.6</v>
+      </c>
+      <c r="AA14" s="29">
+        <v>7.1150000000000002</v>
+      </c>
+      <c r="AB14" s="19">
+        <v>301</v>
+      </c>
+      <c r="AC14" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="AD14" s="20">
+        <v>7.1</v>
+      </c>
+      <c r="AE14" s="20">
+        <v>34</v>
+      </c>
+      <c r="AF14" s="20">
+        <v>18.68</v>
+      </c>
+      <c r="AG14" s="20">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AI14" s="20"/>
-      <c r="AJ14" s="20"/>
-      <c r="AK14" s="20"/>
+      <c r="AJ14" s="20">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="20">
+        <v>0</v>
+      </c>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
       <c r="AN14" s="47">
@@ -3576,30 +3985,30 @@
       <c r="AV14" s="44"/>
       <c r="AW14" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.2079567999999992E-3</v>
       </c>
       <c r="AX14" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.1565028</v>
       </c>
       <c r="AY14" s="20">
-        <f t="shared" si="15"/>
-        <v>1670</v>
-      </c>
-      <c r="AZ14" s="21" t="e">
+        <f t="shared" si="16"/>
+        <v>1688.88</v>
+      </c>
+      <c r="AZ14" s="21">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>4.7368670361422954E-3</v>
       </c>
       <c r="BA14" s="21">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4.7058823529411761E-3</v>
       </c>
       <c r="BB14" s="21">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BC14" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD14" s="21">
@@ -3611,7 +4020,7 @@
         <v/>
       </c>
       <c r="BF14" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG14" s="21">
@@ -3705,12 +4114,12 @@
         <v>0</v>
       </c>
       <c r="AX15" s="16">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>0.23317493759999997</v>
       </c>
       <c r="AY15" s="16">
-        <f t="shared" si="15"/>
-        <v>1655</v>
+        <f t="shared" si="16"/>
+        <v>1671.74</v>
       </c>
       <c r="AZ15" s="17" t="e">
         <f t="shared" si="5"/>
@@ -3725,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="BC15" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD15" s="17" t="str">
@@ -3738,7 +4147,7 @@
       </c>
       <c r="BF15" s="17">
         <f>IF(O15&lt;1.5, IF(B15&lt;&gt;"Julia",((3-O15)*AY15)/400, ""),0)</f>
-        <v>12.4125</v>
+        <v>12.53805</v>
       </c>
       <c r="BG15" s="17" t="str">
         <f t="shared" si="2"/>
@@ -3754,7 +4163,7 @@
       </c>
       <c r="BJ15" s="53">
         <f t="shared" si="11"/>
-        <v>12.4125</v>
+        <v>12.53805</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.25">
@@ -3831,12 +4240,12 @@
         <v>0</v>
       </c>
       <c r="AX16" s="33">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>0.19342998720000004</v>
       </c>
       <c r="AY16" s="33">
-        <f t="shared" si="15"/>
-        <v>1655</v>
+        <f t="shared" si="16"/>
+        <v>1674.64</v>
       </c>
       <c r="AZ16" s="34" t="e">
         <f t="shared" si="5"/>
@@ -3851,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="BC16" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD16" s="64" t="str">
@@ -3863,8 +4272,8 @@
         <v/>
       </c>
       <c r="BF16" s="34">
-        <f t="shared" si="17"/>
-        <v>12.4125</v>
+        <f t="shared" si="18"/>
+        <v>12.559800000000001</v>
       </c>
       <c r="BG16" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3880,7 +4289,7 @@
       </c>
       <c r="BJ16" s="51">
         <f t="shared" si="11"/>
-        <v>12.4125</v>
+        <v>12.559800000000001</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.25">
@@ -3957,12 +4366,12 @@
         <v>0</v>
       </c>
       <c r="AX17" s="33">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>0.1928335464</v>
       </c>
       <c r="AY17" s="33">
-        <f t="shared" si="15"/>
-        <v>1655</v>
+        <f t="shared" si="16"/>
+        <v>1669.43</v>
       </c>
       <c r="AZ17" s="34" t="e">
         <f t="shared" si="5"/>
@@ -3977,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="BC17" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD17" s="64" t="str">
@@ -3989,8 +4398,8 @@
         <v/>
       </c>
       <c r="BF17" s="34">
-        <f t="shared" si="17"/>
-        <v>12.4125</v>
+        <f t="shared" si="18"/>
+        <v>12.520725000000001</v>
       </c>
       <c r="BG17" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4006,7 +4415,7 @@
       </c>
       <c r="BJ17" s="51">
         <f t="shared" si="11"/>
-        <v>12.4125</v>
+        <v>12.520725000000001</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.25">
@@ -4083,12 +4492,12 @@
         <v>0</v>
       </c>
       <c r="AX18" s="33">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>0.29846668319999997</v>
       </c>
       <c r="AY18" s="33">
-        <f t="shared" si="15"/>
-        <v>1655</v>
+        <f t="shared" si="16"/>
+        <v>1670.11</v>
       </c>
       <c r="AZ18" s="34" t="e">
         <f t="shared" si="5"/>
@@ -4103,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="BC18" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD18" s="64" t="str">
@@ -4115,8 +4524,8 @@
         <v>0</v>
       </c>
       <c r="BF18" s="34">
-        <f t="shared" si="17"/>
-        <v>12.4125</v>
+        <f t="shared" si="18"/>
+        <v>12.525824999999999</v>
       </c>
       <c r="BG18" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4132,7 +4541,7 @@
       </c>
       <c r="BJ18" s="51">
         <f t="shared" si="11"/>
-        <v>12.4125</v>
+        <v>12.525824999999999</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.25">
@@ -4209,12 +4618,12 @@
         <v>0</v>
       </c>
       <c r="AX19" s="33">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>0.18475989119999997</v>
       </c>
       <c r="AY19" s="33">
-        <f t="shared" si="15"/>
-        <v>1655</v>
+        <f t="shared" si="16"/>
+        <v>1673.23</v>
       </c>
       <c r="AZ19" s="34" t="e">
         <f t="shared" si="5"/>
@@ -4229,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="BC19" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD19" s="64">
@@ -4241,7 +4650,7 @@
         <v/>
       </c>
       <c r="BF19" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG19" s="34">
@@ -4335,12 +4744,12 @@
         <v>0</v>
       </c>
       <c r="AX20" s="20">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>0.19699096319999998</v>
       </c>
       <c r="AY20" s="20">
-        <f t="shared" si="15"/>
-        <v>1655</v>
+        <f t="shared" si="16"/>
+        <v>1673.88</v>
       </c>
       <c r="AZ20" s="21" t="e">
         <f t="shared" si="5"/>
@@ -4355,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="BC20" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD20" s="21">
@@ -4367,7 +4776,7 @@
         <v/>
       </c>
       <c r="BF20" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG20" s="21">
@@ -4461,12 +4870,12 @@
         <v>0</v>
       </c>
       <c r="AX21" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY21" s="16">
-        <f t="shared" si="15"/>
-        <v>1640</v>
+        <f t="shared" si="16"/>
+        <v>1656.74</v>
       </c>
       <c r="AZ21" s="17" t="e">
         <f t="shared" si="5"/>
@@ -4481,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="BC21" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD21" s="17" t="str">
@@ -4493,8 +4902,8 @@
         <v>0</v>
       </c>
       <c r="BF21" s="17">
-        <f t="shared" si="17"/>
-        <v>12.3</v>
+        <f t="shared" si="18"/>
+        <v>12.425550000000001</v>
       </c>
       <c r="BG21" s="17" t="str">
         <f t="shared" si="2"/>
@@ -4510,7 +4919,7 @@
       </c>
       <c r="BJ21" s="51">
         <f t="shared" si="11"/>
-        <v>12.3</v>
+        <v>12.425550000000001</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.25">
@@ -4587,12 +4996,12 @@
         <v>0</v>
       </c>
       <c r="AX22" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY22" s="33">
-        <f t="shared" si="15"/>
-        <v>1640</v>
+        <f t="shared" si="16"/>
+        <v>1659.64</v>
       </c>
       <c r="AZ22" s="34" t="e">
         <f t="shared" si="5"/>
@@ -4607,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="BC22" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD22" s="64" t="str">
@@ -4619,8 +5028,8 @@
         <v/>
       </c>
       <c r="BF22" s="34">
-        <f t="shared" si="17"/>
-        <v>12.3</v>
+        <f t="shared" si="18"/>
+        <v>12.4473</v>
       </c>
       <c r="BG22" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4636,7 +5045,7 @@
       </c>
       <c r="BJ22" s="51">
         <f t="shared" si="11"/>
-        <v>12.3</v>
+        <v>12.4473</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.25">
@@ -4713,12 +5122,12 @@
         <v>0</v>
       </c>
       <c r="AX23" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY23" s="33">
-        <f t="shared" si="15"/>
-        <v>1640</v>
+        <f t="shared" si="16"/>
+        <v>1654.43</v>
       </c>
       <c r="AZ23" s="34" t="e">
         <f t="shared" si="5"/>
@@ -4733,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="BC23" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD23" s="64" t="str">
@@ -4745,8 +5154,8 @@
         <v/>
       </c>
       <c r="BF23" s="34">
-        <f t="shared" si="17"/>
-        <v>12.3</v>
+        <f t="shared" si="18"/>
+        <v>12.408225</v>
       </c>
       <c r="BG23" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4762,7 +5171,7 @@
       </c>
       <c r="BJ23" s="51">
         <f t="shared" si="11"/>
-        <v>12.3</v>
+        <v>12.408225</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.25">
@@ -4839,12 +5248,12 @@
         <v>0</v>
       </c>
       <c r="AX24" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY24" s="33">
-        <f t="shared" si="15"/>
-        <v>1640</v>
+        <f t="shared" si="16"/>
+        <v>1655.11</v>
       </c>
       <c r="AZ24" s="34" t="e">
         <f t="shared" si="5"/>
@@ -4859,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="BC24" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD24" s="64" t="str">
@@ -4871,8 +5280,8 @@
         <v>0</v>
       </c>
       <c r="BF24" s="34">
-        <f t="shared" si="17"/>
-        <v>12.3</v>
+        <f t="shared" si="18"/>
+        <v>12.413325</v>
       </c>
       <c r="BG24" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4888,7 +5297,7 @@
       </c>
       <c r="BJ24" s="51">
         <f t="shared" si="11"/>
-        <v>12.3</v>
+        <v>12.413325</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.25">
@@ -4965,12 +5374,12 @@
         <v>0</v>
       </c>
       <c r="AX25" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY25" s="33">
-        <f t="shared" si="15"/>
-        <v>1640</v>
+        <f t="shared" si="16"/>
+        <v>1658.23</v>
       </c>
       <c r="AZ25" s="34" t="e">
         <f t="shared" si="5"/>
@@ -4985,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="BC25" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD25" s="64">
@@ -4997,7 +5406,7 @@
         <v/>
       </c>
       <c r="BF25" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG25" s="34">
@@ -5091,12 +5500,12 @@
         <v>0</v>
       </c>
       <c r="AX26" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY26" s="20">
-        <f t="shared" si="15"/>
-        <v>1640</v>
+        <f t="shared" si="16"/>
+        <v>1658.88</v>
       </c>
       <c r="AZ26" s="21" t="e">
         <f t="shared" si="5"/>
@@ -5111,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="BC26" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD26" s="21">
@@ -5123,7 +5532,7 @@
         <v/>
       </c>
       <c r="BF26" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG26" s="21">
@@ -5217,12 +5626,12 @@
         <v>0</v>
       </c>
       <c r="AX27" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY27" s="16">
-        <f t="shared" si="15"/>
-        <v>1625</v>
+        <f t="shared" si="16"/>
+        <v>1641.74</v>
       </c>
       <c r="AZ27" s="17" t="e">
         <f t="shared" si="5"/>
@@ -5237,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="BC27" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD27" s="17" t="str">
@@ -5249,8 +5658,8 @@
         <v>0</v>
       </c>
       <c r="BF27" s="17">
-        <f t="shared" si="17"/>
-        <v>12.1875</v>
+        <f t="shared" si="18"/>
+        <v>12.31305</v>
       </c>
       <c r="BG27" s="17" t="str">
         <f t="shared" si="2"/>
@@ -5266,7 +5675,7 @@
       </c>
       <c r="BJ27" s="53">
         <f t="shared" si="11"/>
-        <v>12.1875</v>
+        <v>12.31305</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.25">
@@ -5343,12 +5752,12 @@
         <v>0</v>
       </c>
       <c r="AX28" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY28" s="33">
-        <f t="shared" si="15"/>
-        <v>1625</v>
+        <f t="shared" si="16"/>
+        <v>1644.64</v>
       </c>
       <c r="AZ28" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5363,7 +5772,7 @@
         <v>0</v>
       </c>
       <c r="BC28" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD28" s="64" t="str">
@@ -5375,8 +5784,8 @@
         <v/>
       </c>
       <c r="BF28" s="34">
-        <f t="shared" si="17"/>
-        <v>12.1875</v>
+        <f t="shared" si="18"/>
+        <v>12.3348</v>
       </c>
       <c r="BG28" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5392,7 +5801,7 @@
       </c>
       <c r="BJ28" s="51">
         <f t="shared" si="11"/>
-        <v>12.1875</v>
+        <v>12.3348</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.25">
@@ -5469,12 +5878,12 @@
         <v>0</v>
       </c>
       <c r="AX29" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY29" s="33">
-        <f t="shared" si="15"/>
-        <v>1625</v>
+        <f t="shared" si="16"/>
+        <v>1639.43</v>
       </c>
       <c r="AZ29" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5489,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="BC29" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD29" s="64" t="str">
@@ -5501,8 +5910,8 @@
         <v/>
       </c>
       <c r="BF29" s="34">
-        <f t="shared" si="17"/>
-        <v>12.1875</v>
+        <f t="shared" si="18"/>
+        <v>12.295724999999999</v>
       </c>
       <c r="BG29" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5518,7 +5927,7 @@
       </c>
       <c r="BJ29" s="51">
         <f t="shared" si="11"/>
-        <v>12.1875</v>
+        <v>12.295724999999999</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.25">
@@ -5595,12 +6004,12 @@
         <v>0</v>
       </c>
       <c r="AX30" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY30" s="33">
-        <f t="shared" si="15"/>
-        <v>1625</v>
+        <f t="shared" si="16"/>
+        <v>1640.11</v>
       </c>
       <c r="AZ30" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5615,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="BC30" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD30" s="64" t="str">
@@ -5627,8 +6036,8 @@
         <v>0</v>
       </c>
       <c r="BF30" s="34">
-        <f t="shared" si="17"/>
-        <v>12.1875</v>
+        <f t="shared" si="18"/>
+        <v>12.300825</v>
       </c>
       <c r="BG30" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5644,7 +6053,7 @@
       </c>
       <c r="BJ30" s="51">
         <f t="shared" si="11"/>
-        <v>12.1875</v>
+        <v>12.300825</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.25">
@@ -5721,12 +6130,12 @@
         <v>0</v>
       </c>
       <c r="AX31" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY31" s="33">
-        <f t="shared" si="15"/>
-        <v>1625</v>
+        <f t="shared" si="16"/>
+        <v>1643.23</v>
       </c>
       <c r="AZ31" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5741,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="BC31" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD31" s="64">
@@ -5753,7 +6162,7 @@
         <v/>
       </c>
       <c r="BF31" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG31" s="34">
@@ -5847,12 +6256,12 @@
         <v>0</v>
       </c>
       <c r="AX32" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY32" s="20">
-        <f t="shared" si="15"/>
-        <v>1625</v>
+        <f t="shared" si="16"/>
+        <v>1643.88</v>
       </c>
       <c r="AZ32" s="21" t="e">
         <f t="shared" si="5"/>
@@ -5867,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="BC32" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD32" s="21">
@@ -5879,7 +6288,7 @@
         <v/>
       </c>
       <c r="BF32" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG32" s="21">
@@ -5973,12 +6382,12 @@
         <v>0</v>
       </c>
       <c r="AX33" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY33" s="16">
-        <f t="shared" si="15"/>
-        <v>1610</v>
+        <f t="shared" si="16"/>
+        <v>1626.74</v>
       </c>
       <c r="AZ33" s="17" t="e">
         <f t="shared" si="5"/>
@@ -5993,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="BC33" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD33" s="17" t="str">
@@ -6005,8 +6414,8 @@
         <v>0</v>
       </c>
       <c r="BF33" s="17">
-        <f t="shared" si="17"/>
-        <v>12.074999999999999</v>
+        <f t="shared" si="18"/>
+        <v>12.20055</v>
       </c>
       <c r="BG33" s="17" t="str">
         <f t="shared" si="2"/>
@@ -6022,7 +6431,7 @@
       </c>
       <c r="BJ33" s="51">
         <f t="shared" si="11"/>
-        <v>12.074999999999999</v>
+        <v>12.20055</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.25">
@@ -6099,12 +6508,12 @@
         <v>0</v>
       </c>
       <c r="AX34" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY34" s="33">
-        <f t="shared" si="15"/>
-        <v>1610</v>
+        <f t="shared" si="16"/>
+        <v>1629.64</v>
       </c>
       <c r="AZ34" s="34" t="e">
         <f t="shared" si="5"/>
@@ -6119,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="BC34" s="34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD34" s="64" t="str">
@@ -6131,8 +6540,8 @@
         <v/>
       </c>
       <c r="BF34" s="34">
-        <f t="shared" si="17"/>
-        <v>12.074999999999999</v>
+        <f t="shared" si="18"/>
+        <v>12.222300000000001</v>
       </c>
       <c r="BG34" s="34" t="str">
         <f t="shared" si="2"/>
@@ -6148,7 +6557,7 @@
       </c>
       <c r="BJ34" s="51">
         <f t="shared" si="11"/>
-        <v>12.074999999999999</v>
+        <v>12.222300000000001</v>
       </c>
     </row>
     <row r="35" spans="1:62" x14ac:dyDescent="0.25">
@@ -6225,27 +6634,27 @@
         <v>0</v>
       </c>
       <c r="AX35" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY35" s="33">
-        <f t="shared" si="15"/>
-        <v>1610</v>
+        <f t="shared" si="16"/>
+        <v>1624.43</v>
       </c>
       <c r="AZ35" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA35" s="34">
-        <f t="shared" ref="BA35:BA66" si="18">AJ35/AO35</f>
+        <f t="shared" ref="BA35:BA66" si="19">AJ35/AO35</f>
         <v>0</v>
       </c>
       <c r="BB35" s="34">
-        <f t="shared" ref="BB35:BB66" si="19">AI35*24</f>
+        <f t="shared" ref="BB35:BB66" si="20">AI35*24</f>
         <v>0</v>
       </c>
       <c r="BC35" s="34">
-        <f t="shared" ref="BC35:BC66" si="20">IF(B35="Python",AT35*AO35/24/60,"")</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD35" s="64" t="str">
@@ -6257,8 +6666,8 @@
         <v/>
       </c>
       <c r="BF35" s="34">
-        <f t="shared" si="17"/>
-        <v>12.074999999999999</v>
+        <f t="shared" si="18"/>
+        <v>12.183225</v>
       </c>
       <c r="BG35" s="34" t="str">
         <f t="shared" ref="BG35:BG66" si="22">IF(B35="Julia",AV35*AY35,"")</f>
@@ -6274,7 +6683,7 @@
       </c>
       <c r="BJ35" s="51">
         <f t="shared" si="11"/>
-        <v>12.074999999999999</v>
+        <v>12.183225</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.25">
@@ -6351,27 +6760,27 @@
         <v>0</v>
       </c>
       <c r="AX36" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY36" s="33">
-        <f t="shared" si="15"/>
-        <v>1610</v>
+        <f t="shared" si="16"/>
+        <v>1625.11</v>
       </c>
       <c r="AZ36" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA36" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB36" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC36" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD36" s="64" t="str">
@@ -6383,8 +6792,8 @@
         <v>0</v>
       </c>
       <c r="BF36" s="34">
-        <f t="shared" si="17"/>
-        <v>12.074999999999999</v>
+        <f t="shared" si="18"/>
+        <v>12.188324999999999</v>
       </c>
       <c r="BG36" s="34" t="str">
         <f t="shared" si="22"/>
@@ -6400,7 +6809,7 @@
       </c>
       <c r="BJ36" s="51">
         <f t="shared" si="11"/>
-        <v>12.074999999999999</v>
+        <v>12.188324999999999</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.25">
@@ -6477,27 +6886,27 @@
         <v>0</v>
       </c>
       <c r="AX37" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY37" s="33">
-        <f t="shared" si="15"/>
-        <v>1610</v>
+        <f t="shared" si="16"/>
+        <v>1628.23</v>
       </c>
       <c r="AZ37" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA37" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB37" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC37" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD37" s="64">
@@ -6509,7 +6918,7 @@
         <v/>
       </c>
       <c r="BF37" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG37" s="34">
@@ -6603,27 +7012,27 @@
         <v>0</v>
       </c>
       <c r="AX38" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY38" s="20">
-        <f t="shared" si="15"/>
-        <v>1610</v>
+        <f t="shared" si="16"/>
+        <v>1628.88</v>
       </c>
       <c r="AZ38" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA38" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB38" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC38" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD38" s="21">
@@ -6635,7 +7044,7 @@
         <v/>
       </c>
       <c r="BF38" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG38" s="21">
@@ -6729,27 +7138,27 @@
         <v>0</v>
       </c>
       <c r="AX39" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY39" s="16">
-        <f t="shared" si="15"/>
-        <v>1595</v>
+        <f t="shared" si="16"/>
+        <v>1611.74</v>
       </c>
       <c r="AZ39" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA39" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB39" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC39" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD39" s="17" t="str">
@@ -6761,8 +7170,8 @@
         <v>0</v>
       </c>
       <c r="BF39" s="17">
-        <f t="shared" si="17"/>
-        <v>11.9625</v>
+        <f t="shared" si="18"/>
+        <v>12.088050000000001</v>
       </c>
       <c r="BG39" s="17" t="str">
         <f t="shared" si="22"/>
@@ -6778,7 +7187,7 @@
       </c>
       <c r="BJ39" s="53">
         <f t="shared" si="11"/>
-        <v>11.9625</v>
+        <v>12.088050000000001</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.25">
@@ -6855,27 +7264,27 @@
         <v>0</v>
       </c>
       <c r="AX40" s="33">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AY40" s="33">
-        <f t="shared" si="15"/>
-        <v>1595</v>
+        <f t="shared" si="16"/>
+        <v>1614.64</v>
       </c>
       <c r="AZ40" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA40" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB40" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC40" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD40" s="64" t="str">
@@ -6887,8 +7296,8 @@
         <v/>
       </c>
       <c r="BF40" s="34">
-        <f t="shared" si="17"/>
-        <v>11.9625</v>
+        <f t="shared" si="18"/>
+        <v>12.1098</v>
       </c>
       <c r="BG40" s="34" t="str">
         <f t="shared" si="22"/>
@@ -6904,7 +7313,7 @@
       </c>
       <c r="BJ40" s="51">
         <f t="shared" si="11"/>
-        <v>11.9625</v>
+        <v>12.1098</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.25">
@@ -6986,22 +7395,22 @@
       </c>
       <c r="AY41" s="33">
         <f t="shared" ref="AY41:AY72" si="24">AY35+SUM(AF41:AH41,AL41:AM41)-AN41</f>
-        <v>1595</v>
+        <v>1609.43</v>
       </c>
       <c r="AZ41" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA41" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB41" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC41" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD41" s="64" t="str">
@@ -7013,8 +7422,8 @@
         <v/>
       </c>
       <c r="BF41" s="34">
-        <f t="shared" si="17"/>
-        <v>11.9625</v>
+        <f t="shared" si="18"/>
+        <v>12.070724999999999</v>
       </c>
       <c r="BG41" s="34" t="str">
         <f t="shared" si="22"/>
@@ -7030,7 +7439,7 @@
       </c>
       <c r="BJ41" s="51">
         <f t="shared" si="11"/>
-        <v>11.9625</v>
+        <v>12.070724999999999</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.25">
@@ -7112,22 +7521,22 @@
       </c>
       <c r="AY42" s="33">
         <f t="shared" si="24"/>
-        <v>1595</v>
+        <v>1610.11</v>
       </c>
       <c r="AZ42" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA42" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB42" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC42" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD42" s="64" t="str">
@@ -7139,8 +7548,8 @@
         <v>0</v>
       </c>
       <c r="BF42" s="34">
-        <f t="shared" si="17"/>
-        <v>11.9625</v>
+        <f t="shared" si="18"/>
+        <v>12.075825</v>
       </c>
       <c r="BG42" s="34" t="str">
         <f t="shared" si="22"/>
@@ -7156,7 +7565,7 @@
       </c>
       <c r="BJ42" s="51">
         <f t="shared" si="11"/>
-        <v>11.9625</v>
+        <v>12.075825</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.25">
@@ -7238,22 +7647,22 @@
       </c>
       <c r="AY43" s="33">
         <f t="shared" si="24"/>
-        <v>1595</v>
+        <v>1613.23</v>
       </c>
       <c r="AZ43" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA43" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB43" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC43" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD43" s="64">
@@ -7265,7 +7674,7 @@
         <v/>
       </c>
       <c r="BF43" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG43" s="34">
@@ -7364,22 +7773,22 @@
       </c>
       <c r="AY44" s="20">
         <f t="shared" si="24"/>
-        <v>1595</v>
+        <v>1613.88</v>
       </c>
       <c r="AZ44" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA44" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB44" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC44" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD44" s="21">
@@ -7391,7 +7800,7 @@
         <v/>
       </c>
       <c r="BF44" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG44" s="21">
@@ -7490,22 +7899,22 @@
       </c>
       <c r="AY45" s="16">
         <f t="shared" si="24"/>
-        <v>1580</v>
+        <v>1596.74</v>
       </c>
       <c r="AZ45" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA45" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB45" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC45" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD45" s="17" t="str">
@@ -7517,8 +7926,8 @@
         <v>0</v>
       </c>
       <c r="BF45" s="17">
-        <f t="shared" si="17"/>
-        <v>11.85</v>
+        <f t="shared" si="18"/>
+        <v>11.97555</v>
       </c>
       <c r="BG45" s="17" t="str">
         <f t="shared" si="22"/>
@@ -7534,7 +7943,7 @@
       </c>
       <c r="BJ45" s="51">
         <f t="shared" si="11"/>
-        <v>11.85</v>
+        <v>11.97555</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.25">
@@ -7616,22 +8025,22 @@
       </c>
       <c r="AY46" s="33">
         <f t="shared" si="24"/>
-        <v>1580</v>
+        <v>1599.64</v>
       </c>
       <c r="AZ46" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA46" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB46" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC46" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD46" s="64" t="str">
@@ -7643,8 +8052,8 @@
         <v/>
       </c>
       <c r="BF46" s="34">
-        <f t="shared" si="17"/>
-        <v>11.85</v>
+        <f t="shared" si="18"/>
+        <v>11.997300000000001</v>
       </c>
       <c r="BG46" s="34" t="str">
         <f t="shared" si="22"/>
@@ -7660,7 +8069,7 @@
       </c>
       <c r="BJ46" s="51">
         <f t="shared" si="11"/>
-        <v>11.85</v>
+        <v>11.997300000000001</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.25">
@@ -7742,22 +8151,22 @@
       </c>
       <c r="AY47" s="33">
         <f t="shared" si="24"/>
-        <v>1580</v>
+        <v>1594.43</v>
       </c>
       <c r="AZ47" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA47" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB47" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC47" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD47" s="64" t="str">
@@ -7769,8 +8178,8 @@
         <v/>
       </c>
       <c r="BF47" s="34">
-        <f t="shared" si="17"/>
-        <v>11.85</v>
+        <f t="shared" si="18"/>
+        <v>11.958225000000001</v>
       </c>
       <c r="BG47" s="34" t="str">
         <f t="shared" si="22"/>
@@ -7786,7 +8195,7 @@
       </c>
       <c r="BJ47" s="51">
         <f t="shared" si="11"/>
-        <v>11.85</v>
+        <v>11.958225000000001</v>
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.25">
@@ -7868,22 +8277,22 @@
       </c>
       <c r="AY48" s="33">
         <f t="shared" si="24"/>
-        <v>1580</v>
+        <v>1595.11</v>
       </c>
       <c r="AZ48" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA48" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB48" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC48" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD48" s="64" t="str">
@@ -7895,8 +8304,8 @@
         <v>0</v>
       </c>
       <c r="BF48" s="34">
-        <f t="shared" si="17"/>
-        <v>11.85</v>
+        <f t="shared" si="18"/>
+        <v>11.963324999999999</v>
       </c>
       <c r="BG48" s="34" t="str">
         <f t="shared" si="22"/>
@@ -7912,7 +8321,7 @@
       </c>
       <c r="BJ48" s="51">
         <f t="shared" si="11"/>
-        <v>11.85</v>
+        <v>11.963324999999999</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.25">
@@ -7994,22 +8403,22 @@
       </c>
       <c r="AY49" s="33">
         <f t="shared" si="24"/>
-        <v>1580</v>
+        <v>1598.23</v>
       </c>
       <c r="AZ49" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA49" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB49" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC49" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD49" s="64">
@@ -8021,7 +8430,7 @@
         <v/>
       </c>
       <c r="BF49" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG49" s="34">
@@ -8120,22 +8529,22 @@
       </c>
       <c r="AY50" s="20">
         <f t="shared" si="24"/>
-        <v>1580</v>
+        <v>1598.88</v>
       </c>
       <c r="AZ50" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA50" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB50" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC50" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD50" s="21">
@@ -8147,7 +8556,7 @@
         <v/>
       </c>
       <c r="BF50" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG50" s="21">
@@ -8246,22 +8655,22 @@
       </c>
       <c r="AY51" s="16">
         <f t="shared" si="24"/>
-        <v>1565</v>
+        <v>1581.74</v>
       </c>
       <c r="AZ51" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA51" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB51" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC51" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD51" s="17" t="str">
@@ -8273,8 +8682,8 @@
         <v>0</v>
       </c>
       <c r="BF51" s="17">
-        <f t="shared" si="17"/>
-        <v>11.737500000000001</v>
+        <f t="shared" si="18"/>
+        <v>11.863050000000001</v>
       </c>
       <c r="BG51" s="17" t="str">
         <f t="shared" si="22"/>
@@ -8290,7 +8699,7 @@
       </c>
       <c r="BJ51" s="53">
         <f t="shared" si="11"/>
-        <v>11.737500000000001</v>
+        <v>11.863050000000001</v>
       </c>
     </row>
     <row r="52" spans="1:62" x14ac:dyDescent="0.25">
@@ -8372,22 +8781,22 @@
       </c>
       <c r="AY52" s="33">
         <f t="shared" si="24"/>
-        <v>1565</v>
+        <v>1584.64</v>
       </c>
       <c r="AZ52" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA52" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB52" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC52" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD52" s="64" t="str">
@@ -8399,8 +8808,8 @@
         <v/>
       </c>
       <c r="BF52" s="34">
-        <f t="shared" si="17"/>
-        <v>11.737500000000001</v>
+        <f t="shared" si="18"/>
+        <v>11.8848</v>
       </c>
       <c r="BG52" s="34" t="str">
         <f t="shared" si="22"/>
@@ -8416,7 +8825,7 @@
       </c>
       <c r="BJ52" s="51">
         <f t="shared" si="11"/>
-        <v>11.737500000000001</v>
+        <v>11.8848</v>
       </c>
     </row>
     <row r="53" spans="1:62" x14ac:dyDescent="0.25">
@@ -8498,22 +8907,22 @@
       </c>
       <c r="AY53" s="33">
         <f t="shared" si="24"/>
-        <v>1565</v>
+        <v>1579.43</v>
       </c>
       <c r="AZ53" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA53" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB53" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD53" s="64" t="str">
@@ -8525,8 +8934,8 @@
         <v/>
       </c>
       <c r="BF53" s="34">
-        <f t="shared" si="17"/>
-        <v>11.737500000000001</v>
+        <f t="shared" si="18"/>
+        <v>11.845725</v>
       </c>
       <c r="BG53" s="34" t="str">
         <f t="shared" si="22"/>
@@ -8542,7 +8951,7 @@
       </c>
       <c r="BJ53" s="51">
         <f t="shared" si="11"/>
-        <v>11.737500000000001</v>
+        <v>11.845725</v>
       </c>
     </row>
     <row r="54" spans="1:62" x14ac:dyDescent="0.25">
@@ -8624,22 +9033,22 @@
       </c>
       <c r="AY54" s="33">
         <f t="shared" si="24"/>
-        <v>1565</v>
+        <v>1580.11</v>
       </c>
       <c r="AZ54" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA54" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB54" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC54" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD54" s="64" t="str">
@@ -8651,8 +9060,8 @@
         <v>0</v>
       </c>
       <c r="BF54" s="34">
-        <f t="shared" si="17"/>
-        <v>11.737500000000001</v>
+        <f t="shared" si="18"/>
+        <v>11.850825</v>
       </c>
       <c r="BG54" s="34" t="str">
         <f t="shared" si="22"/>
@@ -8668,7 +9077,7 @@
       </c>
       <c r="BJ54" s="51">
         <f t="shared" si="11"/>
-        <v>11.737500000000001</v>
+        <v>11.850825</v>
       </c>
     </row>
     <row r="55" spans="1:62" x14ac:dyDescent="0.25">
@@ -8750,22 +9159,22 @@
       </c>
       <c r="AY55" s="33">
         <f t="shared" si="24"/>
-        <v>1565</v>
+        <v>1583.23</v>
       </c>
       <c r="AZ55" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA55" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB55" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC55" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD55" s="64">
@@ -8777,7 +9186,7 @@
         <v/>
       </c>
       <c r="BF55" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG55" s="34">
@@ -8876,22 +9285,22 @@
       </c>
       <c r="AY56" s="20">
         <f t="shared" si="24"/>
-        <v>1565</v>
+        <v>1583.88</v>
       </c>
       <c r="AZ56" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA56" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB56" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC56" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD56" s="21">
@@ -8903,7 +9312,7 @@
         <v/>
       </c>
       <c r="BF56" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG56" s="21">
@@ -9002,22 +9411,22 @@
       </c>
       <c r="AY57" s="16">
         <f t="shared" si="24"/>
-        <v>1550</v>
+        <v>1566.74</v>
       </c>
       <c r="AZ57" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA57" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB57" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC57" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD57" s="17" t="str">
@@ -9029,8 +9438,8 @@
         <v>0</v>
       </c>
       <c r="BF57" s="17">
-        <f t="shared" si="17"/>
-        <v>11.625</v>
+        <f t="shared" si="18"/>
+        <v>11.75055</v>
       </c>
       <c r="BG57" s="17" t="str">
         <f t="shared" si="22"/>
@@ -9046,7 +9455,7 @@
       </c>
       <c r="BJ57" s="51">
         <f t="shared" si="11"/>
-        <v>11.625</v>
+        <v>11.75055</v>
       </c>
     </row>
     <row r="58" spans="1:62" x14ac:dyDescent="0.25">
@@ -9128,22 +9537,22 @@
       </c>
       <c r="AY58" s="33">
         <f t="shared" si="24"/>
-        <v>1550</v>
+        <v>1569.64</v>
       </c>
       <c r="AZ58" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA58" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB58" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC58" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD58" s="64" t="str">
@@ -9155,8 +9564,8 @@
         <v/>
       </c>
       <c r="BF58" s="34">
-        <f t="shared" si="17"/>
-        <v>11.625</v>
+        <f t="shared" si="18"/>
+        <v>11.7723</v>
       </c>
       <c r="BG58" s="34" t="str">
         <f t="shared" si="22"/>
@@ -9172,7 +9581,7 @@
       </c>
       <c r="BJ58" s="51">
         <f t="shared" si="11"/>
-        <v>11.625</v>
+        <v>11.7723</v>
       </c>
     </row>
     <row r="59" spans="1:62" x14ac:dyDescent="0.25">
@@ -9254,22 +9663,22 @@
       </c>
       <c r="AY59" s="33">
         <f t="shared" si="24"/>
-        <v>1550</v>
+        <v>1564.43</v>
       </c>
       <c r="AZ59" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA59" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB59" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC59" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD59" s="64" t="str">
@@ -9281,8 +9690,8 @@
         <v/>
       </c>
       <c r="BF59" s="34">
-        <f t="shared" si="17"/>
-        <v>11.625</v>
+        <f t="shared" si="18"/>
+        <v>11.733224999999999</v>
       </c>
       <c r="BG59" s="34" t="str">
         <f t="shared" si="22"/>
@@ -9298,7 +9707,7 @@
       </c>
       <c r="BJ59" s="51">
         <f t="shared" si="11"/>
-        <v>11.625</v>
+        <v>11.733224999999999</v>
       </c>
     </row>
     <row r="60" spans="1:62" x14ac:dyDescent="0.25">
@@ -9380,22 +9789,22 @@
       </c>
       <c r="AY60" s="33">
         <f t="shared" si="24"/>
-        <v>1550</v>
+        <v>1565.11</v>
       </c>
       <c r="AZ60" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA60" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB60" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC60" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD60" s="64" t="str">
@@ -9407,8 +9816,8 @@
         <v>0</v>
       </c>
       <c r="BF60" s="34">
-        <f t="shared" si="17"/>
-        <v>11.625</v>
+        <f t="shared" si="18"/>
+        <v>11.738325</v>
       </c>
       <c r="BG60" s="34" t="str">
         <f t="shared" si="22"/>
@@ -9424,7 +9833,7 @@
       </c>
       <c r="BJ60" s="51">
         <f t="shared" si="11"/>
-        <v>11.625</v>
+        <v>11.738325</v>
       </c>
     </row>
     <row r="61" spans="1:62" x14ac:dyDescent="0.25">
@@ -9506,22 +9915,22 @@
       </c>
       <c r="AY61" s="33">
         <f t="shared" si="24"/>
-        <v>1550</v>
+        <v>1568.23</v>
       </c>
       <c r="AZ61" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA61" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB61" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC61" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD61" s="64">
@@ -9533,7 +9942,7 @@
         <v/>
       </c>
       <c r="BF61" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG61" s="34">
@@ -9632,22 +10041,22 @@
       </c>
       <c r="AY62" s="20">
         <f t="shared" si="24"/>
-        <v>1550</v>
+        <v>1568.88</v>
       </c>
       <c r="AZ62" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA62" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB62" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC62" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD62" s="21">
@@ -9659,7 +10068,7 @@
         <v/>
       </c>
       <c r="BF62" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG62" s="21">
@@ -9758,22 +10167,22 @@
       </c>
       <c r="AY63" s="16">
         <f t="shared" si="24"/>
-        <v>1535</v>
+        <v>1551.74</v>
       </c>
       <c r="AZ63" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA63" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB63" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC63" s="17" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD63" s="17" t="str">
@@ -9785,8 +10194,8 @@
         <v>0</v>
       </c>
       <c r="BF63" s="17">
-        <f t="shared" si="17"/>
-        <v>11.512499999999999</v>
+        <f t="shared" si="18"/>
+        <v>11.63805</v>
       </c>
       <c r="BG63" s="17" t="str">
         <f t="shared" si="22"/>
@@ -9802,7 +10211,7 @@
       </c>
       <c r="BJ63" s="53">
         <f t="shared" si="11"/>
-        <v>11.512499999999999</v>
+        <v>11.63805</v>
       </c>
     </row>
     <row r="64" spans="1:62" x14ac:dyDescent="0.25">
@@ -9884,22 +10293,22 @@
       </c>
       <c r="AY64" s="33">
         <f t="shared" si="24"/>
-        <v>1535</v>
+        <v>1554.64</v>
       </c>
       <c r="AZ64" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA64" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB64" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC64" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD64" s="64" t="str">
@@ -9911,8 +10320,8 @@
         <v/>
       </c>
       <c r="BF64" s="34">
-        <f t="shared" si="17"/>
-        <v>11.512499999999999</v>
+        <f t="shared" si="18"/>
+        <v>11.659800000000001</v>
       </c>
       <c r="BG64" s="34" t="str">
         <f t="shared" si="22"/>
@@ -9928,7 +10337,7 @@
       </c>
       <c r="BJ64" s="51">
         <f t="shared" si="11"/>
-        <v>11.512499999999999</v>
+        <v>11.659800000000001</v>
       </c>
     </row>
     <row r="65" spans="1:62" x14ac:dyDescent="0.25">
@@ -10010,22 +10419,22 @@
       </c>
       <c r="AY65" s="33">
         <f t="shared" si="24"/>
-        <v>1535</v>
+        <v>1549.43</v>
       </c>
       <c r="AZ65" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA65" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB65" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC65" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BD65" s="64" t="str">
@@ -10037,8 +10446,8 @@
         <v/>
       </c>
       <c r="BF65" s="34">
-        <f t="shared" si="17"/>
-        <v>11.512499999999999</v>
+        <f t="shared" si="18"/>
+        <v>11.620725</v>
       </c>
       <c r="BG65" s="34" t="str">
         <f t="shared" si="22"/>
@@ -10054,7 +10463,7 @@
       </c>
       <c r="BJ65" s="51">
         <f t="shared" si="11"/>
-        <v>11.512499999999999</v>
+        <v>11.620725</v>
       </c>
     </row>
     <row r="66" spans="1:62" x14ac:dyDescent="0.25">
@@ -10136,22 +10545,22 @@
       </c>
       <c r="AY66" s="33">
         <f t="shared" si="24"/>
-        <v>1535</v>
+        <v>1550.11</v>
       </c>
       <c r="AZ66" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA66" s="34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="BB66" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="BC66" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD66" s="64" t="str">
@@ -10163,8 +10572,8 @@
         <v>0</v>
       </c>
       <c r="BF66" s="34">
-        <f t="shared" si="17"/>
-        <v>11.512499999999999</v>
+        <f t="shared" si="18"/>
+        <v>11.625824999999999</v>
       </c>
       <c r="BG66" s="34" t="str">
         <f t="shared" si="22"/>
@@ -10180,7 +10589,7 @@
       </c>
       <c r="BJ66" s="51">
         <f t="shared" si="11"/>
-        <v>11.512499999999999</v>
+        <v>11.625824999999999</v>
       </c>
     </row>
     <row r="67" spans="1:62" x14ac:dyDescent="0.25">
@@ -10262,7 +10671,7 @@
       </c>
       <c r="AY67" s="33">
         <f t="shared" si="24"/>
-        <v>1535</v>
+        <v>1553.23</v>
       </c>
       <c r="AZ67" s="34" t="e">
         <f t="shared" si="5"/>
@@ -10277,11 +10686,11 @@
         <v>0</v>
       </c>
       <c r="BC67" s="34" t="str">
-        <f t="shared" ref="BC67:BC80" si="27">IF(B67="Python",AT67*AO67/24/60,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="BD67" s="64">
-        <f t="shared" ref="BD67:BD80" si="28">IF(B67="Julia",AU67*AY67/24/60,"")</f>
+        <f t="shared" ref="BD67:BD80" si="27">IF(B67="Julia",AU67*AY67/24/60,"")</f>
         <v>0</v>
       </c>
       <c r="BE67" s="61" t="str">
@@ -10289,11 +10698,11 @@
         <v/>
       </c>
       <c r="BF67" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="BG67" s="34">
-        <f t="shared" ref="BG67:BG80" si="29">IF(B67="Julia",AV67*AY67,"")</f>
+        <f t="shared" ref="BG67:BG80" si="28">IF(B67="Julia",AV67*AY67,"")</f>
         <v>0</v>
       </c>
       <c r="BH67" s="49">
@@ -10379,7 +10788,7 @@
       <c r="AU68" s="20"/>
       <c r="AV68" s="44"/>
       <c r="AW68" s="19">
-        <f t="shared" ref="AW68:AW80" si="30">AS68*I68*AY68/1000</f>
+        <f t="shared" ref="AW68:AW80" si="29">AS68*I68*AY68/1000</f>
         <v>0</v>
       </c>
       <c r="AX68" s="20">
@@ -10388,10 +10797,10 @@
       </c>
       <c r="AY68" s="20">
         <f t="shared" si="24"/>
-        <v>1535</v>
+        <v>1553.88</v>
       </c>
       <c r="AZ68" s="21" t="e">
-        <f t="shared" ref="AZ68:AZ80" si="31">IF(ISBLANK(AJ68),NA(),IFERROR(AJ68/AY68,0))</f>
+        <f t="shared" ref="AZ68:AZ80" si="30">IF(ISBLANK(AJ68),NA(),IFERROR(AJ68/AY68,0))</f>
         <v>#N/A</v>
       </c>
       <c r="BA68" s="21">
@@ -10403,35 +10812,35 @@
         <v>0</v>
       </c>
       <c r="BC68" s="21" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="BD68" s="21">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BD68" s="21">
+        <v>0</v>
+      </c>
+      <c r="BE68" s="62" t="str">
+        <f t="shared" ref="BE68:BE80" si="31">IF(B68="No MPC", AS68*I68*AY68/1000,"")</f>
+        <v/>
+      </c>
+      <c r="BF68" s="21" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BG68" s="21">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="BE68" s="62" t="str">
-        <f t="shared" ref="BE68:BE80" si="32">IF(B68="No MPC", AS68*I68*AY68/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BF68" s="21" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="BG68" s="21">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="BH68" s="50">
-        <f t="shared" ref="BH68:BH80" si="33">IF(BC68&lt;&gt;"",BC68/0.000385,IF(BD68&lt;&gt;"",BD68/0.000385,BE68/0.000385))</f>
+        <f t="shared" ref="BH68:BH80" si="32">IF(BC68&lt;&gt;"",BC68/0.000385,IF(BD68&lt;&gt;"",BD68/0.000385,BE68/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BI68" s="70">
-        <f t="shared" ref="BI68:BI74" si="34">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
+        <f t="shared" ref="BI68:BI74" si="33">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
         <v>0</v>
       </c>
       <c r="BJ68" s="52">
-        <f t="shared" ref="BJ68:BJ80" si="35">IF(BF68&lt;&gt;"",BF68,BG68)</f>
+        <f t="shared" ref="BJ68:BJ80" si="34">IF(BF68&lt;&gt;"",BF68,BG68)</f>
         <v>0</v>
       </c>
     </row>
@@ -10505,7 +10914,7 @@
       <c r="AU69" s="16"/>
       <c r="AV69" s="42"/>
       <c r="AW69" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX69" s="16">
@@ -10514,10 +10923,10 @@
       </c>
       <c r="AY69" s="16">
         <f t="shared" si="24"/>
-        <v>1520</v>
+        <v>1536.74</v>
       </c>
       <c r="AZ69" s="17" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA69" s="17">
@@ -10529,36 +10938,36 @@
         <v>0</v>
       </c>
       <c r="BC69" s="17" t="str">
+        <f t="shared" ref="BC69:BC80" si="35">IF(B69="Python",AT69*AY69/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD69" s="17" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BD69" s="17" t="str">
+      <c r="BE69" s="60">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BF69" s="17">
+        <f t="shared" si="18"/>
+        <v>11.525550000000001</v>
+      </c>
+      <c r="BG69" s="17" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="BE69" s="60">
+      <c r="BH69" s="49">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="BF69" s="17">
-        <f t="shared" si="17"/>
-        <v>11.4</v>
-      </c>
-      <c r="BG69" s="17" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="BH69" s="49">
+      <c r="BI69" s="69">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BI69" s="69">
+      <c r="BJ69" s="51">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="BJ69" s="51">
-        <f t="shared" si="35"/>
-        <v>11.4</v>
+        <v>11.525550000000001</v>
       </c>
     </row>
     <row r="70" spans="1:62" x14ac:dyDescent="0.25">
@@ -10631,7 +11040,7 @@
       <c r="AU70" s="33"/>
       <c r="AV70" s="43"/>
       <c r="AW70" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX70" s="33">
@@ -10640,10 +11049,10 @@
       </c>
       <c r="AY70" s="33">
         <f t="shared" si="24"/>
-        <v>1520</v>
+        <v>1539.64</v>
       </c>
       <c r="AZ70" s="34" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA70" s="34">
@@ -10655,36 +11064,36 @@
         <v>0</v>
       </c>
       <c r="BC70" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BD70" s="64" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BD70" s="64" t="str">
+        <v/>
+      </c>
+      <c r="BE70" s="61" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BF70" s="34">
+        <f t="shared" si="18"/>
+        <v>11.5473</v>
+      </c>
+      <c r="BG70" s="34" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="BE70" s="61" t="str">
+      <c r="BH70" s="49">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="BF70" s="34">
-        <f t="shared" si="17"/>
-        <v>11.4</v>
-      </c>
-      <c r="BG70" s="34" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="BH70" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI70" s="69">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BI70" s="69">
+      <c r="BJ70" s="51">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="BJ70" s="51">
-        <f t="shared" si="35"/>
-        <v>11.4</v>
+        <v>11.5473</v>
       </c>
     </row>
     <row r="71" spans="1:62" x14ac:dyDescent="0.25">
@@ -10757,7 +11166,7 @@
       <c r="AU71" s="33"/>
       <c r="AV71" s="43"/>
       <c r="AW71" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX71" s="33">
@@ -10766,10 +11175,10 @@
       </c>
       <c r="AY71" s="33">
         <f t="shared" si="24"/>
-        <v>1520</v>
+        <v>1534.43</v>
       </c>
       <c r="AZ71" s="34" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA71" s="34">
@@ -10781,36 +11190,36 @@
         <v>0</v>
       </c>
       <c r="BC71" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BD71" s="64" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BD71" s="64" t="str">
+        <v/>
+      </c>
+      <c r="BE71" s="61" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BF71" s="34">
+        <f t="shared" si="18"/>
+        <v>11.508224999999999</v>
+      </c>
+      <c r="BG71" s="34" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="BE71" s="61" t="str">
+      <c r="BH71" s="49">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="BF71" s="34">
-        <f t="shared" si="17"/>
-        <v>11.4</v>
-      </c>
-      <c r="BG71" s="34" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="BH71" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI71" s="69">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BI71" s="69">
+      <c r="BJ71" s="51">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="BJ71" s="51">
-        <f t="shared" si="35"/>
-        <v>11.4</v>
+        <v>11.508224999999999</v>
       </c>
     </row>
     <row r="72" spans="1:62" x14ac:dyDescent="0.25">
@@ -10883,7 +11292,7 @@
       <c r="AU72" s="33"/>
       <c r="AV72" s="43"/>
       <c r="AW72" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX72" s="33">
@@ -10892,10 +11301,10 @@
       </c>
       <c r="AY72" s="33">
         <f t="shared" si="24"/>
-        <v>1520</v>
+        <v>1535.11</v>
       </c>
       <c r="AZ72" s="34" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA72" s="34">
@@ -10907,36 +11316,36 @@
         <v>0</v>
       </c>
       <c r="BC72" s="34" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BD72" s="64" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BD72" s="64" t="str">
+      <c r="BE72" s="61">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="BF72" s="34">
+        <f t="shared" si="18"/>
+        <v>11.513325</v>
+      </c>
+      <c r="BG72" s="34" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="BE72" s="61">
+      <c r="BH72" s="49">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="BF72" s="34">
-        <f t="shared" si="17"/>
-        <v>11.4</v>
-      </c>
-      <c r="BG72" s="34" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="BH72" s="49">
+      <c r="BI72" s="69">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BI72" s="69">
+      <c r="BJ72" s="51">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="BJ72" s="51">
-        <f t="shared" si="35"/>
-        <v>11.4</v>
+        <v>11.513325</v>
       </c>
     </row>
     <row r="73" spans="1:62" x14ac:dyDescent="0.25">
@@ -11009,7 +11418,7 @@
       <c r="AU73" s="33"/>
       <c r="AV73" s="43"/>
       <c r="AW73" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX73" s="33">
@@ -11018,10 +11427,10 @@
       </c>
       <c r="AY73" s="33">
         <f t="shared" ref="AY73:AY80" si="37">AY67+SUM(AF73:AH73,AL73:AM73)-AN73</f>
-        <v>1520</v>
+        <v>1538.23</v>
       </c>
       <c r="AZ73" s="34" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA73" s="34">
@@ -11033,35 +11442,35 @@
         <v>0</v>
       </c>
       <c r="BC73" s="34" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BD73" s="64">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BD73" s="64">
+        <v>0</v>
+      </c>
+      <c r="BE73" s="61" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BF73" s="34" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BG73" s="34">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="BE73" s="61" t="str">
+      <c r="BH73" s="49">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="BF73" s="34" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="BG73" s="34">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="BH73" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI73" s="69">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BI73" s="69">
+      <c r="BJ73" s="51">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="BJ73" s="51">
-        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -11135,7 +11544,7 @@
       <c r="AU74" s="20"/>
       <c r="AV74" s="44"/>
       <c r="AW74" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX74" s="20">
@@ -11144,10 +11553,10 @@
       </c>
       <c r="AY74" s="20">
         <f t="shared" si="37"/>
-        <v>1520</v>
+        <v>1538.88</v>
       </c>
       <c r="AZ74" s="21" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA74" s="21">
@@ -11159,15 +11568,15 @@
         <v>0</v>
       </c>
       <c r="BC74" s="21" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BD74" s="21">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BD74" s="21">
-        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BE74" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BF74" s="21" t="str">
@@ -11175,19 +11584,19 @@
         <v/>
       </c>
       <c r="BG74" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BH74" s="49">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BI74" s="69">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BI74" s="69">
+      <c r="BJ74" s="51">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="BJ74" s="51">
-        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -11261,7 +11670,7 @@
       <c r="AU75" s="4"/>
       <c r="AV75" s="25"/>
       <c r="AW75" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX75" s="16">
@@ -11270,10 +11679,10 @@
       </c>
       <c r="AY75" s="16">
         <f t="shared" si="37"/>
-        <v>1505</v>
+        <v>1521.74</v>
       </c>
       <c r="AZ75" s="17" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA75" s="17">
@@ -11285,33 +11694,33 @@
         <v>0</v>
       </c>
       <c r="BC75" s="17" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BD75" s="17" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BD75" s="17" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
       <c r="BE75" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BF75" s="17">
         <f t="shared" si="38"/>
-        <v>11.2875</v>
+        <v>11.41305</v>
       </c>
       <c r="BG75" s="17" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BH75" s="48">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BI75" s="65"/>
       <c r="BJ75" s="53">
-        <f t="shared" si="35"/>
-        <v>11.2875</v>
+        <f t="shared" si="34"/>
+        <v>11.41305</v>
       </c>
     </row>
     <row r="76" spans="1:62" x14ac:dyDescent="0.25">
@@ -11384,7 +11793,7 @@
       <c r="AU76" s="30"/>
       <c r="AV76" s="2"/>
       <c r="AW76" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX76" s="33">
@@ -11393,10 +11802,10 @@
       </c>
       <c r="AY76" s="33">
         <f t="shared" si="37"/>
-        <v>1505</v>
+        <v>1524.64</v>
       </c>
       <c r="AZ76" s="34" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA76" s="34">
@@ -11408,33 +11817,33 @@
         <v>0</v>
       </c>
       <c r="BC76" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BD76" s="64" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BD76" s="64" t="str">
-        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BE76" s="61" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BF76" s="34">
         <f t="shared" si="38"/>
-        <v>11.2875</v>
+        <v>11.434800000000001</v>
       </c>
       <c r="BG76" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BH76" s="49">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BI76" s="66"/>
       <c r="BJ76" s="51">
-        <f t="shared" si="35"/>
-        <v>11.2875</v>
+        <f t="shared" si="34"/>
+        <v>11.434800000000001</v>
       </c>
     </row>
     <row r="77" spans="1:62" x14ac:dyDescent="0.25">
@@ -11507,7 +11916,7 @@
       <c r="AU77" s="33"/>
       <c r="AV77" s="43"/>
       <c r="AW77" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX77" s="33">
@@ -11516,10 +11925,10 @@
       </c>
       <c r="AY77" s="33">
         <f t="shared" si="37"/>
-        <v>1505</v>
+        <v>1519.43</v>
       </c>
       <c r="AZ77" s="34" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA77" s="34">
@@ -11531,33 +11940,33 @@
         <v>0</v>
       </c>
       <c r="BC77" s="34">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BD77" s="64" t="str">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BD77" s="64" t="str">
-        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BE77" s="61" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BF77" s="34">
         <f t="shared" si="38"/>
-        <v>11.2875</v>
+        <v>11.395725000000001</v>
       </c>
       <c r="BG77" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BH77" s="49">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BI77" s="66"/>
       <c r="BJ77" s="51">
-        <f t="shared" si="35"/>
-        <v>11.2875</v>
+        <f t="shared" si="34"/>
+        <v>11.395725000000001</v>
       </c>
     </row>
     <row r="78" spans="1:62" x14ac:dyDescent="0.25">
@@ -11630,7 +12039,7 @@
       <c r="AU78" s="33"/>
       <c r="AV78" s="43"/>
       <c r="AW78" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX78" s="33">
@@ -11639,10 +12048,10 @@
       </c>
       <c r="AY78" s="33">
         <f t="shared" si="37"/>
-        <v>1505</v>
+        <v>1520.11</v>
       </c>
       <c r="AZ78" s="34" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA78" s="34">
@@ -11654,33 +12063,33 @@
         <v>0</v>
       </c>
       <c r="BC78" s="34" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BD78" s="64" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BD78" s="64" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
       <c r="BE78" s="61">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BF78" s="34">
         <f t="shared" si="38"/>
-        <v>11.2875</v>
+        <v>11.400824999999999</v>
       </c>
       <c r="BG78" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BH78" s="49">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BI78" s="66"/>
       <c r="BJ78" s="51">
-        <f t="shared" si="35"/>
-        <v>11.2875</v>
+        <f t="shared" si="34"/>
+        <v>11.400824999999999</v>
       </c>
     </row>
     <row r="79" spans="1:62" x14ac:dyDescent="0.25">
@@ -11753,7 +12162,7 @@
       <c r="AU79" s="33"/>
       <c r="AV79" s="43"/>
       <c r="AW79" s="18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX79" s="33">
@@ -11762,10 +12171,10 @@
       </c>
       <c r="AY79" s="33">
         <f t="shared" si="37"/>
-        <v>1505</v>
+        <v>1523.23</v>
       </c>
       <c r="AZ79" s="34" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA79" s="34">
@@ -11777,15 +12186,15 @@
         <v>0</v>
       </c>
       <c r="BC79" s="34" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BD79" s="64">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BD79" s="64">
-        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BE79" s="61" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BF79" s="34" t="str">
@@ -11793,16 +12202,16 @@
         <v/>
       </c>
       <c r="BG79" s="34">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BH79" s="49">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BI79" s="66"/>
       <c r="BJ79" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
@@ -11876,7 +12285,7 @@
       <c r="AU80" s="20"/>
       <c r="AV80" s="44"/>
       <c r="AW80" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AX80" s="20">
@@ -11885,10 +12294,10 @@
       </c>
       <c r="AY80" s="20">
         <f t="shared" si="37"/>
-        <v>1505</v>
+        <v>1523.88</v>
       </c>
       <c r="AZ80" s="21" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="BA80" s="21">
@@ -11900,15 +12309,15 @@
         <v>0</v>
       </c>
       <c r="BC80" s="21" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BD80" s="21">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BD80" s="21">
-        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BE80" s="62" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BF80" s="21" t="str">
@@ -11916,16 +12325,16 @@
         <v/>
       </c>
       <c r="BG80" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BH80" s="50">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BI80" s="67"/>
       <c r="BJ80" s="52">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
@@ -11947,17 +12356,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY3:BB80">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="11">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="11">
       <formula>LEN(TRIM(AY3))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW3:AX80">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="2">
       <formula>LEN(TRIM(AW3))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU3:AV80">
-    <cfRule type="expression" dxfId="1" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>IF($B3 = "Julia", TRUE, FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11967,15 +12376,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -12198,6 +12598,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12217,14 +12626,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12243,6 +12644,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>

--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1456" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C30635D3-09A0-4173-9F39-19F0C3F69858}"/>
+  <xr:revisionPtr revIDLastSave="1580" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72B66EAB-A363-4679-9E46-99848A85ED23}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MasterDataTable!$A$2:$BG$314</definedName>
@@ -948,7 +949,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -1036,6 +1037,10 @@
     <xf numFmtId="166" fontId="0" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="39" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="39" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1487,82 +1492,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="72" t="s">
+      <c r="A1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="85" t="s">
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="77"/>
+      <c r="T1" s="77"/>
+      <c r="U1" s="77"/>
+      <c r="V1" s="77"/>
+      <c r="W1" s="77"/>
+      <c r="X1" s="77"/>
+      <c r="Y1" s="77"/>
+      <c r="Z1" s="77"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="86"/>
-      <c r="AD1" s="86"/>
-      <c r="AE1" s="86"/>
-      <c r="AF1" s="86"/>
-      <c r="AG1" s="86"/>
-      <c r="AH1" s="86"/>
-      <c r="AI1" s="86"/>
-      <c r="AJ1" s="86"/>
-      <c r="AK1" s="86"/>
-      <c r="AL1" s="86"/>
-      <c r="AM1" s="86"/>
-      <c r="AN1" s="87"/>
-      <c r="AO1" s="80" t="s">
+      <c r="AC1" s="90"/>
+      <c r="AD1" s="90"/>
+      <c r="AE1" s="90"/>
+      <c r="AF1" s="90"/>
+      <c r="AG1" s="90"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="90"/>
+      <c r="AJ1" s="90"/>
+      <c r="AK1" s="90"/>
+      <c r="AL1" s="90"/>
+      <c r="AM1" s="90"/>
+      <c r="AN1" s="91"/>
+      <c r="AO1" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="AP1" s="80"/>
-      <c r="AQ1" s="80"/>
-      <c r="AR1" s="80"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="82" t="s">
+      <c r="AP1" s="84"/>
+      <c r="AQ1" s="84"/>
+      <c r="AR1" s="84"/>
+      <c r="AS1" s="85"/>
+      <c r="AT1" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="AU1" s="83"/>
-      <c r="AV1" s="84"/>
-      <c r="AW1" s="78" t="s">
+      <c r="AU1" s="87"/>
+      <c r="AV1" s="88"/>
+      <c r="AW1" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="AX1" s="79"/>
-      <c r="AY1" s="79"/>
-      <c r="AZ1" s="79"/>
-      <c r="BA1" s="79"/>
-      <c r="BB1" s="79"/>
-      <c r="BC1" s="79"/>
-      <c r="BD1" s="79"/>
-      <c r="BE1" s="79"/>
-      <c r="BF1" s="79"/>
-      <c r="BG1" s="79"/>
-      <c r="BH1" s="75" t="s">
+      <c r="AX1" s="83"/>
+      <c r="AY1" s="83"/>
+      <c r="AZ1" s="83"/>
+      <c r="BA1" s="83"/>
+      <c r="BB1" s="83"/>
+      <c r="BC1" s="83"/>
+      <c r="BD1" s="83"/>
+      <c r="BE1" s="83"/>
+      <c r="BF1" s="83"/>
+      <c r="BG1" s="83"/>
+      <c r="BH1" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="BI1" s="76"/>
-      <c r="BJ1" s="77"/>
+      <c r="BI1" s="80"/>
+      <c r="BJ1" s="81"/>
     </row>
     <row r="2" spans="1:62" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
@@ -1863,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="AL3" s="16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="16">
         <v>0</v>
@@ -2056,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="AL4" s="33">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM4" s="33">
         <v>0</v>
@@ -2251,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="AL5" s="33">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM5" s="33">
         <v>0</v>
@@ -2446,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="AL6" s="33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM6" s="33">
         <v>0</v>
@@ -2639,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="AL7" s="33">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM7" s="33">
         <v>0</v>
@@ -2837,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="AL8" s="20">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AM8" s="20">
         <v>0</v>
@@ -2941,7 +2946,9 @@
         <v>45450.408518518503</v>
       </c>
       <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
+      <c r="G9" s="10">
+        <v>465.95</v>
+      </c>
       <c r="H9" s="10">
         <v>19.399999999999999</v>
       </c>
@@ -3021,17 +3028,25 @@
         <v>0</v>
       </c>
       <c r="AH9" s="16">
-        <v>0.2</v>
-      </c>
-      <c r="AI9" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="AI9" s="16">
+        <v>9.7663103999999987E-3</v>
+      </c>
       <c r="AJ9" s="16">
         <v>8</v>
       </c>
       <c r="AK9" s="16">
         <v>0</v>
       </c>
-      <c r="AL9" s="16"/>
-      <c r="AM9" s="16"/>
+      <c r="AL9" s="16">
+        <f t="shared" ref="AL9:AL20" si="15">AJ9-AJ3</f>
+        <v>8</v>
+      </c>
+      <c r="AM9" s="16">
+        <f t="shared" ref="AM9:AM20" si="16">AK9-AK3</f>
+        <v>0</v>
+      </c>
       <c r="AN9" s="45">
         <v>15</v>
       </c>
@@ -3055,19 +3070,19 @@
       <c r="AV9" s="42"/>
       <c r="AW9" s="15">
         <f t="shared" si="3"/>
-        <v>9.7156223999999985E-3</v>
+        <v>9.7663103999999987E-3</v>
       </c>
       <c r="AX9" s="16">
-        <f t="shared" ref="AX9:AX40" si="15">AW3*24</f>
+        <f t="shared" ref="AX9:AX40" si="17">AW3*24</f>
         <v>0.16378199999999998</v>
       </c>
       <c r="AY9" s="16">
         <f>AY3+SUM(AF9:AH9,AL9:AM9)-AN9</f>
-        <v>1686.74</v>
+        <v>1695.54</v>
       </c>
       <c r="AZ9" s="17">
         <f>IF(ISBLANK(AJ9),NA(),IFERROR(AJ9/AY9,0))</f>
-        <v>4.7428767919181379E-3</v>
+        <v>4.7182608490510397E-3</v>
       </c>
       <c r="BA9" s="17">
         <f t="shared" si="6"/>
@@ -3075,7 +3090,7 @@
       </c>
       <c r="BB9" s="17">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.23439144959999997</v>
       </c>
       <c r="BC9" s="17" t="str">
         <f t="shared" si="13"/>
@@ -3086,12 +3101,12 @@
         <v/>
       </c>
       <c r="BE9" s="60">
-        <f t="shared" si="8"/>
-        <v>9.7156223999999985E-3</v>
+        <f>IF(B9="No MPC", AS9*I9*AY9/1000,"")</f>
+        <v>9.7663103999999987E-3</v>
       </c>
       <c r="BF9" s="17">
         <f>IF(O9&lt;10, IF(B9&lt;&gt;"Julia",((5-O9)*AY9)/400, ""),0)</f>
-        <v>17.246916500000001</v>
+        <v>17.336896499999998</v>
       </c>
       <c r="BG9" s="17" t="str">
         <f t="shared" si="2"/>
@@ -3099,15 +3114,15 @@
       </c>
       <c r="BH9" s="49">
         <f t="shared" si="9"/>
-        <v>25.235382857142856</v>
+        <v>25.367039999999999</v>
       </c>
       <c r="BI9" s="69">
         <f t="shared" si="10"/>
-        <v>9.7156223999999985E-3</v>
+        <v>9.7663103999999987E-3</v>
       </c>
       <c r="BJ9" s="51">
         <f t="shared" si="11"/>
-        <v>17.246916500000001</v>
+        <v>17.336896499999998</v>
       </c>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.25">
@@ -3127,7 +3142,9 @@
         <v>45450.411412037</v>
       </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="32"/>
+      <c r="G10" s="32">
+        <v>446.74</v>
+      </c>
       <c r="H10" s="32">
         <v>16.100000000000001</v>
       </c>
@@ -3207,17 +3224,25 @@
         <v>0</v>
       </c>
       <c r="AH10" s="33">
-        <v>0.2</v>
-      </c>
-      <c r="AI10" s="33"/>
+        <v>1</v>
+      </c>
+      <c r="AI10" s="33">
+        <v>9.0267334057285136E-3</v>
+      </c>
       <c r="AJ10" s="33">
         <v>6</v>
       </c>
       <c r="AK10" s="33">
         <v>0</v>
       </c>
-      <c r="AL10" s="33"/>
-      <c r="AM10" s="33"/>
+      <c r="AL10" s="74">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
+      <c r="AM10" s="33">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="AN10" s="46">
         <v>15</v>
       </c>
@@ -3236,24 +3261,26 @@
       <c r="AS10" s="33">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AT10" s="18"/>
+      <c r="AT10" s="18">
+        <v>7.6622197686031096E-3</v>
+      </c>
       <c r="AU10" s="33"/>
       <c r="AV10" s="43"/>
       <c r="AW10" s="18">
         <f t="shared" si="3"/>
-        <v>8.0595828000000012E-3</v>
+        <v>8.0920187999999997E-3</v>
       </c>
       <c r="AX10" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.15043679999999998</v>
       </c>
       <c r="AY10" s="33">
-        <f t="shared" ref="AY10:AY40" si="16">AY4+SUM(AF10:AH10,AL10:AM10)-AN10</f>
-        <v>1689.64</v>
+        <f t="shared" ref="AY10:AY40" si="18">AY4+SUM(AF10:AH10,AL10:AM10)-AN10</f>
+        <v>1696.44</v>
       </c>
       <c r="AZ10" s="34">
         <f t="shared" si="5"/>
-        <v>3.5510522951634664E-3</v>
+        <v>3.5368182782768622E-3</v>
       </c>
       <c r="BA10" s="34">
         <f t="shared" si="6"/>
@@ -3261,11 +3288,11 @@
       </c>
       <c r="BB10" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.21664160173748431</v>
       </c>
       <c r="BC10" s="34">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>9.0267334057285136E-3</v>
       </c>
       <c r="BD10" s="64" t="str">
         <f t="shared" si="1"/>
@@ -3276,8 +3303,8 @@
         <v/>
       </c>
       <c r="BF10" s="34">
-        <f t="shared" ref="BF10:BF12" si="17">IF(O10&lt;10, IF(B10&lt;&gt;"Julia",((5-O10)*AY10)/400, ""),0)</f>
-        <v>17.530015000000002</v>
+        <f t="shared" ref="BF10:BF12" si="19">IF(O10&lt;10, IF(B10&lt;&gt;"Julia",((5-O10)*AY10)/400, ""),0)</f>
+        <v>17.600565000000003</v>
       </c>
       <c r="BG10" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3285,15 +3312,15 @@
       </c>
       <c r="BH10" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>23.446060794100038</v>
       </c>
       <c r="BI10" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>9.0267334057285136E-3</v>
       </c>
       <c r="BJ10" s="51">
         <f t="shared" si="11"/>
-        <v>17.530015000000002</v>
+        <v>17.600565000000003</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.25">
@@ -3313,7 +3340,9 @@
         <v>45450.415150462999</v>
       </c>
       <c r="F11" s="11"/>
-      <c r="G11" s="32"/>
+      <c r="G11" s="32">
+        <v>467.44</v>
+      </c>
       <c r="H11" s="32">
         <v>16.100000000000001</v>
       </c>
@@ -3393,17 +3422,25 @@
         <v>0</v>
       </c>
       <c r="AH11" s="33">
-        <v>0.2</v>
-      </c>
-      <c r="AI11" s="33"/>
+        <v>1</v>
+      </c>
+      <c r="AI11" s="33">
+        <v>8.7115764713592454E-3</v>
+      </c>
       <c r="AJ11" s="33">
         <v>6</v>
       </c>
       <c r="AK11" s="33">
         <v>0</v>
       </c>
-      <c r="AL11" s="33"/>
-      <c r="AM11" s="33"/>
+      <c r="AL11" s="74">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
+      <c r="AM11" s="33">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="AN11" s="46">
         <v>15</v>
       </c>
@@ -3422,24 +3459,26 @@
       <c r="AS11" s="33">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AT11" s="18"/>
+      <c r="AT11" s="18">
+        <v>7.41748320379683E-3</v>
+      </c>
       <c r="AU11" s="33"/>
       <c r="AV11" s="43"/>
       <c r="AW11" s="18">
         <f t="shared" si="3"/>
-        <v>8.0347310999999994E-3</v>
+        <v>8.0671671000000014E-3</v>
       </c>
       <c r="AX11" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.16135559999999999</v>
       </c>
       <c r="AY11" s="33">
-        <f t="shared" si="16"/>
-        <v>1684.43</v>
+        <f t="shared" si="18"/>
+        <v>1691.23</v>
       </c>
       <c r="AZ11" s="34">
         <f t="shared" si="5"/>
-        <v>3.5620358222069187E-3</v>
+        <v>3.5477137941025169E-3</v>
       </c>
       <c r="BA11" s="34">
         <f t="shared" si="6"/>
@@ -3447,11 +3486,11 @@
       </c>
       <c r="BB11" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.20907783531262189</v>
       </c>
       <c r="BC11" s="34">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>8.7115764713592454E-3</v>
       </c>
       <c r="BD11" s="64" t="str">
         <f t="shared" si="1"/>
@@ -3462,8 +3501,8 @@
         <v/>
       </c>
       <c r="BF11" s="34">
-        <f t="shared" si="17"/>
-        <v>17.181186</v>
+        <f t="shared" si="19"/>
+        <v>17.250546</v>
       </c>
       <c r="BG11" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3471,15 +3510,15 @@
       </c>
       <c r="BH11" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>22.62747135417986</v>
       </c>
       <c r="BI11" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>8.7115764713592454E-3</v>
       </c>
       <c r="BJ11" s="51">
         <f t="shared" si="11"/>
-        <v>17.181186</v>
+        <v>17.250546</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.25">
@@ -3499,7 +3538,9 @@
         <v>45450.439641203702</v>
       </c>
       <c r="F12" s="11"/>
-      <c r="G12" s="32"/>
+      <c r="G12" s="32">
+        <v>546.27</v>
+      </c>
       <c r="H12" s="32">
         <v>25.1</v>
       </c>
@@ -3579,17 +3620,25 @@
         <v>0</v>
       </c>
       <c r="AH12" s="33">
-        <v>0.2</v>
-      </c>
-      <c r="AI12" s="33"/>
+        <v>1</v>
+      </c>
+      <c r="AI12" s="33">
+        <v>1.25158158E-2</v>
+      </c>
       <c r="AJ12" s="33">
         <v>10</v>
       </c>
       <c r="AK12" s="33">
         <v>0</v>
       </c>
-      <c r="AL12" s="33"/>
-      <c r="AM12" s="33"/>
+      <c r="AL12" s="74">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="AM12" s="33">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="AN12" s="46">
         <v>15</v>
       </c>
@@ -3613,19 +3662,19 @@
       <c r="AV12" s="43"/>
       <c r="AW12" s="18">
         <f t="shared" si="3"/>
-        <v>1.2436111799999998E-2</v>
+        <v>1.25158158E-2</v>
       </c>
       <c r="AX12" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.19532519999999998</v>
       </c>
       <c r="AY12" s="33">
-        <f t="shared" si="16"/>
-        <v>1685.11</v>
+        <f t="shared" si="18"/>
+        <v>1695.91</v>
       </c>
       <c r="AZ12" s="34">
         <f t="shared" si="5"/>
-        <v>5.9343306965123944E-3</v>
+        <v>5.8965393210724621E-3</v>
       </c>
       <c r="BA12" s="34">
         <f t="shared" si="6"/>
@@ -3633,7 +3682,7 @@
       </c>
       <c r="BB12" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.30037957920000002</v>
       </c>
       <c r="BC12" s="34" t="str">
         <f t="shared" si="13"/>
@@ -3645,11 +3694,11 @@
       </c>
       <c r="BE12" s="61">
         <f t="shared" si="8"/>
-        <v>1.2436111799999998E-2</v>
+        <v>1.25158158E-2</v>
       </c>
       <c r="BF12" s="34">
-        <f t="shared" si="17"/>
-        <v>21.063874999999999</v>
+        <f t="shared" si="19"/>
+        <v>21.198875000000001</v>
       </c>
       <c r="BG12" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3657,15 +3706,15 @@
       </c>
       <c r="BH12" s="49">
         <f t="shared" si="9"/>
-        <v>32.30158909090909</v>
+        <v>32.508612467532465</v>
       </c>
       <c r="BI12" s="69">
         <f t="shared" si="10"/>
-        <v>1.2436111799999998E-2</v>
+        <v>1.25158158E-2</v>
       </c>
       <c r="BJ12" s="51">
         <f t="shared" si="11"/>
-        <v>21.063874999999999</v>
+        <v>21.198875000000001</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.25">
@@ -3685,7 +3734,9 @@
         <v>45450.444930555597</v>
       </c>
       <c r="F13" s="11"/>
-      <c r="G13" s="32"/>
+      <c r="G13" s="32">
+        <v>428.11</v>
+      </c>
       <c r="H13" s="32">
         <v>15.4</v>
       </c>
@@ -3765,17 +3816,25 @@
         <v>0</v>
       </c>
       <c r="AH13" s="33">
-        <v>0.2</v>
-      </c>
-      <c r="AI13" s="33"/>
+        <v>1</v>
+      </c>
+      <c r="AI13" s="33">
+        <v>1.5235230244764976E-2</v>
+      </c>
       <c r="AJ13" s="33">
         <v>7</v>
       </c>
       <c r="AK13" s="33">
         <v>0</v>
       </c>
-      <c r="AL13" s="33"/>
-      <c r="AM13" s="33"/>
+      <c r="AL13" s="74">
+        <f t="shared" si="15"/>
+        <v>7</v>
+      </c>
+      <c r="AM13" s="33">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="AN13" s="46">
         <v>15</v>
       </c>
@@ -3795,23 +3854,27 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AT13" s="18"/>
-      <c r="AU13" s="33"/>
-      <c r="AV13" s="43"/>
+      <c r="AU13">
+        <v>1.2935344040177099E-2</v>
+      </c>
+      <c r="AV13">
+        <v>7.5395846178023399E-3</v>
+      </c>
       <c r="AW13" s="18">
         <f t="shared" si="3"/>
-        <v>7.6983287999999993E-3</v>
+        <v>7.7338967999999991E-3</v>
       </c>
       <c r="AX13" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.14679719999999999</v>
       </c>
       <c r="AY13" s="33">
-        <f t="shared" si="16"/>
-        <v>1688.23</v>
+        <f t="shared" si="18"/>
+        <v>1696.03</v>
       </c>
       <c r="AZ13" s="34">
         <f t="shared" si="5"/>
-        <v>4.1463544659199282E-3</v>
+        <v>4.1272854843369513E-3</v>
       </c>
       <c r="BA13" s="34">
         <f t="shared" si="6"/>
@@ -3819,7 +3882,7 @@
       </c>
       <c r="BB13" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.36564552587435944</v>
       </c>
       <c r="BC13" s="34" t="str">
         <f t="shared" si="13"/>
@@ -3827,31 +3890,31 @@
       </c>
       <c r="BD13" s="64">
         <f>IF(B13="Julia",AU13*AY13/24/60,"")</f>
-        <v>0</v>
+        <v>1.5235230244764976E-2</v>
       </c>
       <c r="BE13" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="BF13" s="34">
-        <f t="shared" ref="BF13:BF73" si="18">IF(O13&lt;1.5, IF(B13&lt;&gt;"Julia",((3-O13)*AY13)/400, ""),0)</f>
-        <v>0</v>
+      <c r="BF13" s="71">
+        <f>IF(O13&lt;10, IF(B13&lt;&gt;"Jul",((5-O13)*AY13)/400, ""),0)</f>
+        <v>13.907446</v>
       </c>
       <c r="BG13" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12.787361699331303</v>
       </c>
       <c r="BH13" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>39.572026609779158</v>
       </c>
       <c r="BI13" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BJ13" s="51">
+        <v>1.5235230244764976E-2</v>
+      </c>
+      <c r="BJ13" s="73">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>13.907446</v>
       </c>
     </row>
     <row r="14" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3871,7 +3934,9 @@
         <v>45450.4586921296</v>
       </c>
       <c r="F14" s="13"/>
-      <c r="G14" s="14"/>
+      <c r="G14" s="14">
+        <v>446.1</v>
+      </c>
       <c r="H14" s="14">
         <v>16.5</v>
       </c>
@@ -3951,17 +4016,25 @@
         <v>0</v>
       </c>
       <c r="AH14" s="20">
-        <v>0.2</v>
-      </c>
-      <c r="AI14" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="AI14" s="20">
+        <v>8.2507248000000012E-3</v>
+      </c>
       <c r="AJ14" s="20">
         <v>8</v>
       </c>
       <c r="AK14" s="20">
         <v>0</v>
       </c>
-      <c r="AL14" s="20"/>
-      <c r="AM14" s="20"/>
+      <c r="AL14" s="20">
+        <f t="shared" si="15"/>
+        <v>8</v>
+      </c>
+      <c r="AM14" s="20">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="AN14" s="47">
         <v>15</v>
       </c>
@@ -3981,23 +4054,29 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AT14" s="19"/>
-      <c r="AU14" s="20"/>
-      <c r="AV14" s="44"/>
+      <c r="AU14" s="20">
+        <f>BE14*60*24/AY14</f>
+        <v>6.998400000000001E-3</v>
+      </c>
+      <c r="AV14" s="20">
+        <f>BF14/AY14</f>
+        <v>1.035E-2</v>
+      </c>
       <c r="AW14" s="19">
         <f t="shared" si="3"/>
-        <v>8.2079567999999992E-3</v>
+        <v>8.2507248000000012E-3</v>
       </c>
       <c r="AX14" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.1565028</v>
       </c>
       <c r="AY14" s="20">
-        <f t="shared" si="16"/>
-        <v>1688.88</v>
+        <f t="shared" si="18"/>
+        <v>1697.68</v>
       </c>
       <c r="AZ14" s="21">
         <f t="shared" si="5"/>
-        <v>4.7368670361422954E-3</v>
+        <v>4.7123132745864943E-3</v>
       </c>
       <c r="BA14" s="21">
         <f t="shared" si="6"/>
@@ -4005,7 +4084,7 @@
       </c>
       <c r="BB14" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.19801739520000003</v>
       </c>
       <c r="BC14" s="21" t="str">
         <f t="shared" si="13"/>
@@ -4013,31 +4092,31 @@
       </c>
       <c r="BD14" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BE14" s="62" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BF14" s="21" t="str">
-        <f t="shared" si="18"/>
-        <v/>
+        <v>8.2507248000000012E-3</v>
+      </c>
+      <c r="BE14" s="62">
+        <f>AS14*I14*AY14/1000</f>
+        <v>8.2507248000000012E-3</v>
+      </c>
+      <c r="BF14" s="72">
+        <f>IF(O14&lt;10, IF(B14&lt;&gt;"Jul",((5-O14)*AY14)/400, ""),0)</f>
+        <v>17.570988</v>
       </c>
       <c r="BG14" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17.570988</v>
       </c>
       <c r="BH14" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>21.430454025974029</v>
       </c>
       <c r="BI14" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BJ14" s="51">
+        <v>8.2507248000000012E-3</v>
+      </c>
+      <c r="BJ14" s="73">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>17.570988</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.25">
@@ -4053,41 +4132,109 @@
       <c r="D15" s="4">
         <v>2</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5">
+        <v>45451.506053240701</v>
+      </c>
       <c r="F15" s="9"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
-      <c r="AA15" s="27"/>
-      <c r="AB15" s="15"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="16"/>
-      <c r="AE15" s="16"/>
-      <c r="AF15" s="16"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="16"/>
+      <c r="G15" s="10">
+        <v>993.18</v>
+      </c>
+      <c r="H15" s="10">
+        <v>24</v>
+      </c>
+      <c r="I15" s="10">
+        <v>23.6</v>
+      </c>
+      <c r="J15" s="10">
+        <v>98.2</v>
+      </c>
+      <c r="K15" s="10">
+        <v>16.7</v>
+      </c>
+      <c r="L15" s="10">
+        <v>323</v>
+      </c>
+      <c r="M15" s="10">
+        <v>1.38</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="O15" s="10">
+        <v>0.34</v>
+      </c>
+      <c r="P15" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="R15" s="10">
+        <v>3.72</v>
+      </c>
+      <c r="S15" s="10">
+        <v>7.0839999999999996</v>
+      </c>
+      <c r="T15" s="10">
+        <v>114.9</v>
+      </c>
+      <c r="U15" s="10">
+        <v>26.3</v>
+      </c>
+      <c r="V15" s="10">
+        <v>2.98</v>
+      </c>
+      <c r="W15" s="10">
+        <v>136.4</v>
+      </c>
+      <c r="X15" s="10">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="Y15" s="10">
+        <v>100.7</v>
+      </c>
+      <c r="Z15" s="10">
+        <v>21.3</v>
+      </c>
+      <c r="AA15" s="27">
+        <v>7.1219999999999999</v>
+      </c>
+      <c r="AB15" s="15">
+        <v>299</v>
+      </c>
+      <c r="AC15" s="16">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="AD15" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="AE15" s="16">
+        <v>34</v>
+      </c>
+      <c r="AF15" s="16">
+        <v>23.41</v>
+      </c>
+      <c r="AG15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="16">
+        <v>2</v>
+      </c>
       <c r="AI15" s="16"/>
-      <c r="AJ15" s="16"/>
-      <c r="AK15" s="16"/>
-      <c r="AL15" s="16"/>
-      <c r="AM15" s="16"/>
+      <c r="AJ15" s="16">
+        <v>22.3</v>
+      </c>
+      <c r="AK15" s="16">
+        <v>19.55</v>
+      </c>
+      <c r="AL15" s="16">
+        <f t="shared" si="15"/>
+        <v>14.3</v>
+      </c>
+      <c r="AM15" s="16">
+        <f t="shared" si="16"/>
+        <v>19.55</v>
+      </c>
       <c r="AN15" s="45">
         <v>15</v>
       </c>
@@ -4111,23 +4258,23 @@
       <c r="AV15" s="42"/>
       <c r="AW15" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.2317784E-2</v>
       </c>
       <c r="AX15" s="16">
-        <f t="shared" si="15"/>
-        <v>0.23317493759999997</v>
+        <f t="shared" si="17"/>
+        <v>0.23439144959999997</v>
       </c>
       <c r="AY15" s="16">
-        <f t="shared" si="16"/>
-        <v>1671.74</v>
-      </c>
-      <c r="AZ15" s="17" t="e">
+        <f>AY9+SUM(AF15:AH15,AL15:AM15)-AN15</f>
+        <v>1739.8</v>
+      </c>
+      <c r="AZ15" s="17">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>1.2817565237383609E-2</v>
       </c>
       <c r="BA15" s="17">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.3117647058823529E-2</v>
       </c>
       <c r="BB15" s="17">
         <f t="shared" si="7"/>
@@ -4143,11 +4290,11 @@
       </c>
       <c r="BE15" s="60">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.2317784E-2</v>
       </c>
       <c r="BF15" s="17">
         <f>IF(O15&lt;1.5, IF(B15&lt;&gt;"Julia",((3-O15)*AY15)/400, ""),0)</f>
-        <v>12.53805</v>
+        <v>11.56967</v>
       </c>
       <c r="BG15" s="17" t="str">
         <f t="shared" si="2"/>
@@ -4155,15 +4302,15 @@
       </c>
       <c r="BH15" s="48">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>31.994244155844157</v>
       </c>
       <c r="BI15" s="68">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1.2317784E-2</v>
       </c>
       <c r="BJ15" s="53">
         <f t="shared" si="11"/>
-        <v>12.53805</v>
+        <v>11.56967</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.25">
@@ -4179,41 +4326,109 @@
       <c r="D16" s="30">
         <v>2</v>
       </c>
-      <c r="E16" s="31"/>
+      <c r="E16" s="31">
+        <v>45451.516516203701</v>
+      </c>
       <c r="F16" s="11"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="28"/>
-      <c r="AB16" s="18"/>
-      <c r="AC16" s="33"/>
-      <c r="AD16" s="33"/>
-      <c r="AE16" s="33"/>
-      <c r="AF16" s="33"/>
-      <c r="AG16" s="33"/>
-      <c r="AH16" s="33"/>
+      <c r="G16" s="32">
+        <v>931.29</v>
+      </c>
+      <c r="H16" s="32">
+        <v>21.7</v>
+      </c>
+      <c r="I16" s="32">
+        <v>21.4</v>
+      </c>
+      <c r="J16" s="32">
+        <v>98.7</v>
+      </c>
+      <c r="K16" s="32">
+        <v>17</v>
+      </c>
+      <c r="L16" s="32">
+        <v>329</v>
+      </c>
+      <c r="M16" s="32">
+        <v>1.26</v>
+      </c>
+      <c r="N16" s="32">
+        <v>0.4</v>
+      </c>
+      <c r="O16" s="32">
+        <v>0.09</v>
+      </c>
+      <c r="P16" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="Q16" s="32">
+        <v>0.09</v>
+      </c>
+      <c r="R16" s="32">
+        <v>3.73</v>
+      </c>
+      <c r="S16" s="32">
+        <v>7.1239999999999997</v>
+      </c>
+      <c r="T16" s="32">
+        <v>121.4</v>
+      </c>
+      <c r="U16" s="32">
+        <v>26.9</v>
+      </c>
+      <c r="V16" s="32">
+        <v>2.87</v>
+      </c>
+      <c r="W16" s="32">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="X16" s="32">
+        <v>38.6</v>
+      </c>
+      <c r="Y16" s="32">
+        <v>106.5</v>
+      </c>
+      <c r="Z16" s="32">
+        <v>21.7</v>
+      </c>
+      <c r="AA16" s="28">
+        <v>7.1630000000000003</v>
+      </c>
+      <c r="AB16" s="18">
+        <v>299</v>
+      </c>
+      <c r="AC16" s="33">
+        <v>0.435</v>
+      </c>
+      <c r="AD16" s="33">
+        <v>7.1</v>
+      </c>
+      <c r="AE16" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF16" s="33">
+        <v>25.196999999999999</v>
+      </c>
+      <c r="AG16" s="33">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="33">
+        <v>1.43</v>
+      </c>
       <c r="AI16" s="33"/>
-      <c r="AJ16" s="33"/>
-      <c r="AK16" s="33"/>
-      <c r="AL16" s="33"/>
-      <c r="AM16" s="33"/>
+      <c r="AJ16" s="33">
+        <v>19.2</v>
+      </c>
+      <c r="AK16" s="33">
+        <v>19.34</v>
+      </c>
+      <c r="AL16" s="33">
+        <f t="shared" si="15"/>
+        <v>13.2</v>
+      </c>
+      <c r="AM16" s="33">
+        <f t="shared" si="16"/>
+        <v>19.34</v>
+      </c>
       <c r="AN16" s="46">
         <v>15</v>
       </c>
@@ -4232,28 +4447,30 @@
       <c r="AS16" s="33">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AT16" s="18"/>
+      <c r="AT16" s="18">
+        <v>5.39005278937314E-3</v>
+      </c>
       <c r="AU16" s="33"/>
       <c r="AV16" s="43"/>
       <c r="AW16" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.1174696939999998E-2</v>
       </c>
       <c r="AX16" s="33">
-        <f t="shared" si="15"/>
-        <v>0.19342998720000004</v>
+        <f t="shared" si="17"/>
+        <v>0.19420845119999999</v>
       </c>
       <c r="AY16" s="33">
-        <f t="shared" si="16"/>
-        <v>1674.64</v>
-      </c>
-      <c r="AZ16" s="34" t="e">
+        <f t="shared" si="18"/>
+        <v>1740.607</v>
+      </c>
+      <c r="AZ16" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>1.1030634715360791E-2</v>
       </c>
       <c r="BA16" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.1294117647058823E-2</v>
       </c>
       <c r="BB16" s="34">
         <f t="shared" si="7"/>
@@ -4261,7 +4478,7 @@
       </c>
       <c r="BC16" s="34">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>6.5152525108002875E-3</v>
       </c>
       <c r="BD16" s="64" t="str">
         <f t="shared" si="1"/>
@@ -4272,8 +4489,8 @@
         <v/>
       </c>
       <c r="BF16" s="34">
-        <f t="shared" si="18"/>
-        <v>12.559800000000001</v>
+        <f t="shared" ref="BF16:BF73" si="20">IF(O16&lt;1.5, IF(B16&lt;&gt;"Julia",((3-O16)*AY16)/400, ""),0)</f>
+        <v>12.662915925</v>
       </c>
       <c r="BG16" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4281,15 +4498,15 @@
       </c>
       <c r="BH16" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>16.922733794286462</v>
       </c>
       <c r="BI16" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6.5152525108002875E-3</v>
       </c>
       <c r="BJ16" s="51">
         <f t="shared" si="11"/>
-        <v>12.559800000000001</v>
+        <v>12.662915925</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.25">
@@ -4305,41 +4522,109 @@
       <c r="D17" s="30">
         <v>2</v>
       </c>
-      <c r="E17" s="31"/>
+      <c r="E17" s="31">
+        <v>45451.5221296296</v>
+      </c>
       <c r="F17" s="11"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="32"/>
-      <c r="W17" s="32"/>
-      <c r="X17" s="32"/>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="32"/>
-      <c r="AA17" s="28"/>
-      <c r="AB17" s="18"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="33"/>
-      <c r="AE17" s="33"/>
-      <c r="AF17" s="33"/>
-      <c r="AG17" s="33"/>
-      <c r="AH17" s="33"/>
+      <c r="G17" s="32">
+        <v>945.81</v>
+      </c>
+      <c r="H17" s="32">
+        <v>23.6</v>
+      </c>
+      <c r="I17" s="32">
+        <v>23.2</v>
+      </c>
+      <c r="J17" s="32">
+        <v>98.2</v>
+      </c>
+      <c r="K17" s="32">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="L17" s="32">
+        <v>320</v>
+      </c>
+      <c r="M17" s="32">
+        <v>1.21</v>
+      </c>
+      <c r="N17" s="32">
+        <v>0.42</v>
+      </c>
+      <c r="O17" s="32">
+        <v>0.23</v>
+      </c>
+      <c r="P17" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="Q17" s="32">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R17" s="32">
+        <v>3.38</v>
+      </c>
+      <c r="S17" s="32">
+        <v>7.1180000000000003</v>
+      </c>
+      <c r="T17" s="32">
+        <v>105</v>
+      </c>
+      <c r="U17" s="32">
+        <v>0</v>
+      </c>
+      <c r="V17" s="32">
+        <v>3.01</v>
+      </c>
+      <c r="W17" s="32">
+        <v>135.4</v>
+      </c>
+      <c r="X17" s="32">
+        <v>32.9</v>
+      </c>
+      <c r="Y17" s="32">
+        <v>92.1</v>
+      </c>
+      <c r="Z17" s="32">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="28">
+        <v>7.1559999999999997</v>
+      </c>
+      <c r="AB17" s="18">
+        <v>301</v>
+      </c>
+      <c r="AC17" s="33">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="AD17" s="33">
+        <v>7.11</v>
+      </c>
+      <c r="AE17" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF17" s="33">
+        <v>19.446999999999999</v>
+      </c>
+      <c r="AG17" s="33">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="33">
+        <v>5.78</v>
+      </c>
       <c r="AI17" s="33"/>
-      <c r="AJ17" s="33"/>
-      <c r="AK17" s="33"/>
-      <c r="AL17" s="33"/>
-      <c r="AM17" s="33"/>
+      <c r="AJ17" s="33">
+        <v>19</v>
+      </c>
+      <c r="AK17" s="33">
+        <v>19.73</v>
+      </c>
+      <c r="AL17" s="33">
+        <f t="shared" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="AM17" s="33">
+        <f t="shared" si="16"/>
+        <v>19.73</v>
+      </c>
       <c r="AN17" s="46">
         <v>15</v>
       </c>
@@ -4358,28 +4643,30 @@
       <c r="AS17" s="33">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AT17" s="18"/>
+      <c r="AT17" s="18">
+        <v>5.6161059279389199E-3</v>
+      </c>
       <c r="AU17" s="33"/>
       <c r="AV17" s="43"/>
       <c r="AW17" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.2069941519999999E-2</v>
       </c>
       <c r="AX17" s="33">
-        <f t="shared" si="15"/>
-        <v>0.1928335464</v>
+        <f t="shared" si="17"/>
+        <v>0.19361201040000003</v>
       </c>
       <c r="AY17" s="33">
-        <f t="shared" si="16"/>
-        <v>1669.43</v>
-      </c>
-      <c r="AZ17" s="34" t="e">
+        <f t="shared" si="18"/>
+        <v>1734.1870000000001</v>
+      </c>
+      <c r="AZ17" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>1.0956142561327008E-2</v>
       </c>
       <c r="BA17" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.1176470588235295E-2</v>
       </c>
       <c r="BB17" s="34">
         <f t="shared" si="7"/>
@@ -4387,7 +4674,7 @@
       </c>
       <c r="BC17" s="34">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>6.7634568686490365E-3</v>
       </c>
       <c r="BD17" s="64" t="str">
         <f t="shared" si="1"/>
@@ -4398,8 +4685,8 @@
         <v/>
       </c>
       <c r="BF17" s="34">
-        <f t="shared" si="18"/>
-        <v>12.520725000000001</v>
+        <f t="shared" si="20"/>
+        <v>12.009244975000001</v>
       </c>
       <c r="BG17" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4407,15 +4694,15 @@
       </c>
       <c r="BH17" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>17.567420438049446</v>
       </c>
       <c r="BI17" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6.7634568686490365E-3</v>
       </c>
       <c r="BJ17" s="51">
         <f t="shared" si="11"/>
-        <v>12.520725000000001</v>
+        <v>12.009244975000001</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.25">
@@ -4431,41 +4718,99 @@
       <c r="D18" s="30">
         <v>2</v>
       </c>
-      <c r="E18" s="31"/>
+      <c r="E18" s="31">
+        <v>45451.5255555556</v>
+      </c>
       <c r="F18" s="11"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
       <c r="J18" s="32"/>
       <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="32"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="32"/>
-      <c r="U18" s="32"/>
-      <c r="V18" s="32"/>
-      <c r="W18" s="32"/>
-      <c r="X18" s="32"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="32"/>
-      <c r="AA18" s="28"/>
-      <c r="AB18" s="18"/>
-      <c r="AC18" s="33"/>
-      <c r="AD18" s="33"/>
-      <c r="AE18" s="33"/>
-      <c r="AF18" s="33"/>
-      <c r="AG18" s="33"/>
-      <c r="AH18" s="33"/>
+      <c r="L18" s="32">
+        <v>303</v>
+      </c>
+      <c r="M18" s="32">
+        <v>0.39</v>
+      </c>
+      <c r="N18" s="32">
+        <v>0.31</v>
+      </c>
+      <c r="O18" s="32">
+        <v>0</v>
+      </c>
+      <c r="P18" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="32">
+        <v>0.25</v>
+      </c>
+      <c r="R18" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="S18" s="32">
+        <v>7.36</v>
+      </c>
+      <c r="T18" s="32">
+        <v>152.9</v>
+      </c>
+      <c r="U18" s="32">
+        <v>18</v>
+      </c>
+      <c r="V18" s="32">
+        <v>5.22</v>
+      </c>
+      <c r="W18" s="32">
+        <v>127.5</v>
+      </c>
+      <c r="X18" s="32">
+        <v>84.4</v>
+      </c>
+      <c r="Y18" s="32">
+        <v>134.1</v>
+      </c>
+      <c r="Z18" s="32">
+        <v>14.6</v>
+      </c>
+      <c r="AA18" s="28">
+        <v>7.4029999999999996</v>
+      </c>
+      <c r="AB18" s="18">
+        <v>300</v>
+      </c>
+      <c r="AC18" s="33">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="AD18" s="33">
+        <v>7.31</v>
+      </c>
+      <c r="AE18" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF18" s="33">
+        <v>14.912000000000001</v>
+      </c>
+      <c r="AG18" s="33">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="33">
+        <v>1.1499999999999999</v>
+      </c>
       <c r="AI18" s="33"/>
-      <c r="AJ18" s="33"/>
-      <c r="AK18" s="33"/>
-      <c r="AL18" s="33"/>
-      <c r="AM18" s="33"/>
+      <c r="AJ18" s="33">
+        <v>28.02</v>
+      </c>
+      <c r="AK18" s="33">
+        <v>24.67</v>
+      </c>
+      <c r="AL18" s="33">
+        <f t="shared" si="15"/>
+        <v>18.02</v>
+      </c>
+      <c r="AM18" s="33">
+        <f t="shared" si="16"/>
+        <v>24.67</v>
+      </c>
       <c r="AN18" s="46">
         <v>15</v>
       </c>
@@ -4492,20 +4837,20 @@
         <v>0</v>
       </c>
       <c r="AX18" s="33">
-        <f t="shared" si="15"/>
-        <v>0.29846668319999997</v>
+        <f t="shared" si="17"/>
+        <v>0.30037957920000002</v>
       </c>
       <c r="AY18" s="33">
-        <f t="shared" si="16"/>
-        <v>1670.11</v>
-      </c>
-      <c r="AZ18" s="34" t="e">
+        <f t="shared" si="18"/>
+        <v>1739.662</v>
+      </c>
+      <c r="AZ18" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>1.610657702473239E-2</v>
       </c>
       <c r="BA18" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.6482352941176469E-2</v>
       </c>
       <c r="BB18" s="34">
         <f t="shared" si="7"/>
@@ -4524,8 +4869,8 @@
         <v>0</v>
       </c>
       <c r="BF18" s="34">
-        <f t="shared" si="18"/>
-        <v>12.525824999999999</v>
+        <f t="shared" si="20"/>
+        <v>13.047464999999999</v>
       </c>
       <c r="BG18" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4541,7 +4886,7 @@
       </c>
       <c r="BJ18" s="51">
         <f t="shared" si="11"/>
-        <v>12.525824999999999</v>
+        <v>13.047464999999999</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.25">
@@ -4557,41 +4902,109 @@
       <c r="D19" s="30">
         <v>2</v>
       </c>
-      <c r="E19" s="31"/>
+      <c r="E19" s="31">
+        <v>45451.528067129599</v>
+      </c>
       <c r="F19" s="11"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="32"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="32"/>
-      <c r="U19" s="32"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="32"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="18"/>
-      <c r="AC19" s="33"/>
-      <c r="AD19" s="33"/>
-      <c r="AE19" s="33"/>
-      <c r="AF19" s="33"/>
-      <c r="AG19" s="33"/>
-      <c r="AH19" s="33"/>
+      <c r="G19" s="32">
+        <v>868.48</v>
+      </c>
+      <c r="H19" s="32">
+        <v>19.8</v>
+      </c>
+      <c r="I19" s="32">
+        <v>19.3</v>
+      </c>
+      <c r="J19" s="32">
+        <v>97.5</v>
+      </c>
+      <c r="K19" s="32">
+        <v>17.3</v>
+      </c>
+      <c r="L19" s="32">
+        <v>347</v>
+      </c>
+      <c r="M19" s="32">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N19" s="32">
+        <v>0.42</v>
+      </c>
+      <c r="O19" s="32">
+        <v>2.14</v>
+      </c>
+      <c r="P19" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="Q19" s="32">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R19" s="32">
+        <v>3.74</v>
+      </c>
+      <c r="S19" s="32">
+        <v>7.109</v>
+      </c>
+      <c r="T19" s="32">
+        <v>108.2</v>
+      </c>
+      <c r="U19" s="32">
+        <v>14.8</v>
+      </c>
+      <c r="V19" s="32">
+        <v>3.06</v>
+      </c>
+      <c r="W19" s="32">
+        <v>142.9</v>
+      </c>
+      <c r="X19" s="32">
+        <v>33.1</v>
+      </c>
+      <c r="Y19" s="32">
+        <v>94.9</v>
+      </c>
+      <c r="Z19" s="32">
+        <v>12</v>
+      </c>
+      <c r="AA19" s="28">
+        <v>7.1470000000000002</v>
+      </c>
+      <c r="AB19" s="18">
+        <v>298</v>
+      </c>
+      <c r="AC19" s="33">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="AD19" s="33">
+        <v>7.13</v>
+      </c>
+      <c r="AE19" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF19" s="33">
+        <v>24.227</v>
+      </c>
+      <c r="AG19" s="33">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="33">
+        <v>3.54</v>
+      </c>
       <c r="AI19" s="33"/>
-      <c r="AJ19" s="33"/>
-      <c r="AK19" s="33"/>
-      <c r="AL19" s="33"/>
-      <c r="AM19" s="33"/>
+      <c r="AJ19" s="33">
+        <v>28.89</v>
+      </c>
+      <c r="AK19" s="33">
+        <v>15.88</v>
+      </c>
+      <c r="AL19" s="33">
+        <f t="shared" si="15"/>
+        <v>21.89</v>
+      </c>
+      <c r="AM19" s="33">
+        <f t="shared" si="16"/>
+        <v>15.88</v>
+      </c>
       <c r="AN19" s="46">
         <v>15</v>
       </c>
@@ -4611,27 +5024,31 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AT19" s="18"/>
-      <c r="AU19" s="33"/>
-      <c r="AV19" s="43"/>
+      <c r="AU19">
+        <v>1.52722913680596E-2</v>
+      </c>
+      <c r="AV19" s="43">
+        <v>2.2770951490618898E-3</v>
+      </c>
       <c r="AW19" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.0112622930000001E-2</v>
       </c>
       <c r="AX19" s="33">
-        <f t="shared" si="15"/>
-        <v>0.18475989119999997</v>
+        <f t="shared" si="17"/>
+        <v>0.18561352319999996</v>
       </c>
       <c r="AY19" s="33">
-        <f t="shared" si="16"/>
-        <v>1673.23</v>
-      </c>
-      <c r="AZ19" s="34" t="e">
+        <f t="shared" si="18"/>
+        <v>1746.567</v>
+      </c>
+      <c r="AZ19" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>1.6541020184166998E-2</v>
       </c>
       <c r="BA19" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.6994117647058823E-2</v>
       </c>
       <c r="BB19" s="34">
         <f t="shared" si="7"/>
@@ -4643,31 +5060,28 @@
       </c>
       <c r="BD19" s="64">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.8523666748498438E-2</v>
       </c>
       <c r="BE19" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="BF19" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
+      <c r="BF19" s="34"/>
       <c r="BG19" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.9770992432115779</v>
       </c>
       <c r="BH19" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48.113420125969974</v>
       </c>
       <c r="BI19" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1.8523666748498438E-2</v>
       </c>
       <c r="BJ19" s="51">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3.9770992432115779</v>
       </c>
     </row>
     <row r="20" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4683,41 +5097,109 @@
       <c r="D20" s="7">
         <v>2</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="8">
+        <v>45451.5307060185</v>
+      </c>
       <c r="F20" s="13"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="19"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="20"/>
-      <c r="AE20" s="20"/>
-      <c r="AF20" s="20"/>
-      <c r="AG20" s="20"/>
-      <c r="AH20" s="20"/>
+      <c r="G20" s="14">
+        <v>952.58</v>
+      </c>
+      <c r="H20" s="14">
+        <v>20.9</v>
+      </c>
+      <c r="I20" s="14">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="J20" s="14">
+        <v>97.5</v>
+      </c>
+      <c r="K20" s="14">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="L20" s="14">
+        <v>319</v>
+      </c>
+      <c r="M20" s="14">
+        <v>1.33</v>
+      </c>
+      <c r="N20" s="14">
+        <v>0.41</v>
+      </c>
+      <c r="O20" s="14">
+        <v>0</v>
+      </c>
+      <c r="P20" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="Q20" s="14">
+        <v>0.12</v>
+      </c>
+      <c r="R20" s="14">
+        <v>1.9</v>
+      </c>
+      <c r="S20" s="14">
+        <v>7.3280000000000003</v>
+      </c>
+      <c r="T20" s="14">
+        <v>117.4</v>
+      </c>
+      <c r="U20" s="14">
+        <v>30.4</v>
+      </c>
+      <c r="V20" s="14">
+        <v>3.53</v>
+      </c>
+      <c r="W20" s="14">
+        <v>138</v>
+      </c>
+      <c r="X20" s="14">
+        <v>60.2</v>
+      </c>
+      <c r="Y20" s="14">
+        <v>103</v>
+      </c>
+      <c r="Z20" s="14">
+        <v>24.6</v>
+      </c>
+      <c r="AA20" s="29">
+        <v>7.3710000000000004</v>
+      </c>
+      <c r="AB20" s="19">
+        <v>300</v>
+      </c>
+      <c r="AC20" s="20">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="AD20" s="20">
+        <v>7.3</v>
+      </c>
+      <c r="AE20" s="20">
+        <v>34</v>
+      </c>
+      <c r="AF20" s="20">
+        <v>21.77</v>
+      </c>
+      <c r="AG20" s="20">
+        <v>3.22</v>
+      </c>
+      <c r="AH20" s="20">
+        <v>3.55</v>
+      </c>
       <c r="AI20" s="20"/>
-      <c r="AJ20" s="20"/>
-      <c r="AK20" s="20"/>
-      <c r="AL20" s="20"/>
-      <c r="AM20" s="20"/>
+      <c r="AJ20" s="20">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="AK20" s="20">
+        <v>20.98</v>
+      </c>
+      <c r="AL20" s="20">
+        <f t="shared" si="15"/>
+        <v>12.149999999999999</v>
+      </c>
+      <c r="AM20" s="20">
+        <f t="shared" si="16"/>
+        <v>20.98</v>
+      </c>
       <c r="AN20" s="47">
         <v>15</v>
       </c>
@@ -4737,27 +5219,31 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AT20" s="19"/>
-      <c r="AU20" s="20"/>
-      <c r="AV20" s="44"/>
+      <c r="AU20" s="20">
+        <v>2.1013375291705799E-2</v>
+      </c>
+      <c r="AV20" s="44">
+        <v>4.8817390308066597E-3</v>
+      </c>
       <c r="AW20" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.0675421999999999E-2</v>
       </c>
       <c r="AX20" s="20">
-        <f t="shared" si="15"/>
-        <v>0.19699096319999998</v>
+        <f t="shared" si="17"/>
+        <v>0.19801739520000003</v>
       </c>
       <c r="AY20" s="20">
-        <f t="shared" si="16"/>
-        <v>1673.88</v>
-      </c>
-      <c r="AZ20" s="21" t="e">
+        <f t="shared" si="18"/>
+        <v>1744.3500000000001</v>
+      </c>
+      <c r="AZ20" s="21">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>1.1551580818069767E-2</v>
       </c>
       <c r="BA20" s="21">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.1852941176470587E-2</v>
       </c>
       <c r="BB20" s="21">
         <f t="shared" si="7"/>
@@ -4769,31 +5255,31 @@
       </c>
       <c r="BD20" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.54546397153382E-2</v>
       </c>
       <c r="BE20" s="62" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="BF20" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG20" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.5154614783875981</v>
       </c>
       <c r="BH20" s="50">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>66.11594731256676</v>
       </c>
       <c r="BI20" s="70">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.54546397153382E-2</v>
       </c>
       <c r="BJ20" s="52">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8.5154614783875981</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.25">
@@ -4870,12 +5356,12 @@
         <v>0</v>
       </c>
       <c r="AX21" s="16">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>0.29562681600000001</v>
       </c>
       <c r="AY21" s="16">
-        <f t="shared" si="16"/>
-        <v>1656.74</v>
+        <f t="shared" si="18"/>
+        <v>1724.8</v>
       </c>
       <c r="AZ21" s="17" t="e">
         <f t="shared" si="5"/>
@@ -4902,8 +5388,8 @@
         <v>0</v>
       </c>
       <c r="BF21" s="17">
-        <f t="shared" si="18"/>
-        <v>12.425550000000001</v>
+        <f t="shared" si="20"/>
+        <v>12.936</v>
       </c>
       <c r="BG21" s="17" t="str">
         <f t="shared" si="2"/>
@@ -4919,7 +5405,7 @@
       </c>
       <c r="BJ21" s="51">
         <f t="shared" si="11"/>
-        <v>12.425550000000001</v>
+        <v>12.936</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.25">
@@ -4996,12 +5482,12 @@
         <v>0</v>
       </c>
       <c r="AX22" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>0.26819272655999993</v>
       </c>
       <c r="AY22" s="33">
-        <f t="shared" si="16"/>
-        <v>1659.64</v>
+        <f t="shared" si="18"/>
+        <v>1725.607</v>
       </c>
       <c r="AZ22" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5028,8 +5514,8 @@
         <v/>
       </c>
       <c r="BF22" s="34">
-        <f t="shared" si="18"/>
-        <v>12.4473</v>
+        <f t="shared" si="20"/>
+        <v>12.942052499999999</v>
       </c>
       <c r="BG22" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5045,7 +5531,7 @@
       </c>
       <c r="BJ22" s="51">
         <f t="shared" si="11"/>
-        <v>12.4473</v>
+        <v>12.942052499999999</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.25">
@@ -5122,12 +5608,12 @@
         <v>0</v>
       </c>
       <c r="AX23" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>0.28967859647999994</v>
       </c>
       <c r="AY23" s="33">
-        <f t="shared" si="16"/>
-        <v>1654.43</v>
+        <f t="shared" si="18"/>
+        <v>1719.1870000000001</v>
       </c>
       <c r="AZ23" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5154,8 +5640,8 @@
         <v/>
       </c>
       <c r="BF23" s="34">
-        <f t="shared" si="18"/>
-        <v>12.408225</v>
+        <f t="shared" si="20"/>
+        <v>12.893902500000001</v>
       </c>
       <c r="BG23" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5171,7 +5657,7 @@
       </c>
       <c r="BJ23" s="51">
         <f t="shared" si="11"/>
-        <v>12.408225</v>
+        <v>12.893902500000001</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.25">
@@ -5248,12 +5734,12 @@
         <v>0</v>
       </c>
       <c r="AX24" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY24" s="33">
-        <f t="shared" si="16"/>
-        <v>1655.11</v>
+        <f t="shared" si="18"/>
+        <v>1724.662</v>
       </c>
       <c r="AZ24" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5280,8 +5766,8 @@
         <v>0</v>
       </c>
       <c r="BF24" s="34">
-        <f t="shared" si="18"/>
-        <v>12.413325</v>
+        <f t="shared" si="20"/>
+        <v>12.934965</v>
       </c>
       <c r="BG24" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5297,7 +5783,7 @@
       </c>
       <c r="BJ24" s="51">
         <f t="shared" si="11"/>
-        <v>12.413325</v>
+        <v>12.934965</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.25">
@@ -5374,12 +5860,12 @@
         <v>0</v>
       </c>
       <c r="AX25" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>0.24270295032</v>
       </c>
       <c r="AY25" s="33">
-        <f t="shared" si="16"/>
-        <v>1658.23</v>
+        <f t="shared" si="18"/>
+        <v>1731.567</v>
       </c>
       <c r="AZ25" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5406,7 +5892,7 @@
         <v/>
       </c>
       <c r="BF25" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG25" s="34">
@@ -5500,12 +5986,12 @@
         <v>0</v>
       </c>
       <c r="AX26" s="20">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>0.25621012799999998</v>
       </c>
       <c r="AY26" s="20">
-        <f t="shared" si="16"/>
-        <v>1658.88</v>
+        <f t="shared" si="18"/>
+        <v>1729.3500000000001</v>
       </c>
       <c r="AZ26" s="21" t="e">
         <f t="shared" si="5"/>
@@ -5532,7 +6018,7 @@
         <v/>
       </c>
       <c r="BF26" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG26" s="21">
@@ -5626,12 +6112,12 @@
         <v>0</v>
       </c>
       <c r="AX27" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY27" s="16">
-        <f t="shared" si="16"/>
-        <v>1641.74</v>
+        <f t="shared" si="18"/>
+        <v>1709.8</v>
       </c>
       <c r="AZ27" s="17" t="e">
         <f t="shared" si="5"/>
@@ -5658,8 +6144,8 @@
         <v>0</v>
       </c>
       <c r="BF27" s="17">
-        <f t="shared" si="18"/>
-        <v>12.31305</v>
+        <f t="shared" si="20"/>
+        <v>12.823499999999999</v>
       </c>
       <c r="BG27" s="17" t="str">
         <f t="shared" si="2"/>
@@ -5675,7 +6161,7 @@
       </c>
       <c r="BJ27" s="53">
         <f t="shared" si="11"/>
-        <v>12.31305</v>
+        <v>12.823499999999999</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.25">
@@ -5752,12 +6238,12 @@
         <v>0</v>
       </c>
       <c r="AX28" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY28" s="33">
-        <f t="shared" si="16"/>
-        <v>1644.64</v>
+        <f t="shared" si="18"/>
+        <v>1710.607</v>
       </c>
       <c r="AZ28" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5784,8 +6270,8 @@
         <v/>
       </c>
       <c r="BF28" s="34">
-        <f t="shared" si="18"/>
-        <v>12.3348</v>
+        <f t="shared" si="20"/>
+        <v>12.8295525</v>
       </c>
       <c r="BG28" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5801,7 +6287,7 @@
       </c>
       <c r="BJ28" s="51">
         <f t="shared" si="11"/>
-        <v>12.3348</v>
+        <v>12.8295525</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.25">
@@ -5878,12 +6364,12 @@
         <v>0</v>
       </c>
       <c r="AX29" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY29" s="33">
-        <f t="shared" si="16"/>
-        <v>1639.43</v>
+        <f t="shared" si="18"/>
+        <v>1704.1870000000001</v>
       </c>
       <c r="AZ29" s="34" t="e">
         <f t="shared" si="5"/>
@@ -5910,8 +6396,8 @@
         <v/>
       </c>
       <c r="BF29" s="34">
-        <f t="shared" si="18"/>
-        <v>12.295724999999999</v>
+        <f t="shared" si="20"/>
+        <v>12.781402500000002</v>
       </c>
       <c r="BG29" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5927,7 +6413,7 @@
       </c>
       <c r="BJ29" s="51">
         <f t="shared" si="11"/>
-        <v>12.295724999999999</v>
+        <v>12.781402500000002</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.25">
@@ -6004,12 +6490,12 @@
         <v>0</v>
       </c>
       <c r="AX30" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY30" s="33">
-        <f t="shared" si="16"/>
-        <v>1640.11</v>
+        <f t="shared" si="18"/>
+        <v>1709.662</v>
       </c>
       <c r="AZ30" s="34" t="e">
         <f t="shared" si="5"/>
@@ -6036,8 +6522,8 @@
         <v>0</v>
       </c>
       <c r="BF30" s="34">
-        <f t="shared" si="18"/>
-        <v>12.300825</v>
+        <f t="shared" si="20"/>
+        <v>12.822464999999999</v>
       </c>
       <c r="BG30" s="34" t="str">
         <f t="shared" si="2"/>
@@ -6053,7 +6539,7 @@
       </c>
       <c r="BJ30" s="51">
         <f t="shared" si="11"/>
-        <v>12.300825</v>
+        <v>12.822464999999999</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.25">
@@ -6130,12 +6616,12 @@
         <v>0</v>
       </c>
       <c r="AX31" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY31" s="33">
-        <f t="shared" si="16"/>
-        <v>1643.23</v>
+        <f t="shared" si="18"/>
+        <v>1716.567</v>
       </c>
       <c r="AZ31" s="34" t="e">
         <f t="shared" si="5"/>
@@ -6162,7 +6648,7 @@
         <v/>
       </c>
       <c r="BF31" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG31" s="34">
@@ -6256,12 +6742,12 @@
         <v>0</v>
       </c>
       <c r="AX32" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY32" s="20">
-        <f t="shared" si="16"/>
-        <v>1643.88</v>
+        <f t="shared" si="18"/>
+        <v>1714.3500000000001</v>
       </c>
       <c r="AZ32" s="21" t="e">
         <f t="shared" si="5"/>
@@ -6288,7 +6774,7 @@
         <v/>
       </c>
       <c r="BF32" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG32" s="21">
@@ -6382,12 +6868,12 @@
         <v>0</v>
       </c>
       <c r="AX33" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY33" s="16">
-        <f t="shared" si="16"/>
-        <v>1626.74</v>
+        <f t="shared" si="18"/>
+        <v>1694.8</v>
       </c>
       <c r="AZ33" s="17" t="e">
         <f t="shared" si="5"/>
@@ -6414,8 +6900,8 @@
         <v>0</v>
       </c>
       <c r="BF33" s="17">
-        <f t="shared" si="18"/>
-        <v>12.20055</v>
+        <f t="shared" si="20"/>
+        <v>12.710999999999999</v>
       </c>
       <c r="BG33" s="17" t="str">
         <f t="shared" si="2"/>
@@ -6431,7 +6917,7 @@
       </c>
       <c r="BJ33" s="51">
         <f t="shared" si="11"/>
-        <v>12.20055</v>
+        <v>12.710999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.25">
@@ -6508,12 +6994,12 @@
         <v>0</v>
       </c>
       <c r="AX34" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY34" s="33">
-        <f t="shared" si="16"/>
-        <v>1629.64</v>
+        <f t="shared" si="18"/>
+        <v>1695.607</v>
       </c>
       <c r="AZ34" s="34" t="e">
         <f t="shared" si="5"/>
@@ -6540,8 +7026,8 @@
         <v/>
       </c>
       <c r="BF34" s="34">
-        <f t="shared" si="18"/>
-        <v>12.222300000000001</v>
+        <f t="shared" si="20"/>
+        <v>12.717052499999999</v>
       </c>
       <c r="BG34" s="34" t="str">
         <f t="shared" si="2"/>
@@ -6557,7 +7043,7 @@
       </c>
       <c r="BJ34" s="51">
         <f t="shared" si="11"/>
-        <v>12.222300000000001</v>
+        <v>12.717052499999999</v>
       </c>
     </row>
     <row r="35" spans="1:62" x14ac:dyDescent="0.25">
@@ -6634,23 +7120,23 @@
         <v>0</v>
       </c>
       <c r="AX35" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY35" s="33">
-        <f t="shared" si="16"/>
-        <v>1624.43</v>
+        <f t="shared" si="18"/>
+        <v>1689.1870000000001</v>
       </c>
       <c r="AZ35" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA35" s="34">
-        <f t="shared" ref="BA35:BA66" si="19">AJ35/AO35</f>
+        <f t="shared" ref="BA35:BA66" si="21">AJ35/AO35</f>
         <v>0</v>
       </c>
       <c r="BB35" s="34">
-        <f t="shared" ref="BB35:BB66" si="20">AI35*24</f>
+        <f t="shared" ref="BB35:BB66" si="22">AI35*24</f>
         <v>0</v>
       </c>
       <c r="BC35" s="34">
@@ -6658,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="BD35" s="64" t="str">
-        <f t="shared" ref="BD35:BD66" si="21">IF(B35="Julia",AU35*AY35/24/60,"")</f>
+        <f t="shared" ref="BD35:BD66" si="23">IF(B35="Julia",AU35*AY35/24/60,"")</f>
         <v/>
       </c>
       <c r="BE35" s="61" t="str">
@@ -6666,11 +7152,11 @@
         <v/>
       </c>
       <c r="BF35" s="34">
-        <f t="shared" si="18"/>
-        <v>12.183225</v>
+        <f t="shared" si="20"/>
+        <v>12.668902500000002</v>
       </c>
       <c r="BG35" s="34" t="str">
-        <f t="shared" ref="BG35:BG66" si="22">IF(B35="Julia",AV35*AY35,"")</f>
+        <f t="shared" ref="BG35:BG66" si="24">IF(B35="Julia",AV35*AY35,"")</f>
         <v/>
       </c>
       <c r="BH35" s="49">
@@ -6683,7 +7169,7 @@
       </c>
       <c r="BJ35" s="51">
         <f t="shared" si="11"/>
-        <v>12.183225</v>
+        <v>12.668902500000002</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.25">
@@ -6760,23 +7246,23 @@
         <v>0</v>
       </c>
       <c r="AX36" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY36" s="33">
-        <f t="shared" si="16"/>
-        <v>1625.11</v>
+        <f t="shared" si="18"/>
+        <v>1694.662</v>
       </c>
       <c r="AZ36" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA36" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB36" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC36" s="34" t="str">
@@ -6784,7 +7270,7 @@
         <v/>
       </c>
       <c r="BD36" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE36" s="61">
@@ -6792,11 +7278,11 @@
         <v>0</v>
       </c>
       <c r="BF36" s="34">
-        <f t="shared" si="18"/>
-        <v>12.188324999999999</v>
+        <f t="shared" si="20"/>
+        <v>12.709965</v>
       </c>
       <c r="BG36" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH36" s="49">
@@ -6809,7 +7295,7 @@
       </c>
       <c r="BJ36" s="51">
         <f t="shared" si="11"/>
-        <v>12.188324999999999</v>
+        <v>12.709965</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.25">
@@ -6886,23 +7372,23 @@
         <v>0</v>
       </c>
       <c r="AX37" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY37" s="33">
-        <f t="shared" si="16"/>
-        <v>1628.23</v>
+        <f t="shared" si="18"/>
+        <v>1701.567</v>
       </c>
       <c r="AZ37" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA37" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB37" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC37" s="34" t="str">
@@ -6910,7 +7396,7 @@
         <v/>
       </c>
       <c r="BD37" s="64">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE37" s="61" t="str">
@@ -6918,11 +7404,11 @@
         <v/>
       </c>
       <c r="BF37" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG37" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH37" s="49">
@@ -7012,23 +7498,23 @@
         <v>0</v>
       </c>
       <c r="AX38" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY38" s="20">
-        <f t="shared" si="16"/>
-        <v>1628.88</v>
+        <f t="shared" si="18"/>
+        <v>1699.3500000000001</v>
       </c>
       <c r="AZ38" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA38" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB38" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC38" s="21" t="str">
@@ -7036,7 +7522,7 @@
         <v/>
       </c>
       <c r="BD38" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE38" s="62" t="str">
@@ -7044,11 +7530,11 @@
         <v/>
       </c>
       <c r="BF38" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG38" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH38" s="49">
@@ -7138,23 +7624,23 @@
         <v>0</v>
       </c>
       <c r="AX39" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY39" s="16">
-        <f t="shared" si="16"/>
-        <v>1611.74</v>
+        <f t="shared" si="18"/>
+        <v>1679.8</v>
       </c>
       <c r="AZ39" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA39" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB39" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC39" s="17" t="str">
@@ -7162,7 +7648,7 @@
         <v/>
       </c>
       <c r="BD39" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE39" s="60">
@@ -7170,11 +7656,11 @@
         <v>0</v>
       </c>
       <c r="BF39" s="17">
-        <f t="shared" si="18"/>
-        <v>12.088050000000001</v>
+        <f t="shared" si="20"/>
+        <v>12.5985</v>
       </c>
       <c r="BG39" s="17" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH39" s="48">
@@ -7187,7 +7673,7 @@
       </c>
       <c r="BJ39" s="53">
         <f t="shared" si="11"/>
-        <v>12.088050000000001</v>
+        <v>12.5985</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.25">
@@ -7264,23 +7750,23 @@
         <v>0</v>
       </c>
       <c r="AX40" s="33">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AY40" s="33">
-        <f t="shared" si="16"/>
-        <v>1614.64</v>
+        <f t="shared" si="18"/>
+        <v>1680.607</v>
       </c>
       <c r="AZ40" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA40" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB40" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC40" s="34">
@@ -7288,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="BD40" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE40" s="61" t="str">
@@ -7296,11 +7782,11 @@
         <v/>
       </c>
       <c r="BF40" s="34">
-        <f t="shared" si="18"/>
-        <v>12.1098</v>
+        <f t="shared" si="20"/>
+        <v>12.6045525</v>
       </c>
       <c r="BG40" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH40" s="49">
@@ -7313,7 +7799,7 @@
       </c>
       <c r="BJ40" s="51">
         <f t="shared" si="11"/>
-        <v>12.1098</v>
+        <v>12.6045525</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.25">
@@ -7390,23 +7876,23 @@
         <v>0</v>
       </c>
       <c r="AX41" s="33">
-        <f t="shared" ref="AX41:AX72" si="23">AW35*24</f>
+        <f t="shared" ref="AX41:AX72" si="25">AW35*24</f>
         <v>0</v>
       </c>
       <c r="AY41" s="33">
-        <f t="shared" ref="AY41:AY72" si="24">AY35+SUM(AF41:AH41,AL41:AM41)-AN41</f>
-        <v>1609.43</v>
+        <f t="shared" ref="AY41:AY72" si="26">AY35+SUM(AF41:AH41,AL41:AM41)-AN41</f>
+        <v>1674.1870000000001</v>
       </c>
       <c r="AZ41" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA41" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB41" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC41" s="34">
@@ -7414,7 +7900,7 @@
         <v>0</v>
       </c>
       <c r="BD41" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE41" s="61" t="str">
@@ -7422,11 +7908,11 @@
         <v/>
       </c>
       <c r="BF41" s="34">
-        <f t="shared" si="18"/>
-        <v>12.070724999999999</v>
+        <f t="shared" si="20"/>
+        <v>12.556402500000001</v>
       </c>
       <c r="BG41" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH41" s="49">
@@ -7439,7 +7925,7 @@
       </c>
       <c r="BJ41" s="51">
         <f t="shared" si="11"/>
-        <v>12.070724999999999</v>
+        <v>12.556402500000001</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.25">
@@ -7516,23 +8002,23 @@
         <v>0</v>
       </c>
       <c r="AX42" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY42" s="33">
-        <f t="shared" si="24"/>
-        <v>1610.11</v>
+        <f t="shared" si="26"/>
+        <v>1679.662</v>
       </c>
       <c r="AZ42" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA42" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB42" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC42" s="34" t="str">
@@ -7540,7 +8026,7 @@
         <v/>
       </c>
       <c r="BD42" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE42" s="61">
@@ -7548,11 +8034,11 @@
         <v>0</v>
       </c>
       <c r="BF42" s="34">
-        <f t="shared" si="18"/>
-        <v>12.075825</v>
+        <f t="shared" si="20"/>
+        <v>12.597465</v>
       </c>
       <c r="BG42" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH42" s="49">
@@ -7565,7 +8051,7 @@
       </c>
       <c r="BJ42" s="51">
         <f t="shared" si="11"/>
-        <v>12.075825</v>
+        <v>12.597465</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.25">
@@ -7642,23 +8128,23 @@
         <v>0</v>
       </c>
       <c r="AX43" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY43" s="33">
-        <f t="shared" si="24"/>
-        <v>1613.23</v>
+        <f t="shared" si="26"/>
+        <v>1686.567</v>
       </c>
       <c r="AZ43" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA43" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB43" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC43" s="34" t="str">
@@ -7666,7 +8152,7 @@
         <v/>
       </c>
       <c r="BD43" s="64">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE43" s="61" t="str">
@@ -7674,11 +8160,11 @@
         <v/>
       </c>
       <c r="BF43" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG43" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH43" s="49">
@@ -7768,23 +8254,23 @@
         <v>0</v>
       </c>
       <c r="AX44" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY44" s="20">
-        <f t="shared" si="24"/>
-        <v>1613.88</v>
+        <f t="shared" si="26"/>
+        <v>1684.3500000000001</v>
       </c>
       <c r="AZ44" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA44" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB44" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC44" s="21" t="str">
@@ -7792,7 +8278,7 @@
         <v/>
       </c>
       <c r="BD44" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE44" s="62" t="str">
@@ -7800,11 +8286,11 @@
         <v/>
       </c>
       <c r="BF44" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG44" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH44" s="50">
@@ -7894,23 +8380,23 @@
         <v>0</v>
       </c>
       <c r="AX45" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY45" s="16">
-        <f t="shared" si="24"/>
-        <v>1596.74</v>
+        <f t="shared" si="26"/>
+        <v>1664.8</v>
       </c>
       <c r="AZ45" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA45" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB45" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC45" s="17" t="str">
@@ -7918,7 +8404,7 @@
         <v/>
       </c>
       <c r="BD45" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE45" s="60">
@@ -7926,11 +8412,11 @@
         <v>0</v>
       </c>
       <c r="BF45" s="17">
-        <f t="shared" si="18"/>
-        <v>11.97555</v>
+        <f t="shared" si="20"/>
+        <v>12.485999999999999</v>
       </c>
       <c r="BG45" s="17" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH45" s="49">
@@ -7943,7 +8429,7 @@
       </c>
       <c r="BJ45" s="51">
         <f t="shared" si="11"/>
-        <v>11.97555</v>
+        <v>12.485999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.25">
@@ -8020,23 +8506,23 @@
         <v>0</v>
       </c>
       <c r="AX46" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY46" s="33">
-        <f t="shared" si="24"/>
-        <v>1599.64</v>
+        <f t="shared" si="26"/>
+        <v>1665.607</v>
       </c>
       <c r="AZ46" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA46" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB46" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC46" s="34">
@@ -8044,7 +8530,7 @@
         <v>0</v>
       </c>
       <c r="BD46" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE46" s="61" t="str">
@@ -8052,11 +8538,11 @@
         <v/>
       </c>
       <c r="BF46" s="34">
-        <f t="shared" si="18"/>
-        <v>11.997300000000001</v>
+        <f t="shared" si="20"/>
+        <v>12.4920525</v>
       </c>
       <c r="BG46" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH46" s="49">
@@ -8069,7 +8555,7 @@
       </c>
       <c r="BJ46" s="51">
         <f t="shared" si="11"/>
-        <v>11.997300000000001</v>
+        <v>12.4920525</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.25">
@@ -8146,23 +8632,23 @@
         <v>0</v>
       </c>
       <c r="AX47" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY47" s="33">
-        <f t="shared" si="24"/>
-        <v>1594.43</v>
+        <f t="shared" si="26"/>
+        <v>1659.1870000000001</v>
       </c>
       <c r="AZ47" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA47" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB47" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC47" s="34">
@@ -8170,7 +8656,7 @@
         <v>0</v>
       </c>
       <c r="BD47" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE47" s="61" t="str">
@@ -8178,11 +8664,11 @@
         <v/>
       </c>
       <c r="BF47" s="34">
-        <f t="shared" si="18"/>
-        <v>11.958225000000001</v>
+        <f t="shared" si="20"/>
+        <v>12.443902500000002</v>
       </c>
       <c r="BG47" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH47" s="49">
@@ -8195,7 +8681,7 @@
       </c>
       <c r="BJ47" s="51">
         <f t="shared" si="11"/>
-        <v>11.958225000000001</v>
+        <v>12.443902500000002</v>
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.25">
@@ -8272,23 +8758,23 @@
         <v>0</v>
       </c>
       <c r="AX48" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY48" s="33">
-        <f t="shared" si="24"/>
-        <v>1595.11</v>
+        <f t="shared" si="26"/>
+        <v>1664.662</v>
       </c>
       <c r="AZ48" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA48" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB48" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC48" s="34" t="str">
@@ -8296,7 +8782,7 @@
         <v/>
       </c>
       <c r="BD48" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE48" s="61">
@@ -8304,11 +8790,11 @@
         <v>0</v>
       </c>
       <c r="BF48" s="34">
-        <f t="shared" si="18"/>
-        <v>11.963324999999999</v>
+        <f t="shared" si="20"/>
+        <v>12.484964999999999</v>
       </c>
       <c r="BG48" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH48" s="49">
@@ -8321,7 +8807,7 @@
       </c>
       <c r="BJ48" s="51">
         <f t="shared" si="11"/>
-        <v>11.963324999999999</v>
+        <v>12.484964999999999</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.25">
@@ -8398,23 +8884,23 @@
         <v>0</v>
       </c>
       <c r="AX49" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY49" s="33">
-        <f t="shared" si="24"/>
-        <v>1598.23</v>
+        <f t="shared" si="26"/>
+        <v>1671.567</v>
       </c>
       <c r="AZ49" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA49" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB49" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC49" s="34" t="str">
@@ -8422,7 +8908,7 @@
         <v/>
       </c>
       <c r="BD49" s="64">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE49" s="61" t="str">
@@ -8430,11 +8916,11 @@
         <v/>
       </c>
       <c r="BF49" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG49" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH49" s="49">
@@ -8524,23 +9010,23 @@
         <v>0</v>
       </c>
       <c r="AX50" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY50" s="20">
-        <f t="shared" si="24"/>
-        <v>1598.88</v>
+        <f t="shared" si="26"/>
+        <v>1669.3500000000001</v>
       </c>
       <c r="AZ50" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA50" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB50" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC50" s="21" t="str">
@@ -8548,7 +9034,7 @@
         <v/>
       </c>
       <c r="BD50" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE50" s="62" t="str">
@@ -8556,11 +9042,11 @@
         <v/>
       </c>
       <c r="BF50" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG50" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH50" s="49">
@@ -8650,23 +9136,23 @@
         <v>0</v>
       </c>
       <c r="AX51" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY51" s="16">
-        <f t="shared" si="24"/>
-        <v>1581.74</v>
+        <f t="shared" si="26"/>
+        <v>1649.8</v>
       </c>
       <c r="AZ51" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA51" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB51" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC51" s="17" t="str">
@@ -8674,7 +9160,7 @@
         <v/>
       </c>
       <c r="BD51" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE51" s="60">
@@ -8682,11 +9168,11 @@
         <v>0</v>
       </c>
       <c r="BF51" s="17">
-        <f t="shared" si="18"/>
-        <v>11.863050000000001</v>
+        <f t="shared" si="20"/>
+        <v>12.3735</v>
       </c>
       <c r="BG51" s="17" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH51" s="48">
@@ -8699,7 +9185,7 @@
       </c>
       <c r="BJ51" s="53">
         <f t="shared" si="11"/>
-        <v>11.863050000000001</v>
+        <v>12.3735</v>
       </c>
     </row>
     <row r="52" spans="1:62" x14ac:dyDescent="0.25">
@@ -8776,23 +9262,23 @@
         <v>0</v>
       </c>
       <c r="AX52" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY52" s="33">
-        <f t="shared" si="24"/>
-        <v>1584.64</v>
+        <f t="shared" si="26"/>
+        <v>1650.607</v>
       </c>
       <c r="AZ52" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA52" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB52" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC52" s="34">
@@ -8800,7 +9286,7 @@
         <v>0</v>
       </c>
       <c r="BD52" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE52" s="61" t="str">
@@ -8808,11 +9294,11 @@
         <v/>
       </c>
       <c r="BF52" s="34">
-        <f t="shared" si="18"/>
-        <v>11.8848</v>
+        <f t="shared" si="20"/>
+        <v>12.379552499999999</v>
       </c>
       <c r="BG52" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH52" s="49">
@@ -8825,7 +9311,7 @@
       </c>
       <c r="BJ52" s="51">
         <f t="shared" si="11"/>
-        <v>11.8848</v>
+        <v>12.379552499999999</v>
       </c>
     </row>
     <row r="53" spans="1:62" x14ac:dyDescent="0.25">
@@ -8902,23 +9388,23 @@
         <v>0</v>
       </c>
       <c r="AX53" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY53" s="33">
-        <f t="shared" si="24"/>
-        <v>1579.43</v>
+        <f t="shared" si="26"/>
+        <v>1644.1870000000001</v>
       </c>
       <c r="AZ53" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA53" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB53" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC53" s="34">
@@ -8926,7 +9412,7 @@
         <v>0</v>
       </c>
       <c r="BD53" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE53" s="61" t="str">
@@ -8934,11 +9420,11 @@
         <v/>
       </c>
       <c r="BF53" s="34">
-        <f t="shared" si="18"/>
-        <v>11.845725</v>
+        <f t="shared" si="20"/>
+        <v>12.331402500000001</v>
       </c>
       <c r="BG53" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH53" s="49">
@@ -8951,7 +9437,7 @@
       </c>
       <c r="BJ53" s="51">
         <f t="shared" si="11"/>
-        <v>11.845725</v>
+        <v>12.331402500000001</v>
       </c>
     </row>
     <row r="54" spans="1:62" x14ac:dyDescent="0.25">
@@ -9028,23 +9514,23 @@
         <v>0</v>
       </c>
       <c r="AX54" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY54" s="33">
-        <f t="shared" si="24"/>
-        <v>1580.11</v>
+        <f t="shared" si="26"/>
+        <v>1649.662</v>
       </c>
       <c r="AZ54" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA54" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB54" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC54" s="34" t="str">
@@ -9052,7 +9538,7 @@
         <v/>
       </c>
       <c r="BD54" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE54" s="61">
@@ -9060,11 +9546,11 @@
         <v>0</v>
       </c>
       <c r="BF54" s="34">
-        <f t="shared" si="18"/>
-        <v>11.850825</v>
+        <f t="shared" si="20"/>
+        <v>12.372465</v>
       </c>
       <c r="BG54" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH54" s="49">
@@ -9077,7 +9563,7 @@
       </c>
       <c r="BJ54" s="51">
         <f t="shared" si="11"/>
-        <v>11.850825</v>
+        <v>12.372465</v>
       </c>
     </row>
     <row r="55" spans="1:62" x14ac:dyDescent="0.25">
@@ -9154,23 +9640,23 @@
         <v>0</v>
       </c>
       <c r="AX55" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY55" s="33">
-        <f t="shared" si="24"/>
-        <v>1583.23</v>
+        <f t="shared" si="26"/>
+        <v>1656.567</v>
       </c>
       <c r="AZ55" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA55" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB55" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC55" s="34" t="str">
@@ -9178,7 +9664,7 @@
         <v/>
       </c>
       <c r="BD55" s="64">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE55" s="61" t="str">
@@ -9186,11 +9672,11 @@
         <v/>
       </c>
       <c r="BF55" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG55" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH55" s="49">
@@ -9280,23 +9766,23 @@
         <v>0</v>
       </c>
       <c r="AX56" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY56" s="20">
-        <f t="shared" si="24"/>
-        <v>1583.88</v>
+        <f t="shared" si="26"/>
+        <v>1654.3500000000001</v>
       </c>
       <c r="AZ56" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA56" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB56" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC56" s="21" t="str">
@@ -9304,7 +9790,7 @@
         <v/>
       </c>
       <c r="BD56" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE56" s="62" t="str">
@@ -9312,11 +9798,11 @@
         <v/>
       </c>
       <c r="BF56" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG56" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH56" s="50">
@@ -9406,23 +9892,23 @@
         <v>0</v>
       </c>
       <c r="AX57" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY57" s="16">
-        <f t="shared" si="24"/>
-        <v>1566.74</v>
+        <f t="shared" si="26"/>
+        <v>1634.8</v>
       </c>
       <c r="AZ57" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA57" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB57" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC57" s="17" t="str">
@@ -9430,7 +9916,7 @@
         <v/>
       </c>
       <c r="BD57" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE57" s="60">
@@ -9438,11 +9924,11 @@
         <v>0</v>
       </c>
       <c r="BF57" s="17">
-        <f t="shared" si="18"/>
-        <v>11.75055</v>
+        <f t="shared" si="20"/>
+        <v>12.260999999999999</v>
       </c>
       <c r="BG57" s="17" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH57" s="49">
@@ -9455,7 +9941,7 @@
       </c>
       <c r="BJ57" s="51">
         <f t="shared" si="11"/>
-        <v>11.75055</v>
+        <v>12.260999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:62" x14ac:dyDescent="0.25">
@@ -9532,23 +10018,23 @@
         <v>0</v>
       </c>
       <c r="AX58" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY58" s="33">
-        <f t="shared" si="24"/>
-        <v>1569.64</v>
+        <f t="shared" si="26"/>
+        <v>1635.607</v>
       </c>
       <c r="AZ58" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA58" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB58" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC58" s="34">
@@ -9556,7 +10042,7 @@
         <v>0</v>
       </c>
       <c r="BD58" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE58" s="61" t="str">
@@ -9564,11 +10050,11 @@
         <v/>
       </c>
       <c r="BF58" s="34">
-        <f t="shared" si="18"/>
-        <v>11.7723</v>
+        <f t="shared" si="20"/>
+        <v>12.2670525</v>
       </c>
       <c r="BG58" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH58" s="49">
@@ -9581,7 +10067,7 @@
       </c>
       <c r="BJ58" s="51">
         <f t="shared" si="11"/>
-        <v>11.7723</v>
+        <v>12.2670525</v>
       </c>
     </row>
     <row r="59" spans="1:62" x14ac:dyDescent="0.25">
@@ -9658,23 +10144,23 @@
         <v>0</v>
       </c>
       <c r="AX59" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY59" s="33">
-        <f t="shared" si="24"/>
-        <v>1564.43</v>
+        <f t="shared" si="26"/>
+        <v>1629.1870000000001</v>
       </c>
       <c r="AZ59" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA59" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB59" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC59" s="34">
@@ -9682,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="BD59" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE59" s="61" t="str">
@@ -9690,11 +10176,11 @@
         <v/>
       </c>
       <c r="BF59" s="34">
-        <f t="shared" si="18"/>
-        <v>11.733224999999999</v>
+        <f t="shared" si="20"/>
+        <v>12.218902500000002</v>
       </c>
       <c r="BG59" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH59" s="49">
@@ -9707,7 +10193,7 @@
       </c>
       <c r="BJ59" s="51">
         <f t="shared" si="11"/>
-        <v>11.733224999999999</v>
+        <v>12.218902500000002</v>
       </c>
     </row>
     <row r="60" spans="1:62" x14ac:dyDescent="0.25">
@@ -9784,23 +10270,23 @@
         <v>0</v>
       </c>
       <c r="AX60" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY60" s="33">
-        <f t="shared" si="24"/>
-        <v>1565.11</v>
+        <f t="shared" si="26"/>
+        <v>1634.662</v>
       </c>
       <c r="AZ60" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA60" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB60" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC60" s="34" t="str">
@@ -9808,7 +10294,7 @@
         <v/>
       </c>
       <c r="BD60" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE60" s="61">
@@ -9816,11 +10302,11 @@
         <v>0</v>
       </c>
       <c r="BF60" s="34">
-        <f t="shared" si="18"/>
-        <v>11.738325</v>
+        <f t="shared" si="20"/>
+        <v>12.259964999999999</v>
       </c>
       <c r="BG60" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH60" s="49">
@@ -9833,7 +10319,7 @@
       </c>
       <c r="BJ60" s="51">
         <f t="shared" si="11"/>
-        <v>11.738325</v>
+        <v>12.259964999999999</v>
       </c>
     </row>
     <row r="61" spans="1:62" x14ac:dyDescent="0.25">
@@ -9910,23 +10396,23 @@
         <v>0</v>
       </c>
       <c r="AX61" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY61" s="33">
-        <f t="shared" si="24"/>
-        <v>1568.23</v>
+        <f t="shared" si="26"/>
+        <v>1641.567</v>
       </c>
       <c r="AZ61" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA61" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB61" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC61" s="34" t="str">
@@ -9934,7 +10420,7 @@
         <v/>
       </c>
       <c r="BD61" s="64">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE61" s="61" t="str">
@@ -9942,11 +10428,11 @@
         <v/>
       </c>
       <c r="BF61" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG61" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH61" s="49">
@@ -10036,23 +10522,23 @@
         <v>0</v>
       </c>
       <c r="AX62" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY62" s="20">
-        <f t="shared" si="24"/>
-        <v>1568.88</v>
+        <f t="shared" si="26"/>
+        <v>1639.3500000000001</v>
       </c>
       <c r="AZ62" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA62" s="21">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB62" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC62" s="21" t="str">
@@ -10060,7 +10546,7 @@
         <v/>
       </c>
       <c r="BD62" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BE62" s="62" t="str">
@@ -10068,11 +10554,11 @@
         <v/>
       </c>
       <c r="BF62" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG62" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BH62" s="49">
@@ -10162,23 +10648,23 @@
         <v>0</v>
       </c>
       <c r="AX63" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY63" s="16">
-        <f t="shared" si="24"/>
-        <v>1551.74</v>
+        <f t="shared" si="26"/>
+        <v>1619.8</v>
       </c>
       <c r="AZ63" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA63" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB63" s="17">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC63" s="17" t="str">
@@ -10186,7 +10672,7 @@
         <v/>
       </c>
       <c r="BD63" s="17" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE63" s="60">
@@ -10194,11 +10680,11 @@
         <v>0</v>
       </c>
       <c r="BF63" s="17">
-        <f t="shared" si="18"/>
-        <v>11.63805</v>
+        <f t="shared" si="20"/>
+        <v>12.148499999999999</v>
       </c>
       <c r="BG63" s="17" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH63" s="48">
@@ -10211,7 +10697,7 @@
       </c>
       <c r="BJ63" s="53">
         <f t="shared" si="11"/>
-        <v>11.63805</v>
+        <v>12.148499999999999</v>
       </c>
     </row>
     <row r="64" spans="1:62" x14ac:dyDescent="0.25">
@@ -10288,23 +10774,23 @@
         <v>0</v>
       </c>
       <c r="AX64" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY64" s="33">
-        <f t="shared" si="24"/>
-        <v>1554.64</v>
+        <f t="shared" si="26"/>
+        <v>1620.607</v>
       </c>
       <c r="AZ64" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA64" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB64" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC64" s="34">
@@ -10312,7 +10798,7 @@
         <v>0</v>
       </c>
       <c r="BD64" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE64" s="61" t="str">
@@ -10320,11 +10806,11 @@
         <v/>
       </c>
       <c r="BF64" s="34">
-        <f t="shared" si="18"/>
-        <v>11.659800000000001</v>
+        <f t="shared" si="20"/>
+        <v>12.154552499999999</v>
       </c>
       <c r="BG64" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH64" s="49">
@@ -10337,7 +10823,7 @@
       </c>
       <c r="BJ64" s="51">
         <f t="shared" si="11"/>
-        <v>11.659800000000001</v>
+        <v>12.154552499999999</v>
       </c>
     </row>
     <row r="65" spans="1:62" x14ac:dyDescent="0.25">
@@ -10414,23 +10900,23 @@
         <v>0</v>
       </c>
       <c r="AX65" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY65" s="33">
-        <f t="shared" si="24"/>
-        <v>1549.43</v>
+        <f t="shared" si="26"/>
+        <v>1614.1870000000001</v>
       </c>
       <c r="AZ65" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA65" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB65" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC65" s="34">
@@ -10438,7 +10924,7 @@
         <v>0</v>
       </c>
       <c r="BD65" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE65" s="61" t="str">
@@ -10446,11 +10932,11 @@
         <v/>
       </c>
       <c r="BF65" s="34">
-        <f t="shared" si="18"/>
-        <v>11.620725</v>
+        <f t="shared" si="20"/>
+        <v>12.106402500000002</v>
       </c>
       <c r="BG65" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH65" s="49">
@@ -10463,7 +10949,7 @@
       </c>
       <c r="BJ65" s="51">
         <f t="shared" si="11"/>
-        <v>11.620725</v>
+        <v>12.106402500000002</v>
       </c>
     </row>
     <row r="66" spans="1:62" x14ac:dyDescent="0.25">
@@ -10540,23 +11026,23 @@
         <v>0</v>
       </c>
       <c r="AX66" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY66" s="33">
-        <f t="shared" si="24"/>
-        <v>1550.11</v>
+        <f t="shared" si="26"/>
+        <v>1619.662</v>
       </c>
       <c r="AZ66" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA66" s="34">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="BB66" s="34">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BC66" s="34" t="str">
@@ -10564,7 +11050,7 @@
         <v/>
       </c>
       <c r="BD66" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="BE66" s="61">
@@ -10572,11 +11058,11 @@
         <v>0</v>
       </c>
       <c r="BF66" s="34">
-        <f t="shared" si="18"/>
-        <v>11.625824999999999</v>
+        <f t="shared" si="20"/>
+        <v>12.147465</v>
       </c>
       <c r="BG66" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH66" s="49">
@@ -10589,7 +11075,7 @@
       </c>
       <c r="BJ66" s="51">
         <f t="shared" si="11"/>
-        <v>11.625824999999999</v>
+        <v>12.147465</v>
       </c>
     </row>
     <row r="67" spans="1:62" x14ac:dyDescent="0.25">
@@ -10666,23 +11152,23 @@
         <v>0</v>
       </c>
       <c r="AX67" s="33">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY67" s="33">
-        <f t="shared" si="24"/>
-        <v>1553.23</v>
+        <f t="shared" si="26"/>
+        <v>1626.567</v>
       </c>
       <c r="AZ67" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA67" s="34">
-        <f t="shared" ref="BA67:BA80" si="25">AJ67/AO67</f>
+        <f t="shared" ref="BA67:BA80" si="27">AJ67/AO67</f>
         <v>0</v>
       </c>
       <c r="BB67" s="34">
-        <f t="shared" ref="BB67:BB80" si="26">AI67*24</f>
+        <f t="shared" ref="BB67:BB80" si="28">AI67*24</f>
         <v>0</v>
       </c>
       <c r="BC67" s="34" t="str">
@@ -10690,7 +11176,7 @@
         <v/>
       </c>
       <c r="BD67" s="64">
-        <f t="shared" ref="BD67:BD80" si="27">IF(B67="Julia",AU67*AY67/24/60,"")</f>
+        <f t="shared" ref="BD67:BD80" si="29">IF(B67="Julia",AU67*AY67/24/60,"")</f>
         <v>0</v>
       </c>
       <c r="BE67" s="61" t="str">
@@ -10698,11 +11184,11 @@
         <v/>
       </c>
       <c r="BF67" s="34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG67" s="34">
-        <f t="shared" ref="BG67:BG80" si="28">IF(B67="Julia",AV67*AY67,"")</f>
+        <f t="shared" ref="BG67:BG80" si="30">IF(B67="Julia",AV67*AY67,"")</f>
         <v>0</v>
       </c>
       <c r="BH67" s="49">
@@ -10788,27 +11274,27 @@
       <c r="AU68" s="20"/>
       <c r="AV68" s="44"/>
       <c r="AW68" s="19">
-        <f t="shared" ref="AW68:AW80" si="29">AS68*I68*AY68/1000</f>
+        <f t="shared" ref="AW68:AW80" si="31">AS68*I68*AY68/1000</f>
         <v>0</v>
       </c>
       <c r="AX68" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY68" s="20">
-        <f t="shared" si="24"/>
-        <v>1553.88</v>
+        <f t="shared" si="26"/>
+        <v>1624.3500000000001</v>
       </c>
       <c r="AZ68" s="21" t="e">
-        <f t="shared" ref="AZ68:AZ80" si="30">IF(ISBLANK(AJ68),NA(),IFERROR(AJ68/AY68,0))</f>
+        <f t="shared" ref="AZ68:AZ80" si="32">IF(ISBLANK(AJ68),NA(),IFERROR(AJ68/AY68,0))</f>
         <v>#N/A</v>
       </c>
       <c r="BA68" s="21">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BB68" s="21">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BC68" s="21" t="str">
@@ -10816,31 +11302,31 @@
         <v/>
       </c>
       <c r="BD68" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE68" s="62" t="str">
-        <f t="shared" ref="BE68:BE80" si="31">IF(B68="No MPC", AS68*I68*AY68/1000,"")</f>
+        <f t="shared" ref="BE68:BE80" si="33">IF(B68="No MPC", AS68*I68*AY68/1000,"")</f>
         <v/>
       </c>
       <c r="BF68" s="21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="BG68" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BH68" s="50">
-        <f t="shared" ref="BH68:BH80" si="32">IF(BC68&lt;&gt;"",BC68/0.000385,IF(BD68&lt;&gt;"",BD68/0.000385,BE68/0.000385))</f>
+        <f t="shared" ref="BH68:BH80" si="34">IF(BC68&lt;&gt;"",BC68/0.000385,IF(BD68&lt;&gt;"",BD68/0.000385,BE68/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BI68" s="70">
-        <f t="shared" ref="BI68:BI74" si="33">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
+        <f t="shared" ref="BI68:BI74" si="35">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
         <v>0</v>
       </c>
       <c r="BJ68" s="52">
-        <f t="shared" ref="BJ68:BJ80" si="34">IF(BF68&lt;&gt;"",BF68,BG68)</f>
+        <f t="shared" ref="BJ68:BJ80" si="36">IF(BF68&lt;&gt;"",BF68,BG68)</f>
         <v>0</v>
       </c>
     </row>
@@ -10914,60 +11400,60 @@
       <c r="AU69" s="16"/>
       <c r="AV69" s="42"/>
       <c r="AW69" s="15">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX69" s="16">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AY69" s="16">
+        <f t="shared" si="26"/>
+        <v>1604.8</v>
+      </c>
+      <c r="AZ69" s="17" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA69" s="17">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB69" s="17">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC69" s="17" t="str">
+        <f t="shared" ref="BC69:BC80" si="37">IF(B69="Python",AT69*AY69/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD69" s="17" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX69" s="16">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AY69" s="16">
-        <f t="shared" si="24"/>
-        <v>1536.74</v>
-      </c>
-      <c r="AZ69" s="17" t="e">
+        <v/>
+      </c>
+      <c r="BE69" s="60">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BF69" s="17">
+        <f t="shared" si="20"/>
+        <v>12.036</v>
+      </c>
+      <c r="BG69" s="17" t="str">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA69" s="17">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB69" s="17">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC69" s="17" t="str">
-        <f t="shared" ref="BC69:BC80" si="35">IF(B69="Python",AT69*AY69/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD69" s="17" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BE69" s="60">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BF69" s="17">
-        <f t="shared" si="18"/>
-        <v>11.525550000000001</v>
-      </c>
-      <c r="BG69" s="17" t="str">
-        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BH69" s="49">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BI69" s="69">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BJ69" s="51">
-        <f t="shared" si="34"/>
-        <v>11.525550000000001</v>
+        <f t="shared" si="36"/>
+        <v>12.036</v>
       </c>
     </row>
     <row r="70" spans="1:62" x14ac:dyDescent="0.25">
@@ -11040,60 +11526,60 @@
       <c r="AU70" s="33"/>
       <c r="AV70" s="43"/>
       <c r="AW70" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX70" s="33">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AY70" s="33">
+        <f t="shared" si="26"/>
+        <v>1605.607</v>
+      </c>
+      <c r="AZ70" s="34" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA70" s="34">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB70" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC70" s="34">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BD70" s="64" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX70" s="33">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AY70" s="33">
-        <f t="shared" si="24"/>
-        <v>1539.64</v>
-      </c>
-      <c r="AZ70" s="34" t="e">
+        <v/>
+      </c>
+      <c r="BE70" s="61" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="BF70" s="34">
+        <f t="shared" si="20"/>
+        <v>12.0420525</v>
+      </c>
+      <c r="BG70" s="34" t="str">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA70" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB70" s="34">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC70" s="34">
+        <v/>
+      </c>
+      <c r="BH70" s="49">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BI70" s="69">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="BD70" s="64" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BE70" s="61" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BF70" s="34">
-        <f t="shared" si="18"/>
-        <v>11.5473</v>
-      </c>
-      <c r="BG70" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH70" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI70" s="69">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
       <c r="BJ70" s="51">
-        <f t="shared" si="34"/>
-        <v>11.5473</v>
+        <f t="shared" si="36"/>
+        <v>12.0420525</v>
       </c>
     </row>
     <row r="71" spans="1:62" x14ac:dyDescent="0.25">
@@ -11166,60 +11652,60 @@
       <c r="AU71" s="33"/>
       <c r="AV71" s="43"/>
       <c r="AW71" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX71" s="33">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AY71" s="33">
+        <f t="shared" si="26"/>
+        <v>1599.1870000000001</v>
+      </c>
+      <c r="AZ71" s="34" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA71" s="34">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB71" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC71" s="34">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BD71" s="64" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX71" s="33">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AY71" s="33">
-        <f t="shared" si="24"/>
-        <v>1534.43</v>
-      </c>
-      <c r="AZ71" s="34" t="e">
+        <v/>
+      </c>
+      <c r="BE71" s="61" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="BF71" s="34">
+        <f t="shared" si="20"/>
+        <v>11.993902500000001</v>
+      </c>
+      <c r="BG71" s="34" t="str">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA71" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB71" s="34">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC71" s="34">
+        <v/>
+      </c>
+      <c r="BH71" s="49">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BI71" s="69">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="BD71" s="64" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BE71" s="61" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BF71" s="34">
-        <f t="shared" si="18"/>
-        <v>11.508224999999999</v>
-      </c>
-      <c r="BG71" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH71" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI71" s="69">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
       <c r="BJ71" s="51">
-        <f t="shared" si="34"/>
-        <v>11.508224999999999</v>
+        <f t="shared" si="36"/>
+        <v>11.993902500000001</v>
       </c>
     </row>
     <row r="72" spans="1:62" x14ac:dyDescent="0.25">
@@ -11292,60 +11778,60 @@
       <c r="AU72" s="33"/>
       <c r="AV72" s="43"/>
       <c r="AW72" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX72" s="33">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AY72" s="33">
+        <f t="shared" si="26"/>
+        <v>1604.662</v>
+      </c>
+      <c r="AZ72" s="34" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA72" s="34">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB72" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC72" s="34" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="BD72" s="64" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX72" s="33">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AY72" s="33">
-        <f t="shared" si="24"/>
-        <v>1535.11</v>
-      </c>
-      <c r="AZ72" s="34" t="e">
+        <v/>
+      </c>
+      <c r="BE72" s="61">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BF72" s="34">
+        <f t="shared" si="20"/>
+        <v>12.034965</v>
+      </c>
+      <c r="BG72" s="34" t="str">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA72" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB72" s="34">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC72" s="34" t="str">
+        <v/>
+      </c>
+      <c r="BH72" s="49">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BI72" s="69">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="BD72" s="64" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BE72" s="61">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BF72" s="34">
-        <f t="shared" si="18"/>
-        <v>11.513325</v>
-      </c>
-      <c r="BG72" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BH72" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI72" s="69">
-        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BJ72" s="51">
-        <f t="shared" si="34"/>
-        <v>11.513325</v>
+        <f t="shared" si="36"/>
+        <v>12.034965</v>
       </c>
     </row>
     <row r="73" spans="1:62" x14ac:dyDescent="0.25">
@@ -11418,59 +11904,59 @@
       <c r="AU73" s="33"/>
       <c r="AV73" s="43"/>
       <c r="AW73" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX73" s="33">
+        <f t="shared" ref="AX73:AX80" si="38">AW67*24</f>
+        <v>0</v>
+      </c>
+      <c r="AY73" s="33">
+        <f t="shared" ref="AY73:AY80" si="39">AY67+SUM(AF73:AH73,AL73:AM73)-AN73</f>
+        <v>1611.567</v>
+      </c>
+      <c r="AZ73" s="34" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA73" s="34">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB73" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC73" s="34" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="BD73" s="64">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AX73" s="33">
-        <f t="shared" ref="AX73:AX80" si="36">AW67*24</f>
-        <v>0</v>
-      </c>
-      <c r="AY73" s="33">
-        <f t="shared" ref="AY73:AY80" si="37">AY67+SUM(AF73:AH73,AL73:AM73)-AN73</f>
-        <v>1538.23</v>
-      </c>
-      <c r="AZ73" s="34" t="e">
+      <c r="BE73" s="61" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="BF73" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="BG73" s="34">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA73" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB73" s="34">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC73" s="34" t="str">
+        <v>0</v>
+      </c>
+      <c r="BH73" s="49">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BI73" s="69">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="BD73" s="64">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BE73" s="61" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BF73" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="BG73" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BH73" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI73" s="69">
-        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BJ73" s="51">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
@@ -11544,59 +12030,59 @@
       <c r="AU74" s="20"/>
       <c r="AV74" s="44"/>
       <c r="AW74" s="19">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX74" s="20">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AY74" s="20">
+        <f t="shared" si="39"/>
+        <v>1609.3500000000001</v>
+      </c>
+      <c r="AZ74" s="21" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA74" s="21">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB74" s="21">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC74" s="21" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="BD74" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AX74" s="20">
+      <c r="BE74" s="62" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="BF74" s="21" t="str">
+        <f t="shared" ref="BF74:BF80" si="40">IF(O74&lt;1.5, IF(B74&lt;&gt;"Julia",((3-O74)*AY74)/400, ""),0)</f>
+        <v/>
+      </c>
+      <c r="BG74" s="21">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BH74" s="49">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BI74" s="69">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BJ74" s="51">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AY74" s="20">
-        <f t="shared" si="37"/>
-        <v>1538.88</v>
-      </c>
-      <c r="AZ74" s="21" t="e">
-        <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA74" s="21">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB74" s="21">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC74" s="21" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="BD74" s="21">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BE74" s="62" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BF74" s="21" t="str">
-        <f t="shared" ref="BF74:BF80" si="38">IF(O74&lt;1.5, IF(B74&lt;&gt;"Julia",((3-O74)*AY74)/400, ""),0)</f>
-        <v/>
-      </c>
-      <c r="BG74" s="21">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BH74" s="49">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="BI74" s="69">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BJ74" s="51">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
@@ -11670,57 +12156,57 @@
       <c r="AU75" s="4"/>
       <c r="AV75" s="25"/>
       <c r="AW75" s="15">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX75" s="16">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AY75" s="16">
+        <f t="shared" si="39"/>
+        <v>1589.8</v>
+      </c>
+      <c r="AZ75" s="17" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA75" s="17">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB75" s="17">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC75" s="17" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="BD75" s="17" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX75" s="16">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AY75" s="16">
-        <f t="shared" si="37"/>
-        <v>1521.74</v>
-      </c>
-      <c r="AZ75" s="17" t="e">
+        <v/>
+      </c>
+      <c r="BE75" s="60">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BF75" s="17">
+        <f t="shared" si="40"/>
+        <v>11.923499999999999</v>
+      </c>
+      <c r="BG75" s="17" t="str">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA75" s="17">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB75" s="17">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC75" s="17" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="BD75" s="17" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BE75" s="60">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BF75" s="17">
-        <f t="shared" si="38"/>
-        <v>11.41305</v>
-      </c>
-      <c r="BG75" s="17" t="str">
-        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BH75" s="48">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BI75" s="65"/>
       <c r="BJ75" s="53">
-        <f t="shared" si="34"/>
-        <v>11.41305</v>
+        <f t="shared" si="36"/>
+        <v>11.923499999999999</v>
       </c>
     </row>
     <row r="76" spans="1:62" x14ac:dyDescent="0.25">
@@ -11793,57 +12279,57 @@
       <c r="AU76" s="30"/>
       <c r="AV76" s="2"/>
       <c r="AW76" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX76" s="33">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AY76" s="33">
+        <f t="shared" si="39"/>
+        <v>1590.607</v>
+      </c>
+      <c r="AZ76" s="34" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA76" s="34">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB76" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC76" s="34">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BD76" s="64" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX76" s="33">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AY76" s="33">
-        <f t="shared" si="37"/>
-        <v>1524.64</v>
-      </c>
-      <c r="AZ76" s="34" t="e">
+        <v/>
+      </c>
+      <c r="BE76" s="61" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="BF76" s="34">
+        <f t="shared" si="40"/>
+        <v>11.9295525</v>
+      </c>
+      <c r="BG76" s="34" t="str">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA76" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB76" s="34">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC76" s="34">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BD76" s="64" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BE76" s="61" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BF76" s="34">
-        <f t="shared" si="38"/>
-        <v>11.434800000000001</v>
-      </c>
-      <c r="BG76" s="34" t="str">
-        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BH76" s="49">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BI76" s="66"/>
       <c r="BJ76" s="51">
-        <f t="shared" si="34"/>
-        <v>11.434800000000001</v>
+        <f t="shared" si="36"/>
+        <v>11.9295525</v>
       </c>
     </row>
     <row r="77" spans="1:62" x14ac:dyDescent="0.25">
@@ -11916,57 +12402,57 @@
       <c r="AU77" s="33"/>
       <c r="AV77" s="43"/>
       <c r="AW77" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX77" s="33">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AY77" s="33">
+        <f t="shared" si="39"/>
+        <v>1584.1870000000001</v>
+      </c>
+      <c r="AZ77" s="34" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA77" s="34">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB77" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC77" s="34">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BD77" s="64" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX77" s="33">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AY77" s="33">
-        <f t="shared" si="37"/>
-        <v>1519.43</v>
-      </c>
-      <c r="AZ77" s="34" t="e">
+        <v/>
+      </c>
+      <c r="BE77" s="61" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="BF77" s="34">
+        <f t="shared" si="40"/>
+        <v>11.881402500000002</v>
+      </c>
+      <c r="BG77" s="34" t="str">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA77" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB77" s="34">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC77" s="34">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BD77" s="64" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BE77" s="61" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BF77" s="34">
-        <f t="shared" si="38"/>
-        <v>11.395725000000001</v>
-      </c>
-      <c r="BG77" s="34" t="str">
-        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BH77" s="49">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BI77" s="66"/>
       <c r="BJ77" s="51">
-        <f t="shared" si="34"/>
-        <v>11.395725000000001</v>
+        <f t="shared" si="36"/>
+        <v>11.881402500000002</v>
       </c>
     </row>
     <row r="78" spans="1:62" x14ac:dyDescent="0.25">
@@ -12039,57 +12525,57 @@
       <c r="AU78" s="33"/>
       <c r="AV78" s="43"/>
       <c r="AW78" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX78" s="33">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AY78" s="33">
+        <f t="shared" si="39"/>
+        <v>1589.662</v>
+      </c>
+      <c r="AZ78" s="34" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA78" s="34">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB78" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC78" s="34" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="BD78" s="64" t="str">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="AX78" s="33">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AY78" s="33">
-        <f t="shared" si="37"/>
-        <v>1520.11</v>
-      </c>
-      <c r="AZ78" s="34" t="e">
+        <v/>
+      </c>
+      <c r="BE78" s="61">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BF78" s="34">
+        <f t="shared" si="40"/>
+        <v>11.922464999999999</v>
+      </c>
+      <c r="BG78" s="34" t="str">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA78" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB78" s="34">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC78" s="34" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="BD78" s="64" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="BE78" s="61">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BF78" s="34">
-        <f t="shared" si="38"/>
-        <v>11.400824999999999</v>
-      </c>
-      <c r="BG78" s="34" t="str">
-        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BH78" s="49">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BI78" s="66"/>
       <c r="BJ78" s="51">
-        <f t="shared" si="34"/>
-        <v>11.400824999999999</v>
+        <f t="shared" si="36"/>
+        <v>11.922464999999999</v>
       </c>
     </row>
     <row r="79" spans="1:62" x14ac:dyDescent="0.25">
@@ -12162,56 +12648,56 @@
       <c r="AU79" s="33"/>
       <c r="AV79" s="43"/>
       <c r="AW79" s="18">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX79" s="33">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AY79" s="33">
+        <f t="shared" si="39"/>
+        <v>1596.567</v>
+      </c>
+      <c r="AZ79" s="34" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA79" s="34">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB79" s="34">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC79" s="34" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="BD79" s="64">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AX79" s="33">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AY79" s="33">
-        <f t="shared" si="37"/>
-        <v>1523.23</v>
-      </c>
-      <c r="AZ79" s="34" t="e">
+      <c r="BE79" s="61" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="BF79" s="34" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="BG79" s="34">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA79" s="34">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB79" s="34">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC79" s="34" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="BD79" s="64">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BE79" s="61" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BF79" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="BG79" s="34">
-        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BH79" s="49">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BI79" s="66"/>
       <c r="BJ79" s="51">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
@@ -12285,56 +12771,56 @@
       <c r="AU80" s="20"/>
       <c r="AV80" s="44"/>
       <c r="AW80" s="19">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AX80" s="20">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AY80" s="20">
+        <f t="shared" si="39"/>
+        <v>1594.3500000000001</v>
+      </c>
+      <c r="AZ80" s="21" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA80" s="21">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BB80" s="21">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BC80" s="21" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="BD80" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="AX80" s="20">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AY80" s="20">
-        <f t="shared" si="37"/>
-        <v>1523.88</v>
-      </c>
-      <c r="AZ80" s="21" t="e">
+      <c r="BE80" s="62" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="BF80" s="21" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="BG80" s="21">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA80" s="21">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="BB80" s="21">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="BC80" s="21" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="BD80" s="21">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BE80" s="62" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="BF80" s="21" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="BG80" s="21">
-        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BH80" s="50">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BI80" s="67"/>
       <c r="BJ80" s="52">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
@@ -12372,6 +12858,15 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A841E7D6-1405-4AC8-A599-0CE4601ECD66}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -12655,10 +13150,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1580" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72B66EAB-A363-4679-9E46-99848A85ED23}"/>
+  <xr:revisionPtr revIDLastSave="1645" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69A7FE9A-BF74-489D-8FAF-9A17F257F02E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1483,15 +1483,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BJ80"/>
-  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="10.7109375" customWidth="1"/>
-    <col min="6" max="59" width="12.7109375" customWidth="1"/>
-    <col min="60" max="60" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="61" max="62" width="16.28515625" customWidth="1"/>
+    <col min="2" max="4" width="10.6640625" customWidth="1"/>
+    <col min="6" max="59" width="12.6640625" customWidth="1"/>
+    <col min="60" max="60" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:62" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="BI1" s="80"/>
       <c r="BJ1" s="81"/>
     </row>
-    <row r="2" spans="1:62" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:62" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="36" t="s">
         <v>3</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>54</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>55</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>57</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>58</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>53</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>8</v>
       </c>
       <c r="AM9" s="16">
-        <f t="shared" ref="AM9:AM20" si="16">AK9-AK3</f>
+        <f t="shared" ref="AM9:AM26" si="16">AK9-AK3</f>
         <v>0</v>
       </c>
       <c r="AN9" s="45">
@@ -3070,19 +3070,19 @@
       <c r="AV9" s="42"/>
       <c r="AW9" s="15">
         <f t="shared" si="3"/>
-        <v>9.7663103999999987E-3</v>
+        <v>9.8469503999999985E-3</v>
       </c>
       <c r="AX9" s="16">
         <f t="shared" ref="AX9:AX40" si="17">AW3*24</f>
         <v>0.16378199999999998</v>
       </c>
       <c r="AY9" s="16">
-        <f>AY3+SUM(AF9:AH9,AL9:AM9)-AN9</f>
-        <v>1695.54</v>
+        <f>AO9+SUM(AF9:AH9,AJ9:AK9)-((AN9+1)*D9)</f>
+        <v>1709.54</v>
       </c>
       <c r="AZ9" s="17">
         <f>IF(ISBLANK(AJ9),NA(),IFERROR(AJ9/AY9,0))</f>
-        <v>4.7182608490510397E-3</v>
+        <v>4.6796214186272328E-3</v>
       </c>
       <c r="BA9" s="17">
         <f t="shared" si="6"/>
@@ -3102,11 +3102,11 @@
       </c>
       <c r="BE9" s="60">
         <f>IF(B9="No MPC", AS9*I9*AY9/1000,"")</f>
-        <v>9.7663103999999987E-3</v>
+        <v>9.8469503999999985E-3</v>
       </c>
       <c r="BF9" s="17">
         <f>IF(O9&lt;10, IF(B9&lt;&gt;"Julia",((5-O9)*AY9)/400, ""),0)</f>
-        <v>17.336896499999998</v>
+        <v>17.4800465</v>
       </c>
       <c r="BG9" s="17" t="str">
         <f t="shared" si="2"/>
@@ -3114,18 +3114,18 @@
       </c>
       <c r="BH9" s="49">
         <f t="shared" si="9"/>
-        <v>25.367039999999999</v>
+        <v>25.576494545454544</v>
       </c>
       <c r="BI9" s="69">
         <f t="shared" si="10"/>
-        <v>9.7663103999999987E-3</v>
+        <v>9.8469503999999985E-3</v>
       </c>
       <c r="BJ9" s="51">
         <f t="shared" si="11"/>
-        <v>17.336896499999998</v>
+        <v>17.4800465</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -3268,19 +3268,19 @@
       <c r="AV10" s="43"/>
       <c r="AW10" s="18">
         <f t="shared" si="3"/>
-        <v>8.0920187999999997E-3</v>
+        <v>8.1587988000000004E-3</v>
       </c>
       <c r="AX10" s="33">
         <f t="shared" si="17"/>
         <v>0.15043679999999998</v>
       </c>
       <c r="AY10" s="33">
-        <f t="shared" ref="AY10:AY40" si="18">AY4+SUM(AF10:AH10,AL10:AM10)-AN10</f>
-        <v>1696.44</v>
+        <f t="shared" ref="AY10:AY26" si="18">AO10+SUM(AF10:AH10,AJ10:AK10)-((AN10+1)*D10)</f>
+        <v>1710.44</v>
       </c>
       <c r="AZ10" s="34">
         <f t="shared" si="5"/>
-        <v>3.5368182782768622E-3</v>
+        <v>3.5078693201749255E-3</v>
       </c>
       <c r="BA10" s="34">
         <f t="shared" si="6"/>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="BC10" s="34">
         <f t="shared" si="13"/>
-        <v>9.0267334057285136E-3</v>
+        <v>9.1012272090343783E-3</v>
       </c>
       <c r="BD10" s="64" t="str">
         <f t="shared" si="1"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="BF10" s="34">
         <f t="shared" ref="BF10:BF12" si="19">IF(O10&lt;10, IF(B10&lt;&gt;"Julia",((5-O10)*AY10)/400, ""),0)</f>
-        <v>17.600565000000003</v>
+        <v>17.745815000000004</v>
       </c>
       <c r="BG10" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3312,18 +3312,18 @@
       </c>
       <c r="BH10" s="49">
         <f t="shared" si="9"/>
-        <v>23.446060794100038</v>
+        <v>23.639551192297088</v>
       </c>
       <c r="BI10" s="69">
         <f t="shared" si="10"/>
-        <v>9.0267334057285136E-3</v>
+        <v>9.1012272090343783E-3</v>
       </c>
       <c r="BJ10" s="51">
         <f t="shared" si="11"/>
-        <v>17.600565000000003</v>
+        <v>17.745815000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
@@ -3466,7 +3466,7 @@
       <c r="AV11" s="43"/>
       <c r="AW11" s="18">
         <f t="shared" si="3"/>
-        <v>8.0671671000000014E-3</v>
+        <v>8.1339471000000003E-3</v>
       </c>
       <c r="AX11" s="33">
         <f t="shared" si="17"/>
@@ -3474,11 +3474,11 @@
       </c>
       <c r="AY11" s="33">
         <f t="shared" si="18"/>
-        <v>1691.23</v>
+        <v>1705.23</v>
       </c>
       <c r="AZ11" s="34">
         <f t="shared" si="5"/>
-        <v>3.5477137941025169E-3</v>
+        <v>3.5185869354867087E-3</v>
       </c>
       <c r="BA11" s="34">
         <f t="shared" si="6"/>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="BC11" s="34">
         <f t="shared" si="13"/>
-        <v>8.7115764713592454E-3</v>
+        <v>8.7836908913961585E-3</v>
       </c>
       <c r="BD11" s="64" t="str">
         <f t="shared" si="1"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="BF11" s="34">
         <f t="shared" si="19"/>
-        <v>17.250546</v>
+        <v>17.393346000000001</v>
       </c>
       <c r="BG11" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3510,18 +3510,18 @@
       </c>
       <c r="BH11" s="49">
         <f t="shared" si="9"/>
-        <v>22.62747135417986</v>
+        <v>22.814781536093918</v>
       </c>
       <c r="BI11" s="69">
         <f t="shared" si="10"/>
-        <v>8.7115764713592454E-3</v>
+        <v>8.7836908913961585E-3</v>
       </c>
       <c r="BJ11" s="51">
         <f t="shared" si="11"/>
-        <v>17.250546</v>
+        <v>17.393346000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
@@ -3662,7 +3662,7 @@
       <c r="AV12" s="43"/>
       <c r="AW12" s="18">
         <f t="shared" si="3"/>
-        <v>1.25158158E-2</v>
+        <v>1.26191358E-2</v>
       </c>
       <c r="AX12" s="33">
         <f t="shared" si="17"/>
@@ -3670,11 +3670,11 @@
       </c>
       <c r="AY12" s="33">
         <f t="shared" si="18"/>
-        <v>1695.91</v>
+        <v>1709.91</v>
       </c>
       <c r="AZ12" s="34">
         <f t="shared" si="5"/>
-        <v>5.8965393210724621E-3</v>
+        <v>5.8482610195858256E-3</v>
       </c>
       <c r="BA12" s="34">
         <f t="shared" si="6"/>
@@ -3694,11 +3694,11 @@
       </c>
       <c r="BE12" s="61">
         <f t="shared" si="8"/>
-        <v>1.25158158E-2</v>
+        <v>1.26191358E-2</v>
       </c>
       <c r="BF12" s="34">
         <f t="shared" si="19"/>
-        <v>21.198875000000001</v>
+        <v>21.373875000000002</v>
       </c>
       <c r="BG12" s="34" t="str">
         <f t="shared" si="2"/>
@@ -3706,18 +3706,18 @@
       </c>
       <c r="BH12" s="49">
         <f t="shared" si="9"/>
-        <v>32.508612467532465</v>
+        <v>32.776976103896104</v>
       </c>
       <c r="BI12" s="69">
         <f t="shared" si="10"/>
-        <v>1.25158158E-2</v>
+        <v>1.26191358E-2</v>
       </c>
       <c r="BJ12" s="51">
         <f t="shared" si="11"/>
-        <v>21.198875000000001</v>
+        <v>21.373875000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="AW13" s="18">
         <f t="shared" si="3"/>
-        <v>7.7338967999999991E-3</v>
+        <v>7.797736799999999E-3</v>
       </c>
       <c r="AX13" s="33">
         <f t="shared" si="17"/>
@@ -3870,11 +3870,11 @@
       </c>
       <c r="AY13" s="33">
         <f t="shared" si="18"/>
-        <v>1696.03</v>
+        <v>1710.03</v>
       </c>
       <c r="AZ13" s="34">
         <f t="shared" si="5"/>
-        <v>4.1272854843369513E-3</v>
+        <v>4.0934954357525893E-3</v>
       </c>
       <c r="BA13" s="34">
         <f t="shared" si="6"/>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="BD13" s="64">
         <f>IF(B13="Julia",AU13*AY13/24/60,"")</f>
-        <v>1.5235230244764976E-2</v>
+        <v>1.5360990534044473E-2</v>
       </c>
       <c r="BE13" s="61" t="str">
         <f t="shared" si="8"/>
@@ -3898,26 +3898,26 @@
       </c>
       <c r="BF13" s="71">
         <f>IF(O13&lt;10, IF(B13&lt;&gt;"Jul",((5-O13)*AY13)/400, ""),0)</f>
-        <v>13.907446</v>
+        <v>14.022246000000001</v>
       </c>
       <c r="BG13" s="34">
         <f t="shared" si="2"/>
-        <v>12.787361699331303</v>
+        <v>12.892915883980535</v>
       </c>
       <c r="BH13" s="49">
         <f t="shared" si="9"/>
-        <v>39.572026609779158</v>
+        <v>39.89867671180383</v>
       </c>
       <c r="BI13" s="69">
         <f t="shared" si="10"/>
-        <v>1.5235230244764976E-2</v>
+        <v>1.5360990534044473E-2</v>
       </c>
       <c r="BJ13" s="73">
         <f t="shared" si="11"/>
-        <v>13.907446</v>
+        <v>14.022246000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>58</v>
       </c>
@@ -4056,7 +4056,7 @@
       <c r="AT14" s="19"/>
       <c r="AU14" s="20">
         <f>BE14*60*24/AY14</f>
-        <v>6.998400000000001E-3</v>
+        <v>6.9983999999999992E-3</v>
       </c>
       <c r="AV14" s="20">
         <f>BF14/AY14</f>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AW14" s="19">
         <f t="shared" si="3"/>
-        <v>8.2507248000000012E-3</v>
+        <v>8.3187647999999996E-3</v>
       </c>
       <c r="AX14" s="20">
         <f t="shared" si="17"/>
@@ -4072,11 +4072,11 @@
       </c>
       <c r="AY14" s="20">
         <f t="shared" si="18"/>
-        <v>1697.68</v>
+        <v>1711.68</v>
       </c>
       <c r="AZ14" s="21">
         <f t="shared" si="5"/>
-        <v>4.7123132745864943E-3</v>
+        <v>4.6737707982800521E-3</v>
       </c>
       <c r="BA14" s="21">
         <f t="shared" si="6"/>
@@ -4092,34 +4092,34 @@
       </c>
       <c r="BD14" s="21">
         <f t="shared" si="1"/>
-        <v>8.2507248000000012E-3</v>
+        <v>8.3187647999999996E-3</v>
       </c>
       <c r="BE14" s="62">
         <f>AS14*I14*AY14/1000</f>
-        <v>8.2507248000000012E-3</v>
+        <v>8.3187647999999996E-3</v>
       </c>
       <c r="BF14" s="72">
         <f>IF(O14&lt;10, IF(B14&lt;&gt;"Jul",((5-O14)*AY14)/400, ""),0)</f>
-        <v>17.570988</v>
+        <v>17.715888</v>
       </c>
       <c r="BG14" s="21">
         <f t="shared" si="2"/>
-        <v>17.570988</v>
+        <v>17.715888</v>
       </c>
       <c r="BH14" s="49">
         <f t="shared" si="9"/>
-        <v>21.430454025974029</v>
+        <v>21.607181298701299</v>
       </c>
       <c r="BI14" s="69">
         <f t="shared" si="10"/>
-        <v>8.2507248000000012E-3</v>
+        <v>8.3187647999999996E-3</v>
       </c>
       <c r="BJ14" s="73">
         <f t="shared" si="11"/>
-        <v>17.570988</v>
+        <v>17.715888</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>53</v>
       </c>
@@ -4220,7 +4220,9 @@
       <c r="AH15" s="16">
         <v>2</v>
       </c>
-      <c r="AI15" s="16"/>
+      <c r="AI15" s="16">
+        <v>1.2285640799999999E-2</v>
+      </c>
       <c r="AJ15" s="16">
         <v>22.3</v>
       </c>
@@ -4228,7 +4230,7 @@
         <v>19.55</v>
       </c>
       <c r="AL15" s="16">
-        <f t="shared" si="15"/>
+        <f>AJ15-AJ9</f>
         <v>14.3</v>
       </c>
       <c r="AM15" s="16">
@@ -4258,19 +4260,19 @@
       <c r="AV15" s="42"/>
       <c r="AW15" s="15">
         <f t="shared" si="3"/>
-        <v>1.2317784E-2</v>
+        <v>1.2285640799999999E-2</v>
       </c>
       <c r="AX15" s="16">
         <f t="shared" si="17"/>
-        <v>0.23439144959999997</v>
+        <v>0.23632680959999997</v>
       </c>
       <c r="AY15" s="16">
-        <f>AY9+SUM(AF15:AH15,AL15:AM15)-AN15</f>
-        <v>1739.8</v>
+        <f t="shared" si="18"/>
+        <v>1735.26</v>
       </c>
       <c r="AZ15" s="17">
         <f t="shared" si="5"/>
-        <v>1.2817565237383609E-2</v>
+        <v>1.2851100123324459E-2</v>
       </c>
       <c r="BA15" s="17">
         <f t="shared" si="6"/>
@@ -4278,7 +4280,7 @@
       </c>
       <c r="BB15" s="17">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.29485537919999999</v>
       </c>
       <c r="BC15" s="17" t="str">
         <f t="shared" si="13"/>
@@ -4290,11 +4292,11 @@
       </c>
       <c r="BE15" s="60">
         <f t="shared" si="8"/>
-        <v>1.2317784E-2</v>
+        <v>1.2285640799999999E-2</v>
       </c>
       <c r="BF15" s="17">
         <f>IF(O15&lt;1.5, IF(B15&lt;&gt;"Julia",((3-O15)*AY15)/400, ""),0)</f>
-        <v>11.56967</v>
+        <v>11.539479000000002</v>
       </c>
       <c r="BG15" s="17" t="str">
         <f t="shared" si="2"/>
@@ -4302,18 +4304,18 @@
       </c>
       <c r="BH15" s="48">
         <f t="shared" si="9"/>
-        <v>31.994244155844157</v>
+        <v>31.910755324675325</v>
       </c>
       <c r="BI15" s="68">
         <f t="shared" si="10"/>
-        <v>1.2317784E-2</v>
+        <v>1.2285640799999999E-2</v>
       </c>
       <c r="BJ15" s="53">
         <f t="shared" si="11"/>
-        <v>11.56967</v>
+        <v>11.539479000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
@@ -4414,7 +4416,9 @@
       <c r="AH16" s="33">
         <v>1.43</v>
       </c>
-      <c r="AI16" s="33"/>
+      <c r="AI16" s="33">
+        <v>6.4874039047218583E-3</v>
+      </c>
       <c r="AJ16" s="33">
         <v>19.2</v>
       </c>
@@ -4454,19 +4458,19 @@
       <c r="AV16" s="43"/>
       <c r="AW16" s="18">
         <f t="shared" si="3"/>
-        <v>1.1174696939999998E-2</v>
+        <v>1.1126932139999997E-2</v>
       </c>
       <c r="AX16" s="33">
         <f t="shared" si="17"/>
-        <v>0.19420845119999999</v>
+        <v>0.19581117120000002</v>
       </c>
       <c r="AY16" s="33">
         <f t="shared" si="18"/>
-        <v>1740.607</v>
+        <v>1733.1669999999999</v>
       </c>
       <c r="AZ16" s="34">
         <f t="shared" si="5"/>
-        <v>1.1030634715360791E-2</v>
+        <v>1.1077986137515889E-2</v>
       </c>
       <c r="BA16" s="34">
         <f t="shared" si="6"/>
@@ -4474,11 +4478,11 @@
       </c>
       <c r="BB16" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.15569769371332459</v>
       </c>
       <c r="BC16" s="34">
         <f t="shared" si="13"/>
-        <v>6.5152525108002875E-3</v>
+        <v>6.4874039047218583E-3</v>
       </c>
       <c r="BD16" s="64" t="str">
         <f t="shared" si="1"/>
@@ -4490,7 +4494,7 @@
       </c>
       <c r="BF16" s="34">
         <f t="shared" ref="BF16:BF73" si="20">IF(O16&lt;1.5, IF(B16&lt;&gt;"Julia",((3-O16)*AY16)/400, ""),0)</f>
-        <v>12.662915925</v>
+        <v>12.608789925000002</v>
       </c>
       <c r="BG16" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4498,18 +4502,18 @@
       </c>
       <c r="BH16" s="49">
         <f t="shared" si="9"/>
-        <v>16.922733794286462</v>
+        <v>16.850399752524307</v>
       </c>
       <c r="BI16" s="69">
         <f t="shared" si="10"/>
-        <v>6.5152525108002875E-3</v>
+        <v>6.4874039047218583E-3</v>
       </c>
       <c r="BJ16" s="51">
         <f t="shared" si="11"/>
-        <v>12.662915925</v>
+        <v>12.608789925000002</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>55</v>
       </c>
@@ -4610,7 +4614,9 @@
       <c r="AH17" s="33">
         <v>5.78</v>
       </c>
-      <c r="AI17" s="33"/>
+      <c r="AI17" s="33">
+        <v>6.7547597046078529E-3</v>
+      </c>
       <c r="AJ17" s="33">
         <v>19</v>
       </c>
@@ -4650,19 +4656,19 @@
       <c r="AV17" s="43"/>
       <c r="AW17" s="18">
         <f t="shared" si="3"/>
-        <v>1.2069941519999999E-2</v>
+        <v>1.205442072E-2</v>
       </c>
       <c r="AX17" s="33">
         <f t="shared" si="17"/>
-        <v>0.19361201040000003</v>
+        <v>0.19521473040000001</v>
       </c>
       <c r="AY17" s="33">
         <f t="shared" si="18"/>
-        <v>1734.1870000000001</v>
+        <v>1731.9570000000001</v>
       </c>
       <c r="AZ17" s="34">
         <f t="shared" si="5"/>
-        <v>1.0956142561327008E-2</v>
+        <v>1.0970249261384664E-2</v>
       </c>
       <c r="BA17" s="34">
         <f t="shared" si="6"/>
@@ -4670,11 +4676,11 @@
       </c>
       <c r="BB17" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.16211423291058846</v>
       </c>
       <c r="BC17" s="34">
         <f t="shared" si="13"/>
-        <v>6.7634568686490365E-3</v>
+        <v>6.7547597046078529E-3</v>
       </c>
       <c r="BD17" s="64" t="str">
         <f t="shared" si="1"/>
@@ -4686,7 +4692,7 @@
       </c>
       <c r="BF17" s="34">
         <f t="shared" si="20"/>
-        <v>12.009244975000001</v>
+        <v>11.993802225000001</v>
       </c>
       <c r="BG17" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4694,18 +4700,18 @@
       </c>
       <c r="BH17" s="49">
         <f t="shared" si="9"/>
-        <v>17.567420438049446</v>
+        <v>17.544830401578839</v>
       </c>
       <c r="BI17" s="69">
         <f t="shared" si="10"/>
-        <v>6.7634568686490365E-3</v>
+        <v>6.7547597046078529E-3</v>
       </c>
       <c r="BJ17" s="51">
         <f t="shared" si="11"/>
-        <v>12.009244975000001</v>
+        <v>11.993802225000001</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -4796,7 +4802,9 @@
       <c r="AH18" s="33">
         <v>1.1499999999999999</v>
       </c>
-      <c r="AI18" s="33"/>
+      <c r="AI18" s="33">
+        <v>0</v>
+      </c>
       <c r="AJ18" s="33">
         <v>28.02</v>
       </c>
@@ -4838,15 +4846,15 @@
       </c>
       <c r="AX18" s="33">
         <f t="shared" si="17"/>
-        <v>0.30037957920000002</v>
+        <v>0.30285925920000001</v>
       </c>
       <c r="AY18" s="33">
         <f t="shared" si="18"/>
-        <v>1739.662</v>
+        <v>1736.752</v>
       </c>
       <c r="AZ18" s="34">
         <f t="shared" si="5"/>
-        <v>1.610657702473239E-2</v>
+        <v>1.6133564262485377E-2</v>
       </c>
       <c r="BA18" s="34">
         <f t="shared" si="6"/>
@@ -4870,7 +4878,7 @@
       </c>
       <c r="BF18" s="34">
         <f t="shared" si="20"/>
-        <v>13.047464999999999</v>
+        <v>13.025639999999999</v>
       </c>
       <c r="BG18" s="34" t="str">
         <f t="shared" si="2"/>
@@ -4886,10 +4894,10 @@
       </c>
       <c r="BJ18" s="51">
         <f t="shared" si="11"/>
-        <v>13.047464999999999</v>
+        <v>13.025639999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
@@ -4990,7 +4998,9 @@
       <c r="AH19" s="33">
         <v>3.54</v>
       </c>
-      <c r="AI19" s="33"/>
+      <c r="AI19" s="33">
+        <v>1.6993613868659822E-2</v>
+      </c>
       <c r="AJ19" s="33">
         <v>28.89</v>
       </c>
@@ -5025,26 +5035,26 @@
       </c>
       <c r="AT19" s="18"/>
       <c r="AU19">
-        <v>1.52722913680596E-2</v>
+        <v>1.40593414393777E-2</v>
       </c>
       <c r="AV19" s="43">
         <v>2.2770951490618898E-3</v>
       </c>
       <c r="AW19" s="18">
         <f t="shared" si="3"/>
-        <v>1.0112622930000001E-2</v>
+        <v>1.0077709230000001E-2</v>
       </c>
       <c r="AX19" s="33">
         <f t="shared" si="17"/>
-        <v>0.18561352319999996</v>
+        <v>0.18714568319999997</v>
       </c>
       <c r="AY19" s="33">
         <f t="shared" si="18"/>
-        <v>1746.567</v>
+        <v>1740.537</v>
       </c>
       <c r="AZ19" s="34">
         <f t="shared" si="5"/>
-        <v>1.6541020184166998E-2</v>
+        <v>1.6598325689140766E-2</v>
       </c>
       <c r="BA19" s="34">
         <f t="shared" si="6"/>
@@ -5052,7 +5062,7 @@
       </c>
       <c r="BB19" s="34">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.40784673284783574</v>
       </c>
       <c r="BC19" s="34" t="str">
         <f t="shared" si="13"/>
@@ -5060,7 +5070,7 @@
       </c>
       <c r="BD19" s="64">
         <f t="shared" si="1"/>
-        <v>1.8523666748498438E-2</v>
+        <v>1.6993613868659822E-2</v>
       </c>
       <c r="BE19" s="61" t="str">
         <f t="shared" si="8"/>
@@ -5069,22 +5079,22 @@
       <c r="BF19" s="34"/>
       <c r="BG19" s="34">
         <f t="shared" si="2"/>
-        <v>3.9770992432115779</v>
+        <v>3.9633683594627347</v>
       </c>
       <c r="BH19" s="49">
         <f t="shared" si="9"/>
-        <v>48.113420125969974</v>
+        <v>44.139256801713827</v>
       </c>
       <c r="BI19" s="69">
         <f t="shared" si="10"/>
-        <v>1.8523666748498438E-2</v>
+        <v>1.6993613868659822E-2</v>
       </c>
       <c r="BJ19" s="51">
         <f t="shared" si="11"/>
-        <v>3.9770992432115779</v>
+        <v>3.9633683594627347</v>
       </c>
     </row>
-    <row r="20" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>58</v>
       </c>
@@ -5185,7 +5195,9 @@
       <c r="AH20" s="20">
         <v>3.55</v>
       </c>
-      <c r="AI20" s="20"/>
+      <c r="AI20" s="20">
+        <v>2.4710181546437494E-2</v>
+      </c>
       <c r="AJ20" s="20">
         <v>20.149999999999999</v>
       </c>
@@ -5219,27 +5231,27 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AT20" s="19"/>
-      <c r="AU20" s="20">
-        <v>2.1013375291705799E-2</v>
+      <c r="AU20">
+        <v>2.0477226071043401E-2</v>
       </c>
       <c r="AV20" s="44">
         <v>4.8817390308066597E-3</v>
       </c>
       <c r="AW20" s="19">
         <f t="shared" si="3"/>
-        <v>1.0675421999999999E-2</v>
+        <v>1.0634540399999998E-2</v>
       </c>
       <c r="AX20" s="20">
         <f t="shared" si="17"/>
-        <v>0.19801739520000003</v>
+        <v>0.19965035519999999</v>
       </c>
       <c r="AY20" s="20">
         <f t="shared" si="18"/>
-        <v>1744.3500000000001</v>
+        <v>1737.67</v>
       </c>
       <c r="AZ20" s="21">
         <f t="shared" si="5"/>
-        <v>1.1551580818069767E-2</v>
+        <v>1.1595987730696851E-2</v>
       </c>
       <c r="BA20" s="21">
         <f t="shared" si="6"/>
@@ -5247,7 +5259,7 @@
       </c>
       <c r="BB20" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.59304435711449988</v>
       </c>
       <c r="BC20" s="21" t="str">
         <f t="shared" si="13"/>
@@ -5255,7 +5267,7 @@
       </c>
       <c r="BD20" s="21">
         <f t="shared" si="1"/>
-        <v>2.54546397153382E-2</v>
+        <v>2.4710181546437494E-2</v>
       </c>
       <c r="BE20" s="62" t="str">
         <f t="shared" si="8"/>
@@ -5267,22 +5279,22 @@
       </c>
       <c r="BG20" s="21">
         <f t="shared" si="2"/>
-        <v>8.5154614783875981</v>
+        <v>8.4828514616618094</v>
       </c>
       <c r="BH20" s="50">
         <f t="shared" si="9"/>
-        <v>66.11594731256676</v>
+        <v>64.182289731006477</v>
       </c>
       <c r="BI20" s="70">
         <f t="shared" si="10"/>
-        <v>2.54546397153382E-2</v>
+        <v>2.4710181546437494E-2</v>
       </c>
       <c r="BJ20" s="52">
         <f t="shared" si="11"/>
-        <v>8.5154614783875981</v>
+        <v>8.4828514616618094</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
@@ -5297,39 +5309,105 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="10"/>
-      <c r="Y21" s="10"/>
-      <c r="Z21" s="10"/>
-      <c r="AA21" s="27"/>
-      <c r="AB21" s="15"/>
-      <c r="AC21" s="16"/>
-      <c r="AD21" s="16"/>
-      <c r="AE21" s="16"/>
-      <c r="AF21" s="16"/>
-      <c r="AG21" s="16"/>
-      <c r="AH21" s="16"/>
+      <c r="G21" s="10">
+        <v>1357.44</v>
+      </c>
+      <c r="H21" s="10">
+        <v>26.9</v>
+      </c>
+      <c r="I21" s="10">
+        <v>26.1</v>
+      </c>
+      <c r="J21" s="10">
+        <v>96.7</v>
+      </c>
+      <c r="K21" s="10">
+        <v>16.3</v>
+      </c>
+      <c r="L21" s="10">
+        <v>349</v>
+      </c>
+      <c r="M21" s="10">
+        <v>2.34</v>
+      </c>
+      <c r="N21" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="O21" s="10">
+        <v>0</v>
+      </c>
+      <c r="P21" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="R21" s="10">
+        <v>4.42</v>
+      </c>
+      <c r="S21" s="10">
+        <v>7.2889999999999997</v>
+      </c>
+      <c r="T21" s="10">
+        <v>97</v>
+      </c>
+      <c r="U21" s="10">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="V21" s="10">
+        <v>3.21</v>
+      </c>
+      <c r="W21" s="10">
+        <v>151.6</v>
+      </c>
+      <c r="X21" s="10">
+        <v>45.4</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>85.1</v>
+      </c>
+      <c r="Z21" s="10">
+        <v>15.5</v>
+      </c>
+      <c r="AA21" s="27">
+        <v>7.3310000000000004</v>
+      </c>
+      <c r="AB21" s="15">
+        <v>299</v>
+      </c>
+      <c r="AC21" s="16">
+        <v>0.503</v>
+      </c>
+      <c r="AD21" s="16">
+        <v>7.3</v>
+      </c>
+      <c r="AE21" s="16">
+        <v>34</v>
+      </c>
+      <c r="AF21" s="16">
+        <v>31.315000000000001</v>
+      </c>
+      <c r="AG21" s="16">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="AH21" s="16">
+        <v>2.73</v>
+      </c>
       <c r="AI21" s="16"/>
-      <c r="AJ21" s="16"/>
-      <c r="AK21" s="16"/>
-      <c r="AL21" s="16"/>
-      <c r="AM21" s="16"/>
+      <c r="AJ21" s="16">
+        <v>39.03</v>
+      </c>
+      <c r="AK21" s="16">
+        <v>31.97</v>
+      </c>
+      <c r="AL21" s="16">
+        <f>AJ21-AJ15</f>
+        <v>16.73</v>
+      </c>
+      <c r="AM21" s="16">
+        <f t="shared" si="16"/>
+        <v>12.419999999999998</v>
+      </c>
       <c r="AN21" s="45">
         <v>15</v>
       </c>
@@ -5353,23 +5431,23 @@
       <c r="AV21" s="42"/>
       <c r="AW21" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.37621646E-2</v>
       </c>
       <c r="AX21" s="16">
         <f t="shared" si="17"/>
-        <v>0.29562681600000001</v>
+        <v>0.29485537919999999</v>
       </c>
       <c r="AY21" s="16">
         <f t="shared" si="18"/>
-        <v>1724.8</v>
-      </c>
-      <c r="AZ21" s="17" t="e">
+        <v>1757.62</v>
+      </c>
+      <c r="AZ21" s="17">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>2.2206165155152995E-2</v>
       </c>
       <c r="BA21" s="17">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2.2958823529411764E-2</v>
       </c>
       <c r="BB21" s="17">
         <f t="shared" si="7"/>
@@ -5385,11 +5463,11 @@
       </c>
       <c r="BE21" s="60">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1.37621646E-2</v>
       </c>
       <c r="BF21" s="17">
         <f t="shared" si="20"/>
-        <v>12.936</v>
+        <v>13.18215</v>
       </c>
       <c r="BG21" s="17" t="str">
         <f t="shared" si="2"/>
@@ -5397,18 +5475,18 @@
       </c>
       <c r="BH21" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>35.745882077922076</v>
       </c>
       <c r="BI21" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1.37621646E-2</v>
       </c>
       <c r="BJ21" s="51">
         <f t="shared" si="11"/>
-        <v>12.936</v>
+        <v>13.18215</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -5423,39 +5501,105 @@
       </c>
       <c r="E22" s="31"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
-      <c r="T22" s="32"/>
-      <c r="U22" s="32"/>
-      <c r="V22" s="32"/>
-      <c r="W22" s="32"/>
-      <c r="X22" s="32"/>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="28"/>
-      <c r="AB22" s="18"/>
-      <c r="AC22" s="33"/>
-      <c r="AD22" s="33"/>
-      <c r="AE22" s="33"/>
-      <c r="AF22" s="33"/>
-      <c r="AG22" s="33"/>
-      <c r="AH22" s="33"/>
+      <c r="G22" s="32">
+        <v>1295.5</v>
+      </c>
+      <c r="H22" s="32">
+        <v>24.3</v>
+      </c>
+      <c r="I22" s="32">
+        <v>23.4</v>
+      </c>
+      <c r="J22" s="32">
+        <v>96</v>
+      </c>
+      <c r="K22" s="32">
+        <v>16.2</v>
+      </c>
+      <c r="L22" s="32">
+        <v>354</v>
+      </c>
+      <c r="M22" s="32">
+        <v>3.12</v>
+      </c>
+      <c r="N22" s="32">
+        <v>0.39</v>
+      </c>
+      <c r="O22" s="32">
+        <v>0</v>
+      </c>
+      <c r="P22" s="32">
+        <v>0.05</v>
+      </c>
+      <c r="Q22" s="32">
+        <v>0.12</v>
+      </c>
+      <c r="R22" s="32">
+        <v>5.05</v>
+      </c>
+      <c r="S22" s="32">
+        <v>7.2779999999999996</v>
+      </c>
+      <c r="T22" s="32">
+        <v>95</v>
+      </c>
+      <c r="U22" s="32">
+        <v>39.6</v>
+      </c>
+      <c r="V22" s="32">
+        <v>3.8</v>
+      </c>
+      <c r="W22" s="32">
+        <v>155.6</v>
+      </c>
+      <c r="X22" s="32">
+        <v>43.2</v>
+      </c>
+      <c r="Y22" s="32">
+        <v>83.3</v>
+      </c>
+      <c r="Z22" s="32">
+        <v>32</v>
+      </c>
+      <c r="AA22" s="28">
+        <v>7.319</v>
+      </c>
+      <c r="AB22" s="18">
+        <v>299</v>
+      </c>
+      <c r="AC22" s="33">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="AD22" s="33">
+        <v>7.3</v>
+      </c>
+      <c r="AE22" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF22" s="33">
+        <v>33.53</v>
+      </c>
+      <c r="AG22" s="33">
+        <v>3.91</v>
+      </c>
+      <c r="AH22" s="33">
+        <v>1.93</v>
+      </c>
       <c r="AI22" s="33"/>
-      <c r="AJ22" s="33"/>
-      <c r="AK22" s="33"/>
-      <c r="AL22" s="33"/>
-      <c r="AM22" s="33"/>
+      <c r="AJ22" s="33">
+        <v>29.1</v>
+      </c>
+      <c r="AK22" s="33">
+        <v>32.9</v>
+      </c>
+      <c r="AL22" s="33">
+        <f t="shared" ref="AL22:AL26" si="21">AJ22-AJ16</f>
+        <v>9.9000000000000021</v>
+      </c>
+      <c r="AM22" s="33">
+        <f t="shared" si="16"/>
+        <v>13.559999999999999</v>
+      </c>
       <c r="AN22" s="46">
         <v>15</v>
       </c>
@@ -5479,23 +5623,23 @@
       <c r="AV22" s="43"/>
       <c r="AW22" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.2308657399999997E-2</v>
       </c>
       <c r="AX22" s="33">
         <f t="shared" si="17"/>
-        <v>0.26819272655999993</v>
+        <v>0.26704637135999992</v>
       </c>
       <c r="AY22" s="33">
         <f t="shared" si="18"/>
-        <v>1725.607</v>
-      </c>
-      <c r="AZ22" s="34" t="e">
+        <v>1753.37</v>
+      </c>
+      <c r="AZ22" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>1.6596611097486558E-2</v>
       </c>
       <c r="BA22" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.7117647058823529E-2</v>
       </c>
       <c r="BB22" s="34">
         <f t="shared" si="7"/>
@@ -5515,7 +5659,7 @@
       </c>
       <c r="BF22" s="34">
         <f t="shared" si="20"/>
-        <v>12.942052499999999</v>
+        <v>13.150274999999999</v>
       </c>
       <c r="BG22" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5531,10 +5675,10 @@
       </c>
       <c r="BJ22" s="51">
         <f t="shared" si="11"/>
-        <v>12.942052499999999</v>
+        <v>13.150274999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -5549,39 +5693,105 @@
       </c>
       <c r="E23" s="31"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="32"/>
-      <c r="Q23" s="32"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="32"/>
-      <c r="T23" s="32"/>
-      <c r="U23" s="32"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="32"/>
-      <c r="X23" s="32"/>
-      <c r="Y23" s="32"/>
-      <c r="Z23" s="32"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="18"/>
-      <c r="AC23" s="33"/>
-      <c r="AD23" s="33"/>
-      <c r="AE23" s="33"/>
-      <c r="AF23" s="33"/>
-      <c r="AG23" s="33"/>
-      <c r="AH23" s="33"/>
+      <c r="G23" s="32">
+        <v>1377.43</v>
+      </c>
+      <c r="H23" s="32">
+        <v>24.3</v>
+      </c>
+      <c r="I23" s="32">
+        <v>23.1</v>
+      </c>
+      <c r="J23" s="32">
+        <v>95.1</v>
+      </c>
+      <c r="K23" s="32">
+        <v>16</v>
+      </c>
+      <c r="L23" s="32">
+        <v>335</v>
+      </c>
+      <c r="M23" s="32">
+        <v>3.02</v>
+      </c>
+      <c r="N23" s="32">
+        <v>0.4</v>
+      </c>
+      <c r="O23" s="32">
+        <v>0</v>
+      </c>
+      <c r="P23" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="Q23" s="32">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R23" s="32">
+        <v>4.63</v>
+      </c>
+      <c r="S23" s="32">
+        <v>7.2460000000000004</v>
+      </c>
+      <c r="T23" s="32">
+        <v>83.5</v>
+      </c>
+      <c r="U23" s="32">
+        <v>33.9</v>
+      </c>
+      <c r="V23" s="32">
+        <v>3.72</v>
+      </c>
+      <c r="W23" s="32">
+        <v>148.1</v>
+      </c>
+      <c r="X23" s="32">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="Y23" s="32">
+        <v>73.3</v>
+      </c>
+      <c r="Z23" s="32">
+        <v>27.4</v>
+      </c>
+      <c r="AA23" s="28">
+        <v>7.2869999999999999</v>
+      </c>
+      <c r="AB23" s="18">
+        <v>300</v>
+      </c>
+      <c r="AC23" s="33">
+        <v>0.52</v>
+      </c>
+      <c r="AD23" s="33">
+        <v>7.27</v>
+      </c>
+      <c r="AE23" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF23" s="33">
+        <v>27.27</v>
+      </c>
+      <c r="AG23" s="33">
+        <v>3.55</v>
+      </c>
+      <c r="AH23" s="33">
+        <v>5.8</v>
+      </c>
       <c r="AI23" s="33"/>
-      <c r="AJ23" s="33"/>
-      <c r="AK23" s="33"/>
-      <c r="AL23" s="33"/>
-      <c r="AM23" s="33"/>
+      <c r="AJ23" s="33">
+        <v>28.91</v>
+      </c>
+      <c r="AK23" s="33">
+        <v>32.65</v>
+      </c>
+      <c r="AL23" s="33">
+        <f t="shared" si="21"/>
+        <v>9.91</v>
+      </c>
+      <c r="AM23" s="33">
+        <f t="shared" si="16"/>
+        <v>12.919999999999998</v>
+      </c>
       <c r="AN23" s="46">
         <v>15</v>
       </c>
@@ -5605,23 +5815,23 @@
       <c r="AV23" s="43"/>
       <c r="AW23" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.2128747400000001E-2</v>
       </c>
       <c r="AX23" s="33">
         <f t="shared" si="17"/>
-        <v>0.28967859647999994</v>
+        <v>0.28930609728000001</v>
       </c>
       <c r="AY23" s="33">
         <f t="shared" si="18"/>
-        <v>1719.1870000000001</v>
-      </c>
-      <c r="AZ23" s="34" t="e">
-        <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>1750.18</v>
+      </c>
+      <c r="AZ23" s="34">
+        <f>IF(ISBLANK(AJ23),NA(),IFERROR(AJ23/AY23,0))</f>
+        <v>1.6518300974756882E-2</v>
       </c>
       <c r="BA23" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.7005882352941176E-2</v>
       </c>
       <c r="BB23" s="34">
         <f t="shared" si="7"/>
@@ -5641,7 +5851,7 @@
       </c>
       <c r="BF23" s="34">
         <f t="shared" si="20"/>
-        <v>12.893902500000001</v>
+        <v>13.12635</v>
       </c>
       <c r="BG23" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5657,10 +5867,10 @@
       </c>
       <c r="BJ23" s="51">
         <f t="shared" si="11"/>
-        <v>12.893902500000001</v>
+        <v>13.12635</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>56</v>
       </c>
@@ -5675,7 +5885,6 @@
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="32"/>
       <c r="H24" s="32"/>
       <c r="I24" s="32"/>
       <c r="J24" s="32"/>
@@ -5739,10 +5948,10 @@
       </c>
       <c r="AY24" s="33">
         <f t="shared" si="18"/>
-        <v>1724.662</v>
+        <v>1652</v>
       </c>
       <c r="AZ24" s="34" t="e">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(AJ24),NA(),IFERROR(AJ24/AY24,0))</f>
         <v>#N/A</v>
       </c>
       <c r="BA24" s="34">
@@ -5767,7 +5976,7 @@
       </c>
       <c r="BF24" s="34">
         <f t="shared" si="20"/>
-        <v>12.934965</v>
+        <v>12.39</v>
       </c>
       <c r="BG24" s="34" t="str">
         <f t="shared" si="2"/>
@@ -5783,10 +5992,10 @@
       </c>
       <c r="BJ24" s="51">
         <f t="shared" si="11"/>
-        <v>12.934965</v>
+        <v>12.39</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
@@ -5801,39 +6010,105 @@
       </c>
       <c r="E25" s="31"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="32"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="32"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="32"/>
-      <c r="T25" s="32"/>
-      <c r="U25" s="32"/>
-      <c r="V25" s="32"/>
-      <c r="W25" s="32"/>
-      <c r="X25" s="32"/>
-      <c r="Y25" s="32"/>
-      <c r="Z25" s="32"/>
-      <c r="AA25" s="28"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="33"/>
-      <c r="AD25" s="33"/>
-      <c r="AE25" s="33"/>
-      <c r="AF25" s="33"/>
-      <c r="AG25" s="33"/>
-      <c r="AH25" s="33"/>
+      <c r="G25" s="32">
+        <v>1329.46</v>
+      </c>
+      <c r="H25" s="32">
+        <v>22.8</v>
+      </c>
+      <c r="I25" s="32">
+        <v>22.1</v>
+      </c>
+      <c r="J25" s="32">
+        <v>97.2</v>
+      </c>
+      <c r="K25" s="32">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="L25" s="32">
+        <v>343</v>
+      </c>
+      <c r="M25" s="32">
+        <v>2.14</v>
+      </c>
+      <c r="N25" s="32">
+        <v>0.37</v>
+      </c>
+      <c r="O25" s="32">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="P25" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="Q25" s="32">
+        <v>0.06</v>
+      </c>
+      <c r="R25" s="32">
+        <v>3.62</v>
+      </c>
+      <c r="S25" s="32">
+        <v>7.1669999999999998</v>
+      </c>
+      <c r="T25" s="32">
+        <v>109.5</v>
+      </c>
+      <c r="U25" s="32">
+        <v>18.5</v>
+      </c>
+      <c r="V25" s="32">
+        <v>2.58</v>
+      </c>
+      <c r="W25" s="32">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="X25" s="32">
+        <v>38.4</v>
+      </c>
+      <c r="Y25" s="32">
+        <v>96</v>
+      </c>
+      <c r="Z25" s="32">
+        <v>14.9</v>
+      </c>
+      <c r="AA25" s="28">
+        <v>7.2060000000000004</v>
+      </c>
+      <c r="AB25" s="18">
+        <v>298</v>
+      </c>
+      <c r="AC25" s="33">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="AD25" s="33">
+        <v>7.18</v>
+      </c>
+      <c r="AE25" s="33">
+        <v>34</v>
+      </c>
+      <c r="AF25" s="33">
+        <v>24.77</v>
+      </c>
+      <c r="AG25" s="33">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="33">
+        <v>4.7699999999999996</v>
+      </c>
       <c r="AI25" s="33"/>
-      <c r="AJ25" s="33"/>
-      <c r="AK25" s="33"/>
-      <c r="AL25" s="33"/>
-      <c r="AM25" s="33"/>
+      <c r="AJ25" s="33">
+        <v>52.6</v>
+      </c>
+      <c r="AK25" s="33">
+        <v>20.73</v>
+      </c>
+      <c r="AL25" s="33">
+        <f t="shared" si="21"/>
+        <v>23.71</v>
+      </c>
+      <c r="AM25" s="33">
+        <f t="shared" si="16"/>
+        <v>4.8499999999999996</v>
+      </c>
       <c r="AN25" s="46">
         <v>15</v>
       </c>
@@ -5853,27 +6128,31 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AT25" s="18"/>
-      <c r="AU25" s="33"/>
-      <c r="AV25" s="43"/>
+      <c r="AU25" s="33">
+        <v>1.8952529242655902E-2</v>
+      </c>
+      <c r="AV25" s="43">
+        <v>3.0538307540188799E-3</v>
+      </c>
       <c r="AW25" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.1634788099999998E-2</v>
       </c>
       <c r="AX25" s="33">
         <f t="shared" si="17"/>
-        <v>0.24270295032</v>
+        <v>0.24186502152</v>
       </c>
       <c r="AY25" s="33">
         <f t="shared" si="18"/>
-        <v>1731.567</v>
-      </c>
-      <c r="AZ25" s="34" t="e">
+        <v>1754.87</v>
+      </c>
+      <c r="AZ25" s="34">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>2.9973730247824629E-2</v>
       </c>
       <c r="BA25" s="34">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3.0941176470588236E-2</v>
       </c>
       <c r="BB25" s="34">
         <f t="shared" si="7"/>
@@ -5885,7 +6164,7 @@
       </c>
       <c r="BD25" s="64">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.3096684022263579E-2</v>
       </c>
       <c r="BE25" s="61" t="str">
         <f t="shared" si="8"/>
@@ -5897,22 +6176,22 @@
       </c>
       <c r="BG25" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.3590759753051112</v>
       </c>
       <c r="BH25" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>59.991387070814497</v>
       </c>
       <c r="BI25" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.3096684022263579E-2</v>
       </c>
       <c r="BJ25" s="51">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5.3590759753051112</v>
       </c>
     </row>
-    <row r="26" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>58</v>
       </c>
@@ -5927,39 +6206,105 @@
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="13"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="19"/>
-      <c r="AC26" s="20"/>
-      <c r="AD26" s="20"/>
-      <c r="AE26" s="20"/>
-      <c r="AF26" s="20"/>
-      <c r="AG26" s="20"/>
-      <c r="AH26" s="20"/>
+      <c r="G26" s="32">
+        <v>1424.87</v>
+      </c>
+      <c r="H26" s="14">
+        <v>24.2</v>
+      </c>
+      <c r="I26" s="14">
+        <v>23.4</v>
+      </c>
+      <c r="J26" s="14">
+        <v>96.8</v>
+      </c>
+      <c r="K26" s="14">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="L26" s="14">
+        <v>328</v>
+      </c>
+      <c r="M26" s="14">
+        <v>1.48</v>
+      </c>
+      <c r="N26" s="14">
+        <v>0.36</v>
+      </c>
+      <c r="O26" s="14">
+        <v>0.86</v>
+      </c>
+      <c r="P26" s="14">
+        <v>0.19</v>
+      </c>
+      <c r="Q26" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="R26" s="14">
+        <v>1.91</v>
+      </c>
+      <c r="S26" s="14">
+        <v>7.2450000000000001</v>
+      </c>
+      <c r="T26" s="14">
+        <v>121.9</v>
+      </c>
+      <c r="U26" s="14">
+        <v>24.8</v>
+      </c>
+      <c r="V26" s="14">
+        <v>2.77</v>
+      </c>
+      <c r="W26" s="14">
+        <v>140.9</v>
+      </c>
+      <c r="X26" s="14">
+        <v>51.4</v>
+      </c>
+      <c r="Y26" s="14">
+        <v>106.9</v>
+      </c>
+      <c r="Z26" s="14">
+        <v>20</v>
+      </c>
+      <c r="AA26" s="29">
+        <v>7.2859999999999996</v>
+      </c>
+      <c r="AB26" s="19">
+        <v>297</v>
+      </c>
+      <c r="AC26" s="20">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="AD26" s="20">
+        <v>7.3</v>
+      </c>
+      <c r="AE26" s="20">
+        <v>34</v>
+      </c>
+      <c r="AF26" s="20">
+        <v>21.77</v>
+      </c>
+      <c r="AG26" s="20">
+        <v>14.266</v>
+      </c>
+      <c r="AH26" s="20">
+        <v>4.76</v>
+      </c>
       <c r="AI26" s="20"/>
-      <c r="AJ26" s="20"/>
-      <c r="AK26" s="20"/>
-      <c r="AL26" s="20"/>
-      <c r="AM26" s="20"/>
+      <c r="AJ26" s="20">
+        <v>51</v>
+      </c>
+      <c r="AK26" s="20">
+        <v>30.11</v>
+      </c>
+      <c r="AL26" s="20">
+        <f t="shared" si="21"/>
+        <v>30.85</v>
+      </c>
+      <c r="AM26" s="20">
+        <f t="shared" si="16"/>
+        <v>9.129999999999999</v>
+      </c>
       <c r="AN26" s="47">
         <v>15</v>
       </c>
@@ -5979,27 +6324,31 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AT26" s="19"/>
-      <c r="AU26" s="20"/>
-      <c r="AV26" s="44"/>
+      <c r="AU26" s="20">
+        <v>1.7933852E-2</v>
+      </c>
+      <c r="AV26" s="44">
+        <v>4.2153110000000002E-3</v>
+      </c>
       <c r="AW26" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.2452820119999998E-2</v>
       </c>
       <c r="AX26" s="20">
         <f t="shared" si="17"/>
-        <v>0.25621012799999998</v>
+        <v>0.25522896959999997</v>
       </c>
       <c r="AY26" s="20">
         <f t="shared" si="18"/>
-        <v>1729.3500000000001</v>
-      </c>
-      <c r="AZ26" s="21" t="e">
+        <v>1773.9059999999999</v>
+      </c>
+      <c r="AZ26" s="21">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>2.8750114154865027E-2</v>
       </c>
       <c r="BA26" s="21">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BB26" s="21">
         <f t="shared" si="7"/>
@@ -6011,7 +6360,7 @@
       </c>
       <c r="BD26" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.2092338656883332E-2</v>
       </c>
       <c r="BE26" s="62" t="str">
         <f t="shared" si="8"/>
@@ -6023,22 +6372,22 @@
       </c>
       <c r="BG26" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.4775654747660001</v>
       </c>
       <c r="BH26" s="49">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>57.382697810086583</v>
       </c>
       <c r="BI26" s="69">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2.2092338656883332E-2</v>
       </c>
       <c r="BJ26" s="51">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7.4775654747660001</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>53</v>
       </c>
@@ -6113,11 +6462,11 @@
       </c>
       <c r="AX27" s="16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>0.33029195039999998</v>
       </c>
       <c r="AY27" s="16">
-        <f t="shared" si="18"/>
-        <v>1709.8</v>
+        <f t="shared" ref="AY27:AY40" si="22">AY21+SUM(AF27:AH27,AL27:AM27)-AN27</f>
+        <v>1742.62</v>
       </c>
       <c r="AZ27" s="17" t="e">
         <f t="shared" si="5"/>
@@ -6145,7 +6494,7 @@
       </c>
       <c r="BF27" s="17">
         <f t="shared" si="20"/>
-        <v>12.823499999999999</v>
+        <v>13.069649999999999</v>
       </c>
       <c r="BG27" s="17" t="str">
         <f t="shared" si="2"/>
@@ -6161,10 +6510,10 @@
       </c>
       <c r="BJ27" s="53">
         <f t="shared" si="11"/>
-        <v>12.823499999999999</v>
+        <v>13.069649999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -6239,11 +6588,11 @@
       </c>
       <c r="AX28" s="33">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>0.29540777759999992</v>
       </c>
       <c r="AY28" s="33">
-        <f t="shared" si="18"/>
-        <v>1710.607</v>
+        <f t="shared" si="22"/>
+        <v>1738.37</v>
       </c>
       <c r="AZ28" s="34" t="e">
         <f t="shared" si="5"/>
@@ -6271,7 +6620,7 @@
       </c>
       <c r="BF28" s="34">
         <f t="shared" si="20"/>
-        <v>12.8295525</v>
+        <v>13.037775</v>
       </c>
       <c r="BG28" s="34" t="str">
         <f t="shared" si="2"/>
@@ -6287,10 +6636,10 @@
       </c>
       <c r="BJ28" s="51">
         <f t="shared" si="11"/>
-        <v>12.8295525</v>
+        <v>13.037775</v>
       </c>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>55</v>
       </c>
@@ -6365,11 +6714,11 @@
       </c>
       <c r="AX29" s="33">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>0.29108993760000001</v>
       </c>
       <c r="AY29" s="33">
-        <f t="shared" si="18"/>
-        <v>1704.1870000000001</v>
+        <f t="shared" si="22"/>
+        <v>1735.18</v>
       </c>
       <c r="AZ29" s="34" t="e">
         <f t="shared" si="5"/>
@@ -6397,7 +6746,7 @@
       </c>
       <c r="BF29" s="34">
         <f t="shared" si="20"/>
-        <v>12.781402500000002</v>
+        <v>13.01385</v>
       </c>
       <c r="BG29" s="34" t="str">
         <f t="shared" si="2"/>
@@ -6413,10 +6762,10 @@
       </c>
       <c r="BJ29" s="51">
         <f t="shared" si="11"/>
-        <v>12.781402500000002</v>
+        <v>13.01385</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
@@ -6494,8 +6843,8 @@
         <v>0</v>
       </c>
       <c r="AY30" s="33">
-        <f t="shared" si="18"/>
-        <v>1709.662</v>
+        <f t="shared" si="22"/>
+        <v>1637</v>
       </c>
       <c r="AZ30" s="34" t="e">
         <f t="shared" si="5"/>
@@ -6523,7 +6872,7 @@
       </c>
       <c r="BF30" s="34">
         <f t="shared" si="20"/>
-        <v>12.822464999999999</v>
+        <v>12.2775</v>
       </c>
       <c r="BG30" s="34" t="str">
         <f t="shared" si="2"/>
@@ -6539,10 +6888,10 @@
       </c>
       <c r="BJ30" s="51">
         <f t="shared" si="11"/>
-        <v>12.822464999999999</v>
+        <v>12.2775</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>57</v>
       </c>
@@ -6617,11 +6966,11 @@
       </c>
       <c r="AX31" s="33">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>0.27923491439999992</v>
       </c>
       <c r="AY31" s="33">
-        <f t="shared" si="18"/>
-        <v>1716.567</v>
+        <f t="shared" si="22"/>
+        <v>1739.87</v>
       </c>
       <c r="AZ31" s="34" t="e">
         <f t="shared" si="5"/>
@@ -6668,7 +7017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>58</v>
       </c>
@@ -6743,11 +7092,11 @@
       </c>
       <c r="AX32" s="20">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>0.29886768287999993</v>
       </c>
       <c r="AY32" s="20">
-        <f t="shared" si="18"/>
-        <v>1714.3500000000001</v>
+        <f t="shared" si="22"/>
+        <v>1758.9059999999999</v>
       </c>
       <c r="AZ32" s="21" t="e">
         <f t="shared" si="5"/>
@@ -6794,7 +7143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>53</v>
       </c>
@@ -6872,8 +7221,8 @@
         <v>0</v>
       </c>
       <c r="AY33" s="16">
-        <f t="shared" si="18"/>
-        <v>1694.8</v>
+        <f t="shared" si="22"/>
+        <v>1727.62</v>
       </c>
       <c r="AZ33" s="17" t="e">
         <f t="shared" si="5"/>
@@ -6901,7 +7250,7 @@
       </c>
       <c r="BF33" s="17">
         <f t="shared" si="20"/>
-        <v>12.710999999999999</v>
+        <v>12.957149999999999</v>
       </c>
       <c r="BG33" s="17" t="str">
         <f t="shared" si="2"/>
@@ -6917,10 +7266,10 @@
       </c>
       <c r="BJ33" s="51">
         <f t="shared" si="11"/>
-        <v>12.710999999999999</v>
+        <v>12.957149999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>54</v>
       </c>
@@ -6998,8 +7347,8 @@
         <v>0</v>
       </c>
       <c r="AY34" s="33">
-        <f t="shared" si="18"/>
-        <v>1695.607</v>
+        <f t="shared" si="22"/>
+        <v>1723.37</v>
       </c>
       <c r="AZ34" s="34" t="e">
         <f t="shared" si="5"/>
@@ -7027,7 +7376,7 @@
       </c>
       <c r="BF34" s="34">
         <f t="shared" si="20"/>
-        <v>12.717052499999999</v>
+        <v>12.925274999999999</v>
       </c>
       <c r="BG34" s="34" t="str">
         <f t="shared" si="2"/>
@@ -7043,10 +7392,10 @@
       </c>
       <c r="BJ34" s="51">
         <f t="shared" si="11"/>
-        <v>12.717052499999999</v>
+        <v>12.925274999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
@@ -7124,19 +7473,19 @@
         <v>0</v>
       </c>
       <c r="AY35" s="33">
-        <f t="shared" si="18"/>
-        <v>1689.1870000000001</v>
+        <f t="shared" si="22"/>
+        <v>1720.18</v>
       </c>
       <c r="AZ35" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA35" s="34">
-        <f t="shared" ref="BA35:BA66" si="21">AJ35/AO35</f>
+        <f t="shared" ref="BA35:BA66" si="23">AJ35/AO35</f>
         <v>0</v>
       </c>
       <c r="BB35" s="34">
-        <f t="shared" ref="BB35:BB66" si="22">AI35*24</f>
+        <f t="shared" ref="BB35:BB66" si="24">AI35*24</f>
         <v>0</v>
       </c>
       <c r="BC35" s="34">
@@ -7144,7 +7493,7 @@
         <v>0</v>
       </c>
       <c r="BD35" s="64" t="str">
-        <f t="shared" ref="BD35:BD66" si="23">IF(B35="Julia",AU35*AY35/24/60,"")</f>
+        <f t="shared" ref="BD35:BD66" si="25">IF(B35="Julia",AU35*AY35/24/60,"")</f>
         <v/>
       </c>
       <c r="BE35" s="61" t="str">
@@ -7153,10 +7502,10 @@
       </c>
       <c r="BF35" s="34">
         <f t="shared" si="20"/>
-        <v>12.668902500000002</v>
+        <v>12.901350000000001</v>
       </c>
       <c r="BG35" s="34" t="str">
-        <f t="shared" ref="BG35:BG66" si="24">IF(B35="Julia",AV35*AY35,"")</f>
+        <f t="shared" ref="BG35:BG66" si="26">IF(B35="Julia",AV35*AY35,"")</f>
         <v/>
       </c>
       <c r="BH35" s="49">
@@ -7169,10 +7518,10 @@
       </c>
       <c r="BJ35" s="51">
         <f t="shared" si="11"/>
-        <v>12.668902500000002</v>
+        <v>12.901350000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>56</v>
       </c>
@@ -7250,19 +7599,19 @@
         <v>0</v>
       </c>
       <c r="AY36" s="33">
-        <f t="shared" si="18"/>
-        <v>1694.662</v>
+        <f t="shared" si="22"/>
+        <v>1622</v>
       </c>
       <c r="AZ36" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA36" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB36" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC36" s="34" t="str">
@@ -7270,7 +7619,7 @@
         <v/>
       </c>
       <c r="BD36" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE36" s="61">
@@ -7279,10 +7628,10 @@
       </c>
       <c r="BF36" s="34">
         <f t="shared" si="20"/>
-        <v>12.709965</v>
+        <v>12.164999999999999</v>
       </c>
       <c r="BG36" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH36" s="49">
@@ -7295,10 +7644,10 @@
       </c>
       <c r="BJ36" s="51">
         <f t="shared" si="11"/>
-        <v>12.709965</v>
+        <v>12.164999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>57</v>
       </c>
@@ -7376,19 +7725,19 @@
         <v>0</v>
       </c>
       <c r="AY37" s="33">
-        <f t="shared" si="18"/>
-        <v>1701.567</v>
+        <f t="shared" si="22"/>
+        <v>1724.87</v>
       </c>
       <c r="AZ37" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA37" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB37" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC37" s="34" t="str">
@@ -7396,7 +7745,7 @@
         <v/>
       </c>
       <c r="BD37" s="64">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE37" s="61" t="str">
@@ -7408,7 +7757,7 @@
         <v/>
       </c>
       <c r="BG37" s="34">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH37" s="49">
@@ -7424,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>58</v>
       </c>
@@ -7502,19 +7851,19 @@
         <v>0</v>
       </c>
       <c r="AY38" s="20">
-        <f t="shared" si="18"/>
-        <v>1699.3500000000001</v>
+        <f t="shared" si="22"/>
+        <v>1743.9059999999999</v>
       </c>
       <c r="AZ38" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA38" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB38" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC38" s="21" t="str">
@@ -7522,7 +7871,7 @@
         <v/>
       </c>
       <c r="BD38" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE38" s="62" t="str">
@@ -7534,7 +7883,7 @@
         <v/>
       </c>
       <c r="BG38" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH38" s="49">
@@ -7550,7 +7899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>53</v>
       </c>
@@ -7628,19 +7977,19 @@
         <v>0</v>
       </c>
       <c r="AY39" s="16">
-        <f t="shared" si="18"/>
-        <v>1679.8</v>
+        <f t="shared" si="22"/>
+        <v>1712.62</v>
       </c>
       <c r="AZ39" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA39" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB39" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC39" s="17" t="str">
@@ -7648,7 +7997,7 @@
         <v/>
       </c>
       <c r="BD39" s="17" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE39" s="60">
@@ -7657,10 +8006,10 @@
       </c>
       <c r="BF39" s="17">
         <f t="shared" si="20"/>
-        <v>12.5985</v>
+        <v>12.84465</v>
       </c>
       <c r="BG39" s="17" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH39" s="48">
@@ -7673,10 +8022,10 @@
       </c>
       <c r="BJ39" s="53">
         <f t="shared" si="11"/>
-        <v>12.5985</v>
+        <v>12.84465</v>
       </c>
     </row>
-    <row r="40" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>54</v>
       </c>
@@ -7754,19 +8103,19 @@
         <v>0</v>
       </c>
       <c r="AY40" s="33">
-        <f t="shared" si="18"/>
-        <v>1680.607</v>
+        <f t="shared" si="22"/>
+        <v>1708.37</v>
       </c>
       <c r="AZ40" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA40" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB40" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC40" s="34">
@@ -7774,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="BD40" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE40" s="61" t="str">
@@ -7783,10 +8132,10 @@
       </c>
       <c r="BF40" s="34">
         <f t="shared" si="20"/>
-        <v>12.6045525</v>
+        <v>12.812774999999998</v>
       </c>
       <c r="BG40" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH40" s="49">
@@ -7799,10 +8148,10 @@
       </c>
       <c r="BJ40" s="51">
         <f t="shared" si="11"/>
-        <v>12.6045525</v>
+        <v>12.812774999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>55</v>
       </c>
@@ -7876,23 +8225,23 @@
         <v>0</v>
       </c>
       <c r="AX41" s="33">
-        <f t="shared" ref="AX41:AX72" si="25">AW35*24</f>
+        <f t="shared" ref="AX41:AX72" si="27">AW35*24</f>
         <v>0</v>
       </c>
       <c r="AY41" s="33">
-        <f t="shared" ref="AY41:AY72" si="26">AY35+SUM(AF41:AH41,AL41:AM41)-AN41</f>
-        <v>1674.1870000000001</v>
+        <f t="shared" ref="AY41:AY72" si="28">AY35+SUM(AF41:AH41,AL41:AM41)-AN41</f>
+        <v>1705.18</v>
       </c>
       <c r="AZ41" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA41" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB41" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC41" s="34">
@@ -7900,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="BD41" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE41" s="61" t="str">
@@ -7909,10 +8258,10 @@
       </c>
       <c r="BF41" s="34">
         <f t="shared" si="20"/>
-        <v>12.556402500000001</v>
+        <v>12.78885</v>
       </c>
       <c r="BG41" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH41" s="49">
@@ -7925,10 +8274,10 @@
       </c>
       <c r="BJ41" s="51">
         <f t="shared" si="11"/>
-        <v>12.556402500000001</v>
+        <v>12.78885</v>
       </c>
     </row>
-    <row r="42" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>56</v>
       </c>
@@ -8002,23 +8351,23 @@
         <v>0</v>
       </c>
       <c r="AX42" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY42" s="33">
-        <f t="shared" si="26"/>
-        <v>1679.662</v>
+        <f t="shared" si="28"/>
+        <v>1607</v>
       </c>
       <c r="AZ42" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA42" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB42" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC42" s="34" t="str">
@@ -8026,7 +8375,7 @@
         <v/>
       </c>
       <c r="BD42" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE42" s="61">
@@ -8035,10 +8384,10 @@
       </c>
       <c r="BF42" s="34">
         <f t="shared" si="20"/>
-        <v>12.597465</v>
+        <v>12.0525</v>
       </c>
       <c r="BG42" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH42" s="49">
@@ -8051,10 +8400,10 @@
       </c>
       <c r="BJ42" s="51">
         <f t="shared" si="11"/>
-        <v>12.597465</v>
+        <v>12.0525</v>
       </c>
     </row>
-    <row r="43" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>57</v>
       </c>
@@ -8128,23 +8477,23 @@
         <v>0</v>
       </c>
       <c r="AX43" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY43" s="33">
-        <f t="shared" si="26"/>
-        <v>1686.567</v>
+        <f t="shared" si="28"/>
+        <v>1709.87</v>
       </c>
       <c r="AZ43" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA43" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB43" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC43" s="34" t="str">
@@ -8152,7 +8501,7 @@
         <v/>
       </c>
       <c r="BD43" s="64">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE43" s="61" t="str">
@@ -8164,7 +8513,7 @@
         <v/>
       </c>
       <c r="BG43" s="34">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH43" s="49">
@@ -8180,7 +8529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>58</v>
       </c>
@@ -8254,23 +8603,23 @@
         <v>0</v>
       </c>
       <c r="AX44" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY44" s="20">
-        <f t="shared" si="26"/>
-        <v>1684.3500000000001</v>
+        <f t="shared" si="28"/>
+        <v>1728.9059999999999</v>
       </c>
       <c r="AZ44" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA44" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB44" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC44" s="21" t="str">
@@ -8278,7 +8627,7 @@
         <v/>
       </c>
       <c r="BD44" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE44" s="62" t="str">
@@ -8290,7 +8639,7 @@
         <v/>
       </c>
       <c r="BG44" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH44" s="50">
@@ -8306,7 +8655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>53</v>
       </c>
@@ -8380,23 +8729,23 @@
         <v>0</v>
       </c>
       <c r="AX45" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY45" s="16">
-        <f t="shared" si="26"/>
-        <v>1664.8</v>
+        <f t="shared" si="28"/>
+        <v>1697.62</v>
       </c>
       <c r="AZ45" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA45" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB45" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC45" s="17" t="str">
@@ -8404,7 +8753,7 @@
         <v/>
       </c>
       <c r="BD45" s="17" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE45" s="60">
@@ -8413,10 +8762,10 @@
       </c>
       <c r="BF45" s="17">
         <f t="shared" si="20"/>
-        <v>12.485999999999999</v>
+        <v>12.732149999999999</v>
       </c>
       <c r="BG45" s="17" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH45" s="49">
@@ -8429,10 +8778,10 @@
       </c>
       <c r="BJ45" s="51">
         <f t="shared" si="11"/>
-        <v>12.485999999999999</v>
+        <v>12.732149999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>54</v>
       </c>
@@ -8506,23 +8855,23 @@
         <v>0</v>
       </c>
       <c r="AX46" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY46" s="33">
-        <f t="shared" si="26"/>
-        <v>1665.607</v>
+        <f t="shared" si="28"/>
+        <v>1693.37</v>
       </c>
       <c r="AZ46" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA46" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB46" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC46" s="34">
@@ -8530,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="BD46" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE46" s="61" t="str">
@@ -8539,10 +8888,10 @@
       </c>
       <c r="BF46" s="34">
         <f t="shared" si="20"/>
-        <v>12.4920525</v>
+        <v>12.700275</v>
       </c>
       <c r="BG46" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH46" s="49">
@@ -8555,10 +8904,10 @@
       </c>
       <c r="BJ46" s="51">
         <f t="shared" si="11"/>
-        <v>12.4920525</v>
+        <v>12.700275</v>
       </c>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>55</v>
       </c>
@@ -8632,23 +8981,23 @@
         <v>0</v>
       </c>
       <c r="AX47" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY47" s="33">
-        <f t="shared" si="26"/>
-        <v>1659.1870000000001</v>
+        <f t="shared" si="28"/>
+        <v>1690.18</v>
       </c>
       <c r="AZ47" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA47" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB47" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC47" s="34">
@@ -8656,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="BD47" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE47" s="61" t="str">
@@ -8665,10 +9014,10 @@
       </c>
       <c r="BF47" s="34">
         <f t="shared" si="20"/>
-        <v>12.443902500000002</v>
+        <v>12.676349999999999</v>
       </c>
       <c r="BG47" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH47" s="49">
@@ -8681,10 +9030,10 @@
       </c>
       <c r="BJ47" s="51">
         <f t="shared" si="11"/>
-        <v>12.443902500000002</v>
+        <v>12.676349999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
@@ -8758,23 +9107,23 @@
         <v>0</v>
       </c>
       <c r="AX48" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY48" s="33">
-        <f t="shared" si="26"/>
-        <v>1664.662</v>
+        <f t="shared" si="28"/>
+        <v>1592</v>
       </c>
       <c r="AZ48" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA48" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB48" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC48" s="34" t="str">
@@ -8782,7 +9131,7 @@
         <v/>
       </c>
       <c r="BD48" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE48" s="61">
@@ -8791,10 +9140,10 @@
       </c>
       <c r="BF48" s="34">
         <f t="shared" si="20"/>
-        <v>12.484964999999999</v>
+        <v>11.94</v>
       </c>
       <c r="BG48" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH48" s="49">
@@ -8807,10 +9156,10 @@
       </c>
       <c r="BJ48" s="51">
         <f t="shared" si="11"/>
-        <v>12.484964999999999</v>
+        <v>11.94</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -8884,23 +9233,23 @@
         <v>0</v>
       </c>
       <c r="AX49" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY49" s="33">
-        <f t="shared" si="26"/>
-        <v>1671.567</v>
+        <f t="shared" si="28"/>
+        <v>1694.87</v>
       </c>
       <c r="AZ49" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA49" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB49" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC49" s="34" t="str">
@@ -8908,7 +9257,7 @@
         <v/>
       </c>
       <c r="BD49" s="64">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE49" s="61" t="str">
@@ -8920,7 +9269,7 @@
         <v/>
       </c>
       <c r="BG49" s="34">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH49" s="49">
@@ -8936,7 +9285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>58</v>
       </c>
@@ -9010,23 +9359,23 @@
         <v>0</v>
       </c>
       <c r="AX50" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY50" s="20">
-        <f t="shared" si="26"/>
-        <v>1669.3500000000001</v>
+        <f t="shared" si="28"/>
+        <v>1713.9059999999999</v>
       </c>
       <c r="AZ50" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA50" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB50" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC50" s="21" t="str">
@@ -9034,7 +9383,7 @@
         <v/>
       </c>
       <c r="BD50" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE50" s="62" t="str">
@@ -9046,7 +9395,7 @@
         <v/>
       </c>
       <c r="BG50" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH50" s="49">
@@ -9062,7 +9411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
@@ -9136,23 +9485,23 @@
         <v>0</v>
       </c>
       <c r="AX51" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY51" s="16">
-        <f t="shared" si="26"/>
-        <v>1649.8</v>
+        <f t="shared" si="28"/>
+        <v>1682.62</v>
       </c>
       <c r="AZ51" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA51" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB51" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC51" s="17" t="str">
@@ -9160,7 +9509,7 @@
         <v/>
       </c>
       <c r="BD51" s="17" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE51" s="60">
@@ -9169,10 +9518,10 @@
       </c>
       <c r="BF51" s="17">
         <f t="shared" si="20"/>
-        <v>12.3735</v>
+        <v>12.61965</v>
       </c>
       <c r="BG51" s="17" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH51" s="48">
@@ -9185,10 +9534,10 @@
       </c>
       <c r="BJ51" s="53">
         <f t="shared" si="11"/>
-        <v>12.3735</v>
+        <v>12.61965</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>54</v>
       </c>
@@ -9262,23 +9611,23 @@
         <v>0</v>
       </c>
       <c r="AX52" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY52" s="33">
-        <f t="shared" si="26"/>
-        <v>1650.607</v>
+        <f t="shared" si="28"/>
+        <v>1678.37</v>
       </c>
       <c r="AZ52" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA52" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB52" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC52" s="34">
@@ -9286,7 +9635,7 @@
         <v>0</v>
       </c>
       <c r="BD52" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE52" s="61" t="str">
@@ -9295,10 +9644,10 @@
       </c>
       <c r="BF52" s="34">
         <f t="shared" si="20"/>
-        <v>12.379552499999999</v>
+        <v>12.587774999999999</v>
       </c>
       <c r="BG52" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH52" s="49">
@@ -9311,10 +9660,10 @@
       </c>
       <c r="BJ52" s="51">
         <f t="shared" si="11"/>
-        <v>12.379552499999999</v>
+        <v>12.587774999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>55</v>
       </c>
@@ -9388,23 +9737,23 @@
         <v>0</v>
       </c>
       <c r="AX53" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY53" s="33">
-        <f t="shared" si="26"/>
-        <v>1644.1870000000001</v>
+        <f t="shared" si="28"/>
+        <v>1675.18</v>
       </c>
       <c r="AZ53" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA53" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB53" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC53" s="34">
@@ -9412,7 +9761,7 @@
         <v>0</v>
       </c>
       <c r="BD53" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE53" s="61" t="str">
@@ -9421,10 +9770,10 @@
       </c>
       <c r="BF53" s="34">
         <f t="shared" si="20"/>
-        <v>12.331402500000001</v>
+        <v>12.56385</v>
       </c>
       <c r="BG53" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH53" s="49">
@@ -9437,10 +9786,10 @@
       </c>
       <c r="BJ53" s="51">
         <f t="shared" si="11"/>
-        <v>12.331402500000001</v>
+        <v>12.56385</v>
       </c>
     </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>56</v>
       </c>
@@ -9514,23 +9863,23 @@
         <v>0</v>
       </c>
       <c r="AX54" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY54" s="33">
-        <f t="shared" si="26"/>
-        <v>1649.662</v>
+        <f t="shared" si="28"/>
+        <v>1577</v>
       </c>
       <c r="AZ54" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA54" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB54" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC54" s="34" t="str">
@@ -9538,7 +9887,7 @@
         <v/>
       </c>
       <c r="BD54" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE54" s="61">
@@ -9547,10 +9896,10 @@
       </c>
       <c r="BF54" s="34">
         <f t="shared" si="20"/>
-        <v>12.372465</v>
+        <v>11.827500000000001</v>
       </c>
       <c r="BG54" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH54" s="49">
@@ -9563,10 +9912,10 @@
       </c>
       <c r="BJ54" s="51">
         <f t="shared" si="11"/>
-        <v>12.372465</v>
+        <v>11.827500000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>57</v>
       </c>
@@ -9640,23 +9989,23 @@
         <v>0</v>
       </c>
       <c r="AX55" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY55" s="33">
-        <f t="shared" si="26"/>
-        <v>1656.567</v>
+        <f t="shared" si="28"/>
+        <v>1679.87</v>
       </c>
       <c r="AZ55" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA55" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB55" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC55" s="34" t="str">
@@ -9664,7 +10013,7 @@
         <v/>
       </c>
       <c r="BD55" s="64">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE55" s="61" t="str">
@@ -9676,7 +10025,7 @@
         <v/>
       </c>
       <c r="BG55" s="34">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH55" s="49">
@@ -9692,7 +10041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
@@ -9766,23 +10115,23 @@
         <v>0</v>
       </c>
       <c r="AX56" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY56" s="20">
-        <f t="shared" si="26"/>
-        <v>1654.3500000000001</v>
+        <f t="shared" si="28"/>
+        <v>1698.9059999999999</v>
       </c>
       <c r="AZ56" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA56" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB56" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC56" s="21" t="str">
@@ -9790,7 +10139,7 @@
         <v/>
       </c>
       <c r="BD56" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE56" s="62" t="str">
@@ -9802,7 +10151,7 @@
         <v/>
       </c>
       <c r="BG56" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH56" s="50">
@@ -9818,7 +10167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>53</v>
       </c>
@@ -9892,23 +10241,23 @@
         <v>0</v>
       </c>
       <c r="AX57" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY57" s="16">
-        <f t="shared" si="26"/>
-        <v>1634.8</v>
+        <f t="shared" si="28"/>
+        <v>1667.62</v>
       </c>
       <c r="AZ57" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA57" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB57" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC57" s="17" t="str">
@@ -9916,7 +10265,7 @@
         <v/>
       </c>
       <c r="BD57" s="17" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE57" s="60">
@@ -9925,10 +10274,10 @@
       </c>
       <c r="BF57" s="17">
         <f t="shared" si="20"/>
-        <v>12.260999999999999</v>
+        <v>12.507149999999999</v>
       </c>
       <c r="BG57" s="17" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH57" s="49">
@@ -9941,10 +10290,10 @@
       </c>
       <c r="BJ57" s="51">
         <f t="shared" si="11"/>
-        <v>12.260999999999999</v>
+        <v>12.507149999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>54</v>
       </c>
@@ -10018,23 +10367,23 @@
         <v>0</v>
       </c>
       <c r="AX58" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY58" s="33">
-        <f t="shared" si="26"/>
-        <v>1635.607</v>
+        <f t="shared" si="28"/>
+        <v>1663.37</v>
       </c>
       <c r="AZ58" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA58" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB58" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC58" s="34">
@@ -10042,7 +10391,7 @@
         <v>0</v>
       </c>
       <c r="BD58" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE58" s="61" t="str">
@@ -10051,10 +10400,10 @@
       </c>
       <c r="BF58" s="34">
         <f t="shared" si="20"/>
-        <v>12.2670525</v>
+        <v>12.475275</v>
       </c>
       <c r="BG58" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH58" s="49">
@@ -10067,10 +10416,10 @@
       </c>
       <c r="BJ58" s="51">
         <f t="shared" si="11"/>
-        <v>12.2670525</v>
+        <v>12.475275</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>55</v>
       </c>
@@ -10144,23 +10493,23 @@
         <v>0</v>
       </c>
       <c r="AX59" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY59" s="33">
-        <f t="shared" si="26"/>
-        <v>1629.1870000000001</v>
+        <f t="shared" si="28"/>
+        <v>1660.18</v>
       </c>
       <c r="AZ59" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA59" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB59" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC59" s="34">
@@ -10168,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="BD59" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE59" s="61" t="str">
@@ -10177,10 +10526,10 @@
       </c>
       <c r="BF59" s="34">
         <f t="shared" si="20"/>
-        <v>12.218902500000002</v>
+        <v>12.45135</v>
       </c>
       <c r="BG59" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH59" s="49">
@@ -10193,10 +10542,10 @@
       </c>
       <c r="BJ59" s="51">
         <f t="shared" si="11"/>
-        <v>12.218902500000002</v>
+        <v>12.45135</v>
       </c>
     </row>
-    <row r="60" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>56</v>
       </c>
@@ -10270,23 +10619,23 @@
         <v>0</v>
       </c>
       <c r="AX60" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY60" s="33">
-        <f t="shared" si="26"/>
-        <v>1634.662</v>
+        <f t="shared" si="28"/>
+        <v>1562</v>
       </c>
       <c r="AZ60" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA60" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB60" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC60" s="34" t="str">
@@ -10294,7 +10643,7 @@
         <v/>
       </c>
       <c r="BD60" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE60" s="61">
@@ -10303,10 +10652,10 @@
       </c>
       <c r="BF60" s="34">
         <f t="shared" si="20"/>
-        <v>12.259964999999999</v>
+        <v>11.715</v>
       </c>
       <c r="BG60" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH60" s="49">
@@ -10319,10 +10668,10 @@
       </c>
       <c r="BJ60" s="51">
         <f t="shared" si="11"/>
-        <v>12.259964999999999</v>
+        <v>11.715</v>
       </c>
     </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>57</v>
       </c>
@@ -10396,23 +10745,23 @@
         <v>0</v>
       </c>
       <c r="AX61" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY61" s="33">
-        <f t="shared" si="26"/>
-        <v>1641.567</v>
+        <f t="shared" si="28"/>
+        <v>1664.87</v>
       </c>
       <c r="AZ61" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA61" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB61" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC61" s="34" t="str">
@@ -10420,7 +10769,7 @@
         <v/>
       </c>
       <c r="BD61" s="64">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE61" s="61" t="str">
@@ -10432,7 +10781,7 @@
         <v/>
       </c>
       <c r="BG61" s="34">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH61" s="49">
@@ -10448,7 +10797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>58</v>
       </c>
@@ -10522,23 +10871,23 @@
         <v>0</v>
       </c>
       <c r="AX62" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY62" s="20">
-        <f t="shared" si="26"/>
-        <v>1639.3500000000001</v>
+        <f t="shared" si="28"/>
+        <v>1683.9059999999999</v>
       </c>
       <c r="AZ62" s="21" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA62" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB62" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC62" s="21" t="str">
@@ -10546,7 +10895,7 @@
         <v/>
       </c>
       <c r="BD62" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BE62" s="62" t="str">
@@ -10558,7 +10907,7 @@
         <v/>
       </c>
       <c r="BG62" s="21">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BH62" s="49">
@@ -10574,7 +10923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>53</v>
       </c>
@@ -10648,23 +10997,23 @@
         <v>0</v>
       </c>
       <c r="AX63" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY63" s="16">
-        <f t="shared" si="26"/>
-        <v>1619.8</v>
+        <f t="shared" si="28"/>
+        <v>1652.62</v>
       </c>
       <c r="AZ63" s="17" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA63" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB63" s="17">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC63" s="17" t="str">
@@ -10672,7 +11021,7 @@
         <v/>
       </c>
       <c r="BD63" s="17" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE63" s="60">
@@ -10681,10 +11030,10 @@
       </c>
       <c r="BF63" s="17">
         <f t="shared" si="20"/>
-        <v>12.148499999999999</v>
+        <v>12.394649999999999</v>
       </c>
       <c r="BG63" s="17" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH63" s="48">
@@ -10697,10 +11046,10 @@
       </c>
       <c r="BJ63" s="53">
         <f t="shared" si="11"/>
-        <v>12.148499999999999</v>
+        <v>12.394649999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>54</v>
       </c>
@@ -10774,23 +11123,23 @@
         <v>0</v>
       </c>
       <c r="AX64" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY64" s="33">
-        <f t="shared" si="26"/>
-        <v>1620.607</v>
+        <f t="shared" si="28"/>
+        <v>1648.37</v>
       </c>
       <c r="AZ64" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA64" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB64" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC64" s="34">
@@ -10798,7 +11147,7 @@
         <v>0</v>
       </c>
       <c r="BD64" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE64" s="61" t="str">
@@ -10807,10 +11156,10 @@
       </c>
       <c r="BF64" s="34">
         <f t="shared" si="20"/>
-        <v>12.154552499999999</v>
+        <v>12.362774999999999</v>
       </c>
       <c r="BG64" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH64" s="49">
@@ -10823,10 +11172,10 @@
       </c>
       <c r="BJ64" s="51">
         <f t="shared" si="11"/>
-        <v>12.154552499999999</v>
+        <v>12.362774999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>55</v>
       </c>
@@ -10900,23 +11249,23 @@
         <v>0</v>
       </c>
       <c r="AX65" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY65" s="33">
-        <f t="shared" si="26"/>
-        <v>1614.1870000000001</v>
+        <f t="shared" si="28"/>
+        <v>1645.18</v>
       </c>
       <c r="AZ65" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA65" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB65" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC65" s="34">
@@ -10924,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="BD65" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE65" s="61" t="str">
@@ -10933,10 +11282,10 @@
       </c>
       <c r="BF65" s="34">
         <f t="shared" si="20"/>
-        <v>12.106402500000002</v>
+        <v>12.338850000000001</v>
       </c>
       <c r="BG65" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH65" s="49">
@@ -10949,10 +11298,10 @@
       </c>
       <c r="BJ65" s="51">
         <f t="shared" si="11"/>
-        <v>12.106402500000002</v>
+        <v>12.338850000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>56</v>
       </c>
@@ -11026,23 +11375,23 @@
         <v>0</v>
       </c>
       <c r="AX66" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY66" s="33">
-        <f t="shared" si="26"/>
-        <v>1619.662</v>
+        <f t="shared" si="28"/>
+        <v>1547</v>
       </c>
       <c r="AZ66" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA66" s="34">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="BB66" s="34">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="BC66" s="34" t="str">
@@ -11050,7 +11399,7 @@
         <v/>
       </c>
       <c r="BD66" s="64" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BE66" s="61">
@@ -11059,10 +11408,10 @@
       </c>
       <c r="BF66" s="34">
         <f t="shared" si="20"/>
-        <v>12.147465</v>
+        <v>11.602499999999999</v>
       </c>
       <c r="BG66" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="BH66" s="49">
@@ -11075,10 +11424,10 @@
       </c>
       <c r="BJ66" s="51">
         <f t="shared" si="11"/>
-        <v>12.147465</v>
+        <v>11.602499999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>57</v>
       </c>
@@ -11152,23 +11501,23 @@
         <v>0</v>
       </c>
       <c r="AX67" s="33">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY67" s="33">
-        <f t="shared" si="26"/>
-        <v>1626.567</v>
+        <f t="shared" si="28"/>
+        <v>1649.87</v>
       </c>
       <c r="AZ67" s="34" t="e">
         <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="BA67" s="34">
-        <f t="shared" ref="BA67:BA80" si="27">AJ67/AO67</f>
+        <f t="shared" ref="BA67:BA80" si="29">AJ67/AO67</f>
         <v>0</v>
       </c>
       <c r="BB67" s="34">
-        <f t="shared" ref="BB67:BB80" si="28">AI67*24</f>
+        <f t="shared" ref="BB67:BB80" si="30">AI67*24</f>
         <v>0</v>
       </c>
       <c r="BC67" s="34" t="str">
@@ -11176,7 +11525,7 @@
         <v/>
       </c>
       <c r="BD67" s="64">
-        <f t="shared" ref="BD67:BD80" si="29">IF(B67="Julia",AU67*AY67/24/60,"")</f>
+        <f t="shared" ref="BD67:BD80" si="31">IF(B67="Julia",AU67*AY67/24/60,"")</f>
         <v>0</v>
       </c>
       <c r="BE67" s="61" t="str">
@@ -11188,7 +11537,7 @@
         <v/>
       </c>
       <c r="BG67" s="34">
-        <f t="shared" ref="BG67:BG80" si="30">IF(B67="Julia",AV67*AY67,"")</f>
+        <f t="shared" ref="BG67:BG80" si="32">IF(B67="Julia",AV67*AY67,"")</f>
         <v>0</v>
       </c>
       <c r="BH67" s="49">
@@ -11204,7 +11553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>58</v>
       </c>
@@ -11274,27 +11623,27 @@
       <c r="AU68" s="20"/>
       <c r="AV68" s="44"/>
       <c r="AW68" s="19">
-        <f t="shared" ref="AW68:AW80" si="31">AS68*I68*AY68/1000</f>
+        <f t="shared" ref="AW68:AW80" si="33">AS68*I68*AY68/1000</f>
         <v>0</v>
       </c>
       <c r="AX68" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AY68" s="20">
-        <f t="shared" si="26"/>
-        <v>1624.3500000000001</v>
+        <f t="shared" si="28"/>
+        <v>1668.9059999999999</v>
       </c>
       <c r="AZ68" s="21" t="e">
-        <f t="shared" ref="AZ68:AZ80" si="32">IF(ISBLANK(AJ68),NA(),IFERROR(AJ68/AY68,0))</f>
+        <f t="shared" ref="AZ68:AZ80" si="34">IF(ISBLANK(AJ68),NA(),IFERROR(AJ68/AY68,0))</f>
         <v>#N/A</v>
       </c>
       <c r="BA68" s="21">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BB68" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BC68" s="21" t="str">
@@ -11302,11 +11651,11 @@
         <v/>
       </c>
       <c r="BD68" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE68" s="62" t="str">
-        <f t="shared" ref="BE68:BE80" si="33">IF(B68="No MPC", AS68*I68*AY68/1000,"")</f>
+        <f t="shared" ref="BE68:BE80" si="35">IF(B68="No MPC", AS68*I68*AY68/1000,"")</f>
         <v/>
       </c>
       <c r="BF68" s="21" t="str">
@@ -11314,23 +11663,23 @@
         <v/>
       </c>
       <c r="BG68" s="21">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BH68" s="50">
-        <f t="shared" ref="BH68:BH80" si="34">IF(BC68&lt;&gt;"",BC68/0.000385,IF(BD68&lt;&gt;"",BD68/0.000385,BE68/0.000385))</f>
+        <f t="shared" ref="BH68:BH80" si="36">IF(BC68&lt;&gt;"",BC68/0.000385,IF(BD68&lt;&gt;"",BD68/0.000385,BE68/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BI68" s="70">
-        <f t="shared" ref="BI68:BI74" si="35">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
+        <f t="shared" ref="BI68:BI74" si="37">IF(BC68&lt;&gt;"",BC68,IF(BD68&lt;&gt;"",BD68,BE68))</f>
         <v>0</v>
       </c>
       <c r="BJ68" s="52">
-        <f t="shared" ref="BJ68:BJ80" si="36">IF(BF68&lt;&gt;"",BF68,BG68)</f>
+        <f t="shared" ref="BJ68:BJ80" si="38">IF(BF68&lt;&gt;"",BF68,BG68)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>53</v>
       </c>
@@ -11400,63 +11749,63 @@
       <c r="AU69" s="16"/>
       <c r="AV69" s="42"/>
       <c r="AW69" s="15">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX69" s="16">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AY69" s="16">
+        <f t="shared" si="28"/>
+        <v>1637.62</v>
+      </c>
+      <c r="AZ69" s="17" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA69" s="17">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB69" s="17">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC69" s="17" t="str">
+        <f t="shared" ref="BC69:BC80" si="39">IF(B69="Python",AT69*AY69/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BD69" s="17" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AX69" s="16">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AY69" s="16">
-        <f t="shared" si="26"/>
-        <v>1604.8</v>
-      </c>
-      <c r="AZ69" s="17" t="e">
-        <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA69" s="17">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB69" s="17">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC69" s="17" t="str">
-        <f t="shared" ref="BC69:BC80" si="37">IF(B69="Python",AT69*AY69/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BD69" s="17" t="str">
-        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE69" s="60">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BF69" s="17">
         <f t="shared" si="20"/>
-        <v>12.036</v>
+        <v>12.28215</v>
       </c>
       <c r="BG69" s="17" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BH69" s="49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI69" s="69">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BJ69" s="51">
-        <f t="shared" si="36"/>
-        <v>12.036</v>
+        <f t="shared" si="38"/>
+        <v>12.28215</v>
       </c>
     </row>
-    <row r="70" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>54</v>
       </c>
@@ -11526,63 +11875,63 @@
       <c r="AU70" s="33"/>
       <c r="AV70" s="43"/>
       <c r="AW70" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX70" s="33">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AY70" s="33">
+        <f t="shared" si="28"/>
+        <v>1633.37</v>
+      </c>
+      <c r="AZ70" s="34" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA70" s="34">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB70" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC70" s="34">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BD70" s="64" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AX70" s="33">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AY70" s="33">
-        <f t="shared" si="26"/>
-        <v>1605.607</v>
-      </c>
-      <c r="AZ70" s="34" t="e">
-        <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA70" s="34">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB70" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC70" s="34">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="BD70" s="64" t="str">
-        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE70" s="61" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BF70" s="34">
         <f t="shared" si="20"/>
-        <v>12.0420525</v>
+        <v>12.250274999999998</v>
       </c>
       <c r="BG70" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BH70" s="49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI70" s="69">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BJ70" s="51">
-        <f t="shared" si="36"/>
-        <v>12.0420525</v>
+        <f t="shared" si="38"/>
+        <v>12.250274999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>55</v>
       </c>
@@ -11652,63 +12001,63 @@
       <c r="AU71" s="33"/>
       <c r="AV71" s="43"/>
       <c r="AW71" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX71" s="33">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AY71" s="33">
+        <f t="shared" si="28"/>
+        <v>1630.18</v>
+      </c>
+      <c r="AZ71" s="34" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA71" s="34">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB71" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC71" s="34">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BD71" s="64" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AX71" s="33">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AY71" s="33">
-        <f t="shared" si="26"/>
-        <v>1599.1870000000001</v>
-      </c>
-      <c r="AZ71" s="34" t="e">
-        <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA71" s="34">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB71" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC71" s="34">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="BD71" s="64" t="str">
-        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE71" s="61" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BF71" s="34">
         <f t="shared" si="20"/>
-        <v>11.993902500000001</v>
+        <v>12.22635</v>
       </c>
       <c r="BG71" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BH71" s="49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI71" s="69">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BJ71" s="51">
-        <f t="shared" si="36"/>
-        <v>11.993902500000001</v>
+        <f t="shared" si="38"/>
+        <v>12.22635</v>
       </c>
     </row>
-    <row r="72" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>56</v>
       </c>
@@ -11778,63 +12127,63 @@
       <c r="AU72" s="33"/>
       <c r="AV72" s="43"/>
       <c r="AW72" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX72" s="33">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AY72" s="33">
+        <f t="shared" si="28"/>
+        <v>1532</v>
+      </c>
+      <c r="AZ72" s="34" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA72" s="34">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB72" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC72" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BD72" s="64" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AX72" s="33">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AY72" s="33">
-        <f t="shared" si="26"/>
-        <v>1604.662</v>
-      </c>
-      <c r="AZ72" s="34" t="e">
-        <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA72" s="34">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB72" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC72" s="34" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="BD72" s="64" t="str">
-        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE72" s="61">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BF72" s="34">
         <f t="shared" si="20"/>
-        <v>12.034965</v>
+        <v>11.49</v>
       </c>
       <c r="BG72" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="BH72" s="49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI72" s="69">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BJ72" s="51">
-        <f t="shared" si="36"/>
-        <v>12.034965</v>
+        <f t="shared" si="38"/>
+        <v>11.49</v>
       </c>
     </row>
-    <row r="73" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>57</v>
       </c>
@@ -11904,39 +12253,39 @@
       <c r="AU73" s="33"/>
       <c r="AV73" s="43"/>
       <c r="AW73" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX73" s="33">
+        <f t="shared" ref="AX73:AX80" si="40">AW67*24</f>
+        <v>0</v>
+      </c>
+      <c r="AY73" s="33">
+        <f t="shared" ref="AY73:AY80" si="41">AY67+SUM(AF73:AH73,AL73:AM73)-AN73</f>
+        <v>1634.87</v>
+      </c>
+      <c r="AZ73" s="34" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA73" s="34">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB73" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC73" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BD73" s="64">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AX73" s="33">
-        <f t="shared" ref="AX73:AX80" si="38">AW67*24</f>
-        <v>0</v>
-      </c>
-      <c r="AY73" s="33">
-        <f t="shared" ref="AY73:AY80" si="39">AY67+SUM(AF73:AH73,AL73:AM73)-AN73</f>
-        <v>1611.567</v>
-      </c>
-      <c r="AZ73" s="34" t="e">
-        <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA73" s="34">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB73" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC73" s="34" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="BD73" s="64">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
       <c r="BE73" s="61" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BF73" s="34" t="str">
@@ -11944,23 +12293,23 @@
         <v/>
       </c>
       <c r="BG73" s="34">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BH73" s="49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI73" s="69">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BJ73" s="51">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>58</v>
       </c>
@@ -12030,63 +12379,63 @@
       <c r="AU74" s="20"/>
       <c r="AV74" s="44"/>
       <c r="AW74" s="19">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX74" s="20">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AY74" s="20">
+        <f t="shared" si="41"/>
+        <v>1653.9059999999999</v>
+      </c>
+      <c r="AZ74" s="21" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA74" s="21">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB74" s="21">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC74" s="21" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BD74" s="21">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AX74" s="20">
+      <c r="BE74" s="62" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BF74" s="21" t="str">
+        <f t="shared" ref="BF74:BF80" si="42">IF(O74&lt;1.5, IF(B74&lt;&gt;"Julia",((3-O74)*AY74)/400, ""),0)</f>
+        <v/>
+      </c>
+      <c r="BG74" s="21">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="BH74" s="49">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="BI74" s="69">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BJ74" s="51">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AY74" s="20">
-        <f t="shared" si="39"/>
-        <v>1609.3500000000001</v>
-      </c>
-      <c r="AZ74" s="21" t="e">
-        <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA74" s="21">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB74" s="21">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC74" s="21" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="BD74" s="21">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="BE74" s="62" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="BF74" s="21" t="str">
-        <f t="shared" ref="BF74:BF80" si="40">IF(O74&lt;1.5, IF(B74&lt;&gt;"Julia",((3-O74)*AY74)/400, ""),0)</f>
-        <v/>
-      </c>
-      <c r="BG74" s="21">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="BH74" s="49">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="BI74" s="69">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BJ74" s="51">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="75" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>53</v>
       </c>
@@ -12156,60 +12505,60 @@
       <c r="AU75" s="4"/>
       <c r="AV75" s="25"/>
       <c r="AW75" s="15">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX75" s="16">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AY75" s="16">
+        <f t="shared" si="41"/>
+        <v>1622.62</v>
+      </c>
+      <c r="AZ75" s="17" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA75" s="17">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB75" s="17">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC75" s="17" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BD75" s="17" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AX75" s="16">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AY75" s="16">
-        <f t="shared" si="39"/>
-        <v>1589.8</v>
-      </c>
-      <c r="AZ75" s="17" t="e">
+        <v/>
+      </c>
+      <c r="BE75" s="60">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BF75" s="17">
+        <f t="shared" si="42"/>
+        <v>12.169649999999999</v>
+      </c>
+      <c r="BG75" s="17" t="str">
         <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA75" s="17">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB75" s="17">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC75" s="17" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="BD75" s="17" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="BE75" s="60">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BF75" s="17">
-        <f t="shared" si="40"/>
-        <v>11.923499999999999</v>
-      </c>
-      <c r="BG75" s="17" t="str">
-        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BH75" s="48">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI75" s="65"/>
       <c r="BJ75" s="53">
-        <f t="shared" si="36"/>
-        <v>11.923499999999999</v>
+        <f t="shared" si="38"/>
+        <v>12.169649999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>54</v>
       </c>
@@ -12279,60 +12628,60 @@
       <c r="AU76" s="30"/>
       <c r="AV76" s="2"/>
       <c r="AW76" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX76" s="33">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AY76" s="33">
+        <f t="shared" si="41"/>
+        <v>1618.37</v>
+      </c>
+      <c r="AZ76" s="34" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA76" s="34">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB76" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC76" s="34">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BD76" s="64" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AX76" s="33">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AY76" s="33">
-        <f t="shared" si="39"/>
-        <v>1590.607</v>
-      </c>
-      <c r="AZ76" s="34" t="e">
+        <v/>
+      </c>
+      <c r="BE76" s="61" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BF76" s="34">
+        <f t="shared" si="42"/>
+        <v>12.137775</v>
+      </c>
+      <c r="BG76" s="34" t="str">
         <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA76" s="34">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB76" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC76" s="34">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="BD76" s="64" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="BE76" s="61" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="BF76" s="34">
-        <f t="shared" si="40"/>
-        <v>11.9295525</v>
-      </c>
-      <c r="BG76" s="34" t="str">
-        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BH76" s="49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI76" s="66"/>
       <c r="BJ76" s="51">
-        <f t="shared" si="36"/>
-        <v>11.9295525</v>
+        <f t="shared" si="38"/>
+        <v>12.137775</v>
       </c>
     </row>
-    <row r="77" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>55</v>
       </c>
@@ -12402,60 +12751,60 @@
       <c r="AU77" s="33"/>
       <c r="AV77" s="43"/>
       <c r="AW77" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX77" s="33">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AY77" s="33">
+        <f t="shared" si="41"/>
+        <v>1615.18</v>
+      </c>
+      <c r="AZ77" s="34" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA77" s="34">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB77" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC77" s="34">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BD77" s="64" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AX77" s="33">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AY77" s="33">
-        <f t="shared" si="39"/>
-        <v>1584.1870000000001</v>
-      </c>
-      <c r="AZ77" s="34" t="e">
+        <v/>
+      </c>
+      <c r="BE77" s="61" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BF77" s="34">
+        <f t="shared" si="42"/>
+        <v>12.113849999999999</v>
+      </c>
+      <c r="BG77" s="34" t="str">
         <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA77" s="34">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB77" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC77" s="34">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="BD77" s="64" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="BE77" s="61" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="BF77" s="34">
-        <f t="shared" si="40"/>
-        <v>11.881402500000002</v>
-      </c>
-      <c r="BG77" s="34" t="str">
-        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BH77" s="49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI77" s="66"/>
       <c r="BJ77" s="51">
-        <f t="shared" si="36"/>
-        <v>11.881402500000002</v>
+        <f t="shared" si="38"/>
+        <v>12.113849999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>56</v>
       </c>
@@ -12525,60 +12874,60 @@
       <c r="AU78" s="33"/>
       <c r="AV78" s="43"/>
       <c r="AW78" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX78" s="33">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AY78" s="33">
+        <f t="shared" si="41"/>
+        <v>1517</v>
+      </c>
+      <c r="AZ78" s="34" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA78" s="34">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB78" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC78" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BD78" s="64" t="str">
         <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AX78" s="33">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AY78" s="33">
-        <f t="shared" si="39"/>
-        <v>1589.662</v>
-      </c>
-      <c r="AZ78" s="34" t="e">
+        <v/>
+      </c>
+      <c r="BE78" s="61">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BF78" s="34">
+        <f t="shared" si="42"/>
+        <v>11.3775</v>
+      </c>
+      <c r="BG78" s="34" t="str">
         <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA78" s="34">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB78" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC78" s="34" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="BD78" s="64" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="BE78" s="61">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BF78" s="34">
-        <f t="shared" si="40"/>
-        <v>11.922464999999999</v>
-      </c>
-      <c r="BG78" s="34" t="str">
-        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="BH78" s="49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI78" s="66"/>
       <c r="BJ78" s="51">
-        <f t="shared" si="36"/>
-        <v>11.922464999999999</v>
+        <f t="shared" si="38"/>
+        <v>11.3775</v>
       </c>
     </row>
-    <row r="79" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>57</v>
       </c>
@@ -12648,60 +12997,60 @@
       <c r="AU79" s="33"/>
       <c r="AV79" s="43"/>
       <c r="AW79" s="18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX79" s="33">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AY79" s="33">
+        <f t="shared" si="41"/>
+        <v>1619.87</v>
+      </c>
+      <c r="AZ79" s="34" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA79" s="34">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB79" s="34">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC79" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BD79" s="64">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AX79" s="33">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AY79" s="33">
-        <f t="shared" si="39"/>
-        <v>1596.567</v>
-      </c>
-      <c r="AZ79" s="34" t="e">
+      <c r="BE79" s="61" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BF79" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BG79" s="34">
         <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA79" s="34">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB79" s="34">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC79" s="34" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="BD79" s="64">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="BE79" s="61" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="BF79" s="34" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="BG79" s="34">
-        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BH79" s="49">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI79" s="66"/>
       <c r="BJ79" s="51">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>58</v>
       </c>
@@ -12771,56 +13120,56 @@
       <c r="AU80" s="20"/>
       <c r="AV80" s="44"/>
       <c r="AW80" s="19">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AX80" s="20">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AY80" s="20">
+        <f t="shared" si="41"/>
+        <v>1638.9059999999999</v>
+      </c>
+      <c r="AZ80" s="21" t="e">
+        <f t="shared" si="34"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BA80" s="21">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="BB80" s="21">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BC80" s="21" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BD80" s="21">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AX80" s="20">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AY80" s="20">
-        <f t="shared" si="39"/>
-        <v>1594.3500000000001</v>
-      </c>
-      <c r="AZ80" s="21" t="e">
+      <c r="BE80" s="62" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BF80" s="21" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BG80" s="21">
         <f t="shared" si="32"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BA80" s="21">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BB80" s="21">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="BC80" s="21" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="BD80" s="21">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="BE80" s="62" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="BF80" s="21" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="BG80" s="21">
-        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BH80" s="50">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BI80" s="67"/>
       <c r="BJ80" s="52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
@@ -12864,13 +13213,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A841E7D6-1405-4AC8-A599-0CE4601ECD66}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -13093,15 +13451,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -13121,6 +13470,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13135,14 +13492,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1742" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D644DC48-D77B-41C8-B743-96FF15BFA3F6}"/>
+  <xr:revisionPtr revIDLastSave="1778" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B97F46-6D67-4F11-B758-F20B70141FBE}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1178,10 +1178,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1927,18 +1923,18 @@
         <v/>
       </c>
       <c r="BE3" s="14" t="str">
-        <f>IF(B3="Julia",AV3*AZ3/24/60,"")</f>
+        <f t="shared" ref="BE3:BE34" si="1">IF(B3="Julia",AV3*AZ3/24/60,"")</f>
         <v/>
       </c>
       <c r="BF3" s="57">
-        <f>IF(B3="No MPC", AT3*J3*AZ3/1000,"")</f>
+        <f t="shared" ref="BF3:BF13" si="2">IF(B3="No MPC", AT3*J3*AZ3/1000,"")</f>
         <v>6.8242499999999996E-3</v>
       </c>
       <c r="BG3" s="14">
         <v>0</v>
       </c>
       <c r="BH3" s="14" t="str">
-        <f>IF(B3="Julia",AW3*AZ3,"")</f>
+        <f t="shared" ref="BH3:BH34" si="3">IF(B3="Julia",AW3*AZ3,"")</f>
         <v/>
       </c>
       <c r="BI3" s="45">
@@ -2097,11 +2093,11 @@
       <c r="AV4" s="30"/>
       <c r="AW4" s="40"/>
       <c r="AX4" s="15">
-        <f t="shared" ref="AX4:AX59" si="1">AT4*J4*AZ4/1000</f>
+        <f t="shared" ref="AX4:AX59" si="4">AT4*J4*AZ4/1000</f>
         <v>6.2681999999999989E-3</v>
       </c>
       <c r="AY4" s="30">
-        <f t="shared" ref="AY4:AY8" si="2">AX4*24</f>
+        <f t="shared" ref="AY4:AY8" si="5">AX4*24</f>
         <v>0.15043679999999998</v>
       </c>
       <c r="AZ4" s="30">
@@ -2109,46 +2105,46 @@
         <v>1685</v>
       </c>
       <c r="BA4" s="31">
-        <f t="shared" ref="BA4:BA59" si="3">IF(ISBLANK(AK4),NA(),IFERROR(AK4/AZ4,0))</f>
+        <f t="shared" ref="BA4:BA59" si="6">IF(ISBLANK(AK4),NA(),IFERROR(AK4/AZ4,0))</f>
         <v>0</v>
       </c>
       <c r="BB4" s="31">
-        <f t="shared" ref="BB4:BB32" si="4">AK4/AP4</f>
+        <f t="shared" ref="BB4:BB32" si="7">AK4/AP4</f>
         <v>0</v>
       </c>
       <c r="BC4" s="31">
-        <f t="shared" ref="BC4:BC32" si="5">AJ4*24</f>
+        <f t="shared" ref="BC4:BC32" si="8">AJ4*24</f>
         <v>0.12637499999999999</v>
       </c>
       <c r="BD4" s="31">
-        <f>IF(B4="Python",AU4*AZ4/24/60,"")</f>
+        <f t="shared" ref="BD4:BD35" si="9">IF(B4="Python",AU4*AZ4/24/60,"")</f>
         <v>5.2656249999999995E-3</v>
       </c>
       <c r="BE4" s="61" t="str">
-        <f>IF(B4="Julia",AV4*AZ4/24/60,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="BF4" s="58" t="str">
-        <f>IF(B4="No MPC", AT4*J4*AZ4/1000,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BG4" s="31">
         <v>0</v>
       </c>
       <c r="BH4" s="31" t="str">
-        <f>IF(B4="Julia",AW4*AZ4,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI4" s="46">
-        <f t="shared" ref="BI4:BI59" si="6">IF(BD4&lt;&gt;"",BD4/0.000385,IF(BE4&lt;&gt;"",BE4/0.000385,BF4/0.000385))</f>
+        <f t="shared" ref="BI4:BI59" si="10">IF(BD4&lt;&gt;"",BD4/0.000385,IF(BE4&lt;&gt;"",BE4/0.000385,BF4/0.000385))</f>
         <v>13.676948051948051</v>
       </c>
       <c r="BJ4" s="66">
-        <f t="shared" ref="BJ4:BJ59" si="7">IF(BD4&lt;&gt;"",BD4,IF(BE4&lt;&gt;"",BE4,BF4))</f>
+        <f t="shared" ref="BJ4:BJ59" si="11">IF(BD4&lt;&gt;"",BD4,IF(BE4&lt;&gt;"",BE4,BF4))</f>
         <v>5.2656249999999995E-3</v>
       </c>
       <c r="BK4" s="48">
-        <f t="shared" ref="BK4:BK59" si="8">IF(BG4&lt;&gt;"",BG4,BH4)</f>
+        <f t="shared" ref="BK4:BK59" si="12">IF(BG4&lt;&gt;"",BG4,BH4)</f>
         <v>0</v>
       </c>
     </row>
@@ -2295,11 +2291,11 @@
       <c r="AV5" s="30"/>
       <c r="AW5" s="40"/>
       <c r="AX5" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>6.7231499999999998E-3</v>
       </c>
       <c r="AY5" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.16135559999999999</v>
       </c>
       <c r="AZ5" s="30">
@@ -2307,46 +2303,46 @@
         <v>1685</v>
       </c>
       <c r="BA5" s="31">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB5" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC5" s="31">
+        <f t="shared" si="8"/>
+        <v>0.12637499999999999</v>
+      </c>
+      <c r="BD5" s="31">
+        <f t="shared" si="9"/>
+        <v>5.2656249999999995E-3</v>
+      </c>
+      <c r="BE5" s="61" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="BF5" s="58" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="BG5" s="31">
+        <v>0</v>
+      </c>
+      <c r="BH5" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BB5" s="31">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BC5" s="31">
-        <f t="shared" si="5"/>
-        <v>0.12637499999999999</v>
-      </c>
-      <c r="BD5" s="31">
-        <f>IF(B5="Python",AU5*AZ5/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BI5" s="46">
+        <f t="shared" si="10"/>
+        <v>13.676948051948051</v>
+      </c>
+      <c r="BJ5" s="66">
+        <f t="shared" si="11"/>
         <v>5.2656249999999995E-3</v>
       </c>
-      <c r="BE5" s="61" t="str">
-        <f>IF(B5="Julia",AV5*AZ5/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF5" s="58" t="str">
-        <f>IF(B5="No MPC", AT5*J5*AZ5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG5" s="31">
-        <v>0</v>
-      </c>
-      <c r="BH5" s="31" t="str">
-        <f>IF(B5="Julia",AW5*AZ5,"")</f>
-        <v/>
-      </c>
-      <c r="BI5" s="46">
-        <f t="shared" si="6"/>
-        <v>13.676948051948051</v>
-      </c>
-      <c r="BJ5" s="66">
-        <f t="shared" si="7"/>
-        <v>5.2656249999999995E-3</v>
-      </c>
       <c r="BK5" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -2491,11 +2487,11 @@
       <c r="AV6" s="30"/>
       <c r="AW6" s="40"/>
       <c r="AX6" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>8.1385499999999996E-3</v>
       </c>
       <c r="AY6" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.19532519999999998</v>
       </c>
       <c r="AZ6" s="30">
@@ -2503,46 +2499,46 @@
         <v>1685</v>
       </c>
       <c r="BA6" s="31">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB6" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BC6" s="31">
+        <f t="shared" si="8"/>
+        <v>0.19532519999999998</v>
+      </c>
+      <c r="BD6" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE6" s="61" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="BF6" s="58">
+        <f t="shared" si="2"/>
+        <v>8.1385499999999996E-3</v>
+      </c>
+      <c r="BG6" s="31">
+        <v>0</v>
+      </c>
+      <c r="BH6" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BB6" s="31">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BC6" s="31">
-        <f t="shared" si="5"/>
-        <v>0.19532519999999998</v>
-      </c>
-      <c r="BD6" s="31" t="str">
-        <f>IF(B6="Python",AU6*AZ6/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE6" s="61" t="str">
-        <f>IF(B6="Julia",AV6*AZ6/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF6" s="58">
-        <f>IF(B6="No MPC", AT6*J6*AZ6/1000,"")</f>
+        <v/>
+      </c>
+      <c r="BI6" s="46">
+        <f t="shared" si="10"/>
+        <v>21.13909090909091</v>
+      </c>
+      <c r="BJ6" s="66">
+        <f t="shared" si="11"/>
         <v>8.1385499999999996E-3</v>
       </c>
-      <c r="BG6" s="31">
-        <v>0</v>
-      </c>
-      <c r="BH6" s="31" t="str">
-        <f>IF(B6="Julia",AW6*AZ6,"")</f>
-        <v/>
-      </c>
-      <c r="BI6" s="46">
-        <f t="shared" si="6"/>
-        <v>21.13909090909091</v>
-      </c>
-      <c r="BJ6" s="66">
-        <f t="shared" si="7"/>
-        <v>8.1385499999999996E-3</v>
-      </c>
       <c r="BK6" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -2691,11 +2687,11 @@
         <v>0</v>
       </c>
       <c r="AX7" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>6.1165499999999992E-3</v>
       </c>
       <c r="AY7" s="30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.14679719999999999</v>
       </c>
       <c r="AZ7" s="30">
@@ -2703,27 +2699,27 @@
         <v>1685</v>
       </c>
       <c r="BA7" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB7" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BC7" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.14679719999999971</v>
       </c>
       <c r="BD7" s="31" t="str">
-        <f>IF(B7="Python",AU7*AZ7/24/60,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="BE7" s="60">
-        <f>IF(B7="Julia",AV7*AZ7/24/60,"")</f>
+        <f t="shared" si="1"/>
         <v>6.116549999999988E-3</v>
       </c>
       <c r="BF7" s="60" t="str">
-        <f>IF(B7="No MPC", AT7*J7*AZ7/1000,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BG7" s="31" t="str">
@@ -2731,19 +2727,19 @@
         <v/>
       </c>
       <c r="BH7" s="31">
-        <f>IF(B7="Julia",AW7*AZ7,"")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BI7" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>15.887142857142827</v>
       </c>
       <c r="BJ7" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>6.116549999999988E-3</v>
       </c>
       <c r="BK7" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -2892,11 +2888,11 @@
         <v>0</v>
       </c>
       <c r="AX8" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>6.5209499999999993E-3</v>
       </c>
       <c r="AY8" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.1565028</v>
       </c>
       <c r="AZ8" s="17">
@@ -2904,27 +2900,27 @@
         <v>1685</v>
       </c>
       <c r="BA8" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="BB8" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="BC8" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.15650279999999972</v>
       </c>
       <c r="BD8" s="18" t="str">
-        <f>IF(B8="Python",AU8*AZ8/24/60,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="BE8" s="60">
-        <f>IF(B8="Julia",AV8*AZ8/24/60,"")</f>
+        <f t="shared" si="1"/>
         <v>6.520949999999988E-3</v>
       </c>
       <c r="BF8" s="59" t="str">
-        <f>IF(B8="No MPC", AT8*J8*AZ8/1000,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BG8" s="18" t="str">
@@ -2932,19 +2928,19 @@
         <v/>
       </c>
       <c r="BH8" s="18">
-        <f>IF(B8="Julia",AW8*AZ8,"")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BI8" s="47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>16.937532467532439</v>
       </c>
       <c r="BJ8" s="67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>6.520949999999988E-3</v>
       </c>
       <c r="BK8" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -3062,11 +3058,11 @@
         <v>0</v>
       </c>
       <c r="AM9" s="13">
-        <f t="shared" ref="AM9:AM20" si="9">AK9-AK3</f>
+        <f t="shared" ref="AM9:AM20" si="13">AK9-AK3</f>
         <v>8</v>
       </c>
       <c r="AN9" s="13">
-        <f t="shared" ref="AN9:AN20" si="10">AL9-AL3</f>
+        <f t="shared" ref="AN9:AN20" si="14">AL9-AL3</f>
         <v>0</v>
       </c>
       <c r="AO9" s="42">
@@ -3091,15 +3087,15 @@
       <c r="AV9" s="13"/>
       <c r="AW9" s="39"/>
       <c r="AX9" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>9.8469503999999985E-3</v>
       </c>
       <c r="AY9" s="13">
-        <f t="shared" ref="AY9:AY23" si="11">AX3*24</f>
+        <f t="shared" ref="AY9:AY23" si="15">AX3*24</f>
         <v>0.16378199999999998</v>
       </c>
       <c r="AZ9" s="13">
-        <f>AP9+SUM(AG9:AI9,AK9:AL9)-((AO9+1)*D9)</f>
+        <f t="shared" ref="AZ9:AZ40" si="16">AP9+SUM(AG9:AI9,AK9:AL9)-((AO9+1)*D9)</f>
         <v>1709.54</v>
       </c>
       <c r="BA9" s="14">
@@ -3107,23 +3103,23 @@
         <v>4.6796214186272328E-3</v>
       </c>
       <c r="BB9" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>4.7058823529411761E-3</v>
       </c>
       <c r="BC9" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.23439144959999997</v>
       </c>
       <c r="BD9" s="14" t="str">
-        <f>IF(B9="Python",AU9*AZ9/24/60,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="BE9" s="14" t="str">
-        <f>IF(B9="Julia",AV9*AZ9/24/60,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="BF9" s="57">
-        <f>IF(B9="No MPC", AT9*J9*AZ9/1000,"")</f>
+        <f t="shared" si="2"/>
         <v>9.8469503999999985E-3</v>
       </c>
       <c r="BG9" s="14">
@@ -3131,19 +3127,19 @@
         <v>17.4800465</v>
       </c>
       <c r="BH9" s="14" t="str">
-        <f>IF(B9="Julia",AW9*AZ9,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI9" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>25.576494545454544</v>
       </c>
       <c r="BJ9" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>9.8469503999999985E-3</v>
       </c>
       <c r="BK9" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>17.4800465</v>
       </c>
     </row>
@@ -3261,11 +3257,11 @@
         <v>0</v>
       </c>
       <c r="AM10" s="71">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
       <c r="AN10" s="30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AO10" s="43">
@@ -3292,39 +3288,39 @@
       <c r="AV10" s="30"/>
       <c r="AW10" s="40"/>
       <c r="AX10" s="15">
+        <f t="shared" si="4"/>
+        <v>8.1587988000000004E-3</v>
+      </c>
+      <c r="AY10" s="30">
+        <f t="shared" si="15"/>
+        <v>0.15043679999999998</v>
+      </c>
+      <c r="AZ10" s="30">
+        <f t="shared" si="16"/>
+        <v>1710.44</v>
+      </c>
+      <c r="BA10" s="31">
+        <f t="shared" si="6"/>
+        <v>3.5078693201749255E-3</v>
+      </c>
+      <c r="BB10" s="31">
+        <f t="shared" si="7"/>
+        <v>3.5294117647058825E-3</v>
+      </c>
+      <c r="BC10" s="31">
+        <f t="shared" si="8"/>
+        <v>0.21664160173748431</v>
+      </c>
+      <c r="BD10" s="31">
+        <f t="shared" si="9"/>
+        <v>9.1012272090343783E-3</v>
+      </c>
+      <c r="BE10" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>8.1587988000000004E-3</v>
-      </c>
-      <c r="AY10" s="30">
-        <f t="shared" si="11"/>
-        <v>0.15043679999999998</v>
-      </c>
-      <c r="AZ10" s="30">
-        <f>AP10+SUM(AG10:AI10,AK10:AL10)-((AO10+1)*D10)</f>
-        <v>1710.44</v>
-      </c>
-      <c r="BA10" s="31">
-        <f t="shared" si="3"/>
-        <v>3.5078693201749255E-3</v>
-      </c>
-      <c r="BB10" s="31">
-        <f t="shared" si="4"/>
-        <v>3.5294117647058825E-3</v>
-      </c>
-      <c r="BC10" s="31">
-        <f t="shared" si="5"/>
-        <v>0.21664160173748431</v>
-      </c>
-      <c r="BD10" s="31">
-        <f>IF(B10="Python",AU10*AZ10/24/60,"")</f>
-        <v>9.1012272090343783E-3</v>
-      </c>
-      <c r="BE10" s="61" t="str">
-        <f>IF(B10="Julia",AV10*AZ10/24/60,"")</f>
         <v/>
       </c>
       <c r="BF10" s="58" t="str">
-        <f>IF(B10="No MPC", AT10*J10*AZ10/1000,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BG10" s="31">
@@ -3332,19 +3328,19 @@
         <v>17.745815000000004</v>
       </c>
       <c r="BH10" s="31" t="str">
-        <f>IF(B10="Julia",AW10*AZ10,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI10" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>23.639551192297088</v>
       </c>
       <c r="BJ10" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>9.1012272090343783E-3</v>
       </c>
       <c r="BK10" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>17.745815000000004</v>
       </c>
     </row>
@@ -3462,11 +3458,11 @@
         <v>0</v>
       </c>
       <c r="AM11" s="71">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
       <c r="AN11" s="30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AO11" s="43">
@@ -3493,39 +3489,39 @@
       <c r="AV11" s="30"/>
       <c r="AW11" s="40"/>
       <c r="AX11" s="15">
+        <f t="shared" si="4"/>
+        <v>8.1339471000000003E-3</v>
+      </c>
+      <c r="AY11" s="30">
+        <f t="shared" si="15"/>
+        <v>0.16135559999999999</v>
+      </c>
+      <c r="AZ11" s="30">
+        <f t="shared" si="16"/>
+        <v>1705.23</v>
+      </c>
+      <c r="BA11" s="31">
+        <f t="shared" si="6"/>
+        <v>3.5185869354867087E-3</v>
+      </c>
+      <c r="BB11" s="31">
+        <f t="shared" si="7"/>
+        <v>3.5294117647058825E-3</v>
+      </c>
+      <c r="BC11" s="31">
+        <f t="shared" si="8"/>
+        <v>0.20907783531262189</v>
+      </c>
+      <c r="BD11" s="31">
+        <f t="shared" si="9"/>
+        <v>8.7836908913961585E-3</v>
+      </c>
+      <c r="BE11" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>8.1339471000000003E-3</v>
-      </c>
-      <c r="AY11" s="30">
-        <f t="shared" si="11"/>
-        <v>0.16135559999999999</v>
-      </c>
-      <c r="AZ11" s="30">
-        <f>AP11+SUM(AG11:AI11,AK11:AL11)-((AO11+1)*D11)</f>
-        <v>1705.23</v>
-      </c>
-      <c r="BA11" s="31">
-        <f t="shared" si="3"/>
-        <v>3.5185869354867087E-3</v>
-      </c>
-      <c r="BB11" s="31">
-        <f t="shared" si="4"/>
-        <v>3.5294117647058825E-3</v>
-      </c>
-      <c r="BC11" s="31">
-        <f t="shared" si="5"/>
-        <v>0.20907783531262189</v>
-      </c>
-      <c r="BD11" s="31">
-        <f>IF(B11="Python",AU11*AZ11/24/60,"")</f>
-        <v>8.7836908913961585E-3</v>
-      </c>
-      <c r="BE11" s="61" t="str">
-        <f>IF(B11="Julia",AV11*AZ11/24/60,"")</f>
         <v/>
       </c>
       <c r="BF11" s="58" t="str">
-        <f>IF(B11="No MPC", AT11*J11*AZ11/1000,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BG11" s="31">
@@ -3533,19 +3529,19 @@
         <v>17.393346000000001</v>
       </c>
       <c r="BH11" s="31" t="str">
-        <f>IF(B11="Julia",AW11*AZ11,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI11" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>22.814781536093918</v>
       </c>
       <c r="BJ11" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>8.7836908913961585E-3</v>
       </c>
       <c r="BK11" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>17.393346000000001</v>
       </c>
     </row>
@@ -3663,11 +3659,11 @@
         <v>0</v>
       </c>
       <c r="AM12" s="71">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="AN12" s="30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AO12" s="43">
@@ -3692,39 +3688,39 @@
       <c r="AV12" s="30"/>
       <c r="AW12" s="40"/>
       <c r="AX12" s="15">
+        <f t="shared" si="4"/>
+        <v>1.26191358E-2</v>
+      </c>
+      <c r="AY12" s="30">
+        <f t="shared" si="15"/>
+        <v>0.19532519999999998</v>
+      </c>
+      <c r="AZ12" s="30">
+        <f t="shared" si="16"/>
+        <v>1709.91</v>
+      </c>
+      <c r="BA12" s="31">
+        <f t="shared" si="6"/>
+        <v>5.8482610195858256E-3</v>
+      </c>
+      <c r="BB12" s="31">
+        <f t="shared" si="7"/>
+        <v>5.8823529411764705E-3</v>
+      </c>
+      <c r="BC12" s="31">
+        <f t="shared" si="8"/>
+        <v>0.30037957920000002</v>
+      </c>
+      <c r="BD12" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE12" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>1.26191358E-2</v>
-      </c>
-      <c r="AY12" s="30">
-        <f t="shared" si="11"/>
-        <v>0.19532519999999998</v>
-      </c>
-      <c r="AZ12" s="30">
-        <f>AP12+SUM(AG12:AI12,AK12:AL12)-((AO12+1)*D12)</f>
-        <v>1709.91</v>
-      </c>
-      <c r="BA12" s="31">
-        <f t="shared" si="3"/>
-        <v>5.8482610195858256E-3</v>
-      </c>
-      <c r="BB12" s="31">
-        <f t="shared" si="4"/>
-        <v>5.8823529411764705E-3</v>
-      </c>
-      <c r="BC12" s="31">
-        <f t="shared" si="5"/>
-        <v>0.30037957920000002</v>
-      </c>
-      <c r="BD12" s="31" t="str">
-        <f>IF(B12="Python",AU12*AZ12/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE12" s="61" t="str">
-        <f>IF(B12="Julia",AV12*AZ12/24/60,"")</f>
         <v/>
       </c>
       <c r="BF12" s="58">
-        <f>IF(B12="No MPC", AT12*J12*AZ12/1000,"")</f>
+        <f t="shared" si="2"/>
         <v>1.26191358E-2</v>
       </c>
       <c r="BG12" s="31">
@@ -3732,19 +3728,19 @@
         <v>21.373875000000002</v>
       </c>
       <c r="BH12" s="31" t="str">
-        <f>IF(B12="Julia",AW12*AZ12,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI12" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>32.776976103896104</v>
       </c>
       <c r="BJ12" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.26191358E-2</v>
       </c>
       <c r="BK12" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>21.373875000000002</v>
       </c>
     </row>
@@ -3862,11 +3858,11 @@
         <v>0</v>
       </c>
       <c r="AM13" s="71">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="AN13" s="30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AO13" s="43">
@@ -3895,39 +3891,39 @@
         <v>7.5395846178023399E-3</v>
       </c>
       <c r="AX13" s="15">
+        <f t="shared" si="4"/>
+        <v>7.797736799999999E-3</v>
+      </c>
+      <c r="AY13" s="30">
+        <f t="shared" si="15"/>
+        <v>0.14679719999999999</v>
+      </c>
+      <c r="AZ13" s="30">
+        <f t="shared" si="16"/>
+        <v>1710.03</v>
+      </c>
+      <c r="BA13" s="31">
+        <f t="shared" si="6"/>
+        <v>4.0934954357525893E-3</v>
+      </c>
+      <c r="BB13" s="31">
+        <f t="shared" si="7"/>
+        <v>4.1176470588235297E-3</v>
+      </c>
+      <c r="BC13" s="31">
+        <f t="shared" si="8"/>
+        <v>0.36564552587435944</v>
+      </c>
+      <c r="BD13" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE13" s="61">
         <f t="shared" si="1"/>
-        <v>7.797736799999999E-3</v>
-      </c>
-      <c r="AY13" s="30">
-        <f t="shared" si="11"/>
-        <v>0.14679719999999999</v>
-      </c>
-      <c r="AZ13" s="30">
-        <f>AP13+SUM(AG13:AI13,AK13:AL13)-((AO13+1)*D13)</f>
-        <v>1710.03</v>
-      </c>
-      <c r="BA13" s="31">
-        <f t="shared" si="3"/>
-        <v>4.0934954357525893E-3</v>
-      </c>
-      <c r="BB13" s="31">
-        <f t="shared" si="4"/>
-        <v>4.1176470588235297E-3</v>
-      </c>
-      <c r="BC13" s="31">
-        <f t="shared" si="5"/>
-        <v>0.36564552587435944</v>
-      </c>
-      <c r="BD13" s="31" t="str">
-        <f>IF(B13="Python",AU13*AZ13/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE13" s="61">
-        <f>IF(B13="Julia",AV13*AZ13/24/60,"")</f>
         <v>1.5360990534044473E-2</v>
       </c>
       <c r="BF13" s="58" t="str">
-        <f>IF(B13="No MPC", AT13*J13*AZ13/1000,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="BG13" s="68">
@@ -3935,19 +3931,19 @@
         <v>14.022246000000001</v>
       </c>
       <c r="BH13" s="31">
-        <f>IF(B13="Julia",AW13*AZ13,"")</f>
+        <f t="shared" si="3"/>
         <v>12.892915883980535</v>
       </c>
       <c r="BI13" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>39.89867671180383</v>
       </c>
       <c r="BJ13" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.5360990534044473E-2</v>
       </c>
       <c r="BK13" s="70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>14.022246000000001</v>
       </c>
     </row>
@@ -4065,11 +4061,11 @@
         <v>0</v>
       </c>
       <c r="AM14" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
       <c r="AN14" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AO14" s="44">
@@ -4100,35 +4096,35 @@
         <v>1.035E-2</v>
       </c>
       <c r="AX14" s="16">
+        <f t="shared" si="4"/>
+        <v>8.3187647999999996E-3</v>
+      </c>
+      <c r="AY14" s="17">
+        <f t="shared" si="15"/>
+        <v>0.1565028</v>
+      </c>
+      <c r="AZ14" s="17">
+        <f t="shared" si="16"/>
+        <v>1711.68</v>
+      </c>
+      <c r="BA14" s="18">
+        <f t="shared" si="6"/>
+        <v>4.6737707982800521E-3</v>
+      </c>
+      <c r="BB14" s="18">
+        <f t="shared" si="7"/>
+        <v>4.7058823529411761E-3</v>
+      </c>
+      <c r="BC14" s="18">
+        <f t="shared" si="8"/>
+        <v>0.19801739520000003</v>
+      </c>
+      <c r="BD14" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE14" s="18">
         <f t="shared" si="1"/>
-        <v>8.3187647999999996E-3</v>
-      </c>
-      <c r="AY14" s="17">
-        <f t="shared" si="11"/>
-        <v>0.1565028</v>
-      </c>
-      <c r="AZ14" s="17">
-        <f>AP14+SUM(AG14:AI14,AK14:AL14)-((AO14+1)*D14)</f>
-        <v>1711.68</v>
-      </c>
-      <c r="BA14" s="18">
-        <f t="shared" si="3"/>
-        <v>4.6737707982800521E-3</v>
-      </c>
-      <c r="BB14" s="18">
-        <f t="shared" si="4"/>
-        <v>4.7058823529411761E-3</v>
-      </c>
-      <c r="BC14" s="18">
-        <f t="shared" si="5"/>
-        <v>0.19801739520000003</v>
-      </c>
-      <c r="BD14" s="18" t="str">
-        <f>IF(B14="Python",AU14*AZ14/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE14" s="18">
-        <f>IF(B14="Julia",AV14*AZ14/24/60,"")</f>
         <v>8.3187647999999996E-3</v>
       </c>
       <c r="BF14" s="59">
@@ -4140,19 +4136,19 @@
         <v>17.715888</v>
       </c>
       <c r="BH14" s="18">
-        <f>IF(B14="Julia",AW14*AZ14,"")</f>
+        <f t="shared" si="3"/>
         <v>17.715888</v>
       </c>
       <c r="BI14" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>21.607181298701299</v>
       </c>
       <c r="BJ14" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>8.3187647999999996E-3</v>
       </c>
       <c r="BK14" s="70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>17.715888</v>
       </c>
     </row>
@@ -4274,7 +4270,7 @@
         <v>14.3</v>
       </c>
       <c r="AN15" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>19.55</v>
       </c>
       <c r="AO15" s="42">
@@ -4299,39 +4295,39 @@
       <c r="AV15" s="13"/>
       <c r="AW15" s="39"/>
       <c r="AX15" s="12">
+        <f t="shared" si="4"/>
+        <v>1.2285640799999999E-2</v>
+      </c>
+      <c r="AY15" s="13">
+        <f t="shared" si="15"/>
+        <v>0.23632680959999997</v>
+      </c>
+      <c r="AZ15" s="13">
+        <f t="shared" si="16"/>
+        <v>1735.26</v>
+      </c>
+      <c r="BA15" s="14">
+        <f t="shared" si="6"/>
+        <v>1.2851100123324459E-2</v>
+      </c>
+      <c r="BB15" s="14">
+        <f t="shared" si="7"/>
+        <v>1.3117647058823529E-2</v>
+      </c>
+      <c r="BC15" s="14">
+        <f t="shared" si="8"/>
+        <v>0.29485537919999999</v>
+      </c>
+      <c r="BD15" s="14" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE15" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>1.2285640799999999E-2</v>
-      </c>
-      <c r="AY15" s="13">
-        <f t="shared" si="11"/>
-        <v>0.23632680959999997</v>
-      </c>
-      <c r="AZ15" s="13">
-        <f>AP15+SUM(AG15:AI15,AK15:AL15)-((AO15+1)*D15)</f>
-        <v>1735.26</v>
-      </c>
-      <c r="BA15" s="14">
-        <f t="shared" si="3"/>
-        <v>1.2851100123324459E-2</v>
-      </c>
-      <c r="BB15" s="14">
-        <f t="shared" si="4"/>
-        <v>1.3117647058823529E-2</v>
-      </c>
-      <c r="BC15" s="14">
-        <f t="shared" si="5"/>
-        <v>0.29485537919999999</v>
-      </c>
-      <c r="BD15" s="14" t="str">
-        <f>IF(B15="Python",AU15*AZ15/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE15" s="14" t="str">
-        <f>IF(B15="Julia",AV15*AZ15/24/60,"")</f>
         <v/>
       </c>
       <c r="BF15" s="57">
-        <f>IF(B15="No MPC", AT15*J15*AZ15/1000,"")</f>
+        <f t="shared" ref="BF15:BF46" si="17">IF(B15="No MPC", AT15*J15*AZ15/1000,"")</f>
         <v>1.2285640799999999E-2</v>
       </c>
       <c r="BG15" s="14">
@@ -4339,19 +4335,19 @@
         <v>11.539479000000002</v>
       </c>
       <c r="BH15" s="14" t="str">
-        <f>IF(B15="Julia",AW15*AZ15,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI15" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>31.910755324675325</v>
       </c>
       <c r="BJ15" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.2285640799999999E-2</v>
       </c>
       <c r="BK15" s="50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.539479000000002</v>
       </c>
     </row>
@@ -4469,11 +4465,11 @@
         <v>19.34</v>
       </c>
       <c r="AM16" s="30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>13.2</v>
       </c>
       <c r="AN16" s="30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>19.34</v>
       </c>
       <c r="AO16" s="43">
@@ -4500,39 +4496,39 @@
       <c r="AV16" s="30"/>
       <c r="AW16" s="40"/>
       <c r="AX16" s="15">
+        <f t="shared" si="4"/>
+        <v>1.1126932139999997E-2</v>
+      </c>
+      <c r="AY16" s="30">
+        <f t="shared" si="15"/>
+        <v>0.19581117120000002</v>
+      </c>
+      <c r="AZ16" s="30">
+        <f t="shared" si="16"/>
+        <v>1733.1669999999999</v>
+      </c>
+      <c r="BA16" s="31">
+        <f t="shared" si="6"/>
+        <v>1.1077986137515889E-2</v>
+      </c>
+      <c r="BB16" s="31">
+        <f t="shared" si="7"/>
+        <v>1.1294117647058823E-2</v>
+      </c>
+      <c r="BC16" s="31">
+        <f t="shared" si="8"/>
+        <v>0.15569769371332459</v>
+      </c>
+      <c r="BD16" s="31">
+        <f t="shared" si="9"/>
+        <v>6.4874039047218583E-3</v>
+      </c>
+      <c r="BE16" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>1.1126932139999997E-2</v>
-      </c>
-      <c r="AY16" s="30">
-        <f t="shared" si="11"/>
-        <v>0.19581117120000002</v>
-      </c>
-      <c r="AZ16" s="30">
-        <f>AP16+SUM(AG16:AI16,AK16:AL16)-((AO16+1)*D16)</f>
-        <v>1733.1669999999999</v>
-      </c>
-      <c r="BA16" s="31">
-        <f t="shared" si="3"/>
-        <v>1.1077986137515889E-2</v>
-      </c>
-      <c r="BB16" s="31">
-        <f t="shared" si="4"/>
-        <v>1.1294117647058823E-2</v>
-      </c>
-      <c r="BC16" s="31">
-        <f t="shared" si="5"/>
-        <v>0.15569769371332459</v>
-      </c>
-      <c r="BD16" s="31">
-        <f>IF(B16="Python",AU16*AZ16/24/60,"")</f>
-        <v>6.4874039047218583E-3</v>
-      </c>
-      <c r="BE16" s="61" t="str">
-        <f>IF(B16="Julia",AV16*AZ16/24/60,"")</f>
         <v/>
       </c>
       <c r="BF16" s="58" t="str">
-        <f>IF(B16="No MPC", AT16*J16*AZ16/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG16" s="31">
@@ -4540,19 +4536,19 @@
         <v>12.608789925000002</v>
       </c>
       <c r="BH16" s="31" t="str">
-        <f>IF(B16="Julia",AW16*AZ16,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI16" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>16.850399752524307</v>
       </c>
       <c r="BJ16" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>6.4874039047218583E-3</v>
       </c>
       <c r="BK16" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>12.608789925000002</v>
       </c>
     </row>
@@ -4670,11 +4666,11 @@
         <v>19.73</v>
       </c>
       <c r="AM17" s="30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
       <c r="AN17" s="30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>19.73</v>
       </c>
       <c r="AO17" s="43">
@@ -4701,39 +4697,39 @@
       <c r="AV17" s="30"/>
       <c r="AW17" s="40"/>
       <c r="AX17" s="15">
+        <f t="shared" si="4"/>
+        <v>1.205442072E-2</v>
+      </c>
+      <c r="AY17" s="30">
+        <f t="shared" si="15"/>
+        <v>0.19521473040000001</v>
+      </c>
+      <c r="AZ17" s="30">
+        <f t="shared" si="16"/>
+        <v>1731.9570000000001</v>
+      </c>
+      <c r="BA17" s="31">
+        <f t="shared" si="6"/>
+        <v>1.0970249261384664E-2</v>
+      </c>
+      <c r="BB17" s="31">
+        <f t="shared" si="7"/>
+        <v>1.1176470588235295E-2</v>
+      </c>
+      <c r="BC17" s="31">
+        <f t="shared" si="8"/>
+        <v>0.16211423291058846</v>
+      </c>
+      <c r="BD17" s="31">
+        <f t="shared" si="9"/>
+        <v>6.7547597046078529E-3</v>
+      </c>
+      <c r="BE17" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>1.205442072E-2</v>
-      </c>
-      <c r="AY17" s="30">
-        <f t="shared" si="11"/>
-        <v>0.19521473040000001</v>
-      </c>
-      <c r="AZ17" s="30">
-        <f>AP17+SUM(AG17:AI17,AK17:AL17)-((AO17+1)*D17)</f>
-        <v>1731.9570000000001</v>
-      </c>
-      <c r="BA17" s="31">
-        <f t="shared" si="3"/>
-        <v>1.0970249261384664E-2</v>
-      </c>
-      <c r="BB17" s="31">
-        <f t="shared" si="4"/>
-        <v>1.1176470588235295E-2</v>
-      </c>
-      <c r="BC17" s="31">
-        <f t="shared" si="5"/>
-        <v>0.16211423291058846</v>
-      </c>
-      <c r="BD17" s="31">
-        <f>IF(B17="Python",AU17*AZ17/24/60,"")</f>
-        <v>6.7547597046078529E-3</v>
-      </c>
-      <c r="BE17" s="61" t="str">
-        <f>IF(B17="Julia",AV17*AZ17/24/60,"")</f>
         <v/>
       </c>
       <c r="BF17" s="58" t="str">
-        <f>IF(B17="No MPC", AT17*J17*AZ17/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG17" s="31">
@@ -4741,19 +4737,19 @@
         <v>11.993802225000001</v>
       </c>
       <c r="BH17" s="31" t="str">
-        <f>IF(B17="Julia",AW17*AZ17,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI17" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>17.544830401578839</v>
       </c>
       <c r="BJ17" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>6.7547597046078529E-3</v>
       </c>
       <c r="BK17" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.993802225000001</v>
       </c>
     </row>
@@ -4861,11 +4857,11 @@
         <v>24.67</v>
       </c>
       <c r="AM18" s="30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>18.02</v>
       </c>
       <c r="AN18" s="30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>24.67</v>
       </c>
       <c r="AO18" s="43">
@@ -4890,39 +4886,39 @@
       <c r="AV18" s="30"/>
       <c r="AW18" s="40"/>
       <c r="AX18" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AY18" s="30">
+        <f t="shared" si="15"/>
+        <v>0.30285925920000001</v>
+      </c>
+      <c r="AZ18" s="30">
+        <f t="shared" si="16"/>
+        <v>1736.752</v>
+      </c>
+      <c r="BA18" s="31">
+        <f t="shared" si="6"/>
+        <v>1.6133564262485377E-2</v>
+      </c>
+      <c r="BB18" s="31">
+        <f t="shared" si="7"/>
+        <v>1.6482352941176469E-2</v>
+      </c>
+      <c r="BC18" s="31">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BD18" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE18" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AY18" s="30">
-        <f t="shared" si="11"/>
-        <v>0.30285925920000001</v>
-      </c>
-      <c r="AZ18" s="30">
-        <f>AP18+SUM(AG18:AI18,AK18:AL18)-((AO18+1)*D18)</f>
-        <v>1736.752</v>
-      </c>
-      <c r="BA18" s="31">
-        <f t="shared" si="3"/>
-        <v>1.6133564262485377E-2</v>
-      </c>
-      <c r="BB18" s="31">
-        <f t="shared" si="4"/>
-        <v>1.6482352941176469E-2</v>
-      </c>
-      <c r="BC18" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD18" s="31" t="str">
-        <f>IF(B18="Python",AU18*AZ18/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE18" s="61" t="str">
-        <f>IF(B18="Julia",AV18*AZ18/24/60,"")</f>
         <v/>
       </c>
       <c r="BF18" s="58">
-        <f>IF(B18="No MPC", AT18*J18*AZ18/1000,"")</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="BG18" s="31">
@@ -4930,19 +4926,19 @@
         <v>13.025639999999999</v>
       </c>
       <c r="BH18" s="31" t="str">
-        <f>IF(B18="Julia",AW18*AZ18,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI18" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ18" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK18" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>13.025639999999999</v>
       </c>
     </row>
@@ -5060,11 +5056,11 @@
         <v>15.88</v>
       </c>
       <c r="AM19" s="30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>21.89</v>
       </c>
       <c r="AN19" s="30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>15.88</v>
       </c>
       <c r="AO19" s="43">
@@ -5093,56 +5089,56 @@
         <v>2.2770951490618898E-3</v>
       </c>
       <c r="AX19" s="15">
+        <f t="shared" si="4"/>
+        <v>1.0077709230000001E-2</v>
+      </c>
+      <c r="AY19" s="30">
+        <f t="shared" si="15"/>
+        <v>0.18714568319999997</v>
+      </c>
+      <c r="AZ19" s="30">
+        <f t="shared" si="16"/>
+        <v>1740.537</v>
+      </c>
+      <c r="BA19" s="31">
+        <f t="shared" si="6"/>
+        <v>1.6598325689140766E-2</v>
+      </c>
+      <c r="BB19" s="31">
+        <f t="shared" si="7"/>
+        <v>1.6994117647058823E-2</v>
+      </c>
+      <c r="BC19" s="31">
+        <f t="shared" si="8"/>
+        <v>0.40784673284783574</v>
+      </c>
+      <c r="BD19" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE19" s="61">
         <f t="shared" si="1"/>
-        <v>1.0077709230000001E-2</v>
-      </c>
-      <c r="AY19" s="30">
-        <f t="shared" si="11"/>
-        <v>0.18714568319999997</v>
-      </c>
-      <c r="AZ19" s="30">
-        <f>AP19+SUM(AG19:AI19,AK19:AL19)-((AO19+1)*D19)</f>
-        <v>1740.537</v>
-      </c>
-      <c r="BA19" s="31">
-        <f t="shared" si="3"/>
-        <v>1.6598325689140766E-2</v>
-      </c>
-      <c r="BB19" s="31">
-        <f t="shared" si="4"/>
-        <v>1.6994117647058823E-2</v>
-      </c>
-      <c r="BC19" s="31">
-        <f t="shared" si="5"/>
-        <v>0.40784673284783574</v>
-      </c>
-      <c r="BD19" s="31" t="str">
-        <f>IF(B19="Python",AU19*AZ19/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE19" s="61">
-        <f>IF(B19="Julia",AV19*AZ19/24/60,"")</f>
         <v>1.6993613868659822E-2</v>
       </c>
       <c r="BF19" s="58" t="str">
-        <f>IF(B19="No MPC", AT19*J19*AZ19/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG19" s="31"/>
       <c r="BH19" s="31">
-        <f>IF(B19="Julia",AW19*AZ19,"")</f>
+        <f t="shared" si="3"/>
         <v>3.9633683594627347</v>
       </c>
       <c r="BI19" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>44.139256801713827</v>
       </c>
       <c r="BJ19" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.6993613868659822E-2</v>
       </c>
       <c r="BK19" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.9633683594627347</v>
       </c>
     </row>
@@ -5260,11 +5256,11 @@
         <v>20.98</v>
       </c>
       <c r="AM20" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>12.149999999999999</v>
       </c>
       <c r="AN20" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20.98</v>
       </c>
       <c r="AO20" s="44">
@@ -5293,59 +5289,59 @@
         <v>4.8817390308066597E-3</v>
       </c>
       <c r="AX20" s="16">
+        <f t="shared" si="4"/>
+        <v>1.0634540399999998E-2</v>
+      </c>
+      <c r="AY20" s="17">
+        <f t="shared" si="15"/>
+        <v>0.19965035519999999</v>
+      </c>
+      <c r="AZ20" s="17">
+        <f t="shared" si="16"/>
+        <v>1737.67</v>
+      </c>
+      <c r="BA20" s="18">
+        <f t="shared" si="6"/>
+        <v>1.1595987730696851E-2</v>
+      </c>
+      <c r="BB20" s="18">
+        <f t="shared" si="7"/>
+        <v>1.1852941176470587E-2</v>
+      </c>
+      <c r="BC20" s="18">
+        <f t="shared" si="8"/>
+        <v>0.59304435711449988</v>
+      </c>
+      <c r="BD20" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE20" s="18">
         <f t="shared" si="1"/>
-        <v>1.0634540399999998E-2</v>
-      </c>
-      <c r="AY20" s="17">
+        <v>2.4710181546437494E-2</v>
+      </c>
+      <c r="BF20" s="59" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="BG20" s="18" t="str">
+        <f t="shared" ref="BG20:BG28" si="18">IF(P20&lt;1.5, IF(B20&lt;&gt;"Julia",((3-P20)*AZ20)/400, ""),0)</f>
+        <v/>
+      </c>
+      <c r="BH20" s="18">
+        <f t="shared" si="3"/>
+        <v>8.4828514616618094</v>
+      </c>
+      <c r="BI20" s="47">
+        <f t="shared" si="10"/>
+        <v>64.182289731006477</v>
+      </c>
+      <c r="BJ20" s="67">
         <f t="shared" si="11"/>
-        <v>0.19965035519999999</v>
-      </c>
-      <c r="AZ20" s="17">
-        <f>AP20+SUM(AG20:AI20,AK20:AL20)-((AO20+1)*D20)</f>
-        <v>1737.67</v>
-      </c>
-      <c r="BA20" s="18">
-        <f t="shared" si="3"/>
-        <v>1.1595987730696851E-2</v>
-      </c>
-      <c r="BB20" s="18">
-        <f t="shared" si="4"/>
-        <v>1.1852941176470587E-2</v>
-      </c>
-      <c r="BC20" s="18">
-        <f t="shared" si="5"/>
-        <v>0.59304435711449988</v>
-      </c>
-      <c r="BD20" s="18" t="str">
-        <f>IF(B20="Python",AU20*AZ20/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE20" s="18">
-        <f>IF(B20="Julia",AV20*AZ20/24/60,"")</f>
         <v>2.4710181546437494E-2</v>
       </c>
-      <c r="BF20" s="59" t="str">
-        <f>IF(B20="No MPC", AT20*J20*AZ20/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG20" s="18" t="str">
-        <f>IF(P20&lt;1.5, IF(B20&lt;&gt;"Julia",((3-P20)*AZ20)/400, ""),0)</f>
-        <v/>
-      </c>
-      <c r="BH20" s="18">
-        <f>IF(B20="Julia",AW20*AZ20,"")</f>
-        <v>8.4828514616618094</v>
-      </c>
-      <c r="BI20" s="47">
-        <f t="shared" si="6"/>
-        <v>64.182289731006477</v>
-      </c>
-      <c r="BJ20" s="67">
-        <f t="shared" si="7"/>
-        <v>2.4710181546437494E-2</v>
-      </c>
       <c r="BK20" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>8.4828514616618094</v>
       </c>
     </row>
@@ -5463,11 +5459,11 @@
         <v>31.97</v>
       </c>
       <c r="AM21" s="13">
-        <f t="shared" ref="AM21:AN23" si="12">AK21-AK15</f>
+        <f t="shared" ref="AM21:AN23" si="19">AK21-AK15</f>
         <v>16.73</v>
       </c>
       <c r="AN21" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>12.419999999999998</v>
       </c>
       <c r="AO21" s="42">
@@ -5492,59 +5488,59 @@
       <c r="AV21" s="13"/>
       <c r="AW21" s="39"/>
       <c r="AX21" s="12">
+        <f t="shared" si="4"/>
+        <v>1.37621646E-2</v>
+      </c>
+      <c r="AY21" s="13">
+        <f t="shared" si="15"/>
+        <v>0.29485537919999999</v>
+      </c>
+      <c r="AZ21" s="13">
+        <f t="shared" si="16"/>
+        <v>1757.62</v>
+      </c>
+      <c r="BA21" s="14">
+        <f t="shared" si="6"/>
+        <v>2.2206165155152995E-2</v>
+      </c>
+      <c r="BB21" s="14">
+        <f t="shared" si="7"/>
+        <v>2.2958823529411764E-2</v>
+      </c>
+      <c r="BC21" s="14">
+        <f t="shared" si="8"/>
+        <v>0.33029195039999998</v>
+      </c>
+      <c r="BD21" s="14" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE21" s="14" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="BF21" s="57">
+        <f t="shared" si="17"/>
         <v>1.37621646E-2</v>
       </c>
-      <c r="AY21" s="13">
+      <c r="BG21" s="14">
+        <f t="shared" si="18"/>
+        <v>13.18215</v>
+      </c>
+      <c r="BH21" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="BI21" s="46">
+        <f t="shared" si="10"/>
+        <v>35.745882077922076</v>
+      </c>
+      <c r="BJ21" s="66">
         <f t="shared" si="11"/>
-        <v>0.29485537919999999</v>
-      </c>
-      <c r="AZ21" s="13">
-        <f>AP21+SUM(AG21:AI21,AK21:AL21)-((AO21+1)*D21)</f>
-        <v>1757.62</v>
-      </c>
-      <c r="BA21" s="14">
-        <f t="shared" si="3"/>
-        <v>2.2206165155152995E-2</v>
-      </c>
-      <c r="BB21" s="14">
-        <f t="shared" si="4"/>
-        <v>2.2958823529411764E-2</v>
-      </c>
-      <c r="BC21" s="14">
-        <f t="shared" si="5"/>
-        <v>0.33029195039999998</v>
-      </c>
-      <c r="BD21" s="14" t="str">
-        <f>IF(B21="Python",AU21*AZ21/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE21" s="14" t="str">
-        <f>IF(B21="Julia",AV21*AZ21/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF21" s="57">
-        <f>IF(B21="No MPC", AT21*J21*AZ21/1000,"")</f>
         <v>1.37621646E-2</v>
       </c>
-      <c r="BG21" s="14">
-        <f>IF(P21&lt;1.5, IF(B21&lt;&gt;"Julia",((3-P21)*AZ21)/400, ""),0)</f>
-        <v>13.18215</v>
-      </c>
-      <c r="BH21" s="14" t="str">
-        <f>IF(B21="Julia",AW21*AZ21,"")</f>
-        <v/>
-      </c>
-      <c r="BI21" s="46">
-        <f t="shared" si="6"/>
-        <v>35.745882077922076</v>
-      </c>
-      <c r="BJ21" s="66">
-        <f t="shared" si="7"/>
-        <v>1.37621646E-2</v>
-      </c>
       <c r="BK21" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>13.18215</v>
       </c>
     </row>
@@ -5662,11 +5658,11 @@
         <v>32.9</v>
       </c>
       <c r="AM22" s="30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>9.9000000000000021</v>
       </c>
       <c r="AN22" s="30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>13.559999999999999</v>
       </c>
       <c r="AO22" s="43">
@@ -5693,59 +5689,59 @@
       <c r="AV22" s="30"/>
       <c r="AW22" s="40"/>
       <c r="AX22" s="15">
+        <f t="shared" si="4"/>
+        <v>1.2308657399999997E-2</v>
+      </c>
+      <c r="AY22" s="30">
+        <f t="shared" si="15"/>
+        <v>0.26704637135999992</v>
+      </c>
+      <c r="AZ22" s="30">
+        <f t="shared" si="16"/>
+        <v>1753.37</v>
+      </c>
+      <c r="BA22" s="31">
+        <f t="shared" si="6"/>
+        <v>1.6596611097486558E-2</v>
+      </c>
+      <c r="BB22" s="31">
+        <f t="shared" si="7"/>
+        <v>1.7117647058823529E-2</v>
+      </c>
+      <c r="BC22" s="31">
+        <f t="shared" si="8"/>
+        <v>0.37272908663161136</v>
+      </c>
+      <c r="BD22" s="31">
+        <f t="shared" si="9"/>
+        <v>1.5530378609650473E-2</v>
+      </c>
+      <c r="BE22" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>1.2308657399999997E-2</v>
-      </c>
-      <c r="AY22" s="30">
+        <v/>
+      </c>
+      <c r="BF22" s="58" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="BG22" s="31">
+        <f t="shared" si="18"/>
+        <v>13.150274999999999</v>
+      </c>
+      <c r="BH22" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="BI22" s="46">
+        <f t="shared" si="10"/>
+        <v>40.338645739351882</v>
+      </c>
+      <c r="BJ22" s="66">
         <f t="shared" si="11"/>
-        <v>0.26704637135999992</v>
-      </c>
-      <c r="AZ22" s="30">
-        <f>AP22+SUM(AG22:AI22,AK22:AL22)-((AO22+1)*D22)</f>
-        <v>1753.37</v>
-      </c>
-      <c r="BA22" s="31">
-        <f t="shared" si="3"/>
-        <v>1.6596611097486558E-2</v>
-      </c>
-      <c r="BB22" s="31">
-        <f t="shared" si="4"/>
-        <v>1.7117647058823529E-2</v>
-      </c>
-      <c r="BC22" s="31">
-        <f t="shared" si="5"/>
-        <v>0.37272908663161136</v>
-      </c>
-      <c r="BD22" s="31">
-        <f>IF(B22="Python",AU22*AZ22/24/60,"")</f>
         <v>1.5530378609650473E-2</v>
       </c>
-      <c r="BE22" s="61" t="str">
-        <f>IF(B22="Julia",AV22*AZ22/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF22" s="58" t="str">
-        <f>IF(B22="No MPC", AT22*J22*AZ22/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG22" s="31">
-        <f>IF(P22&lt;1.5, IF(B22&lt;&gt;"Julia",((3-P22)*AZ22)/400, ""),0)</f>
-        <v>13.150274999999999</v>
-      </c>
-      <c r="BH22" s="31" t="str">
-        <f>IF(B22="Julia",AW22*AZ22,"")</f>
-        <v/>
-      </c>
-      <c r="BI22" s="46">
-        <f t="shared" si="6"/>
-        <v>40.338645739351882</v>
-      </c>
-      <c r="BJ22" s="66">
-        <f t="shared" si="7"/>
-        <v>1.5530378609650473E-2</v>
-      </c>
       <c r="BK22" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>13.150274999999999</v>
       </c>
     </row>
@@ -5863,11 +5859,11 @@
         <v>32.65</v>
       </c>
       <c r="AM23" s="30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>9.91</v>
       </c>
       <c r="AN23" s="30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>12.919999999999998</v>
       </c>
       <c r="AO23" s="43">
@@ -5894,15 +5890,15 @@
       <c r="AV23" s="30"/>
       <c r="AW23" s="40"/>
       <c r="AX23" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.2128747400000001E-2</v>
       </c>
       <c r="AY23" s="30">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0.28930609728000001</v>
       </c>
       <c r="AZ23" s="30">
-        <f>AP23+SUM(AG23:AI23,AK23:AL23)-((AO23+1)*D23)</f>
+        <f t="shared" si="16"/>
         <v>1750.18</v>
       </c>
       <c r="BA23" s="31">
@@ -5910,43 +5906,43 @@
         <v>1.6518300974756882E-2</v>
       </c>
       <c r="BB23" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1.7005882352941176E-2</v>
       </c>
       <c r="BC23" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.33085613966484767</v>
       </c>
       <c r="BD23" s="31">
-        <f>IF(B23="Python",AU23*AZ23/24/60,"")</f>
+        <f t="shared" si="9"/>
         <v>1.378567248603532E-2</v>
       </c>
       <c r="BE23" s="61" t="str">
-        <f>IF(B23="Julia",AV23*AZ23/24/60,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="BF23" s="58" t="str">
-        <f>IF(B23="No MPC", AT23*J23*AZ23/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG23" s="31">
-        <f>IF(P23&lt;1.5, IF(B23&lt;&gt;"Julia",((3-P23)*AZ23)/400, ""),0)</f>
+        <f t="shared" si="18"/>
         <v>13.12635</v>
       </c>
       <c r="BH23" s="31" t="str">
-        <f>IF(B23="Julia",AW23*AZ23,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="BI23" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>35.806941522169666</v>
       </c>
       <c r="BJ23" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.378567248603532E-2</v>
       </c>
       <c r="BK23" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>13.12635</v>
       </c>
     </row>
@@ -6064,11 +6060,11 @@
         <v>20.73</v>
       </c>
       <c r="AM24" s="30">
-        <f t="shared" ref="AM24:AN30" si="13">AK24-AK19</f>
+        <f t="shared" ref="AM24:AN30" si="20">AK24-AK19</f>
         <v>23.71</v>
       </c>
       <c r="AN24" s="30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>4.8499999999999996</v>
       </c>
       <c r="AO24" s="43">
@@ -6097,59 +6093,59 @@
         <v>3.0538307540188799E-3</v>
       </c>
       <c r="AX24" s="15">
+        <f t="shared" si="4"/>
+        <v>1.1634788099999998E-2</v>
+      </c>
+      <c r="AY24" s="30">
+        <f t="shared" ref="AY24:AY70" si="21">AX19*24</f>
+        <v>0.24186502152</v>
+      </c>
+      <c r="AZ24" s="30">
+        <f t="shared" si="16"/>
+        <v>1754.87</v>
+      </c>
+      <c r="BA24" s="31">
+        <f t="shared" si="6"/>
+        <v>2.9973730247824629E-2</v>
+      </c>
+      <c r="BB24" s="31">
+        <f t="shared" si="7"/>
+        <v>3.0941176470588236E-2</v>
+      </c>
+      <c r="BC24" s="31">
+        <f t="shared" si="8"/>
+        <v>0.58759022932349991</v>
+      </c>
+      <c r="BD24" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE24" s="61">
         <f t="shared" si="1"/>
-        <v>1.1634788099999998E-2</v>
-      </c>
-      <c r="AY24" s="30">
-        <f t="shared" ref="AY24:AY70" si="14">AX19*24</f>
-        <v>0.24186502152</v>
-      </c>
-      <c r="AZ24" s="30">
-        <f>AP24+SUM(AG24:AI24,AK24:AL24)-((AO24+1)*D24)</f>
-        <v>1754.87</v>
-      </c>
-      <c r="BA24" s="31">
+        <v>2.4482926221812498E-2</v>
+      </c>
+      <c r="BF24" s="58" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="BG24" s="31" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BH24" s="31">
         <f t="shared" si="3"/>
-        <v>2.9973730247824629E-2</v>
-      </c>
-      <c r="BB24" s="31">
-        <f t="shared" si="4"/>
-        <v>3.0941176470588236E-2</v>
-      </c>
-      <c r="BC24" s="31">
-        <f t="shared" si="5"/>
-        <v>0.58759022932349991</v>
-      </c>
-      <c r="BD24" s="31" t="str">
-        <f>IF(B24="Python",AU24*AZ24/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE24" s="61">
-        <f>IF(B24="Julia",AV24*AZ24/24/60,"")</f>
+        <v>5.3590759753051112</v>
+      </c>
+      <c r="BI24" s="46">
+        <f t="shared" si="10"/>
+        <v>63.592016160551943</v>
+      </c>
+      <c r="BJ24" s="66">
+        <f t="shared" si="11"/>
         <v>2.4482926221812498E-2</v>
       </c>
-      <c r="BF24" s="58" t="str">
-        <f>IF(B24="No MPC", AT24*J24*AZ24/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG24" s="31" t="str">
-        <f>IF(P24&lt;1.5, IF(B24&lt;&gt;"Julia",((3-P24)*AZ24)/400, ""),0)</f>
-        <v/>
-      </c>
-      <c r="BH24" s="31">
-        <f>IF(B24="Julia",AW24*AZ24,"")</f>
-        <v>5.3590759753051112</v>
-      </c>
-      <c r="BI24" s="46">
-        <f t="shared" si="6"/>
-        <v>63.592016160551943</v>
-      </c>
-      <c r="BJ24" s="66">
-        <f t="shared" si="7"/>
-        <v>2.4482926221812498E-2</v>
-      </c>
       <c r="BK24" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>5.3590759753051112</v>
       </c>
     </row>
@@ -6267,11 +6263,11 @@
         <v>30.11</v>
       </c>
       <c r="AM25" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>30.85</v>
       </c>
       <c r="AN25" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>9.129999999999999</v>
       </c>
       <c r="AO25" s="44">
@@ -6300,59 +6296,59 @@
         <v>4.2153110000000002E-3</v>
       </c>
       <c r="AX25" s="16">
+        <f t="shared" si="4"/>
+        <v>1.2452820119999998E-2</v>
+      </c>
+      <c r="AY25" s="17">
+        <f t="shared" si="21"/>
+        <v>0.25522896959999997</v>
+      </c>
+      <c r="AZ25" s="17">
+        <f t="shared" si="16"/>
+        <v>1773.9059999999999</v>
+      </c>
+      <c r="BA25" s="18">
+        <f t="shared" si="6"/>
+        <v>2.8750114154865027E-2</v>
+      </c>
+      <c r="BB25" s="18">
+        <f t="shared" si="7"/>
+        <v>0.03</v>
+      </c>
+      <c r="BC25" s="18">
+        <f t="shared" si="8"/>
+        <v>0.53113548411480005</v>
+      </c>
+      <c r="BD25" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE25" s="18">
         <f t="shared" si="1"/>
-        <v>1.2452820119999998E-2</v>
-      </c>
-      <c r="AY25" s="17">
-        <f t="shared" si="14"/>
-        <v>0.25522896959999997</v>
-      </c>
-      <c r="AZ25" s="17">
-        <f>AP25+SUM(AG25:AI25,AK25:AL25)-((AO25+1)*D25)</f>
-        <v>1773.9059999999999</v>
-      </c>
-      <c r="BA25" s="18">
+        <v>2.2130645171450001E-2</v>
+      </c>
+      <c r="BF25" s="59" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="BG25" s="18" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="BH25" s="18">
         <f t="shared" si="3"/>
-        <v>2.8750114154865027E-2</v>
-      </c>
-      <c r="BB25" s="18">
-        <f t="shared" si="4"/>
-        <v>0.03</v>
-      </c>
-      <c r="BC25" s="18">
-        <f t="shared" si="5"/>
-        <v>0.53113548411480005</v>
-      </c>
-      <c r="BD25" s="18" t="str">
-        <f>IF(B25="Python",AU25*AZ25/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE25" s="18">
-        <f>IF(B25="Julia",AV25*AZ25/24/60,"")</f>
+        <v>7.4775654747660001</v>
+      </c>
+      <c r="BI25" s="46">
+        <f t="shared" si="10"/>
+        <v>57.482195250519489</v>
+      </c>
+      <c r="BJ25" s="66">
+        <f t="shared" si="11"/>
         <v>2.2130645171450001E-2</v>
       </c>
-      <c r="BF25" s="59" t="str">
-        <f>IF(B25="No MPC", AT25*J25*AZ25/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG25" s="18" t="str">
-        <f>IF(P25&lt;1.5, IF(B25&lt;&gt;"Julia",((3-P25)*AZ25)/400, ""),0)</f>
-        <v/>
-      </c>
-      <c r="BH25" s="18">
-        <f>IF(B25="Julia",AW25*AZ25,"")</f>
-        <v>7.4775654747660001</v>
-      </c>
-      <c r="BI25" s="46">
-        <f t="shared" si="6"/>
-        <v>57.482195250519489</v>
-      </c>
-      <c r="BJ25" s="66">
-        <f t="shared" si="7"/>
-        <v>2.2130645171450001E-2</v>
-      </c>
       <c r="BK25" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>7.4775654747660001</v>
       </c>
     </row>
@@ -6460,7 +6456,9 @@
       <c r="AI26" s="13">
         <v>4</v>
       </c>
-      <c r="AJ26" s="13"/>
+      <c r="AJ26" s="13">
+        <v>1.3502837699999999E-2</v>
+      </c>
       <c r="AK26" s="13">
         <v>57</v>
       </c>
@@ -6468,11 +6466,11 @@
         <v>46</v>
       </c>
       <c r="AM26" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>17.97</v>
       </c>
       <c r="AN26" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>14.030000000000001</v>
       </c>
       <c r="AO26" s="42">
@@ -6497,59 +6495,59 @@
       <c r="AV26" s="13"/>
       <c r="AW26" s="39"/>
       <c r="AX26" s="12">
+        <f t="shared" si="4"/>
+        <v>1.3502837699999999E-2</v>
+      </c>
+      <c r="AY26" s="13">
+        <f t="shared" si="21"/>
+        <v>0.33029195039999998</v>
+      </c>
+      <c r="AZ26" s="13">
+        <f t="shared" si="16"/>
+        <v>1779.03</v>
+      </c>
+      <c r="BA26" s="14">
+        <f t="shared" si="6"/>
+        <v>3.2039931872986968E-2</v>
+      </c>
+      <c r="BB26" s="14">
+        <f t="shared" si="7"/>
+        <v>3.3529411764705884E-2</v>
+      </c>
+      <c r="BC26" s="14">
+        <f t="shared" si="8"/>
+        <v>0.32406810479999998</v>
+      </c>
+      <c r="BD26" s="14" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE26" s="14" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="BF26" s="57">
+        <f t="shared" si="17"/>
         <v>1.3502837699999999E-2</v>
       </c>
-      <c r="AY26" s="13">
-        <f t="shared" si="14"/>
-        <v>0.33029195039999998</v>
-      </c>
-      <c r="AZ26" s="13">
-        <f>AP26+SUM(AG26:AI26,AK26:AL26)-((AO26+1)*D26)</f>
-        <v>1779.03</v>
-      </c>
-      <c r="BA26" s="14">
+      <c r="BG26" s="14">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BH26" s="14" t="str">
         <f t="shared" si="3"/>
-        <v>3.2039931872986968E-2</v>
-      </c>
-      <c r="BB26" s="14">
-        <f t="shared" si="4"/>
-        <v>3.3529411764705884E-2</v>
-      </c>
-      <c r="BC26" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD26" s="14" t="str">
-        <f>IF(B26="Python",AU26*AZ26/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE26" s="14" t="str">
-        <f>IF(B26="Julia",AV26*AZ26/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF26" s="57">
-        <f>IF(B26="No MPC", AT26*J26*AZ26/1000,"")</f>
+        <v/>
+      </c>
+      <c r="BI26" s="45">
+        <f t="shared" si="10"/>
+        <v>35.072305714285712</v>
+      </c>
+      <c r="BJ26" s="65">
+        <f t="shared" si="11"/>
         <v>1.3502837699999999E-2</v>
       </c>
-      <c r="BG26" s="14">
-        <f>IF(P26&lt;1.5, IF(B26&lt;&gt;"Julia",((3-P26)*AZ26)/400, ""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH26" s="14" t="str">
-        <f>IF(B26="Julia",AW26*AZ26,"")</f>
-        <v/>
-      </c>
-      <c r="BI26" s="45">
-        <f t="shared" si="6"/>
-        <v>35.072305714285712</v>
-      </c>
-      <c r="BJ26" s="65">
-        <f t="shared" si="7"/>
-        <v>1.3502837699999999E-2</v>
-      </c>
       <c r="BK26" s="50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -6657,7 +6655,9 @@
       <c r="AI27" s="30">
         <v>3</v>
       </c>
-      <c r="AJ27" s="30"/>
+      <c r="AJ27" s="30">
+        <v>4.4315646613239966E-2</v>
+      </c>
       <c r="AK27" s="30">
         <v>49</v>
       </c>
@@ -6665,11 +6665,11 @@
         <v>47</v>
       </c>
       <c r="AM27" s="30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>19.899999999999999</v>
       </c>
       <c r="AN27" s="30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>14.100000000000001</v>
       </c>
       <c r="AO27" s="43">
@@ -6696,59 +6696,59 @@
       <c r="AV27" s="30"/>
       <c r="AW27" s="40"/>
       <c r="AX27" s="15">
+        <f t="shared" si="4"/>
+        <v>1.1170971E-2</v>
+      </c>
+      <c r="AY27" s="30">
+        <f t="shared" si="21"/>
+        <v>0.29540777759999992</v>
+      </c>
+      <c r="AZ27" s="30">
+        <f t="shared" si="16"/>
+        <v>1773.17</v>
+      </c>
+      <c r="BA27" s="31">
+        <f t="shared" si="6"/>
+        <v>2.7634124195649597E-2</v>
+      </c>
+      <c r="BB27" s="31">
+        <f t="shared" si="7"/>
+        <v>2.8823529411764706E-2</v>
+      </c>
+      <c r="BC27" s="31">
+        <f t="shared" si="8"/>
+        <v>1.0635755187177591</v>
+      </c>
+      <c r="BD27" s="31">
+        <f t="shared" si="9"/>
+        <v>4.4315646613239966E-2</v>
+      </c>
+      <c r="BE27" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>1.1170971E-2</v>
-      </c>
-      <c r="AY27" s="30">
-        <f t="shared" si="14"/>
-        <v>0.29540777759999992</v>
-      </c>
-      <c r="AZ27" s="30">
-        <f>AP27+SUM(AG27:AI27,AK27:AL27)-((AO27+1)*D27)</f>
-        <v>1773.17</v>
-      </c>
-      <c r="BA27" s="31">
+        <v/>
+      </c>
+      <c r="BF27" s="58" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="BG27" s="31">
+        <f t="shared" si="18"/>
+        <v>6.7380460000000006</v>
+      </c>
+      <c r="BH27" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>2.7634124195649597E-2</v>
-      </c>
-      <c r="BB27" s="31">
-        <f t="shared" si="4"/>
-        <v>2.8823529411764706E-2</v>
-      </c>
-      <c r="BC27" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD27" s="31">
-        <f>IF(B27="Python",AU27*AZ27/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BI27" s="46">
+        <f t="shared" si="10"/>
+        <v>115.10557561880512</v>
+      </c>
+      <c r="BJ27" s="66">
+        <f t="shared" si="11"/>
         <v>4.4315646613239966E-2</v>
       </c>
-      <c r="BE27" s="61" t="str">
-        <f>IF(B27="Julia",AV27*AZ27/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF27" s="58" t="str">
-        <f>IF(B27="No MPC", AT27*J27*AZ27/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG27" s="31">
-        <f>IF(P27&lt;1.5, IF(B27&lt;&gt;"Julia",((3-P27)*AZ27)/400, ""),0)</f>
-        <v>6.7380460000000006</v>
-      </c>
-      <c r="BH27" s="31" t="str">
-        <f>IF(B27="Julia",AW27*AZ27,"")</f>
-        <v/>
-      </c>
-      <c r="BI27" s="46">
-        <f t="shared" si="6"/>
-        <v>115.10557561880512</v>
-      </c>
-      <c r="BJ27" s="66">
-        <f t="shared" si="7"/>
-        <v>4.4315646613239966E-2</v>
-      </c>
       <c r="BK27" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>6.7380460000000006</v>
       </c>
     </row>
@@ -6856,7 +6856,9 @@
       <c r="AI28" s="30">
         <v>6</v>
       </c>
-      <c r="AJ28" s="30"/>
+      <c r="AJ28" s="30">
+        <v>4.4316995715709212E-2</v>
+      </c>
       <c r="AK28" s="30">
         <v>47</v>
       </c>
@@ -6864,11 +6866,11 @@
         <v>47</v>
       </c>
       <c r="AM28" s="30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>18.09</v>
       </c>
       <c r="AN28" s="30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>14.350000000000001</v>
       </c>
       <c r="AO28" s="43">
@@ -6895,59 +6897,59 @@
       <c r="AV28" s="30"/>
       <c r="AW28" s="40"/>
       <c r="AX28" s="15">
+        <f t="shared" si="4"/>
+        <v>1.17288015E-2</v>
+      </c>
+      <c r="AY28" s="30">
+        <f t="shared" si="21"/>
+        <v>0.29108993760000001</v>
+      </c>
+      <c r="AZ28" s="30">
+        <f t="shared" si="16"/>
+        <v>1769.05</v>
+      </c>
+      <c r="BA28" s="31">
+        <f t="shared" si="6"/>
+        <v>2.656793194087222E-2</v>
+      </c>
+      <c r="BB28" s="31">
+        <f t="shared" si="7"/>
+        <v>2.7647058823529413E-2</v>
+      </c>
+      <c r="BC28" s="31">
+        <f t="shared" si="8"/>
+        <v>1.0636078971770211</v>
+      </c>
+      <c r="BD28" s="31">
+        <f t="shared" si="9"/>
+        <v>4.4316995715709212E-2</v>
+      </c>
+      <c r="BE28" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>1.17288015E-2</v>
-      </c>
-      <c r="AY28" s="30">
-        <f t="shared" si="14"/>
-        <v>0.29108993760000001</v>
-      </c>
-      <c r="AZ28" s="30">
-        <f>AP28+SUM(AG28:AI28,AK28:AL28)-((AO28+1)*D28)</f>
-        <v>1769.05</v>
-      </c>
-      <c r="BA28" s="31">
+        <v/>
+      </c>
+      <c r="BF28" s="58" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="BG28" s="31">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="BH28" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>2.656793194087222E-2</v>
-      </c>
-      <c r="BB28" s="31">
-        <f t="shared" si="4"/>
-        <v>2.7647058823529413E-2</v>
-      </c>
-      <c r="BC28" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD28" s="31">
-        <f>IF(B28="Python",AU28*AZ28/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BI28" s="46">
+        <f t="shared" si="10"/>
+        <v>115.10907978106289</v>
+      </c>
+      <c r="BJ28" s="66">
+        <f t="shared" si="11"/>
         <v>4.4316995715709212E-2</v>
       </c>
-      <c r="BE28" s="61" t="str">
-        <f>IF(B28="Julia",AV28*AZ28/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF28" s="58" t="str">
-        <f>IF(B28="No MPC", AT28*J28*AZ28/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG28" s="31">
-        <f>IF(P28&lt;1.5, IF(B28&lt;&gt;"Julia",((3-P28)*AZ28)/400, ""),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BH28" s="31" t="str">
-        <f>IF(B28="Julia",AW28*AZ28,"")</f>
-        <v/>
-      </c>
-      <c r="BI28" s="46">
-        <f t="shared" si="6"/>
-        <v>115.10907978106289</v>
-      </c>
-      <c r="BJ28" s="66">
-        <f t="shared" si="7"/>
-        <v>4.4316995715709212E-2</v>
-      </c>
       <c r="BK28" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -7055,7 +7057,9 @@
       <c r="AI29" s="30">
         <v>6</v>
       </c>
-      <c r="AJ29" s="30"/>
+      <c r="AJ29" s="30">
+        <v>1.4000061328465761E-2</v>
+      </c>
       <c r="AK29" s="30">
         <v>85</v>
       </c>
@@ -7063,11 +7067,11 @@
         <v>27</v>
       </c>
       <c r="AM29" s="30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>32.4</v>
       </c>
       <c r="AN29" s="30">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>6.27</v>
       </c>
       <c r="AO29" s="43">
@@ -7096,56 +7100,56 @@
         <v>2.3715861773774098E-3</v>
       </c>
       <c r="AX29" s="15">
+        <f t="shared" si="4"/>
+        <v>1.19533344E-2</v>
+      </c>
+      <c r="AY29" s="30">
+        <f t="shared" si="21"/>
+        <v>0.27923491439999992</v>
+      </c>
+      <c r="AZ29" s="30">
+        <f t="shared" si="16"/>
+        <v>1778.77</v>
+      </c>
+      <c r="BA29" s="31">
+        <f t="shared" si="6"/>
+        <v>4.7785829533891398E-2</v>
+      </c>
+      <c r="BB29" s="31">
+        <f t="shared" si="7"/>
+        <v>0.05</v>
+      </c>
+      <c r="BC29" s="31">
+        <f t="shared" si="8"/>
+        <v>0.33600147188317825</v>
+      </c>
+      <c r="BD29" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE29" s="61">
         <f t="shared" si="1"/>
-        <v>1.19533344E-2</v>
-      </c>
-      <c r="AY29" s="30">
-        <f t="shared" si="14"/>
-        <v>0.27923491439999992</v>
-      </c>
-      <c r="AZ29" s="30">
-        <f>AP29+SUM(AG29:AI29,AK29:AL29)-((AO29+1)*D29)</f>
-        <v>1778.77</v>
-      </c>
-      <c r="BA29" s="31">
-        <f t="shared" si="3"/>
-        <v>4.7785829533891398E-2</v>
-      </c>
-      <c r="BB29" s="31">
-        <f t="shared" si="4"/>
-        <v>0.05</v>
-      </c>
-      <c r="BC29" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD29" s="31" t="str">
-        <f>IF(B29="Python",AU29*AZ29/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE29" s="61">
-        <f>IF(B29="Julia",AV29*AZ29/24/60,"")</f>
         <v>1.4000061328465761E-2</v>
       </c>
       <c r="BF29" s="58" t="str">
-        <f>IF(B29="No MPC", AT29*J29*AZ29/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG29" s="31"/>
       <c r="BH29" s="31">
-        <f>IF(B29="Julia",AW29*AZ29,"")</f>
+        <f t="shared" si="3"/>
         <v>4.2185063447336155</v>
       </c>
       <c r="BI29" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>36.363795658352629</v>
       </c>
       <c r="BJ29" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.4000061328465761E-2</v>
       </c>
       <c r="BK29" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.2185063447336155</v>
       </c>
     </row>
@@ -7253,7 +7257,9 @@
       <c r="AI30" s="17">
         <v>6</v>
       </c>
-      <c r="AJ30" s="17"/>
+      <c r="AJ30" s="17">
+        <v>2.1265523894556992E-2</v>
+      </c>
       <c r="AK30" s="17">
         <v>81</v>
       </c>
@@ -7261,11 +7267,11 @@
         <v>38</v>
       </c>
       <c r="AM30" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AN30" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>7.8900000000000006</v>
       </c>
       <c r="AO30" s="44">
@@ -7294,56 +7300,56 @@
         <v>2.0375862739135898E-3</v>
       </c>
       <c r="AX30" s="16">
+        <f t="shared" si="4"/>
+        <v>1.27752228E-2</v>
+      </c>
+      <c r="AY30" s="17">
+        <f t="shared" si="21"/>
+        <v>0.29886768287999993</v>
+      </c>
+      <c r="AZ30" s="17">
+        <f t="shared" si="16"/>
+        <v>1804.41</v>
+      </c>
+      <c r="BA30" s="18">
+        <f t="shared" si="6"/>
+        <v>4.4890019452341758E-2</v>
+      </c>
+      <c r="BB30" s="18">
+        <f t="shared" si="7"/>
+        <v>4.764705882352941E-2</v>
+      </c>
+      <c r="BC30" s="18">
+        <f t="shared" si="8"/>
+        <v>0.51037257346936782</v>
+      </c>
+      <c r="BD30" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE30" s="18">
         <f t="shared" si="1"/>
-        <v>1.27752228E-2</v>
-      </c>
-      <c r="AY30" s="17">
-        <f t="shared" si="14"/>
-        <v>0.29886768287999993</v>
-      </c>
-      <c r="AZ30" s="17">
-        <f>AP30+SUM(AG30:AI30,AK30:AL30)-((AO30+1)*D30)</f>
-        <v>1804.41</v>
-      </c>
-      <c r="BA30" s="18">
-        <f t="shared" si="3"/>
-        <v>4.4890019452341758E-2</v>
-      </c>
-      <c r="BB30" s="18">
-        <f t="shared" si="4"/>
-        <v>4.764705882352941E-2</v>
-      </c>
-      <c r="BC30" s="18">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD30" s="18" t="str">
-        <f>IF(B30="Python",AU30*AZ30/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE30" s="18">
-        <f>IF(B30="Julia",AV30*AZ30/24/60,"")</f>
         <v>2.1265523894556992E-2</v>
       </c>
       <c r="BF30" s="59" t="str">
-        <f>IF(B30="No MPC", AT30*J30*AZ30/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG30" s="18"/>
       <c r="BH30" s="18">
-        <f>IF(B30="Julia",AW30*AZ30,"")</f>
+        <f t="shared" si="3"/>
         <v>3.6766410485124208</v>
       </c>
       <c r="BI30" s="47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>55.235126998849331</v>
       </c>
       <c r="BJ30" s="67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.1265523894556992E-2</v>
       </c>
       <c r="BK30" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>3.6766410485124208</v>
       </c>
     </row>
@@ -7365,39 +7371,105 @@
         <v>2716.05</v>
       </c>
       <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-      <c r="AB31" s="24"/>
-      <c r="AC31" s="12"/>
-      <c r="AD31" s="13"/>
-      <c r="AE31" s="13"/>
-      <c r="AF31" s="13"/>
-      <c r="AG31" s="13"/>
-      <c r="AH31" s="13"/>
-      <c r="AI31" s="13"/>
+      <c r="H31" s="9">
+        <v>2295.9</v>
+      </c>
+      <c r="I31" s="9">
+        <v>24.8</v>
+      </c>
+      <c r="J31" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="K31" s="9">
+        <v>94.8</v>
+      </c>
+      <c r="L31" s="9">
+        <v>16.3</v>
+      </c>
+      <c r="M31" s="9">
+        <v>353</v>
+      </c>
+      <c r="N31" s="9">
+        <v>1.18</v>
+      </c>
+      <c r="O31" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P31" s="9">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="Q31" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="R31" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="S31" s="9">
+        <v>3.26</v>
+      </c>
+      <c r="T31" s="9">
+        <v>7.2489999999999997</v>
+      </c>
+      <c r="U31" s="9">
+        <v>118.6</v>
+      </c>
+      <c r="V31" s="9">
+        <v>46.7</v>
+      </c>
+      <c r="W31" s="9">
+        <v>2.72</v>
+      </c>
+      <c r="X31" s="9">
+        <v>155</v>
+      </c>
+      <c r="Y31" s="9">
+        <v>50.6</v>
+      </c>
+      <c r="Z31" s="9">
+        <v>104</v>
+      </c>
+      <c r="AA31" s="9">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AB31" s="24">
+        <v>7.2910000000000004</v>
+      </c>
+      <c r="AC31" s="12">
+        <v>299</v>
+      </c>
+      <c r="AD31" s="13">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="AE31" s="13">
+        <v>7.3</v>
+      </c>
+      <c r="AF31" s="13">
+        <v>34</v>
+      </c>
+      <c r="AG31" s="13">
+        <v>31.32</v>
+      </c>
+      <c r="AH31" s="13">
+        <v>21.46</v>
+      </c>
+      <c r="AI31" s="13">
+        <v>5</v>
+      </c>
       <c r="AJ31" s="13"/>
-      <c r="AK31" s="13"/>
-      <c r="AL31" s="13"/>
-      <c r="AM31" s="13"/>
-      <c r="AN31" s="13"/>
+      <c r="AK31" s="13">
+        <v>76</v>
+      </c>
+      <c r="AL31" s="13">
+        <v>46</v>
+      </c>
+      <c r="AM31" s="13">
+        <f t="shared" ref="AM31:AM35" si="22">AK31-AK26</f>
+        <v>19</v>
+      </c>
+      <c r="AN31" s="13">
+        <f t="shared" ref="AN31:AN35" si="23">AL31-AL26</f>
+        <v>0</v>
+      </c>
       <c r="AO31" s="42">
         <v>15</v>
       </c>
@@ -7420,60 +7492,60 @@
       <c r="AV31" s="13"/>
       <c r="AW31" s="39"/>
       <c r="AX31" s="12">
+        <f t="shared" si="4"/>
+        <v>1.6917932E-2</v>
+      </c>
+      <c r="AY31" s="13">
+        <f t="shared" si="21"/>
+        <v>0.32406810479999998</v>
+      </c>
+      <c r="AZ31" s="13">
+        <f t="shared" si="16"/>
+        <v>1799.78</v>
+      </c>
+      <c r="BA31" s="14">
+        <f t="shared" si="6"/>
+        <v>4.2227383346853505E-2</v>
+      </c>
+      <c r="BB31" s="14">
+        <f t="shared" si="7"/>
+        <v>4.4705882352941179E-2</v>
+      </c>
+      <c r="BC31" s="14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BD31" s="14" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE31" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AY31" s="13">
-        <f t="shared" si="14"/>
-        <v>0.32406810479999998</v>
-      </c>
-      <c r="AZ31" s="13">
-        <f>AP31+SUM(AG31:AI31,AK31:AL31)-((AO31+1)*D31)</f>
-        <v>1620</v>
-      </c>
-      <c r="BA31" s="14" t="e">
+        <v/>
+      </c>
+      <c r="BF31" s="57">
+        <f t="shared" si="17"/>
+        <v>1.6917932E-2</v>
+      </c>
+      <c r="BG31" s="14">
+        <f t="shared" ref="BG31:BG70" si="24">IF(P31&lt;1.5, IF(B31&lt;&gt;"Julia",((3-P31)*AZ31)/400, ""),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH31" s="14" t="str">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB31" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BC31" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD31" s="14" t="str">
-        <f>IF(B31="Python",AU31*AZ31/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE31" s="14" t="str">
-        <f>IF(B31="Julia",AV31*AZ31/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF31" s="57">
-        <f>IF(B31="No MPC", AT31*J31*AZ31/1000,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BG31" s="14">
-        <f>IF(P31&lt;1.5, IF(B31&lt;&gt;"Julia",((3-P31)*AZ31)/400, ""),0)</f>
-        <v>12.15</v>
-      </c>
-      <c r="BH31" s="14" t="str">
-        <f>IF(B31="Julia",AW31*AZ31,"")</f>
         <v/>
       </c>
       <c r="BI31" s="46">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>43.942680519480525</v>
       </c>
       <c r="BJ31" s="66">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.6917932E-2</v>
       </c>
       <c r="BK31" s="48">
-        <f t="shared" si="8"/>
-        <v>12.15</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:63" x14ac:dyDescent="0.3">
@@ -7494,39 +7566,105 @@
         <v>2716.05</v>
       </c>
       <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="25"/>
-      <c r="AC32" s="15"/>
-      <c r="AD32" s="30"/>
-      <c r="AE32" s="30"/>
-      <c r="AF32" s="30"/>
-      <c r="AG32" s="30"/>
-      <c r="AH32" s="30"/>
-      <c r="AI32" s="30"/>
+      <c r="H32" s="29">
+        <v>2198.355</v>
+      </c>
+      <c r="I32" s="29">
+        <v>20.8</v>
+      </c>
+      <c r="J32" s="29">
+        <v>19.3</v>
+      </c>
+      <c r="K32" s="29">
+        <v>93</v>
+      </c>
+      <c r="L32" s="29">
+        <v>17.3</v>
+      </c>
+      <c r="M32" s="29">
+        <v>396</v>
+      </c>
+      <c r="N32" s="29">
+        <v>1.32</v>
+      </c>
+      <c r="O32" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="P32" s="29">
+        <v>5.62</v>
+      </c>
+      <c r="Q32" s="29">
+        <v>0.23</v>
+      </c>
+      <c r="R32" s="29">
+        <v>0.32</v>
+      </c>
+      <c r="S32" s="29">
+        <v>2.87</v>
+      </c>
+      <c r="T32" s="29">
+        <v>7.2560000000000002</v>
+      </c>
+      <c r="U32" s="29">
+        <v>143.9</v>
+      </c>
+      <c r="V32" s="29">
+        <v>42.6</v>
+      </c>
+      <c r="W32" s="29">
+        <v>2.06</v>
+      </c>
+      <c r="X32" s="29">
+        <v>158</v>
+      </c>
+      <c r="Y32" s="29">
+        <v>62.3</v>
+      </c>
+      <c r="Z32" s="29">
+        <v>126.2</v>
+      </c>
+      <c r="AA32" s="29">
+        <v>34.5</v>
+      </c>
+      <c r="AB32" s="25">
+        <v>7.2969999999999997</v>
+      </c>
+      <c r="AC32" s="15">
+        <v>299</v>
+      </c>
+      <c r="AD32" s="30">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="AE32" s="30">
+        <v>7.28</v>
+      </c>
+      <c r="AF32" s="30">
+        <v>34</v>
+      </c>
+      <c r="AG32" s="30">
+        <v>33.53</v>
+      </c>
+      <c r="AH32" s="30">
+        <v>6.72</v>
+      </c>
+      <c r="AI32" s="30">
+        <v>3</v>
+      </c>
       <c r="AJ32" s="30"/>
-      <c r="AK32" s="30"/>
-      <c r="AL32" s="30"/>
-      <c r="AM32" s="30"/>
-      <c r="AN32" s="30"/>
+      <c r="AK32" s="30">
+        <v>107</v>
+      </c>
+      <c r="AL32" s="30">
+        <v>55</v>
+      </c>
+      <c r="AM32" s="30">
+        <f t="shared" si="22"/>
+        <v>58</v>
+      </c>
+      <c r="AN32" s="30">
+        <f t="shared" si="23"/>
+        <v>8</v>
+      </c>
       <c r="AO32" s="43">
         <v>15</v>
       </c>
@@ -7549,60 +7687,60 @@
       <c r="AV32" s="30"/>
       <c r="AW32" s="40"/>
       <c r="AX32" s="15">
+        <f t="shared" si="4"/>
+        <v>1.409093E-2</v>
+      </c>
+      <c r="AY32" s="30">
+        <f t="shared" si="21"/>
+        <v>0.26810330399999999</v>
+      </c>
+      <c r="AZ32" s="30">
+        <f t="shared" si="16"/>
+        <v>1825.25</v>
+      </c>
+      <c r="BA32" s="31">
+        <f t="shared" si="6"/>
+        <v>5.8622106560745103E-2</v>
+      </c>
+      <c r="BB32" s="31">
+        <f t="shared" si="7"/>
+        <v>6.2941176470588237E-2</v>
+      </c>
+      <c r="BC32" s="31">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BD32" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BE32" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AY32" s="30">
-        <f t="shared" si="14"/>
-        <v>0.26810330399999999</v>
-      </c>
-      <c r="AZ32" s="30">
-        <f>AP32+SUM(AG32:AI32,AK32:AL32)-((AO32+1)*D32)</f>
-        <v>1620</v>
-      </c>
-      <c r="BA32" s="31" t="e">
+        <v/>
+      </c>
+      <c r="BF32" s="58" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="BG32" s="31">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="BH32" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB32" s="31">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BC32" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD32" s="31">
-        <f>IF(B32="Python",AU32*AZ32/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE32" s="61" t="str">
-        <f>IF(B32="Julia",AV32*AZ32/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF32" s="58" t="str">
-        <f>IF(B32="No MPC", AT32*J32*AZ32/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG32" s="31">
-        <f>IF(P32&lt;1.5, IF(B32&lt;&gt;"Julia",((3-P32)*AZ32)/400, ""),0)</f>
-        <v>12.15</v>
-      </c>
-      <c r="BH32" s="31" t="str">
-        <f>IF(B32="Julia",AW32*AZ32,"")</f>
         <v/>
       </c>
       <c r="BI32" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ32" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK32" s="48">
-        <f t="shared" si="8"/>
-        <v>12.15</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:63" x14ac:dyDescent="0.3">
@@ -7623,39 +7761,105 @@
         <v>2716.05</v>
       </c>
       <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="29"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="29"/>
-      <c r="W33" s="29"/>
-      <c r="X33" s="29"/>
-      <c r="Y33" s="29"/>
-      <c r="Z33" s="29"/>
-      <c r="AA33" s="29"/>
-      <c r="AB33" s="25"/>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="30"/>
-      <c r="AE33" s="30"/>
-      <c r="AF33" s="30"/>
-      <c r="AG33" s="30"/>
-      <c r="AH33" s="30"/>
-      <c r="AI33" s="30"/>
+      <c r="H33" s="29">
+        <v>2270.1149999999998</v>
+      </c>
+      <c r="I33" s="29">
+        <v>21.7</v>
+      </c>
+      <c r="J33" s="29">
+        <v>20</v>
+      </c>
+      <c r="K33" s="29">
+        <v>92.5</v>
+      </c>
+      <c r="L33" s="29">
+        <v>17</v>
+      </c>
+      <c r="M33" s="29">
+        <v>376</v>
+      </c>
+      <c r="N33" s="29">
+        <v>1.28</v>
+      </c>
+      <c r="O33" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="P33" s="29">
+        <v>5.03</v>
+      </c>
+      <c r="Q33" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="R33" s="29">
+        <v>0.54</v>
+      </c>
+      <c r="S33" s="29">
+        <v>2.76</v>
+      </c>
+      <c r="T33" s="29">
+        <v>7.24</v>
+      </c>
+      <c r="U33" s="29">
+        <v>109.8</v>
+      </c>
+      <c r="V33" s="29">
+        <v>40.4</v>
+      </c>
+      <c r="W33" s="29">
+        <v>2.12</v>
+      </c>
+      <c r="X33" s="29">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="Y33" s="29">
+        <v>45.7</v>
+      </c>
+      <c r="Z33" s="29">
+        <v>96.3</v>
+      </c>
+      <c r="AA33" s="29">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="AB33" s="25">
+        <v>7.2809999999999997</v>
+      </c>
+      <c r="AC33" s="15">
+        <v>299</v>
+      </c>
+      <c r="AD33" s="30">
+        <v>0.503</v>
+      </c>
+      <c r="AE33" s="30">
+        <v>7.28</v>
+      </c>
+      <c r="AF33" s="30">
+        <v>34</v>
+      </c>
+      <c r="AG33" s="30">
+        <v>27.27</v>
+      </c>
+      <c r="AH33" s="30">
+        <v>10.57</v>
+      </c>
+      <c r="AI33" s="30">
+        <v>7</v>
+      </c>
       <c r="AJ33" s="30"/>
-      <c r="AK33" s="30"/>
-      <c r="AL33" s="30"/>
-      <c r="AM33" s="30"/>
-      <c r="AN33" s="30"/>
+      <c r="AK33" s="30">
+        <v>104</v>
+      </c>
+      <c r="AL33" s="30">
+        <v>47</v>
+      </c>
+      <c r="AM33" s="30">
+        <f t="shared" si="22"/>
+        <v>57</v>
+      </c>
+      <c r="AN33" s="30">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AO33" s="43">
         <v>15</v>
       </c>
@@ -7678,60 +7882,60 @@
       <c r="AV33" s="30"/>
       <c r="AW33" s="40"/>
       <c r="AX33" s="15">
+        <f t="shared" si="4"/>
+        <v>1.452672E-2</v>
+      </c>
+      <c r="AY33" s="30">
+        <f t="shared" si="21"/>
+        <v>0.28149123600000003</v>
+      </c>
+      <c r="AZ33" s="30">
+        <f t="shared" si="16"/>
+        <v>1815.84</v>
+      </c>
+      <c r="BA33" s="31">
+        <f t="shared" si="6"/>
+        <v>5.7273768613974804E-2</v>
+      </c>
+      <c r="BB33" s="31">
+        <f t="shared" ref="BB33:BB58" si="25">AK33/AP33</f>
+        <v>6.1176470588235297E-2</v>
+      </c>
+      <c r="BC33" s="31">
+        <f t="shared" ref="BC33:BC58" si="26">AJ33*24</f>
+        <v>0</v>
+      </c>
+      <c r="BD33" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BE33" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AY33" s="30">
-        <f t="shared" si="14"/>
-        <v>0.28149123600000003</v>
-      </c>
-      <c r="AZ33" s="30">
-        <f>AP33+SUM(AG33:AI33,AK33:AL33)-((AO33+1)*D33)</f>
-        <v>1620</v>
-      </c>
-      <c r="BA33" s="31" t="e">
+        <v/>
+      </c>
+      <c r="BF33" s="58" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="BG33" s="31">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="BH33" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB33" s="31">
-        <f t="shared" ref="BB33:BB58" si="15">AK33/AP33</f>
-        <v>0</v>
-      </c>
-      <c r="BC33" s="31">
-        <f t="shared" ref="BC33:BC58" si="16">AJ33*24</f>
-        <v>0</v>
-      </c>
-      <c r="BD33" s="31">
-        <f>IF(B33="Python",AU33*AZ33/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BE33" s="61" t="str">
-        <f>IF(B33="Julia",AV33*AZ33/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BF33" s="58" t="str">
-        <f>IF(B33="No MPC", AT33*J33*AZ33/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG33" s="31">
-        <f>IF(P33&lt;1.5, IF(B33&lt;&gt;"Julia",((3-P33)*AZ33)/400, ""),0)</f>
-        <v>12.15</v>
-      </c>
-      <c r="BH33" s="31" t="str">
-        <f>IF(B33="Julia",AW33*AZ33,"")</f>
         <v/>
       </c>
       <c r="BI33" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ33" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK33" s="48">
-        <f t="shared" si="8"/>
-        <v>12.15</v>
+        <f t="shared" si="12"/>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:63" x14ac:dyDescent="0.3">
@@ -7752,39 +7956,105 @@
         <v>2716.05</v>
       </c>
       <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="29"/>
-      <c r="M34" s="29"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="29"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="29"/>
-      <c r="S34" s="29"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-      <c r="W34" s="29"/>
-      <c r="X34" s="29"/>
-      <c r="Y34" s="29"/>
-      <c r="Z34" s="29"/>
-      <c r="AA34" s="29"/>
-      <c r="AB34" s="25"/>
-      <c r="AC34" s="15"/>
-      <c r="AD34" s="30"/>
-      <c r="AE34" s="30"/>
-      <c r="AF34" s="30"/>
-      <c r="AG34" s="30"/>
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
+      <c r="H34" s="29">
+        <v>2325.9450000000002</v>
+      </c>
+      <c r="I34" s="29">
+        <v>21.8</v>
+      </c>
+      <c r="J34" s="29">
+        <v>20.9</v>
+      </c>
+      <c r="K34" s="29">
+        <v>95.8</v>
+      </c>
+      <c r="L34" s="29">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M34" s="29">
+        <v>349</v>
+      </c>
+      <c r="N34" s="29">
+        <v>1.44</v>
+      </c>
+      <c r="O34" s="29">
+        <v>0.27</v>
+      </c>
+      <c r="P34" s="29">
+        <v>1.33</v>
+      </c>
+      <c r="Q34" s="29">
+        <v>0.16</v>
+      </c>
+      <c r="R34" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="S34" s="29">
+        <v>1.83</v>
+      </c>
+      <c r="T34" s="29">
+        <v>7.2539999999999996</v>
+      </c>
+      <c r="U34" s="29">
+        <v>131.6</v>
+      </c>
+      <c r="V34" s="29">
+        <v>12.7</v>
+      </c>
+      <c r="W34" s="29">
+        <v>2.08</v>
+      </c>
+      <c r="X34" s="29">
+        <v>149.1</v>
+      </c>
+      <c r="Y34" s="29">
+        <v>56.7</v>
+      </c>
+      <c r="Z34" s="29">
+        <v>115.4</v>
+      </c>
+      <c r="AA34" s="29">
+        <v>10.3</v>
+      </c>
+      <c r="AB34" s="25">
+        <v>7.2949999999999999</v>
+      </c>
+      <c r="AC34" s="15">
+        <v>299</v>
+      </c>
+      <c r="AD34" s="30">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="AE34" s="30">
+        <v>7.3</v>
+      </c>
+      <c r="AF34" s="30">
+        <v>34</v>
+      </c>
+      <c r="AG34" s="30">
+        <v>24.77</v>
+      </c>
+      <c r="AH34" s="30">
+        <v>3.99</v>
+      </c>
+      <c r="AI34" s="30">
+        <v>8</v>
+      </c>
       <c r="AJ34" s="30"/>
-      <c r="AK34" s="30"/>
-      <c r="AL34" s="30"/>
-      <c r="AM34" s="30"/>
-      <c r="AN34" s="30"/>
+      <c r="AK34" s="30">
+        <v>107</v>
+      </c>
+      <c r="AL34" s="30">
+        <v>32</v>
+      </c>
+      <c r="AM34" s="30">
+        <f t="shared" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="AN34" s="30">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
       <c r="AO34" s="43">
         <v>15</v>
       </c>
@@ -7807,59 +8077,59 @@
       <c r="AV34" s="30"/>
       <c r="AW34" s="40"/>
       <c r="AX34" s="15">
+        <f t="shared" si="4"/>
+        <v>1.5012553599999999E-2</v>
+      </c>
+      <c r="AY34" s="30">
+        <f t="shared" si="21"/>
+        <v>0.28688002559999998</v>
+      </c>
+      <c r="AZ34" s="30">
+        <f t="shared" si="16"/>
+        <v>1795.76</v>
+      </c>
+      <c r="BA34" s="31">
+        <f t="shared" si="6"/>
+        <v>5.9584799750523457E-2</v>
+      </c>
+      <c r="BB34" s="31">
+        <f t="shared" si="25"/>
+        <v>6.2941176470588237E-2</v>
+      </c>
+      <c r="BC34" s="31">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BD34" s="31" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="BE34" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AY34" s="30">
-        <f t="shared" si="14"/>
-        <v>0.28688002559999998</v>
-      </c>
-      <c r="AZ34" s="30">
-        <f>AP34+SUM(AG34:AI34,AK34:AL34)-((AO34+1)*D34)</f>
-        <v>1620</v>
-      </c>
-      <c r="BA34" s="31" t="e">
+      <c r="BF34" s="58" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="BG34" s="31" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="BH34" s="31">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB34" s="31">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="BC34" s="31">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="BD34" s="31" t="str">
-        <f>IF(B34="Python",AU34*AZ34/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BE34" s="61">
-        <f>IF(B34="Julia",AV34*AZ34/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BF34" s="58" t="str">
-        <f>IF(B34="No MPC", AT34*J34*AZ34/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BG34" s="31" t="str">
-        <f>IF(P34&lt;1.5, IF(B34&lt;&gt;"Julia",((3-P34)*AZ34)/400, ""),0)</f>
-        <v/>
-      </c>
-      <c r="BH34" s="31">
-        <f>IF(B34="Julia",AW34*AZ34,"")</f>
         <v>0</v>
       </c>
       <c r="BI34" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ34" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK34" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -7882,38 +8152,102 @@
       </c>
       <c r="G35" s="11"/>
       <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
-      <c r="U35" s="11"/>
-      <c r="V35" s="11"/>
-      <c r="W35" s="11"/>
-      <c r="X35" s="11"/>
-      <c r="Y35" s="11"/>
-      <c r="Z35" s="11"/>
-      <c r="AA35" s="11"/>
-      <c r="AB35" s="26"/>
-      <c r="AC35" s="16"/>
-      <c r="AD35" s="17"/>
-      <c r="AE35" s="17"/>
-      <c r="AF35" s="17"/>
-      <c r="AG35" s="17"/>
-      <c r="AH35" s="17"/>
-      <c r="AI35" s="17"/>
+      <c r="I35" s="11">
+        <v>25.2</v>
+      </c>
+      <c r="J35" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="K35" s="11">
+        <v>96.9</v>
+      </c>
+      <c r="L35" s="11">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="M35" s="11">
+        <v>329</v>
+      </c>
+      <c r="N35" s="11">
+        <v>1.47</v>
+      </c>
+      <c r="O35" s="11">
+        <v>0.26</v>
+      </c>
+      <c r="P35" s="11">
+        <v>1.21</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="R35" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="S35" s="11">
+        <v>1</v>
+      </c>
+      <c r="T35" s="11">
+        <v>7.2539999999999996</v>
+      </c>
+      <c r="U35" s="11">
+        <v>133.6</v>
+      </c>
+      <c r="V35" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="W35" s="11">
+        <v>2.06</v>
+      </c>
+      <c r="X35" s="11">
+        <v>143.69999999999999</v>
+      </c>
+      <c r="Y35" s="11">
+        <v>57.6</v>
+      </c>
+      <c r="Z35" s="11">
+        <v>117.1</v>
+      </c>
+      <c r="AA35" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="AB35" s="26">
+        <v>7.2960000000000003</v>
+      </c>
+      <c r="AC35" s="16">
+        <v>301</v>
+      </c>
+      <c r="AD35" s="17">
+        <v>0.495</v>
+      </c>
+      <c r="AE35" s="17">
+        <v>7.3</v>
+      </c>
+      <c r="AF35" s="17">
+        <v>34</v>
+      </c>
+      <c r="AG35" s="17">
+        <v>21.77</v>
+      </c>
+      <c r="AH35" s="17">
+        <v>28</v>
+      </c>
+      <c r="AI35" s="17">
+        <v>8</v>
+      </c>
       <c r="AJ35" s="17"/>
-      <c r="AK35" s="17"/>
-      <c r="AL35" s="17"/>
-      <c r="AM35" s="17"/>
-      <c r="AN35" s="17"/>
+      <c r="AK35" s="17">
+        <v>111</v>
+      </c>
+      <c r="AL35" s="17">
+        <v>43</v>
+      </c>
+      <c r="AM35" s="17">
+        <f t="shared" si="22"/>
+        <v>30</v>
+      </c>
+      <c r="AN35" s="17">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
       <c r="AO35" s="44">
         <v>15</v>
       </c>
@@ -7936,59 +8270,59 @@
       <c r="AV35" s="17"/>
       <c r="AW35" s="41"/>
       <c r="AX35" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1.7951346E-2</v>
       </c>
       <c r="AY35" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0.30660534719999999</v>
       </c>
       <c r="AZ35" s="17">
-        <f>AP35+SUM(AG35:AI35,AK35:AL35)-((AO35+1)*D35)</f>
-        <v>1620</v>
-      </c>
-      <c r="BA35" s="18" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <f t="shared" si="16"/>
+        <v>1831.77</v>
+      </c>
+      <c r="BA35" s="18">
+        <f t="shared" si="6"/>
+        <v>6.0597127368610691E-2</v>
       </c>
       <c r="BB35" s="18">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="25"/>
+        <v>6.5294117647058822E-2</v>
       </c>
       <c r="BC35" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD35" s="18" t="str">
-        <f>IF(B35="Python",AU35*AZ35/24/60,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="BE35" s="18">
-        <f>IF(B35="Julia",AV35*AZ35/24/60,"")</f>
+        <f t="shared" ref="BE35:BE70" si="27">IF(B35="Julia",AV35*AZ35/24/60,"")</f>
         <v>0</v>
       </c>
       <c r="BF35" s="59" t="str">
-        <f>IF(B35="No MPC", AT35*J35*AZ35/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG35" s="18" t="str">
-        <f>IF(P35&lt;1.5, IF(B35&lt;&gt;"Julia",((3-P35)*AZ35)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH35" s="18">
-        <f>IF(B35="Julia",AW35*AZ35,"")</f>
+        <f t="shared" ref="BH35:BH70" si="28">IF(B35="Julia",AW35*AZ35,"")</f>
         <v>0</v>
       </c>
       <c r="BI35" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ35" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK35" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -8065,59 +8399,59 @@
       <c r="AV36" s="13"/>
       <c r="AW36" s="39"/>
       <c r="AX36" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY36" s="13">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>0.40603036800000003</v>
       </c>
       <c r="AZ36" s="13">
-        <f>AP36+SUM(AG36:AI36,AK36:AL36)-((AO36+1)*D36)</f>
+        <f t="shared" si="16"/>
         <v>1604</v>
       </c>
       <c r="BA36" s="14" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB36" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC36" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD36" s="14" t="str">
-        <f>IF(B36="Python",AU36*AZ36/24/60,"")</f>
+        <f t="shared" ref="BD36:BD70" si="29">IF(B36="Python",AU36*AZ36/24/60,"")</f>
         <v/>
       </c>
       <c r="BE36" s="14" t="str">
-        <f>IF(B36="Julia",AV36*AZ36/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF36" s="57">
-        <f>IF(B36="No MPC", AT36*J36*AZ36/1000,"")</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="BG36" s="14">
-        <f>IF(P36&lt;1.5, IF(B36&lt;&gt;"Julia",((3-P36)*AZ36)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>12.03</v>
       </c>
       <c r="BH36" s="14" t="str">
-        <f>IF(B36="Julia",AW36*AZ36,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI36" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ36" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK36" s="50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>12.03</v>
       </c>
     </row>
@@ -8194,59 +8528,59 @@
       <c r="AV37" s="30"/>
       <c r="AW37" s="40"/>
       <c r="AX37" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY37" s="30">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>0.33818231999999998</v>
       </c>
       <c r="AZ37" s="30">
-        <f>AP37+SUM(AG37:AI37,AK37:AL37)-((AO37+1)*D37)</f>
+        <f t="shared" si="16"/>
         <v>1604</v>
       </c>
       <c r="BA37" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB37" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC37" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD37" s="31">
-        <f>IF(B37="Python",AU37*AZ37/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE37" s="61" t="str">
-        <f>IF(B37="Julia",AV37*AZ37/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF37" s="58" t="str">
-        <f>IF(B37="No MPC", AT37*J37*AZ37/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG37" s="31">
-        <f>IF(P37&lt;1.5, IF(B37&lt;&gt;"Julia",((3-P37)*AZ37)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>12.03</v>
       </c>
       <c r="BH37" s="31" t="str">
-        <f>IF(B37="Julia",AW37*AZ37,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI37" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ37" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK37" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>12.03</v>
       </c>
     </row>
@@ -8323,59 +8657,59 @@
       <c r="AV38" s="30"/>
       <c r="AW38" s="40"/>
       <c r="AX38" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY38" s="30">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>0.34864128</v>
       </c>
       <c r="AZ38" s="30">
-        <f>AP38+SUM(AG38:AI38,AK38:AL38)-((AO38+1)*D38)</f>
+        <f t="shared" si="16"/>
         <v>1604</v>
       </c>
       <c r="BA38" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB38" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC38" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD38" s="31">
-        <f>IF(B38="Python",AU38*AZ38/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE38" s="61" t="str">
-        <f>IF(B38="Julia",AV38*AZ38/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF38" s="58" t="str">
-        <f>IF(B38="No MPC", AT38*J38*AZ38/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG38" s="31">
-        <f>IF(P38&lt;1.5, IF(B38&lt;&gt;"Julia",((3-P38)*AZ38)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>12.03</v>
       </c>
       <c r="BH38" s="31" t="str">
-        <f>IF(B38="Julia",AW38*AZ38,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI38" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ38" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK38" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>12.03</v>
       </c>
     </row>
@@ -8452,59 +8786,59 @@
       <c r="AV39" s="30"/>
       <c r="AW39" s="40"/>
       <c r="AX39" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY39" s="30">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>0.36030128639999998</v>
       </c>
       <c r="AZ39" s="30">
-        <f>AP39+SUM(AG39:AI39,AK39:AL39)-((AO39+1)*D39)</f>
+        <f t="shared" si="16"/>
         <v>1604</v>
       </c>
       <c r="BA39" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB39" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC39" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD39" s="31" t="str">
-        <f>IF(B39="Python",AU39*AZ39/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE39" s="61">
-        <f>IF(B39="Julia",AV39*AZ39/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF39" s="58" t="str">
-        <f>IF(B39="No MPC", AT39*J39*AZ39/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG39" s="31" t="str">
-        <f>IF(P39&lt;1.5, IF(B39&lt;&gt;"Julia",((3-P39)*AZ39)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH39" s="31">
-        <f>IF(B39="Julia",AW39*AZ39,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI39" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ39" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK39" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -8581,59 +8915,59 @@
       <c r="AV40" s="17"/>
       <c r="AW40" s="41"/>
       <c r="AX40" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY40" s="17">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>0.430832304</v>
       </c>
       <c r="AZ40" s="17">
-        <f>AP40+SUM(AG40:AI40,AK40:AL40)-((AO40+1)*D40)</f>
+        <f t="shared" si="16"/>
         <v>1604</v>
       </c>
       <c r="BA40" s="18" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB40" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC40" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD40" s="18" t="str">
-        <f>IF(B40="Python",AU40*AZ40/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE40" s="18">
-        <f>IF(B40="Julia",AV40*AZ40/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF40" s="59" t="str">
-        <f>IF(B40="No MPC", AT40*J40*AZ40/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG40" s="18" t="str">
-        <f>IF(P40&lt;1.5, IF(B40&lt;&gt;"Julia",((3-P40)*AZ40)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH40" s="18">
-        <f>IF(B40="Julia",AW40*AZ40,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI40" s="47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ40" s="67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK40" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -8710,59 +9044,59 @@
       <c r="AV41" s="13"/>
       <c r="AW41" s="39"/>
       <c r="AX41" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY41" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ41" s="13">
-        <f>AP41+SUM(AG41:AI41,AK41:AL41)-((AO41+1)*D41)</f>
+        <f t="shared" ref="AZ41:AZ70" si="30">AP41+SUM(AG41:AI41,AK41:AL41)-((AO41+1)*D41)</f>
         <v>1588</v>
       </c>
       <c r="BA41" s="14" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB41" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC41" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD41" s="14" t="str">
-        <f>IF(B41="Python",AU41*AZ41/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE41" s="14" t="str">
-        <f>IF(B41="Julia",AV41*AZ41/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF41" s="57">
-        <f>IF(B41="No MPC", AT41*J41*AZ41/1000,"")</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="BG41" s="14">
-        <f>IF(P41&lt;1.5, IF(B41&lt;&gt;"Julia",((3-P41)*AZ41)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.91</v>
       </c>
       <c r="BH41" s="14" t="str">
-        <f>IF(B41="Julia",AW41*AZ41,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI41" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ41" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK41" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.91</v>
       </c>
     </row>
@@ -8839,59 +9173,59 @@
       <c r="AV42" s="30"/>
       <c r="AW42" s="40"/>
       <c r="AX42" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY42" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ42" s="30">
-        <f>AP42+SUM(AG42:AI42,AK42:AL42)-((AO42+1)*D42)</f>
+        <f t="shared" si="30"/>
         <v>1588</v>
       </c>
       <c r="BA42" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB42" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC42" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD42" s="31">
-        <f>IF(B42="Python",AU42*AZ42/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE42" s="61" t="str">
-        <f>IF(B42="Julia",AV42*AZ42/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF42" s="58" t="str">
-        <f>IF(B42="No MPC", AT42*J42*AZ42/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG42" s="31">
-        <f>IF(P42&lt;1.5, IF(B42&lt;&gt;"Julia",((3-P42)*AZ42)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.91</v>
       </c>
       <c r="BH42" s="31" t="str">
-        <f>IF(B42="Julia",AW42*AZ42,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI42" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ42" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK42" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.91</v>
       </c>
     </row>
@@ -8968,59 +9302,59 @@
       <c r="AV43" s="30"/>
       <c r="AW43" s="40"/>
       <c r="AX43" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY43" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ43" s="30">
-        <f>AP43+SUM(AG43:AI43,AK43:AL43)-((AO43+1)*D43)</f>
+        <f t="shared" si="30"/>
         <v>1588</v>
       </c>
       <c r="BA43" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB43" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC43" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD43" s="31">
-        <f>IF(B43="Python",AU43*AZ43/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE43" s="61" t="str">
-        <f>IF(B43="Julia",AV43*AZ43/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF43" s="58" t="str">
-        <f>IF(B43="No MPC", AT43*J43*AZ43/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG43" s="31">
-        <f>IF(P43&lt;1.5, IF(B43&lt;&gt;"Julia",((3-P43)*AZ43)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.91</v>
       </c>
       <c r="BH43" s="31" t="str">
-        <f>IF(B43="Julia",AW43*AZ43,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI43" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ43" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK43" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.91</v>
       </c>
     </row>
@@ -9097,59 +9431,59 @@
       <c r="AV44" s="30"/>
       <c r="AW44" s="40"/>
       <c r="AX44" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY44" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ44" s="30">
-        <f>AP44+SUM(AG44:AI44,AK44:AL44)-((AO44+1)*D44)</f>
+        <f t="shared" si="30"/>
         <v>1588</v>
       </c>
       <c r="BA44" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB44" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC44" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD44" s="31" t="str">
-        <f>IF(B44="Python",AU44*AZ44/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE44" s="61">
-        <f>IF(B44="Julia",AV44*AZ44/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF44" s="58" t="str">
-        <f>IF(B44="No MPC", AT44*J44*AZ44/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG44" s="31" t="str">
-        <f>IF(P44&lt;1.5, IF(B44&lt;&gt;"Julia",((3-P44)*AZ44)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH44" s="31">
-        <f>IF(B44="Julia",AW44*AZ44,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI44" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ44" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK44" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -9226,59 +9560,59 @@
       <c r="AV45" s="17"/>
       <c r="AW45" s="41"/>
       <c r="AX45" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY45" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ45" s="17">
-        <f>AP45+SUM(AG45:AI45,AK45:AL45)-((AO45+1)*D45)</f>
+        <f t="shared" si="30"/>
         <v>1588</v>
       </c>
       <c r="BA45" s="18" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB45" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC45" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD45" s="18" t="str">
-        <f>IF(B45="Python",AU45*AZ45/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE45" s="18">
-        <f>IF(B45="Julia",AV45*AZ45/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF45" s="59" t="str">
-        <f>IF(B45="No MPC", AT45*J45*AZ45/1000,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="BG45" s="18" t="str">
-        <f>IF(P45&lt;1.5, IF(B45&lt;&gt;"Julia",((3-P45)*AZ45)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH45" s="18">
-        <f>IF(B45="Julia",AW45*AZ45,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI45" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ45" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK45" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -9355,59 +9689,59 @@
       <c r="AV46" s="13"/>
       <c r="AW46" s="39"/>
       <c r="AX46" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY46" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ46" s="13">
-        <f>AP46+SUM(AG46:AI46,AK46:AL46)-((AO46+1)*D46)</f>
+        <f t="shared" si="30"/>
         <v>1572</v>
       </c>
       <c r="BA46" s="14" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB46" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC46" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD46" s="14" t="str">
-        <f>IF(B46="Python",AU46*AZ46/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE46" s="14" t="str">
-        <f>IF(B46="Julia",AV46*AZ46/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF46" s="57">
-        <f>IF(B46="No MPC", AT46*J46*AZ46/1000,"")</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="BG46" s="14">
-        <f>IF(P46&lt;1.5, IF(B46&lt;&gt;"Julia",((3-P46)*AZ46)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.79</v>
       </c>
       <c r="BH46" s="14" t="str">
-        <f>IF(B46="Julia",AW46*AZ46,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI46" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ46" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK46" s="50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.79</v>
       </c>
     </row>
@@ -9484,59 +9818,59 @@
       <c r="AV47" s="30"/>
       <c r="AW47" s="40"/>
       <c r="AX47" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY47" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ47" s="30">
-        <f>AP47+SUM(AG47:AI47,AK47:AL47)-((AO47+1)*D47)</f>
+        <f t="shared" si="30"/>
         <v>1572</v>
       </c>
       <c r="BA47" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB47" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC47" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD47" s="31">
-        <f>IF(B47="Python",AU47*AZ47/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE47" s="61" t="str">
-        <f>IF(B47="Julia",AV47*AZ47/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF47" s="58" t="str">
-        <f>IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
+        <f t="shared" ref="BF47:BF70" si="31">IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
         <v/>
       </c>
       <c r="BG47" s="31">
-        <f>IF(P47&lt;1.5, IF(B47&lt;&gt;"Julia",((3-P47)*AZ47)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.79</v>
       </c>
       <c r="BH47" s="31" t="str">
-        <f>IF(B47="Julia",AW47*AZ47,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI47" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ47" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK47" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.79</v>
       </c>
     </row>
@@ -9613,59 +9947,59 @@
       <c r="AV48" s="30"/>
       <c r="AW48" s="40"/>
       <c r="AX48" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY48" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ48" s="30">
-        <f>AP48+SUM(AG48:AI48,AK48:AL48)-((AO48+1)*D48)</f>
+        <f t="shared" si="30"/>
         <v>1572</v>
       </c>
       <c r="BA48" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB48" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC48" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD48" s="31">
-        <f>IF(B48="Python",AU48*AZ48/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE48" s="61" t="str">
-        <f>IF(B48="Julia",AV48*AZ48/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF48" s="58" t="str">
-        <f>IF(B48="No MPC", AT48*J48*AZ48/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG48" s="31">
-        <f>IF(P48&lt;1.5, IF(B48&lt;&gt;"Julia",((3-P48)*AZ48)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.79</v>
       </c>
       <c r="BH48" s="31" t="str">
-        <f>IF(B48="Julia",AW48*AZ48,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI48" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ48" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK48" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.79</v>
       </c>
     </row>
@@ -9742,59 +10076,59 @@
       <c r="AV49" s="30"/>
       <c r="AW49" s="40"/>
       <c r="AX49" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY49" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ49" s="30">
-        <f>AP49+SUM(AG49:AI49,AK49:AL49)-((AO49+1)*D49)</f>
+        <f t="shared" si="30"/>
         <v>1572</v>
       </c>
       <c r="BA49" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB49" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC49" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD49" s="31" t="str">
-        <f>IF(B49="Python",AU49*AZ49/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE49" s="61">
-        <f>IF(B49="Julia",AV49*AZ49/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF49" s="58" t="str">
-        <f>IF(B49="No MPC", AT49*J49*AZ49/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG49" s="31" t="str">
-        <f>IF(P49&lt;1.5, IF(B49&lt;&gt;"Julia",((3-P49)*AZ49)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH49" s="31">
-        <f>IF(B49="Julia",AW49*AZ49,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI49" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ49" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK49" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -9871,59 +10205,59 @@
       <c r="AV50" s="17"/>
       <c r="AW50" s="41"/>
       <c r="AX50" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY50" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ50" s="17">
-        <f>AP50+SUM(AG50:AI50,AK50:AL50)-((AO50+1)*D50)</f>
+        <f t="shared" si="30"/>
         <v>1572</v>
       </c>
       <c r="BA50" s="18" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB50" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC50" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD50" s="18" t="str">
-        <f>IF(B50="Python",AU50*AZ50/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE50" s="18">
-        <f>IF(B50="Julia",AV50*AZ50/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF50" s="59" t="str">
-        <f>IF(B50="No MPC", AT50*J50*AZ50/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG50" s="18" t="str">
-        <f>IF(P50&lt;1.5, IF(B50&lt;&gt;"Julia",((3-P50)*AZ50)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH50" s="18">
-        <f>IF(B50="Julia",AW50*AZ50,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI50" s="47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ50" s="67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK50" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -10000,59 +10334,59 @@
       <c r="AV51" s="13"/>
       <c r="AW51" s="39"/>
       <c r="AX51" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY51" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ51" s="13">
-        <f>AP51+SUM(AG51:AI51,AK51:AL51)-((AO51+1)*D51)</f>
+        <f t="shared" si="30"/>
         <v>1556</v>
       </c>
       <c r="BA51" s="14" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB51" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC51" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD51" s="14" t="str">
-        <f>IF(B51="Python",AU51*AZ51/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE51" s="14" t="str">
-        <f>IF(B51="Julia",AV51*AZ51/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF51" s="57">
-        <f>IF(B51="No MPC", AT51*J51*AZ51/1000,"")</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BG51" s="14">
-        <f>IF(P51&lt;1.5, IF(B51&lt;&gt;"Julia",((3-P51)*AZ51)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.67</v>
       </c>
       <c r="BH51" s="14" t="str">
-        <f>IF(B51="Julia",AW51*AZ51,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI51" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ51" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK51" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.67</v>
       </c>
     </row>
@@ -10129,59 +10463,59 @@
       <c r="AV52" s="30"/>
       <c r="AW52" s="40"/>
       <c r="AX52" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY52" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ52" s="30">
-        <f>AP52+SUM(AG52:AI52,AK52:AL52)-((AO52+1)*D52)</f>
+        <f t="shared" si="30"/>
         <v>1556</v>
       </c>
       <c r="BA52" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB52" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC52" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD52" s="31">
-        <f>IF(B52="Python",AU52*AZ52/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE52" s="61" t="str">
-        <f>IF(B52="Julia",AV52*AZ52/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF52" s="58" t="str">
-        <f>IF(B52="No MPC", AT52*J52*AZ52/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG52" s="31">
-        <f>IF(P52&lt;1.5, IF(B52&lt;&gt;"Julia",((3-P52)*AZ52)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.67</v>
       </c>
       <c r="BH52" s="31" t="str">
-        <f>IF(B52="Julia",AW52*AZ52,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI52" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ52" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK52" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.67</v>
       </c>
     </row>
@@ -10258,59 +10592,59 @@
       <c r="AV53" s="30"/>
       <c r="AW53" s="40"/>
       <c r="AX53" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY53" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ53" s="30">
-        <f>AP53+SUM(AG53:AI53,AK53:AL53)-((AO53+1)*D53)</f>
+        <f t="shared" si="30"/>
         <v>1556</v>
       </c>
       <c r="BA53" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB53" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC53" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD53" s="31">
-        <f>IF(B53="Python",AU53*AZ53/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE53" s="61" t="str">
-        <f>IF(B53="Julia",AV53*AZ53/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF53" s="58" t="str">
-        <f>IF(B53="No MPC", AT53*J53*AZ53/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG53" s="31">
-        <f>IF(P53&lt;1.5, IF(B53&lt;&gt;"Julia",((3-P53)*AZ53)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.67</v>
       </c>
       <c r="BH53" s="31" t="str">
-        <f>IF(B53="Julia",AW53*AZ53,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI53" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ53" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK53" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.67</v>
       </c>
     </row>
@@ -10387,59 +10721,59 @@
       <c r="AV54" s="30"/>
       <c r="AW54" s="40"/>
       <c r="AX54" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY54" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ54" s="30">
-        <f>AP54+SUM(AG54:AI54,AK54:AL54)-((AO54+1)*D54)</f>
+        <f t="shared" si="30"/>
         <v>1556</v>
       </c>
       <c r="BA54" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB54" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC54" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD54" s="31" t="str">
-        <f>IF(B54="Python",AU54*AZ54/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE54" s="61">
-        <f>IF(B54="Julia",AV54*AZ54/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF54" s="58" t="str">
-        <f>IF(B54="No MPC", AT54*J54*AZ54/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG54" s="31" t="str">
-        <f>IF(P54&lt;1.5, IF(B54&lt;&gt;"Julia",((3-P54)*AZ54)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH54" s="31">
-        <f>IF(B54="Julia",AW54*AZ54,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI54" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ54" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK54" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -10516,59 +10850,59 @@
       <c r="AV55" s="17"/>
       <c r="AW55" s="41"/>
       <c r="AX55" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY55" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ55" s="17">
-        <f>AP55+SUM(AG55:AI55,AK55:AL55)-((AO55+1)*D55)</f>
+        <f t="shared" si="30"/>
         <v>1556</v>
       </c>
       <c r="BA55" s="18" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB55" s="18">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC55" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD55" s="18" t="str">
-        <f>IF(B55="Python",AU55*AZ55/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE55" s="18">
-        <f>IF(B55="Julia",AV55*AZ55/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF55" s="59" t="str">
-        <f>IF(B55="No MPC", AT55*J55*AZ55/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG55" s="18" t="str">
-        <f>IF(P55&lt;1.5, IF(B55&lt;&gt;"Julia",((3-P55)*AZ55)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH55" s="18">
-        <f>IF(B55="Julia",AW55*AZ55,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI55" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ55" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK55" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -10645,59 +10979,59 @@
       <c r="AV56" s="13"/>
       <c r="AW56" s="39"/>
       <c r="AX56" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY56" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ56" s="13">
-        <f>AP56+SUM(AG56:AI56,AK56:AL56)-((AO56+1)*D56)</f>
+        <f t="shared" si="30"/>
         <v>1540</v>
       </c>
       <c r="BA56" s="14" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB56" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC56" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD56" s="14" t="str">
-        <f>IF(B56="Python",AU56*AZ56/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE56" s="14" t="str">
-        <f>IF(B56="Julia",AV56*AZ56/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF56" s="57">
-        <f>IF(B56="No MPC", AT56*J56*AZ56/1000,"")</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BG56" s="14">
-        <f>IF(P56&lt;1.5, IF(B56&lt;&gt;"Julia",((3-P56)*AZ56)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.55</v>
       </c>
       <c r="BH56" s="14" t="str">
-        <f>IF(B56="Julia",AW56*AZ56,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI56" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ56" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK56" s="50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.55</v>
       </c>
     </row>
@@ -10774,59 +11108,59 @@
       <c r="AV57" s="30"/>
       <c r="AW57" s="40"/>
       <c r="AX57" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY57" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ57" s="30">
-        <f>AP57+SUM(AG57:AI57,AK57:AL57)-((AO57+1)*D57)</f>
+        <f t="shared" si="30"/>
         <v>1540</v>
       </c>
       <c r="BA57" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB57" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC57" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD57" s="31">
-        <f>IF(B57="Python",AU57*AZ57/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE57" s="61" t="str">
-        <f>IF(B57="Julia",AV57*AZ57/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF57" s="58" t="str">
-        <f>IF(B57="No MPC", AT57*J57*AZ57/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG57" s="31">
-        <f>IF(P57&lt;1.5, IF(B57&lt;&gt;"Julia",((3-P57)*AZ57)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.55</v>
       </c>
       <c r="BH57" s="31" t="str">
-        <f>IF(B57="Julia",AW57*AZ57,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI57" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ57" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK57" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.55</v>
       </c>
     </row>
@@ -10903,59 +11237,59 @@
       <c r="AV58" s="30"/>
       <c r="AW58" s="40"/>
       <c r="AX58" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY58" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ58" s="30">
-        <f>AP58+SUM(AG58:AI58,AK58:AL58)-((AO58+1)*D58)</f>
+        <f t="shared" si="30"/>
         <v>1540</v>
       </c>
       <c r="BA58" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB58" s="31">
-        <f t="shared" si="15"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC58" s="31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD58" s="31">
-        <f>IF(B58="Python",AU58*AZ58/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE58" s="61" t="str">
-        <f>IF(B58="Julia",AV58*AZ58/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF58" s="58" t="str">
-        <f>IF(B58="No MPC", AT58*J58*AZ58/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG58" s="31">
-        <f>IF(P58&lt;1.5, IF(B58&lt;&gt;"Julia",((3-P58)*AZ58)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.55</v>
       </c>
       <c r="BH58" s="31" t="str">
-        <f>IF(B58="Julia",AW58*AZ58,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI58" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ58" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK58" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>11.55</v>
       </c>
     </row>
@@ -11032,59 +11366,59 @@
       <c r="AV59" s="30"/>
       <c r="AW59" s="40"/>
       <c r="AX59" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY59" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ59" s="30">
-        <f>AP59+SUM(AG59:AI59,AK59:AL59)-((AO59+1)*D59)</f>
+        <f t="shared" si="30"/>
         <v>1540</v>
       </c>
       <c r="BA59" s="31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="BB59" s="31">
-        <f t="shared" ref="BB59:BB70" si="17">AK59/AP59</f>
+        <f t="shared" ref="BB59:BB70" si="32">AK59/AP59</f>
         <v>0</v>
       </c>
       <c r="BC59" s="31">
-        <f t="shared" ref="BC59:BC70" si="18">AJ59*24</f>
+        <f t="shared" ref="BC59:BC70" si="33">AJ59*24</f>
         <v>0</v>
       </c>
       <c r="BD59" s="31" t="str">
-        <f>IF(B59="Python",AU59*AZ59/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE59" s="61">
-        <f>IF(B59="Julia",AV59*AZ59/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF59" s="58" t="str">
-        <f>IF(B59="No MPC", AT59*J59*AZ59/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG59" s="31" t="str">
-        <f>IF(P59&lt;1.5, IF(B59&lt;&gt;"Julia",((3-P59)*AZ59)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH59" s="31">
-        <f>IF(B59="Julia",AW59*AZ59,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI59" s="46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BJ59" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BK59" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -11161,59 +11495,59 @@
       <c r="AV60" s="17"/>
       <c r="AW60" s="41"/>
       <c r="AX60" s="16">
-        <f t="shared" ref="AX60:AX70" si="19">AT60*J60*AZ60/1000</f>
+        <f t="shared" ref="AX60:AX70" si="34">AT60*J60*AZ60/1000</f>
         <v>0</v>
       </c>
       <c r="AY60" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ60" s="17">
-        <f>AP60+SUM(AG60:AI60,AK60:AL60)-((AO60+1)*D60)</f>
+        <f t="shared" si="30"/>
         <v>1540</v>
       </c>
       <c r="BA60" s="18" t="e">
-        <f t="shared" ref="BA60:BA70" si="20">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
+        <f t="shared" ref="BA60:BA70" si="35">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
         <v>#N/A</v>
       </c>
       <c r="BB60" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC60" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD60" s="18" t="str">
-        <f>IF(B60="Python",AU60*AZ60/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE60" s="18">
-        <f>IF(B60="Julia",AV60*AZ60/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF60" s="59" t="str">
-        <f>IF(B60="No MPC", AT60*J60*AZ60/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG60" s="18" t="str">
-        <f>IF(P60&lt;1.5, IF(B60&lt;&gt;"Julia",((3-P60)*AZ60)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH60" s="18">
-        <f>IF(B60="Julia",AW60*AZ60,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI60" s="47">
-        <f t="shared" ref="BI60:BI70" si="21">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
+        <f t="shared" ref="BI60:BI70" si="36">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BJ60" s="67">
-        <f t="shared" ref="BJ60:BJ65" si="22">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
+        <f t="shared" ref="BJ60:BJ65" si="37">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
         <v>0</v>
       </c>
       <c r="BK60" s="49">
-        <f t="shared" ref="BK60:BK70" si="23">IF(BG60&lt;&gt;"",BG60,BH60)</f>
+        <f t="shared" ref="BK60:BK70" si="38">IF(BG60&lt;&gt;"",BG60,BH60)</f>
         <v>0</v>
       </c>
     </row>
@@ -11290,59 +11624,59 @@
       <c r="AV61" s="13"/>
       <c r="AW61" s="39"/>
       <c r="AX61" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY61" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ61" s="13">
-        <f>AP61+SUM(AG61:AI61,AK61:AL61)-((AO61+1)*D61)</f>
+        <f t="shared" si="30"/>
         <v>1524</v>
       </c>
       <c r="BA61" s="14" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB61" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC61" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD61" s="14" t="str">
-        <f>IF(B61="Python",AU61*AZ61/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE61" s="14" t="str">
-        <f>IF(B61="Julia",AV61*AZ61/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF61" s="57">
-        <f>IF(B61="No MPC", AT61*J61*AZ61/1000,"")</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BG61" s="14">
-        <f>IF(P61&lt;1.5, IF(B61&lt;&gt;"Julia",((3-P61)*AZ61)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.43</v>
       </c>
       <c r="BH61" s="14" t="str">
-        <f>IF(B61="Julia",AW61*AZ61,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI61" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ61" s="66">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BK61" s="48">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>11.43</v>
       </c>
     </row>
@@ -11419,59 +11753,59 @@
       <c r="AV62" s="30"/>
       <c r="AW62" s="40"/>
       <c r="AX62" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY62" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ62" s="30">
-        <f>AP62+SUM(AG62:AI62,AK62:AL62)-((AO62+1)*D62)</f>
+        <f t="shared" si="30"/>
         <v>1524</v>
       </c>
       <c r="BA62" s="31" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB62" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC62" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD62" s="31">
-        <f>IF(B62="Python",AU62*AZ62/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE62" s="61" t="str">
-        <f>IF(B62="Julia",AV62*AZ62/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF62" s="58" t="str">
-        <f>IF(B62="No MPC", AT62*J62*AZ62/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG62" s="31">
-        <f>IF(P62&lt;1.5, IF(B62&lt;&gt;"Julia",((3-P62)*AZ62)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.43</v>
       </c>
       <c r="BH62" s="31" t="str">
-        <f>IF(B62="Julia",AW62*AZ62,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI62" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ62" s="66">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BK62" s="48">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>11.43</v>
       </c>
     </row>
@@ -11548,59 +11882,59 @@
       <c r="AV63" s="30"/>
       <c r="AW63" s="40"/>
       <c r="AX63" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY63" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ63" s="30">
-        <f>AP63+SUM(AG63:AI63,AK63:AL63)-((AO63+1)*D63)</f>
+        <f t="shared" si="30"/>
         <v>1524</v>
       </c>
       <c r="BA63" s="31" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB63" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC63" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD63" s="31">
-        <f>IF(B63="Python",AU63*AZ63/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE63" s="61" t="str">
-        <f>IF(B63="Julia",AV63*AZ63/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF63" s="58" t="str">
-        <f>IF(B63="No MPC", AT63*J63*AZ63/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG63" s="31">
-        <f>IF(P63&lt;1.5, IF(B63&lt;&gt;"Julia",((3-P63)*AZ63)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.43</v>
       </c>
       <c r="BH63" s="31" t="str">
-        <f>IF(B63="Julia",AW63*AZ63,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI63" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ63" s="66">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BK63" s="48">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>11.43</v>
       </c>
     </row>
@@ -11677,59 +12011,59 @@
       <c r="AV64" s="30"/>
       <c r="AW64" s="40"/>
       <c r="AX64" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY64" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ64" s="30">
-        <f>AP64+SUM(AG64:AI64,AK64:AL64)-((AO64+1)*D64)</f>
+        <f t="shared" si="30"/>
         <v>1524</v>
       </c>
       <c r="BA64" s="31" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB64" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC64" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD64" s="31" t="str">
-        <f>IF(B64="Python",AU64*AZ64/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE64" s="61">
-        <f>IF(B64="Julia",AV64*AZ64/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF64" s="58" t="str">
-        <f>IF(B64="No MPC", AT64*J64*AZ64/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG64" s="31" t="str">
-        <f>IF(P64&lt;1.5, IF(B64&lt;&gt;"Julia",((3-P64)*AZ64)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH64" s="31">
-        <f>IF(B64="Julia",AW64*AZ64,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI64" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ64" s="66">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BK64" s="48">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
@@ -11806,59 +12140,59 @@
       <c r="AV65" s="17"/>
       <c r="AW65" s="41"/>
       <c r="AX65" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY65" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ65" s="17">
-        <f>AP65+SUM(AG65:AI65,AK65:AL65)-((AO65+1)*D65)</f>
+        <f t="shared" si="30"/>
         <v>1524</v>
       </c>
       <c r="BA65" s="18" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB65" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC65" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD65" s="18" t="str">
-        <f>IF(B65="Python",AU65*AZ65/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE65" s="18">
-        <f>IF(B65="Julia",AV65*AZ65/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF65" s="59" t="str">
-        <f>IF(B65="No MPC", AT65*J65*AZ65/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG65" s="18" t="str">
-        <f>IF(P65&lt;1.5, IF(B65&lt;&gt;"Julia",((3-P65)*AZ65)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH65" s="18">
-        <f>IF(B65="Julia",AW65*AZ65,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI65" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ65" s="66">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BK65" s="48">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
@@ -11935,56 +12269,56 @@
       <c r="AV66" s="4"/>
       <c r="AW66" s="22"/>
       <c r="AX66" s="12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY66" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ66" s="13">
-        <f>AP66+SUM(AG66:AI66,AK66:AL66)-((AO66+1)*D66)</f>
+        <f t="shared" si="30"/>
         <v>1508</v>
       </c>
       <c r="BA66" s="14" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB66" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC66" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD66" s="14" t="str">
-        <f>IF(B66="Python",AU66*AZ66/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE66" s="14" t="str">
-        <f>IF(B66="Julia",AV66*AZ66/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF66" s="57">
-        <f>IF(B66="No MPC", AT66*J66*AZ66/1000,"")</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BG66" s="14">
-        <f>IF(P66&lt;1.5, IF(B66&lt;&gt;"Julia",((3-P66)*AZ66)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.31</v>
       </c>
       <c r="BH66" s="14" t="str">
-        <f>IF(B66="Julia",AW66*AZ66,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI66" s="45">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ66" s="62"/>
       <c r="BK66" s="50">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>11.31</v>
       </c>
     </row>
@@ -12061,56 +12395,56 @@
       <c r="AV67" s="27"/>
       <c r="AW67" s="2"/>
       <c r="AX67" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY67" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ67" s="30">
-        <f>AP67+SUM(AG67:AI67,AK67:AL67)-((AO67+1)*D67)</f>
+        <f t="shared" si="30"/>
         <v>1508</v>
       </c>
       <c r="BA67" s="31" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB67" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC67" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD67" s="31">
-        <f>IF(B67="Python",AU67*AZ67/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE67" s="61" t="str">
-        <f>IF(B67="Julia",AV67*AZ67/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF67" s="58" t="str">
-        <f>IF(B67="No MPC", AT67*J67*AZ67/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG67" s="31">
-        <f>IF(P67&lt;1.5, IF(B67&lt;&gt;"Julia",((3-P67)*AZ67)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.31</v>
       </c>
       <c r="BH67" s="31" t="str">
-        <f>IF(B67="Julia",AW67*AZ67,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI67" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ67" s="63"/>
       <c r="BK67" s="48">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>11.31</v>
       </c>
     </row>
@@ -12187,56 +12521,56 @@
       <c r="AV68" s="30"/>
       <c r="AW68" s="40"/>
       <c r="AX68" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY68" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ68" s="30">
-        <f>AP68+SUM(AG68:AI68,AK68:AL68)-((AO68+1)*D68)</f>
+        <f t="shared" si="30"/>
         <v>1508</v>
       </c>
       <c r="BA68" s="31" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB68" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC68" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD68" s="31">
-        <f>IF(B68="Python",AU68*AZ68/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BE68" s="61" t="str">
-        <f>IF(B68="Julia",AV68*AZ68/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF68" s="58" t="str">
-        <f>IF(B68="No MPC", AT68*J68*AZ68/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG68" s="31">
-        <f>IF(P68&lt;1.5, IF(B68&lt;&gt;"Julia",((3-P68)*AZ68)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v>11.31</v>
       </c>
       <c r="BH68" s="31" t="str">
-        <f>IF(B68="Julia",AW68*AZ68,"")</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="BI68" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ68" s="63"/>
       <c r="BK68" s="48">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>11.31</v>
       </c>
     </row>
@@ -12313,56 +12647,56 @@
       <c r="AV69" s="30"/>
       <c r="AW69" s="40"/>
       <c r="AX69" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY69" s="30">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ69" s="30">
-        <f>AP69+SUM(AG69:AI69,AK69:AL69)-((AO69+1)*D69)</f>
+        <f t="shared" si="30"/>
         <v>1508</v>
       </c>
       <c r="BA69" s="31" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB69" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC69" s="31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD69" s="31" t="str">
-        <f>IF(B69="Python",AU69*AZ69/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE69" s="61">
-        <f>IF(B69="Julia",AV69*AZ69/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF69" s="58" t="str">
-        <f>IF(B69="No MPC", AT69*J69*AZ69/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG69" s="31" t="str">
-        <f>IF(P69&lt;1.5, IF(B69&lt;&gt;"Julia",((3-P69)*AZ69)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH69" s="31">
-        <f>IF(B69="Julia",AW69*AZ69,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI69" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ69" s="63"/>
       <c r="BK69" s="48">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
@@ -12439,56 +12773,56 @@
       <c r="AV70" s="17"/>
       <c r="AW70" s="41"/>
       <c r="AX70" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AY70" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AZ70" s="17">
-        <f>AP70+SUM(AG70:AI70,AK70:AL70)-((AO70+1)*D70)</f>
+        <f t="shared" si="30"/>
         <v>1508</v>
       </c>
       <c r="BA70" s="18" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="BB70" s="18">
-        <f t="shared" si="17"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BC70" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="BD70" s="18" t="str">
-        <f>IF(B70="Python",AU70*AZ70/24/60,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BE70" s="18">
-        <f>IF(B70="Julia",AV70*AZ70/24/60,"")</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="BF70" s="59" t="str">
-        <f>IF(B70="No MPC", AT70*J70*AZ70/1000,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BG70" s="18" t="str">
-        <f>IF(P70&lt;1.5, IF(B70&lt;&gt;"Julia",((3-P70)*AZ70)/400, ""),0)</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="BH70" s="18">
-        <f>IF(B70="Julia",AW70*AZ70,"")</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="BI70" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BJ70" s="64"/>
       <c r="BK70" s="49">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
@@ -12534,21 +12868,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12775,27 +13100,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12820,9 +13145,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1778" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B97F46-6D67-4F11-B758-F20B70141FBE}"/>
+  <xr:revisionPtr revIDLastSave="1841" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{837ABAE3-FB6F-4FDF-883D-57F616BF18AE}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1479,6 +1479,7 @@
   <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="60" width="12.6640625" customWidth="1"/>
     <col min="61" max="61" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="62" max="63" width="16.33203125" customWidth="1"/>
@@ -7366,7 +7367,9 @@
       <c r="D31" s="4">
         <v>5</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="5">
+        <v>45454.412476851903</v>
+      </c>
       <c r="F31" s="4">
         <v>2716.05</v>
       </c>
@@ -7455,7 +7458,9 @@
       <c r="AI31" s="13">
         <v>5</v>
       </c>
-      <c r="AJ31" s="13"/>
+      <c r="AJ31" s="13">
+        <v>1.6917932E-2</v>
+      </c>
       <c r="AK31" s="13">
         <v>76</v>
       </c>
@@ -7513,7 +7518,7 @@
       </c>
       <c r="BC31" s="14">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.40603036800000003</v>
       </c>
       <c r="BD31" s="14" t="str">
         <f t="shared" si="9"/>
@@ -7561,7 +7566,9 @@
       <c r="D32" s="27">
         <v>5</v>
       </c>
-      <c r="E32" s="28"/>
+      <c r="E32" s="28">
+        <v>45454.415717592601</v>
+      </c>
       <c r="F32" s="27">
         <v>2716.05</v>
       </c>
@@ -7650,7 +7657,9 @@
       <c r="AI32" s="30">
         <v>3</v>
       </c>
-      <c r="AJ32" s="30"/>
+      <c r="AJ32" s="30">
+        <v>3.6440233892207234E-2</v>
+      </c>
       <c r="AK32" s="30">
         <v>107</v>
       </c>
@@ -7683,7 +7692,9 @@
       <c r="AT32" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU32" s="15"/>
+      <c r="AU32" s="15">
+        <v>2.87489038787993E-2</v>
+      </c>
       <c r="AV32" s="30"/>
       <c r="AW32" s="40"/>
       <c r="AX32" s="15">
@@ -7708,11 +7719,11 @@
       </c>
       <c r="BC32" s="31">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.87456561341297356</v>
       </c>
       <c r="BD32" s="31">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3.6440233892207234E-2</v>
       </c>
       <c r="BE32" s="61" t="str">
         <f t="shared" si="1"/>
@@ -7732,11 +7743,11 @@
       </c>
       <c r="BI32" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>94.649958161577231</v>
       </c>
       <c r="BJ32" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3.6440233892207234E-2</v>
       </c>
       <c r="BK32" s="48">
         <f t="shared" si="12"/>
@@ -7756,7 +7767,9 @@
       <c r="D33" s="27">
         <v>5</v>
       </c>
-      <c r="E33" s="28"/>
+      <c r="E33" s="28">
+        <v>45454.421145833301</v>
+      </c>
       <c r="F33" s="27">
         <v>2716.05</v>
       </c>
@@ -7845,7 +7858,9 @@
       <c r="AI33" s="30">
         <v>7</v>
       </c>
-      <c r="AJ33" s="30"/>
+      <c r="AJ33" s="30">
+        <v>3.2747608574761916E-2</v>
+      </c>
       <c r="AK33" s="30">
         <v>104</v>
       </c>
@@ -7878,7 +7893,9 @@
       <c r="AT33" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU33" s="15"/>
+      <c r="AU33" s="15">
+        <v>2.5969554777765198E-2</v>
+      </c>
       <c r="AV33" s="30"/>
       <c r="AW33" s="40"/>
       <c r="AX33" s="15">
@@ -7903,11 +7920,11 @@
       </c>
       <c r="BC33" s="31">
         <f t="shared" ref="BC33:BC58" si="26">AJ33*24</f>
-        <v>0</v>
+        <v>0.78594260579428599</v>
       </c>
       <c r="BD33" s="31">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3.2747608574761916E-2</v>
       </c>
       <c r="BE33" s="61" t="str">
         <f t="shared" si="1"/>
@@ -7927,11 +7944,11 @@
       </c>
       <c r="BI33" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>85.058723570810173</v>
       </c>
       <c r="BJ33" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3.2747608574761916E-2</v>
       </c>
       <c r="BK33" s="48">
         <f t="shared" si="12"/>
@@ -7951,7 +7968,9 @@
       <c r="D34" s="27">
         <v>5</v>
       </c>
-      <c r="E34" s="28"/>
+      <c r="E34" s="28">
+        <v>45454.425034722197</v>
+      </c>
       <c r="F34" s="27">
         <v>2716.05</v>
       </c>
@@ -8040,7 +8059,9 @@
       <c r="AI34" s="30">
         <v>8</v>
       </c>
-      <c r="AJ34" s="30"/>
+      <c r="AJ34" s="30">
+        <v>2.2234696197237742E-2</v>
+      </c>
       <c r="AK34" s="30">
         <v>107</v>
       </c>
@@ -8074,8 +8095,12 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU34" s="15"/>
-      <c r="AV34" s="30"/>
-      <c r="AW34" s="40"/>
+      <c r="AV34" s="30">
+        <v>1.7829755938445199E-2</v>
+      </c>
+      <c r="AW34" s="40">
+        <v>4.2762477749490602E-3</v>
+      </c>
       <c r="AX34" s="15">
         <f t="shared" si="4"/>
         <v>1.5012553599999999E-2</v>
@@ -8098,7 +8123,7 @@
       </c>
       <c r="BC34" s="31">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>0.53363270873370583</v>
       </c>
       <c r="BD34" s="31" t="str">
         <f t="shared" si="9"/>
@@ -8106,7 +8131,7 @@
       </c>
       <c r="BE34" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.2234696197237742E-2</v>
       </c>
       <c r="BF34" s="58" t="str">
         <f t="shared" si="17"/>
@@ -8118,19 +8143,19 @@
       </c>
       <c r="BH34" s="31">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.6791147043425241</v>
       </c>
       <c r="BI34" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>57.752457655162971</v>
       </c>
       <c r="BJ34" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.2234696197237742E-2</v>
       </c>
       <c r="BK34" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>7.6791147043425241</v>
       </c>
     </row>
     <row r="35" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8146,12 +8171,16 @@
       <c r="D35" s="7">
         <v>5</v>
       </c>
-      <c r="E35" s="8"/>
+      <c r="E35" s="8">
+        <v>45454.4282060185</v>
+      </c>
       <c r="F35" s="7">
         <v>2716.05</v>
       </c>
       <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+      <c r="H35" s="11">
+        <v>2518.02</v>
+      </c>
       <c r="I35" s="11">
         <v>25.2</v>
       </c>
@@ -8233,7 +8262,9 @@
       <c r="AI35" s="17">
         <v>8</v>
       </c>
-      <c r="AJ35" s="17"/>
+      <c r="AJ35" s="17">
+        <v>2.5244879709235456E-2</v>
+      </c>
       <c r="AK35" s="17">
         <v>111</v>
       </c>
@@ -8267,8 +8298,12 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU35" s="16"/>
-      <c r="AV35" s="17"/>
-      <c r="AW35" s="41"/>
+      <c r="AV35" s="17">
+        <v>1.9845628425675201E-2</v>
+      </c>
+      <c r="AW35" s="41">
+        <v>5.6019013817215999E-3</v>
+      </c>
       <c r="AX35" s="16">
         <f t="shared" si="4"/>
         <v>1.7951346E-2</v>
@@ -8291,7 +8326,7 @@
       </c>
       <c r="BC35" s="18">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>0.60587711302165093</v>
       </c>
       <c r="BD35" s="18" t="str">
         <f t="shared" si="9"/>
@@ -8299,7 +8334,7 @@
       </c>
       <c r="BE35" s="18">
         <f t="shared" ref="BE35:BE70" si="27">IF(B35="Julia",AV35*AZ35/24/60,"")</f>
-        <v>0</v>
+        <v>2.5244879709235456E-2</v>
       </c>
       <c r="BF35" s="59" t="str">
         <f t="shared" si="17"/>
@@ -8311,19 +8346,19 @@
       </c>
       <c r="BH35" s="18">
         <f t="shared" ref="BH35:BH70" si="28">IF(B35="Julia",AW35*AZ35,"")</f>
-        <v>0</v>
+        <v>10.261394893996174</v>
       </c>
       <c r="BI35" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>65.571116127884309</v>
       </c>
       <c r="BJ35" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.5244879709235456E-2</v>
       </c>
       <c r="BK35" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>10.261394893996174</v>
       </c>
     </row>
     <row r="36" spans="1:63" x14ac:dyDescent="0.3">
@@ -8339,44 +8374,112 @@
       <c r="D36" s="27">
         <v>6</v>
       </c>
-      <c r="E36" s="28"/>
+      <c r="E36" s="28">
+        <v>45455.407187500001</v>
+      </c>
       <c r="F36">
         <v>3307.9</v>
       </c>
       <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="29"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-      <c r="W36" s="29"/>
-      <c r="X36" s="29"/>
-      <c r="Y36" s="29"/>
-      <c r="Z36" s="29"/>
-      <c r="AA36" s="29"/>
-      <c r="AB36" s="25"/>
-      <c r="AC36" s="12"/>
-      <c r="AD36" s="13"/>
-      <c r="AE36" s="13"/>
-      <c r="AF36" s="13"/>
-      <c r="AG36" s="13"/>
-      <c r="AH36" s="13"/>
-      <c r="AI36" s="13"/>
+      <c r="H36" s="29">
+        <v>2801.43</v>
+      </c>
+      <c r="I36" s="29">
+        <v>23.9</v>
+      </c>
+      <c r="J36" s="29">
+        <v>22.4</v>
+      </c>
+      <c r="K36" s="29">
+        <v>93.6</v>
+      </c>
+      <c r="L36" s="29">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="M36" s="29">
+        <v>365</v>
+      </c>
+      <c r="N36" s="29">
+        <v>1</v>
+      </c>
+      <c r="O36" s="29">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="P36" s="29">
+        <v>2.63</v>
+      </c>
+      <c r="Q36" s="29">
+        <v>0.26</v>
+      </c>
+      <c r="R36" s="29">
+        <v>0.02</v>
+      </c>
+      <c r="S36" s="29">
+        <v>2.78</v>
+      </c>
+      <c r="T36" s="29">
+        <v>7.2560000000000002</v>
+      </c>
+      <c r="U36" s="29">
+        <v>112.8</v>
+      </c>
+      <c r="V36" s="29">
+        <v>28.8</v>
+      </c>
+      <c r="W36" s="29">
+        <v>2.59</v>
+      </c>
+      <c r="X36" s="29">
+        <v>155.4</v>
+      </c>
+      <c r="Y36" s="29">
+        <v>48.9</v>
+      </c>
+      <c r="Z36" s="29">
+        <v>99</v>
+      </c>
+      <c r="AA36" s="29">
+        <v>23.3</v>
+      </c>
+      <c r="AB36" s="25">
+        <v>7.298</v>
+      </c>
+      <c r="AC36" s="12">
+        <v>299</v>
+      </c>
+      <c r="AD36" s="13">
+        <v>0.49700000000000005</v>
+      </c>
+      <c r="AE36" s="13">
+        <v>7.3</v>
+      </c>
+      <c r="AF36" s="13">
+        <v>34</v>
+      </c>
+      <c r="AG36" s="13">
+        <v>31.32</v>
+      </c>
+      <c r="AH36" s="13">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="AI36" s="13">
+        <v>6</v>
+      </c>
       <c r="AJ36" s="13"/>
-      <c r="AK36" s="13"/>
-      <c r="AL36" s="13"/>
-      <c r="AM36" s="13"/>
-      <c r="AN36" s="13"/>
+      <c r="AK36" s="13">
+        <v>100</v>
+      </c>
+      <c r="AL36" s="13">
+        <v>46</v>
+      </c>
+      <c r="AM36" s="13">
+        <f t="shared" ref="AM36:AM40" si="29">AK36-AK31</f>
+        <v>24</v>
+      </c>
+      <c r="AN36" s="13">
+        <f t="shared" ref="AN36:AN40" si="30">AL36-AL31</f>
+        <v>0</v>
+      </c>
       <c r="AO36" s="42">
         <v>15</v>
       </c>
@@ -8400,30 +8503,30 @@
       <c r="AW36" s="39"/>
       <c r="AX36" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6329779199999998E-2</v>
       </c>
       <c r="AY36" s="13">
         <f t="shared" si="21"/>
         <v>0.40603036800000003</v>
       </c>
       <c r="AZ36" s="13">
-        <f t="shared" si="16"/>
-        <v>1604</v>
-      </c>
-      <c r="BA36" s="14" t="e">
+        <f>AP36+SUM(AG36:AI36,AK36:AL36)-((AO36+1)*D36)</f>
+        <v>1822.52</v>
+      </c>
+      <c r="BA36" s="14">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>5.4869082369466457E-2</v>
       </c>
       <c r="BB36" s="14">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="BC36" s="14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD36" s="14" t="str">
-        <f t="shared" ref="BD36:BD70" si="29">IF(B36="Python",AU36*AZ36/24/60,"")</f>
+        <f t="shared" ref="BD36:BD70" si="31">IF(B36="Python",AU36*AZ36/24/60,"")</f>
         <v/>
       </c>
       <c r="BE36" s="14" t="str">
@@ -8432,11 +8535,11 @@
       </c>
       <c r="BF36" s="57">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.6329779199999998E-2</v>
       </c>
       <c r="BG36" s="14">
         <f t="shared" si="24"/>
-        <v>12.03</v>
+        <v>0</v>
       </c>
       <c r="BH36" s="14" t="str">
         <f t="shared" si="28"/>
@@ -8444,15 +8547,15 @@
       </c>
       <c r="BI36" s="45">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>42.41501090909091</v>
       </c>
       <c r="BJ36" s="65">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.6329779199999998E-2</v>
       </c>
       <c r="BK36" s="50">
         <f t="shared" si="12"/>
-        <v>12.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.3">
@@ -8468,44 +8571,112 @@
       <c r="D37" s="27">
         <v>6</v>
       </c>
-      <c r="E37" s="28"/>
+      <c r="E37" s="28">
+        <v>45455.410543981503</v>
+      </c>
       <c r="F37">
         <v>3307.9</v>
       </c>
       <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="10"/>
-      <c r="Z37" s="29"/>
-      <c r="AA37" s="29"/>
-      <c r="AB37" s="25"/>
-      <c r="AC37" s="15"/>
-      <c r="AD37" s="30"/>
-      <c r="AE37" s="30"/>
-      <c r="AF37" s="30"/>
-      <c r="AG37" s="30"/>
-      <c r="AH37" s="30"/>
-      <c r="AI37" s="30"/>
+      <c r="H37" s="29">
+        <v>2795.67</v>
+      </c>
+      <c r="I37" s="29">
+        <v>21.4</v>
+      </c>
+      <c r="J37" s="29">
+        <v>20.3</v>
+      </c>
+      <c r="K37" s="29">
+        <v>95.3</v>
+      </c>
+      <c r="L37">
+        <v>18</v>
+      </c>
+      <c r="M37" s="29">
+        <v>414</v>
+      </c>
+      <c r="N37" s="29">
+        <v>1.62</v>
+      </c>
+      <c r="O37" s="29">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P37" s="29">
+        <v>6.08</v>
+      </c>
+      <c r="Q37" s="29">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R37" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="S37" s="29">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="T37" s="29">
+        <v>7.194</v>
+      </c>
+      <c r="U37" s="29">
+        <v>155.9</v>
+      </c>
+      <c r="V37" s="29">
+        <v>21</v>
+      </c>
+      <c r="W37" s="29">
+        <v>1.79</v>
+      </c>
+      <c r="X37" s="29">
+        <v>164.1</v>
+      </c>
+      <c r="Y37" s="10">
+        <v>58.4</v>
+      </c>
+      <c r="Z37" s="29">
+        <v>136.69999999999999</v>
+      </c>
+      <c r="AA37" s="29">
+        <v>17</v>
+      </c>
+      <c r="AB37" s="25">
+        <v>7.234</v>
+      </c>
+      <c r="AC37" s="15">
+        <v>300</v>
+      </c>
+      <c r="AD37" s="30">
+        <v>0.49700000000000005</v>
+      </c>
+      <c r="AE37" s="30">
+        <v>7.22</v>
+      </c>
+      <c r="AF37" s="30">
+        <v>34</v>
+      </c>
+      <c r="AG37" s="30">
+        <v>33.53</v>
+      </c>
+      <c r="AH37" s="30">
+        <v>6.72</v>
+      </c>
+      <c r="AI37" s="30">
+        <v>4</v>
+      </c>
       <c r="AJ37" s="30"/>
-      <c r="AK37" s="30"/>
-      <c r="AL37" s="30"/>
-      <c r="AM37" s="30"/>
-      <c r="AN37" s="30"/>
+      <c r="AK37" s="30">
+        <v>160</v>
+      </c>
+      <c r="AL37" s="30">
+        <v>55</v>
+      </c>
+      <c r="AM37" s="30">
+        <f t="shared" si="29"/>
+        <v>53</v>
+      </c>
+      <c r="AN37" s="30">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
       <c r="AO37" s="43">
         <v>15</v>
       </c>
@@ -8524,12 +8695,14 @@
       <c r="AT37" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU37" s="15"/>
+      <c r="AU37" s="15">
+        <v>1.3368395543308501E-2</v>
+      </c>
       <c r="AV37" s="30"/>
       <c r="AW37" s="40"/>
       <c r="AX37" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.512959E-2</v>
       </c>
       <c r="AY37" s="30">
         <f t="shared" si="21"/>
@@ -8537,23 +8710,23 @@
       </c>
       <c r="AZ37" s="30">
         <f t="shared" si="16"/>
-        <v>1604</v>
-      </c>
-      <c r="BA37" s="31" t="e">
+        <v>1863.25</v>
+      </c>
+      <c r="BA37" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>8.5871461156581244E-2</v>
       </c>
       <c r="BB37" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>9.4117647058823528E-2</v>
       </c>
       <c r="BC37" s="31">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD37" s="31">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>1.7297682636159419E-2</v>
       </c>
       <c r="BE37" s="61" t="str">
         <f t="shared" si="27"/>
@@ -8565,7 +8738,7 @@
       </c>
       <c r="BG37" s="31">
         <f t="shared" si="24"/>
-        <v>12.03</v>
+        <v>0</v>
       </c>
       <c r="BH37" s="31" t="str">
         <f t="shared" si="28"/>
@@ -8573,15 +8746,15 @@
       </c>
       <c r="BI37" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>44.929045808206283</v>
       </c>
       <c r="BJ37" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.7297682636159419E-2</v>
       </c>
       <c r="BK37" s="48">
         <f t="shared" si="12"/>
-        <v>12.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:63" x14ac:dyDescent="0.3">
@@ -8597,44 +8770,112 @@
       <c r="D38" s="27">
         <v>6</v>
       </c>
-      <c r="E38" s="28"/>
+      <c r="E38" s="28">
+        <v>45455.413958333302</v>
+      </c>
       <c r="F38">
         <v>3307.9</v>
       </c>
       <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-      <c r="W38" s="29"/>
-      <c r="X38" s="29"/>
-      <c r="Y38" s="29"/>
-      <c r="Z38" s="29"/>
-      <c r="AA38" s="29"/>
-      <c r="AB38" s="25"/>
-      <c r="AC38" s="15"/>
-      <c r="AD38" s="30"/>
-      <c r="AE38" s="30"/>
-      <c r="AF38" s="30"/>
-      <c r="AG38" s="30"/>
-      <c r="AH38" s="30"/>
-      <c r="AI38" s="30"/>
+      <c r="H38" s="29">
+        <v>2845.89</v>
+      </c>
+      <c r="I38" s="29">
+        <v>21.6</v>
+      </c>
+      <c r="J38" s="29">
+        <v>20.3</v>
+      </c>
+      <c r="K38" s="29">
+        <v>94.2</v>
+      </c>
+      <c r="L38" s="29">
+        <v>17.5</v>
+      </c>
+      <c r="M38" s="29">
+        <v>400</v>
+      </c>
+      <c r="N38" s="29">
+        <v>1.54</v>
+      </c>
+      <c r="O38" s="29">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P38" s="29">
+        <v>5.62</v>
+      </c>
+      <c r="Q38" s="29">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R38" s="29">
+        <v>1.03</v>
+      </c>
+      <c r="S38" s="29">
+        <v>2.1</v>
+      </c>
+      <c r="T38" s="29">
+        <v>7.2380000000000004</v>
+      </c>
+      <c r="U38" s="29">
+        <v>121.7</v>
+      </c>
+      <c r="V38" s="29">
+        <v>18.2</v>
+      </c>
+      <c r="W38" s="29">
+        <v>1.86</v>
+      </c>
+      <c r="X38" s="29">
+        <v>155.6</v>
+      </c>
+      <c r="Y38" s="29">
+        <v>50.5</v>
+      </c>
+      <c r="Z38" s="29">
+        <v>106.7</v>
+      </c>
+      <c r="AA38" s="29">
+        <v>14.7</v>
+      </c>
+      <c r="AB38" s="25">
+        <v>7.2789999999999999</v>
+      </c>
+      <c r="AC38" s="15">
+        <v>301</v>
+      </c>
+      <c r="AD38" s="30">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="AE38" s="30">
+        <v>7.27</v>
+      </c>
+      <c r="AF38" s="30">
+        <v>34</v>
+      </c>
+      <c r="AG38" s="30">
+        <v>27.27</v>
+      </c>
+      <c r="AH38" s="30">
+        <v>10.57</v>
+      </c>
+      <c r="AI38" s="30">
+        <v>7</v>
+      </c>
       <c r="AJ38" s="30"/>
-      <c r="AK38" s="30"/>
-      <c r="AL38" s="30"/>
-      <c r="AM38" s="30"/>
-      <c r="AN38" s="30"/>
+      <c r="AK38" s="30">
+        <v>152</v>
+      </c>
+      <c r="AL38" s="30">
+        <v>47</v>
+      </c>
+      <c r="AM38" s="30">
+        <f t="shared" si="29"/>
+        <v>48</v>
+      </c>
+      <c r="AN38" s="30">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
       <c r="AO38" s="43">
         <v>15</v>
       </c>
@@ -8653,12 +8894,14 @@
       <c r="AT38" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU38" s="15"/>
+      <c r="AU38" s="15">
+        <v>1.6192580649375399E-2</v>
+      </c>
       <c r="AV38" s="30"/>
       <c r="AW38" s="40"/>
       <c r="AX38" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.5004460800000001E-2</v>
       </c>
       <c r="AY38" s="30">
         <f t="shared" si="21"/>
@@ -8666,23 +8909,23 @@
       </c>
       <c r="AZ38" s="30">
         <f t="shared" si="16"/>
-        <v>1604</v>
-      </c>
-      <c r="BA38" s="31" t="e">
+        <v>1847.84</v>
+      </c>
+      <c r="BA38" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>8.2258204173521518E-2</v>
       </c>
       <c r="BB38" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>8.9411764705882357E-2</v>
       </c>
       <c r="BC38" s="31">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD38" s="31">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>2.077867932440405E-2</v>
       </c>
       <c r="BE38" s="61" t="str">
         <f t="shared" si="27"/>
@@ -8694,7 +8937,7 @@
       </c>
       <c r="BG38" s="31">
         <f t="shared" si="24"/>
-        <v>12.03</v>
+        <v>0</v>
       </c>
       <c r="BH38" s="31" t="str">
         <f t="shared" si="28"/>
@@ -8702,15 +8945,15 @@
       </c>
       <c r="BI38" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>53.970595647802732</v>
       </c>
       <c r="BJ38" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.077867932440405E-2</v>
       </c>
       <c r="BK38" s="48">
         <f t="shared" si="12"/>
-        <v>12.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:63" x14ac:dyDescent="0.3">
@@ -8726,44 +8969,112 @@
       <c r="D39" s="27">
         <v>6</v>
       </c>
-      <c r="E39" s="28"/>
+      <c r="E39" s="28">
+        <v>45455.418726851902</v>
+      </c>
       <c r="F39">
         <v>3307.9</v>
       </c>
       <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="29"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="29"/>
-      <c r="R39" s="29"/>
-      <c r="S39" s="29"/>
-      <c r="T39" s="29"/>
-      <c r="U39" s="29"/>
-      <c r="V39" s="29"/>
-      <c r="W39" s="29"/>
-      <c r="X39" s="29"/>
-      <c r="Y39" s="29"/>
-      <c r="Z39" s="29"/>
-      <c r="AA39" s="29"/>
-      <c r="AB39" s="25"/>
-      <c r="AC39" s="15"/>
-      <c r="AD39" s="30"/>
-      <c r="AE39" s="30"/>
-      <c r="AF39" s="30"/>
-      <c r="AG39" s="30"/>
-      <c r="AH39" s="30"/>
-      <c r="AI39" s="30"/>
+      <c r="H39" s="29">
+        <v>2965.59</v>
+      </c>
+      <c r="I39" s="29">
+        <v>23.6</v>
+      </c>
+      <c r="J39" s="29">
+        <v>22.8</v>
+      </c>
+      <c r="K39" s="29">
+        <v>96.4</v>
+      </c>
+      <c r="L39" s="29">
+        <v>17.2</v>
+      </c>
+      <c r="M39" s="29">
+        <v>351</v>
+      </c>
+      <c r="N39" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="O39" s="29">
+        <v>0.26</v>
+      </c>
+      <c r="P39" s="29">
+        <v>2.65</v>
+      </c>
+      <c r="Q39" s="29">
+        <v>0.22</v>
+      </c>
+      <c r="R39" s="29">
+        <v>0</v>
+      </c>
+      <c r="S39" s="29">
+        <v>1.29</v>
+      </c>
+      <c r="T39" s="29">
+        <v>7.2629999999999999</v>
+      </c>
+      <c r="U39" s="29">
+        <v>131.1</v>
+      </c>
+      <c r="V39" s="29">
+        <v>21.2</v>
+      </c>
+      <c r="W39" s="29">
+        <v>1.92</v>
+      </c>
+      <c r="X39" s="29">
+        <v>150.9</v>
+      </c>
+      <c r="Y39" s="29">
+        <v>57.6</v>
+      </c>
+      <c r="Z39" s="29">
+        <v>115</v>
+      </c>
+      <c r="AA39" s="29">
+        <v>17.2</v>
+      </c>
+      <c r="AB39" s="25">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AC39" s="15">
+        <v>300</v>
+      </c>
+      <c r="AD39" s="30">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="AE39" s="30">
+        <v>7.3</v>
+      </c>
+      <c r="AF39" s="30">
+        <v>34</v>
+      </c>
+      <c r="AG39" s="30">
+        <v>24.77</v>
+      </c>
+      <c r="AH39" s="30">
+        <v>8.68</v>
+      </c>
+      <c r="AI39" s="30">
+        <v>10</v>
+      </c>
       <c r="AJ39" s="30"/>
-      <c r="AK39" s="30"/>
-      <c r="AL39" s="30"/>
-      <c r="AM39" s="30"/>
-      <c r="AN39" s="30"/>
+      <c r="AK39" s="30">
+        <v>138</v>
+      </c>
+      <c r="AL39" s="30">
+        <v>40</v>
+      </c>
+      <c r="AM39" s="30">
+        <f t="shared" si="29"/>
+        <v>31</v>
+      </c>
+      <c r="AN39" s="30">
+        <f t="shared" si="30"/>
+        <v>8</v>
+      </c>
       <c r="AO39" s="43">
         <v>15</v>
       </c>
@@ -8783,11 +9094,15 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU39" s="15"/>
-      <c r="AV39" s="30"/>
-      <c r="AW39" s="40"/>
+      <c r="AV39" s="30">
+        <v>1.7536108436848299E-2</v>
+      </c>
+      <c r="AW39" s="40">
+        <v>4.6517617677274302E-3</v>
+      </c>
       <c r="AX39" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6648104000000004E-2</v>
       </c>
       <c r="AY39" s="30">
         <f t="shared" si="21"/>
@@ -8795,51 +9110,48 @@
       </c>
       <c r="AZ39" s="30">
         <f t="shared" si="16"/>
-        <v>1604</v>
-      </c>
-      <c r="BA39" s="31" t="e">
+        <v>1825.45</v>
+      </c>
+      <c r="BA39" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>7.559779780328138E-2</v>
       </c>
       <c r="BB39" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>8.1176470588235294E-2</v>
       </c>
       <c r="BC39" s="31">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD39" s="31" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE39" s="61">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2.2230061906975504E-2</v>
       </c>
       <c r="BF39" s="58" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BG39" s="31" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
+      <c r="BG39" s="31"/>
       <c r="BH39" s="31">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>8.4915585188980369</v>
       </c>
       <c r="BI39" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>57.740420537598716</v>
       </c>
       <c r="BJ39" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.2230061906975504E-2</v>
       </c>
       <c r="BK39" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>8.4915585188980369</v>
       </c>
     </row>
     <row r="40" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8855,44 +9167,112 @@
       <c r="D40" s="27">
         <v>6</v>
       </c>
-      <c r="E40" s="28"/>
+      <c r="E40" s="28">
+        <v>45455.421655092599</v>
+      </c>
       <c r="F40">
         <v>3307.9</v>
       </c>
       <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="25"/>
-      <c r="AC40" s="16"/>
-      <c r="AD40" s="17"/>
-      <c r="AE40" s="17"/>
-      <c r="AF40" s="17"/>
-      <c r="AG40" s="17"/>
-      <c r="AH40" s="17"/>
-      <c r="AI40" s="17"/>
+      <c r="H40" s="29">
+        <v>3271.2750000000001</v>
+      </c>
+      <c r="I40" s="29">
+        <v>25.1</v>
+      </c>
+      <c r="J40" s="29">
+        <v>24.5</v>
+      </c>
+      <c r="K40" s="29">
+        <v>97.7</v>
+      </c>
+      <c r="L40" s="29">
+        <v>16.7</v>
+      </c>
+      <c r="M40" s="29">
+        <v>343</v>
+      </c>
+      <c r="N40" s="29">
+        <v>1.59</v>
+      </c>
+      <c r="O40" s="29">
+        <v>0.26</v>
+      </c>
+      <c r="P40" s="29">
+        <v>1.36</v>
+      </c>
+      <c r="Q40" s="29">
+        <v>0.23</v>
+      </c>
+      <c r="R40" s="29">
+        <v>0</v>
+      </c>
+      <c r="S40" s="29">
+        <v>0.63</v>
+      </c>
+      <c r="T40" s="29">
+        <v>7.2539999999999996</v>
+      </c>
+      <c r="U40" s="29">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="V40" s="29">
+        <v>21.3</v>
+      </c>
+      <c r="W40" s="29">
+        <v>1.92</v>
+      </c>
+      <c r="X40" s="29">
+        <v>149.4</v>
+      </c>
+      <c r="Y40" s="29">
+        <v>58.3</v>
+      </c>
+      <c r="Z40" s="29">
+        <v>118.5</v>
+      </c>
+      <c r="AA40" s="29">
+        <v>17.3</v>
+      </c>
+      <c r="AB40" s="25">
+        <v>7.2960000000000003</v>
+      </c>
+      <c r="AC40" s="16">
+        <v>303</v>
+      </c>
+      <c r="AD40" s="17">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="AE40" s="17">
+        <v>7.3</v>
+      </c>
+      <c r="AF40" s="17">
+        <v>34</v>
+      </c>
+      <c r="AG40" s="17">
+        <v>21.77</v>
+      </c>
+      <c r="AH40" s="17">
+        <v>30.46</v>
+      </c>
+      <c r="AI40" s="17">
+        <v>10</v>
+      </c>
       <c r="AJ40" s="17"/>
-      <c r="AK40" s="17"/>
-      <c r="AL40" s="17"/>
-      <c r="AM40" s="17"/>
-      <c r="AN40" s="17"/>
+      <c r="AK40" s="17">
+        <v>147</v>
+      </c>
+      <c r="AL40" s="17">
+        <v>54</v>
+      </c>
+      <c r="AM40" s="17">
+        <f t="shared" si="29"/>
+        <v>36</v>
+      </c>
+      <c r="AN40" s="17">
+        <f t="shared" si="30"/>
+        <v>11</v>
+      </c>
       <c r="AO40" s="44">
         <v>15</v>
       </c>
@@ -8912,11 +9292,15 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU40" s="16"/>
-      <c r="AV40" s="17"/>
-      <c r="AW40" s="41"/>
+      <c r="AV40" s="17">
+        <v>1.61476013472261E-2</v>
+      </c>
+      <c r="AW40" s="41">
+        <v>1.2435898508473199E-3</v>
+      </c>
       <c r="AX40" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.8298854E-2</v>
       </c>
       <c r="AY40" s="17">
         <f t="shared" si="21"/>
@@ -8924,27 +9308,27 @@
       </c>
       <c r="AZ40" s="17">
         <f t="shared" si="16"/>
-        <v>1604</v>
-      </c>
-      <c r="BA40" s="18" t="e">
+        <v>1867.23</v>
+      </c>
+      <c r="BA40" s="18">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>7.8726241544962328E-2</v>
       </c>
       <c r="BB40" s="18">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>8.6470588235294119E-2</v>
       </c>
       <c r="BC40" s="18">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD40" s="18" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE40" s="18">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2.0938392821931242E-2</v>
       </c>
       <c r="BF40" s="59" t="str">
         <f t="shared" si="17"/>
@@ -8956,19 +9340,19 @@
       </c>
       <c r="BH40" s="18">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>2.3220682771976411</v>
       </c>
       <c r="BI40" s="47">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>54.385435901120111</v>
       </c>
       <c r="BJ40" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.0938392821931242E-2</v>
       </c>
       <c r="BK40" s="49">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2.3220682771976411</v>
       </c>
     </row>
     <row r="41" spans="1:63" x14ac:dyDescent="0.3">
@@ -8984,44 +9368,112 @@
       <c r="D41" s="4">
         <v>7</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="5">
+        <v>45456.4049884259</v>
+      </c>
       <c r="F41" s="4">
         <v>3888.32</v>
       </c>
       <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
-      <c r="Y41" s="9"/>
-      <c r="Z41" s="9"/>
-      <c r="AA41" s="9"/>
-      <c r="AB41" s="24"/>
-      <c r="AC41" s="12"/>
-      <c r="AD41" s="13"/>
-      <c r="AE41" s="13"/>
-      <c r="AF41" s="13"/>
-      <c r="AG41" s="13"/>
-      <c r="AH41" s="13"/>
-      <c r="AI41" s="13"/>
+      <c r="H41" s="9">
+        <v>3347.97</v>
+      </c>
+      <c r="I41" s="9">
+        <v>24</v>
+      </c>
+      <c r="J41" s="9">
+        <v>22.6</v>
+      </c>
+      <c r="K41" s="9">
+        <v>94.4</v>
+      </c>
+      <c r="L41" s="9">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="M41" s="9">
+        <v>365</v>
+      </c>
+      <c r="N41" s="9">
+        <v>1.07</v>
+      </c>
+      <c r="O41" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="P41" s="9">
+        <v>2.82</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>0.26</v>
+      </c>
+      <c r="R41" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="S41" s="9">
+        <v>2.35</v>
+      </c>
+      <c r="T41" s="9">
+        <v>7.2539999999999996</v>
+      </c>
+      <c r="U41" s="9">
+        <v>114.8</v>
+      </c>
+      <c r="V41" s="9">
+        <v>29.2</v>
+      </c>
+      <c r="W41" s="9">
+        <v>2.38</v>
+      </c>
+      <c r="X41" s="9">
+        <v>156.9</v>
+      </c>
+      <c r="Y41" s="9">
+        <v>49.4</v>
+      </c>
+      <c r="Z41" s="9">
+        <v>100.7</v>
+      </c>
+      <c r="AA41" s="9">
+        <v>23.6</v>
+      </c>
+      <c r="AB41" s="24">
+        <v>7.2949999999999999</v>
+      </c>
+      <c r="AC41" s="12">
+        <v>301</v>
+      </c>
+      <c r="AD41" s="13">
+        <v>0.495</v>
+      </c>
+      <c r="AE41" s="13">
+        <v>7.3</v>
+      </c>
+      <c r="AF41" s="13">
+        <v>34</v>
+      </c>
+      <c r="AG41" s="13">
+        <v>31.32</v>
+      </c>
+      <c r="AH41" s="13">
+        <v>48.44</v>
+      </c>
+      <c r="AI41" s="13">
+        <v>6</v>
+      </c>
       <c r="AJ41" s="13"/>
-      <c r="AK41" s="13"/>
-      <c r="AL41" s="13"/>
-      <c r="AM41" s="13"/>
-      <c r="AN41" s="13"/>
+      <c r="AK41" s="13">
+        <v>124</v>
+      </c>
+      <c r="AL41" s="13">
+        <v>46</v>
+      </c>
+      <c r="AM41" s="13">
+        <f t="shared" ref="AM41:AM45" si="32">AK41-AK36</f>
+        <v>24</v>
+      </c>
+      <c r="AN41" s="13">
+        <f t="shared" ref="AN41:AN45" si="33">AL41-AL36</f>
+        <v>0</v>
+      </c>
       <c r="AO41" s="42">
         <v>15</v>
       </c>
@@ -9045,30 +9497,30 @@
       <c r="AW41" s="39"/>
       <c r="AX41" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6667590400000001E-2</v>
       </c>
       <c r="AY41" s="13">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.39191470079999996</v>
       </c>
       <c r="AZ41" s="13">
-        <f t="shared" ref="AZ41:AZ70" si="30">AP41+SUM(AG41:AI41,AK41:AL41)-((AO41+1)*D41)</f>
-        <v>1588</v>
-      </c>
-      <c r="BA41" s="14" t="e">
+        <f t="shared" ref="AZ41:AZ70" si="34">AP41+SUM(AG41:AI41,AK41:AL41)-((AO41+1)*D41)</f>
+        <v>1843.76</v>
+      </c>
+      <c r="BA41" s="14">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>6.7253872521369371E-2</v>
       </c>
       <c r="BB41" s="14">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>7.2941176470588232E-2</v>
       </c>
       <c r="BC41" s="14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD41" s="14" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE41" s="14" t="str">
@@ -9077,11 +9529,11 @@
       </c>
       <c r="BF41" s="57">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.6667590400000001E-2</v>
       </c>
       <c r="BG41" s="14">
         <f t="shared" si="24"/>
-        <v>11.91</v>
+        <v>0</v>
       </c>
       <c r="BH41" s="14" t="str">
         <f t="shared" si="28"/>
@@ -9089,15 +9541,15 @@
       </c>
       <c r="BI41" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>43.292442597402605</v>
       </c>
       <c r="BJ41" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.6667590400000001E-2</v>
       </c>
       <c r="BK41" s="48">
         <f t="shared" si="12"/>
-        <v>11.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:63" x14ac:dyDescent="0.3">
@@ -9113,44 +9565,112 @@
       <c r="D42" s="27">
         <v>7</v>
       </c>
-      <c r="E42" s="28"/>
+      <c r="E42" s="28">
+        <v>45456.408564814803</v>
+      </c>
       <c r="F42" s="27">
         <v>3888.32</v>
       </c>
       <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-      <c r="S42" s="29"/>
-      <c r="T42" s="29"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
-      <c r="W42" s="29"/>
-      <c r="X42" s="29"/>
-      <c r="Y42" s="29"/>
-      <c r="Z42" s="29"/>
-      <c r="AA42" s="29"/>
-      <c r="AB42" s="25"/>
-      <c r="AC42" s="15"/>
-      <c r="AD42" s="30"/>
-      <c r="AE42" s="30"/>
-      <c r="AF42" s="30"/>
-      <c r="AG42" s="30"/>
-      <c r="AH42" s="30"/>
-      <c r="AI42" s="30"/>
+      <c r="H42" s="29">
+        <v>3384.48</v>
+      </c>
+      <c r="I42" s="29">
+        <v>21.4</v>
+      </c>
+      <c r="J42" s="29">
+        <v>20.5</v>
+      </c>
+      <c r="K42" s="29">
+        <v>96</v>
+      </c>
+      <c r="L42" s="29">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="M42" s="29">
+        <v>402</v>
+      </c>
+      <c r="N42" s="29">
+        <v>1.69</v>
+      </c>
+      <c r="O42" s="29">
+        <v>0.26</v>
+      </c>
+      <c r="P42" s="29">
+        <v>3.4</v>
+      </c>
+      <c r="Q42" s="29">
+        <v>0.43</v>
+      </c>
+      <c r="R42" s="29">
+        <v>0.11</v>
+      </c>
+      <c r="S42" s="29">
+        <v>1.93</v>
+      </c>
+      <c r="T42" s="29">
+        <v>7.2320000000000002</v>
+      </c>
+      <c r="U42" s="29">
+        <v>156.6</v>
+      </c>
+      <c r="V42" s="29">
+        <v>21.3</v>
+      </c>
+      <c r="W42" s="29">
+        <v>1.6</v>
+      </c>
+      <c r="X42" s="29">
+        <v>165.4</v>
+      </c>
+      <c r="Y42" s="29">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="Z42" s="29">
+        <v>137.30000000000001</v>
+      </c>
+      <c r="AA42" s="29">
+        <v>17.2</v>
+      </c>
+      <c r="AB42" s="25">
+        <v>7.2729999999999997</v>
+      </c>
+      <c r="AC42" s="15">
+        <v>300</v>
+      </c>
+      <c r="AD42" s="30">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="AE42" s="30">
+        <v>7.25</v>
+      </c>
+      <c r="AF42" s="30">
+        <v>34</v>
+      </c>
+      <c r="AG42" s="30">
+        <v>33.53</v>
+      </c>
+      <c r="AH42" s="30">
+        <v>6.72</v>
+      </c>
+      <c r="AI42" s="30">
+        <v>5</v>
+      </c>
       <c r="AJ42" s="30"/>
-      <c r="AK42" s="30"/>
-      <c r="AL42" s="30"/>
-      <c r="AM42" s="30"/>
-      <c r="AN42" s="30"/>
+      <c r="AK42" s="30">
+        <v>187</v>
+      </c>
+      <c r="AL42" s="30">
+        <v>55</v>
+      </c>
+      <c r="AM42" s="30">
+        <f t="shared" si="32"/>
+        <v>27</v>
+      </c>
+      <c r="AN42" s="30">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
       <c r="AO42" s="43">
         <v>15</v>
       </c>
@@ -9174,30 +9694,30 @@
       <c r="AW42" s="40"/>
       <c r="AX42" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.537705E-2</v>
       </c>
       <c r="AY42" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.36311016000000002</v>
       </c>
       <c r="AZ42" s="30">
-        <f t="shared" si="30"/>
-        <v>1588</v>
-      </c>
-      <c r="BA42" s="31" t="e">
+        <f t="shared" si="34"/>
+        <v>1875.25</v>
+      </c>
+      <c r="BA42" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>9.9720037328356215E-2</v>
       </c>
       <c r="BB42" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BC42" s="31">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD42" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE42" s="61" t="str">
@@ -9210,7 +9730,7 @@
       </c>
       <c r="BG42" s="31">
         <f t="shared" si="24"/>
-        <v>11.91</v>
+        <v>0</v>
       </c>
       <c r="BH42" s="31" t="str">
         <f t="shared" si="28"/>
@@ -9226,7 +9746,7 @@
       </c>
       <c r="BK42" s="48">
         <f t="shared" si="12"/>
-        <v>11.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:63" x14ac:dyDescent="0.3">
@@ -9242,44 +9762,112 @@
       <c r="D43" s="27">
         <v>7</v>
       </c>
-      <c r="E43" s="28"/>
+      <c r="E43" s="28">
+        <v>45456.4118171296</v>
+      </c>
       <c r="F43" s="27">
         <v>3888.32</v>
       </c>
       <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
-      <c r="AA43" s="29"/>
-      <c r="AB43" s="25"/>
-      <c r="AC43" s="15"/>
-      <c r="AD43" s="30"/>
-      <c r="AE43" s="30"/>
-      <c r="AF43" s="30"/>
-      <c r="AG43" s="30"/>
-      <c r="AH43" s="30"/>
-      <c r="AI43" s="30"/>
+      <c r="H43" s="29">
+        <v>3525.24</v>
+      </c>
+      <c r="I43" s="29">
+        <v>20.8</v>
+      </c>
+      <c r="J43" s="29">
+        <v>19.7</v>
+      </c>
+      <c r="K43" s="29">
+        <v>94.8</v>
+      </c>
+      <c r="L43" s="29">
+        <v>18</v>
+      </c>
+      <c r="M43" s="29">
+        <v>382</v>
+      </c>
+      <c r="N43" s="29">
+        <v>1.69</v>
+      </c>
+      <c r="O43" s="29">
+        <v>0.26</v>
+      </c>
+      <c r="P43" s="29">
+        <v>3.58</v>
+      </c>
+      <c r="Q43" s="29">
+        <v>0.48</v>
+      </c>
+      <c r="R43" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="S43" s="29">
+        <v>1.71</v>
+      </c>
+      <c r="T43" s="29">
+        <v>7.24</v>
+      </c>
+      <c r="U43" s="29">
+        <v>128.5</v>
+      </c>
+      <c r="V43" s="29">
+        <v>13.6</v>
+      </c>
+      <c r="W43" s="29">
+        <v>1.68</v>
+      </c>
+      <c r="X43" s="29">
+        <v>157.69999999999999</v>
+      </c>
+      <c r="Y43" s="29">
+        <v>53.5</v>
+      </c>
+      <c r="Z43" s="29">
+        <v>112.7</v>
+      </c>
+      <c r="AA43" s="29">
+        <v>11</v>
+      </c>
+      <c r="AB43" s="25">
+        <v>7.2809999999999997</v>
+      </c>
+      <c r="AC43" s="15">
+        <v>300</v>
+      </c>
+      <c r="AD43" s="30">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="AE43" s="30">
+        <v>7.26</v>
+      </c>
+      <c r="AF43" s="30">
+        <v>34</v>
+      </c>
+      <c r="AG43" s="30">
+        <v>27.27</v>
+      </c>
+      <c r="AH43" s="30">
+        <v>10.57</v>
+      </c>
+      <c r="AI43" s="30">
+        <v>7</v>
+      </c>
       <c r="AJ43" s="30"/>
-      <c r="AK43" s="30"/>
-      <c r="AL43" s="30"/>
-      <c r="AM43" s="30"/>
-      <c r="AN43" s="30"/>
+      <c r="AK43" s="30">
+        <v>183</v>
+      </c>
+      <c r="AL43" s="30">
+        <v>47</v>
+      </c>
+      <c r="AM43" s="30">
+        <f t="shared" si="32"/>
+        <v>31</v>
+      </c>
+      <c r="AN43" s="30">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
       <c r="AO43" s="43">
         <v>15</v>
       </c>
@@ -9303,30 +9891,30 @@
       <c r="AW43" s="40"/>
       <c r="AX43" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.46791792E-2</v>
       </c>
       <c r="AY43" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.36010705920000002</v>
       </c>
       <c r="AZ43" s="30">
-        <f t="shared" si="30"/>
-        <v>1588</v>
-      </c>
-      <c r="BA43" s="31" t="e">
+        <f t="shared" si="34"/>
+        <v>1862.8400000000001</v>
+      </c>
+      <c r="BA43" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>9.8237100341414182E-2</v>
       </c>
       <c r="BB43" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.10764705882352942</v>
       </c>
       <c r="BC43" s="31">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD43" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE43" s="61" t="str">
@@ -9339,7 +9927,7 @@
       </c>
       <c r="BG43" s="31">
         <f t="shared" si="24"/>
-        <v>11.91</v>
+        <v>0</v>
       </c>
       <c r="BH43" s="31" t="str">
         <f t="shared" si="28"/>
@@ -9355,7 +9943,7 @@
       </c>
       <c r="BK43" s="48">
         <f t="shared" si="12"/>
-        <v>11.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:63" x14ac:dyDescent="0.3">
@@ -9371,44 +9959,112 @@
       <c r="D44" s="27">
         <v>7</v>
       </c>
-      <c r="E44" s="28"/>
+      <c r="E44" s="28">
+        <v>45456.416608796302</v>
+      </c>
       <c r="F44" s="27">
         <v>3888.32</v>
       </c>
       <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29"/>
-      <c r="M44" s="29"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="29"/>
-      <c r="P44" s="29"/>
-      <c r="Q44" s="29"/>
-      <c r="R44" s="29"/>
-      <c r="S44" s="29"/>
-      <c r="T44" s="29"/>
-      <c r="U44" s="29"/>
-      <c r="V44" s="29"/>
-      <c r="W44" s="29"/>
-      <c r="X44" s="29"/>
-      <c r="Y44" s="29"/>
-      <c r="Z44" s="29"/>
-      <c r="AA44" s="29"/>
-      <c r="AB44" s="25"/>
-      <c r="AC44" s="15"/>
-      <c r="AD44" s="30"/>
-      <c r="AE44" s="30"/>
-      <c r="AF44" s="30"/>
-      <c r="AG44" s="30"/>
-      <c r="AH44" s="30"/>
-      <c r="AI44" s="30"/>
+      <c r="H44" s="29">
+        <v>3579.9450000000002</v>
+      </c>
+      <c r="I44" s="29">
+        <v>22.7</v>
+      </c>
+      <c r="J44" s="29">
+        <v>21.8</v>
+      </c>
+      <c r="K44" s="29">
+        <v>96.3</v>
+      </c>
+      <c r="L44" s="29">
+        <v>17.3</v>
+      </c>
+      <c r="M44" s="29">
+        <v>363</v>
+      </c>
+      <c r="N44" s="29">
+        <v>1.53</v>
+      </c>
+      <c r="O44" s="29">
+        <v>0.23</v>
+      </c>
+      <c r="P44" s="29">
+        <v>2.94</v>
+      </c>
+      <c r="Q44" s="29">
+        <v>0.34</v>
+      </c>
+      <c r="R44" s="29">
+        <v>0.03</v>
+      </c>
+      <c r="S44" s="29">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="T44" s="29">
+        <v>7.2320000000000002</v>
+      </c>
+      <c r="U44" s="29">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="V44" s="29">
+        <v>12.5</v>
+      </c>
+      <c r="W44" s="29">
+        <v>1.68</v>
+      </c>
+      <c r="X44" s="29">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="Y44" s="29">
+        <v>56.1</v>
+      </c>
+      <c r="Z44" s="29">
+        <v>120.4</v>
+      </c>
+      <c r="AA44" s="29">
+        <v>10.1</v>
+      </c>
+      <c r="AB44" s="25">
+        <v>7.2729999999999997</v>
+      </c>
+      <c r="AC44" s="15">
+        <v>300</v>
+      </c>
+      <c r="AD44" s="30">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="AE44" s="30">
+        <v>7.27</v>
+      </c>
+      <c r="AF44" s="30">
+        <v>34</v>
+      </c>
+      <c r="AG44" s="30">
+        <v>24.77</v>
+      </c>
+      <c r="AH44" s="30">
+        <v>8.94</v>
+      </c>
+      <c r="AI44" s="30">
+        <v>11</v>
+      </c>
       <c r="AJ44" s="30"/>
-      <c r="AK44" s="30"/>
-      <c r="AL44" s="30"/>
-      <c r="AM44" s="30"/>
-      <c r="AN44" s="30"/>
+      <c r="AK44" s="30">
+        <v>170</v>
+      </c>
+      <c r="AL44" s="30">
+        <v>50</v>
+      </c>
+      <c r="AM44" s="30">
+        <f t="shared" si="32"/>
+        <v>32</v>
+      </c>
+      <c r="AN44" s="30">
+        <f t="shared" si="33"/>
+        <v>10</v>
+      </c>
       <c r="AO44" s="43">
         <v>15</v>
       </c>
@@ -9432,30 +10088,30 @@
       <c r="AW44" s="40"/>
       <c r="AX44" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6155631200000003E-2</v>
       </c>
       <c r="AY44" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.39955449600000009</v>
       </c>
       <c r="AZ44" s="30">
-        <f t="shared" si="30"/>
-        <v>1588</v>
-      </c>
-      <c r="BA44" s="31" t="e">
+        <f t="shared" si="34"/>
+        <v>1852.71</v>
+      </c>
+      <c r="BA44" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>9.1757479583960785E-2</v>
       </c>
       <c r="BB44" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BC44" s="31">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD44" s="31" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE44" s="61">
@@ -9466,9 +10122,9 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="BG44" s="31" t="str">
+      <c r="BG44" s="31">
         <f t="shared" si="24"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH44" s="31">
         <f t="shared" si="28"/>
@@ -9500,44 +10156,112 @@
       <c r="D45" s="7">
         <v>7</v>
       </c>
-      <c r="E45" s="8"/>
+      <c r="E45" s="8">
+        <v>45456.431018518502</v>
+      </c>
       <c r="F45" s="7">
         <v>3888.32</v>
       </c>
       <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="11"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
-      <c r="T45" s="11"/>
-      <c r="U45" s="11"/>
-      <c r="V45" s="11"/>
-      <c r="W45" s="11"/>
-      <c r="X45" s="11"/>
-      <c r="Y45" s="11"/>
-      <c r="Z45" s="11"/>
-      <c r="AA45" s="11"/>
-      <c r="AB45" s="26"/>
-      <c r="AC45" s="16"/>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="17"/>
-      <c r="AF45" s="17"/>
-      <c r="AG45" s="17"/>
-      <c r="AH45" s="17"/>
-      <c r="AI45" s="17"/>
+      <c r="H45" s="11">
+        <v>3974.04</v>
+      </c>
+      <c r="I45" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="J45" s="11">
+        <v>23.1</v>
+      </c>
+      <c r="K45" s="11">
+        <v>97.3</v>
+      </c>
+      <c r="L45" s="11">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M45" s="11">
+        <v>332</v>
+      </c>
+      <c r="N45" s="11">
+        <v>1.99</v>
+      </c>
+      <c r="O45" s="11">
+        <v>0.24</v>
+      </c>
+      <c r="P45" s="11">
+        <v>0.19</v>
+      </c>
+      <c r="Q45" s="11">
+        <v>0.32</v>
+      </c>
+      <c r="R45" s="11">
+        <v>0</v>
+      </c>
+      <c r="S45" s="11">
+        <v>0.32</v>
+      </c>
+      <c r="T45" s="11">
+        <v>7.2569999999999997</v>
+      </c>
+      <c r="U45" s="11">
+        <v>137.19999999999999</v>
+      </c>
+      <c r="V45" s="11">
+        <v>15.3</v>
+      </c>
+      <c r="W45" s="11">
+        <v>1.85</v>
+      </c>
+      <c r="X45" s="11">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="Y45" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="Z45" s="11">
+        <v>120.3</v>
+      </c>
+      <c r="AA45" s="11">
+        <v>12.4</v>
+      </c>
+      <c r="AB45" s="26">
+        <v>7.298</v>
+      </c>
+      <c r="AC45" s="16">
+        <v>301</v>
+      </c>
+      <c r="AD45" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="AE45" s="17">
+        <v>7.3</v>
+      </c>
+      <c r="AF45" s="17">
+        <v>34</v>
+      </c>
+      <c r="AG45" s="17">
+        <v>21.77</v>
+      </c>
+      <c r="AH45" s="17">
+        <v>33.89</v>
+      </c>
+      <c r="AI45" s="17">
+        <v>11</v>
+      </c>
       <c r="AJ45" s="17"/>
-      <c r="AK45" s="17"/>
-      <c r="AL45" s="17"/>
-      <c r="AM45" s="17"/>
-      <c r="AN45" s="17"/>
+      <c r="AK45" s="17">
+        <v>178</v>
+      </c>
+      <c r="AL45" s="17">
+        <v>57</v>
+      </c>
+      <c r="AM45" s="17">
+        <f t="shared" si="32"/>
+        <v>31</v>
+      </c>
+      <c r="AN45" s="17">
+        <f t="shared" si="33"/>
+        <v>3</v>
+      </c>
       <c r="AO45" s="44">
         <v>15</v>
       </c>
@@ -9561,30 +10285,30 @@
       <c r="AW45" s="41"/>
       <c r="AX45" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.74604584E-2</v>
       </c>
       <c r="AY45" s="17">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.43917249599999997</v>
       </c>
       <c r="AZ45" s="17">
-        <f t="shared" si="30"/>
-        <v>1588</v>
-      </c>
-      <c r="BA45" s="18" t="e">
+        <f t="shared" si="34"/>
+        <v>1889.6599999999999</v>
+      </c>
+      <c r="BA45" s="18">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>9.4196839643110403E-2</v>
       </c>
       <c r="BB45" s="18">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.10470588235294118</v>
       </c>
       <c r="BC45" s="18">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BD45" s="18" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE45" s="18">
@@ -9694,10 +10418,10 @@
       </c>
       <c r="AY46" s="13">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.40002216960000003</v>
       </c>
       <c r="AZ46" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1572</v>
       </c>
       <c r="BA46" s="14" t="e">
@@ -9713,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="BD46" s="14" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE46" s="14" t="str">
@@ -9823,10 +10547,10 @@
       </c>
       <c r="AY47" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.36904919999999997</v>
       </c>
       <c r="AZ47" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1572</v>
       </c>
       <c r="BA47" s="31" t="e">
@@ -9842,7 +10566,7 @@
         <v>0</v>
       </c>
       <c r="BD47" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE47" s="61" t="str">
@@ -9850,7 +10574,7 @@
         <v/>
       </c>
       <c r="BF47" s="58" t="str">
-        <f t="shared" ref="BF47:BF70" si="31">IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
+        <f t="shared" ref="BF47:BF70" si="35">IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
         <v/>
       </c>
       <c r="BG47" s="31">
@@ -9952,10 +10676,10 @@
       </c>
       <c r="AY48" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.35230030079999997</v>
       </c>
       <c r="AZ48" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1572</v>
       </c>
       <c r="BA48" s="31" t="e">
@@ -9971,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="BD48" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE48" s="61" t="str">
@@ -9979,7 +10703,7 @@
         <v/>
       </c>
       <c r="BF48" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG48" s="31">
@@ -10081,10 +10805,10 @@
       </c>
       <c r="AY49" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.38773514880000004</v>
       </c>
       <c r="AZ49" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1572</v>
       </c>
       <c r="BA49" s="31" t="e">
@@ -10100,7 +10824,7 @@
         <v>0</v>
       </c>
       <c r="BD49" s="31" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE49" s="61">
@@ -10108,7 +10832,7 @@
         <v>0</v>
       </c>
       <c r="BF49" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG49" s="31" t="str">
@@ -10210,10 +10934,10 @@
       </c>
       <c r="AY50" s="17">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.41905100159999997</v>
       </c>
       <c r="AZ50" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1572</v>
       </c>
       <c r="BA50" s="18" t="e">
@@ -10229,7 +10953,7 @@
         <v>0</v>
       </c>
       <c r="BD50" s="18" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE50" s="18">
@@ -10237,7 +10961,7 @@
         <v>0</v>
       </c>
       <c r="BF50" s="59" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG50" s="18" t="str">
@@ -10342,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="AZ51" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1556</v>
       </c>
       <c r="BA51" s="14" t="e">
@@ -10358,7 +11082,7 @@
         <v>0</v>
       </c>
       <c r="BD51" s="14" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE51" s="14" t="str">
@@ -10366,7 +11090,7 @@
         <v/>
       </c>
       <c r="BF51" s="57">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BG51" s="14">
@@ -10471,7 +11195,7 @@
         <v>0</v>
       </c>
       <c r="AZ52" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1556</v>
       </c>
       <c r="BA52" s="31" t="e">
@@ -10487,7 +11211,7 @@
         <v>0</v>
       </c>
       <c r="BD52" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE52" s="61" t="str">
@@ -10495,7 +11219,7 @@
         <v/>
       </c>
       <c r="BF52" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG52" s="31">
@@ -10600,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="AZ53" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1556</v>
       </c>
       <c r="BA53" s="31" t="e">
@@ -10616,7 +11340,7 @@
         <v>0</v>
       </c>
       <c r="BD53" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE53" s="61" t="str">
@@ -10624,7 +11348,7 @@
         <v/>
       </c>
       <c r="BF53" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG53" s="31">
@@ -10729,7 +11453,7 @@
         <v>0</v>
       </c>
       <c r="AZ54" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1556</v>
       </c>
       <c r="BA54" s="31" t="e">
@@ -10745,7 +11469,7 @@
         <v>0</v>
       </c>
       <c r="BD54" s="31" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE54" s="61">
@@ -10753,7 +11477,7 @@
         <v>0</v>
       </c>
       <c r="BF54" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG54" s="31" t="str">
@@ -10858,7 +11582,7 @@
         <v>0</v>
       </c>
       <c r="AZ55" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1556</v>
       </c>
       <c r="BA55" s="18" t="e">
@@ -10874,7 +11598,7 @@
         <v>0</v>
       </c>
       <c r="BD55" s="18" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE55" s="18">
@@ -10882,7 +11606,7 @@
         <v>0</v>
       </c>
       <c r="BF55" s="59" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG55" s="18" t="str">
@@ -10987,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="AZ56" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1540</v>
       </c>
       <c r="BA56" s="14" t="e">
@@ -11003,7 +11727,7 @@
         <v>0</v>
       </c>
       <c r="BD56" s="14" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE56" s="14" t="str">
@@ -11011,7 +11735,7 @@
         <v/>
       </c>
       <c r="BF56" s="57">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BG56" s="14">
@@ -11116,7 +11840,7 @@
         <v>0</v>
       </c>
       <c r="AZ57" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1540</v>
       </c>
       <c r="BA57" s="31" t="e">
@@ -11132,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="BD57" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE57" s="61" t="str">
@@ -11140,7 +11864,7 @@
         <v/>
       </c>
       <c r="BF57" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG57" s="31">
@@ -11245,7 +11969,7 @@
         <v>0</v>
       </c>
       <c r="AZ58" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1540</v>
       </c>
       <c r="BA58" s="31" t="e">
@@ -11261,7 +11985,7 @@
         <v>0</v>
       </c>
       <c r="BD58" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE58" s="61" t="str">
@@ -11269,7 +11993,7 @@
         <v/>
       </c>
       <c r="BF58" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG58" s="31">
@@ -11374,7 +12098,7 @@
         <v>0</v>
       </c>
       <c r="AZ59" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1540</v>
       </c>
       <c r="BA59" s="31" t="e">
@@ -11382,15 +12106,15 @@
         <v>#N/A</v>
       </c>
       <c r="BB59" s="31">
-        <f t="shared" ref="BB59:BB70" si="32">AK59/AP59</f>
+        <f t="shared" ref="BB59:BB70" si="36">AK59/AP59</f>
         <v>0</v>
       </c>
       <c r="BC59" s="31">
-        <f t="shared" ref="BC59:BC70" si="33">AJ59*24</f>
+        <f t="shared" ref="BC59:BC70" si="37">AJ59*24</f>
         <v>0</v>
       </c>
       <c r="BD59" s="31" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE59" s="61">
@@ -11398,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="BF59" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG59" s="31" t="str">
@@ -11495,7 +12219,7 @@
       <c r="AV60" s="17"/>
       <c r="AW60" s="41"/>
       <c r="AX60" s="16">
-        <f t="shared" ref="AX60:AX70" si="34">AT60*J60*AZ60/1000</f>
+        <f t="shared" ref="AX60:AX70" si="38">AT60*J60*AZ60/1000</f>
         <v>0</v>
       </c>
       <c r="AY60" s="17">
@@ -11503,23 +12227,23 @@
         <v>0</v>
       </c>
       <c r="AZ60" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1540</v>
       </c>
       <c r="BA60" s="18" t="e">
-        <f t="shared" ref="BA60:BA70" si="35">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
+        <f t="shared" ref="BA60:BA70" si="39">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
         <v>#N/A</v>
       </c>
       <c r="BB60" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC60" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD60" s="18" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE60" s="18">
@@ -11527,7 +12251,7 @@
         <v>0</v>
       </c>
       <c r="BF60" s="59" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG60" s="18" t="str">
@@ -11539,15 +12263,15 @@
         <v>0</v>
       </c>
       <c r="BI60" s="47">
-        <f t="shared" ref="BI60:BI70" si="36">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
+        <f t="shared" ref="BI60:BI70" si="40">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BJ60" s="67">
-        <f t="shared" ref="BJ60:BJ65" si="37">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
+        <f t="shared" ref="BJ60:BJ65" si="41">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
         <v>0</v>
       </c>
       <c r="BK60" s="49">
-        <f t="shared" ref="BK60:BK70" si="38">IF(BG60&lt;&gt;"",BG60,BH60)</f>
+        <f t="shared" ref="BK60:BK70" si="42">IF(BG60&lt;&gt;"",BG60,BH60)</f>
         <v>0</v>
       </c>
     </row>
@@ -11624,7 +12348,7 @@
       <c r="AV61" s="13"/>
       <c r="AW61" s="39"/>
       <c r="AX61" s="12">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY61" s="13">
@@ -11632,23 +12356,23 @@
         <v>0</v>
       </c>
       <c r="AZ61" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1524</v>
       </c>
       <c r="BA61" s="14" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB61" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC61" s="14">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD61" s="14" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE61" s="14" t="str">
@@ -11656,7 +12380,7 @@
         <v/>
       </c>
       <c r="BF61" s="57">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BG61" s="14">
@@ -11668,15 +12392,15 @@
         <v/>
       </c>
       <c r="BI61" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ61" s="66">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BK61" s="48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>11.43</v>
       </c>
     </row>
@@ -11753,7 +12477,7 @@
       <c r="AV62" s="30"/>
       <c r="AW62" s="40"/>
       <c r="AX62" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY62" s="30">
@@ -11761,23 +12485,23 @@
         <v>0</v>
       </c>
       <c r="AZ62" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1524</v>
       </c>
       <c r="BA62" s="31" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB62" s="31">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC62" s="31">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD62" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE62" s="61" t="str">
@@ -11785,7 +12509,7 @@
         <v/>
       </c>
       <c r="BF62" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG62" s="31">
@@ -11797,15 +12521,15 @@
         <v/>
       </c>
       <c r="BI62" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ62" s="66">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BK62" s="48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>11.43</v>
       </c>
     </row>
@@ -11882,7 +12606,7 @@
       <c r="AV63" s="30"/>
       <c r="AW63" s="40"/>
       <c r="AX63" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY63" s="30">
@@ -11890,23 +12614,23 @@
         <v>0</v>
       </c>
       <c r="AZ63" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1524</v>
       </c>
       <c r="BA63" s="31" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB63" s="31">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC63" s="31">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD63" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE63" s="61" t="str">
@@ -11914,7 +12638,7 @@
         <v/>
       </c>
       <c r="BF63" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG63" s="31">
@@ -11926,15 +12650,15 @@
         <v/>
       </c>
       <c r="BI63" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ63" s="66">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BK63" s="48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>11.43</v>
       </c>
     </row>
@@ -12011,7 +12735,7 @@
       <c r="AV64" s="30"/>
       <c r="AW64" s="40"/>
       <c r="AX64" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY64" s="30">
@@ -12019,23 +12743,23 @@
         <v>0</v>
       </c>
       <c r="AZ64" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1524</v>
       </c>
       <c r="BA64" s="31" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB64" s="31">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC64" s="31">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD64" s="31" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE64" s="61">
@@ -12043,7 +12767,7 @@
         <v>0</v>
       </c>
       <c r="BF64" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG64" s="31" t="str">
@@ -12055,15 +12779,15 @@
         <v>0</v>
       </c>
       <c r="BI64" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ64" s="66">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BK64" s="48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
     </row>
@@ -12140,7 +12864,7 @@
       <c r="AV65" s="17"/>
       <c r="AW65" s="41"/>
       <c r="AX65" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY65" s="17">
@@ -12148,23 +12872,23 @@
         <v>0</v>
       </c>
       <c r="AZ65" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1524</v>
       </c>
       <c r="BA65" s="18" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB65" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC65" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD65" s="18" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE65" s="18">
@@ -12172,7 +12896,7 @@
         <v>0</v>
       </c>
       <c r="BF65" s="59" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG65" s="18" t="str">
@@ -12184,15 +12908,15 @@
         <v>0</v>
       </c>
       <c r="BI65" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ65" s="66">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BK65" s="48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
     </row>
@@ -12269,7 +12993,7 @@
       <c r="AV66" s="4"/>
       <c r="AW66" s="22"/>
       <c r="AX66" s="12">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY66" s="13">
@@ -12277,23 +13001,23 @@
         <v>0</v>
       </c>
       <c r="AZ66" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1508</v>
       </c>
       <c r="BA66" s="14" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB66" s="14">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC66" s="14">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD66" s="14" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE66" s="14" t="str">
@@ -12301,7 +13025,7 @@
         <v/>
       </c>
       <c r="BF66" s="57">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BG66" s="14">
@@ -12313,12 +13037,12 @@
         <v/>
       </c>
       <c r="BI66" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ66" s="62"/>
       <c r="BK66" s="50">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>11.31</v>
       </c>
     </row>
@@ -12395,7 +13119,7 @@
       <c r="AV67" s="27"/>
       <c r="AW67" s="2"/>
       <c r="AX67" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY67" s="30">
@@ -12403,23 +13127,23 @@
         <v>0</v>
       </c>
       <c r="AZ67" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1508</v>
       </c>
       <c r="BA67" s="31" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB67" s="31">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC67" s="31">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD67" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE67" s="61" t="str">
@@ -12427,7 +13151,7 @@
         <v/>
       </c>
       <c r="BF67" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG67" s="31">
@@ -12439,12 +13163,12 @@
         <v/>
       </c>
       <c r="BI67" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ67" s="63"/>
       <c r="BK67" s="48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>11.31</v>
       </c>
     </row>
@@ -12521,7 +13245,7 @@
       <c r="AV68" s="30"/>
       <c r="AW68" s="40"/>
       <c r="AX68" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY68" s="30">
@@ -12529,23 +13253,23 @@
         <v>0</v>
       </c>
       <c r="AZ68" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1508</v>
       </c>
       <c r="BA68" s="31" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB68" s="31">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC68" s="31">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD68" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BE68" s="61" t="str">
@@ -12553,7 +13277,7 @@
         <v/>
       </c>
       <c r="BF68" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG68" s="31">
@@ -12565,12 +13289,12 @@
         <v/>
       </c>
       <c r="BI68" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ68" s="63"/>
       <c r="BK68" s="48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>11.31</v>
       </c>
     </row>
@@ -12647,7 +13371,7 @@
       <c r="AV69" s="30"/>
       <c r="AW69" s="40"/>
       <c r="AX69" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY69" s="30">
@@ -12655,23 +13379,23 @@
         <v>0</v>
       </c>
       <c r="AZ69" s="30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1508</v>
       </c>
       <c r="BA69" s="31" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB69" s="31">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC69" s="31">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD69" s="31" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE69" s="61">
@@ -12679,7 +13403,7 @@
         <v>0</v>
       </c>
       <c r="BF69" s="58" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG69" s="31" t="str">
@@ -12691,12 +13415,12 @@
         <v>0</v>
       </c>
       <c r="BI69" s="46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ69" s="63"/>
       <c r="BK69" s="48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
     </row>
@@ -12773,7 +13497,7 @@
       <c r="AV70" s="17"/>
       <c r="AW70" s="41"/>
       <c r="AX70" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AY70" s="17">
@@ -12781,23 +13505,23 @@
         <v>0</v>
       </c>
       <c r="AZ70" s="17">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>1508</v>
       </c>
       <c r="BA70" s="18" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#N/A</v>
       </c>
       <c r="BB70" s="18">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BC70" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD70" s="18" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BE70" s="18">
@@ -12805,7 +13529,7 @@
         <v>0</v>
       </c>
       <c r="BF70" s="59" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG70" s="18" t="str">
@@ -12817,12 +13541,12 @@
         <v>0</v>
       </c>
       <c r="BI70" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BJ70" s="64"/>
       <c r="BK70" s="49">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
     </row>
@@ -12868,15 +13592,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -13099,6 +13814,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -13118,14 +13842,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13140,6 +13856,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1841" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{837ABAE3-FB6F-4FDF-883D-57F616BF18AE}"/>
+  <xr:revisionPtr revIDLastSave="1845" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FE016DD-E658-4756-9B9A-DA23EF794DAA}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3720" yWindow="3135" windowWidth="36000" windowHeight="19215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -1476,16 +1476,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BK70"/>
-  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="60" width="12.6640625" customWidth="1"/>
-    <col min="61" max="61" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="62" max="63" width="16.33203125" customWidth="1"/>
+    <col min="2" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="60" width="12.7109375" customWidth="1"/>
+    <col min="61" max="61" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="62" max="63" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:63" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="BJ1" s="77"/>
       <c r="BK1" s="78"/>
     </row>
-    <row r="2" spans="1:63" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:63" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>3</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>54</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>55</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>57</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>58</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>53</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>17.4800465</v>
       </c>
     </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>17.745815000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>17.393346000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>21.373875000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>14.022246000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>58</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>17.715888</v>
       </c>
     </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>53</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>11.539479000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>12.608789925000002</v>
       </c>
     </row>
-    <row r="17" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>55</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>11.993802225000001</v>
       </c>
     </row>
-    <row r="18" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>13.025639999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>3.9633683594627347</v>
       </c>
     </row>
-    <row r="20" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>8.4828514616618094</v>
       </c>
     </row>
-    <row r="21" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>13.18215</v>
       </c>
     </row>
-    <row r="22" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>13.150274999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>13.12635</v>
       </c>
     </row>
-    <row r="24" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>57</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>5.3590759753051112</v>
       </c>
     </row>
-    <row r="25" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>58</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>7.4775654747660001</v>
       </c>
     </row>
-    <row r="26" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>6.7380460000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -7154,7 +7154,7 @@
         <v>4.2185063447336155</v>
       </c>
     </row>
-    <row r="30" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>3.6766410485124208</v>
       </c>
     </row>
-    <row r="31" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>53</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>54</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>55</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>57</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>7.6791147043425241</v>
       </c>
     </row>
-    <row r="35" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>58</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>10.261394893996174</v>
       </c>
     </row>
-    <row r="36" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>53</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>54</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>55</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>57</v>
       </c>
@@ -9154,7 +9154,7 @@
         <v>8.4915585188980369</v>
       </c>
     </row>
-    <row r="40" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>58</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>2.3220682771976411</v>
       </c>
     </row>
-    <row r="41" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>53</v>
       </c>
@@ -9467,11 +9467,11 @@
         <v>46</v>
       </c>
       <c r="AM41" s="13">
-        <f t="shared" ref="AM41:AM45" si="32">AK41-AK36</f>
+        <f t="shared" ref="AM41:AN45" si="32">AK41-AK36</f>
         <v>24</v>
       </c>
       <c r="AN41" s="13">
-        <f t="shared" ref="AN41:AN45" si="33">AL41-AL36</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AO41" s="42">
@@ -9504,7 +9504,7 @@
         <v>0.39191470079999996</v>
       </c>
       <c r="AZ41" s="13">
-        <f t="shared" ref="AZ41:AZ70" si="34">AP41+SUM(AG41:AI41,AK41:AL41)-((AO41+1)*D41)</f>
+        <f t="shared" ref="AZ41:AZ70" si="33">AP41+SUM(AG41:AI41,AK41:AL41)-((AO41+1)*D41)</f>
         <v>1843.76</v>
       </c>
       <c r="BA41" s="14">
@@ -9552,7 +9552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>54</v>
       </c>
@@ -9668,7 +9668,7 @@
         <v>27</v>
       </c>
       <c r="AN42" s="30">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AO42" s="43">
@@ -9689,7 +9689,9 @@
       <c r="AT42" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU42" s="15"/>
+      <c r="AU42" s="15">
+        <v>2.5062731433902599E-2</v>
+      </c>
       <c r="AV42" s="30"/>
       <c r="AW42" s="40"/>
       <c r="AX42" s="15">
@@ -9701,7 +9703,7 @@
         <v>0.36311016000000002</v>
       </c>
       <c r="AZ42" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1875.25</v>
       </c>
       <c r="BA42" s="31">
@@ -9718,7 +9720,7 @@
       </c>
       <c r="BD42" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>3.2638116056545728E-2</v>
       </c>
       <c r="BE42" s="61" t="str">
         <f t="shared" si="27"/>
@@ -9738,18 +9740,18 @@
       </c>
       <c r="BI42" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>84.774327419599302</v>
       </c>
       <c r="BJ42" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3.2638116056545728E-2</v>
       </c>
       <c r="BK42" s="48">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>55</v>
       </c>
@@ -9865,7 +9867,7 @@
         <v>31</v>
       </c>
       <c r="AN43" s="30">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AO43" s="43">
@@ -9886,7 +9888,9 @@
       <c r="AT43" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU43" s="15"/>
+      <c r="AU43" s="15">
+        <v>1.39703591248772E-2</v>
+      </c>
       <c r="AV43" s="30"/>
       <c r="AW43" s="40"/>
       <c r="AX43" s="15">
@@ -9898,7 +9902,7 @@
         <v>0.36010705920000002</v>
       </c>
       <c r="AZ43" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1862.8400000000001</v>
       </c>
       <c r="BA43" s="31">
@@ -9915,7 +9919,7 @@
       </c>
       <c r="BD43" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.8072599855684893E-2</v>
       </c>
       <c r="BE43" s="61" t="str">
         <f t="shared" si="27"/>
@@ -9935,18 +9939,18 @@
       </c>
       <c r="BI43" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>46.941817806973752</v>
       </c>
       <c r="BJ43" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.8072599855684893E-2</v>
       </c>
       <c r="BK43" s="48">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>57</v>
       </c>
@@ -10062,7 +10066,7 @@
         <v>32</v>
       </c>
       <c r="AN44" s="30">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>10</v>
       </c>
       <c r="AO44" s="43">
@@ -10084,8 +10088,12 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU44" s="15"/>
-      <c r="AV44" s="30"/>
-      <c r="AW44" s="40"/>
+      <c r="AV44" s="30">
+        <v>1.4730434815927999E-2</v>
+      </c>
+      <c r="AW44" s="40">
+        <v>9.9999999999999995E-8</v>
+      </c>
       <c r="AX44" s="15">
         <f t="shared" si="4"/>
         <v>1.6155631200000003E-2</v>
@@ -10095,7 +10103,7 @@
         <v>0.39955449600000009</v>
       </c>
       <c r="AZ44" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1852.71</v>
       </c>
       <c r="BA44" s="31">
@@ -10116,7 +10124,7 @@
       </c>
       <c r="BE44" s="61">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1.8952238810984696E-2</v>
       </c>
       <c r="BF44" s="58" t="str">
         <f t="shared" si="17"/>
@@ -10128,22 +10136,22 @@
       </c>
       <c r="BH44" s="31">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.8527099999999998E-4</v>
       </c>
       <c r="BI44" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>49.226594314245965</v>
       </c>
       <c r="BJ44" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.8952238810984696E-2</v>
       </c>
       <c r="BK44" s="48">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>58</v>
       </c>
@@ -10259,7 +10267,7 @@
         <v>31</v>
       </c>
       <c r="AN45" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>3</v>
       </c>
       <c r="AO45" s="44">
@@ -10281,8 +10289,12 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU45" s="16"/>
-      <c r="AV45" s="17"/>
-      <c r="AW45" s="41"/>
+      <c r="AV45" s="17">
+        <v>1.6126704454023699E-2</v>
+      </c>
+      <c r="AW45" s="41">
+        <v>1.63930790240546E-3</v>
+      </c>
       <c r="AX45" s="16">
         <f t="shared" si="4"/>
         <v>1.74604584E-2</v>
@@ -10292,7 +10304,7 @@
         <v>0.43917249599999997</v>
       </c>
       <c r="AZ45" s="17">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1889.6599999999999</v>
       </c>
       <c r="BA45" s="18">
@@ -10313,7 +10325,7 @@
       </c>
       <c r="BE45" s="18">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2.1162491901798905E-2</v>
       </c>
       <c r="BF45" s="59" t="str">
         <f t="shared" si="17"/>
@@ -10325,22 +10337,22 @@
       </c>
       <c r="BH45" s="18">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>3.0977345708595014</v>
       </c>
       <c r="BI45" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>54.967511433243914</v>
       </c>
       <c r="BJ45" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.1162491901798905E-2</v>
       </c>
       <c r="BK45" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3.0977345708595014</v>
       </c>
     </row>
-    <row r="46" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>53</v>
       </c>
@@ -10421,7 +10433,7 @@
         <v>0.40002216960000003</v>
       </c>
       <c r="AZ46" s="13">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1572</v>
       </c>
       <c r="BA46" s="14" t="e">
@@ -10469,7 +10481,7 @@
         <v>11.79</v>
       </c>
     </row>
-    <row r="47" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
@@ -10550,7 +10562,7 @@
         <v>0.36904919999999997</v>
       </c>
       <c r="AZ47" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1572</v>
       </c>
       <c r="BA47" s="31" t="e">
@@ -10574,7 +10586,7 @@
         <v/>
       </c>
       <c r="BF47" s="58" t="str">
-        <f t="shared" ref="BF47:BF70" si="35">IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
+        <f t="shared" ref="BF47:BF70" si="34">IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
         <v/>
       </c>
       <c r="BG47" s="31">
@@ -10598,7 +10610,7 @@
         <v>11.79</v>
       </c>
     </row>
-    <row r="48" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>55</v>
       </c>
@@ -10679,7 +10691,7 @@
         <v>0.35230030079999997</v>
       </c>
       <c r="AZ48" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1572</v>
       </c>
       <c r="BA48" s="31" t="e">
@@ -10703,7 +10715,7 @@
         <v/>
       </c>
       <c r="BF48" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG48" s="31">
@@ -10727,7 +10739,7 @@
         <v>11.79</v>
       </c>
     </row>
-    <row r="49" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -10808,7 +10820,7 @@
         <v>0.38773514880000004</v>
       </c>
       <c r="AZ49" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1572</v>
       </c>
       <c r="BA49" s="31" t="e">
@@ -10832,7 +10844,7 @@
         <v>0</v>
       </c>
       <c r="BF49" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG49" s="31" t="str">
@@ -10856,7 +10868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>58</v>
       </c>
@@ -10937,7 +10949,7 @@
         <v>0.41905100159999997</v>
       </c>
       <c r="AZ50" s="17">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1572</v>
       </c>
       <c r="BA50" s="18" t="e">
@@ -10961,7 +10973,7 @@
         <v>0</v>
       </c>
       <c r="BF50" s="59" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG50" s="18" t="str">
@@ -10985,7 +10997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
@@ -11066,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="AZ51" s="13">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1556</v>
       </c>
       <c r="BA51" s="14" t="e">
@@ -11090,7 +11102,7 @@
         <v/>
       </c>
       <c r="BF51" s="57">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BG51" s="14">
@@ -11114,7 +11126,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="52" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>54</v>
       </c>
@@ -11195,7 +11207,7 @@
         <v>0</v>
       </c>
       <c r="AZ52" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1556</v>
       </c>
       <c r="BA52" s="31" t="e">
@@ -11219,7 +11231,7 @@
         <v/>
       </c>
       <c r="BF52" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG52" s="31">
@@ -11243,7 +11255,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="53" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>55</v>
       </c>
@@ -11324,7 +11336,7 @@
         <v>0</v>
       </c>
       <c r="AZ53" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1556</v>
       </c>
       <c r="BA53" s="31" t="e">
@@ -11348,7 +11360,7 @@
         <v/>
       </c>
       <c r="BF53" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG53" s="31">
@@ -11372,7 +11384,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="54" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -11453,7 +11465,7 @@
         <v>0</v>
       </c>
       <c r="AZ54" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1556</v>
       </c>
       <c r="BA54" s="31" t="e">
@@ -11477,7 +11489,7 @@
         <v>0</v>
       </c>
       <c r="BF54" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG54" s="31" t="str">
@@ -11501,7 +11513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -11582,7 +11594,7 @@
         <v>0</v>
       </c>
       <c r="AZ55" s="17">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1556</v>
       </c>
       <c r="BA55" s="18" t="e">
@@ -11606,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="BF55" s="59" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG55" s="18" t="str">
@@ -11630,7 +11642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>53</v>
       </c>
@@ -11711,7 +11723,7 @@
         <v>0</v>
       </c>
       <c r="AZ56" s="13">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1540</v>
       </c>
       <c r="BA56" s="14" t="e">
@@ -11735,7 +11747,7 @@
         <v/>
       </c>
       <c r="BF56" s="57">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BG56" s="14">
@@ -11759,7 +11771,7 @@
         <v>11.55</v>
       </c>
     </row>
-    <row r="57" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>54</v>
       </c>
@@ -11840,7 +11852,7 @@
         <v>0</v>
       </c>
       <c r="AZ57" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1540</v>
       </c>
       <c r="BA57" s="31" t="e">
@@ -11864,7 +11876,7 @@
         <v/>
       </c>
       <c r="BF57" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG57" s="31">
@@ -11888,7 +11900,7 @@
         <v>11.55</v>
       </c>
     </row>
-    <row r="58" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>55</v>
       </c>
@@ -11969,7 +11981,7 @@
         <v>0</v>
       </c>
       <c r="AZ58" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1540</v>
       </c>
       <c r="BA58" s="31" t="e">
@@ -11993,7 +12005,7 @@
         <v/>
       </c>
       <c r="BF58" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG58" s="31">
@@ -12017,7 +12029,7 @@
         <v>11.55</v>
       </c>
     </row>
-    <row r="59" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
@@ -12098,7 +12110,7 @@
         <v>0</v>
       </c>
       <c r="AZ59" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1540</v>
       </c>
       <c r="BA59" s="31" t="e">
@@ -12106,11 +12118,11 @@
         <v>#N/A</v>
       </c>
       <c r="BB59" s="31">
-        <f t="shared" ref="BB59:BB70" si="36">AK59/AP59</f>
+        <f t="shared" ref="BB59:BB70" si="35">AK59/AP59</f>
         <v>0</v>
       </c>
       <c r="BC59" s="31">
-        <f t="shared" ref="BC59:BC70" si="37">AJ59*24</f>
+        <f t="shared" ref="BC59:BC70" si="36">AJ59*24</f>
         <v>0</v>
       </c>
       <c r="BD59" s="31" t="str">
@@ -12122,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="BF59" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG59" s="31" t="str">
@@ -12146,7 +12158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
@@ -12219,7 +12231,7 @@
       <c r="AV60" s="17"/>
       <c r="AW60" s="41"/>
       <c r="AX60" s="16">
-        <f t="shared" ref="AX60:AX70" si="38">AT60*J60*AZ60/1000</f>
+        <f t="shared" ref="AX60:AX70" si="37">AT60*J60*AZ60/1000</f>
         <v>0</v>
       </c>
       <c r="AY60" s="17">
@@ -12227,19 +12239,19 @@
         <v>0</v>
       </c>
       <c r="AZ60" s="17">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1540</v>
       </c>
       <c r="BA60" s="18" t="e">
-        <f t="shared" ref="BA60:BA70" si="39">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
+        <f t="shared" ref="BA60:BA70" si="38">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
         <v>#N/A</v>
       </c>
       <c r="BB60" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC60" s="18">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC60" s="18">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD60" s="18" t="str">
@@ -12251,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="BF60" s="59" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG60" s="18" t="str">
@@ -12263,19 +12275,19 @@
         <v>0</v>
       </c>
       <c r="BI60" s="47">
-        <f t="shared" ref="BI60:BI70" si="40">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
+        <f t="shared" ref="BI60:BI70" si="39">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BJ60" s="67">
-        <f t="shared" ref="BJ60:BJ65" si="41">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
+        <f t="shared" ref="BJ60:BJ65" si="40">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
         <v>0</v>
       </c>
       <c r="BK60" s="49">
-        <f t="shared" ref="BK60:BK70" si="42">IF(BG60&lt;&gt;"",BG60,BH60)</f>
+        <f t="shared" ref="BK60:BK70" si="41">IF(BG60&lt;&gt;"",BG60,BH60)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>53</v>
       </c>
@@ -12348,7 +12360,7 @@
       <c r="AV61" s="13"/>
       <c r="AW61" s="39"/>
       <c r="AX61" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY61" s="13">
@@ -12356,19 +12368,19 @@
         <v>0</v>
       </c>
       <c r="AZ61" s="13">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA61" s="14" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB61" s="14">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC61" s="14">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC61" s="14">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD61" s="14" t="str">
@@ -12380,7 +12392,7 @@
         <v/>
       </c>
       <c r="BF61" s="57">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BG61" s="14">
@@ -12392,19 +12404,19 @@
         <v/>
       </c>
       <c r="BI61" s="46">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BJ61" s="66">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="BJ61" s="66">
+      <c r="BK61" s="48">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="BK61" s="48">
-        <f t="shared" si="42"/>
         <v>11.43</v>
       </c>
     </row>
-    <row r="62" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>54</v>
       </c>
@@ -12477,7 +12489,7 @@
       <c r="AV62" s="30"/>
       <c r="AW62" s="40"/>
       <c r="AX62" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY62" s="30">
@@ -12485,19 +12497,19 @@
         <v>0</v>
       </c>
       <c r="AZ62" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA62" s="31" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB62" s="31">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC62" s="31">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC62" s="31">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD62" s="31">
@@ -12509,7 +12521,7 @@
         <v/>
       </c>
       <c r="BF62" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG62" s="31">
@@ -12521,19 +12533,19 @@
         <v/>
       </c>
       <c r="BI62" s="46">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BJ62" s="66">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="BJ62" s="66">
+      <c r="BK62" s="48">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="BK62" s="48">
-        <f t="shared" si="42"/>
         <v>11.43</v>
       </c>
     </row>
-    <row r="63" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>55</v>
       </c>
@@ -12606,7 +12618,7 @@
       <c r="AV63" s="30"/>
       <c r="AW63" s="40"/>
       <c r="AX63" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY63" s="30">
@@ -12614,19 +12626,19 @@
         <v>0</v>
       </c>
       <c r="AZ63" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA63" s="31" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB63" s="31">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC63" s="31">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC63" s="31">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD63" s="31">
@@ -12638,7 +12650,7 @@
         <v/>
       </c>
       <c r="BF63" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG63" s="31">
@@ -12650,19 +12662,19 @@
         <v/>
       </c>
       <c r="BI63" s="46">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BJ63" s="66">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="BJ63" s="66">
+      <c r="BK63" s="48">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="BK63" s="48">
-        <f t="shared" si="42"/>
         <v>11.43</v>
       </c>
     </row>
-    <row r="64" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>57</v>
       </c>
@@ -12735,7 +12747,7 @@
       <c r="AV64" s="30"/>
       <c r="AW64" s="40"/>
       <c r="AX64" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY64" s="30">
@@ -12743,19 +12755,19 @@
         <v>0</v>
       </c>
       <c r="AZ64" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA64" s="31" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB64" s="31">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC64" s="31">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC64" s="31">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD64" s="31" t="str">
@@ -12767,7 +12779,7 @@
         <v>0</v>
       </c>
       <c r="BF64" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG64" s="31" t="str">
@@ -12779,19 +12791,19 @@
         <v>0</v>
       </c>
       <c r="BI64" s="46">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BJ64" s="66">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="BJ64" s="66">
+      <c r="BK64" s="48">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="BK64" s="48">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="65" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>58</v>
       </c>
@@ -12864,7 +12876,7 @@
       <c r="AV65" s="17"/>
       <c r="AW65" s="41"/>
       <c r="AX65" s="16">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY65" s="17">
@@ -12872,19 +12884,19 @@
         <v>0</v>
       </c>
       <c r="AZ65" s="17">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA65" s="18" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB65" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC65" s="18">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC65" s="18">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD65" s="18" t="str">
@@ -12896,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="BF65" s="59" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG65" s="18" t="str">
@@ -12908,19 +12920,19 @@
         <v>0</v>
       </c>
       <c r="BI65" s="46">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="BJ65" s="66">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="BJ65" s="66">
+      <c r="BK65" s="48">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="BK65" s="48">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="66" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>53</v>
       </c>
@@ -12993,7 +13005,7 @@
       <c r="AV66" s="4"/>
       <c r="AW66" s="22"/>
       <c r="AX66" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY66" s="13">
@@ -13001,19 +13013,19 @@
         <v>0</v>
       </c>
       <c r="AZ66" s="13">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1508</v>
       </c>
       <c r="BA66" s="14" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB66" s="14">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC66" s="14">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC66" s="14">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD66" s="14" t="str">
@@ -13025,7 +13037,7 @@
         <v/>
       </c>
       <c r="BF66" s="57">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="BG66" s="14">
@@ -13037,16 +13049,16 @@
         <v/>
       </c>
       <c r="BI66" s="45">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BJ66" s="62"/>
       <c r="BK66" s="50">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>11.31</v>
       </c>
     </row>
-    <row r="67" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>54</v>
       </c>
@@ -13119,7 +13131,7 @@
       <c r="AV67" s="27"/>
       <c r="AW67" s="2"/>
       <c r="AX67" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY67" s="30">
@@ -13127,19 +13139,19 @@
         <v>0</v>
       </c>
       <c r="AZ67" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1508</v>
       </c>
       <c r="BA67" s="31" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB67" s="31">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC67" s="31">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC67" s="31">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD67" s="31">
@@ -13151,7 +13163,7 @@
         <v/>
       </c>
       <c r="BF67" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG67" s="31">
@@ -13163,16 +13175,16 @@
         <v/>
       </c>
       <c r="BI67" s="46">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BJ67" s="63"/>
       <c r="BK67" s="48">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>11.31</v>
       </c>
     </row>
-    <row r="68" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>55</v>
       </c>
@@ -13245,7 +13257,7 @@
       <c r="AV68" s="30"/>
       <c r="AW68" s="40"/>
       <c r="AX68" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY68" s="30">
@@ -13253,19 +13265,19 @@
         <v>0</v>
       </c>
       <c r="AZ68" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1508</v>
       </c>
       <c r="BA68" s="31" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB68" s="31">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC68" s="31">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC68" s="31">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD68" s="31">
@@ -13277,7 +13289,7 @@
         <v/>
       </c>
       <c r="BF68" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG68" s="31">
@@ -13289,16 +13301,16 @@
         <v/>
       </c>
       <c r="BI68" s="46">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BJ68" s="63"/>
       <c r="BK68" s="48">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>11.31</v>
       </c>
     </row>
-    <row r="69" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>57</v>
       </c>
@@ -13371,7 +13383,7 @@
       <c r="AV69" s="30"/>
       <c r="AW69" s="40"/>
       <c r="AX69" s="15">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY69" s="30">
@@ -13379,19 +13391,19 @@
         <v>0</v>
       </c>
       <c r="AZ69" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1508</v>
       </c>
       <c r="BA69" s="31" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB69" s="31">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC69" s="31">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC69" s="31">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD69" s="31" t="str">
@@ -13403,7 +13415,7 @@
         <v>0</v>
       </c>
       <c r="BF69" s="58" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG69" s="31" t="str">
@@ -13415,16 +13427,16 @@
         <v>0</v>
       </c>
       <c r="BI69" s="46">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BJ69" s="63"/>
       <c r="BK69" s="48">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>58</v>
       </c>
@@ -13497,7 +13509,7 @@
       <c r="AV70" s="17"/>
       <c r="AW70" s="41"/>
       <c r="AX70" s="16">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AY70" s="17">
@@ -13505,19 +13517,19 @@
         <v>0</v>
       </c>
       <c r="AZ70" s="17">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>1508</v>
       </c>
       <c r="BA70" s="18" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>#N/A</v>
       </c>
       <c r="BB70" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BC70" s="18">
         <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="BC70" s="18">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BD70" s="18" t="str">
@@ -13529,7 +13541,7 @@
         <v>0</v>
       </c>
       <c r="BF70" s="59" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG70" s="18" t="str">
@@ -13541,12 +13553,12 @@
         <v>0</v>
       </c>
       <c r="BI70" s="47">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BJ70" s="64"/>
       <c r="BK70" s="49">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
     </row>
@@ -13585,13 +13597,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A841E7D6-1405-4AC8-A599-0CE4601ECD66}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -13814,34 +13853,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13858,29 +13895,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1845" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FE016DD-E658-4756-9B9A-DA23EF794DAA}"/>
+  <xr:revisionPtr revIDLastSave="1871" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85D6E467-87DE-440E-A6D3-135711F6C709}"/>
   <bookViews>
-    <workbookView xWindow="-3720" yWindow="3135" windowWidth="36000" windowHeight="19215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -952,7 +952,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -1092,6 +1092,7 @@
     <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1476,16 +1477,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BK70"/>
-  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="60" width="12.7109375" customWidth="1"/>
-    <col min="61" max="61" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="62" max="63" width="16.28515625" customWidth="1"/>
+    <col min="2" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="60" width="12.6640625" customWidth="1"/>
+    <col min="61" max="61" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="63" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:63" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1565,7 @@
       <c r="BJ1" s="77"/>
       <c r="BK1" s="78"/>
     </row>
-    <row r="2" spans="1:63" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:63" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="33" t="s">
         <v>3</v>
       </c>
@@ -1755,7 +1756,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -1951,7 +1952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>54</v>
       </c>
@@ -2149,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>55</v>
       </c>
@@ -2347,7 +2348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
@@ -2543,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>57</v>
       </c>
@@ -2744,7 +2745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>58</v>
       </c>
@@ -2945,7 +2946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>53</v>
       </c>
@@ -3144,7 +3145,7 @@
         <v>17.4800465</v>
       </c>
     </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -3345,7 +3346,7 @@
         <v>17.745815000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
@@ -3546,7 +3547,7 @@
         <v>17.393346000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
@@ -3745,7 +3746,7 @@
         <v>21.373875000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
@@ -3948,7 +3949,7 @@
         <v>14.022246000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>58</v>
       </c>
@@ -4153,7 +4154,7 @@
         <v>17.715888</v>
       </c>
     </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>53</v>
       </c>
@@ -4352,7 +4353,7 @@
         <v>11.539479000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
@@ -4553,7 +4554,7 @@
         <v>12.608789925000002</v>
       </c>
     </row>
-    <row r="17" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>55</v>
       </c>
@@ -4754,7 +4755,7 @@
         <v>11.993802225000001</v>
       </c>
     </row>
-    <row r="18" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -4943,7 +4944,7 @@
         <v>13.025639999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
@@ -5143,7 +5144,7 @@
         <v>3.9633683594627347</v>
       </c>
     </row>
-    <row r="20" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -5346,7 +5347,7 @@
         <v>8.4828514616618094</v>
       </c>
     </row>
-    <row r="21" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
@@ -5545,7 +5546,7 @@
         <v>13.18215</v>
       </c>
     </row>
-    <row r="22" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -5746,7 +5747,7 @@
         <v>13.150274999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -5947,7 +5948,7 @@
         <v>13.12635</v>
       </c>
     </row>
-    <row r="24" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>57</v>
       </c>
@@ -6150,7 +6151,7 @@
         <v>5.3590759753051112</v>
       </c>
     </row>
-    <row r="25" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>58</v>
       </c>
@@ -6353,7 +6354,7 @@
         <v>7.4775654747660001</v>
       </c>
     </row>
-    <row r="26" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
@@ -6552,7 +6553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
@@ -6753,7 +6754,7 @@
         <v>6.7380460000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -6954,7 +6955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -7154,7 +7155,7 @@
         <v>4.2185063447336155</v>
       </c>
     </row>
-    <row r="30" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -7354,7 +7355,7 @@
         <v>3.6766410485124208</v>
       </c>
     </row>
-    <row r="31" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>53</v>
       </c>
@@ -7553,7 +7554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>54</v>
       </c>
@@ -7754,7 +7755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>55</v>
       </c>
@@ -7955,7 +7956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>57</v>
       </c>
@@ -8158,7 +8159,7 @@
         <v>7.6791147043425241</v>
       </c>
     </row>
-    <row r="35" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>58</v>
       </c>
@@ -8361,7 +8362,7 @@
         <v>10.261394893996174</v>
       </c>
     </row>
-    <row r="36" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>53</v>
       </c>
@@ -8558,7 +8559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>54</v>
       </c>
@@ -8757,7 +8758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>55</v>
       </c>
@@ -8956,7 +8957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>57</v>
       </c>
@@ -9154,7 +9155,7 @@
         <v>8.4915585188980369</v>
       </c>
     </row>
-    <row r="40" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>58</v>
       </c>
@@ -9355,7 +9356,7 @@
         <v>2.3220682771976411</v>
       </c>
     </row>
-    <row r="41" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>53</v>
       </c>
@@ -9552,7 +9553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>54</v>
       </c>
@@ -9751,7 +9752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>55</v>
       </c>
@@ -9950,7 +9951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>57</v>
       </c>
@@ -10151,7 +10152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>58</v>
       </c>
@@ -10352,7 +10353,7 @@
         <v>3.0977345708595014</v>
       </c>
     </row>
-    <row r="46" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>53</v>
       </c>
@@ -10370,39 +10371,105 @@
         <v>4309.7</v>
       </c>
       <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
-      <c r="X46" s="27"/>
-      <c r="Y46" s="27"/>
-      <c r="Z46" s="27"/>
-      <c r="AA46" s="27"/>
-      <c r="AB46" s="2"/>
-      <c r="AC46" s="3"/>
-      <c r="AD46" s="4"/>
-      <c r="AE46" s="4"/>
-      <c r="AF46" s="4"/>
-      <c r="AG46" s="4"/>
-      <c r="AH46" s="4"/>
-      <c r="AI46" s="4"/>
+      <c r="H46" s="29">
+        <v>3868.2750000000001</v>
+      </c>
+      <c r="I46" s="27">
+        <v>22.5</v>
+      </c>
+      <c r="J46" s="27">
+        <v>21.1</v>
+      </c>
+      <c r="K46" s="27">
+        <v>93.8</v>
+      </c>
+      <c r="L46" s="27">
+        <v>16.7</v>
+      </c>
+      <c r="M46" s="27">
+        <v>369</v>
+      </c>
+      <c r="N46" s="27">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="O46" s="27">
+        <v>0.22</v>
+      </c>
+      <c r="P46" s="27">
+        <v>2.76</v>
+      </c>
+      <c r="Q46" s="27">
+        <v>0.19</v>
+      </c>
+      <c r="R46" s="27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="S46" s="27">
+        <v>1.86</v>
+      </c>
+      <c r="T46" s="27">
+        <v>7.2590000000000003</v>
+      </c>
+      <c r="U46" s="27">
+        <v>118.5</v>
+      </c>
+      <c r="V46" s="27">
+        <v>30.4</v>
+      </c>
+      <c r="W46" s="27">
+        <v>2.19</v>
+      </c>
+      <c r="X46" s="27">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="Y46" s="27">
+        <v>51.6</v>
+      </c>
+      <c r="Z46" s="27">
+        <v>104</v>
+      </c>
+      <c r="AA46" s="27">
+        <v>24.6</v>
+      </c>
+      <c r="AB46" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD46" s="4">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="AE46" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="AF46" s="4">
+        <v>34</v>
+      </c>
+      <c r="AG46" s="4">
+        <v>31.32</v>
+      </c>
+      <c r="AH46" s="4">
+        <v>59.68</v>
+      </c>
+      <c r="AI46" s="4">
+        <v>7</v>
+      </c>
       <c r="AJ46" s="4"/>
-      <c r="AK46" s="4"/>
-      <c r="AL46" s="4"/>
-      <c r="AM46" s="4"/>
-      <c r="AN46" s="4"/>
+      <c r="AK46" s="13">
+        <v>148</v>
+      </c>
+      <c r="AL46" s="13">
+        <v>46</v>
+      </c>
+      <c r="AM46" s="13">
+        <f t="shared" ref="AM46:AM50" si="34">AK46-AK41</f>
+        <v>24</v>
+      </c>
+      <c r="AN46" s="13">
+        <f t="shared" ref="AN46:AN50" si="35">AL46-AL41</f>
+        <v>0</v>
+      </c>
       <c r="AO46" s="42">
         <v>15</v>
       </c>
@@ -10426,7 +10493,7 @@
       <c r="AW46" s="39"/>
       <c r="AX46" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.5732160000000002E-2</v>
       </c>
       <c r="AY46" s="13">
         <f t="shared" si="21"/>
@@ -10434,15 +10501,15 @@
       </c>
       <c r="AZ46" s="13">
         <f t="shared" si="33"/>
-        <v>1572</v>
-      </c>
-      <c r="BA46" s="14" t="e">
+        <v>1864</v>
+      </c>
+      <c r="BA46" s="14">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>7.9399141630901282E-2</v>
       </c>
       <c r="BB46" s="14">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>8.7058823529411758E-2</v>
       </c>
       <c r="BC46" s="14">
         <f t="shared" si="26"/>
@@ -10458,11 +10525,11 @@
       </c>
       <c r="BF46" s="57">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.5732160000000002E-2</v>
       </c>
       <c r="BG46" s="14">
         <f t="shared" si="24"/>
-        <v>11.79</v>
+        <v>0</v>
       </c>
       <c r="BH46" s="14" t="str">
         <f t="shared" si="28"/>
@@ -10470,18 +10537,18 @@
       </c>
       <c r="BI46" s="45">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>40.862753246753257</v>
       </c>
       <c r="BJ46" s="65">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.5732160000000002E-2</v>
       </c>
       <c r="BK46" s="50">
         <f t="shared" si="12"/>
-        <v>11.79</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>54</v>
       </c>
@@ -10499,39 +10566,105 @@
         <v>4309.7</v>
       </c>
       <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="27"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="27"/>
-      <c r="R47" s="27"/>
-      <c r="S47" s="27"/>
-      <c r="T47" s="27"/>
-      <c r="U47" s="27"/>
-      <c r="V47" s="27"/>
-      <c r="W47" s="27"/>
-      <c r="X47" s="27"/>
-      <c r="Y47" s="27"/>
-      <c r="Z47" s="27"/>
-      <c r="AA47" s="27"/>
-      <c r="AB47" s="2"/>
-      <c r="AC47" s="1"/>
-      <c r="AD47" s="27"/>
-      <c r="AE47" s="27"/>
-      <c r="AF47" s="27"/>
-      <c r="AG47" s="27"/>
-      <c r="AH47" s="27"/>
-      <c r="AI47" s="27"/>
+      <c r="H47" s="29">
+        <v>4008.18</v>
+      </c>
+      <c r="I47" s="27">
+        <v>20.2</v>
+      </c>
+      <c r="J47" s="27">
+        <v>19.3</v>
+      </c>
+      <c r="K47" s="27">
+        <v>95.8</v>
+      </c>
+      <c r="L47" s="27">
+        <v>18.2</v>
+      </c>
+      <c r="M47" s="27">
+        <v>402</v>
+      </c>
+      <c r="N47" s="27">
+        <v>2.38</v>
+      </c>
+      <c r="O47" s="27">
+        <v>0.24</v>
+      </c>
+      <c r="P47" s="27">
+        <v>2.5</v>
+      </c>
+      <c r="Q47" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="R47" s="27">
+        <v>1.26</v>
+      </c>
+      <c r="S47" s="27">
+        <v>1.45</v>
+      </c>
+      <c r="T47" s="27">
+        <v>7.218</v>
+      </c>
+      <c r="U47" s="27">
+        <v>159.5</v>
+      </c>
+      <c r="V47" s="27">
+        <v>37</v>
+      </c>
+      <c r="W47" s="27">
+        <v>1.57</v>
+      </c>
+      <c r="X47" s="27">
+        <v>170.1</v>
+      </c>
+      <c r="Y47" s="27">
+        <v>63.1</v>
+      </c>
+      <c r="Z47" s="27">
+        <v>139.9</v>
+      </c>
+      <c r="AA47" s="27">
+        <v>29.9</v>
+      </c>
+      <c r="AB47" s="2">
+        <v>7.258</v>
+      </c>
+      <c r="AC47" s="1">
+        <v>300</v>
+      </c>
+      <c r="AD47" s="27">
+        <v>0.503</v>
+      </c>
+      <c r="AE47" s="27">
+        <v>7.23</v>
+      </c>
+      <c r="AF47" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG47" s="27">
+        <v>33.53</v>
+      </c>
+      <c r="AH47" s="27">
+        <v>6.72</v>
+      </c>
+      <c r="AI47" s="27">
+        <v>5</v>
+      </c>
       <c r="AJ47" s="27"/>
-      <c r="AK47" s="27"/>
-      <c r="AL47" s="27"/>
-      <c r="AM47" s="27"/>
-      <c r="AN47" s="27"/>
+      <c r="AK47" s="89">
+        <v>232</v>
+      </c>
+      <c r="AL47" s="89">
+        <v>55</v>
+      </c>
+      <c r="AM47" s="30">
+        <f t="shared" si="34"/>
+        <v>45</v>
+      </c>
+      <c r="AN47" s="30">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
       <c r="AO47" s="43">
         <v>15</v>
       </c>
@@ -10555,7 +10688,7 @@
       <c r="AW47" s="40"/>
       <c r="AX47" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.470081E-2</v>
       </c>
       <c r="AY47" s="30">
         <f t="shared" si="21"/>
@@ -10563,15 +10696,15 @@
       </c>
       <c r="AZ47" s="30">
         <f t="shared" si="33"/>
-        <v>1572</v>
-      </c>
-      <c r="BA47" s="31" t="e">
+        <v>1904.25</v>
+      </c>
+      <c r="BA47" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.1218327425495602</v>
       </c>
       <c r="BB47" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.13647058823529412</v>
       </c>
       <c r="BC47" s="31">
         <f t="shared" si="26"/>
@@ -10586,12 +10719,12 @@
         <v/>
       </c>
       <c r="BF47" s="58" t="str">
-        <f t="shared" ref="BF47:BF70" si="34">IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
+        <f t="shared" ref="BF47:BF70" si="36">IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
         <v/>
       </c>
       <c r="BG47" s="31">
         <f t="shared" si="24"/>
-        <v>11.79</v>
+        <v>0</v>
       </c>
       <c r="BH47" s="31" t="str">
         <f t="shared" si="28"/>
@@ -10607,10 +10740,10 @@
       </c>
       <c r="BK47" s="48">
         <f t="shared" si="12"/>
-        <v>11.79</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>55</v>
       </c>
@@ -10628,39 +10761,105 @@
         <v>4309.7</v>
       </c>
       <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="27"/>
-      <c r="K48" s="27"/>
-      <c r="L48" s="27"/>
-      <c r="M48" s="27"/>
-      <c r="N48" s="27"/>
-      <c r="O48" s="27"/>
-      <c r="P48" s="27"/>
-      <c r="Q48" s="27"/>
-      <c r="R48" s="27"/>
-      <c r="S48" s="27"/>
-      <c r="T48" s="27"/>
-      <c r="U48" s="27"/>
-      <c r="V48" s="27"/>
-      <c r="W48" s="27"/>
-      <c r="X48" s="27"/>
-      <c r="Y48" s="27"/>
-      <c r="Z48" s="27"/>
-      <c r="AA48" s="27"/>
-      <c r="AB48" s="2"/>
-      <c r="AC48" s="1"/>
-      <c r="AD48" s="27"/>
-      <c r="AE48" s="27"/>
-      <c r="AF48" s="27"/>
-      <c r="AG48" s="27"/>
-      <c r="AH48" s="27"/>
-      <c r="AI48" s="27"/>
+      <c r="H48" s="29">
+        <v>3993.915</v>
+      </c>
+      <c r="I48" s="27">
+        <v>20.9</v>
+      </c>
+      <c r="J48" s="27">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K48" s="27">
+        <v>95.4</v>
+      </c>
+      <c r="L48" s="27">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="M48" s="27">
+        <v>376</v>
+      </c>
+      <c r="N48" s="27">
+        <v>2.15</v>
+      </c>
+      <c r="O48" s="27">
+        <v>0.23</v>
+      </c>
+      <c r="P48" s="27">
+        <v>0.97</v>
+      </c>
+      <c r="Q48" s="27">
+        <v>0.42</v>
+      </c>
+      <c r="R48" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="S48" s="27">
+        <v>1.05</v>
+      </c>
+      <c r="T48" s="27">
+        <v>7.2809999999999997</v>
+      </c>
+      <c r="U48" s="27">
+        <v>133.19999999999999</v>
+      </c>
+      <c r="V48" s="27">
+        <v>13</v>
+      </c>
+      <c r="W48" s="27">
+        <v>1.62</v>
+      </c>
+      <c r="X48" s="27">
+        <v>159.80000000000001</v>
+      </c>
+      <c r="Y48" s="27">
+        <v>61.2</v>
+      </c>
+      <c r="Z48" s="27">
+        <v>116.8</v>
+      </c>
+      <c r="AA48" s="27">
+        <v>10.5</v>
+      </c>
+      <c r="AB48" s="2">
+        <v>7.3230000000000004</v>
+      </c>
+      <c r="AC48" s="1">
+        <v>302</v>
+      </c>
+      <c r="AD48" s="27">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="AE48" s="27">
+        <v>7.3</v>
+      </c>
+      <c r="AF48" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG48" s="27">
+        <v>27.27</v>
+      </c>
+      <c r="AH48" s="27">
+        <v>10.57</v>
+      </c>
+      <c r="AI48" s="27">
+        <v>7</v>
+      </c>
       <c r="AJ48" s="27"/>
-      <c r="AK48" s="27"/>
-      <c r="AL48" s="27"/>
-      <c r="AM48" s="27"/>
-      <c r="AN48" s="27"/>
+      <c r="AK48" s="89">
+        <v>210</v>
+      </c>
+      <c r="AL48" s="89">
+        <v>47</v>
+      </c>
+      <c r="AM48" s="30">
+        <f t="shared" si="34"/>
+        <v>27</v>
+      </c>
+      <c r="AN48" s="30">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
       <c r="AO48" s="43">
         <v>15</v>
       </c>
@@ -10684,7 +10883,7 @@
       <c r="AW48" s="40"/>
       <c r="AX48" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.4915766400000001E-2</v>
       </c>
       <c r="AY48" s="30">
         <f t="shared" si="21"/>
@@ -10692,15 +10891,15 @@
       </c>
       <c r="AZ48" s="30">
         <f t="shared" si="33"/>
-        <v>1572</v>
-      </c>
-      <c r="BA48" s="31" t="e">
+        <v>1873.8400000000001</v>
+      </c>
+      <c r="BA48" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.11206933356102974</v>
       </c>
       <c r="BB48" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.12352941176470589</v>
       </c>
       <c r="BC48" s="31">
         <f t="shared" si="26"/>
@@ -10715,12 +10914,12 @@
         <v/>
       </c>
       <c r="BF48" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG48" s="31">
         <f t="shared" si="24"/>
-        <v>11.79</v>
+        <v>9.5097380000000022</v>
       </c>
       <c r="BH48" s="31" t="str">
         <f t="shared" si="28"/>
@@ -10736,10 +10935,10 @@
       </c>
       <c r="BK48" s="48">
         <f t="shared" si="12"/>
-        <v>11.79</v>
+        <v>9.5097380000000022</v>
       </c>
     </row>
-    <row r="49" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -10757,39 +10956,105 @@
         <v>4309.7</v>
       </c>
       <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
-      <c r="W49" s="27"/>
-      <c r="X49" s="27"/>
-      <c r="Y49" s="27"/>
-      <c r="Z49" s="27"/>
-      <c r="AA49" s="27"/>
-      <c r="AB49" s="2"/>
-      <c r="AC49" s="1"/>
-      <c r="AD49" s="27"/>
-      <c r="AE49" s="27"/>
-      <c r="AF49" s="27"/>
-      <c r="AG49" s="27"/>
-      <c r="AH49" s="27"/>
-      <c r="AI49" s="27"/>
+      <c r="H49" s="29">
+        <v>4201.8450000000003</v>
+      </c>
+      <c r="I49" s="27">
+        <v>21.1</v>
+      </c>
+      <c r="J49" s="27">
+        <v>20.3</v>
+      </c>
+      <c r="K49" s="27">
+        <v>96.3</v>
+      </c>
+      <c r="L49" s="27">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="M49" s="27">
+        <v>0</v>
+      </c>
+      <c r="N49" s="27">
+        <v>1.8</v>
+      </c>
+      <c r="O49" s="27">
+        <v>0.22</v>
+      </c>
+      <c r="P49" s="27">
+        <v>0.62</v>
+      </c>
+      <c r="Q49" s="27">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="R49" s="27">
+        <v>0.03</v>
+      </c>
+      <c r="S49" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="T49" s="27">
+        <v>7.258</v>
+      </c>
+      <c r="U49" s="27">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="V49" s="27">
+        <v>2.7</v>
+      </c>
+      <c r="W49" s="27">
+        <v>1.63</v>
+      </c>
+      <c r="X49" s="27">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="Y49" s="27">
+        <v>56.4</v>
+      </c>
+      <c r="Z49" s="27">
+        <v>113.8</v>
+      </c>
+      <c r="AA49" s="27">
+        <v>2.1</v>
+      </c>
+      <c r="AB49" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="AC49" s="1">
+        <v>298</v>
+      </c>
+      <c r="AD49" s="27">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="AE49" s="27">
+        <v>7.3</v>
+      </c>
+      <c r="AF49" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG49" s="27">
+        <v>24.77</v>
+      </c>
+      <c r="AH49" s="27">
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="AI49" s="27">
+        <v>12</v>
+      </c>
       <c r="AJ49" s="27"/>
-      <c r="AK49" s="27"/>
-      <c r="AL49" s="27"/>
-      <c r="AM49" s="27"/>
-      <c r="AN49" s="27"/>
+      <c r="AK49" s="89">
+        <v>198</v>
+      </c>
+      <c r="AL49" s="89">
+        <v>50</v>
+      </c>
+      <c r="AM49" s="30">
+        <f t="shared" si="34"/>
+        <v>28</v>
+      </c>
+      <c r="AN49" s="30">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
       <c r="AO49" s="43">
         <v>15</v>
       </c>
@@ -10813,7 +11078,7 @@
       <c r="AW49" s="40"/>
       <c r="AX49" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.51530568E-2</v>
       </c>
       <c r="AY49" s="30">
         <f t="shared" si="21"/>
@@ -10821,15 +11086,15 @@
       </c>
       <c r="AZ49" s="30">
         <f t="shared" si="33"/>
-        <v>1572</v>
-      </c>
-      <c r="BA49" s="31" t="e">
+        <v>1866.1399999999999</v>
+      </c>
+      <c r="BA49" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.10610136431350274</v>
       </c>
       <c r="BB49" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.11647058823529412</v>
       </c>
       <c r="BC49" s="31">
         <f t="shared" si="26"/>
@@ -10844,7 +11109,7 @@
         <v>0</v>
       </c>
       <c r="BF49" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG49" s="31" t="str">
@@ -10868,7 +11133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>58</v>
       </c>
@@ -10886,39 +11151,105 @@
         <v>4309.7</v>
       </c>
       <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="27"/>
-      <c r="J50" s="27"/>
-      <c r="K50" s="27"/>
-      <c r="L50" s="27"/>
-      <c r="M50" s="27"/>
-      <c r="N50" s="27"/>
-      <c r="O50" s="27"/>
-      <c r="P50" s="27"/>
-      <c r="Q50" s="27"/>
-      <c r="R50" s="27"/>
-      <c r="S50" s="27"/>
-      <c r="T50" s="27"/>
-      <c r="U50" s="27"/>
-      <c r="V50" s="27"/>
-      <c r="W50" s="27"/>
-      <c r="X50" s="27"/>
-      <c r="Y50" s="27"/>
-      <c r="Z50" s="27"/>
-      <c r="AA50" s="27"/>
-      <c r="AB50" s="2"/>
-      <c r="AC50" s="6"/>
-      <c r="AD50" s="7"/>
-      <c r="AE50" s="7"/>
-      <c r="AF50" s="7"/>
-      <c r="AG50" s="7"/>
-      <c r="AH50" s="7"/>
-      <c r="AI50" s="7"/>
+      <c r="H50" s="29">
+        <v>4781.4750000000004</v>
+      </c>
+      <c r="I50" s="27">
+        <v>23.4</v>
+      </c>
+      <c r="J50" s="27">
+        <v>22.5</v>
+      </c>
+      <c r="K50" s="27">
+        <v>96.1</v>
+      </c>
+      <c r="L50" s="27">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M50" s="27">
+        <v>336</v>
+      </c>
+      <c r="N50" s="27">
+        <v>2.65</v>
+      </c>
+      <c r="O50" s="27">
+        <v>0.22</v>
+      </c>
+      <c r="P50" s="27">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="Q50" s="27">
+        <v>0.37</v>
+      </c>
+      <c r="R50" s="27">
+        <v>0.04</v>
+      </c>
+      <c r="S50" s="27">
+        <v>0.16</v>
+      </c>
+      <c r="T50" s="27">
+        <v>7.2610000000000001</v>
+      </c>
+      <c r="U50" s="27">
+        <v>133.30000000000001</v>
+      </c>
+      <c r="V50" s="27">
+        <v>25.2</v>
+      </c>
+      <c r="W50" s="27">
+        <v>1.77</v>
+      </c>
+      <c r="X50" s="27">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="Y50" s="27">
+        <v>58.3</v>
+      </c>
+      <c r="Z50" s="27">
+        <v>116.9</v>
+      </c>
+      <c r="AA50" s="27">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="AB50" s="2">
+        <v>7.3019999999999996</v>
+      </c>
+      <c r="AC50" s="6">
+        <v>299</v>
+      </c>
+      <c r="AD50" s="7">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="AE50" s="7">
+        <v>7.3</v>
+      </c>
+      <c r="AF50" s="7">
+        <v>34</v>
+      </c>
+      <c r="AG50" s="7">
+        <v>21.77</v>
+      </c>
+      <c r="AH50" s="7">
+        <v>41.39</v>
+      </c>
+      <c r="AI50" s="7">
+        <v>12</v>
+      </c>
       <c r="AJ50" s="7"/>
-      <c r="AK50" s="7"/>
-      <c r="AL50" s="7"/>
-      <c r="AM50" s="7"/>
-      <c r="AN50" s="7"/>
+      <c r="AK50" s="17">
+        <v>208</v>
+      </c>
+      <c r="AL50" s="17">
+        <v>60</v>
+      </c>
+      <c r="AM50" s="17">
+        <f t="shared" si="34"/>
+        <v>30</v>
+      </c>
+      <c r="AN50" s="17">
+        <f t="shared" si="35"/>
+        <v>3</v>
+      </c>
       <c r="AO50" s="44">
         <v>15</v>
       </c>
@@ -10942,7 +11273,7 @@
       <c r="AW50" s="41"/>
       <c r="AX50" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.7236440000000002E-2</v>
       </c>
       <c r="AY50" s="17">
         <f t="shared" si="21"/>
@@ -10950,15 +11281,15 @@
       </c>
       <c r="AZ50" s="17">
         <f t="shared" si="33"/>
-        <v>1572</v>
-      </c>
-      <c r="BA50" s="18" t="e">
+        <v>1915.1599999999999</v>
+      </c>
+      <c r="BA50" s="18">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.10860711376595168</v>
       </c>
       <c r="BB50" s="18">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.12235294117647059</v>
       </c>
       <c r="BC50" s="18">
         <f t="shared" si="26"/>
@@ -10973,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="BF50" s="59" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG50" s="18" t="str">
@@ -10997,7 +11328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
@@ -11075,7 +11406,7 @@
       </c>
       <c r="AY51" s="13">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.37757184000000005</v>
       </c>
       <c r="AZ51" s="13">
         <f t="shared" si="33"/>
@@ -11102,7 +11433,7 @@
         <v/>
       </c>
       <c r="BF51" s="57">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BG51" s="14">
@@ -11126,7 +11457,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="52" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>54</v>
       </c>
@@ -11204,7 +11535,7 @@
       </c>
       <c r="AY52" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.35281943999999998</v>
       </c>
       <c r="AZ52" s="30">
         <f t="shared" si="33"/>
@@ -11231,7 +11562,7 @@
         <v/>
       </c>
       <c r="BF52" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG52" s="31">
@@ -11255,7 +11586,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="53" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>55</v>
       </c>
@@ -11333,7 +11664,7 @@
       </c>
       <c r="AY53" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.3579783936</v>
       </c>
       <c r="AZ53" s="30">
         <f t="shared" si="33"/>
@@ -11360,7 +11691,7 @@
         <v/>
       </c>
       <c r="BF53" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG53" s="31">
@@ -11384,7 +11715,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="54" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -11462,7 +11793,7 @@
       </c>
       <c r="AY54" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.36367336319999999</v>
       </c>
       <c r="AZ54" s="30">
         <f t="shared" si="33"/>
@@ -11489,7 +11820,7 @@
         <v>0</v>
       </c>
       <c r="BF54" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG54" s="31" t="str">
@@ -11513,7 +11844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -11591,7 +11922,7 @@
       </c>
       <c r="AY55" s="17">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.41367456000000002</v>
       </c>
       <c r="AZ55" s="17">
         <f t="shared" si="33"/>
@@ -11618,7 +11949,7 @@
         <v>0</v>
       </c>
       <c r="BF55" s="59" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG55" s="18" t="str">
@@ -11642,7 +11973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>53</v>
       </c>
@@ -11747,7 +12078,7 @@
         <v/>
       </c>
       <c r="BF56" s="57">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BG56" s="14">
@@ -11771,7 +12102,7 @@
         <v>11.55</v>
       </c>
     </row>
-    <row r="57" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>54</v>
       </c>
@@ -11876,7 +12207,7 @@
         <v/>
       </c>
       <c r="BF57" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG57" s="31">
@@ -11900,7 +12231,7 @@
         <v>11.55</v>
       </c>
     </row>
-    <row r="58" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>55</v>
       </c>
@@ -12005,7 +12336,7 @@
         <v/>
       </c>
       <c r="BF58" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG58" s="31">
@@ -12029,7 +12360,7 @@
         <v>11.55</v>
       </c>
     </row>
-    <row r="59" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
@@ -12118,11 +12449,11 @@
         <v>#N/A</v>
       </c>
       <c r="BB59" s="31">
-        <f t="shared" ref="BB59:BB70" si="35">AK59/AP59</f>
+        <f t="shared" ref="BB59:BB70" si="37">AK59/AP59</f>
         <v>0</v>
       </c>
       <c r="BC59" s="31">
-        <f t="shared" ref="BC59:BC70" si="36">AJ59*24</f>
+        <f t="shared" ref="BC59:BC70" si="38">AJ59*24</f>
         <v>0</v>
       </c>
       <c r="BD59" s="31" t="str">
@@ -12134,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="BF59" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG59" s="31" t="str">
@@ -12158,7 +12489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
@@ -12231,7 +12562,7 @@
       <c r="AV60" s="17"/>
       <c r="AW60" s="41"/>
       <c r="AX60" s="16">
-        <f t="shared" ref="AX60:AX70" si="37">AT60*J60*AZ60/1000</f>
+        <f t="shared" ref="AX60:AX70" si="39">AT60*J60*AZ60/1000</f>
         <v>0</v>
       </c>
       <c r="AY60" s="17">
@@ -12243,15 +12574,15 @@
         <v>1540</v>
       </c>
       <c r="BA60" s="18" t="e">
-        <f t="shared" ref="BA60:BA70" si="38">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
+        <f t="shared" ref="BA60:BA70" si="40">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
         <v>#N/A</v>
       </c>
       <c r="BB60" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BC60" s="18">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BD60" s="18" t="str">
@@ -12263,7 +12594,7 @@
         <v>0</v>
       </c>
       <c r="BF60" s="59" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG60" s="18" t="str">
@@ -12275,19 +12606,19 @@
         <v>0</v>
       </c>
       <c r="BI60" s="47">
-        <f t="shared" ref="BI60:BI70" si="39">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
+        <f t="shared" ref="BI60:BI70" si="41">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BJ60" s="67">
-        <f t="shared" ref="BJ60:BJ65" si="40">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
+        <f t="shared" ref="BJ60:BJ65" si="42">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
         <v>0</v>
       </c>
       <c r="BK60" s="49">
-        <f t="shared" ref="BK60:BK70" si="41">IF(BG60&lt;&gt;"",BG60,BH60)</f>
+        <f t="shared" ref="BK60:BK70" si="43">IF(BG60&lt;&gt;"",BG60,BH60)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>53</v>
       </c>
@@ -12360,7 +12691,7 @@
       <c r="AV61" s="13"/>
       <c r="AW61" s="39"/>
       <c r="AX61" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY61" s="13">
@@ -12372,15 +12703,15 @@
         <v>1524</v>
       </c>
       <c r="BA61" s="14" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB61" s="14">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC61" s="14">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB61" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC61" s="14">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD61" s="14" t="str">
@@ -12392,7 +12723,7 @@
         <v/>
       </c>
       <c r="BF61" s="57">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BG61" s="14">
@@ -12404,19 +12735,19 @@
         <v/>
       </c>
       <c r="BI61" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ61" s="66">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BK61" s="48">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.43</v>
       </c>
     </row>
-    <row r="62" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>54</v>
       </c>
@@ -12489,7 +12820,7 @@
       <c r="AV62" s="30"/>
       <c r="AW62" s="40"/>
       <c r="AX62" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY62" s="30">
@@ -12501,15 +12832,15 @@
         <v>1524</v>
       </c>
       <c r="BA62" s="31" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB62" s="31">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC62" s="31">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB62" s="31">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC62" s="31">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD62" s="31">
@@ -12521,7 +12852,7 @@
         <v/>
       </c>
       <c r="BF62" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG62" s="31">
@@ -12533,19 +12864,19 @@
         <v/>
       </c>
       <c r="BI62" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ62" s="66">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BK62" s="48">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.43</v>
       </c>
     </row>
-    <row r="63" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>55</v>
       </c>
@@ -12618,7 +12949,7 @@
       <c r="AV63" s="30"/>
       <c r="AW63" s="40"/>
       <c r="AX63" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY63" s="30">
@@ -12630,15 +12961,15 @@
         <v>1524</v>
       </c>
       <c r="BA63" s="31" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB63" s="31">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC63" s="31">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB63" s="31">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC63" s="31">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD63" s="31">
@@ -12650,7 +12981,7 @@
         <v/>
       </c>
       <c r="BF63" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG63" s="31">
@@ -12662,19 +12993,19 @@
         <v/>
       </c>
       <c r="BI63" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ63" s="66">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BK63" s="48">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.43</v>
       </c>
     </row>
-    <row r="64" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>57</v>
       </c>
@@ -12747,7 +13078,7 @@
       <c r="AV64" s="30"/>
       <c r="AW64" s="40"/>
       <c r="AX64" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY64" s="30">
@@ -12759,15 +13090,15 @@
         <v>1524</v>
       </c>
       <c r="BA64" s="31" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB64" s="31">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC64" s="31">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB64" s="31">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC64" s="31">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD64" s="31" t="str">
@@ -12779,7 +13110,7 @@
         <v>0</v>
       </c>
       <c r="BF64" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG64" s="31" t="str">
@@ -12791,19 +13122,19 @@
         <v>0</v>
       </c>
       <c r="BI64" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ64" s="66">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BK64" s="48">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>58</v>
       </c>
@@ -12876,7 +13207,7 @@
       <c r="AV65" s="17"/>
       <c r="AW65" s="41"/>
       <c r="AX65" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY65" s="17">
@@ -12888,15 +13219,15 @@
         <v>1524</v>
       </c>
       <c r="BA65" s="18" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB65" s="18">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC65" s="18">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB65" s="18">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC65" s="18">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD65" s="18" t="str">
@@ -12908,7 +13239,7 @@
         <v>0</v>
       </c>
       <c r="BF65" s="59" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG65" s="18" t="str">
@@ -12920,19 +13251,19 @@
         <v>0</v>
       </c>
       <c r="BI65" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ65" s="66">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BK65" s="48">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>53</v>
       </c>
@@ -13005,7 +13336,7 @@
       <c r="AV66" s="4"/>
       <c r="AW66" s="22"/>
       <c r="AX66" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY66" s="13">
@@ -13017,15 +13348,15 @@
         <v>1508</v>
       </c>
       <c r="BA66" s="14" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB66" s="14">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC66" s="14">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB66" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC66" s="14">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD66" s="14" t="str">
@@ -13037,7 +13368,7 @@
         <v/>
       </c>
       <c r="BF66" s="57">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BG66" s="14">
@@ -13049,16 +13380,16 @@
         <v/>
       </c>
       <c r="BI66" s="45">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ66" s="62"/>
       <c r="BK66" s="50">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.31</v>
       </c>
     </row>
-    <row r="67" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>54</v>
       </c>
@@ -13131,7 +13462,7 @@
       <c r="AV67" s="27"/>
       <c r="AW67" s="2"/>
       <c r="AX67" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY67" s="30">
@@ -13143,15 +13474,15 @@
         <v>1508</v>
       </c>
       <c r="BA67" s="31" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB67" s="31">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC67" s="31">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB67" s="31">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC67" s="31">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD67" s="31">
@@ -13163,7 +13494,7 @@
         <v/>
       </c>
       <c r="BF67" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG67" s="31">
@@ -13175,16 +13506,16 @@
         <v/>
       </c>
       <c r="BI67" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ67" s="63"/>
       <c r="BK67" s="48">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.31</v>
       </c>
     </row>
-    <row r="68" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>55</v>
       </c>
@@ -13257,7 +13588,7 @@
       <c r="AV68" s="30"/>
       <c r="AW68" s="40"/>
       <c r="AX68" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY68" s="30">
@@ -13269,15 +13600,15 @@
         <v>1508</v>
       </c>
       <c r="BA68" s="31" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB68" s="31">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC68" s="31">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB68" s="31">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC68" s="31">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD68" s="31">
@@ -13289,7 +13620,7 @@
         <v/>
       </c>
       <c r="BF68" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG68" s="31">
@@ -13301,16 +13632,16 @@
         <v/>
       </c>
       <c r="BI68" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ68" s="63"/>
       <c r="BK68" s="48">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.31</v>
       </c>
     </row>
-    <row r="69" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>57</v>
       </c>
@@ -13383,7 +13714,7 @@
       <c r="AV69" s="30"/>
       <c r="AW69" s="40"/>
       <c r="AX69" s="15">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY69" s="30">
@@ -13395,15 +13726,15 @@
         <v>1508</v>
       </c>
       <c r="BA69" s="31" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB69" s="31">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC69" s="31">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB69" s="31">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC69" s="31">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD69" s="31" t="str">
@@ -13415,7 +13746,7 @@
         <v>0</v>
       </c>
       <c r="BF69" s="58" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG69" s="31" t="str">
@@ -13427,16 +13758,16 @@
         <v>0</v>
       </c>
       <c r="BI69" s="46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ69" s="63"/>
       <c r="BK69" s="48">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>58</v>
       </c>
@@ -13509,7 +13840,7 @@
       <c r="AV70" s="17"/>
       <c r="AW70" s="41"/>
       <c r="AX70" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AY70" s="17">
@@ -13521,15 +13852,15 @@
         <v>1508</v>
       </c>
       <c r="BA70" s="18" t="e">
+        <f t="shared" si="40"/>
+        <v>#N/A</v>
+      </c>
+      <c r="BB70" s="18">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BC70" s="18">
         <f t="shared" si="38"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BB70" s="18">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="BC70" s="18">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="BD70" s="18" t="str">
@@ -13541,7 +13872,7 @@
         <v>0</v>
       </c>
       <c r="BF70" s="59" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BG70" s="18" t="str">
@@ -13553,12 +13884,12 @@
         <v>0</v>
       </c>
       <c r="BI70" s="47">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BJ70" s="64"/>
       <c r="BK70" s="49">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
     </row>
@@ -13597,40 +13928,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A841E7D6-1405-4AC8-A599-0CE4601ECD66}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -13853,32 +14157,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13895,4 +14201,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1871" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85D6E467-87DE-440E-A6D3-135711F6C709}"/>
+  <xr:revisionPtr revIDLastSave="1995" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19C793F4-5BB4-4EE9-BAF9-7EC1C510882B}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -1041,6 +1041,7 @@
     <xf numFmtId="164" fontId="14" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="39" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1092,7 +1093,6 @@
     <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1177,6 +1177,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1479,91 +1483,92 @@
   <dimension ref="A1:BK70"/>
   <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="4" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" hidden="1" customWidth="1"/>
     <col min="6" max="60" width="12.6640625" customWidth="1"/>
     <col min="61" max="61" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="62" max="63" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="73" t="s">
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="75"/>
-      <c r="AC1" s="86" t="s">
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="75"/>
+      <c r="Y1" s="75"/>
+      <c r="Z1" s="75"/>
+      <c r="AA1" s="75"/>
+      <c r="AB1" s="76"/>
+      <c r="AC1" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="AD1" s="87"/>
-      <c r="AE1" s="87"/>
-      <c r="AF1" s="87"/>
-      <c r="AG1" s="87"/>
-      <c r="AH1" s="87"/>
-      <c r="AI1" s="87"/>
-      <c r="AJ1" s="87"/>
-      <c r="AK1" s="87"/>
-      <c r="AL1" s="87"/>
-      <c r="AM1" s="87"/>
-      <c r="AN1" s="87"/>
-      <c r="AO1" s="88"/>
-      <c r="AP1" s="81" t="s">
+      <c r="AD1" s="88"/>
+      <c r="AE1" s="88"/>
+      <c r="AF1" s="88"/>
+      <c r="AG1" s="88"/>
+      <c r="AH1" s="88"/>
+      <c r="AI1" s="88"/>
+      <c r="AJ1" s="88"/>
+      <c r="AK1" s="88"/>
+      <c r="AL1" s="88"/>
+      <c r="AM1" s="88"/>
+      <c r="AN1" s="88"/>
+      <c r="AO1" s="89"/>
+      <c r="AP1" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="82"/>
-      <c r="AU1" s="83" t="s">
+      <c r="AQ1" s="82"/>
+      <c r="AR1" s="82"/>
+      <c r="AS1" s="82"/>
+      <c r="AT1" s="83"/>
+      <c r="AU1" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="AV1" s="84"/>
-      <c r="AW1" s="85"/>
-      <c r="AX1" s="79" t="s">
+      <c r="AV1" s="85"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="AY1" s="80"/>
-      <c r="AZ1" s="80"/>
-      <c r="BA1" s="80"/>
-      <c r="BB1" s="80"/>
-      <c r="BC1" s="80"/>
-      <c r="BD1" s="80"/>
-      <c r="BE1" s="80"/>
-      <c r="BF1" s="80"/>
-      <c r="BG1" s="80"/>
-      <c r="BH1" s="80"/>
-      <c r="BI1" s="76" t="s">
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="81"/>
+      <c r="BA1" s="81"/>
+      <c r="BB1" s="81"/>
+      <c r="BC1" s="81"/>
+      <c r="BD1" s="81"/>
+      <c r="BE1" s="81"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="81"/>
+      <c r="BH1" s="81"/>
+      <c r="BI1" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="BJ1" s="77"/>
-      <c r="BK1" s="78"/>
+      <c r="BJ1" s="78"/>
+      <c r="BK1" s="79"/>
     </row>
     <row r="2" spans="1:63" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="33" t="s">
@@ -10463,11 +10468,11 @@
         <v>46</v>
       </c>
       <c r="AM46" s="13">
-        <f t="shared" ref="AM46:AM50" si="34">AK46-AK41</f>
+        <f t="shared" ref="AM46:AN50" si="34">AK46-AK41</f>
         <v>24</v>
       </c>
       <c r="AN46" s="13">
-        <f t="shared" ref="AN46:AN50" si="35">AL46-AL41</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AO46" s="42">
@@ -10651,10 +10656,10 @@
         <v>5</v>
       </c>
       <c r="AJ47" s="27"/>
-      <c r="AK47" s="89">
+      <c r="AK47" s="30">
         <v>232</v>
       </c>
-      <c r="AL47" s="89">
+      <c r="AL47" s="30">
         <v>55</v>
       </c>
       <c r="AM47" s="30">
@@ -10662,7 +10667,7 @@
         <v>45</v>
       </c>
       <c r="AN47" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AO47" s="43">
@@ -10683,7 +10688,9 @@
       <c r="AT47" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU47" s="15"/>
+      <c r="AU47" s="15">
+        <v>6.41371916769767E-3</v>
+      </c>
       <c r="AV47" s="30"/>
       <c r="AW47" s="40"/>
       <c r="AX47" s="15">
@@ -10712,14 +10719,14 @@
       </c>
       <c r="BD47" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>8.4814755035335331E-3</v>
       </c>
       <c r="BE47" s="61" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF47" s="58" t="str">
-        <f t="shared" ref="BF47:BF70" si="36">IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
+        <f t="shared" ref="BF47:BF70" si="35">IF(B47="No MPC", AT47*J47*AZ47/1000,"")</f>
         <v/>
       </c>
       <c r="BG47" s="31">
@@ -10732,11 +10739,11 @@
       </c>
       <c r="BI47" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>22.029806502684501</v>
       </c>
       <c r="BJ47" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8.4814755035335331E-3</v>
       </c>
       <c r="BK47" s="48">
         <f t="shared" si="12"/>
@@ -10846,10 +10853,10 @@
         <v>7</v>
       </c>
       <c r="AJ48" s="27"/>
-      <c r="AK48" s="89">
+      <c r="AK48" s="72">
         <v>210</v>
       </c>
-      <c r="AL48" s="89">
+      <c r="AL48" s="72">
         <v>47</v>
       </c>
       <c r="AM48" s="30">
@@ -10857,7 +10864,7 @@
         <v>27</v>
       </c>
       <c r="AN48" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AO48" s="43">
@@ -10878,7 +10885,9 @@
       <c r="AT48" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU48" s="15"/>
+      <c r="AU48" s="15">
+        <v>1.6156627905643501E-2</v>
+      </c>
       <c r="AV48" s="30"/>
       <c r="AW48" s="40"/>
       <c r="AX48" s="15">
@@ -10907,14 +10916,14 @@
       </c>
       <c r="BD48" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.1024260857438207E-2</v>
       </c>
       <c r="BE48" s="61" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF48" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG48" s="31">
@@ -10927,11 +10936,11 @@
       </c>
       <c r="BI48" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>54.608469759579762</v>
       </c>
       <c r="BJ48" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.1024260857438207E-2</v>
       </c>
       <c r="BK48" s="48">
         <f t="shared" si="12"/>
@@ -11041,10 +11050,10 @@
         <v>12</v>
       </c>
       <c r="AJ49" s="27"/>
-      <c r="AK49" s="89">
+      <c r="AK49" s="72">
         <v>198</v>
       </c>
-      <c r="AL49" s="89">
+      <c r="AL49" s="72">
         <v>50</v>
       </c>
       <c r="AM49" s="30">
@@ -11052,7 +11061,7 @@
         <v>28</v>
       </c>
       <c r="AN49" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AO49" s="43">
@@ -11074,8 +11083,12 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU49" s="15"/>
-      <c r="AV49" s="30"/>
-      <c r="AW49" s="40"/>
+      <c r="AV49" s="30">
+        <v>1.7874907459397099E-2</v>
+      </c>
+      <c r="AW49" s="30">
+        <v>3.5727604149081598E-3</v>
+      </c>
       <c r="AX49" s="15">
         <f t="shared" si="4"/>
         <v>1.51530568E-2</v>
@@ -11106,10 +11119,10 @@
       </c>
       <c r="BE49" s="61">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2.3164638754360627E-2</v>
       </c>
       <c r="BF49" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG49" s="31" t="str">
@@ -11118,19 +11131,19 @@
       </c>
       <c r="BH49" s="31">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6.6672711206767126</v>
       </c>
       <c r="BI49" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>60.167892868469167</v>
       </c>
       <c r="BJ49" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.3164638754360627E-2</v>
       </c>
       <c r="BK49" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6.6672711206767126</v>
       </c>
     </row>
     <row r="50" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -11247,7 +11260,7 @@
         <v>30</v>
       </c>
       <c r="AN50" s="17">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>3</v>
       </c>
       <c r="AO50" s="44">
@@ -11269,8 +11282,12 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU50" s="16"/>
-      <c r="AV50" s="17"/>
-      <c r="AW50" s="41"/>
+      <c r="AV50" s="17">
+        <v>1.28541289800434E-2</v>
+      </c>
+      <c r="AW50" s="17">
+        <v>3.56209777936082E-3</v>
+      </c>
       <c r="AX50" s="16">
         <f t="shared" si="4"/>
         <v>1.7236440000000002E-2</v>
@@ -11301,10 +11318,10 @@
       </c>
       <c r="BE50" s="18">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1.7095634484319385E-2</v>
       </c>
       <c r="BF50" s="59" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG50" s="18" t="str">
@@ -11313,19 +11330,19 @@
       </c>
       <c r="BH50" s="18">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6.8219871831206671</v>
       </c>
       <c r="BI50" s="47">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>44.404245413816589</v>
       </c>
       <c r="BJ50" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.7095634484319385E-2</v>
       </c>
       <c r="BK50" s="49">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6.8219871831206671</v>
       </c>
     </row>
     <row r="51" spans="1:63" x14ac:dyDescent="0.3">
@@ -11346,39 +11363,99 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
+      <c r="H51" s="9">
+        <v>4357.8</v>
+      </c>
+      <c r="I51" s="4">
+        <v>21.4</v>
+      </c>
+      <c r="J51" s="4">
+        <v>20.2</v>
+      </c>
+      <c r="K51" s="4">
+        <v>94</v>
+      </c>
+      <c r="L51" s="4">
+        <v>17.3</v>
+      </c>
+      <c r="M51" s="4">
+        <v>371</v>
+      </c>
+      <c r="N51" s="4">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="O51" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="P51" s="4">
+        <v>2.37</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="R51" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="S51" s="4">
+        <v>1.48</v>
+      </c>
+      <c r="T51" s="4">
+        <v>7.2679999999999998</v>
+      </c>
+      <c r="U51" s="4">
+        <v>118</v>
+      </c>
+      <c r="V51" s="4">
+        <v>33.9</v>
+      </c>
+      <c r="W51" s="4">
+        <v>2.06</v>
+      </c>
+      <c r="X51" s="4">
+        <v>154.6</v>
+      </c>
       <c r="Y51" s="4"/>
       <c r="Z51" s="4"/>
       <c r="AA51" s="4"/>
-      <c r="AB51" s="22"/>
-      <c r="AC51" s="3"/>
-      <c r="AD51" s="4"/>
-      <c r="AE51" s="4"/>
-      <c r="AF51" s="4"/>
-      <c r="AG51" s="4"/>
-      <c r="AH51" s="4"/>
-      <c r="AI51" s="4"/>
+      <c r="AB51" s="22">
+        <v>7.26</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD51" s="4">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="AE51" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="AF51" s="4">
+        <v>34</v>
+      </c>
+      <c r="AG51" s="4">
+        <v>31.315000000000001</v>
+      </c>
+      <c r="AH51" s="4">
+        <v>68.802000000000007</v>
+      </c>
+      <c r="AI51" s="4">
+        <v>7</v>
+      </c>
       <c r="AJ51" s="4"/>
-      <c r="AK51" s="4"/>
-      <c r="AL51" s="4"/>
-      <c r="AM51" s="4"/>
-      <c r="AN51" s="4"/>
+      <c r="AK51" s="4">
+        <v>169</v>
+      </c>
+      <c r="AL51" s="4">
+        <v>46</v>
+      </c>
+      <c r="AM51" s="4">
+        <f t="shared" ref="AM51:AM55" si="36">AK51-AK46</f>
+        <v>21</v>
+      </c>
+      <c r="AN51" s="4">
+        <f t="shared" ref="AN51:AN55" si="37">AL51-AL46</f>
+        <v>0</v>
+      </c>
       <c r="AO51" s="42">
         <v>15</v>
       </c>
@@ -11402,7 +11479,7 @@
       <c r="AW51" s="39"/>
       <c r="AX51" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.5175185360000001E-2</v>
       </c>
       <c r="AY51" s="13">
         <f t="shared" si="21"/>
@@ -11410,15 +11487,15 @@
       </c>
       <c r="AZ51" s="13">
         <f t="shared" si="33"/>
-        <v>1556</v>
-      </c>
-      <c r="BA51" s="14" t="e">
+        <v>1878.117</v>
+      </c>
+      <c r="BA51" s="14">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>8.9983744356714732E-2</v>
       </c>
       <c r="BB51" s="14">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>9.9411764705882352E-2</v>
       </c>
       <c r="BC51" s="14">
         <f t="shared" si="26"/>
@@ -11433,12 +11510,12 @@
         <v/>
       </c>
       <c r="BF51" s="57">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="35"/>
+        <v>1.5175185360000001E-2</v>
       </c>
       <c r="BG51" s="14">
         <f t="shared" si="24"/>
-        <v>11.67</v>
+        <v>0</v>
       </c>
       <c r="BH51" s="14" t="str">
         <f t="shared" si="28"/>
@@ -11446,15 +11523,15 @@
       </c>
       <c r="BI51" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>39.416065870129877</v>
       </c>
       <c r="BJ51" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.5175185360000001E-2</v>
       </c>
       <c r="BK51" s="48">
         <f t="shared" si="12"/>
-        <v>11.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:63" x14ac:dyDescent="0.3">
@@ -11475,39 +11552,99 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
-      <c r="X52" s="27"/>
+      <c r="H52" s="29">
+        <v>4487.28</v>
+      </c>
+      <c r="I52" s="35">
+        <v>21.6</v>
+      </c>
+      <c r="J52" s="35">
+        <v>20.5</v>
+      </c>
+      <c r="K52" s="35">
+        <v>94.9</v>
+      </c>
+      <c r="L52" s="35">
+        <v>18.2</v>
+      </c>
+      <c r="M52" s="35">
+        <v>394</v>
+      </c>
+      <c r="N52" s="35">
+        <v>2.91</v>
+      </c>
+      <c r="O52" s="35">
+        <v>0.22</v>
+      </c>
+      <c r="P52" s="35">
+        <v>0.03</v>
+      </c>
+      <c r="Q52" s="35">
+        <v>0.52</v>
+      </c>
+      <c r="R52" s="35">
+        <v>0.36</v>
+      </c>
+      <c r="S52" s="35">
+        <v>0.82</v>
+      </c>
+      <c r="T52" s="35">
+        <v>7.2949999999999999</v>
+      </c>
+      <c r="U52" s="35">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="V52" s="35">
+        <v>41.7</v>
+      </c>
+      <c r="W52" s="35">
+        <v>1.56</v>
+      </c>
+      <c r="X52" s="35">
+        <v>170</v>
+      </c>
       <c r="Y52" s="27"/>
       <c r="Z52" s="27"/>
       <c r="AA52" s="27"/>
-      <c r="AB52" s="2"/>
-      <c r="AC52" s="1"/>
-      <c r="AD52" s="27"/>
-      <c r="AE52" s="27"/>
-      <c r="AF52" s="27"/>
-      <c r="AG52" s="27"/>
-      <c r="AH52" s="27"/>
-      <c r="AI52" s="27"/>
+      <c r="AB52" s="2">
+        <v>7.2859999999999996</v>
+      </c>
+      <c r="AC52" s="1">
+        <v>299</v>
+      </c>
+      <c r="AD52" s="27">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="AE52" s="27">
+        <v>7.3</v>
+      </c>
+      <c r="AF52" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG52" s="27">
+        <v>33.526000000000003</v>
+      </c>
+      <c r="AH52" s="27">
+        <v>11.22</v>
+      </c>
+      <c r="AI52" s="35">
+        <v>5</v>
+      </c>
       <c r="AJ52" s="27"/>
-      <c r="AK52" s="27"/>
-      <c r="AL52" s="27"/>
-      <c r="AM52" s="27"/>
-      <c r="AN52" s="27"/>
+      <c r="AK52" s="72">
+        <v>249</v>
+      </c>
+      <c r="AL52" s="72">
+        <v>55</v>
+      </c>
+      <c r="AM52" s="27">
+        <f t="shared" si="36"/>
+        <v>17</v>
+      </c>
+      <c r="AN52" s="27">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="AO52" s="43">
         <v>15</v>
       </c>
@@ -11526,12 +11663,14 @@
       <c r="AT52" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU52" s="15"/>
+      <c r="AU52" s="15">
+        <v>1.61207945281465E-2</v>
+      </c>
       <c r="AV52" s="30"/>
       <c r="AW52" s="40"/>
       <c r="AX52" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.5659917200000002E-2</v>
       </c>
       <c r="AY52" s="30">
         <f t="shared" si="21"/>
@@ -11539,15 +11678,15 @@
       </c>
       <c r="AZ52" s="30">
         <f t="shared" si="33"/>
-        <v>1556</v>
-      </c>
-      <c r="BA52" s="31" t="e">
+        <v>1909.7460000000001</v>
+      </c>
+      <c r="BA52" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.13038383114822599</v>
       </c>
       <c r="BB52" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.14647058823529413</v>
       </c>
       <c r="BC52" s="31">
         <f t="shared" si="26"/>
@@ -11555,19 +11694,19 @@
       </c>
       <c r="BD52" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.1379599213159493E-2</v>
       </c>
       <c r="BE52" s="61" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF52" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG52" s="31">
         <f t="shared" si="24"/>
-        <v>11.67</v>
+        <v>14.179864050000001</v>
       </c>
       <c r="BH52" s="31" t="str">
         <f t="shared" si="28"/>
@@ -11575,15 +11714,15 @@
       </c>
       <c r="BI52" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>55.531426527686996</v>
       </c>
       <c r="BJ52" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.1379599213159493E-2</v>
       </c>
       <c r="BK52" s="48">
         <f t="shared" si="12"/>
-        <v>11.67</v>
+        <v>14.179864050000001</v>
       </c>
     </row>
     <row r="53" spans="1:63" x14ac:dyDescent="0.3">
@@ -11604,39 +11743,99 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="G53" s="29"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="27"/>
-      <c r="K53" s="27"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="27"/>
-      <c r="N53" s="27"/>
-      <c r="O53" s="27"/>
-      <c r="P53" s="27"/>
-      <c r="Q53" s="27"/>
-      <c r="R53" s="27"/>
-      <c r="S53" s="27"/>
-      <c r="T53" s="27"/>
-      <c r="U53" s="27"/>
-      <c r="V53" s="27"/>
-      <c r="W53" s="27"/>
-      <c r="X53" s="27"/>
+      <c r="H53" s="29">
+        <v>4483.5600000000004</v>
+      </c>
+      <c r="I53" s="35">
+        <v>22</v>
+      </c>
+      <c r="J53" s="35">
+        <v>21</v>
+      </c>
+      <c r="K53" s="35">
+        <v>95.4</v>
+      </c>
+      <c r="L53" s="35">
+        <v>18.3</v>
+      </c>
+      <c r="M53" s="35">
+        <v>376</v>
+      </c>
+      <c r="N53" s="35">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O53" s="35">
+        <v>0.21</v>
+      </c>
+      <c r="P53" s="35">
+        <v>0.92</v>
+      </c>
+      <c r="Q53" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="R53" s="35">
+        <v>0.42</v>
+      </c>
+      <c r="S53" s="35">
+        <v>0.88</v>
+      </c>
+      <c r="T53" s="35">
+        <v>7.274</v>
+      </c>
+      <c r="U53" s="35">
+        <v>128.69999999999999</v>
+      </c>
+      <c r="V53" s="35">
+        <v>29</v>
+      </c>
+      <c r="W53" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="X53" s="35">
+        <v>160</v>
+      </c>
       <c r="Y53" s="27"/>
       <c r="Z53" s="27"/>
       <c r="AA53" s="27"/>
-      <c r="AB53" s="2"/>
-      <c r="AC53" s="1"/>
-      <c r="AD53" s="27"/>
-      <c r="AE53" s="27"/>
-      <c r="AF53" s="27"/>
-      <c r="AG53" s="27"/>
-      <c r="AH53" s="27"/>
-      <c r="AI53" s="27"/>
+      <c r="AB53" s="2">
+        <v>7.266</v>
+      </c>
+      <c r="AC53" s="1">
+        <v>301</v>
+      </c>
+      <c r="AD53" s="27">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="AE53" s="27">
+        <v>7.3</v>
+      </c>
+      <c r="AF53" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG53" s="27">
+        <v>27.274000000000001</v>
+      </c>
+      <c r="AH53" s="27">
+        <v>11.551</v>
+      </c>
+      <c r="AI53" s="35">
+        <v>7</v>
+      </c>
       <c r="AJ53" s="27"/>
-      <c r="AK53" s="27"/>
-      <c r="AL53" s="27"/>
-      <c r="AM53" s="27"/>
-      <c r="AN53" s="27"/>
+      <c r="AK53" s="72">
+        <v>237</v>
+      </c>
+      <c r="AL53" s="72">
+        <v>57</v>
+      </c>
+      <c r="AM53" s="27">
+        <f t="shared" si="36"/>
+        <v>27</v>
+      </c>
+      <c r="AN53" s="27">
+        <f t="shared" si="37"/>
+        <v>10</v>
+      </c>
       <c r="AO53" s="43">
         <v>15</v>
       </c>
@@ -11655,12 +11854,14 @@
       <c r="AT53" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU53" s="15"/>
+      <c r="AU53" s="15">
+        <v>1.6995950307655501E-2</v>
+      </c>
       <c r="AV53" s="30"/>
       <c r="AW53" s="40"/>
       <c r="AX53" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.5924930000000004E-2</v>
       </c>
       <c r="AY53" s="30">
         <f t="shared" si="21"/>
@@ -11668,15 +11869,15 @@
       </c>
       <c r="AZ53" s="30">
         <f t="shared" si="33"/>
-        <v>1556</v>
-      </c>
-      <c r="BA53" s="31" t="e">
+        <v>1895.825</v>
+      </c>
+      <c r="BA53" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.12501153851225719</v>
       </c>
       <c r="BB53" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.13941176470588235</v>
       </c>
       <c r="BC53" s="31">
         <f t="shared" si="26"/>
@@ -11684,19 +11885,19 @@
       </c>
       <c r="BD53" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.2375935758340966E-2</v>
       </c>
       <c r="BE53" s="61" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="BF53" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG53" s="31">
         <f t="shared" si="24"/>
-        <v>11.67</v>
+        <v>9.8582900000000002</v>
       </c>
       <c r="BH53" s="31" t="str">
         <f t="shared" si="28"/>
@@ -11704,15 +11905,15 @@
       </c>
       <c r="BI53" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>58.119313658028489</v>
       </c>
       <c r="BJ53" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.2375935758340966E-2</v>
       </c>
       <c r="BK53" s="48">
         <f t="shared" si="12"/>
-        <v>11.67</v>
+        <v>9.8582900000000002</v>
       </c>
     </row>
     <row r="54" spans="1:63" x14ac:dyDescent="0.3">
@@ -11733,39 +11934,99 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="27"/>
-      <c r="K54" s="27"/>
-      <c r="L54" s="27"/>
-      <c r="M54" s="27"/>
-      <c r="N54" s="27"/>
-      <c r="O54" s="27"/>
-      <c r="P54" s="27"/>
-      <c r="Q54" s="27"/>
-      <c r="R54" s="27"/>
-      <c r="S54" s="27"/>
-      <c r="T54" s="27"/>
-      <c r="U54" s="27"/>
-      <c r="V54" s="27"/>
-      <c r="W54" s="27"/>
-      <c r="X54" s="27"/>
+      <c r="H54" s="29">
+        <v>4788.2550000000001</v>
+      </c>
+      <c r="I54" s="35">
+        <v>22.3</v>
+      </c>
+      <c r="J54" s="35">
+        <v>21.3</v>
+      </c>
+      <c r="K54" s="35">
+        <v>95.7</v>
+      </c>
+      <c r="L54" s="35">
+        <v>17.5</v>
+      </c>
+      <c r="M54" s="35">
+        <v>355</v>
+      </c>
+      <c r="N54" s="35">
+        <v>1.99</v>
+      </c>
+      <c r="O54" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="P54" s="35">
+        <v>0.65</v>
+      </c>
+      <c r="Q54" s="35">
+        <v>0.43</v>
+      </c>
+      <c r="R54" s="35">
+        <v>0.11</v>
+      </c>
+      <c r="S54" s="35">
+        <v>0.66</v>
+      </c>
+      <c r="T54" s="35">
+        <v>7.242</v>
+      </c>
+      <c r="U54" s="35">
+        <v>131</v>
+      </c>
+      <c r="V54" s="35">
+        <v>2</v>
+      </c>
+      <c r="W54" s="35">
+        <v>1.52</v>
+      </c>
+      <c r="X54" s="35">
+        <v>156.4</v>
+      </c>
       <c r="Y54" s="27"/>
       <c r="Z54" s="27"/>
       <c r="AA54" s="27"/>
-      <c r="AB54" s="2"/>
-      <c r="AC54" s="1"/>
-      <c r="AD54" s="27"/>
-      <c r="AE54" s="27"/>
-      <c r="AF54" s="27"/>
-      <c r="AG54" s="27"/>
-      <c r="AH54" s="27"/>
-      <c r="AI54" s="27"/>
+      <c r="AB54" s="2">
+        <v>7.2350000000000003</v>
+      </c>
+      <c r="AC54" s="1">
+        <v>302</v>
+      </c>
+      <c r="AD54" s="27">
+        <v>0.49</v>
+      </c>
+      <c r="AE54" s="27">
+        <v>7.29</v>
+      </c>
+      <c r="AF54" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG54" s="27">
+        <v>24.766999999999999</v>
+      </c>
+      <c r="AH54" s="27">
+        <v>10.186</v>
+      </c>
+      <c r="AI54" s="35">
+        <v>12</v>
+      </c>
       <c r="AJ54" s="27"/>
-      <c r="AK54" s="27"/>
-      <c r="AL54" s="27"/>
-      <c r="AM54" s="27"/>
-      <c r="AN54" s="27"/>
+      <c r="AK54" s="72">
+        <v>228</v>
+      </c>
+      <c r="AL54" s="72">
+        <v>57</v>
+      </c>
+      <c r="AM54" s="27">
+        <f t="shared" si="36"/>
+        <v>30</v>
+      </c>
+      <c r="AN54" s="27">
+        <f t="shared" si="37"/>
+        <v>7</v>
+      </c>
       <c r="AO54" s="43">
         <v>15</v>
       </c>
@@ -11785,11 +12046,15 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU54" s="15"/>
-      <c r="AV54" s="30"/>
-      <c r="AW54" s="40"/>
+      <c r="AV54" s="30">
+        <v>1.5830527057502299E-2</v>
+      </c>
+      <c r="AW54" s="40">
+        <v>6.3842230105098105E-4</v>
+      </c>
       <c r="AX54" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6085359560000005E-2</v>
       </c>
       <c r="AY54" s="30">
         <f t="shared" si="21"/>
@@ -11797,15 +12062,15 @@
       </c>
       <c r="AZ54" s="30">
         <f t="shared" si="33"/>
-        <v>1556</v>
-      </c>
-      <c r="BA54" s="31" t="e">
+        <v>1887.953</v>
+      </c>
+      <c r="BA54" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.12076571821438352</v>
       </c>
       <c r="BB54" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.13411764705882354</v>
       </c>
       <c r="BC54" s="31">
         <f t="shared" si="26"/>
@@ -11817,10 +12082,10 @@
       </c>
       <c r="BE54" s="61">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2.0755063229022663E-2</v>
       </c>
       <c r="BF54" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG54" s="31" t="str">
@@ -11829,19 +12094,19 @@
       </c>
       <c r="BH54" s="31">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.2053112985361027</v>
       </c>
       <c r="BI54" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>53.909255140318606</v>
       </c>
       <c r="BJ54" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.0755063229022663E-2</v>
       </c>
       <c r="BK54" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1.2053112985361027</v>
       </c>
     </row>
     <row r="55" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -11862,39 +12127,99 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="7"/>
-      <c r="T55" s="7"/>
-      <c r="U55" s="7"/>
-      <c r="V55" s="7"/>
-      <c r="W55" s="7"/>
-      <c r="X55" s="7"/>
+      <c r="H55" s="11">
+        <v>5197.7700000000004</v>
+      </c>
+      <c r="I55" s="7">
+        <v>22.8</v>
+      </c>
+      <c r="J55" s="7">
+        <v>21.4</v>
+      </c>
+      <c r="K55" s="7">
+        <v>94.1</v>
+      </c>
+      <c r="L55" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="M55" s="7">
+        <v>339</v>
+      </c>
+      <c r="N55" s="7">
+        <v>3.38</v>
+      </c>
+      <c r="O55" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="P55" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="Q55" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="R55" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="S55" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="T55" s="7">
+        <v>7.258</v>
+      </c>
+      <c r="U55" s="7">
+        <v>133.6</v>
+      </c>
+      <c r="V55" s="7">
+        <v>59.3</v>
+      </c>
+      <c r="W55" s="7">
+        <v>1.79</v>
+      </c>
+      <c r="X55" s="7">
+        <v>153.9</v>
+      </c>
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
       <c r="AA55" s="7"/>
-      <c r="AB55" s="23"/>
-      <c r="AC55" s="6"/>
-      <c r="AD55" s="7"/>
-      <c r="AE55" s="7"/>
-      <c r="AF55" s="7"/>
-      <c r="AG55" s="7"/>
-      <c r="AH55" s="7"/>
-      <c r="AI55" s="7"/>
+      <c r="AB55" s="23">
+        <v>7.25</v>
+      </c>
+      <c r="AC55" s="6">
+        <v>299</v>
+      </c>
+      <c r="AD55" s="7">
+        <v>0.499</v>
+      </c>
+      <c r="AE55" s="7">
+        <v>7.3</v>
+      </c>
+      <c r="AF55" s="7">
+        <v>34</v>
+      </c>
+      <c r="AG55" s="7">
+        <v>21.77</v>
+      </c>
+      <c r="AH55" s="7">
+        <v>49.694000000000003</v>
+      </c>
+      <c r="AI55" s="7">
+        <v>12</v>
+      </c>
       <c r="AJ55" s="7"/>
-      <c r="AK55" s="7"/>
-      <c r="AL55" s="7"/>
-      <c r="AM55" s="7"/>
-      <c r="AN55" s="7"/>
+      <c r="AK55" s="7">
+        <v>232</v>
+      </c>
+      <c r="AL55" s="7">
+        <v>68</v>
+      </c>
+      <c r="AM55" s="7">
+        <f t="shared" si="36"/>
+        <v>24</v>
+      </c>
+      <c r="AN55" s="7">
+        <f t="shared" si="37"/>
+        <v>8</v>
+      </c>
       <c r="AO55" s="44">
         <v>15</v>
       </c>
@@ -11914,11 +12239,15 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU55" s="16"/>
-      <c r="AV55" s="17"/>
-      <c r="AW55" s="41"/>
+      <c r="AV55" s="17">
+        <v>1.4162921683942099E-2</v>
+      </c>
+      <c r="AW55" s="41">
+        <v>2.9900690641954698E-3</v>
+      </c>
       <c r="AX55" s="16">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6601811840000001E-2</v>
       </c>
       <c r="AY55" s="17">
         <f t="shared" si="21"/>
@@ -11926,15 +12255,15 @@
       </c>
       <c r="AZ55" s="17">
         <f t="shared" si="33"/>
-        <v>1556</v>
-      </c>
-      <c r="BA55" s="18" t="e">
+        <v>1939.4639999999999</v>
+      </c>
+      <c r="BA55" s="18">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.11962067870298186</v>
       </c>
       <c r="BB55" s="18">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.13647058823529412</v>
       </c>
       <c r="BC55" s="18">
         <f t="shared" si="26"/>
@@ -11946,10 +12275,10 @@
       </c>
       <c r="BE55" s="18">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1.9075331070017416E-2</v>
       </c>
       <c r="BF55" s="59" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG55" s="18" t="str">
@@ -11958,19 +12287,19 @@
       </c>
       <c r="BH55" s="18">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>5.7991313075208026</v>
       </c>
       <c r="BI55" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>49.546314467577709</v>
       </c>
       <c r="BJ55" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.9075331070017416E-2</v>
       </c>
       <c r="BK55" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>5.7991313075208026</v>
       </c>
     </row>
     <row r="56" spans="1:63" x14ac:dyDescent="0.3">
@@ -12051,7 +12380,7 @@
       </c>
       <c r="AY56" s="13">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.36420444864000001</v>
       </c>
       <c r="AZ56" s="13">
         <f t="shared" si="33"/>
@@ -12078,7 +12407,7 @@
         <v/>
       </c>
       <c r="BF56" s="57">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BG56" s="14">
@@ -12180,7 +12509,7 @@
       </c>
       <c r="AY57" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.37583801280000007</v>
       </c>
       <c r="AZ57" s="30">
         <f t="shared" si="33"/>
@@ -12207,7 +12536,7 @@
         <v/>
       </c>
       <c r="BF57" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG57" s="31">
@@ -12309,7 +12638,7 @@
       </c>
       <c r="AY58" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.38219832000000009</v>
       </c>
       <c r="AZ58" s="30">
         <f t="shared" si="33"/>
@@ -12336,7 +12665,7 @@
         <v/>
       </c>
       <c r="BF58" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG58" s="31">
@@ -12438,7 +12767,7 @@
       </c>
       <c r="AY59" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.38604862944000012</v>
       </c>
       <c r="AZ59" s="30">
         <f t="shared" si="33"/>
@@ -12449,11 +12778,11 @@
         <v>#N/A</v>
       </c>
       <c r="BB59" s="31">
-        <f t="shared" ref="BB59:BB70" si="37">AK59/AP59</f>
+        <f t="shared" ref="BB59:BB70" si="38">AK59/AP59</f>
         <v>0</v>
       </c>
       <c r="BC59" s="31">
-        <f t="shared" ref="BC59:BC70" si="38">AJ59*24</f>
+        <f t="shared" ref="BC59:BC70" si="39">AJ59*24</f>
         <v>0</v>
       </c>
       <c r="BD59" s="31" t="str">
@@ -12465,7 +12794,7 @@
         <v>0</v>
       </c>
       <c r="BF59" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG59" s="31" t="str">
@@ -12562,27 +12891,27 @@
       <c r="AV60" s="17"/>
       <c r="AW60" s="41"/>
       <c r="AX60" s="16">
-        <f t="shared" ref="AX60:AX70" si="39">AT60*J60*AZ60/1000</f>
+        <f t="shared" ref="AX60:AX70" si="40">AT60*J60*AZ60/1000</f>
         <v>0</v>
       </c>
       <c r="AY60" s="17">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.39844348416000003</v>
       </c>
       <c r="AZ60" s="17">
         <f t="shared" si="33"/>
         <v>1540</v>
       </c>
       <c r="BA60" s="18" t="e">
-        <f t="shared" ref="BA60:BA70" si="40">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
+        <f t="shared" ref="BA60:BA70" si="41">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
         <v>#N/A</v>
       </c>
       <c r="BB60" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC60" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD60" s="18" t="str">
@@ -12594,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="BF60" s="59" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG60" s="18" t="str">
@@ -12606,15 +12935,15 @@
         <v>0</v>
       </c>
       <c r="BI60" s="47">
-        <f t="shared" ref="BI60:BI70" si="41">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
+        <f t="shared" ref="BI60:BI70" si="42">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BJ60" s="67">
-        <f t="shared" ref="BJ60:BJ65" si="42">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
+        <f t="shared" ref="BJ60:BJ65" si="43">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
         <v>0</v>
       </c>
       <c r="BK60" s="49">
-        <f t="shared" ref="BK60:BK70" si="43">IF(BG60&lt;&gt;"",BG60,BH60)</f>
+        <f t="shared" ref="BK60:BK70" si="44">IF(BG60&lt;&gt;"",BG60,BH60)</f>
         <v>0</v>
       </c>
     </row>
@@ -12691,7 +13020,7 @@
       <c r="AV61" s="13"/>
       <c r="AW61" s="39"/>
       <c r="AX61" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY61" s="13">
@@ -12703,15 +13032,15 @@
         <v>1524</v>
       </c>
       <c r="BA61" s="14" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB61" s="14">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC61" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD61" s="14" t="str">
@@ -12723,7 +13052,7 @@
         <v/>
       </c>
       <c r="BF61" s="57">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BG61" s="14">
@@ -12735,15 +13064,15 @@
         <v/>
       </c>
       <c r="BI61" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ61" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BK61" s="48">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>11.43</v>
       </c>
     </row>
@@ -12820,7 +13149,7 @@
       <c r="AV62" s="30"/>
       <c r="AW62" s="40"/>
       <c r="AX62" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY62" s="30">
@@ -12832,15 +13161,15 @@
         <v>1524</v>
       </c>
       <c r="BA62" s="31" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB62" s="31">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC62" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD62" s="31">
@@ -12852,7 +13181,7 @@
         <v/>
       </c>
       <c r="BF62" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG62" s="31">
@@ -12864,15 +13193,15 @@
         <v/>
       </c>
       <c r="BI62" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ62" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BK62" s="48">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>11.43</v>
       </c>
     </row>
@@ -12949,7 +13278,7 @@
       <c r="AV63" s="30"/>
       <c r="AW63" s="40"/>
       <c r="AX63" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY63" s="30">
@@ -12961,15 +13290,15 @@
         <v>1524</v>
       </c>
       <c r="BA63" s="31" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB63" s="31">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC63" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD63" s="31">
@@ -12981,7 +13310,7 @@
         <v/>
       </c>
       <c r="BF63" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG63" s="31">
@@ -12993,15 +13322,15 @@
         <v/>
       </c>
       <c r="BI63" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ63" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BK63" s="48">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>11.43</v>
       </c>
     </row>
@@ -13078,7 +13407,7 @@
       <c r="AV64" s="30"/>
       <c r="AW64" s="40"/>
       <c r="AX64" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY64" s="30">
@@ -13090,15 +13419,15 @@
         <v>1524</v>
       </c>
       <c r="BA64" s="31" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB64" s="31">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC64" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD64" s="31" t="str">
@@ -13110,7 +13439,7 @@
         <v>0</v>
       </c>
       <c r="BF64" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG64" s="31" t="str">
@@ -13122,15 +13451,15 @@
         <v>0</v>
       </c>
       <c r="BI64" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ64" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BK64" s="48">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
@@ -13207,7 +13536,7 @@
       <c r="AV65" s="17"/>
       <c r="AW65" s="41"/>
       <c r="AX65" s="16">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY65" s="17">
@@ -13219,15 +13548,15 @@
         <v>1524</v>
       </c>
       <c r="BA65" s="18" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB65" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC65" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD65" s="18" t="str">
@@ -13239,7 +13568,7 @@
         <v>0</v>
       </c>
       <c r="BF65" s="59" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG65" s="18" t="str">
@@ -13251,15 +13580,15 @@
         <v>0</v>
       </c>
       <c r="BI65" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ65" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BK65" s="48">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
@@ -13336,7 +13665,7 @@
       <c r="AV66" s="4"/>
       <c r="AW66" s="22"/>
       <c r="AX66" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY66" s="13">
@@ -13348,15 +13677,15 @@
         <v>1508</v>
       </c>
       <c r="BA66" s="14" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB66" s="14">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC66" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD66" s="14" t="str">
@@ -13368,7 +13697,7 @@
         <v/>
       </c>
       <c r="BF66" s="57">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="BG66" s="14">
@@ -13380,12 +13709,12 @@
         <v/>
       </c>
       <c r="BI66" s="45">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ66" s="62"/>
       <c r="BK66" s="50">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>11.31</v>
       </c>
     </row>
@@ -13462,7 +13791,7 @@
       <c r="AV67" s="27"/>
       <c r="AW67" s="2"/>
       <c r="AX67" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY67" s="30">
@@ -13474,15 +13803,15 @@
         <v>1508</v>
       </c>
       <c r="BA67" s="31" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB67" s="31">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC67" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD67" s="31">
@@ -13494,7 +13823,7 @@
         <v/>
       </c>
       <c r="BF67" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG67" s="31">
@@ -13506,12 +13835,12 @@
         <v/>
       </c>
       <c r="BI67" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ67" s="63"/>
       <c r="BK67" s="48">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>11.31</v>
       </c>
     </row>
@@ -13588,7 +13917,7 @@
       <c r="AV68" s="30"/>
       <c r="AW68" s="40"/>
       <c r="AX68" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY68" s="30">
@@ -13600,15 +13929,15 @@
         <v>1508</v>
       </c>
       <c r="BA68" s="31" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB68" s="31">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC68" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD68" s="31">
@@ -13620,7 +13949,7 @@
         <v/>
       </c>
       <c r="BF68" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG68" s="31">
@@ -13632,12 +13961,12 @@
         <v/>
       </c>
       <c r="BI68" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ68" s="63"/>
       <c r="BK68" s="48">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>11.31</v>
       </c>
     </row>
@@ -13714,7 +14043,7 @@
       <c r="AV69" s="30"/>
       <c r="AW69" s="40"/>
       <c r="AX69" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY69" s="30">
@@ -13726,15 +14055,15 @@
         <v>1508</v>
       </c>
       <c r="BA69" s="31" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB69" s="31">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC69" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD69" s="31" t="str">
@@ -13746,7 +14075,7 @@
         <v>0</v>
       </c>
       <c r="BF69" s="58" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG69" s="31" t="str">
@@ -13758,12 +14087,12 @@
         <v>0</v>
       </c>
       <c r="BI69" s="46">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ69" s="63"/>
       <c r="BK69" s="48">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
@@ -13840,7 +14169,7 @@
       <c r="AV70" s="17"/>
       <c r="AW70" s="41"/>
       <c r="AX70" s="16">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AY70" s="17">
@@ -13852,15 +14181,15 @@
         <v>1508</v>
       </c>
       <c r="BA70" s="18" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#N/A</v>
       </c>
       <c r="BB70" s="18">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BC70" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BD70" s="18" t="str">
@@ -13872,7 +14201,7 @@
         <v>0</v>
       </c>
       <c r="BF70" s="59" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BG70" s="18" t="str">
@@ -13884,12 +14213,12 @@
         <v>0</v>
       </c>
       <c r="BI70" s="47">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="BJ70" s="64"/>
       <c r="BK70" s="49">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
@@ -14214,15 +14543,15 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1995" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19C793F4-5BB4-4EE9-BAF9-7EC1C510882B}"/>
+  <xr:revisionPtr revIDLastSave="2105" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46FBB556-837C-4AF9-849E-CF5796052964}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -11418,7 +11418,7 @@
       <c r="Z51" s="4"/>
       <c r="AA51" s="4"/>
       <c r="AB51" s="22">
-        <v>7.26</v>
+        <v>7.31</v>
       </c>
       <c r="AC51" s="3">
         <v>300</v>
@@ -11449,11 +11449,11 @@
         <v>46</v>
       </c>
       <c r="AM51" s="4">
-        <f t="shared" ref="AM51:AM55" si="36">AK51-AK46</f>
+        <f t="shared" ref="AM51:AN55" si="36">AK51-AK46</f>
         <v>21</v>
       </c>
       <c r="AN51" s="4">
-        <f t="shared" ref="AN51:AN55" si="37">AL51-AL46</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AO51" s="42">
@@ -11555,10 +11555,10 @@
       <c r="H52" s="29">
         <v>4487.28</v>
       </c>
-      <c r="I52" s="35">
+      <c r="I52" s="27">
         <v>21.6</v>
       </c>
-      <c r="J52" s="35">
+      <c r="J52" s="27">
         <v>20.5</v>
       </c>
       <c r="K52" s="35">
@@ -11567,13 +11567,13 @@
       <c r="L52" s="35">
         <v>18.2</v>
       </c>
-      <c r="M52" s="35">
+      <c r="M52" s="27">
         <v>394</v>
       </c>
-      <c r="N52" s="35">
+      <c r="N52" s="27">
         <v>2.91</v>
       </c>
-      <c r="O52" s="35">
+      <c r="O52" s="27">
         <v>0.22</v>
       </c>
       <c r="P52" s="35">
@@ -11582,7 +11582,7 @@
       <c r="Q52" s="35">
         <v>0.52</v>
       </c>
-      <c r="R52" s="35">
+      <c r="R52">
         <v>0.36</v>
       </c>
       <c r="S52" s="35">
@@ -11607,7 +11607,7 @@
       <c r="Z52" s="27"/>
       <c r="AA52" s="27"/>
       <c r="AB52" s="2">
-        <v>7.2859999999999996</v>
+        <v>7.3369999999999997</v>
       </c>
       <c r="AC52" s="1">
         <v>299</v>
@@ -11627,14 +11627,14 @@
       <c r="AH52" s="27">
         <v>11.22</v>
       </c>
-      <c r="AI52" s="35">
+      <c r="AI52" s="27">
         <v>5</v>
       </c>
       <c r="AJ52" s="27"/>
-      <c r="AK52" s="72">
+      <c r="AK52" s="30">
         <v>249</v>
       </c>
-      <c r="AL52" s="72">
+      <c r="AL52" s="30">
         <v>55</v>
       </c>
       <c r="AM52" s="27">
@@ -11642,7 +11642,7 @@
         <v>17</v>
       </c>
       <c r="AN52" s="27">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AO52" s="43">
@@ -11773,7 +11773,7 @@
       <c r="Q53" s="35">
         <v>0.5</v>
       </c>
-      <c r="R53" s="35">
+      <c r="R53">
         <v>0.42</v>
       </c>
       <c r="S53" s="35">
@@ -11798,7 +11798,7 @@
       <c r="Z53" s="27"/>
       <c r="AA53" s="27"/>
       <c r="AB53" s="2">
-        <v>7.266</v>
+        <v>7.3159999999999998</v>
       </c>
       <c r="AC53" s="1">
         <v>301</v>
@@ -11833,7 +11833,7 @@
         <v>27</v>
       </c>
       <c r="AN53" s="27">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>10</v>
       </c>
       <c r="AO53" s="43">
@@ -11964,7 +11964,7 @@
       <c r="Q54" s="35">
         <v>0.43</v>
       </c>
-      <c r="R54" s="35">
+      <c r="R54">
         <v>0.11</v>
       </c>
       <c r="S54" s="35">
@@ -11989,7 +11989,7 @@
       <c r="Z54" s="27"/>
       <c r="AA54" s="27"/>
       <c r="AB54" s="2">
-        <v>7.2350000000000003</v>
+        <v>7.2830000000000004</v>
       </c>
       <c r="AC54" s="1">
         <v>302</v>
@@ -12024,7 +12024,7 @@
         <v>30</v>
       </c>
       <c r="AN54" s="27">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>7</v>
       </c>
       <c r="AO54" s="43">
@@ -12182,7 +12182,7 @@
       <c r="Z55" s="7"/>
       <c r="AA55" s="7"/>
       <c r="AB55" s="23">
-        <v>7.25</v>
+        <v>7.2990000000000004</v>
       </c>
       <c r="AC55" s="6">
         <v>299</v>
@@ -12217,7 +12217,7 @@
         <v>24</v>
       </c>
       <c r="AN55" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>8</v>
       </c>
       <c r="AO55" s="44">
@@ -12320,39 +12320,99 @@
         <v>5302.42</v>
       </c>
       <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="27"/>
-      <c r="K56" s="27"/>
-      <c r="L56" s="27"/>
-      <c r="M56" s="27"/>
-      <c r="N56" s="27"/>
-      <c r="O56" s="27"/>
-      <c r="P56" s="27"/>
-      <c r="Q56" s="27"/>
-      <c r="R56" s="27"/>
-      <c r="S56" s="27"/>
-      <c r="T56" s="27"/>
-      <c r="U56" s="27"/>
-      <c r="V56" s="27"/>
-      <c r="W56" s="27"/>
-      <c r="X56" s="27"/>
+      <c r="H56" s="29">
+        <v>4879.29</v>
+      </c>
+      <c r="I56" s="35">
+        <v>21.2</v>
+      </c>
+      <c r="J56" s="35">
+        <v>19.8</v>
+      </c>
+      <c r="K56" s="35">
+        <v>93.4</v>
+      </c>
+      <c r="L56" s="35">
+        <v>17.2</v>
+      </c>
+      <c r="M56" s="35">
+        <v>365</v>
+      </c>
+      <c r="N56" s="35">
+        <v>1.26</v>
+      </c>
+      <c r="O56" s="35">
+        <v>0.18</v>
+      </c>
+      <c r="P56" s="35">
+        <v>1.65</v>
+      </c>
+      <c r="Q56" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="R56" s="35">
+        <v>0.11</v>
+      </c>
+      <c r="S56" s="35">
+        <v>1.07</v>
+      </c>
+      <c r="T56" s="35">
+        <v>7.2619999999999996</v>
+      </c>
+      <c r="U56" s="35">
+        <v>125.5</v>
+      </c>
+      <c r="V56" s="35">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="W56" s="35">
+        <v>2.09</v>
+      </c>
+      <c r="X56" s="35">
+        <v>158</v>
+      </c>
       <c r="Y56" s="27"/>
       <c r="Z56" s="27"/>
       <c r="AA56" s="27"/>
-      <c r="AB56" s="2"/>
-      <c r="AC56" s="3"/>
-      <c r="AD56" s="4"/>
-      <c r="AE56" s="4"/>
-      <c r="AF56" s="4"/>
-      <c r="AG56" s="4"/>
-      <c r="AH56" s="4"/>
-      <c r="AI56" s="4"/>
+      <c r="AB56" s="2">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="AC56" s="3">
+        <v>299</v>
+      </c>
+      <c r="AD56" s="4">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="AE56" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="AF56" s="4">
+        <v>34</v>
+      </c>
+      <c r="AG56" s="4">
+        <v>31.315000000000001</v>
+      </c>
+      <c r="AH56" s="4">
+        <v>78.787000000000006</v>
+      </c>
+      <c r="AI56" s="4">
+        <v>8</v>
+      </c>
       <c r="AJ56" s="4"/>
-      <c r="AK56" s="4"/>
-      <c r="AL56" s="4"/>
-      <c r="AM56" s="4"/>
-      <c r="AN56" s="4"/>
+      <c r="AK56" s="4">
+        <v>194</v>
+      </c>
+      <c r="AL56" s="4">
+        <v>46</v>
+      </c>
+      <c r="AM56" s="4">
+        <f t="shared" ref="AM56:AM60" si="37">AK56-AK51</f>
+        <v>25</v>
+      </c>
+      <c r="AN56" s="4">
+        <f t="shared" ref="AN56:AN60" si="38">AL56-AL51</f>
+        <v>0</v>
+      </c>
       <c r="AO56" s="42">
         <v>15</v>
       </c>
@@ -12376,7 +12436,7 @@
       <c r="AW56" s="39"/>
       <c r="AX56" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.503296784E-2</v>
       </c>
       <c r="AY56" s="13">
         <f t="shared" si="21"/>
@@ -12384,15 +12444,15 @@
       </c>
       <c r="AZ56" s="13">
         <f t="shared" si="33"/>
-        <v>1540</v>
-      </c>
-      <c r="BA56" s="14" t="e">
+        <v>1898.1019999999999</v>
+      </c>
+      <c r="BA56" s="14">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.10220736293413105</v>
       </c>
       <c r="BB56" s="14">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.11411764705882353</v>
       </c>
       <c r="BC56" s="14">
         <f t="shared" si="26"/>
@@ -12408,11 +12468,11 @@
       </c>
       <c r="BF56" s="57">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1.503296784E-2</v>
       </c>
       <c r="BG56" s="14">
         <f t="shared" si="24"/>
-        <v>11.55</v>
+        <v>0</v>
       </c>
       <c r="BH56" s="14" t="str">
         <f t="shared" si="28"/>
@@ -12420,15 +12480,15 @@
       </c>
       <c r="BI56" s="45">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>39.046669714285713</v>
       </c>
       <c r="BJ56" s="65">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.503296784E-2</v>
       </c>
       <c r="BK56" s="50">
         <f t="shared" si="12"/>
-        <v>11.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:63" x14ac:dyDescent="0.3">
@@ -12449,39 +12509,99 @@
         <v>5302.42</v>
       </c>
       <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="27"/>
-      <c r="P57" s="27"/>
-      <c r="Q57" s="27"/>
-      <c r="R57" s="27"/>
-      <c r="S57" s="27"/>
-      <c r="T57" s="27"/>
-      <c r="U57" s="27"/>
-      <c r="V57" s="27"/>
-      <c r="W57" s="27"/>
-      <c r="X57" s="27"/>
+      <c r="H57" s="29">
+        <v>4865.99</v>
+      </c>
+      <c r="I57" s="35">
+        <v>21.8</v>
+      </c>
+      <c r="J57" s="35">
+        <v>20.3</v>
+      </c>
+      <c r="K57" s="35">
+        <v>93.2</v>
+      </c>
+      <c r="L57" s="35">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="M57" s="35">
+        <v>395</v>
+      </c>
+      <c r="N57" s="35">
+        <v>3</v>
+      </c>
+      <c r="O57" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="P57" s="35">
+        <v>0.51</v>
+      </c>
+      <c r="Q57" s="35">
+        <v>0.62</v>
+      </c>
+      <c r="R57" s="35">
+        <v>1.07</v>
+      </c>
+      <c r="S57" s="35">
+        <v>0.78</v>
+      </c>
+      <c r="T57" s="35">
+        <v>7.2679999999999998</v>
+      </c>
+      <c r="U57" s="35">
+        <v>154</v>
+      </c>
+      <c r="V57" s="35">
+        <v>13</v>
+      </c>
+      <c r="W57" s="35">
+        <v>1.45</v>
+      </c>
+      <c r="X57" s="35">
+        <v>168.8</v>
+      </c>
       <c r="Y57" s="27"/>
       <c r="Z57" s="27"/>
       <c r="AA57" s="27"/>
-      <c r="AB57" s="2"/>
-      <c r="AC57" s="1"/>
-      <c r="AD57" s="27"/>
-      <c r="AE57" s="27"/>
-      <c r="AF57" s="27"/>
-      <c r="AG57" s="27"/>
-      <c r="AH57" s="27"/>
-      <c r="AI57" s="27"/>
+      <c r="AB57" s="2">
+        <v>7.3090000000000002</v>
+      </c>
+      <c r="AC57" s="1">
+        <v>299</v>
+      </c>
+      <c r="AD57" s="27">
+        <v>0.496</v>
+      </c>
+      <c r="AE57" s="27">
+        <v>7.28</v>
+      </c>
+      <c r="AF57" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG57" s="27">
+        <v>33.526000000000003</v>
+      </c>
+      <c r="AH57" s="27">
+        <v>14.769</v>
+      </c>
+      <c r="AI57" s="27">
+        <v>6</v>
+      </c>
       <c r="AJ57" s="27"/>
-      <c r="AK57" s="27"/>
-      <c r="AL57" s="27"/>
-      <c r="AM57" s="27"/>
-      <c r="AN57" s="27"/>
+      <c r="AK57" s="72">
+        <v>280</v>
+      </c>
+      <c r="AL57" s="72">
+        <v>70</v>
+      </c>
+      <c r="AM57" s="27">
+        <f t="shared" si="37"/>
+        <v>31</v>
+      </c>
+      <c r="AN57" s="27">
+        <f t="shared" si="38"/>
+        <v>15</v>
+      </c>
       <c r="AO57" s="43">
         <v>15</v>
       </c>
@@ -12505,7 +12625,7 @@
       <c r="AW57" s="40"/>
       <c r="AX57" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.5787675400000003E-2</v>
       </c>
       <c r="AY57" s="30">
         <f t="shared" si="21"/>
@@ -12513,15 +12633,15 @@
       </c>
       <c r="AZ57" s="30">
         <f t="shared" si="33"/>
-        <v>1540</v>
-      </c>
-      <c r="BA57" s="31" t="e">
+        <v>1944.2950000000001</v>
+      </c>
+      <c r="BA57" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.14401106827924776</v>
       </c>
       <c r="BB57" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.16470588235294117</v>
       </c>
       <c r="BC57" s="31">
         <f t="shared" si="26"/>
@@ -12541,7 +12661,7 @@
       </c>
       <c r="BG57" s="31">
         <f t="shared" si="24"/>
-        <v>11.55</v>
+        <v>12.103236375000002</v>
       </c>
       <c r="BH57" s="31" t="str">
         <f t="shared" si="28"/>
@@ -12557,7 +12677,7 @@
       </c>
       <c r="BK57" s="48">
         <f t="shared" si="12"/>
-        <v>11.55</v>
+        <v>12.103236375000002</v>
       </c>
     </row>
     <row r="58" spans="1:63" x14ac:dyDescent="0.3">
@@ -12578,39 +12698,99 @@
         <v>5302.42</v>
       </c>
       <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
-      <c r="X58" s="27"/>
+      <c r="H58" s="29">
+        <v>5056.1850000000004</v>
+      </c>
+      <c r="I58" s="35">
+        <v>21.6</v>
+      </c>
+      <c r="J58" s="35">
+        <v>20.3</v>
+      </c>
+      <c r="K58" s="35">
+        <v>94.3</v>
+      </c>
+      <c r="L58" s="35">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="M58" s="35">
+        <v>386</v>
+      </c>
+      <c r="N58" s="35">
+        <v>2.61</v>
+      </c>
+      <c r="O58" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="P58" s="35">
+        <v>0.82</v>
+      </c>
+      <c r="Q58" s="35">
+        <v>0.64</v>
+      </c>
+      <c r="R58" s="35">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="S58" s="35">
+        <v>0.76</v>
+      </c>
+      <c r="T58" s="35">
+        <v>7.2539999999999996</v>
+      </c>
+      <c r="U58" s="35">
+        <v>129.1</v>
+      </c>
+      <c r="V58" s="35">
+        <v>0</v>
+      </c>
+      <c r="W58" s="35">
+        <v>1.44</v>
+      </c>
+      <c r="X58" s="35">
+        <v>162.6</v>
+      </c>
       <c r="Y58" s="27"/>
       <c r="Z58" s="27"/>
       <c r="AA58" s="27"/>
-      <c r="AB58" s="2"/>
-      <c r="AC58" s="1"/>
-      <c r="AD58" s="27"/>
-      <c r="AE58" s="27"/>
-      <c r="AF58" s="27"/>
-      <c r="AG58" s="27"/>
-      <c r="AH58" s="27"/>
-      <c r="AI58" s="27"/>
+      <c r="AB58" s="2">
+        <v>7.2960000000000003</v>
+      </c>
+      <c r="AC58" s="1">
+        <v>301</v>
+      </c>
+      <c r="AD58" s="27">
+        <v>0.23199999999999998</v>
+      </c>
+      <c r="AE58" s="27">
+        <v>7.28</v>
+      </c>
+      <c r="AF58" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG58" s="27">
+        <v>27.274000000000001</v>
+      </c>
+      <c r="AH58" s="27">
+        <v>12.154</v>
+      </c>
+      <c r="AI58" s="27">
+        <v>7</v>
+      </c>
       <c r="AJ58" s="27"/>
-      <c r="AK58" s="27"/>
-      <c r="AL58" s="27"/>
-      <c r="AM58" s="27"/>
-      <c r="AN58" s="27"/>
+      <c r="AK58" s="72">
+        <v>273</v>
+      </c>
+      <c r="AL58" s="72">
+        <v>68</v>
+      </c>
+      <c r="AM58" s="27">
+        <f t="shared" si="37"/>
+        <v>36</v>
+      </c>
+      <c r="AN58" s="27">
+        <f t="shared" si="38"/>
+        <v>11</v>
+      </c>
       <c r="AO58" s="43">
         <v>15</v>
       </c>
@@ -12634,7 +12814,7 @@
       <c r="AW58" s="40"/>
       <c r="AX58" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.5650715360000001E-2</v>
       </c>
       <c r="AY58" s="30">
         <f t="shared" si="21"/>
@@ -12642,15 +12822,15 @@
       </c>
       <c r="AZ58" s="30">
         <f t="shared" si="33"/>
-        <v>1540</v>
-      </c>
-      <c r="BA58" s="31" t="e">
+        <v>1927.4279999999999</v>
+      </c>
+      <c r="BA58" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.14163953206034155</v>
       </c>
       <c r="BB58" s="31">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.16058823529411764</v>
       </c>
       <c r="BC58" s="31">
         <f t="shared" si="26"/>
@@ -12670,7 +12850,7 @@
       </c>
       <c r="BG58" s="31">
         <f t="shared" si="24"/>
-        <v>11.55</v>
+        <v>10.504482600000001</v>
       </c>
       <c r="BH58" s="31" t="str">
         <f t="shared" si="28"/>
@@ -12686,7 +12866,7 @@
       </c>
       <c r="BK58" s="48">
         <f t="shared" si="12"/>
-        <v>11.55</v>
+        <v>10.504482600000001</v>
       </c>
     </row>
     <row r="59" spans="1:63" x14ac:dyDescent="0.3">
@@ -12707,39 +12887,99 @@
         <v>5302.42</v>
       </c>
       <c r="G59" s="29"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
-      <c r="N59" s="27"/>
-      <c r="O59" s="27"/>
-      <c r="P59" s="27"/>
-      <c r="Q59" s="27"/>
-      <c r="R59" s="27"/>
-      <c r="S59" s="27"/>
-      <c r="T59" s="27"/>
-      <c r="U59" s="27"/>
-      <c r="V59" s="27"/>
-      <c r="W59" s="27"/>
-      <c r="X59" s="27"/>
+      <c r="H59" s="29">
+        <v>5346.89</v>
+      </c>
+      <c r="I59" s="35">
+        <v>22.6</v>
+      </c>
+      <c r="J59" s="35">
+        <v>21</v>
+      </c>
+      <c r="K59" s="35">
+        <v>93</v>
+      </c>
+      <c r="L59" s="35">
+        <v>17.2</v>
+      </c>
+      <c r="M59" s="35">
+        <v>361</v>
+      </c>
+      <c r="N59" s="35">
+        <v>3.53</v>
+      </c>
+      <c r="O59" s="35">
+        <v>0.19</v>
+      </c>
+      <c r="P59" s="35">
+        <v>0.04</v>
+      </c>
+      <c r="Q59" s="35">
+        <v>0.44</v>
+      </c>
+      <c r="R59" s="35">
+        <v>0.63</v>
+      </c>
+      <c r="S59" s="35">
+        <v>0.22</v>
+      </c>
+      <c r="T59" s="35">
+        <v>7.2619999999999996</v>
+      </c>
+      <c r="U59" s="35">
+        <v>138.69999999999999</v>
+      </c>
+      <c r="V59" s="35">
+        <v>0.9</v>
+      </c>
+      <c r="W59" s="35">
+        <v>1.67</v>
+      </c>
+      <c r="X59" s="35">
+        <v>157.5</v>
+      </c>
       <c r="Y59" s="27"/>
       <c r="Z59" s="27"/>
       <c r="AA59" s="27"/>
-      <c r="AB59" s="2"/>
-      <c r="AC59" s="1"/>
-      <c r="AD59" s="27"/>
-      <c r="AE59" s="27"/>
-      <c r="AF59" s="27"/>
-      <c r="AG59" s="27"/>
-      <c r="AH59" s="27"/>
-      <c r="AI59" s="27"/>
+      <c r="AB59" s="2">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AC59" s="1">
+        <v>299</v>
+      </c>
+      <c r="AD59" s="27">
+        <v>0.503</v>
+      </c>
+      <c r="AE59" s="27">
+        <v>7.3</v>
+      </c>
+      <c r="AF59" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG59" s="27">
+        <v>24.766999999999999</v>
+      </c>
+      <c r="AH59" s="27">
+        <v>15.1</v>
+      </c>
+      <c r="AI59" s="27">
+        <v>14</v>
+      </c>
       <c r="AJ59" s="27"/>
-      <c r="AK59" s="27"/>
-      <c r="AL59" s="27"/>
-      <c r="AM59" s="27"/>
-      <c r="AN59" s="27"/>
+      <c r="AK59" s="72">
+        <v>262</v>
+      </c>
+      <c r="AL59" s="72">
+        <v>59</v>
+      </c>
+      <c r="AM59" s="27">
+        <f t="shared" si="37"/>
+        <v>34</v>
+      </c>
+      <c r="AN59" s="27">
+        <f t="shared" si="38"/>
+        <v>2</v>
+      </c>
       <c r="AO59" s="43">
         <v>15</v>
       </c>
@@ -12763,7 +13003,7 @@
       <c r="AW59" s="40"/>
       <c r="AX59" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.6084882800000002E-2</v>
       </c>
       <c r="AY59" s="30">
         <f t="shared" si="21"/>
@@ -12771,18 +13011,18 @@
       </c>
       <c r="AZ59" s="30">
         <f t="shared" si="33"/>
-        <v>1540</v>
-      </c>
-      <c r="BA59" s="31" t="e">
+        <v>1914.8670000000002</v>
+      </c>
+      <c r="BA59" s="31">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
+        <v>0.13682412407754688</v>
       </c>
       <c r="BB59" s="31">
-        <f t="shared" ref="BB59:BB70" si="38">AK59/AP59</f>
-        <v>0</v>
+        <f t="shared" ref="BB59:BB70" si="39">AK59/AP59</f>
+        <v>0.15411764705882353</v>
       </c>
       <c r="BC59" s="31">
-        <f t="shared" ref="BC59:BC70" si="39">AJ59*24</f>
+        <f t="shared" ref="BC59:BC70" si="40">AJ59*24</f>
         <v>0</v>
       </c>
       <c r="BD59" s="31" t="str">
@@ -12836,39 +13076,99 @@
         <v>5302.42</v>
       </c>
       <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="27"/>
-      <c r="S60" s="27"/>
-      <c r="T60" s="27"/>
-      <c r="U60" s="27"/>
-      <c r="V60" s="27"/>
-      <c r="W60" s="27"/>
-      <c r="X60" s="27"/>
+      <c r="H60" s="29">
+        <v>5636.1450000000004</v>
+      </c>
+      <c r="I60" s="35">
+        <v>23.5</v>
+      </c>
+      <c r="J60" s="35">
+        <v>20.9</v>
+      </c>
+      <c r="K60" s="35">
+        <v>89.2</v>
+      </c>
+      <c r="L60" s="35">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M60" s="35">
+        <v>357</v>
+      </c>
+      <c r="N60" s="35">
+        <v>4.24</v>
+      </c>
+      <c r="O60" s="35">
+        <v>0.22</v>
+      </c>
+      <c r="P60" s="35">
+        <v>0.03</v>
+      </c>
+      <c r="Q60" s="35">
+        <v>0.39</v>
+      </c>
+      <c r="R60" s="35">
+        <v>0.31</v>
+      </c>
+      <c r="S60" s="35">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="T60" s="35">
+        <v>7.2539999999999996</v>
+      </c>
+      <c r="U60" s="35">
+        <v>132.30000000000001</v>
+      </c>
+      <c r="V60" s="35">
+        <v>32.9</v>
+      </c>
+      <c r="W60" s="35">
+        <v>1.96</v>
+      </c>
+      <c r="X60" s="35">
+        <v>154.5</v>
+      </c>
       <c r="Y60" s="27"/>
       <c r="Z60" s="27"/>
       <c r="AA60" s="27"/>
-      <c r="AB60" s="2"/>
-      <c r="AC60" s="6"/>
-      <c r="AD60" s="7"/>
-      <c r="AE60" s="7"/>
-      <c r="AF60" s="7"/>
-      <c r="AG60" s="7"/>
-      <c r="AH60" s="7"/>
-      <c r="AI60" s="7"/>
+      <c r="AB60" s="2">
+        <v>7.2949999999999999</v>
+      </c>
+      <c r="AC60" s="6">
+        <v>301</v>
+      </c>
+      <c r="AD60" s="7">
+        <v>0.496</v>
+      </c>
+      <c r="AE60" s="7">
+        <v>7.3</v>
+      </c>
+      <c r="AF60" s="7">
+        <v>34</v>
+      </c>
+      <c r="AG60" s="7">
+        <v>21.77</v>
+      </c>
+      <c r="AH60" s="7">
+        <v>57.984000000000002</v>
+      </c>
+      <c r="AI60" s="7">
+        <v>14</v>
+      </c>
       <c r="AJ60" s="7"/>
-      <c r="AK60" s="7"/>
-      <c r="AL60" s="7"/>
-      <c r="AM60" s="7"/>
-      <c r="AN60" s="7"/>
+      <c r="AK60" s="7">
+        <v>262</v>
+      </c>
+      <c r="AL60" s="7">
+        <v>74</v>
+      </c>
+      <c r="AM60" s="7">
+        <f t="shared" si="37"/>
+        <v>30</v>
+      </c>
+      <c r="AN60" s="7">
+        <f t="shared" si="38"/>
+        <v>6</v>
+      </c>
       <c r="AO60" s="44">
         <v>15</v>
       </c>
@@ -12891,8 +13191,8 @@
       <c r="AV60" s="17"/>
       <c r="AW60" s="41"/>
       <c r="AX60" s="16">
-        <f t="shared" ref="AX60:AX70" si="40">AT60*J60*AZ60/1000</f>
-        <v>0</v>
+        <f t="shared" ref="AX60:AX70" si="41">AT60*J60*AZ60/1000</f>
+        <v>1.6467143439999998E-2</v>
       </c>
       <c r="AY60" s="17">
         <f t="shared" si="21"/>
@@ -12900,18 +13200,18 @@
       </c>
       <c r="AZ60" s="17">
         <f t="shared" si="33"/>
-        <v>1540</v>
-      </c>
-      <c r="BA60" s="18" t="e">
-        <f t="shared" ref="BA60:BA70" si="41">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
-        <v>#N/A</v>
+        <v>1969.7539999999999</v>
+      </c>
+      <c r="BA60" s="18">
+        <f t="shared" ref="BA60:BA70" si="42">IF(ISBLANK(AK60),NA(),IFERROR(AK60/AZ60,0))</f>
+        <v>0.13301153341990929</v>
       </c>
       <c r="BB60" s="18">
-        <f t="shared" si="38"/>
-        <v>0</v>
+        <f t="shared" si="39"/>
+        <v>0.15411764705882353</v>
       </c>
       <c r="BC60" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD60" s="18" t="str">
@@ -12935,15 +13235,15 @@
         <v>0</v>
       </c>
       <c r="BI60" s="47">
-        <f t="shared" ref="BI60:BI70" si="42">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
+        <f t="shared" ref="BI60:BI70" si="43">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BJ60" s="67">
-        <f t="shared" ref="BJ60:BJ65" si="43">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
+        <f t="shared" ref="BJ60:BJ65" si="44">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
         <v>0</v>
       </c>
       <c r="BK60" s="49">
-        <f t="shared" ref="BK60:BK70" si="44">IF(BG60&lt;&gt;"",BG60,BH60)</f>
+        <f t="shared" ref="BK60:BK70" si="45">IF(BG60&lt;&gt;"",BG60,BH60)</f>
         <v>0</v>
       </c>
     </row>
@@ -13020,27 +13320,27 @@
       <c r="AV61" s="13"/>
       <c r="AW61" s="39"/>
       <c r="AX61" s="12">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY61" s="13">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.36079122815999998</v>
       </c>
       <c r="AZ61" s="13">
         <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA61" s="14" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB61" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC61" s="14">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD61" s="14" t="str">
@@ -13064,15 +13364,15 @@
         <v/>
       </c>
       <c r="BI61" s="46">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ61" s="66">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="BK61" s="48">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>11.43</v>
       </c>
     </row>
@@ -13149,27 +13449,27 @@
       <c r="AV62" s="30"/>
       <c r="AW62" s="40"/>
       <c r="AX62" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY62" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.37890420960000004</v>
       </c>
       <c r="AZ62" s="30">
         <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA62" s="31" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB62" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC62" s="31">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD62" s="31">
@@ -13193,15 +13493,15 @@
         <v/>
       </c>
       <c r="BI62" s="46">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ62" s="66">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="BK62" s="48">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>11.43</v>
       </c>
     </row>
@@ -13278,27 +13578,27 @@
       <c r="AV63" s="30"/>
       <c r="AW63" s="40"/>
       <c r="AX63" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY63" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.37561716864000005</v>
       </c>
       <c r="AZ63" s="30">
         <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA63" s="31" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB63" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC63" s="31">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD63" s="31">
@@ -13322,15 +13622,15 @@
         <v/>
       </c>
       <c r="BI63" s="46">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ63" s="66">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="BK63" s="48">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>11.43</v>
       </c>
     </row>
@@ -13407,27 +13707,27 @@
       <c r="AV64" s="30"/>
       <c r="AW64" s="40"/>
       <c r="AX64" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY64" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.38603718720000002</v>
       </c>
       <c r="AZ64" s="30">
         <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA64" s="31" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB64" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC64" s="31">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD64" s="31" t="str">
@@ -13451,15 +13751,15 @@
         <v>0</v>
       </c>
       <c r="BI64" s="46">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ64" s="66">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="BK64" s="48">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
     </row>
@@ -13536,27 +13836,27 @@
       <c r="AV65" s="17"/>
       <c r="AW65" s="41"/>
       <c r="AX65" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY65" s="17">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.39521144255999996</v>
       </c>
       <c r="AZ65" s="17">
         <f t="shared" si="33"/>
         <v>1524</v>
       </c>
       <c r="BA65" s="18" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB65" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC65" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD65" s="18" t="str">
@@ -13580,15 +13880,15 @@
         <v>0</v>
       </c>
       <c r="BI65" s="46">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ65" s="66">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="BK65" s="48">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
     </row>
@@ -13665,7 +13965,7 @@
       <c r="AV66" s="4"/>
       <c r="AW66" s="22"/>
       <c r="AX66" s="12">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY66" s="13">
@@ -13677,15 +13977,15 @@
         <v>1508</v>
       </c>
       <c r="BA66" s="14" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB66" s="14">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC66" s="14">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD66" s="14" t="str">
@@ -13709,12 +14009,12 @@
         <v/>
       </c>
       <c r="BI66" s="45">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ66" s="62"/>
       <c r="BK66" s="50">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>11.31</v>
       </c>
     </row>
@@ -13791,7 +14091,7 @@
       <c r="AV67" s="27"/>
       <c r="AW67" s="2"/>
       <c r="AX67" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY67" s="30">
@@ -13803,15 +14103,15 @@
         <v>1508</v>
       </c>
       <c r="BA67" s="31" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB67" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC67" s="31">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD67" s="31">
@@ -13835,12 +14135,12 @@
         <v/>
       </c>
       <c r="BI67" s="46">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ67" s="63"/>
       <c r="BK67" s="48">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>11.31</v>
       </c>
     </row>
@@ -13917,7 +14217,7 @@
       <c r="AV68" s="30"/>
       <c r="AW68" s="40"/>
       <c r="AX68" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY68" s="30">
@@ -13929,15 +14229,15 @@
         <v>1508</v>
       </c>
       <c r="BA68" s="31" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB68" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC68" s="31">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD68" s="31">
@@ -13961,12 +14261,12 @@
         <v/>
       </c>
       <c r="BI68" s="46">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ68" s="63"/>
       <c r="BK68" s="48">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>11.31</v>
       </c>
     </row>
@@ -14043,7 +14343,7 @@
       <c r="AV69" s="30"/>
       <c r="AW69" s="40"/>
       <c r="AX69" s="15">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY69" s="30">
@@ -14055,15 +14355,15 @@
         <v>1508</v>
       </c>
       <c r="BA69" s="31" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB69" s="31">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC69" s="31">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD69" s="31" t="str">
@@ -14087,12 +14387,12 @@
         <v>0</v>
       </c>
       <c r="BI69" s="46">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ69" s="63"/>
       <c r="BK69" s="48">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
     </row>
@@ -14169,7 +14469,7 @@
       <c r="AV70" s="17"/>
       <c r="AW70" s="41"/>
       <c r="AX70" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AY70" s="17">
@@ -14181,15 +14481,15 @@
         <v>1508</v>
       </c>
       <c r="BA70" s="18" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>#N/A</v>
       </c>
       <c r="BB70" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="BC70" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="BD70" s="18" t="str">
@@ -14213,12 +14513,12 @@
         <v>0</v>
       </c>
       <c r="BI70" s="47">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="BJ70" s="64"/>
       <c r="BK70" s="49">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
     </row>
@@ -14264,6 +14564,24 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -14486,7 +14804,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -14495,25 +14813,24 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14532,27 +14849,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2105" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46FBB556-837C-4AF9-849E-CF5796052964}"/>
+  <xr:revisionPtr revIDLastSave="2144" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2A7BC4C-98A7-4AA2-B124-906AA79E201D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -952,7 +952,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -1042,6 +1042,7 @@
     <xf numFmtId="165" fontId="14" fillId="39" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1177,10 +1178,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1483,92 +1480,91 @@
   <dimension ref="A1:BK70"/>
   <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="4" width="10.6640625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
     <col min="6" max="60" width="12.6640625" customWidth="1"/>
     <col min="61" max="61" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="62" max="63" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="74" t="s">
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="75"/>
-      <c r="W1" s="75"/>
-      <c r="X1" s="75"/>
-      <c r="Y1" s="75"/>
-      <c r="Z1" s="75"/>
-      <c r="AA1" s="75"/>
-      <c r="AB1" s="76"/>
-      <c r="AC1" s="87" t="s">
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
+      <c r="Y1" s="76"/>
+      <c r="Z1" s="76"/>
+      <c r="AA1" s="76"/>
+      <c r="AB1" s="77"/>
+      <c r="AC1" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="88"/>
-      <c r="AF1" s="88"/>
-      <c r="AG1" s="88"/>
-      <c r="AH1" s="88"/>
-      <c r="AI1" s="88"/>
-      <c r="AJ1" s="88"/>
-      <c r="AK1" s="88"/>
-      <c r="AL1" s="88"/>
-      <c r="AM1" s="88"/>
-      <c r="AN1" s="88"/>
-      <c r="AO1" s="89"/>
-      <c r="AP1" s="82" t="s">
+      <c r="AD1" s="89"/>
+      <c r="AE1" s="89"/>
+      <c r="AF1" s="89"/>
+      <c r="AG1" s="89"/>
+      <c r="AH1" s="89"/>
+      <c r="AI1" s="89"/>
+      <c r="AJ1" s="89"/>
+      <c r="AK1" s="89"/>
+      <c r="AL1" s="89"/>
+      <c r="AM1" s="89"/>
+      <c r="AN1" s="89"/>
+      <c r="AO1" s="90"/>
+      <c r="AP1" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="AQ1" s="82"/>
-      <c r="AR1" s="82"/>
-      <c r="AS1" s="82"/>
-      <c r="AT1" s="83"/>
-      <c r="AU1" s="84" t="s">
+      <c r="AQ1" s="83"/>
+      <c r="AR1" s="83"/>
+      <c r="AS1" s="83"/>
+      <c r="AT1" s="84"/>
+      <c r="AU1" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="AV1" s="85"/>
-      <c r="AW1" s="86"/>
-      <c r="AX1" s="80" t="s">
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="87"/>
+      <c r="AX1" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="AY1" s="81"/>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
-      <c r="BC1" s="81"/>
-      <c r="BD1" s="81"/>
-      <c r="BE1" s="81"/>
-      <c r="BF1" s="81"/>
-      <c r="BG1" s="81"/>
-      <c r="BH1" s="81"/>
-      <c r="BI1" s="77" t="s">
+      <c r="AY1" s="82"/>
+      <c r="AZ1" s="82"/>
+      <c r="BA1" s="82"/>
+      <c r="BB1" s="82"/>
+      <c r="BC1" s="82"/>
+      <c r="BD1" s="82"/>
+      <c r="BE1" s="82"/>
+      <c r="BF1" s="82"/>
+      <c r="BG1" s="82"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="BJ1" s="78"/>
-      <c r="BK1" s="79"/>
+      <c r="BJ1" s="79"/>
+      <c r="BK1" s="80"/>
     </row>
     <row r="2" spans="1:63" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="33" t="s">
@@ -3926,7 +3922,7 @@
         <v/>
       </c>
       <c r="BE13" s="61">
-        <f t="shared" si="1"/>
+        <f>IF(B13="Julia",AV13*AZ13/24/60,"")</f>
         <v>1.5360990534044473E-2</v>
       </c>
       <c r="BF13" s="58" t="str">
@@ -11358,7 +11354,9 @@
       <c r="D51" s="4">
         <v>9</v>
       </c>
-      <c r="E51" s="5"/>
+      <c r="E51" s="5">
+        <v>45458.332638888889</v>
+      </c>
       <c r="F51" s="4">
         <v>4805.7299999999996</v>
       </c>
@@ -11414,9 +11412,15 @@
       <c r="X51" s="4">
         <v>154.6</v>
       </c>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
+      <c r="Y51" s="4">
+        <v>52.6</v>
+      </c>
+      <c r="Z51" s="4">
+        <v>103.5</v>
+      </c>
+      <c r="AA51" s="4">
+        <v>27.4</v>
+      </c>
       <c r="AB51" s="22">
         <v>7.31</v>
       </c>
@@ -11547,7 +11551,9 @@
       <c r="D52" s="27">
         <v>9</v>
       </c>
-      <c r="E52" s="28"/>
+      <c r="E52" s="28">
+        <v>45458.337500000001</v>
+      </c>
       <c r="F52" s="27">
         <v>4805.7299999999996</v>
       </c>
@@ -11603,9 +11609,15 @@
       <c r="X52" s="35">
         <v>170</v>
       </c>
-      <c r="Y52" s="27"/>
-      <c r="Z52" s="27"/>
-      <c r="AA52" s="27"/>
+      <c r="Y52" s="27">
+        <v>73.2</v>
+      </c>
+      <c r="Z52" s="27">
+        <v>135.30000000000001</v>
+      </c>
+      <c r="AA52" s="27">
+        <v>33.700000000000003</v>
+      </c>
       <c r="AB52" s="2">
         <v>7.3369999999999997</v>
       </c>
@@ -11738,7 +11750,9 @@
       <c r="D53" s="27">
         <v>9</v>
       </c>
-      <c r="E53" s="28"/>
+      <c r="E53" s="28">
+        <v>45458.341666666667</v>
+      </c>
       <c r="F53" s="27">
         <v>4805.7299999999996</v>
       </c>
@@ -11794,9 +11808,15 @@
       <c r="X53" s="35">
         <v>160</v>
       </c>
-      <c r="Y53" s="27"/>
-      <c r="Z53" s="27"/>
-      <c r="AA53" s="27"/>
+      <c r="Y53" s="27">
+        <v>58.2</v>
+      </c>
+      <c r="Z53" s="27">
+        <v>112.9</v>
+      </c>
+      <c r="AA53" s="27">
+        <v>23.5</v>
+      </c>
       <c r="AB53" s="2">
         <v>7.3159999999999998</v>
       </c>
@@ -11929,7 +11949,9 @@
       <c r="D54" s="27">
         <v>9</v>
       </c>
-      <c r="E54" s="28"/>
+      <c r="E54" s="28">
+        <v>45458.34652777778</v>
+      </c>
       <c r="F54" s="27">
         <v>4805.7299999999996</v>
       </c>
@@ -11985,9 +12007,15 @@
       <c r="X54" s="35">
         <v>156.4</v>
       </c>
-      <c r="Y54" s="27"/>
-      <c r="Z54" s="27"/>
-      <c r="AA54" s="27"/>
+      <c r="Y54" s="27">
+        <v>54.9</v>
+      </c>
+      <c r="Z54" s="27">
+        <v>114.9</v>
+      </c>
+      <c r="AA54" s="27">
+        <v>1.6</v>
+      </c>
       <c r="AB54" s="2">
         <v>7.2830000000000004</v>
       </c>
@@ -12122,7 +12150,9 @@
       <c r="D55" s="7">
         <v>9</v>
       </c>
-      <c r="E55" s="8"/>
+      <c r="E55" s="8">
+        <v>45458.35</v>
+      </c>
       <c r="F55" s="7">
         <v>4805.7299999999996</v>
       </c>
@@ -12178,9 +12208,15 @@
       <c r="X55" s="7">
         <v>153.9</v>
       </c>
-      <c r="Y55" s="7"/>
-      <c r="Z55" s="7"/>
-      <c r="AA55" s="7"/>
+      <c r="Y55" s="7">
+        <v>58.1</v>
+      </c>
+      <c r="Z55" s="7">
+        <v>117.2</v>
+      </c>
+      <c r="AA55" s="7">
+        <v>48.2</v>
+      </c>
       <c r="AB55" s="23">
         <v>7.2990000000000004</v>
       </c>
@@ -12315,7 +12351,9 @@
       <c r="D56" s="27">
         <v>10</v>
       </c>
-      <c r="E56" s="28"/>
+      <c r="E56" s="28">
+        <v>45459.436111111114</v>
+      </c>
       <c r="F56">
         <v>5302.42</v>
       </c>
@@ -12371,9 +12409,15 @@
       <c r="X56" s="35">
         <v>158</v>
       </c>
-      <c r="Y56" s="27"/>
-      <c r="Z56" s="27"/>
-      <c r="AA56" s="27"/>
+      <c r="Y56" s="27">
+        <v>55.1</v>
+      </c>
+      <c r="Z56" s="27">
+        <v>110.1</v>
+      </c>
+      <c r="AA56" s="27">
+        <v>15.4</v>
+      </c>
       <c r="AB56" s="2">
         <v>7.3029999999999999</v>
       </c>
@@ -12504,7 +12548,9 @@
       <c r="D57" s="27">
         <v>10</v>
       </c>
-      <c r="E57" s="28"/>
+      <c r="E57" s="28">
+        <v>45459.439583333333</v>
+      </c>
       <c r="F57">
         <v>5302.42</v>
       </c>
@@ -12560,9 +12606,15 @@
       <c r="X57" s="35">
         <v>168.8</v>
       </c>
-      <c r="Y57" s="27"/>
-      <c r="Z57" s="27"/>
-      <c r="AA57" s="27"/>
+      <c r="Y57" s="27">
+        <v>68.5</v>
+      </c>
+      <c r="Z57" s="27">
+        <v>135.1</v>
+      </c>
+      <c r="AA57" s="27">
+        <v>10.5</v>
+      </c>
       <c r="AB57" s="2">
         <v>7.3090000000000002</v>
       </c>
@@ -12620,7 +12672,9 @@
       <c r="AT57" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU57" s="15"/>
+      <c r="AU57" s="15">
+        <v>1.4318923831324701E-2</v>
+      </c>
       <c r="AV57" s="30"/>
       <c r="AW57" s="40"/>
       <c r="AX57" s="15">
@@ -12649,7 +12703,7 @@
       </c>
       <c r="BD57" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.9333480562934345E-2</v>
       </c>
       <c r="BE57" s="61" t="str">
         <f t="shared" si="27"/>
@@ -12669,11 +12723,11 @@
       </c>
       <c r="BI57" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>50.216832630998304</v>
       </c>
       <c r="BJ57" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.9333480562934345E-2</v>
       </c>
       <c r="BK57" s="48">
         <f t="shared" si="12"/>
@@ -12693,7 +12747,9 @@
       <c r="D58" s="27">
         <v>10</v>
       </c>
-      <c r="E58" s="28"/>
+      <c r="E58" s="28">
+        <v>45459.443055555559</v>
+      </c>
       <c r="F58">
         <v>5302.42</v>
       </c>
@@ -12749,9 +12805,15 @@
       <c r="X58" s="35">
         <v>162.6</v>
       </c>
-      <c r="Y58" s="27"/>
-      <c r="Z58" s="27"/>
-      <c r="AA58" s="27"/>
+      <c r="Y58" s="27">
+        <v>55.7</v>
+      </c>
+      <c r="Z58" s="27">
+        <v>113.2</v>
+      </c>
+      <c r="AA58" s="27">
+        <v>0</v>
+      </c>
       <c r="AB58" s="2">
         <v>7.2960000000000003</v>
       </c>
@@ -12809,7 +12871,9 @@
       <c r="AT58" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU58" s="15"/>
+      <c r="AU58" s="15">
+        <v>4.5000220423366396E-3</v>
+      </c>
       <c r="AV58" s="30"/>
       <c r="AW58" s="40"/>
       <c r="AX58" s="15">
@@ -12838,7 +12902,7 @@
       </c>
       <c r="BD58" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>6.0232420034839057E-3</v>
       </c>
       <c r="BE58" s="61" t="str">
         <f t="shared" si="27"/>
@@ -12858,11 +12922,11 @@
       </c>
       <c r="BI58" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>15.644784424633523</v>
       </c>
       <c r="BJ58" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>6.0232420034839057E-3</v>
       </c>
       <c r="BK58" s="48">
         <f t="shared" si="12"/>
@@ -12882,7 +12946,9 @@
       <c r="D59" s="27">
         <v>10</v>
       </c>
-      <c r="E59" s="28"/>
+      <c r="E59" s="28">
+        <v>45459.445833333331</v>
+      </c>
       <c r="F59">
         <v>5302.42</v>
       </c>
@@ -12938,9 +13004,15 @@
       <c r="X59" s="35">
         <v>157.5</v>
       </c>
-      <c r="Y59" s="27"/>
-      <c r="Z59" s="27"/>
-      <c r="AA59" s="27"/>
+      <c r="Y59" s="27">
+        <v>60.9</v>
+      </c>
+      <c r="Z59" s="27">
+        <v>121.7</v>
+      </c>
+      <c r="AA59" s="27">
+        <v>0.8</v>
+      </c>
       <c r="AB59" s="2">
         <v>7.3040000000000003</v>
       </c>
@@ -12999,8 +13071,12 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU59" s="15"/>
-      <c r="AV59" s="30"/>
-      <c r="AW59" s="40"/>
+      <c r="AV59" s="30">
+        <v>1.2829668311332001E-2</v>
+      </c>
+      <c r="AW59" s="40">
+        <v>3.6499622000315899E-3</v>
+      </c>
       <c r="AX59" s="15">
         <f t="shared" si="4"/>
         <v>1.6084882800000002E-2</v>
@@ -13031,7 +13107,7 @@
       </c>
       <c r="BE59" s="61">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1.7060491993274567E-2</v>
       </c>
       <c r="BF59" s="58" t="str">
         <f t="shared" si="35"/>
@@ -13043,19 +13119,19 @@
       </c>
       <c r="BH59" s="31">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6.9891921680878912</v>
       </c>
       <c r="BI59" s="46">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>44.312966216297582</v>
       </c>
       <c r="BJ59" s="66">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.7060491993274567E-2</v>
       </c>
       <c r="BK59" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6.9891921680878912</v>
       </c>
     </row>
     <row r="60" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -13071,7 +13147,9 @@
       <c r="D60" s="27">
         <v>10</v>
       </c>
-      <c r="E60" s="28"/>
+      <c r="E60" s="28">
+        <v>45459.45</v>
+      </c>
       <c r="F60">
         <v>5302.42</v>
       </c>
@@ -13127,9 +13205,15 @@
       <c r="X60" s="35">
         <v>154.5</v>
       </c>
-      <c r="Y60" s="27"/>
-      <c r="Z60" s="27"/>
-      <c r="AA60" s="27"/>
+      <c r="Y60" s="27">
+        <v>57</v>
+      </c>
+      <c r="Z60" s="27">
+        <v>116</v>
+      </c>
+      <c r="AA60" s="27">
+        <v>26.6</v>
+      </c>
       <c r="AB60" s="2">
         <v>7.2949999999999999</v>
       </c>
@@ -13188,8 +13272,12 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU60" s="16"/>
-      <c r="AV60" s="17"/>
-      <c r="AW60" s="41"/>
+      <c r="AV60" s="17">
+        <v>1.28838942426408E-2</v>
+      </c>
+      <c r="AW60" s="41">
+        <v>3.64837557355967E-3</v>
+      </c>
       <c r="AX60" s="16">
         <f t="shared" ref="AX60:AX70" si="41">AT60*J60*AZ60/1000</f>
         <v>1.6467143439999998E-2</v>
@@ -13220,7 +13308,7 @@
       </c>
       <c r="BE60" s="18">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1.7623682097235197E-2</v>
       </c>
       <c r="BF60" s="59" t="str">
         <f t="shared" si="35"/>
@@ -13232,19 +13320,19 @@
       </c>
       <c r="BH60" s="18">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>7.1864023795214536</v>
       </c>
       <c r="BI60" s="47">
         <f t="shared" ref="BI60:BI70" si="43">IF(BD60&lt;&gt;"",BD60/0.000385,IF(BE60&lt;&gt;"",BE60/0.000385,BF60/0.000385))</f>
-        <v>0</v>
+        <v>45.77579765515636</v>
       </c>
       <c r="BJ60" s="67">
         <f t="shared" ref="BJ60:BJ65" si="44">IF(BD60&lt;&gt;"",BD60,IF(BE60&lt;&gt;"",BE60,BF60))</f>
-        <v>0</v>
+        <v>1.7623682097235197E-2</v>
       </c>
       <c r="BK60" s="49">
         <f t="shared" ref="BK60:BK70" si="45">IF(BG60&lt;&gt;"",BG60,BH60)</f>
-        <v>0</v>
+        <v>7.1864023795214536</v>
       </c>
     </row>
     <row r="61" spans="1:63" x14ac:dyDescent="0.3">
@@ -13260,44 +13348,112 @@
       <c r="D61" s="4">
         <v>11</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5">
+        <v>45460.40902777778</v>
+      </c>
       <c r="F61" s="4">
         <v>5791.69</v>
       </c>
       <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="4"/>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
-      <c r="Z61" s="4"/>
-      <c r="AA61" s="4"/>
-      <c r="AB61" s="22"/>
-      <c r="AC61" s="3"/>
-      <c r="AD61" s="4"/>
-      <c r="AE61" s="4"/>
-      <c r="AF61" s="4"/>
-      <c r="AG61" s="4"/>
-      <c r="AH61" s="4"/>
-      <c r="AI61" s="4"/>
+      <c r="H61" s="9">
+        <v>5329.3050000000003</v>
+      </c>
+      <c r="I61" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="J61" s="4">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K61" s="4">
+        <v>92.3</v>
+      </c>
+      <c r="L61" s="4">
+        <v>17</v>
+      </c>
+      <c r="M61" s="4">
+        <v>373</v>
+      </c>
+      <c r="N61" s="4">
+        <v>1.37</v>
+      </c>
+      <c r="O61" s="4">
+        <v>0.17</v>
+      </c>
+      <c r="P61" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="Q61" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="R61" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="S61" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="T61" s="4">
+        <v>7.2679999999999998</v>
+      </c>
+      <c r="U61" s="4">
+        <v>119.3</v>
+      </c>
+      <c r="V61" s="4">
+        <v>33.6</v>
+      </c>
+      <c r="W61" s="4">
+        <v>1.94</v>
+      </c>
+      <c r="X61" s="4">
+        <v>158.69999999999999</v>
+      </c>
+      <c r="Y61" s="4">
+        <v>53.1</v>
+      </c>
+      <c r="Z61" s="4">
+        <v>104.6</v>
+      </c>
+      <c r="AA61" s="4">
+        <v>27.2</v>
+      </c>
+      <c r="AB61" s="22">
+        <v>7.3090000000000002</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>301</v>
+      </c>
+      <c r="AD61" s="4">
+        <v>0.505</v>
+      </c>
+      <c r="AE61" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="AF61" s="4">
+        <v>34</v>
+      </c>
+      <c r="AG61" s="4">
+        <v>31.32</v>
+      </c>
+      <c r="AH61" s="4">
+        <v>87.16</v>
+      </c>
+      <c r="AI61" s="4">
+        <v>10</v>
+      </c>
       <c r="AJ61" s="4"/>
-      <c r="AK61" s="4"/>
-      <c r="AL61" s="4"/>
-      <c r="AM61" s="4"/>
-      <c r="AN61" s="4"/>
+      <c r="AK61" s="4">
+        <v>214</v>
+      </c>
+      <c r="AL61" s="4">
+        <v>46</v>
+      </c>
+      <c r="AM61" s="4">
+        <f t="shared" ref="AM61:AN65" si="46">AK61-AK56</f>
+        <v>20</v>
+      </c>
+      <c r="AN61" s="4">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
       <c r="AO61" s="42">
         <v>15</v>
       </c>
@@ -13321,7 +13477,7 @@
       <c r="AW61" s="39"/>
       <c r="AX61" s="12">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.52233408E-2</v>
       </c>
       <c r="AY61" s="13">
         <f t="shared" si="21"/>
@@ -13329,15 +13485,15 @@
       </c>
       <c r="AZ61" s="13">
         <f t="shared" si="33"/>
-        <v>1524</v>
-      </c>
-      <c r="BA61" s="14" t="e">
+        <v>1912.48</v>
+      </c>
+      <c r="BA61" s="14">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.11189659499707186</v>
       </c>
       <c r="BB61" s="14">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.12588235294117647</v>
       </c>
       <c r="BC61" s="14">
         <f t="shared" si="40"/>
@@ -13353,11 +13509,11 @@
       </c>
       <c r="BF61" s="57">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1.52233408E-2</v>
       </c>
       <c r="BG61" s="14">
         <f t="shared" si="24"/>
-        <v>11.43</v>
+        <v>9.7536480000000001</v>
       </c>
       <c r="BH61" s="14" t="str">
         <f t="shared" si="28"/>
@@ -13365,15 +13521,15 @@
       </c>
       <c r="BI61" s="46">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>39.541144935064935</v>
       </c>
       <c r="BJ61" s="66">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.52233408E-2</v>
       </c>
       <c r="BK61" s="48">
         <f t="shared" si="45"/>
-        <v>11.43</v>
+        <v>9.7536480000000001</v>
       </c>
     </row>
     <row r="62" spans="1:63" x14ac:dyDescent="0.3">
@@ -13389,44 +13545,112 @@
       <c r="D62" s="27">
         <v>11</v>
       </c>
-      <c r="E62" s="28"/>
+      <c r="E62" s="28">
+        <v>45460.412499999999</v>
+      </c>
       <c r="F62" s="27">
         <v>5791.69</v>
       </c>
       <c r="G62" s="29"/>
-      <c r="H62" s="29"/>
-      <c r="I62" s="27"/>
-      <c r="J62" s="27"/>
-      <c r="K62" s="27"/>
-      <c r="L62" s="27"/>
-      <c r="M62" s="27"/>
-      <c r="N62" s="27"/>
-      <c r="O62" s="27"/>
-      <c r="P62" s="27"/>
-      <c r="Q62" s="27"/>
-      <c r="R62" s="27"/>
-      <c r="S62" s="27"/>
-      <c r="T62" s="27"/>
-      <c r="U62" s="27"/>
-      <c r="V62" s="27"/>
-      <c r="W62" s="27"/>
-      <c r="X62" s="27"/>
-      <c r="Y62" s="27"/>
-      <c r="Z62" s="27"/>
-      <c r="AA62" s="27"/>
-      <c r="AB62" s="2"/>
-      <c r="AC62" s="1"/>
-      <c r="AD62" s="27"/>
-      <c r="AE62" s="27"/>
-      <c r="AF62" s="27"/>
-      <c r="AG62" s="27"/>
-      <c r="AH62" s="27"/>
-      <c r="AI62" s="27"/>
+      <c r="H62" s="29">
+        <v>5295.1049999999996</v>
+      </c>
+      <c r="I62" s="27">
+        <v>20.5</v>
+      </c>
+      <c r="J62" s="27">
+        <v>18.5</v>
+      </c>
+      <c r="K62" s="27">
+        <v>90.2</v>
+      </c>
+      <c r="L62" s="27">
+        <v>17.8</v>
+      </c>
+      <c r="M62" s="27">
+        <v>408</v>
+      </c>
+      <c r="N62" s="27">
+        <v>3.31</v>
+      </c>
+      <c r="O62" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="P62" s="27">
+        <v>0.66</v>
+      </c>
+      <c r="Q62" s="27">
+        <v>0.77</v>
+      </c>
+      <c r="R62" s="27">
+        <v>1.44</v>
+      </c>
+      <c r="S62" s="27">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T62" s="27">
+        <v>7.2380000000000004</v>
+      </c>
+      <c r="U62" s="27">
+        <v>159.6</v>
+      </c>
+      <c r="V62" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="W62" s="27">
+        <v>1.37</v>
+      </c>
+      <c r="X62" s="27">
+        <v>168.5</v>
+      </c>
+      <c r="Y62" s="27">
+        <v>66.2</v>
+      </c>
+      <c r="Z62" s="27">
+        <v>139.9</v>
+      </c>
+      <c r="AA62" s="27">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="AB62" s="2">
+        <v>7.2789999999999999</v>
+      </c>
+      <c r="AC62" s="1">
+        <v>299</v>
+      </c>
+      <c r="AD62" s="27">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="AE62" s="27">
+        <v>7.25</v>
+      </c>
+      <c r="AF62" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG62" s="27">
+        <v>33.53</v>
+      </c>
+      <c r="AH62" s="27">
+        <v>14.77</v>
+      </c>
+      <c r="AI62" s="27">
+        <v>7</v>
+      </c>
       <c r="AJ62" s="27"/>
-      <c r="AK62" s="27"/>
-      <c r="AL62" s="27"/>
-      <c r="AM62" s="27"/>
-      <c r="AN62" s="27"/>
+      <c r="AK62" s="30">
+        <v>307</v>
+      </c>
+      <c r="AL62" s="30">
+        <v>83</v>
+      </c>
+      <c r="AM62" s="27">
+        <f t="shared" si="46"/>
+        <v>27</v>
+      </c>
+      <c r="AN62" s="27">
+        <f t="shared" si="46"/>
+        <v>13</v>
+      </c>
       <c r="AO62" s="43">
         <v>15</v>
       </c>
@@ -13445,12 +13669,14 @@
       <c r="AT62" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU62" s="15"/>
+      <c r="AU62" s="15">
+        <v>4.8973844183032599E-2</v>
+      </c>
       <c r="AV62" s="30"/>
       <c r="AW62" s="40"/>
       <c r="AX62" s="15">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.4572820000000002E-2</v>
       </c>
       <c r="AY62" s="30">
         <f t="shared" si="21"/>
@@ -13458,15 +13684,15 @@
       </c>
       <c r="AZ62" s="30">
         <f t="shared" si="33"/>
-        <v>1524</v>
-      </c>
-      <c r="BA62" s="31" t="e">
+        <v>1969.3000000000002</v>
+      </c>
+      <c r="BA62" s="31">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.15589295688823437</v>
       </c>
       <c r="BB62" s="31">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.18058823529411766</v>
       </c>
       <c r="BC62" s="31">
         <f t="shared" si="40"/>
@@ -13474,7 +13700,7 @@
       </c>
       <c r="BD62" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>6.6975132881698693E-2</v>
       </c>
       <c r="BE62" s="61" t="str">
         <f t="shared" si="27"/>
@@ -13486,7 +13712,7 @@
       </c>
       <c r="BG62" s="31">
         <f t="shared" si="24"/>
-        <v>11.43</v>
+        <v>11.520405</v>
       </c>
       <c r="BH62" s="31" t="str">
         <f t="shared" si="28"/>
@@ -13494,15 +13720,15 @@
       </c>
       <c r="BI62" s="46">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>173.96138410830829</v>
       </c>
       <c r="BJ62" s="66">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>6.6975132881698693E-2</v>
       </c>
       <c r="BK62" s="48">
         <f t="shared" si="45"/>
-        <v>11.43</v>
+        <v>11.520405</v>
       </c>
     </row>
     <row r="63" spans="1:63" x14ac:dyDescent="0.3">
@@ -13518,44 +13744,112 @@
       <c r="D63" s="27">
         <v>11</v>
       </c>
-      <c r="E63" s="28"/>
+      <c r="E63" s="28">
+        <v>45460.415972222225</v>
+      </c>
       <c r="F63" s="27">
         <v>5791.69</v>
       </c>
       <c r="G63" s="29"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="27"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-      <c r="N63" s="27"/>
-      <c r="O63" s="27"/>
-      <c r="P63" s="27"/>
-      <c r="Q63" s="27"/>
-      <c r="R63" s="27"/>
-      <c r="S63" s="27"/>
-      <c r="T63" s="27"/>
-      <c r="U63" s="27"/>
-      <c r="V63" s="27"/>
-      <c r="W63" s="27"/>
-      <c r="X63" s="27"/>
-      <c r="Y63" s="27"/>
-      <c r="Z63" s="27"/>
-      <c r="AA63" s="27"/>
-      <c r="AB63" s="2"/>
-      <c r="AC63" s="1"/>
-      <c r="AD63" s="27"/>
-      <c r="AE63" s="27"/>
-      <c r="AF63" s="27"/>
-      <c r="AG63" s="27"/>
-      <c r="AH63" s="27"/>
-      <c r="AI63" s="27"/>
+      <c r="H63" s="29">
+        <v>5504.16</v>
+      </c>
+      <c r="I63" s="27">
+        <v>21.4</v>
+      </c>
+      <c r="J63" s="27">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K63" s="27">
+        <v>93</v>
+      </c>
+      <c r="L63" s="27">
+        <v>18.2</v>
+      </c>
+      <c r="M63" s="27">
+        <v>385</v>
+      </c>
+      <c r="N63" s="27">
+        <v>2.77</v>
+      </c>
+      <c r="O63" s="27">
+        <v>0.19</v>
+      </c>
+      <c r="P63" s="27">
+        <v>0.01</v>
+      </c>
+      <c r="Q63" s="27">
+        <v>0.45</v>
+      </c>
+      <c r="R63" s="27">
+        <v>0.44</v>
+      </c>
+      <c r="S63" s="27">
+        <v>1.24</v>
+      </c>
+      <c r="T63" s="27">
+        <v>7.2690000000000001</v>
+      </c>
+      <c r="U63" s="27">
+        <v>98.8</v>
+      </c>
+      <c r="V63" s="27">
+        <v>31.6</v>
+      </c>
+      <c r="W63" s="27">
+        <v>1.44</v>
+      </c>
+      <c r="X63" s="27">
+        <v>161.19999999999999</v>
+      </c>
+      <c r="Y63" s="27">
+        <v>44.1</v>
+      </c>
+      <c r="Z63" s="27">
+        <v>86.6</v>
+      </c>
+      <c r="AA63" s="27">
+        <v>25.5</v>
+      </c>
+      <c r="AB63" s="2">
+        <v>7.3109999999999999</v>
+      </c>
+      <c r="AC63" s="1">
+        <v>302</v>
+      </c>
+      <c r="AD63" s="27">
+        <v>0.498</v>
+      </c>
+      <c r="AE63" s="27">
+        <v>7.3</v>
+      </c>
+      <c r="AF63" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG63" s="27">
+        <v>27.27</v>
+      </c>
+      <c r="AH63" s="27">
+        <v>20.65</v>
+      </c>
+      <c r="AI63" s="27">
+        <v>8</v>
+      </c>
       <c r="AJ63" s="27"/>
-      <c r="AK63" s="27"/>
-      <c r="AL63" s="27"/>
-      <c r="AM63" s="27"/>
-      <c r="AN63" s="27"/>
+      <c r="AK63" s="30">
+        <v>282</v>
+      </c>
+      <c r="AL63" s="30">
+        <v>79</v>
+      </c>
+      <c r="AM63" s="27">
+        <f t="shared" si="46"/>
+        <v>9</v>
+      </c>
+      <c r="AN63" s="27">
+        <f t="shared" si="46"/>
+        <v>11</v>
+      </c>
       <c r="AO63" s="43">
         <v>15</v>
       </c>
@@ -13574,12 +13868,14 @@
       <c r="AT63" s="30">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AU63" s="15"/>
+      <c r="AU63" s="15">
+        <v>4.4999999999999997E-3</v>
+      </c>
       <c r="AV63" s="30"/>
       <c r="AW63" s="40"/>
       <c r="AX63" s="15">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.5449723200000001E-2</v>
       </c>
       <c r="AY63" s="30">
         <f t="shared" si="21"/>
@@ -13587,15 +13883,15 @@
       </c>
       <c r="AZ63" s="30">
         <f t="shared" si="33"/>
-        <v>1524</v>
-      </c>
-      <c r="BA63" s="31" t="e">
+        <v>1940.92</v>
+      </c>
+      <c r="BA63" s="31">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.14529192341776065</v>
       </c>
       <c r="BB63" s="31">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.16588235294117648</v>
       </c>
       <c r="BC63" s="31">
         <f t="shared" si="40"/>
@@ -13603,7 +13899,7 @@
       </c>
       <c r="BD63" s="31">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>6.0653749999999996E-3</v>
       </c>
       <c r="BE63" s="61" t="str">
         <f t="shared" si="27"/>
@@ -13615,7 +13911,7 @@
       </c>
       <c r="BG63" s="31">
         <f t="shared" si="24"/>
-        <v>11.43</v>
+        <v>14.508377000000003</v>
       </c>
       <c r="BH63" s="31" t="str">
         <f t="shared" si="28"/>
@@ -13623,15 +13919,15 @@
       </c>
       <c r="BI63" s="46">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>15.754220779220779</v>
       </c>
       <c r="BJ63" s="66">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>6.0653749999999996E-3</v>
       </c>
       <c r="BK63" s="48">
         <f t="shared" si="45"/>
-        <v>11.43</v>
+        <v>14.508377000000003</v>
       </c>
     </row>
     <row r="64" spans="1:63" x14ac:dyDescent="0.3">
@@ -13647,44 +13943,110 @@
       <c r="D64" s="27">
         <v>11</v>
       </c>
-      <c r="E64" s="28"/>
+      <c r="E64" s="28">
+        <v>45460.420138888891</v>
+      </c>
       <c r="F64" s="27">
         <v>5791.69</v>
       </c>
       <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
+      <c r="H64" s="29">
+        <v>5804.2049999999999</v>
+      </c>
+      <c r="I64" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="J64" s="27">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K64" s="27">
+        <v>90.1</v>
+      </c>
+      <c r="L64" s="27">
+        <v>17.2</v>
+      </c>
       <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="27"/>
-      <c r="V64" s="27"/>
-      <c r="W64" s="27"/>
-      <c r="X64" s="27"/>
-      <c r="Y64" s="27"/>
-      <c r="Z64" s="27"/>
-      <c r="AA64" s="27"/>
-      <c r="AB64" s="2"/>
-      <c r="AC64" s="1"/>
-      <c r="AD64" s="27"/>
-      <c r="AE64" s="27"/>
-      <c r="AF64" s="27"/>
-      <c r="AG64" s="27"/>
-      <c r="AH64" s="27"/>
-      <c r="AI64" s="27"/>
+      <c r="N64" s="27">
+        <v>3.99</v>
+      </c>
+      <c r="O64" s="27">
+        <v>0.19</v>
+      </c>
+      <c r="P64" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="Q64" s="27">
+        <v>0.53</v>
+      </c>
+      <c r="R64" s="27">
+        <v>0.99</v>
+      </c>
+      <c r="S64" s="27">
+        <v>0.21</v>
+      </c>
+      <c r="T64" s="27">
+        <v>7.2629999999999999</v>
+      </c>
+      <c r="U64" s="27">
+        <v>126</v>
+      </c>
+      <c r="V64" s="27">
+        <v>25</v>
+      </c>
+      <c r="W64" s="27">
+        <v>1.76</v>
+      </c>
+      <c r="X64" s="27">
+        <v>157.5</v>
+      </c>
+      <c r="Y64" s="27">
+        <v>55.4</v>
+      </c>
+      <c r="Z64" s="27">
+        <v>110.5</v>
+      </c>
+      <c r="AA64" s="27">
+        <v>20.2</v>
+      </c>
+      <c r="AB64" s="2">
+        <v>7.3040000000000003</v>
+      </c>
+      <c r="AC64" s="1">
+        <v>300</v>
+      </c>
+      <c r="AD64" s="27">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="AE64" s="27">
+        <v>7.3</v>
+      </c>
+      <c r="AF64" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG64" s="27">
+        <v>24.77</v>
+      </c>
+      <c r="AH64" s="27">
+        <v>19.440000000000001</v>
+      </c>
+      <c r="AI64" s="27">
+        <v>17</v>
+      </c>
       <c r="AJ64" s="27"/>
-      <c r="AK64" s="27"/>
-      <c r="AL64" s="27"/>
-      <c r="AM64" s="27"/>
-      <c r="AN64" s="27"/>
+      <c r="AK64" s="30">
+        <v>286</v>
+      </c>
+      <c r="AL64" s="30">
+        <v>67</v>
+      </c>
+      <c r="AM64" s="27">
+        <f t="shared" si="46"/>
+        <v>24</v>
+      </c>
+      <c r="AN64" s="27">
+        <f t="shared" si="46"/>
+        <v>8</v>
+      </c>
       <c r="AO64" s="43">
         <v>15</v>
       </c>
@@ -13704,11 +14066,15 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU64" s="15"/>
-      <c r="AV64" s="30"/>
-      <c r="AW64" s="40"/>
+      <c r="AV64">
+        <v>1.4055242069891999E-2</v>
+      </c>
+      <c r="AW64">
+        <v>3.0181124836795399E-3</v>
+      </c>
       <c r="AX64" s="15">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.54281516E-2</v>
       </c>
       <c r="AY64" s="30">
         <f t="shared" si="21"/>
@@ -13716,15 +14082,15 @@
       </c>
       <c r="AZ64" s="30">
         <f t="shared" si="33"/>
-        <v>1524</v>
-      </c>
-      <c r="BA64" s="31" t="e">
+        <v>1938.21</v>
+      </c>
+      <c r="BA64" s="31">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.14755883005453485</v>
       </c>
       <c r="BB64" s="31">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.16823529411764707</v>
       </c>
       <c r="BC64" s="31">
         <f t="shared" si="40"/>
@@ -13736,7 +14102,7 @@
       </c>
       <c r="BE64" s="61">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1.8918063008531508E-2</v>
       </c>
       <c r="BF64" s="58" t="str">
         <f t="shared" si="35"/>
@@ -13748,19 +14114,19 @@
       </c>
       <c r="BH64" s="31">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>5.8497357969925208</v>
       </c>
       <c r="BI64" s="46">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>49.13782599618574</v>
       </c>
       <c r="BJ64" s="66">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1.8918063008531508E-2</v>
       </c>
       <c r="BK64" s="48">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>5.8497357969925208</v>
       </c>
     </row>
     <row r="65" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -13776,44 +14142,112 @@
       <c r="D65" s="7">
         <v>11</v>
       </c>
-      <c r="E65" s="8"/>
+      <c r="E65" s="8">
+        <v>45460.424305555556</v>
+      </c>
       <c r="F65" s="7">
         <v>5791.69</v>
       </c>
       <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="7"/>
-      <c r="K65" s="7"/>
-      <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
-      <c r="N65" s="7"/>
-      <c r="O65" s="7"/>
-      <c r="P65" s="7"/>
-      <c r="Q65" s="7"/>
-      <c r="R65" s="7"/>
-      <c r="S65" s="7"/>
-      <c r="T65" s="7"/>
-      <c r="U65" s="7"/>
-      <c r="V65" s="7"/>
-      <c r="W65" s="7"/>
-      <c r="X65" s="7"/>
-      <c r="Y65" s="7"/>
-      <c r="Z65" s="7"/>
-      <c r="AA65" s="7"/>
-      <c r="AB65" s="23"/>
-      <c r="AC65" s="6"/>
-      <c r="AD65" s="7"/>
-      <c r="AE65" s="7"/>
-      <c r="AF65" s="7"/>
-      <c r="AG65" s="7"/>
-      <c r="AH65" s="7"/>
-      <c r="AI65" s="7"/>
+      <c r="H65" s="11">
+        <v>6174.7049999999999</v>
+      </c>
+      <c r="I65" s="7">
+        <v>22.7</v>
+      </c>
+      <c r="J65" s="7">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="K65" s="7">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="L65" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="M65" s="7">
+        <v>359</v>
+      </c>
+      <c r="N65" s="7">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O65" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="P65" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="Q65" s="7">
+        <v>0.47</v>
+      </c>
+      <c r="R65" s="7">
+        <v>0.92</v>
+      </c>
+      <c r="S65" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="T65" s="7">
+        <v>7.2549999999999999</v>
+      </c>
+      <c r="U65" s="7">
+        <v>122</v>
+      </c>
+      <c r="V65" s="7">
+        <v>43.8</v>
+      </c>
+      <c r="W65" s="7">
+        <v>2.17</v>
+      </c>
+      <c r="X65" s="7">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="Y65" s="7">
+        <v>52.6</v>
+      </c>
+      <c r="Z65" s="7">
+        <v>107</v>
+      </c>
+      <c r="AA65" s="7">
+        <v>35.4</v>
+      </c>
+      <c r="AB65" s="23">
+        <v>7.2960000000000003</v>
+      </c>
+      <c r="AC65" s="6">
+        <v>302</v>
+      </c>
+      <c r="AD65" s="7">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="AE65" s="7">
+        <v>7.3</v>
+      </c>
+      <c r="AF65" s="7">
+        <v>34</v>
+      </c>
+      <c r="AG65" s="7">
+        <v>21.77</v>
+      </c>
+      <c r="AH65" s="7">
+        <v>64.349999999999994</v>
+      </c>
+      <c r="AI65" s="7">
+        <v>17</v>
+      </c>
       <c r="AJ65" s="7"/>
-      <c r="AK65" s="7"/>
-      <c r="AL65" s="7"/>
-      <c r="AM65" s="7"/>
-      <c r="AN65" s="7"/>
+      <c r="AK65" s="7">
+        <v>287</v>
+      </c>
+      <c r="AL65" s="7">
+        <v>82</v>
+      </c>
+      <c r="AM65" s="7">
+        <f t="shared" si="46"/>
+        <v>25</v>
+      </c>
+      <c r="AN65" s="7">
+        <f t="shared" si="46"/>
+        <v>8</v>
+      </c>
       <c r="AO65" s="44">
         <v>15</v>
       </c>
@@ -13833,11 +14267,15 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AU65" s="16"/>
-      <c r="AV65" s="17"/>
-      <c r="AW65" s="41"/>
+      <c r="AV65">
+        <v>2E-3</v>
+      </c>
+      <c r="AW65" s="73">
+        <v>9.9999999999999995E-8</v>
+      </c>
       <c r="AX65" s="16">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.4851132800000002E-2</v>
       </c>
       <c r="AY65" s="17">
         <f t="shared" si="21"/>
@@ -13845,15 +14283,15 @@
       </c>
       <c r="AZ65" s="17">
         <f t="shared" si="33"/>
-        <v>1524</v>
-      </c>
-      <c r="BA65" s="18" t="e">
+        <v>1996.12</v>
+      </c>
+      <c r="BA65" s="18">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.14377893112638521</v>
       </c>
       <c r="BB65" s="18">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.16882352941176471</v>
       </c>
       <c r="BC65" s="18">
         <f t="shared" si="40"/>
@@ -13865,7 +14303,7 @@
       </c>
       <c r="BE65" s="18">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2.7723888888888885E-3</v>
       </c>
       <c r="BF65" s="59" t="str">
         <f t="shared" si="35"/>
@@ -13877,19 +14315,19 @@
       </c>
       <c r="BH65" s="18">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.9961199999999997E-4</v>
       </c>
       <c r="BI65" s="46">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>7.2010101010101</v>
       </c>
       <c r="BJ65" s="66">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>2.7723888888888885E-3</v>
       </c>
       <c r="BK65" s="48">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1.9961199999999997E-4</v>
       </c>
     </row>
     <row r="66" spans="1:63" x14ac:dyDescent="0.3">
@@ -13970,7 +14408,7 @@
       </c>
       <c r="AY66" s="13">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.36536017920000002</v>
       </c>
       <c r="AZ66" s="13">
         <f t="shared" si="33"/>
@@ -14096,7 +14534,7 @@
       </c>
       <c r="AY67" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.34974768000000006</v>
       </c>
       <c r="AZ67" s="30">
         <f t="shared" si="33"/>
@@ -14222,7 +14660,7 @@
       </c>
       <c r="AY68" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.37079335680000003</v>
       </c>
       <c r="AZ68" s="30">
         <f t="shared" si="33"/>
@@ -14348,7 +14786,7 @@
       </c>
       <c r="AY69" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.3702756384</v>
       </c>
       <c r="AZ69" s="30">
         <f t="shared" si="33"/>
@@ -14474,7 +14912,7 @@
       </c>
       <c r="AY70" s="17">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.35642718720000005</v>
       </c>
       <c r="AZ70" s="17">
         <f t="shared" si="33"/>
@@ -14582,6 +15020,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -14804,33 +15251,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14847,12 +15293,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2144" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2A7BC4C-98A7-4AA2-B124-906AA79E201D}"/>
+  <xr:revisionPtr revIDLastSave="2145" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D997BDB0-55D6-4299-A5B3-42665B8E2533}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -14348,7 +14348,9 @@
         <v>6120</v>
       </c>
       <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
+      <c r="H66" s="4">
+        <v>5751.09</v>
+      </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
@@ -14474,7 +14476,9 @@
         <v>6120</v>
       </c>
       <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
+      <c r="H67" s="27">
+        <v>5470.3950000000004</v>
+      </c>
       <c r="I67" s="27"/>
       <c r="J67" s="27"/>
       <c r="K67" s="27"/>
@@ -14600,7 +14604,9 @@
         <v>6120</v>
       </c>
       <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
+      <c r="H68" s="27">
+        <v>5767.0649999999996</v>
+      </c>
       <c r="I68" s="27"/>
       <c r="J68" s="27"/>
       <c r="K68" s="27"/>
@@ -14726,7 +14732,9 @@
         <v>6120</v>
       </c>
       <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
+      <c r="H69" s="27">
+        <v>5949.0450000000001</v>
+      </c>
       <c r="I69" s="27"/>
       <c r="J69" s="27"/>
       <c r="K69" s="27"/>
@@ -14852,7 +14860,9 @@
         <v>6120</v>
       </c>
       <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
+      <c r="H70" s="7">
+        <v>6160.4250000000002</v>
+      </c>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
@@ -15002,33 +15012,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -15251,32 +15234,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15293,4 +15278,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
+++ b/data/MR24-030 Experiment/MR24-030-MasterDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-030-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2145" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D997BDB0-55D6-4299-A5B3-42665B8E2533}"/>
+  <xr:revisionPtr revIDLastSave="2166" documentId="8_{2425AED5-2B3D-4BFD-84B8-542313010F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62FE98CD-365A-49A1-A0B0-CB948C804BE8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14343,7 +14343,9 @@
       <c r="D66" s="4">
         <v>12</v>
       </c>
-      <c r="E66" s="5"/>
+      <c r="E66" s="5">
+        <v>45461.388900462996</v>
+      </c>
       <c r="F66" s="4">
         <v>6120</v>
       </c>
@@ -14351,38 +14353,102 @@
       <c r="H66" s="4">
         <v>5751.09</v>
       </c>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
-      <c r="Z66" s="4"/>
-      <c r="AA66" s="4"/>
-      <c r="AB66" s="22"/>
-      <c r="AC66" s="3"/>
-      <c r="AD66" s="4"/>
-      <c r="AE66" s="4"/>
-      <c r="AF66" s="4"/>
-      <c r="AG66" s="4"/>
-      <c r="AH66" s="4"/>
-      <c r="AI66" s="4"/>
+      <c r="I66" s="4">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="J66" s="4">
+        <v>17.8</v>
+      </c>
+      <c r="K66" s="4">
+        <v>91.8</v>
+      </c>
+      <c r="L66" s="4">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="M66" s="4">
+        <v>377</v>
+      </c>
+      <c r="N66" s="4">
+        <v>1.46</v>
+      </c>
+      <c r="O66" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="P66" s="4">
+        <v>2.34</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>0.17</v>
+      </c>
+      <c r="R66" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="S66" s="4">
+        <v>0.46</v>
+      </c>
+      <c r="T66" s="4">
+        <v>7.2709999999999999</v>
+      </c>
+      <c r="U66" s="4">
+        <v>119.8</v>
+      </c>
+      <c r="V66" s="4">
+        <v>33.5</v>
+      </c>
+      <c r="W66" s="4">
+        <v>1.95</v>
+      </c>
+      <c r="X66" s="4">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="Y66" s="4">
+        <v>53.8</v>
+      </c>
+      <c r="Z66" s="4">
+        <v>105.1</v>
+      </c>
+      <c r="AA66" s="4">
+        <v>27.1</v>
+      </c>
+      <c r="AB66" s="22">
+        <v>7.3129999999999997</v>
+      </c>
+      <c r="AC66" s="3">
+        <v>299</v>
+      </c>
+      <c r="AD66" s="4">
+        <v>50.1</v>
+      </c>
+      <c r="AE66" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="AF66" s="4">
+        <v>34</v>
+      </c>
+      <c r="AG66" s="4">
+        <v>31.32</v>
+      </c>
+      <c r="AH66" s="4">
+        <v>91.54</v>
+      </c>
+      <c r="AI66" s="4">
+        <v>13</v>
+      </c>
       <c r="AJ66" s="4"/>
-      <c r="AK66" s="4"/>
-      <c r="AL66" s="4"/>
-      <c r="AM66" s="4"/>
-      <c r="AN66" s="4"/>
+      <c r="AK66" s="4">
+        <v>236</v>
+      </c>
+      <c r="AL66" s="4">
+        <v>57</v>
+      </c>
+      <c r="AM66" s="4">
+        <f t="shared" ref="AM66:AM70" si="47">AK66-AK61</f>
+        <v>22</v>
+      </c>
+      <c r="AN66" s="4">
+        <f t="shared" ref="AN66:AN70" si="48">AL66-AL61</f>
+        <v>11</v>
+      </c>
       <c r="AO66" s="42">
         <v>15</v>
       </c>
@@ -14406,7 +14472,7 @@
       <c r="AW66" s="22"/>
       <c r="AX66" s="12">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.3790443200000002E-2</v>
       </c>
       <c r="AY66" s="13">
         <f t="shared" si="21"/>
@@ -14414,15 +14480,15 @@
       </c>
       <c r="AZ66" s="13">
         <f t="shared" si="33"/>
-        <v>1508</v>
-      </c>
-      <c r="BA66" s="14" t="e">
+        <v>1936.8600000000001</v>
+      </c>
+      <c r="BA66" s="14">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.12184670032939912</v>
       </c>
       <c r="BB66" s="14">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.13882352941176471</v>
       </c>
       <c r="BC66" s="14">
         <f t="shared" si="40"/>
@@ -14438,11 +14504,11 @@
       </c>
       <c r="BF66" s="57">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1.3790443200000002E-2</v>
       </c>
       <c r="BG66" s="14">
         <f t="shared" si="24"/>
-        <v>11.31</v>
+        <v>0</v>
       </c>
       <c r="BH66" s="14" t="str">
         <f t="shared" si="28"/>
@@ -14450,12 +14516,12 @@
       </c>
       <c r="BI66" s="45">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>35.819332987012992</v>
       </c>
       <c r="BJ66" s="62"/>
       <c r="BK66" s="50">
         <f t="shared" si="45"/>
-        <v>11.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:63" x14ac:dyDescent="0.3">
@@ -14471,7 +14537,9 @@
       <c r="D67" s="27">
         <v>12</v>
       </c>
-      <c r="E67" s="28"/>
+      <c r="E67" s="28">
+        <v>45461.392164351899</v>
+      </c>
       <c r="F67" s="27">
         <v>6120</v>
       </c>
@@ -14479,38 +14547,102 @@
       <c r="H67" s="27">
         <v>5470.3950000000004</v>
       </c>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
-      <c r="S67" s="27"/>
-      <c r="T67" s="27"/>
-      <c r="U67" s="27"/>
-      <c r="V67" s="27"/>
-      <c r="W67" s="27"/>
-      <c r="X67" s="27"/>
-      <c r="Y67" s="27"/>
-      <c r="Z67" s="27"/>
-      <c r="AA67" s="27"/>
-      <c r="AB67" s="2"/>
-      <c r="AC67" s="1"/>
-      <c r="AD67" s="27"/>
-      <c r="AE67" s="27"/>
-      <c r="AF67" s="27"/>
-      <c r="AG67" s="27"/>
-      <c r="AH67" s="27"/>
-      <c r="AI67" s="27"/>
+      <c r="I67" s="27">
+        <v>21</v>
+      </c>
+      <c r="J67" s="27">
+        <v>18.8</v>
+      </c>
+      <c r="K67" s="27">
+        <v>89.6</v>
+      </c>
+      <c r="L67" s="27">
+        <v>17.8</v>
+      </c>
+      <c r="M67" s="27">
+        <v>470</v>
+      </c>
+      <c r="N67" s="27">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="O67" s="27">
+        <v>0.19</v>
+      </c>
+      <c r="P67" s="27">
+        <v>5.85</v>
+      </c>
+      <c r="Q67" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="R67" s="27">
+        <v>4.05</v>
+      </c>
+      <c r="S67" s="27">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="T67" s="27">
+        <v>7.08</v>
+      </c>
+      <c r="U67" s="27">
+        <v>160.19999999999999</v>
+      </c>
+      <c r="V67" s="27">
+        <v>28.2</v>
+      </c>
+      <c r="W67" s="27">
+        <v>1.33</v>
+      </c>
+      <c r="X67" s="27">
+        <v>171.2</v>
+      </c>
+      <c r="Y67" s="27">
+        <v>45.9</v>
+      </c>
+      <c r="Z67" s="27">
+        <v>140.5</v>
+      </c>
+      <c r="AA67" s="27">
+        <v>22.8</v>
+      </c>
+      <c r="AB67" s="2">
+        <v>7.1180000000000003</v>
+      </c>
+      <c r="AC67" s="1">
+        <v>300</v>
+      </c>
+      <c r="AD67" s="27">
+        <v>50.8</v>
+      </c>
+      <c r="AE67" s="27">
+        <v>7.12</v>
+      </c>
+      <c r="AF67" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG67" s="27">
+        <v>33.53</v>
+      </c>
+      <c r="AH67" s="27">
+        <v>14.77</v>
+      </c>
+      <c r="AI67" s="27">
+        <v>12</v>
+      </c>
       <c r="AJ67" s="27"/>
-      <c r="AK67" s="27"/>
-      <c r="AL67" s="27"/>
-      <c r="AM67" s="27"/>
-      <c r="AN67" s="27"/>
+      <c r="AK67" s="72">
+        <v>389</v>
+      </c>
+      <c r="AL67" s="72">
+        <v>95</v>
+      </c>
+      <c r="AM67" s="27">
+        <f t="shared" si="47"/>
+        <v>82</v>
+      </c>
+      <c r="AN67" s="27">
+        <f t="shared" si="48"/>
+        <v>12</v>
+      </c>
       <c r="AO67" s="43">
         <v>15</v>
       </c>
@@ -14534,7 +14666,7 @@
       <c r="AW67" s="2"/>
       <c r="AX67" s="15">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.5433296000000003E-2</v>
       </c>
       <c r="AY67" s="30">
         <f t="shared" si="21"/>
@@ -14542,15 +14674,15 @@
       </c>
       <c r="AZ67" s="30">
         <f t="shared" si="33"/>
-        <v>1508</v>
-      </c>
-      <c r="BA67" s="31" t="e">
+        <v>2052.3000000000002</v>
+      </c>
+      <c r="BA67" s="31">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.1895434390683623</v>
       </c>
       <c r="BB67" s="31">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.2288235294117647</v>
       </c>
       <c r="BC67" s="31">
         <f t="shared" si="40"/>
@@ -14570,7 +14702,7 @@
       </c>
       <c r="BG67" s="31">
         <f t="shared" si="24"/>
-        <v>11.31</v>
+        <v>0</v>
       </c>
       <c r="BH67" s="31" t="str">
         <f t="shared" si="28"/>
@@ -14583,7 +14715,7 @@
       <c r="BJ67" s="63"/>
       <c r="BK67" s="48">
         <f t="shared" si="45"/>
-        <v>11.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:63" x14ac:dyDescent="0.3">
@@ -14599,7 +14731,9 @@
       <c r="D68" s="27">
         <v>12</v>
       </c>
-      <c r="E68" s="28"/>
+      <c r="E68" s="28">
+        <v>45461.395752314798</v>
+      </c>
       <c r="F68" s="27">
         <v>6120</v>
       </c>
@@ -14607,38 +14741,102 @@
       <c r="H68" s="27">
         <v>5767.0649999999996</v>
       </c>
-      <c r="I68" s="27"/>
-      <c r="J68" s="27"/>
-      <c r="K68" s="27"/>
-      <c r="L68" s="27"/>
-      <c r="M68" s="27"/>
-      <c r="N68" s="27"/>
-      <c r="O68" s="27"/>
-      <c r="P68" s="27"/>
-      <c r="Q68" s="27"/>
-      <c r="R68" s="27"/>
-      <c r="S68" s="27"/>
-      <c r="T68" s="27"/>
-      <c r="U68" s="27"/>
-      <c r="V68" s="27"/>
-      <c r="W68" s="27"/>
-      <c r="X68" s="27"/>
-      <c r="Y68" s="27"/>
-      <c r="Z68" s="27"/>
-      <c r="AA68" s="27"/>
-      <c r="AB68" s="2"/>
-      <c r="AC68" s="1"/>
-      <c r="AD68" s="27"/>
-      <c r="AE68" s="27"/>
-      <c r="AF68" s="27"/>
-      <c r="AG68" s="27"/>
-      <c r="AH68" s="27"/>
-      <c r="AI68" s="27"/>
+      <c r="I68" s="27">
+        <v>20.8</v>
+      </c>
+      <c r="J68" s="27">
+        <v>18.8</v>
+      </c>
+      <c r="K68" s="27">
+        <v>90.6</v>
+      </c>
+      <c r="L68" s="27">
+        <v>18</v>
+      </c>
+      <c r="M68" s="27">
+        <v>386</v>
+      </c>
+      <c r="N68" s="27">
+        <v>2.93</v>
+      </c>
+      <c r="O68" s="27">
+        <v>0.18</v>
+      </c>
+      <c r="P68" s="27">
+        <v>0.49</v>
+      </c>
+      <c r="Q68" s="27">
+        <v>0.43</v>
+      </c>
+      <c r="R68" s="27">
+        <v>0.34</v>
+      </c>
+      <c r="S68" s="27">
+        <v>0.59</v>
+      </c>
+      <c r="T68" s="27">
+        <v>7.2759999999999998</v>
+      </c>
+      <c r="U68" s="27">
+        <v>118.2</v>
+      </c>
+      <c r="V68" s="27">
+        <v>22.8</v>
+      </c>
+      <c r="W68" s="27">
+        <v>1.54</v>
+      </c>
+      <c r="X68" s="27">
+        <v>162.80000000000001</v>
+      </c>
+      <c r="Y68" s="27">
+        <v>53.6</v>
+      </c>
+      <c r="Z68" s="27">
+        <v>103.6</v>
+      </c>
+      <c r="AA68" s="27">
+        <v>18.5</v>
+      </c>
+      <c r="AB68" s="2">
+        <v>7.3179999999999996</v>
+      </c>
+      <c r="AC68" s="1">
+        <v>302</v>
+      </c>
+      <c r="AD68" s="27">
+        <v>49.1</v>
+      </c>
+      <c r="AE68" s="27">
+        <v>7.3</v>
+      </c>
+      <c r="AF68" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG68" s="27">
+        <v>27.27</v>
+      </c>
+      <c r="AH68" s="27">
+        <v>24.9</v>
+      </c>
+      <c r="AI68" s="27">
+        <v>9</v>
+      </c>
       <c r="AJ68" s="27"/>
-      <c r="AK68" s="27"/>
-      <c r="AL68" s="27"/>
-      <c r="AM68" s="27"/>
-      <c r="AN68" s="27"/>
+      <c r="AK68" s="72">
+        <v>291</v>
+      </c>
+      <c r="AL68" s="72">
+        <v>95</v>
+      </c>
+      <c r="AM68" s="27">
+        <f t="shared" si="47"/>
+        <v>9</v>
+      </c>
+      <c r="AN68" s="27">
+        <f t="shared" si="48"/>
+        <v>16</v>
+      </c>
       <c r="AO68" s="43">
         <v>15</v>
       </c>
@@ -14662,7 +14860,7 @@
       <c r="AW68" s="40"/>
       <c r="AX68" s="15">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.4702878400000001E-2</v>
       </c>
       <c r="AY68" s="30">
         <f t="shared" si="21"/>
@@ -14670,15 +14868,15 @@
       </c>
       <c r="AZ68" s="30">
         <f t="shared" si="33"/>
-        <v>1508</v>
-      </c>
-      <c r="BA68" s="31" t="e">
+        <v>1955.17</v>
+      </c>
+      <c r="BA68" s="31">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.14883616258432769</v>
       </c>
       <c r="BB68" s="31">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.17117647058823529</v>
       </c>
       <c r="BC68" s="31">
         <f t="shared" si="40"/>
@@ -14698,7 +14896,7 @@
       </c>
       <c r="BG68" s="31">
         <f t="shared" si="24"/>
-        <v>11.31</v>
+        <v>12.26869175</v>
       </c>
       <c r="BH68" s="31" t="str">
         <f t="shared" si="28"/>
@@ -14711,7 +14909,7 @@
       <c r="BJ68" s="63"/>
       <c r="BK68" s="48">
         <f t="shared" si="45"/>
-        <v>11.31</v>
+        <v>12.26869175</v>
       </c>
     </row>
     <row r="69" spans="1:63" x14ac:dyDescent="0.3">
@@ -14727,7 +14925,9 @@
       <c r="D69" s="27">
         <v>12</v>
       </c>
-      <c r="E69" s="28"/>
+      <c r="E69" s="28">
+        <v>45461.399386574099</v>
+      </c>
       <c r="F69" s="27">
         <v>6120</v>
       </c>
@@ -14735,38 +14935,102 @@
       <c r="H69" s="27">
         <v>5949.0450000000001</v>
       </c>
-      <c r="I69" s="27"/>
-      <c r="J69" s="27"/>
-      <c r="K69" s="27"/>
-      <c r="L69" s="27"/>
-      <c r="M69" s="27"/>
-      <c r="N69" s="27"/>
-      <c r="O69" s="27"/>
-      <c r="P69" s="27"/>
-      <c r="Q69" s="27"/>
-      <c r="R69" s="27"/>
-      <c r="S69" s="27"/>
-      <c r="T69" s="27"/>
-      <c r="U69" s="27"/>
-      <c r="V69" s="27"/>
-      <c r="W69" s="27"/>
-      <c r="X69" s="27"/>
-      <c r="Y69" s="27"/>
-      <c r="Z69" s="27"/>
-      <c r="AA69" s="27"/>
-      <c r="AB69" s="2"/>
-      <c r="AC69" s="1"/>
-      <c r="AD69" s="27"/>
-      <c r="AE69" s="27"/>
-      <c r="AF69" s="27"/>
-      <c r="AG69" s="27"/>
-      <c r="AH69" s="27"/>
-      <c r="AI69" s="27"/>
+      <c r="I69" s="27">
+        <v>22</v>
+      </c>
+      <c r="J69" s="27">
+        <v>18.7</v>
+      </c>
+      <c r="K69" s="27">
+        <v>85</v>
+      </c>
+      <c r="L69" s="27">
+        <v>17</v>
+      </c>
+      <c r="M69" s="27">
+        <v>374</v>
+      </c>
+      <c r="N69" s="27">
+        <v>4.28</v>
+      </c>
+      <c r="O69" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="P69" s="27">
+        <v>0.11</v>
+      </c>
+      <c r="Q69" s="27">
+        <v>0.74</v>
+      </c>
+      <c r="R69" s="27">
+        <v>1.68</v>
+      </c>
+      <c r="S69" s="27">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="T69" s="27">
+        <v>7.2530000000000001</v>
+      </c>
+      <c r="U69" s="27">
+        <v>122.9</v>
+      </c>
+      <c r="V69" s="27">
+        <v>24.7</v>
+      </c>
+      <c r="W69" s="27">
+        <v>1.9</v>
+      </c>
+      <c r="X69" s="27">
+        <v>157.69999999999999</v>
+      </c>
+      <c r="Y69" s="27">
+        <v>52.9</v>
+      </c>
+      <c r="Z69" s="27">
+        <v>107.8</v>
+      </c>
+      <c r="AA69" s="27">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AB69" s="2">
+        <v>7.2949999999999999</v>
+      </c>
+      <c r="AC69" s="1">
+        <v>301</v>
+      </c>
+      <c r="AD69" s="27">
+        <v>49.7</v>
+      </c>
+      <c r="AE69" s="27">
+        <v>7.3</v>
+      </c>
+      <c r="AF69" s="27">
+        <v>34</v>
+      </c>
+      <c r="AG69" s="27">
+        <v>24.77</v>
+      </c>
+      <c r="AH69" s="27">
+        <v>23.2</v>
+      </c>
+      <c r="AI69" s="27">
+        <v>22</v>
+      </c>
       <c r="AJ69" s="27"/>
-      <c r="AK69" s="27"/>
-      <c r="AL69" s="27"/>
-      <c r="AM69" s="27"/>
-      <c r="AN69" s="27"/>
+      <c r="AK69" s="72">
+        <v>312</v>
+      </c>
+      <c r="AL69" s="72">
+        <v>74</v>
+      </c>
+      <c r="AM69" s="27">
+        <f t="shared" si="47"/>
+        <v>26</v>
+      </c>
+      <c r="AN69" s="27">
+        <f t="shared" si="48"/>
+        <v>7</v>
+      </c>
       <c r="AO69" s="43">
         <v>15</v>
       </c>
@@ -14790,7 +15054,7 @@
       <c r="AW69" s="40"/>
       <c r="AX69" s="15">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.4690495600000002E-2</v>
       </c>
       <c r="AY69" s="30">
         <f t="shared" si="21"/>
@@ -14798,15 +15062,15 @@
       </c>
       <c r="AZ69" s="30">
         <f t="shared" si="33"/>
-        <v>1508</v>
-      </c>
-      <c r="BA69" s="31" t="e">
+        <v>1963.9700000000003</v>
+      </c>
+      <c r="BA69" s="31">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.15886189707582091</v>
       </c>
       <c r="BB69" s="31">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.18352941176470589</v>
       </c>
       <c r="BC69" s="31">
         <f t="shared" si="40"/>
@@ -14855,7 +15119,9 @@
       <c r="D70" s="7">
         <v>12</v>
       </c>
-      <c r="E70" s="8"/>
+      <c r="E70" s="8">
+        <v>45461.402337963002</v>
+      </c>
       <c r="F70" s="7">
         <v>6120</v>
       </c>
@@ -14863,38 +15129,102 @@
       <c r="H70" s="7">
         <v>6160.4250000000002</v>
       </c>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="7"/>
-      <c r="O70" s="7"/>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="7"/>
-      <c r="R70" s="7"/>
-      <c r="S70" s="7"/>
-      <c r="T70" s="7"/>
-      <c r="U70" s="7"/>
-      <c r="V70" s="7"/>
-      <c r="W70" s="7"/>
-      <c r="X70" s="7"/>
-      <c r="Y70" s="7"/>
-      <c r="Z70" s="7"/>
-      <c r="AA70" s="7"/>
-      <c r="AB70" s="23"/>
-      <c r="AC70" s="6"/>
-      <c r="AD70" s="7"/>
-      <c r="AE70" s="7"/>
-      <c r="AF70" s="7"/>
-      <c r="AG70" s="7"/>
-      <c r="AH70" s="7"/>
-      <c r="AI70" s="7"/>
+      <c r="I70" s="7">
+        <v>24.2</v>
+      </c>
+      <c r="J70" s="7">
+        <v>17.3</v>
+      </c>
+      <c r="K70" s="7">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="L70" s="7">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="M70" s="7">
+        <v>361</v>
+      </c>
+      <c r="N70" s="7">
+        <v>5.59</v>
+      </c>
+      <c r="O70" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P70" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="R70" s="7">
+        <v>0.77</v>
+      </c>
+      <c r="S70" s="7">
+        <v>0.61</v>
+      </c>
+      <c r="T70" s="7">
+        <v>7.2439999999999998</v>
+      </c>
+      <c r="U70" s="7">
+        <v>114.1</v>
+      </c>
+      <c r="V70" s="7">
+        <v>44.7</v>
+      </c>
+      <c r="W70" s="7">
+        <v>2.83</v>
+      </c>
+      <c r="X70" s="7">
+        <v>155.5</v>
+      </c>
+      <c r="Y70" s="7">
+        <v>48</v>
+      </c>
+      <c r="Z70" s="7">
+        <v>100.1</v>
+      </c>
+      <c r="AA70" s="7">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="AB70" s="23">
+        <v>7.2850000000000001</v>
+      </c>
+      <c r="AC70" s="6">
+        <v>302</v>
+      </c>
+      <c r="AD70" s="7">
+        <v>50.3</v>
+      </c>
+      <c r="AE70" s="7">
+        <v>7.3</v>
+      </c>
+      <c r="AF70" s="7">
+        <v>34</v>
+      </c>
+      <c r="AG70" s="7">
+        <v>21.77</v>
+      </c>
+      <c r="AH70" s="7">
+        <v>84.84</v>
+      </c>
+      <c r="AI70" s="7">
+        <v>22</v>
+      </c>
       <c r="AJ70" s="7"/>
-      <c r="AK70" s="7"/>
-      <c r="AL70" s="7"/>
-      <c r="AM70" s="7"/>
-      <c r="AN70" s="7"/>
+      <c r="AK70" s="7">
+        <v>294</v>
+      </c>
+      <c r="AL70" s="7">
+        <v>82</v>
+      </c>
+      <c r="AM70" s="7">
+        <f t="shared" si="47"/>
+        <v>7</v>
+      </c>
+      <c r="AN70" s="7">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="AO70" s="44">
         <v>15</v>
       </c>
@@ -14918,7 +15248,7 @@
       <c r="AW70" s="41"/>
       <c r="AX70" s="16">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>1.3927261200000002E-2</v>
       </c>
       <c r="AY70" s="17">
         <f t="shared" si="21"/>
@@ -14926,15 +15256,15 @@
       </c>
       <c r="AZ70" s="17">
         <f t="shared" si="33"/>
-        <v>1508</v>
-      </c>
-      <c r="BA70" s="18" t="e">
+        <v>2012.6100000000001</v>
+      </c>
+      <c r="BA70" s="18">
         <f t="shared" si="42"/>
-        <v>#N/A</v>
+        <v>0.1460789720810291</v>
       </c>
       <c r="BB70" s="18">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>0.17294117647058824</v>
       </c>
       <c r="BC70" s="18">
         <f t="shared" si="40"/>
